--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end (არ წაშალოთ!!!)\0. ready\ჟურნალი\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1022300-1295-47EC-A32E-EE2377F6569B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C31A5B-1418-4351-AFF7-1AAD97FB8409}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
   <si>
     <t xml:space="preserve">პროგრამა                     </t>
   </si>
@@ -409,6 +409,9 @@
   <si>
     <t>11.02-ში გავაცდინე 3სთ;</t>
   </si>
+  <si>
+    <t>სტატუსი შეუწყდა 09.07.2026-დან</t>
+  </si>
 </sst>
 </file>
 
@@ -760,7 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -807,6 +810,15 @@
     <xf numFmtId="164" fontId="8" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -862,6 +874,12 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -906,12 +924,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1155,97 +1167,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
-      <c r="F1" s="26">
+      <c r="C1" s="25"/>
+      <c r="D1" s="26"/>
+      <c r="F1" s="29">
         <v>4</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="28">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="31">
         <v>3</v>
       </c>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28">
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31">
         <v>4</v>
       </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29">
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="32">
         <v>4</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="29">
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="32">
         <v>4</v>
       </c>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="29">
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="32">
         <v>4</v>
       </c>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="56">
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="59">
         <v>2</v>
       </c>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="58">
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="61">
         <v>4</v>
       </c>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="58">
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="61">
         <v>4</v>
       </c>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="60"/>
-      <c r="AM1" s="58">
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="61">
         <v>2</v>
       </c>
-      <c r="AN1" s="60"/>
-      <c r="AO1" s="58">
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="61">
         <v>4</v>
       </c>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="59"/>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="58">
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="61">
         <v>5</v>
       </c>
-      <c r="AT1" s="59"/>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="60"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="63"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="58">
+      <c r="AY1" s="61">
         <v>5</v>
       </c>
-      <c r="AZ1" s="59"/>
-      <c r="BA1" s="59"/>
-      <c r="BB1" s="59"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="58">
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="61">
         <v>3</v>
       </c>
-      <c r="BE1" s="59"/>
-      <c r="BF1" s="60"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="63"/>
       <c r="BG1" s="4"/>
       <c r="BH1" s="4"/>
       <c r="BI1" s="4"/>
@@ -1335,1600 +1347,1600 @@
       <c r="EO1" s="4"/>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="32" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="P2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="Q2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="R2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="37" t="s">
+      <c r="S2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="T2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="35" t="s">
+      <c r="U2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="W2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="X2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Y2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="54" t="s">
+      <c r="AA2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="54" t="s">
+      <c r="AB2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="35">
+      <c r="AC2" s="38">
         <v>46199</v>
       </c>
-      <c r="AD2" s="35">
+      <c r="AD2" s="38">
         <v>46199</v>
       </c>
-      <c r="AE2" s="35">
+      <c r="AE2" s="38">
         <v>46202</v>
       </c>
-      <c r="AF2" s="35">
+      <c r="AF2" s="38">
         <v>46202</v>
       </c>
-      <c r="AG2" s="35">
+      <c r="AG2" s="38">
         <v>46202</v>
       </c>
-      <c r="AH2" s="35">
+      <c r="AH2" s="38">
         <v>46202</v>
       </c>
-      <c r="AI2" s="35">
+      <c r="AI2" s="38">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="35">
+      <c r="AJ2" s="38">
         <v>46205</v>
       </c>
-      <c r="AK2" s="35">
+      <c r="AK2" s="38">
         <v>46205</v>
       </c>
-      <c r="AL2" s="35">
+      <c r="AL2" s="38">
         <v>46205</v>
       </c>
-      <c r="AM2" s="35">
+      <c r="AM2" s="38">
         <v>46206</v>
       </c>
-      <c r="AN2" s="35">
+      <c r="AN2" s="38">
         <v>46206</v>
       </c>
-      <c r="AO2" s="35">
+      <c r="AO2" s="38">
         <v>46212</v>
       </c>
-      <c r="AP2" s="35">
+      <c r="AP2" s="38">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="35">
+      <c r="AQ2" s="38">
         <v>46212</v>
       </c>
-      <c r="AR2" s="35">
+      <c r="AR2" s="38">
         <v>46212</v>
       </c>
-      <c r="AS2" s="35">
+      <c r="AS2" s="38">
         <v>46213</v>
       </c>
-      <c r="AT2" s="35">
+      <c r="AT2" s="38">
         <v>46213</v>
       </c>
-      <c r="AU2" s="35">
+      <c r="AU2" s="38">
         <v>46213</v>
       </c>
-      <c r="AV2" s="35">
+      <c r="AV2" s="38">
         <v>46213</v>
       </c>
-      <c r="AW2" s="35">
+      <c r="AW2" s="38">
         <v>46213</v>
       </c>
-      <c r="AX2" s="35">
+      <c r="AX2" s="38">
         <v>46218</v>
       </c>
-      <c r="AY2" s="35">
+      <c r="AY2" s="38">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="35">
+      <c r="AZ2" s="38">
         <v>46219</v>
       </c>
-      <c r="BA2" s="35">
+      <c r="BA2" s="38">
         <v>46219</v>
       </c>
-      <c r="BB2" s="35">
+      <c r="BB2" s="38">
         <v>46219</v>
       </c>
-      <c r="BC2" s="35">
+      <c r="BC2" s="38">
         <v>46219</v>
       </c>
-      <c r="BD2" s="35">
+      <c r="BD2" s="38">
         <v>46220</v>
       </c>
-      <c r="BE2" s="35">
+      <c r="BE2" s="38">
         <v>46220</v>
       </c>
-      <c r="BF2" s="35">
+      <c r="BF2" s="38">
         <v>46220</v>
       </c>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
-      <c r="CI2" s="35"/>
-      <c r="CJ2" s="35"/>
-      <c r="CK2" s="35"/>
-      <c r="CL2" s="35"/>
-      <c r="CM2" s="35"/>
-      <c r="CN2" s="35"/>
-      <c r="CO2" s="35"/>
-      <c r="CP2" s="35"/>
-      <c r="CQ2" s="35"/>
-      <c r="CR2" s="35"/>
-      <c r="CS2" s="35"/>
-      <c r="CT2" s="35"/>
-      <c r="CU2" s="35"/>
-      <c r="CV2" s="35"/>
-      <c r="CW2" s="35"/>
-      <c r="CX2" s="35"/>
-      <c r="CY2" s="35"/>
-      <c r="CZ2" s="35"/>
-      <c r="DA2" s="35"/>
-      <c r="DB2" s="35"/>
-      <c r="DC2" s="35"/>
-      <c r="DD2" s="35"/>
-      <c r="DE2" s="35"/>
-      <c r="DF2" s="35"/>
-      <c r="DG2" s="35"/>
-      <c r="DH2" s="35"/>
-      <c r="DI2" s="35"/>
-      <c r="DJ2" s="35"/>
-      <c r="DK2" s="35"/>
-      <c r="DL2" s="35"/>
-      <c r="DM2" s="35"/>
-      <c r="DN2" s="35"/>
-      <c r="DO2" s="35"/>
-      <c r="DP2" s="35"/>
-      <c r="DQ2" s="35"/>
-      <c r="DR2" s="35"/>
-      <c r="DS2" s="35"/>
-      <c r="DT2" s="35"/>
-      <c r="DU2" s="35"/>
-      <c r="DV2" s="35"/>
-      <c r="DW2" s="35"/>
-      <c r="DX2" s="35"/>
-      <c r="DY2" s="35"/>
-      <c r="DZ2" s="35"/>
-      <c r="EA2" s="35"/>
-      <c r="EB2" s="35"/>
-      <c r="EC2" s="35"/>
-      <c r="ED2" s="35"/>
-      <c r="EE2" s="35"/>
-      <c r="EF2" s="35"/>
-      <c r="EG2" s="35"/>
-      <c r="EH2" s="35"/>
-      <c r="EI2" s="35"/>
-      <c r="EJ2" s="35"/>
-      <c r="EK2" s="35"/>
-      <c r="EL2" s="35"/>
-      <c r="EM2" s="35"/>
-      <c r="EN2" s="35"/>
-      <c r="EO2" s="35"/>
+      <c r="BG2" s="38"/>
+      <c r="BH2" s="38"/>
+      <c r="BI2" s="38"/>
+      <c r="BJ2" s="38"/>
+      <c r="BK2" s="38"/>
+      <c r="BL2" s="38"/>
+      <c r="BM2" s="38"/>
+      <c r="BN2" s="38"/>
+      <c r="BO2" s="38"/>
+      <c r="BP2" s="38"/>
+      <c r="BQ2" s="38"/>
+      <c r="BR2" s="38"/>
+      <c r="BS2" s="38"/>
+      <c r="BT2" s="38"/>
+      <c r="BU2" s="38"/>
+      <c r="BV2" s="38"/>
+      <c r="BW2" s="38"/>
+      <c r="BX2" s="38"/>
+      <c r="BY2" s="38"/>
+      <c r="BZ2" s="38"/>
+      <c r="CA2" s="38"/>
+      <c r="CB2" s="38"/>
+      <c r="CC2" s="38"/>
+      <c r="CD2" s="38"/>
+      <c r="CE2" s="38"/>
+      <c r="CF2" s="38"/>
+      <c r="CG2" s="38"/>
+      <c r="CH2" s="38"/>
+      <c r="CI2" s="38"/>
+      <c r="CJ2" s="38"/>
+      <c r="CK2" s="38"/>
+      <c r="CL2" s="38"/>
+      <c r="CM2" s="38"/>
+      <c r="CN2" s="38"/>
+      <c r="CO2" s="38"/>
+      <c r="CP2" s="38"/>
+      <c r="CQ2" s="38"/>
+      <c r="CR2" s="38"/>
+      <c r="CS2" s="38"/>
+      <c r="CT2" s="38"/>
+      <c r="CU2" s="38"/>
+      <c r="CV2" s="38"/>
+      <c r="CW2" s="38"/>
+      <c r="CX2" s="38"/>
+      <c r="CY2" s="38"/>
+      <c r="CZ2" s="38"/>
+      <c r="DA2" s="38"/>
+      <c r="DB2" s="38"/>
+      <c r="DC2" s="38"/>
+      <c r="DD2" s="38"/>
+      <c r="DE2" s="38"/>
+      <c r="DF2" s="38"/>
+      <c r="DG2" s="38"/>
+      <c r="DH2" s="38"/>
+      <c r="DI2" s="38"/>
+      <c r="DJ2" s="38"/>
+      <c r="DK2" s="38"/>
+      <c r="DL2" s="38"/>
+      <c r="DM2" s="38"/>
+      <c r="DN2" s="38"/>
+      <c r="DO2" s="38"/>
+      <c r="DP2" s="38"/>
+      <c r="DQ2" s="38"/>
+      <c r="DR2" s="38"/>
+      <c r="DS2" s="38"/>
+      <c r="DT2" s="38"/>
+      <c r="DU2" s="38"/>
+      <c r="DV2" s="38"/>
+      <c r="DW2" s="38"/>
+      <c r="DX2" s="38"/>
+      <c r="DY2" s="38"/>
+      <c r="DZ2" s="38"/>
+      <c r="EA2" s="38"/>
+      <c r="EB2" s="38"/>
+      <c r="EC2" s="38"/>
+      <c r="ED2" s="38"/>
+      <c r="EE2" s="38"/>
+      <c r="EF2" s="38"/>
+      <c r="EG2" s="38"/>
+      <c r="EH2" s="38"/>
+      <c r="EI2" s="38"/>
+      <c r="EJ2" s="38"/>
+      <c r="EK2" s="38"/>
+      <c r="EL2" s="38"/>
+      <c r="EM2" s="38"/>
+      <c r="EN2" s="38"/>
+      <c r="EO2" s="38"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="54"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
-      <c r="AP3" s="35"/>
-      <c r="AQ3" s="35"/>
-      <c r="AR3" s="35"/>
-      <c r="AS3" s="35"/>
-      <c r="AT3" s="35"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="35"/>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="35"/>
-      <c r="BE3" s="35"/>
-      <c r="BF3" s="35"/>
-      <c r="BG3" s="35"/>
-      <c r="BH3" s="35"/>
-      <c r="BI3" s="35"/>
-      <c r="BJ3" s="35"/>
-      <c r="BK3" s="35"/>
-      <c r="BL3" s="35"/>
-      <c r="BM3" s="35"/>
-      <c r="BN3" s="35"/>
-      <c r="BO3" s="35"/>
-      <c r="BP3" s="35"/>
-      <c r="BQ3" s="35"/>
-      <c r="BR3" s="35"/>
-      <c r="BS3" s="35"/>
-      <c r="BT3" s="35"/>
-      <c r="BU3" s="35"/>
-      <c r="BV3" s="35"/>
-      <c r="BW3" s="35"/>
-      <c r="BX3" s="35"/>
-      <c r="BY3" s="35"/>
-      <c r="BZ3" s="35"/>
-      <c r="CA3" s="35"/>
-      <c r="CB3" s="35"/>
-      <c r="CC3" s="35"/>
-      <c r="CD3" s="35"/>
-      <c r="CE3" s="35"/>
-      <c r="CF3" s="35"/>
-      <c r="CG3" s="35"/>
-      <c r="CH3" s="35"/>
-      <c r="CI3" s="35"/>
-      <c r="CJ3" s="35"/>
-      <c r="CK3" s="35"/>
-      <c r="CL3" s="35"/>
-      <c r="CM3" s="35"/>
-      <c r="CN3" s="35"/>
-      <c r="CO3" s="35"/>
-      <c r="CP3" s="35"/>
-      <c r="CQ3" s="35"/>
-      <c r="CR3" s="35"/>
-      <c r="CS3" s="35"/>
-      <c r="CT3" s="35"/>
-      <c r="CU3" s="35"/>
-      <c r="CV3" s="35"/>
-      <c r="CW3" s="35"/>
-      <c r="CX3" s="35"/>
-      <c r="CY3" s="35"/>
-      <c r="CZ3" s="35"/>
-      <c r="DA3" s="35"/>
-      <c r="DB3" s="35"/>
-      <c r="DC3" s="35"/>
-      <c r="DD3" s="35"/>
-      <c r="DE3" s="35"/>
-      <c r="DF3" s="35"/>
-      <c r="DG3" s="35"/>
-      <c r="DH3" s="35"/>
-      <c r="DI3" s="35"/>
-      <c r="DJ3" s="35"/>
-      <c r="DK3" s="35"/>
-      <c r="DL3" s="35"/>
-      <c r="DM3" s="35"/>
-      <c r="DN3" s="35"/>
-      <c r="DO3" s="35"/>
-      <c r="DP3" s="35"/>
-      <c r="DQ3" s="35"/>
-      <c r="DR3" s="35"/>
-      <c r="DS3" s="35"/>
-      <c r="DT3" s="35"/>
-      <c r="DU3" s="35"/>
-      <c r="DV3" s="35"/>
-      <c r="DW3" s="35"/>
-      <c r="DX3" s="35"/>
-      <c r="DY3" s="35"/>
-      <c r="DZ3" s="35"/>
-      <c r="EA3" s="35"/>
-      <c r="EB3" s="35"/>
-      <c r="EC3" s="35"/>
-      <c r="ED3" s="35"/>
-      <c r="EE3" s="35"/>
-      <c r="EF3" s="35"/>
-      <c r="EG3" s="35"/>
-      <c r="EH3" s="35"/>
-      <c r="EI3" s="35"/>
-      <c r="EJ3" s="35"/>
-      <c r="EK3" s="35"/>
-      <c r="EL3" s="35"/>
-      <c r="EM3" s="35"/>
-      <c r="EN3" s="35"/>
-      <c r="EO3" s="35"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38"/>
+      <c r="AN3" s="38"/>
+      <c r="AO3" s="38"/>
+      <c r="AP3" s="38"/>
+      <c r="AQ3" s="38"/>
+      <c r="AR3" s="38"/>
+      <c r="AS3" s="38"/>
+      <c r="AT3" s="38"/>
+      <c r="AU3" s="38"/>
+      <c r="AV3" s="38"/>
+      <c r="AW3" s="38"/>
+      <c r="AX3" s="38"/>
+      <c r="AY3" s="38"/>
+      <c r="AZ3" s="38"/>
+      <c r="BA3" s="38"/>
+      <c r="BB3" s="38"/>
+      <c r="BC3" s="38"/>
+      <c r="BD3" s="38"/>
+      <c r="BE3" s="38"/>
+      <c r="BF3" s="38"/>
+      <c r="BG3" s="38"/>
+      <c r="BH3" s="38"/>
+      <c r="BI3" s="38"/>
+      <c r="BJ3" s="38"/>
+      <c r="BK3" s="38"/>
+      <c r="BL3" s="38"/>
+      <c r="BM3" s="38"/>
+      <c r="BN3" s="38"/>
+      <c r="BO3" s="38"/>
+      <c r="BP3" s="38"/>
+      <c r="BQ3" s="38"/>
+      <c r="BR3" s="38"/>
+      <c r="BS3" s="38"/>
+      <c r="BT3" s="38"/>
+      <c r="BU3" s="38"/>
+      <c r="BV3" s="38"/>
+      <c r="BW3" s="38"/>
+      <c r="BX3" s="38"/>
+      <c r="BY3" s="38"/>
+      <c r="BZ3" s="38"/>
+      <c r="CA3" s="38"/>
+      <c r="CB3" s="38"/>
+      <c r="CC3" s="38"/>
+      <c r="CD3" s="38"/>
+      <c r="CE3" s="38"/>
+      <c r="CF3" s="38"/>
+      <c r="CG3" s="38"/>
+      <c r="CH3" s="38"/>
+      <c r="CI3" s="38"/>
+      <c r="CJ3" s="38"/>
+      <c r="CK3" s="38"/>
+      <c r="CL3" s="38"/>
+      <c r="CM3" s="38"/>
+      <c r="CN3" s="38"/>
+      <c r="CO3" s="38"/>
+      <c r="CP3" s="38"/>
+      <c r="CQ3" s="38"/>
+      <c r="CR3" s="38"/>
+      <c r="CS3" s="38"/>
+      <c r="CT3" s="38"/>
+      <c r="CU3" s="38"/>
+      <c r="CV3" s="38"/>
+      <c r="CW3" s="38"/>
+      <c r="CX3" s="38"/>
+      <c r="CY3" s="38"/>
+      <c r="CZ3" s="38"/>
+      <c r="DA3" s="38"/>
+      <c r="DB3" s="38"/>
+      <c r="DC3" s="38"/>
+      <c r="DD3" s="38"/>
+      <c r="DE3" s="38"/>
+      <c r="DF3" s="38"/>
+      <c r="DG3" s="38"/>
+      <c r="DH3" s="38"/>
+      <c r="DI3" s="38"/>
+      <c r="DJ3" s="38"/>
+      <c r="DK3" s="38"/>
+      <c r="DL3" s="38"/>
+      <c r="DM3" s="38"/>
+      <c r="DN3" s="38"/>
+      <c r="DO3" s="38"/>
+      <c r="DP3" s="38"/>
+      <c r="DQ3" s="38"/>
+      <c r="DR3" s="38"/>
+      <c r="DS3" s="38"/>
+      <c r="DT3" s="38"/>
+      <c r="DU3" s="38"/>
+      <c r="DV3" s="38"/>
+      <c r="DW3" s="38"/>
+      <c r="DX3" s="38"/>
+      <c r="DY3" s="38"/>
+      <c r="DZ3" s="38"/>
+      <c r="EA3" s="38"/>
+      <c r="EB3" s="38"/>
+      <c r="EC3" s="38"/>
+      <c r="ED3" s="38"/>
+      <c r="EE3" s="38"/>
+      <c r="EF3" s="38"/>
+      <c r="EG3" s="38"/>
+      <c r="EH3" s="38"/>
+      <c r="EI3" s="38"/>
+      <c r="EJ3" s="38"/>
+      <c r="EK3" s="38"/>
+      <c r="EL3" s="38"/>
+      <c r="EM3" s="38"/>
+      <c r="EN3" s="38"/>
+      <c r="EO3" s="38"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="35"/>
-      <c r="AI4" s="35"/>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="35"/>
-      <c r="AO4" s="35"/>
-      <c r="AP4" s="35"/>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="35"/>
-      <c r="AS4" s="35"/>
-      <c r="AT4" s="35"/>
-      <c r="AU4" s="35"/>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="35"/>
-      <c r="AY4" s="35"/>
-      <c r="AZ4" s="35"/>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-      <c r="BE4" s="35"/>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="35"/>
-      <c r="BI4" s="35"/>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="35"/>
-      <c r="BN4" s="35"/>
-      <c r="BO4" s="35"/>
-      <c r="BP4" s="35"/>
-      <c r="BQ4" s="35"/>
-      <c r="BR4" s="35"/>
-      <c r="BS4" s="35"/>
-      <c r="BT4" s="35"/>
-      <c r="BU4" s="35"/>
-      <c r="BV4" s="35"/>
-      <c r="BW4" s="35"/>
-      <c r="BX4" s="35"/>
-      <c r="BY4" s="35"/>
-      <c r="BZ4" s="35"/>
-      <c r="CA4" s="35"/>
-      <c r="CB4" s="35"/>
-      <c r="CC4" s="35"/>
-      <c r="CD4" s="35"/>
-      <c r="CE4" s="35"/>
-      <c r="CF4" s="35"/>
-      <c r="CG4" s="35"/>
-      <c r="CH4" s="35"/>
-      <c r="CI4" s="35"/>
-      <c r="CJ4" s="35"/>
-      <c r="CK4" s="35"/>
-      <c r="CL4" s="35"/>
-      <c r="CM4" s="35"/>
-      <c r="CN4" s="35"/>
-      <c r="CO4" s="35"/>
-      <c r="CP4" s="35"/>
-      <c r="CQ4" s="35"/>
-      <c r="CR4" s="35"/>
-      <c r="CS4" s="35"/>
-      <c r="CT4" s="35"/>
-      <c r="CU4" s="35"/>
-      <c r="CV4" s="35"/>
-      <c r="CW4" s="35"/>
-      <c r="CX4" s="35"/>
-      <c r="CY4" s="35"/>
-      <c r="CZ4" s="35"/>
-      <c r="DA4" s="35"/>
-      <c r="DB4" s="35"/>
-      <c r="DC4" s="35"/>
-      <c r="DD4" s="35"/>
-      <c r="DE4" s="35"/>
-      <c r="DF4" s="35"/>
-      <c r="DG4" s="35"/>
-      <c r="DH4" s="35"/>
-      <c r="DI4" s="35"/>
-      <c r="DJ4" s="35"/>
-      <c r="DK4" s="35"/>
-      <c r="DL4" s="35"/>
-      <c r="DM4" s="35"/>
-      <c r="DN4" s="35"/>
-      <c r="DO4" s="35"/>
-      <c r="DP4" s="35"/>
-      <c r="DQ4" s="35"/>
-      <c r="DR4" s="35"/>
-      <c r="DS4" s="35"/>
-      <c r="DT4" s="35"/>
-      <c r="DU4" s="35"/>
-      <c r="DV4" s="35"/>
-      <c r="DW4" s="35"/>
-      <c r="DX4" s="35"/>
-      <c r="DY4" s="35"/>
-      <c r="DZ4" s="35"/>
-      <c r="EA4" s="35"/>
-      <c r="EB4" s="35"/>
-      <c r="EC4" s="35"/>
-      <c r="ED4" s="35"/>
-      <c r="EE4" s="35"/>
-      <c r="EF4" s="35"/>
-      <c r="EG4" s="35"/>
-      <c r="EH4" s="35"/>
-      <c r="EI4" s="35"/>
-      <c r="EJ4" s="35"/>
-      <c r="EK4" s="35"/>
-      <c r="EL4" s="35"/>
-      <c r="EM4" s="35"/>
-      <c r="EN4" s="35"/>
-      <c r="EO4" s="35"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="38"/>
+      <c r="AL4" s="38"/>
+      <c r="AM4" s="38"/>
+      <c r="AN4" s="38"/>
+      <c r="AO4" s="38"/>
+      <c r="AP4" s="38"/>
+      <c r="AQ4" s="38"/>
+      <c r="AR4" s="38"/>
+      <c r="AS4" s="38"/>
+      <c r="AT4" s="38"/>
+      <c r="AU4" s="38"/>
+      <c r="AV4" s="38"/>
+      <c r="AW4" s="38"/>
+      <c r="AX4" s="38"/>
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="38"/>
+      <c r="BA4" s="38"/>
+      <c r="BB4" s="38"/>
+      <c r="BC4" s="38"/>
+      <c r="BD4" s="38"/>
+      <c r="BE4" s="38"/>
+      <c r="BF4" s="38"/>
+      <c r="BG4" s="38"/>
+      <c r="BH4" s="38"/>
+      <c r="BI4" s="38"/>
+      <c r="BJ4" s="38"/>
+      <c r="BK4" s="38"/>
+      <c r="BL4" s="38"/>
+      <c r="BM4" s="38"/>
+      <c r="BN4" s="38"/>
+      <c r="BO4" s="38"/>
+      <c r="BP4" s="38"/>
+      <c r="BQ4" s="38"/>
+      <c r="BR4" s="38"/>
+      <c r="BS4" s="38"/>
+      <c r="BT4" s="38"/>
+      <c r="BU4" s="38"/>
+      <c r="BV4" s="38"/>
+      <c r="BW4" s="38"/>
+      <c r="BX4" s="38"/>
+      <c r="BY4" s="38"/>
+      <c r="BZ4" s="38"/>
+      <c r="CA4" s="38"/>
+      <c r="CB4" s="38"/>
+      <c r="CC4" s="38"/>
+      <c r="CD4" s="38"/>
+      <c r="CE4" s="38"/>
+      <c r="CF4" s="38"/>
+      <c r="CG4" s="38"/>
+      <c r="CH4" s="38"/>
+      <c r="CI4" s="38"/>
+      <c r="CJ4" s="38"/>
+      <c r="CK4" s="38"/>
+      <c r="CL4" s="38"/>
+      <c r="CM4" s="38"/>
+      <c r="CN4" s="38"/>
+      <c r="CO4" s="38"/>
+      <c r="CP4" s="38"/>
+      <c r="CQ4" s="38"/>
+      <c r="CR4" s="38"/>
+      <c r="CS4" s="38"/>
+      <c r="CT4" s="38"/>
+      <c r="CU4" s="38"/>
+      <c r="CV4" s="38"/>
+      <c r="CW4" s="38"/>
+      <c r="CX4" s="38"/>
+      <c r="CY4" s="38"/>
+      <c r="CZ4" s="38"/>
+      <c r="DA4" s="38"/>
+      <c r="DB4" s="38"/>
+      <c r="DC4" s="38"/>
+      <c r="DD4" s="38"/>
+      <c r="DE4" s="38"/>
+      <c r="DF4" s="38"/>
+      <c r="DG4" s="38"/>
+      <c r="DH4" s="38"/>
+      <c r="DI4" s="38"/>
+      <c r="DJ4" s="38"/>
+      <c r="DK4" s="38"/>
+      <c r="DL4" s="38"/>
+      <c r="DM4" s="38"/>
+      <c r="DN4" s="38"/>
+      <c r="DO4" s="38"/>
+      <c r="DP4" s="38"/>
+      <c r="DQ4" s="38"/>
+      <c r="DR4" s="38"/>
+      <c r="DS4" s="38"/>
+      <c r="DT4" s="38"/>
+      <c r="DU4" s="38"/>
+      <c r="DV4" s="38"/>
+      <c r="DW4" s="38"/>
+      <c r="DX4" s="38"/>
+      <c r="DY4" s="38"/>
+      <c r="DZ4" s="38"/>
+      <c r="EA4" s="38"/>
+      <c r="EB4" s="38"/>
+      <c r="EC4" s="38"/>
+      <c r="ED4" s="38"/>
+      <c r="EE4" s="38"/>
+      <c r="EF4" s="38"/>
+      <c r="EG4" s="38"/>
+      <c r="EH4" s="38"/>
+      <c r="EI4" s="38"/>
+      <c r="EJ4" s="38"/>
+      <c r="EK4" s="38"/>
+      <c r="EL4" s="38"/>
+      <c r="EM4" s="38"/>
+      <c r="EN4" s="38"/>
+      <c r="EO4" s="38"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>110</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="54"/>
-      <c r="AC5" s="35"/>
-      <c r="AD5" s="35"/>
-      <c r="AE5" s="35"/>
-      <c r="AF5" s="35"/>
-      <c r="AG5" s="35"/>
-      <c r="AH5" s="35"/>
-      <c r="AI5" s="35"/>
-      <c r="AJ5" s="35"/>
-      <c r="AK5" s="35"/>
-      <c r="AL5" s="35"/>
-      <c r="AM5" s="35"/>
-      <c r="AN5" s="35"/>
-      <c r="AO5" s="35"/>
-      <c r="AP5" s="35"/>
-      <c r="AQ5" s="35"/>
-      <c r="AR5" s="35"/>
-      <c r="AS5" s="35"/>
-      <c r="AT5" s="35"/>
-      <c r="AU5" s="35"/>
-      <c r="AV5" s="35"/>
-      <c r="AW5" s="35"/>
-      <c r="AX5" s="35"/>
-      <c r="AY5" s="35"/>
-      <c r="AZ5" s="35"/>
-      <c r="BA5" s="35"/>
-      <c r="BB5" s="35"/>
-      <c r="BC5" s="35"/>
-      <c r="BD5" s="35"/>
-      <c r="BE5" s="35"/>
-      <c r="BF5" s="35"/>
-      <c r="BG5" s="35"/>
-      <c r="BH5" s="35"/>
-      <c r="BI5" s="35"/>
-      <c r="BJ5" s="35"/>
-      <c r="BK5" s="35"/>
-      <c r="BL5" s="35"/>
-      <c r="BM5" s="35"/>
-      <c r="BN5" s="35"/>
-      <c r="BO5" s="35"/>
-      <c r="BP5" s="35"/>
-      <c r="BQ5" s="35"/>
-      <c r="BR5" s="35"/>
-      <c r="BS5" s="35"/>
-      <c r="BT5" s="35"/>
-      <c r="BU5" s="35"/>
-      <c r="BV5" s="35"/>
-      <c r="BW5" s="35"/>
-      <c r="BX5" s="35"/>
-      <c r="BY5" s="35"/>
-      <c r="BZ5" s="35"/>
-      <c r="CA5" s="35"/>
-      <c r="CB5" s="35"/>
-      <c r="CC5" s="35"/>
-      <c r="CD5" s="35"/>
-      <c r="CE5" s="35"/>
-      <c r="CF5" s="35"/>
-      <c r="CG5" s="35"/>
-      <c r="CH5" s="35"/>
-      <c r="CI5" s="35"/>
-      <c r="CJ5" s="35"/>
-      <c r="CK5" s="35"/>
-      <c r="CL5" s="35"/>
-      <c r="CM5" s="35"/>
-      <c r="CN5" s="35"/>
-      <c r="CO5" s="35"/>
-      <c r="CP5" s="35"/>
-      <c r="CQ5" s="35"/>
-      <c r="CR5" s="35"/>
-      <c r="CS5" s="35"/>
-      <c r="CT5" s="35"/>
-      <c r="CU5" s="35"/>
-      <c r="CV5" s="35"/>
-      <c r="CW5" s="35"/>
-      <c r="CX5" s="35"/>
-      <c r="CY5" s="35"/>
-      <c r="CZ5" s="35"/>
-      <c r="DA5" s="35"/>
-      <c r="DB5" s="35"/>
-      <c r="DC5" s="35"/>
-      <c r="DD5" s="35"/>
-      <c r="DE5" s="35"/>
-      <c r="DF5" s="35"/>
-      <c r="DG5" s="35"/>
-      <c r="DH5" s="35"/>
-      <c r="DI5" s="35"/>
-      <c r="DJ5" s="35"/>
-      <c r="DK5" s="35"/>
-      <c r="DL5" s="35"/>
-      <c r="DM5" s="35"/>
-      <c r="DN5" s="35"/>
-      <c r="DO5" s="35"/>
-      <c r="DP5" s="35"/>
-      <c r="DQ5" s="35"/>
-      <c r="DR5" s="35"/>
-      <c r="DS5" s="35"/>
-      <c r="DT5" s="35"/>
-      <c r="DU5" s="35"/>
-      <c r="DV5" s="35"/>
-      <c r="DW5" s="35"/>
-      <c r="DX5" s="35"/>
-      <c r="DY5" s="35"/>
-      <c r="DZ5" s="35"/>
-      <c r="EA5" s="35"/>
-      <c r="EB5" s="35"/>
-      <c r="EC5" s="35"/>
-      <c r="ED5" s="35"/>
-      <c r="EE5" s="35"/>
-      <c r="EF5" s="35"/>
-      <c r="EG5" s="35"/>
-      <c r="EH5" s="35"/>
-      <c r="EI5" s="35"/>
-      <c r="EJ5" s="35"/>
-      <c r="EK5" s="35"/>
-      <c r="EL5" s="35"/>
-      <c r="EM5" s="35"/>
-      <c r="EN5" s="35"/>
-      <c r="EO5" s="35"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="38"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="42"/>
+      <c r="AB5" s="42"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="38"/>
+      <c r="AK5" s="38"/>
+      <c r="AL5" s="38"/>
+      <c r="AM5" s="38"/>
+      <c r="AN5" s="38"/>
+      <c r="AO5" s="38"/>
+      <c r="AP5" s="38"/>
+      <c r="AQ5" s="38"/>
+      <c r="AR5" s="38"/>
+      <c r="AS5" s="38"/>
+      <c r="AT5" s="38"/>
+      <c r="AU5" s="38"/>
+      <c r="AV5" s="38"/>
+      <c r="AW5" s="38"/>
+      <c r="AX5" s="38"/>
+      <c r="AY5" s="38"/>
+      <c r="AZ5" s="38"/>
+      <c r="BA5" s="38"/>
+      <c r="BB5" s="38"/>
+      <c r="BC5" s="38"/>
+      <c r="BD5" s="38"/>
+      <c r="BE5" s="38"/>
+      <c r="BF5" s="38"/>
+      <c r="BG5" s="38"/>
+      <c r="BH5" s="38"/>
+      <c r="BI5" s="38"/>
+      <c r="BJ5" s="38"/>
+      <c r="BK5" s="38"/>
+      <c r="BL5" s="38"/>
+      <c r="BM5" s="38"/>
+      <c r="BN5" s="38"/>
+      <c r="BO5" s="38"/>
+      <c r="BP5" s="38"/>
+      <c r="BQ5" s="38"/>
+      <c r="BR5" s="38"/>
+      <c r="BS5" s="38"/>
+      <c r="BT5" s="38"/>
+      <c r="BU5" s="38"/>
+      <c r="BV5" s="38"/>
+      <c r="BW5" s="38"/>
+      <c r="BX5" s="38"/>
+      <c r="BY5" s="38"/>
+      <c r="BZ5" s="38"/>
+      <c r="CA5" s="38"/>
+      <c r="CB5" s="38"/>
+      <c r="CC5" s="38"/>
+      <c r="CD5" s="38"/>
+      <c r="CE5" s="38"/>
+      <c r="CF5" s="38"/>
+      <c r="CG5" s="38"/>
+      <c r="CH5" s="38"/>
+      <c r="CI5" s="38"/>
+      <c r="CJ5" s="38"/>
+      <c r="CK5" s="38"/>
+      <c r="CL5" s="38"/>
+      <c r="CM5" s="38"/>
+      <c r="CN5" s="38"/>
+      <c r="CO5" s="38"/>
+      <c r="CP5" s="38"/>
+      <c r="CQ5" s="38"/>
+      <c r="CR5" s="38"/>
+      <c r="CS5" s="38"/>
+      <c r="CT5" s="38"/>
+      <c r="CU5" s="38"/>
+      <c r="CV5" s="38"/>
+      <c r="CW5" s="38"/>
+      <c r="CX5" s="38"/>
+      <c r="CY5" s="38"/>
+      <c r="CZ5" s="38"/>
+      <c r="DA5" s="38"/>
+      <c r="DB5" s="38"/>
+      <c r="DC5" s="38"/>
+      <c r="DD5" s="38"/>
+      <c r="DE5" s="38"/>
+      <c r="DF5" s="38"/>
+      <c r="DG5" s="38"/>
+      <c r="DH5" s="38"/>
+      <c r="DI5" s="38"/>
+      <c r="DJ5" s="38"/>
+      <c r="DK5" s="38"/>
+      <c r="DL5" s="38"/>
+      <c r="DM5" s="38"/>
+      <c r="DN5" s="38"/>
+      <c r="DO5" s="38"/>
+      <c r="DP5" s="38"/>
+      <c r="DQ5" s="38"/>
+      <c r="DR5" s="38"/>
+      <c r="DS5" s="38"/>
+      <c r="DT5" s="38"/>
+      <c r="DU5" s="38"/>
+      <c r="DV5" s="38"/>
+      <c r="DW5" s="38"/>
+      <c r="DX5" s="38"/>
+      <c r="DY5" s="38"/>
+      <c r="DZ5" s="38"/>
+      <c r="EA5" s="38"/>
+      <c r="EB5" s="38"/>
+      <c r="EC5" s="38"/>
+      <c r="ED5" s="38"/>
+      <c r="EE5" s="38"/>
+      <c r="EF5" s="38"/>
+      <c r="EG5" s="38"/>
+      <c r="EH5" s="38"/>
+      <c r="EI5" s="38"/>
+      <c r="EJ5" s="38"/>
+      <c r="EK5" s="38"/>
+      <c r="EL5" s="38"/>
+      <c r="EM5" s="38"/>
+      <c r="EN5" s="38"/>
+      <c r="EO5" s="38"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>10</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="54"/>
-      <c r="AB6" s="54"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="35"/>
-      <c r="AE6" s="35"/>
-      <c r="AF6" s="35"/>
-      <c r="AG6" s="35"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="35"/>
-      <c r="AJ6" s="35"/>
-      <c r="AK6" s="35"/>
-      <c r="AL6" s="35"/>
-      <c r="AM6" s="35"/>
-      <c r="AN6" s="35"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="35"/>
-      <c r="AQ6" s="35"/>
-      <c r="AR6" s="35"/>
-      <c r="AS6" s="35"/>
-      <c r="AT6" s="35"/>
-      <c r="AU6" s="35"/>
-      <c r="AV6" s="35"/>
-      <c r="AW6" s="35"/>
-      <c r="AX6" s="35"/>
-      <c r="AY6" s="35"/>
-      <c r="AZ6" s="35"/>
-      <c r="BA6" s="35"/>
-      <c r="BB6" s="35"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-      <c r="BE6" s="35"/>
-      <c r="BF6" s="35"/>
-      <c r="BG6" s="35"/>
-      <c r="BH6" s="35"/>
-      <c r="BI6" s="35"/>
-      <c r="BJ6" s="35"/>
-      <c r="BK6" s="35"/>
-      <c r="BL6" s="35"/>
-      <c r="BM6" s="35"/>
-      <c r="BN6" s="35"/>
-      <c r="BO6" s="35"/>
-      <c r="BP6" s="35"/>
-      <c r="BQ6" s="35"/>
-      <c r="BR6" s="35"/>
-      <c r="BS6" s="35"/>
-      <c r="BT6" s="35"/>
-      <c r="BU6" s="35"/>
-      <c r="BV6" s="35"/>
-      <c r="BW6" s="35"/>
-      <c r="BX6" s="35"/>
-      <c r="BY6" s="35"/>
-      <c r="BZ6" s="35"/>
-      <c r="CA6" s="35"/>
-      <c r="CB6" s="35"/>
-      <c r="CC6" s="35"/>
-      <c r="CD6" s="35"/>
-      <c r="CE6" s="35"/>
-      <c r="CF6" s="35"/>
-      <c r="CG6" s="35"/>
-      <c r="CH6" s="35"/>
-      <c r="CI6" s="35"/>
-      <c r="CJ6" s="35"/>
-      <c r="CK6" s="35"/>
-      <c r="CL6" s="35"/>
-      <c r="CM6" s="35"/>
-      <c r="CN6" s="35"/>
-      <c r="CO6" s="35"/>
-      <c r="CP6" s="35"/>
-      <c r="CQ6" s="35"/>
-      <c r="CR6" s="35"/>
-      <c r="CS6" s="35"/>
-      <c r="CT6" s="35"/>
-      <c r="CU6" s="35"/>
-      <c r="CV6" s="35"/>
-      <c r="CW6" s="35"/>
-      <c r="CX6" s="35"/>
-      <c r="CY6" s="35"/>
-      <c r="CZ6" s="35"/>
-      <c r="DA6" s="35"/>
-      <c r="DB6" s="35"/>
-      <c r="DC6" s="35"/>
-      <c r="DD6" s="35"/>
-      <c r="DE6" s="35"/>
-      <c r="DF6" s="35"/>
-      <c r="DG6" s="35"/>
-      <c r="DH6" s="35"/>
-      <c r="DI6" s="35"/>
-      <c r="DJ6" s="35"/>
-      <c r="DK6" s="35"/>
-      <c r="DL6" s="35"/>
-      <c r="DM6" s="35"/>
-      <c r="DN6" s="35"/>
-      <c r="DO6" s="35"/>
-      <c r="DP6" s="35"/>
-      <c r="DQ6" s="35"/>
-      <c r="DR6" s="35"/>
-      <c r="DS6" s="35"/>
-      <c r="DT6" s="35"/>
-      <c r="DU6" s="35"/>
-      <c r="DV6" s="35"/>
-      <c r="DW6" s="35"/>
-      <c r="DX6" s="35"/>
-      <c r="DY6" s="35"/>
-      <c r="DZ6" s="35"/>
-      <c r="EA6" s="35"/>
-      <c r="EB6" s="35"/>
-      <c r="EC6" s="35"/>
-      <c r="ED6" s="35"/>
-      <c r="EE6" s="35"/>
-      <c r="EF6" s="35"/>
-      <c r="EG6" s="35"/>
-      <c r="EH6" s="35"/>
-      <c r="EI6" s="35"/>
-      <c r="EJ6" s="35"/>
-      <c r="EK6" s="35"/>
-      <c r="EL6" s="35"/>
-      <c r="EM6" s="35"/>
-      <c r="EN6" s="35"/>
-      <c r="EO6" s="35"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="42"/>
+      <c r="AB6" s="42"/>
+      <c r="AC6" s="38"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="38"/>
+      <c r="AM6" s="38"/>
+      <c r="AN6" s="38"/>
+      <c r="AO6" s="38"/>
+      <c r="AP6" s="38"/>
+      <c r="AQ6" s="38"/>
+      <c r="AR6" s="38"/>
+      <c r="AS6" s="38"/>
+      <c r="AT6" s="38"/>
+      <c r="AU6" s="38"/>
+      <c r="AV6" s="38"/>
+      <c r="AW6" s="38"/>
+      <c r="AX6" s="38"/>
+      <c r="AY6" s="38"/>
+      <c r="AZ6" s="38"/>
+      <c r="BA6" s="38"/>
+      <c r="BB6" s="38"/>
+      <c r="BC6" s="38"/>
+      <c r="BD6" s="38"/>
+      <c r="BE6" s="38"/>
+      <c r="BF6" s="38"/>
+      <c r="BG6" s="38"/>
+      <c r="BH6" s="38"/>
+      <c r="BI6" s="38"/>
+      <c r="BJ6" s="38"/>
+      <c r="BK6" s="38"/>
+      <c r="BL6" s="38"/>
+      <c r="BM6" s="38"/>
+      <c r="BN6" s="38"/>
+      <c r="BO6" s="38"/>
+      <c r="BP6" s="38"/>
+      <c r="BQ6" s="38"/>
+      <c r="BR6" s="38"/>
+      <c r="BS6" s="38"/>
+      <c r="BT6" s="38"/>
+      <c r="BU6" s="38"/>
+      <c r="BV6" s="38"/>
+      <c r="BW6" s="38"/>
+      <c r="BX6" s="38"/>
+      <c r="BY6" s="38"/>
+      <c r="BZ6" s="38"/>
+      <c r="CA6" s="38"/>
+      <c r="CB6" s="38"/>
+      <c r="CC6" s="38"/>
+      <c r="CD6" s="38"/>
+      <c r="CE6" s="38"/>
+      <c r="CF6" s="38"/>
+      <c r="CG6" s="38"/>
+      <c r="CH6" s="38"/>
+      <c r="CI6" s="38"/>
+      <c r="CJ6" s="38"/>
+      <c r="CK6" s="38"/>
+      <c r="CL6" s="38"/>
+      <c r="CM6" s="38"/>
+      <c r="CN6" s="38"/>
+      <c r="CO6" s="38"/>
+      <c r="CP6" s="38"/>
+      <c r="CQ6" s="38"/>
+      <c r="CR6" s="38"/>
+      <c r="CS6" s="38"/>
+      <c r="CT6" s="38"/>
+      <c r="CU6" s="38"/>
+      <c r="CV6" s="38"/>
+      <c r="CW6" s="38"/>
+      <c r="CX6" s="38"/>
+      <c r="CY6" s="38"/>
+      <c r="CZ6" s="38"/>
+      <c r="DA6" s="38"/>
+      <c r="DB6" s="38"/>
+      <c r="DC6" s="38"/>
+      <c r="DD6" s="38"/>
+      <c r="DE6" s="38"/>
+      <c r="DF6" s="38"/>
+      <c r="DG6" s="38"/>
+      <c r="DH6" s="38"/>
+      <c r="DI6" s="38"/>
+      <c r="DJ6" s="38"/>
+      <c r="DK6" s="38"/>
+      <c r="DL6" s="38"/>
+      <c r="DM6" s="38"/>
+      <c r="DN6" s="38"/>
+      <c r="DO6" s="38"/>
+      <c r="DP6" s="38"/>
+      <c r="DQ6" s="38"/>
+      <c r="DR6" s="38"/>
+      <c r="DS6" s="38"/>
+      <c r="DT6" s="38"/>
+      <c r="DU6" s="38"/>
+      <c r="DV6" s="38"/>
+      <c r="DW6" s="38"/>
+      <c r="DX6" s="38"/>
+      <c r="DY6" s="38"/>
+      <c r="DZ6" s="38"/>
+      <c r="EA6" s="38"/>
+      <c r="EB6" s="38"/>
+      <c r="EC6" s="38"/>
+      <c r="ED6" s="38"/>
+      <c r="EE6" s="38"/>
+      <c r="EF6" s="38"/>
+      <c r="EG6" s="38"/>
+      <c r="EH6" s="38"/>
+      <c r="EI6" s="38"/>
+      <c r="EJ6" s="38"/>
+      <c r="EK6" s="38"/>
+      <c r="EL6" s="38"/>
+      <c r="EM6" s="38"/>
+      <c r="EN6" s="38"/>
+      <c r="EO6" s="38"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="43">
+      <c r="B7" s="50"/>
+      <c r="C7" s="48">
         <v>30</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="55"/>
-      <c r="AB7" s="55"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="36"/>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="36"/>
-      <c r="AH7" s="36"/>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="36"/>
-      <c r="AK7" s="36"/>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="36"/>
-      <c r="AN7" s="36"/>
-      <c r="AO7" s="36"/>
-      <c r="AP7" s="36"/>
-      <c r="AQ7" s="36"/>
-      <c r="AR7" s="36"/>
-      <c r="AS7" s="36"/>
-      <c r="AT7" s="36"/>
-      <c r="AU7" s="36"/>
-      <c r="AV7" s="36"/>
-      <c r="AW7" s="36"/>
-      <c r="AX7" s="36"/>
-      <c r="AY7" s="36"/>
-      <c r="AZ7" s="36"/>
-      <c r="BA7" s="36"/>
-      <c r="BB7" s="36"/>
-      <c r="BC7" s="36"/>
-      <c r="BD7" s="36"/>
-      <c r="BE7" s="36"/>
-      <c r="BF7" s="36"/>
-      <c r="BG7" s="36"/>
-      <c r="BH7" s="36"/>
-      <c r="BI7" s="36"/>
-      <c r="BJ7" s="36"/>
-      <c r="BK7" s="36"/>
-      <c r="BL7" s="36"/>
-      <c r="BM7" s="36"/>
-      <c r="BN7" s="36"/>
-      <c r="BO7" s="36"/>
-      <c r="BP7" s="36"/>
-      <c r="BQ7" s="36"/>
-      <c r="BR7" s="36"/>
-      <c r="BS7" s="36"/>
-      <c r="BT7" s="36"/>
-      <c r="BU7" s="36"/>
-      <c r="BV7" s="36"/>
-      <c r="BW7" s="36"/>
-      <c r="BX7" s="36"/>
-      <c r="BY7" s="36"/>
-      <c r="BZ7" s="36"/>
-      <c r="CA7" s="36"/>
-      <c r="CB7" s="36"/>
-      <c r="CC7" s="36"/>
-      <c r="CD7" s="36"/>
-      <c r="CE7" s="36"/>
-      <c r="CF7" s="36"/>
-      <c r="CG7" s="36"/>
-      <c r="CH7" s="36"/>
-      <c r="CI7" s="36"/>
-      <c r="CJ7" s="36"/>
-      <c r="CK7" s="36"/>
-      <c r="CL7" s="36"/>
-      <c r="CM7" s="36"/>
-      <c r="CN7" s="36"/>
-      <c r="CO7" s="36"/>
-      <c r="CP7" s="36"/>
-      <c r="CQ7" s="36"/>
-      <c r="CR7" s="36"/>
-      <c r="CS7" s="36"/>
-      <c r="CT7" s="36"/>
-      <c r="CU7" s="36"/>
-      <c r="CV7" s="36"/>
-      <c r="CW7" s="36"/>
-      <c r="CX7" s="36"/>
-      <c r="CY7" s="36"/>
-      <c r="CZ7" s="36"/>
-      <c r="DA7" s="36"/>
-      <c r="DB7" s="36"/>
-      <c r="DC7" s="36"/>
-      <c r="DD7" s="36"/>
-      <c r="DE7" s="36"/>
-      <c r="DF7" s="36"/>
-      <c r="DG7" s="36"/>
-      <c r="DH7" s="36"/>
-      <c r="DI7" s="36"/>
-      <c r="DJ7" s="36"/>
-      <c r="DK7" s="36"/>
-      <c r="DL7" s="36"/>
-      <c r="DM7" s="36"/>
-      <c r="DN7" s="36"/>
-      <c r="DO7" s="36"/>
-      <c r="DP7" s="36"/>
-      <c r="DQ7" s="36"/>
-      <c r="DR7" s="36"/>
-      <c r="DS7" s="36"/>
-      <c r="DT7" s="36"/>
-      <c r="DU7" s="36"/>
-      <c r="DV7" s="36"/>
-      <c r="DW7" s="36"/>
-      <c r="DX7" s="36"/>
-      <c r="DY7" s="36"/>
-      <c r="DZ7" s="36"/>
-      <c r="EA7" s="36"/>
-      <c r="EB7" s="36"/>
-      <c r="EC7" s="36"/>
-      <c r="ED7" s="36"/>
-      <c r="EE7" s="36"/>
-      <c r="EF7" s="36"/>
-      <c r="EG7" s="36"/>
-      <c r="EH7" s="36"/>
-      <c r="EI7" s="36"/>
-      <c r="EJ7" s="36"/>
-      <c r="EK7" s="36"/>
-      <c r="EL7" s="36"/>
-      <c r="EM7" s="36"/>
-      <c r="EN7" s="36"/>
-      <c r="EO7" s="36"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="43"/>
+      <c r="AB7" s="43"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="39"/>
+      <c r="AE7" s="39"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="39"/>
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="39"/>
+      <c r="AJ7" s="39"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="39"/>
+      <c r="AN7" s="39"/>
+      <c r="AO7" s="39"/>
+      <c r="AP7" s="39"/>
+      <c r="AQ7" s="39"/>
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="39"/>
+      <c r="AT7" s="39"/>
+      <c r="AU7" s="39"/>
+      <c r="AV7" s="39"/>
+      <c r="AW7" s="39"/>
+      <c r="AX7" s="39"/>
+      <c r="AY7" s="39"/>
+      <c r="AZ7" s="39"/>
+      <c r="BA7" s="39"/>
+      <c r="BB7" s="39"/>
+      <c r="BC7" s="39"/>
+      <c r="BD7" s="39"/>
+      <c r="BE7" s="39"/>
+      <c r="BF7" s="39"/>
+      <c r="BG7" s="39"/>
+      <c r="BH7" s="39"/>
+      <c r="BI7" s="39"/>
+      <c r="BJ7" s="39"/>
+      <c r="BK7" s="39"/>
+      <c r="BL7" s="39"/>
+      <c r="BM7" s="39"/>
+      <c r="BN7" s="39"/>
+      <c r="BO7" s="39"/>
+      <c r="BP7" s="39"/>
+      <c r="BQ7" s="39"/>
+      <c r="BR7" s="39"/>
+      <c r="BS7" s="39"/>
+      <c r="BT7" s="39"/>
+      <c r="BU7" s="39"/>
+      <c r="BV7" s="39"/>
+      <c r="BW7" s="39"/>
+      <c r="BX7" s="39"/>
+      <c r="BY7" s="39"/>
+      <c r="BZ7" s="39"/>
+      <c r="CA7" s="39"/>
+      <c r="CB7" s="39"/>
+      <c r="CC7" s="39"/>
+      <c r="CD7" s="39"/>
+      <c r="CE7" s="39"/>
+      <c r="CF7" s="39"/>
+      <c r="CG7" s="39"/>
+      <c r="CH7" s="39"/>
+      <c r="CI7" s="39"/>
+      <c r="CJ7" s="39"/>
+      <c r="CK7" s="39"/>
+      <c r="CL7" s="39"/>
+      <c r="CM7" s="39"/>
+      <c r="CN7" s="39"/>
+      <c r="CO7" s="39"/>
+      <c r="CP7" s="39"/>
+      <c r="CQ7" s="39"/>
+      <c r="CR7" s="39"/>
+      <c r="CS7" s="39"/>
+      <c r="CT7" s="39"/>
+      <c r="CU7" s="39"/>
+      <c r="CV7" s="39"/>
+      <c r="CW7" s="39"/>
+      <c r="CX7" s="39"/>
+      <c r="CY7" s="39"/>
+      <c r="CZ7" s="39"/>
+      <c r="DA7" s="39"/>
+      <c r="DB7" s="39"/>
+      <c r="DC7" s="39"/>
+      <c r="DD7" s="39"/>
+      <c r="DE7" s="39"/>
+      <c r="DF7" s="39"/>
+      <c r="DG7" s="39"/>
+      <c r="DH7" s="39"/>
+      <c r="DI7" s="39"/>
+      <c r="DJ7" s="39"/>
+      <c r="DK7" s="39"/>
+      <c r="DL7" s="39"/>
+      <c r="DM7" s="39"/>
+      <c r="DN7" s="39"/>
+      <c r="DO7" s="39"/>
+      <c r="DP7" s="39"/>
+      <c r="DQ7" s="39"/>
+      <c r="DR7" s="39"/>
+      <c r="DS7" s="39"/>
+      <c r="DT7" s="39"/>
+      <c r="DU7" s="39"/>
+      <c r="DV7" s="39"/>
+      <c r="DW7" s="39"/>
+      <c r="DX7" s="39"/>
+      <c r="DY7" s="39"/>
+      <c r="DZ7" s="39"/>
+      <c r="EA7" s="39"/>
+      <c r="EB7" s="39"/>
+      <c r="EC7" s="39"/>
+      <c r="ED7" s="39"/>
+      <c r="EE7" s="39"/>
+      <c r="EF7" s="39"/>
+      <c r="EG7" s="39"/>
+      <c r="EH7" s="39"/>
+      <c r="EI7" s="39"/>
+      <c r="EJ7" s="39"/>
+      <c r="EK7" s="39"/>
+      <c r="EL7" s="39"/>
+      <c r="EM7" s="39"/>
+      <c r="EN7" s="39"/>
+      <c r="EO7" s="39"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47">
+      <c r="B8" s="51"/>
+      <c r="C8" s="52">
         <v>150</v>
       </c>
-      <c r="D8" s="41"/>
+      <c r="D8" s="46"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="48">
+      <c r="F8" s="53">
         <v>1</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="53">
         <v>2</v>
       </c>
-      <c r="H8" s="48">
+      <c r="H8" s="53">
         <v>3</v>
       </c>
-      <c r="I8" s="48">
+      <c r="I8" s="53">
         <v>4</v>
       </c>
-      <c r="J8" s="48">
+      <c r="J8" s="53">
         <v>5</v>
       </c>
-      <c r="K8" s="48">
+      <c r="K8" s="53">
         <v>6</v>
       </c>
-      <c r="L8" s="48">
+      <c r="L8" s="53">
         <v>7</v>
       </c>
-      <c r="M8" s="48">
+      <c r="M8" s="53">
         <v>8</v>
       </c>
-      <c r="N8" s="48">
+      <c r="N8" s="53">
         <v>9</v>
       </c>
-      <c r="O8" s="48">
+      <c r="O8" s="53">
         <v>10</v>
       </c>
-      <c r="P8" s="48">
+      <c r="P8" s="53">
         <v>11</v>
       </c>
-      <c r="Q8" s="48">
+      <c r="Q8" s="53">
         <v>12</v>
       </c>
-      <c r="R8" s="48">
+      <c r="R8" s="53">
         <v>13</v>
       </c>
-      <c r="S8" s="48">
+      <c r="S8" s="53">
         <v>14</v>
       </c>
-      <c r="T8" s="48">
+      <c r="T8" s="53">
         <v>15</v>
       </c>
-      <c r="U8" s="48">
+      <c r="U8" s="53">
         <v>16</v>
       </c>
-      <c r="V8" s="48">
+      <c r="V8" s="53">
         <v>17</v>
       </c>
-      <c r="W8" s="48">
+      <c r="W8" s="53">
         <v>18</v>
       </c>
-      <c r="X8" s="48">
+      <c r="X8" s="53">
         <v>19</v>
       </c>
-      <c r="Y8" s="48">
+      <c r="Y8" s="53">
         <v>20</v>
       </c>
-      <c r="Z8" s="48">
+      <c r="Z8" s="53">
         <v>21</v>
       </c>
-      <c r="AA8" s="48">
+      <c r="AA8" s="53">
         <v>22</v>
       </c>
-      <c r="AB8" s="48">
+      <c r="AB8" s="53">
         <v>23</v>
       </c>
-      <c r="AC8" s="48">
+      <c r="AC8" s="53">
         <v>24</v>
       </c>
-      <c r="AD8" s="48">
+      <c r="AD8" s="53">
         <v>25</v>
       </c>
-      <c r="AE8" s="48">
+      <c r="AE8" s="53">
         <v>26</v>
       </c>
-      <c r="AF8" s="48">
+      <c r="AF8" s="53">
         <v>27</v>
       </c>
-      <c r="AG8" s="48">
+      <c r="AG8" s="53">
         <v>28</v>
       </c>
-      <c r="AH8" s="48">
+      <c r="AH8" s="53">
         <v>29</v>
       </c>
-      <c r="AI8" s="48">
+      <c r="AI8" s="53">
         <v>30</v>
       </c>
-      <c r="AJ8" s="48">
+      <c r="AJ8" s="53">
         <v>31</v>
       </c>
-      <c r="AK8" s="48">
+      <c r="AK8" s="53">
         <v>32</v>
       </c>
-      <c r="AL8" s="48">
+      <c r="AL8" s="53">
         <v>33</v>
       </c>
-      <c r="AM8" s="48">
+      <c r="AM8" s="53">
         <v>34</v>
       </c>
-      <c r="AN8" s="48">
+      <c r="AN8" s="53">
         <v>35</v>
       </c>
-      <c r="AO8" s="48">
+      <c r="AO8" s="53">
         <v>36</v>
       </c>
-      <c r="AP8" s="48">
+      <c r="AP8" s="53">
         <v>37</v>
       </c>
-      <c r="AQ8" s="48">
+      <c r="AQ8" s="53">
         <v>38</v>
       </c>
-      <c r="AR8" s="48">
+      <c r="AR8" s="53">
         <v>39</v>
       </c>
-      <c r="AS8" s="48">
+      <c r="AS8" s="53">
         <v>40</v>
       </c>
-      <c r="AT8" s="48">
+      <c r="AT8" s="53">
         <v>41</v>
       </c>
-      <c r="AU8" s="48">
+      <c r="AU8" s="53">
         <v>42</v>
       </c>
-      <c r="AV8" s="48">
+      <c r="AV8" s="53">
         <v>43</v>
       </c>
-      <c r="AW8" s="48">
+      <c r="AW8" s="53">
         <v>44</v>
       </c>
-      <c r="AX8" s="48">
+      <c r="AX8" s="53">
         <v>45</v>
       </c>
-      <c r="AY8" s="48">
+      <c r="AY8" s="53">
         <v>46</v>
       </c>
-      <c r="AZ8" s="48">
+      <c r="AZ8" s="53">
         <v>47</v>
       </c>
-      <c r="BA8" s="48">
+      <c r="BA8" s="53">
         <v>48</v>
       </c>
-      <c r="BB8" s="48">
+      <c r="BB8" s="53">
         <v>49</v>
       </c>
-      <c r="BC8" s="48">
+      <c r="BC8" s="53">
         <v>50</v>
       </c>
-      <c r="BD8" s="48">
+      <c r="BD8" s="53">
         <v>51</v>
       </c>
-      <c r="BE8" s="48">
+      <c r="BE8" s="53">
         <v>52</v>
       </c>
-      <c r="BF8" s="48">
+      <c r="BF8" s="53">
         <v>53</v>
       </c>
-      <c r="BG8" s="48">
+      <c r="BG8" s="53">
         <v>54</v>
       </c>
-      <c r="BH8" s="48">
+      <c r="BH8" s="53">
         <v>55</v>
       </c>
-      <c r="BI8" s="48">
+      <c r="BI8" s="53">
         <v>56</v>
       </c>
-      <c r="BJ8" s="48">
+      <c r="BJ8" s="53">
         <v>57</v>
       </c>
-      <c r="BK8" s="48">
+      <c r="BK8" s="53">
         <v>58</v>
       </c>
-      <c r="BL8" s="48">
+      <c r="BL8" s="53">
         <v>59</v>
       </c>
-      <c r="BM8" s="48">
+      <c r="BM8" s="53">
         <v>60</v>
       </c>
-      <c r="BN8" s="48">
+      <c r="BN8" s="53">
         <v>61</v>
       </c>
-      <c r="BO8" s="48">
+      <c r="BO8" s="53">
         <v>62</v>
       </c>
-      <c r="BP8" s="48">
+      <c r="BP8" s="53">
         <v>63</v>
       </c>
-      <c r="BQ8" s="48">
+      <c r="BQ8" s="53">
         <v>64</v>
       </c>
-      <c r="BR8" s="48">
+      <c r="BR8" s="53">
         <v>65</v>
       </c>
-      <c r="BS8" s="48">
+      <c r="BS8" s="53">
         <v>66</v>
       </c>
-      <c r="BT8" s="48">
+      <c r="BT8" s="53">
         <v>67</v>
       </c>
-      <c r="BU8" s="48">
+      <c r="BU8" s="53">
         <v>68</v>
       </c>
-      <c r="BV8" s="48">
+      <c r="BV8" s="53">
         <v>69</v>
       </c>
-      <c r="BW8" s="48">
+      <c r="BW8" s="53">
         <v>70</v>
       </c>
-      <c r="BX8" s="48">
+      <c r="BX8" s="53">
         <v>71</v>
       </c>
-      <c r="BY8" s="48">
+      <c r="BY8" s="53">
         <v>72</v>
       </c>
-      <c r="BZ8" s="48">
+      <c r="BZ8" s="53">
         <v>73</v>
       </c>
-      <c r="CA8" s="48">
+      <c r="CA8" s="53">
         <v>74</v>
       </c>
-      <c r="CB8" s="48">
+      <c r="CB8" s="53">
         <v>75</v>
       </c>
-      <c r="CC8" s="48">
+      <c r="CC8" s="53">
         <v>76</v>
       </c>
-      <c r="CD8" s="48">
+      <c r="CD8" s="53">
         <v>77</v>
       </c>
-      <c r="CE8" s="48">
+      <c r="CE8" s="53">
         <v>78</v>
       </c>
-      <c r="CF8" s="48">
+      <c r="CF8" s="53">
         <v>79</v>
       </c>
-      <c r="CG8" s="48">
+      <c r="CG8" s="53">
         <v>80</v>
       </c>
-      <c r="CH8" s="48">
+      <c r="CH8" s="53">
         <v>81</v>
       </c>
-      <c r="CI8" s="48">
+      <c r="CI8" s="53">
         <v>82</v>
       </c>
-      <c r="CJ8" s="48">
+      <c r="CJ8" s="53">
         <v>83</v>
       </c>
-      <c r="CK8" s="48">
+      <c r="CK8" s="53">
         <v>84</v>
       </c>
-      <c r="CL8" s="48">
+      <c r="CL8" s="53">
         <v>85</v>
       </c>
-      <c r="CM8" s="48">
+      <c r="CM8" s="53">
         <v>86</v>
       </c>
-      <c r="CN8" s="48">
+      <c r="CN8" s="53">
         <v>87</v>
       </c>
-      <c r="CO8" s="48">
+      <c r="CO8" s="53">
         <v>88</v>
       </c>
-      <c r="CP8" s="48">
+      <c r="CP8" s="53">
         <v>89</v>
       </c>
-      <c r="CQ8" s="48">
+      <c r="CQ8" s="53">
         <v>90</v>
       </c>
-      <c r="CR8" s="48">
+      <c r="CR8" s="53">
         <v>91</v>
       </c>
-      <c r="CS8" s="48">
+      <c r="CS8" s="53">
         <v>92</v>
       </c>
-      <c r="CT8" s="48">
+      <c r="CT8" s="53">
         <v>93</v>
       </c>
-      <c r="CU8" s="48">
+      <c r="CU8" s="53">
         <v>94</v>
       </c>
-      <c r="CV8" s="48">
+      <c r="CV8" s="53">
         <v>95</v>
       </c>
-      <c r="CW8" s="48">
+      <c r="CW8" s="53">
         <v>96</v>
       </c>
-      <c r="CX8" s="48">
+      <c r="CX8" s="53">
         <v>97</v>
       </c>
-      <c r="CY8" s="48">
+      <c r="CY8" s="53">
         <v>98</v>
       </c>
-      <c r="CZ8" s="48">
+      <c r="CZ8" s="53">
         <v>99</v>
       </c>
-      <c r="DA8" s="48">
+      <c r="DA8" s="53">
         <v>100</v>
       </c>
-      <c r="DB8" s="48">
+      <c r="DB8" s="53">
         <v>101</v>
       </c>
-      <c r="DC8" s="48">
+      <c r="DC8" s="53">
         <v>102</v>
       </c>
-      <c r="DD8" s="48">
+      <c r="DD8" s="53">
         <v>103</v>
       </c>
-      <c r="DE8" s="48">
+      <c r="DE8" s="53">
         <v>104</v>
       </c>
-      <c r="DF8" s="48">
+      <c r="DF8" s="53">
         <v>105</v>
       </c>
-      <c r="DG8" s="48">
+      <c r="DG8" s="53">
         <v>106</v>
       </c>
-      <c r="DH8" s="48">
+      <c r="DH8" s="53">
         <v>107</v>
       </c>
-      <c r="DI8" s="48">
+      <c r="DI8" s="53">
         <v>108</v>
       </c>
-      <c r="DJ8" s="48">
+      <c r="DJ8" s="53">
         <v>109</v>
       </c>
-      <c r="DK8" s="48">
+      <c r="DK8" s="53">
         <v>110</v>
       </c>
-      <c r="DL8" s="48">
+      <c r="DL8" s="53">
         <v>111</v>
       </c>
-      <c r="DM8" s="48">
+      <c r="DM8" s="53">
         <v>112</v>
       </c>
-      <c r="DN8" s="48">
+      <c r="DN8" s="53">
         <v>113</v>
       </c>
-      <c r="DO8" s="48">
+      <c r="DO8" s="53">
         <v>114</v>
       </c>
-      <c r="DP8" s="48">
+      <c r="DP8" s="53">
         <v>115</v>
       </c>
-      <c r="DQ8" s="48">
+      <c r="DQ8" s="53">
         <v>116</v>
       </c>
-      <c r="DR8" s="48">
+      <c r="DR8" s="53">
         <v>117</v>
       </c>
-      <c r="DS8" s="48">
+      <c r="DS8" s="53">
         <v>118</v>
       </c>
-      <c r="DT8" s="48">
+      <c r="DT8" s="53">
         <v>119</v>
       </c>
-      <c r="DU8" s="48">
+      <c r="DU8" s="53">
         <v>120</v>
       </c>
-      <c r="DV8" s="48">
+      <c r="DV8" s="53">
         <v>121</v>
       </c>
-      <c r="DW8" s="48">
+      <c r="DW8" s="53">
         <v>122</v>
       </c>
-      <c r="DX8" s="48">
+      <c r="DX8" s="53">
         <v>123</v>
       </c>
-      <c r="DY8" s="48">
+      <c r="DY8" s="53">
         <v>124</v>
       </c>
-      <c r="DZ8" s="48">
+      <c r="DZ8" s="53">
         <v>125</v>
       </c>
-      <c r="EA8" s="48">
+      <c r="EA8" s="53">
         <v>126</v>
       </c>
-      <c r="EB8" s="48">
+      <c r="EB8" s="53">
         <v>127</v>
       </c>
-      <c r="EC8" s="48">
+      <c r="EC8" s="53">
         <v>128</v>
       </c>
-      <c r="ED8" s="48">
+      <c r="ED8" s="53">
         <v>129</v>
       </c>
-      <c r="EE8" s="48">
+      <c r="EE8" s="53">
         <v>130</v>
       </c>
-      <c r="EF8" s="48">
+      <c r="EF8" s="53">
         <v>131</v>
       </c>
-      <c r="EG8" s="48">
+      <c r="EG8" s="53">
         <v>132</v>
       </c>
-      <c r="EH8" s="48">
+      <c r="EH8" s="53">
         <v>133</v>
       </c>
-      <c r="EI8" s="48">
+      <c r="EI8" s="53">
         <v>134</v>
       </c>
-      <c r="EJ8" s="48">
+      <c r="EJ8" s="53">
         <v>135</v>
       </c>
-      <c r="EK8" s="48">
+      <c r="EK8" s="53">
         <v>136</v>
       </c>
-      <c r="EL8" s="48">
+      <c r="EL8" s="53">
         <v>137</v>
       </c>
-      <c r="EM8" s="48">
+      <c r="EM8" s="53">
         <v>138</v>
       </c>
-      <c r="EN8" s="48">
+      <c r="EN8" s="53">
         <v>139</v>
       </c>
-      <c r="EO8" s="48">
+      <c r="EO8" s="53">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="49"/>
-      <c r="AN9" s="49"/>
-      <c r="AO9" s="49"/>
-      <c r="AP9" s="49"/>
-      <c r="AQ9" s="49"/>
-      <c r="AR9" s="49"/>
-      <c r="AS9" s="49"/>
-      <c r="AT9" s="49"/>
-      <c r="AU9" s="49"/>
-      <c r="AV9" s="49"/>
-      <c r="AW9" s="49"/>
-      <c r="AX9" s="49"/>
-      <c r="AY9" s="49"/>
-      <c r="AZ9" s="49"/>
-      <c r="BA9" s="49"/>
-      <c r="BB9" s="49"/>
-      <c r="BC9" s="49"/>
-      <c r="BD9" s="49"/>
-      <c r="BE9" s="49"/>
-      <c r="BF9" s="49"/>
-      <c r="BG9" s="49"/>
-      <c r="BH9" s="49"/>
-      <c r="BI9" s="49"/>
-      <c r="BJ9" s="49"/>
-      <c r="BK9" s="49"/>
-      <c r="BL9" s="49"/>
-      <c r="BM9" s="49"/>
-      <c r="BN9" s="49"/>
-      <c r="BO9" s="49"/>
-      <c r="BP9" s="49"/>
-      <c r="BQ9" s="49"/>
-      <c r="BR9" s="49"/>
-      <c r="BS9" s="49"/>
-      <c r="BT9" s="49"/>
-      <c r="BU9" s="49"/>
-      <c r="BV9" s="49"/>
-      <c r="BW9" s="49"/>
-      <c r="BX9" s="49"/>
-      <c r="BY9" s="49"/>
-      <c r="BZ9" s="49"/>
-      <c r="CA9" s="49"/>
-      <c r="CB9" s="49"/>
-      <c r="CC9" s="49"/>
-      <c r="CD9" s="49"/>
-      <c r="CE9" s="49"/>
-      <c r="CF9" s="49"/>
-      <c r="CG9" s="49"/>
-      <c r="CH9" s="49"/>
-      <c r="CI9" s="49"/>
-      <c r="CJ9" s="49"/>
-      <c r="CK9" s="49"/>
-      <c r="CL9" s="49"/>
-      <c r="CM9" s="49"/>
-      <c r="CN9" s="49"/>
-      <c r="CO9" s="49"/>
-      <c r="CP9" s="49"/>
-      <c r="CQ9" s="49"/>
-      <c r="CR9" s="49"/>
-      <c r="CS9" s="49"/>
-      <c r="CT9" s="49"/>
-      <c r="CU9" s="49"/>
-      <c r="CV9" s="49"/>
-      <c r="CW9" s="49"/>
-      <c r="CX9" s="49"/>
-      <c r="CY9" s="49"/>
-      <c r="CZ9" s="49"/>
-      <c r="DA9" s="49"/>
-      <c r="DB9" s="49"/>
-      <c r="DC9" s="49"/>
-      <c r="DD9" s="49"/>
-      <c r="DE9" s="49"/>
-      <c r="DF9" s="49"/>
-      <c r="DG9" s="49"/>
-      <c r="DH9" s="49"/>
-      <c r="DI9" s="49"/>
-      <c r="DJ9" s="49"/>
-      <c r="DK9" s="49"/>
-      <c r="DL9" s="49"/>
-      <c r="DM9" s="49"/>
-      <c r="DN9" s="49"/>
-      <c r="DO9" s="49"/>
-      <c r="DP9" s="49"/>
-      <c r="DQ9" s="49"/>
-      <c r="DR9" s="49"/>
-      <c r="DS9" s="49"/>
-      <c r="DT9" s="49"/>
-      <c r="DU9" s="49"/>
-      <c r="DV9" s="49"/>
-      <c r="DW9" s="49"/>
-      <c r="DX9" s="49"/>
-      <c r="DY9" s="49"/>
-      <c r="DZ9" s="49"/>
-      <c r="EA9" s="49"/>
-      <c r="EB9" s="49"/>
-      <c r="EC9" s="49"/>
-      <c r="ED9" s="49"/>
-      <c r="EE9" s="49"/>
-      <c r="EF9" s="49"/>
-      <c r="EG9" s="49"/>
-      <c r="EH9" s="49"/>
-      <c r="EI9" s="49"/>
-      <c r="EJ9" s="49"/>
-      <c r="EK9" s="49"/>
-      <c r="EL9" s="49"/>
-      <c r="EM9" s="49"/>
-      <c r="EN9" s="49"/>
-      <c r="EO9" s="49"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="54"/>
+      <c r="AH9" s="54"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="54"/>
+      <c r="AL9" s="54"/>
+      <c r="AM9" s="54"/>
+      <c r="AN9" s="54"/>
+      <c r="AO9" s="54"/>
+      <c r="AP9" s="54"/>
+      <c r="AQ9" s="54"/>
+      <c r="AR9" s="54"/>
+      <c r="AS9" s="54"/>
+      <c r="AT9" s="54"/>
+      <c r="AU9" s="54"/>
+      <c r="AV9" s="54"/>
+      <c r="AW9" s="54"/>
+      <c r="AX9" s="54"/>
+      <c r="AY9" s="54"/>
+      <c r="AZ9" s="54"/>
+      <c r="BA9" s="54"/>
+      <c r="BB9" s="54"/>
+      <c r="BC9" s="54"/>
+      <c r="BD9" s="54"/>
+      <c r="BE9" s="54"/>
+      <c r="BF9" s="54"/>
+      <c r="BG9" s="54"/>
+      <c r="BH9" s="54"/>
+      <c r="BI9" s="54"/>
+      <c r="BJ9" s="54"/>
+      <c r="BK9" s="54"/>
+      <c r="BL9" s="54"/>
+      <c r="BM9" s="54"/>
+      <c r="BN9" s="54"/>
+      <c r="BO9" s="54"/>
+      <c r="BP9" s="54"/>
+      <c r="BQ9" s="54"/>
+      <c r="BR9" s="54"/>
+      <c r="BS9" s="54"/>
+      <c r="BT9" s="54"/>
+      <c r="BU9" s="54"/>
+      <c r="BV9" s="54"/>
+      <c r="BW9" s="54"/>
+      <c r="BX9" s="54"/>
+      <c r="BY9" s="54"/>
+      <c r="BZ9" s="54"/>
+      <c r="CA9" s="54"/>
+      <c r="CB9" s="54"/>
+      <c r="CC9" s="54"/>
+      <c r="CD9" s="54"/>
+      <c r="CE9" s="54"/>
+      <c r="CF9" s="54"/>
+      <c r="CG9" s="54"/>
+      <c r="CH9" s="54"/>
+      <c r="CI9" s="54"/>
+      <c r="CJ9" s="54"/>
+      <c r="CK9" s="54"/>
+      <c r="CL9" s="54"/>
+      <c r="CM9" s="54"/>
+      <c r="CN9" s="54"/>
+      <c r="CO9" s="54"/>
+      <c r="CP9" s="54"/>
+      <c r="CQ9" s="54"/>
+      <c r="CR9" s="54"/>
+      <c r="CS9" s="54"/>
+      <c r="CT9" s="54"/>
+      <c r="CU9" s="54"/>
+      <c r="CV9" s="54"/>
+      <c r="CW9" s="54"/>
+      <c r="CX9" s="54"/>
+      <c r="CY9" s="54"/>
+      <c r="CZ9" s="54"/>
+      <c r="DA9" s="54"/>
+      <c r="DB9" s="54"/>
+      <c r="DC9" s="54"/>
+      <c r="DD9" s="54"/>
+      <c r="DE9" s="54"/>
+      <c r="DF9" s="54"/>
+      <c r="DG9" s="54"/>
+      <c r="DH9" s="54"/>
+      <c r="DI9" s="54"/>
+      <c r="DJ9" s="54"/>
+      <c r="DK9" s="54"/>
+      <c r="DL9" s="54"/>
+      <c r="DM9" s="54"/>
+      <c r="DN9" s="54"/>
+      <c r="DO9" s="54"/>
+      <c r="DP9" s="54"/>
+      <c r="DQ9" s="54"/>
+      <c r="DR9" s="54"/>
+      <c r="DS9" s="54"/>
+      <c r="DT9" s="54"/>
+      <c r="DU9" s="54"/>
+      <c r="DV9" s="54"/>
+      <c r="DW9" s="54"/>
+      <c r="DX9" s="54"/>
+      <c r="DY9" s="54"/>
+      <c r="DZ9" s="54"/>
+      <c r="EA9" s="54"/>
+      <c r="EB9" s="54"/>
+      <c r="EC9" s="54"/>
+      <c r="ED9" s="54"/>
+      <c r="EE9" s="54"/>
+      <c r="EF9" s="54"/>
+      <c r="EG9" s="54"/>
+      <c r="EH9" s="54"/>
+      <c r="EI9" s="54"/>
+      <c r="EJ9" s="54"/>
+      <c r="EK9" s="54"/>
+      <c r="EL9" s="54"/>
+      <c r="EM9" s="54"/>
+      <c r="EN9" s="54"/>
+      <c r="EO9" s="54"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="10"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
@@ -4095,7 +4107,7 @@
       </c>
       <c r="D17" s="15">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="12">
@@ -4157,123 +4169,149 @@
       <c r="AB17" s="12">
         <v>0</v>
       </c>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-      <c r="AS17" s="12"/>
-      <c r="AT17" s="12"/>
-      <c r="AU17" s="12"/>
-      <c r="AV17" s="12"/>
-      <c r="AW17" s="12"/>
-      <c r="AX17" s="12"/>
-      <c r="AY17" s="12"/>
-      <c r="AZ17" s="12"/>
-      <c r="BA17" s="12"/>
-      <c r="BB17" s="12"/>
-      <c r="BC17" s="12"/>
-      <c r="BD17" s="12"/>
-      <c r="BE17" s="12"/>
-      <c r="BF17" s="12"/>
-      <c r="BG17" s="12"/>
-      <c r="BH17" s="12"/>
-      <c r="BI17" s="12"/>
-      <c r="BJ17" s="12"/>
-      <c r="BK17" s="12"/>
-      <c r="BL17" s="12"/>
-      <c r="BM17" s="12"/>
-      <c r="BN17" s="12"/>
-      <c r="BO17" s="12"/>
-      <c r="BP17" s="12"/>
-      <c r="BQ17" s="12"/>
-      <c r="BR17" s="12"/>
-      <c r="BS17" s="12"/>
-      <c r="BT17" s="12"/>
-      <c r="BU17" s="12"/>
-      <c r="BV17" s="12"/>
-      <c r="BW17" s="12"/>
-      <c r="BX17" s="12"/>
-      <c r="BY17" s="12"/>
-      <c r="BZ17" s="12"/>
-      <c r="CA17" s="12"/>
-      <c r="CB17" s="12"/>
-      <c r="CC17" s="12"/>
-      <c r="CD17" s="12"/>
-      <c r="CE17" s="12"/>
-      <c r="CF17" s="12"/>
-      <c r="CG17" s="12"/>
-      <c r="CH17" s="12"/>
-      <c r="CI17" s="12"/>
-      <c r="CJ17" s="12"/>
-      <c r="CK17" s="12"/>
-      <c r="CL17" s="12"/>
-      <c r="CM17" s="12"/>
-      <c r="CN17" s="12"/>
-      <c r="CO17" s="12"/>
-      <c r="CP17" s="12"/>
-      <c r="CQ17" s="12"/>
-      <c r="CR17" s="12"/>
-      <c r="CS17" s="12"/>
-      <c r="CT17" s="12"/>
-      <c r="CU17" s="12"/>
-      <c r="CV17" s="12"/>
-      <c r="CW17" s="12"/>
-      <c r="CX17" s="12"/>
-      <c r="CY17" s="12"/>
-      <c r="CZ17" s="12"/>
-      <c r="DA17" s="12"/>
-      <c r="DB17" s="12"/>
-      <c r="DC17" s="12"/>
-      <c r="DD17" s="12"/>
-      <c r="DE17" s="12"/>
-      <c r="DF17" s="12"/>
-      <c r="DG17" s="12"/>
-      <c r="DH17" s="12"/>
-      <c r="DI17" s="12"/>
-      <c r="DJ17" s="12"/>
-      <c r="DK17" s="12"/>
-      <c r="DL17" s="12"/>
-      <c r="DM17" s="12"/>
-      <c r="DN17" s="12"/>
-      <c r="DO17" s="12"/>
-      <c r="DP17" s="12"/>
-      <c r="DQ17" s="12"/>
-      <c r="DR17" s="12"/>
-      <c r="DS17" s="12"/>
-      <c r="DT17" s="12"/>
-      <c r="DU17" s="12"/>
-      <c r="DV17" s="12"/>
-      <c r="DW17" s="12"/>
-      <c r="DX17" s="12"/>
-      <c r="DY17" s="12"/>
-      <c r="DZ17" s="12"/>
-      <c r="EA17" s="12"/>
-      <c r="EB17" s="12"/>
-      <c r="EC17" s="12"/>
-      <c r="ED17" s="12"/>
-      <c r="EE17" s="12"/>
-      <c r="EF17" s="12"/>
-      <c r="EG17" s="12"/>
-      <c r="EH17" s="12"/>
-      <c r="EI17" s="12"/>
-      <c r="EJ17" s="12"/>
-      <c r="EK17" s="12"/>
-      <c r="EL17" s="12"/>
-      <c r="EM17" s="12"/>
-      <c r="EN17" s="12"/>
-      <c r="EO17" s="12"/>
+      <c r="AC17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="22"/>
+      <c r="AR17" s="22"/>
+      <c r="AS17" s="22"/>
+      <c r="AT17" s="22"/>
+      <c r="AU17" s="22"/>
+      <c r="AV17" s="22"/>
+      <c r="AW17" s="22"/>
+      <c r="AX17" s="22"/>
+      <c r="AY17" s="22"/>
+      <c r="AZ17" s="22"/>
+      <c r="BA17" s="22"/>
+      <c r="BB17" s="22"/>
+      <c r="BC17" s="22"/>
+      <c r="BD17" s="22"/>
+      <c r="BE17" s="22"/>
+      <c r="BF17" s="22"/>
+      <c r="BG17" s="22"/>
+      <c r="BH17" s="22"/>
+      <c r="BI17" s="22"/>
+      <c r="BJ17" s="22"/>
+      <c r="BK17" s="22"/>
+      <c r="BL17" s="22"/>
+      <c r="BM17" s="22"/>
+      <c r="BN17" s="22"/>
+      <c r="BO17" s="22"/>
+      <c r="BP17" s="22"/>
+      <c r="BQ17" s="22"/>
+      <c r="BR17" s="22"/>
+      <c r="BS17" s="22"/>
+      <c r="BT17" s="22"/>
+      <c r="BU17" s="22"/>
+      <c r="BV17" s="22"/>
+      <c r="BW17" s="22"/>
+      <c r="BX17" s="22"/>
+      <c r="BY17" s="22"/>
+      <c r="BZ17" s="22"/>
+      <c r="CA17" s="22"/>
+      <c r="CB17" s="22"/>
+      <c r="CC17" s="22"/>
+      <c r="CD17" s="22"/>
+      <c r="CE17" s="22"/>
+      <c r="CF17" s="22"/>
+      <c r="CG17" s="22"/>
+      <c r="CH17" s="22"/>
+      <c r="CI17" s="22"/>
+      <c r="CJ17" s="22"/>
+      <c r="CK17" s="22"/>
+      <c r="CL17" s="22"/>
+      <c r="CM17" s="22"/>
+      <c r="CN17" s="22"/>
+      <c r="CO17" s="22"/>
+      <c r="CP17" s="22"/>
+      <c r="CQ17" s="22"/>
+      <c r="CR17" s="22"/>
+      <c r="CS17" s="22"/>
+      <c r="CT17" s="22"/>
+      <c r="CU17" s="22"/>
+      <c r="CV17" s="22"/>
+      <c r="CW17" s="22"/>
+      <c r="CX17" s="22"/>
+      <c r="CY17" s="22"/>
+      <c r="CZ17" s="22"/>
+      <c r="DA17" s="22"/>
+      <c r="DB17" s="22"/>
+      <c r="DC17" s="22"/>
+      <c r="DD17" s="22"/>
+      <c r="DE17" s="22"/>
+      <c r="DF17" s="22"/>
+      <c r="DG17" s="22"/>
+      <c r="DH17" s="22"/>
+      <c r="DI17" s="22"/>
+      <c r="DJ17" s="22"/>
+      <c r="DK17" s="22"/>
+      <c r="DL17" s="22"/>
+      <c r="DM17" s="22"/>
+      <c r="DN17" s="22"/>
+      <c r="DO17" s="22"/>
+      <c r="DP17" s="22"/>
+      <c r="DQ17" s="22"/>
+      <c r="DR17" s="22"/>
+      <c r="DS17" s="22"/>
+      <c r="DT17" s="22"/>
+      <c r="DU17" s="22"/>
+      <c r="DV17" s="22"/>
+      <c r="DW17" s="22"/>
+      <c r="DX17" s="22"/>
+      <c r="DY17" s="22"/>
+      <c r="DZ17" s="22"/>
+      <c r="EA17" s="22"/>
+      <c r="EB17" s="22"/>
+      <c r="EC17" s="22"/>
+      <c r="ED17" s="22"/>
+      <c r="EE17" s="22"/>
+      <c r="EF17" s="22"/>
+      <c r="EG17" s="22"/>
+      <c r="EH17" s="22"/>
+      <c r="EI17" s="22"/>
+      <c r="EJ17" s="22"/>
+      <c r="EK17" s="22"/>
+      <c r="EL17" s="22"/>
+      <c r="EM17" s="22"/>
+      <c r="EN17" s="22"/>
+      <c r="EO17" s="23"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
@@ -4763,7 +4801,7 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="12"/>
@@ -4821,36 +4859,96 @@
       <c r="AB21" s="12">
         <v>0</v>
       </c>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="12"/>
-      <c r="AE21" s="12"/>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="12"/>
-      <c r="AI21" s="12"/>
-      <c r="AJ21" s="12"/>
-      <c r="AK21" s="12"/>
-      <c r="AL21" s="12"/>
-      <c r="AM21" s="12"/>
-      <c r="AN21" s="12"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="12"/>
-      <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
-      <c r="AS21" s="12"/>
-      <c r="AT21" s="12"/>
-      <c r="AU21" s="12"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="12"/>
-      <c r="AX21" s="12"/>
-      <c r="AY21" s="12"/>
-      <c r="AZ21" s="12"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="12"/>
-      <c r="BC21" s="12"/>
-      <c r="BD21" s="12"/>
-      <c r="BE21" s="12"/>
-      <c r="BF21" s="12"/>
+      <c r="AC21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="12">
+        <v>0</v>
+      </c>
       <c r="BG21" s="12"/>
       <c r="BH21" s="12"/>
       <c r="BI21" s="12"/>
@@ -5123,7 +5221,7 @@
       </c>
       <c r="D23" s="15">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="12">
@@ -5185,36 +5283,96 @@
       <c r="AB23" s="12">
         <v>0</v>
       </c>
-      <c r="AC23" s="12"/>
-      <c r="AD23" s="12"/>
-      <c r="AE23" s="12"/>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="12"/>
-      <c r="AI23" s="12"/>
-      <c r="AJ23" s="12"/>
-      <c r="AK23" s="12"/>
-      <c r="AL23" s="12"/>
-      <c r="AM23" s="12"/>
-      <c r="AN23" s="12"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="12"/>
-      <c r="AQ23" s="12"/>
-      <c r="AR23" s="12"/>
-      <c r="AS23" s="12"/>
-      <c r="AT23" s="12"/>
-      <c r="AU23" s="12"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="12"/>
-      <c r="AX23" s="12"/>
-      <c r="AY23" s="12"/>
-      <c r="AZ23" s="12"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="12"/>
-      <c r="BC23" s="12"/>
-      <c r="BD23" s="12"/>
-      <c r="BE23" s="12"/>
-      <c r="BF23" s="12"/>
+      <c r="AC23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BD23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BE23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BF23" s="12">
+        <v>0</v>
+      </c>
       <c r="BG23" s="12"/>
       <c r="BH23" s="12"/>
       <c r="BI23" s="12"/>
@@ -5855,7 +6013,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="12"/>
@@ -5913,36 +6071,96 @@
       <c r="AB27" s="12">
         <v>0</v>
       </c>
-      <c r="AC27" s="12"/>
-      <c r="AD27" s="12"/>
-      <c r="AE27" s="12"/>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="12"/>
-      <c r="AI27" s="12"/>
-      <c r="AJ27" s="12"/>
-      <c r="AK27" s="12"/>
-      <c r="AL27" s="12"/>
-      <c r="AM27" s="12"/>
-      <c r="AN27" s="12"/>
-      <c r="AO27" s="12"/>
-      <c r="AP27" s="12"/>
-      <c r="AQ27" s="12"/>
-      <c r="AR27" s="12"/>
-      <c r="AS27" s="12"/>
-      <c r="AT27" s="12"/>
-      <c r="AU27" s="12"/>
-      <c r="AV27" s="12"/>
-      <c r="AW27" s="12"/>
-      <c r="AX27" s="12"/>
-      <c r="AY27" s="12"/>
-      <c r="AZ27" s="12"/>
-      <c r="BA27" s="12"/>
-      <c r="BB27" s="12"/>
-      <c r="BC27" s="12"/>
-      <c r="BD27" s="12"/>
-      <c r="BE27" s="12"/>
-      <c r="BF27" s="12"/>
+      <c r="AC27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BB27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BD27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BE27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BF27" s="12">
+        <v>0</v>
+      </c>
       <c r="BG27" s="12"/>
       <c r="BH27" s="12"/>
       <c r="BI27" s="12"/>
@@ -6045,149 +6263,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="53" t="s">
+      <c r="E28" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="53"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="53"/>
-      <c r="AB28" s="53"/>
-      <c r="AC28" s="53"/>
-      <c r="AD28" s="53"/>
-      <c r="AE28" s="53"/>
-      <c r="AF28" s="53"/>
-      <c r="AG28" s="53"/>
-      <c r="AH28" s="53"/>
-      <c r="AI28" s="53"/>
-      <c r="AJ28" s="53"/>
-      <c r="AK28" s="53"/>
-      <c r="AL28" s="53"/>
-      <c r="AM28" s="53"/>
-      <c r="AN28" s="53"/>
-      <c r="AO28" s="53"/>
-      <c r="AP28" s="53"/>
-      <c r="AQ28" s="53"/>
-      <c r="AR28" s="53"/>
-      <c r="AS28" s="53"/>
-      <c r="AT28" s="53"/>
-      <c r="AU28" s="53"/>
-      <c r="AV28" s="53"/>
-      <c r="AW28" s="53"/>
-      <c r="AX28" s="53"/>
-      <c r="AY28" s="53"/>
-      <c r="AZ28" s="53"/>
-      <c r="BA28" s="53"/>
-      <c r="BB28" s="53"/>
-      <c r="BC28" s="53"/>
-      <c r="BD28" s="53"/>
-      <c r="BE28" s="53"/>
-      <c r="BF28" s="53"/>
-      <c r="BG28" s="53"/>
-      <c r="BH28" s="53"/>
-      <c r="BI28" s="53"/>
-      <c r="BJ28" s="53"/>
-      <c r="BK28" s="53"/>
-      <c r="BL28" s="53"/>
-      <c r="BM28" s="53"/>
-      <c r="BN28" s="53"/>
-      <c r="BO28" s="53"/>
-      <c r="BP28" s="53"/>
-      <c r="BQ28" s="53"/>
-      <c r="BR28" s="53"/>
-      <c r="BS28" s="53"/>
-      <c r="BT28" s="53"/>
-      <c r="BU28" s="53"/>
-      <c r="BV28" s="53"/>
-      <c r="BW28" s="53"/>
-      <c r="BX28" s="53"/>
-      <c r="BY28" s="53"/>
-      <c r="BZ28" s="53"/>
-      <c r="CA28" s="53"/>
-      <c r="CB28" s="53"/>
-      <c r="CC28" s="53"/>
-      <c r="CD28" s="53"/>
-      <c r="CE28" s="53"/>
-      <c r="CF28" s="53"/>
-      <c r="CG28" s="53"/>
-      <c r="CH28" s="53"/>
-      <c r="CI28" s="53"/>
-      <c r="CJ28" s="53"/>
-      <c r="CK28" s="53"/>
-      <c r="CL28" s="53"/>
-      <c r="CM28" s="53"/>
-      <c r="CN28" s="53"/>
-      <c r="CO28" s="53"/>
-      <c r="CP28" s="53"/>
-      <c r="CQ28" s="53"/>
-      <c r="CR28" s="53"/>
-      <c r="CS28" s="53"/>
-      <c r="CT28" s="53"/>
-      <c r="CU28" s="53"/>
-      <c r="CV28" s="53"/>
-      <c r="CW28" s="53"/>
-      <c r="CX28" s="53"/>
-      <c r="CY28" s="53"/>
-      <c r="CZ28" s="53"/>
-      <c r="DA28" s="53"/>
-      <c r="DB28" s="53"/>
-      <c r="DC28" s="53"/>
-      <c r="DD28" s="53"/>
-      <c r="DE28" s="53"/>
-      <c r="DF28" s="53"/>
-      <c r="DG28" s="53"/>
-      <c r="DH28" s="53"/>
-      <c r="DI28" s="53"/>
-      <c r="DJ28" s="53"/>
-      <c r="DK28" s="53"/>
-      <c r="DL28" s="53"/>
-      <c r="DM28" s="53"/>
-      <c r="DN28" s="53"/>
-      <c r="DO28" s="53"/>
-      <c r="DP28" s="53"/>
-      <c r="DQ28" s="53"/>
-      <c r="DR28" s="53"/>
-      <c r="DS28" s="53"/>
-      <c r="DT28" s="53"/>
-      <c r="DU28" s="53"/>
-      <c r="DV28" s="53"/>
-      <c r="DW28" s="53"/>
-      <c r="DX28" s="53"/>
-      <c r="DY28" s="53"/>
-      <c r="DZ28" s="53"/>
-      <c r="EA28" s="53"/>
-      <c r="EB28" s="53"/>
-      <c r="EC28" s="53"/>
-      <c r="ED28" s="53"/>
-      <c r="EE28" s="53"/>
-      <c r="EF28" s="53"/>
-      <c r="EG28" s="53"/>
-      <c r="EH28" s="53"/>
-      <c r="EI28" s="53"/>
-      <c r="EJ28" s="53"/>
-      <c r="EK28" s="53"/>
-      <c r="EL28" s="53"/>
-      <c r="EM28" s="53"/>
-      <c r="EN28" s="53"/>
-      <c r="EO28" s="53"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="58"/>
+      <c r="T28" s="58"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="58"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="58"/>
+      <c r="Y28" s="58"/>
+      <c r="Z28" s="58"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="58"/>
+      <c r="AC28" s="58"/>
+      <c r="AD28" s="58"/>
+      <c r="AE28" s="58"/>
+      <c r="AF28" s="58"/>
+      <c r="AG28" s="58"/>
+      <c r="AH28" s="58"/>
+      <c r="AI28" s="58"/>
+      <c r="AJ28" s="58"/>
+      <c r="AK28" s="58"/>
+      <c r="AL28" s="58"/>
+      <c r="AM28" s="58"/>
+      <c r="AN28" s="58"/>
+      <c r="AO28" s="58"/>
+      <c r="AP28" s="58"/>
+      <c r="AQ28" s="58"/>
+      <c r="AR28" s="58"/>
+      <c r="AS28" s="58"/>
+      <c r="AT28" s="58"/>
+      <c r="AU28" s="58"/>
+      <c r="AV28" s="58"/>
+      <c r="AW28" s="58"/>
+      <c r="AX28" s="58"/>
+      <c r="AY28" s="58"/>
+      <c r="AZ28" s="58"/>
+      <c r="BA28" s="58"/>
+      <c r="BB28" s="58"/>
+      <c r="BC28" s="58"/>
+      <c r="BD28" s="58"/>
+      <c r="BE28" s="58"/>
+      <c r="BF28" s="58"/>
+      <c r="BG28" s="58"/>
+      <c r="BH28" s="58"/>
+      <c r="BI28" s="58"/>
+      <c r="BJ28" s="58"/>
+      <c r="BK28" s="58"/>
+      <c r="BL28" s="58"/>
+      <c r="BM28" s="58"/>
+      <c r="BN28" s="58"/>
+      <c r="BO28" s="58"/>
+      <c r="BP28" s="58"/>
+      <c r="BQ28" s="58"/>
+      <c r="BR28" s="58"/>
+      <c r="BS28" s="58"/>
+      <c r="BT28" s="58"/>
+      <c r="BU28" s="58"/>
+      <c r="BV28" s="58"/>
+      <c r="BW28" s="58"/>
+      <c r="BX28" s="58"/>
+      <c r="BY28" s="58"/>
+      <c r="BZ28" s="58"/>
+      <c r="CA28" s="58"/>
+      <c r="CB28" s="58"/>
+      <c r="CC28" s="58"/>
+      <c r="CD28" s="58"/>
+      <c r="CE28" s="58"/>
+      <c r="CF28" s="58"/>
+      <c r="CG28" s="58"/>
+      <c r="CH28" s="58"/>
+      <c r="CI28" s="58"/>
+      <c r="CJ28" s="58"/>
+      <c r="CK28" s="58"/>
+      <c r="CL28" s="58"/>
+      <c r="CM28" s="58"/>
+      <c r="CN28" s="58"/>
+      <c r="CO28" s="58"/>
+      <c r="CP28" s="58"/>
+      <c r="CQ28" s="58"/>
+      <c r="CR28" s="58"/>
+      <c r="CS28" s="58"/>
+      <c r="CT28" s="58"/>
+      <c r="CU28" s="58"/>
+      <c r="CV28" s="58"/>
+      <c r="CW28" s="58"/>
+      <c r="CX28" s="58"/>
+      <c r="CY28" s="58"/>
+      <c r="CZ28" s="58"/>
+      <c r="DA28" s="58"/>
+      <c r="DB28" s="58"/>
+      <c r="DC28" s="58"/>
+      <c r="DD28" s="58"/>
+      <c r="DE28" s="58"/>
+      <c r="DF28" s="58"/>
+      <c r="DG28" s="58"/>
+      <c r="DH28" s="58"/>
+      <c r="DI28" s="58"/>
+      <c r="DJ28" s="58"/>
+      <c r="DK28" s="58"/>
+      <c r="DL28" s="58"/>
+      <c r="DM28" s="58"/>
+      <c r="DN28" s="58"/>
+      <c r="DO28" s="58"/>
+      <c r="DP28" s="58"/>
+      <c r="DQ28" s="58"/>
+      <c r="DR28" s="58"/>
+      <c r="DS28" s="58"/>
+      <c r="DT28" s="58"/>
+      <c r="DU28" s="58"/>
+      <c r="DV28" s="58"/>
+      <c r="DW28" s="58"/>
+      <c r="DX28" s="58"/>
+      <c r="DY28" s="58"/>
+      <c r="DZ28" s="58"/>
+      <c r="EA28" s="58"/>
+      <c r="EB28" s="58"/>
+      <c r="EC28" s="58"/>
+      <c r="ED28" s="58"/>
+      <c r="EE28" s="58"/>
+      <c r="EF28" s="58"/>
+      <c r="EG28" s="58"/>
+      <c r="EH28" s="58"/>
+      <c r="EI28" s="58"/>
+      <c r="EJ28" s="58"/>
+      <c r="EK28" s="58"/>
+      <c r="EL28" s="58"/>
+      <c r="EM28" s="58"/>
+      <c r="EN28" s="58"/>
+      <c r="EO28" s="58"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6195,7 +6413,19 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="312">
+  <mergeCells count="313">
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
     <mergeCell ref="E28:EO28"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AE1:AH1"/>
@@ -6212,18 +6442,14 @@
     <mergeCell ref="EM8:EM9"/>
     <mergeCell ref="EN8:EN9"/>
     <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
     <mergeCell ref="DZ8:DZ9"/>
     <mergeCell ref="EA8:EA9"/>
     <mergeCell ref="EB8:EB9"/>
     <mergeCell ref="EC8:EC9"/>
     <mergeCell ref="ED8:ED9"/>
     <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="EH8:EH9"/>
     <mergeCell ref="DQ8:DQ9"/>
     <mergeCell ref="DR8:DR9"/>
     <mergeCell ref="DS8:DS9"/>
@@ -6233,17 +6459,6 @@
     <mergeCell ref="DW8:DW9"/>
     <mergeCell ref="DX8:DX9"/>
     <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
     <mergeCell ref="DA8:DA9"/>
     <mergeCell ref="DB8:DB9"/>
     <mergeCell ref="DC8:DC9"/>
@@ -6350,6 +6565,9 @@
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="EH2:EH7"/>
     <mergeCell ref="EI2:EI7"/>
     <mergeCell ref="EJ2:EJ7"/>
@@ -6374,6 +6592,7 @@
     <mergeCell ref="EC2:EC7"/>
     <mergeCell ref="ED2:ED7"/>
     <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="DO2:DO7"/>
     <mergeCell ref="EF2:EF7"/>
     <mergeCell ref="EG2:EG7"/>
     <mergeCell ref="DP2:DP7"/>
@@ -6385,6 +6604,7 @@
     <mergeCell ref="DV2:DV7"/>
     <mergeCell ref="DW2:DW7"/>
     <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="DF2:DF7"/>
     <mergeCell ref="DG2:DG7"/>
     <mergeCell ref="DH2:DH7"/>
     <mergeCell ref="DI2:DI7"/>
@@ -6393,7 +6613,7 @@
     <mergeCell ref="DL2:DL7"/>
     <mergeCell ref="DM2:DM7"/>
     <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="CW2:CW7"/>
     <mergeCell ref="CX2:CX7"/>
     <mergeCell ref="CY2:CY7"/>
     <mergeCell ref="CZ2:CZ7"/>
@@ -6402,7 +6622,7 @@
     <mergeCell ref="DC2:DC7"/>
     <mergeCell ref="DD2:DD7"/>
     <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="CN2:CN7"/>
     <mergeCell ref="CO2:CO7"/>
     <mergeCell ref="CP2:CP7"/>
     <mergeCell ref="CQ2:CQ7"/>
@@ -6411,7 +6631,7 @@
     <mergeCell ref="CT2:CT7"/>
     <mergeCell ref="CU2:CU7"/>
     <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CE2:CE7"/>
     <mergeCell ref="CF2:CF7"/>
     <mergeCell ref="CG2:CG7"/>
     <mergeCell ref="CH2:CH7"/>
@@ -6420,7 +6640,7 @@
     <mergeCell ref="CK2:CK7"/>
     <mergeCell ref="CL2:CL7"/>
     <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="BV2:BV7"/>
     <mergeCell ref="BW2:BW7"/>
     <mergeCell ref="BX2:BX7"/>
     <mergeCell ref="BY2:BY7"/>
@@ -6429,7 +6649,7 @@
     <mergeCell ref="CB2:CB7"/>
     <mergeCell ref="CC2:CC7"/>
     <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="BM2:BM7"/>
     <mergeCell ref="BN2:BN7"/>
     <mergeCell ref="BO2:BO7"/>
     <mergeCell ref="BP2:BP7"/>
@@ -6438,7 +6658,7 @@
     <mergeCell ref="BS2:BS7"/>
     <mergeCell ref="BT2:BT7"/>
     <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BD2:BD7"/>
     <mergeCell ref="BE2:BE7"/>
     <mergeCell ref="BF2:BF7"/>
     <mergeCell ref="BG2:BG7"/>
@@ -6447,7 +6667,7 @@
     <mergeCell ref="BJ2:BJ7"/>
     <mergeCell ref="BK2:BK7"/>
     <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="AU2:AU7"/>
     <mergeCell ref="AV2:AV7"/>
     <mergeCell ref="AW2:AW7"/>
     <mergeCell ref="AX2:AX7"/>
@@ -6456,7 +6676,7 @@
     <mergeCell ref="BA2:BA7"/>
     <mergeCell ref="BB2:BB7"/>
     <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="AL2:AL7"/>
     <mergeCell ref="AM2:AM7"/>
     <mergeCell ref="AN2:AN7"/>
     <mergeCell ref="AO2:AO7"/>
@@ -6465,7 +6685,7 @@
     <mergeCell ref="AR2:AR7"/>
     <mergeCell ref="AS2:AS7"/>
     <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AC2:AC7"/>
     <mergeCell ref="AD2:AD7"/>
     <mergeCell ref="AE2:AE7"/>
     <mergeCell ref="AF2:AF7"/>
@@ -6474,7 +6694,7 @@
     <mergeCell ref="AI2:AI7"/>
     <mergeCell ref="AJ2:AJ7"/>
     <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="T2:T7"/>
     <mergeCell ref="U2:U7"/>
     <mergeCell ref="V2:V7"/>
     <mergeCell ref="W2:W7"/>
@@ -6483,7 +6703,7 @@
     <mergeCell ref="Z2:Z7"/>
     <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AO17:EO17"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="F1:I1"/>
@@ -6507,7 +6727,6 @@
     <mergeCell ref="Q2:Q7"/>
     <mergeCell ref="R2:R7"/>
     <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C31A5B-1418-4351-AFF7-1AAD97FB8409}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B18342-C3C3-4327-9656-0500A04DF61E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,7 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -810,6 +810,9 @@
     <xf numFmtId="164" fontId="8" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1167,98 +1170,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
-      <c r="F1" s="29">
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="F1" s="30">
         <v>4</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="31">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32">
         <v>3</v>
       </c>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31">
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32">
         <v>4</v>
       </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="32">
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33">
         <v>4</v>
       </c>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="32">
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="33">
         <v>4</v>
       </c>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="32">
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="33">
         <v>4</v>
       </c>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="59">
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="60">
         <v>2</v>
       </c>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="61">
+      <c r="AD1" s="61"/>
+      <c r="AE1" s="62">
         <v>4</v>
       </c>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="63"/>
-      <c r="AI1" s="61">
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="64"/>
+      <c r="AI1" s="62">
         <v>4</v>
       </c>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="61">
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="64"/>
+      <c r="AM1" s="62">
         <v>2</v>
       </c>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="61">
+      <c r="AN1" s="64"/>
+      <c r="AO1" s="62">
         <v>4</v>
       </c>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="63"/>
-      <c r="AS1" s="61">
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="64"/>
+      <c r="AS1" s="62">
         <v>5</v>
       </c>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="64"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="61">
+      <c r="AY1" s="62">
         <v>5</v>
       </c>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="63"/>
-      <c r="BD1" s="61">
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="64"/>
+      <c r="BD1" s="62">
         <v>3</v>
       </c>
-      <c r="BE1" s="62"/>
-      <c r="BF1" s="63"/>
-      <c r="BG1" s="4"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="64"/>
+      <c r="BG1" s="21">
+        <v>1</v>
+      </c>
       <c r="BH1" s="4"/>
       <c r="BI1" s="4"/>
       <c r="BJ1" s="4"/>
@@ -1345,1602 +1350,1608 @@
       <c r="EM1" s="4"/>
       <c r="EN1" s="4"/>
       <c r="EO1" s="4"/>
+      <c r="EP1" s="1">
+        <f>SUM(E1:EO1)</f>
+        <v>54</v>
+      </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="35" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="O2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="38" t="s">
+      <c r="P2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="38" t="s">
+      <c r="Q2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="R2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="40" t="s">
+      <c r="S2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="40" t="s">
+      <c r="T2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="38" t="s">
+      <c r="U2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="V2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="40" t="s">
+      <c r="W2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Y2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="Z2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="42" t="s">
+      <c r="AA2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="42" t="s">
+      <c r="AB2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="38">
+      <c r="AC2" s="39">
         <v>46199</v>
       </c>
-      <c r="AD2" s="38">
+      <c r="AD2" s="39">
         <v>46199</v>
       </c>
-      <c r="AE2" s="38">
+      <c r="AE2" s="39">
         <v>46202</v>
       </c>
-      <c r="AF2" s="38">
+      <c r="AF2" s="39">
         <v>46202</v>
       </c>
-      <c r="AG2" s="38">
+      <c r="AG2" s="39">
         <v>46202</v>
       </c>
-      <c r="AH2" s="38">
+      <c r="AH2" s="39">
         <v>46202</v>
       </c>
-      <c r="AI2" s="38">
+      <c r="AI2" s="39">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="38">
+      <c r="AJ2" s="39">
         <v>46205</v>
       </c>
-      <c r="AK2" s="38">
+      <c r="AK2" s="39">
         <v>46205</v>
       </c>
-      <c r="AL2" s="38">
+      <c r="AL2" s="39">
         <v>46205</v>
       </c>
-      <c r="AM2" s="38">
+      <c r="AM2" s="39">
         <v>46206</v>
       </c>
-      <c r="AN2" s="38">
+      <c r="AN2" s="39">
         <v>46206</v>
       </c>
-      <c r="AO2" s="38">
+      <c r="AO2" s="39">
         <v>46212</v>
       </c>
-      <c r="AP2" s="38">
+      <c r="AP2" s="39">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="38">
+      <c r="AQ2" s="39">
         <v>46212</v>
       </c>
-      <c r="AR2" s="38">
+      <c r="AR2" s="39">
         <v>46212</v>
       </c>
-      <c r="AS2" s="38">
+      <c r="AS2" s="39">
         <v>46213</v>
       </c>
-      <c r="AT2" s="38">
+      <c r="AT2" s="39">
         <v>46213</v>
       </c>
-      <c r="AU2" s="38">
+      <c r="AU2" s="39">
         <v>46213</v>
       </c>
-      <c r="AV2" s="38">
+      <c r="AV2" s="39">
         <v>46213</v>
       </c>
-      <c r="AW2" s="38">
+      <c r="AW2" s="39">
         <v>46213</v>
       </c>
-      <c r="AX2" s="38">
+      <c r="AX2" s="39">
         <v>46218</v>
       </c>
-      <c r="AY2" s="38">
+      <c r="AY2" s="39">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="38">
+      <c r="AZ2" s="39">
         <v>46219</v>
       </c>
-      <c r="BA2" s="38">
+      <c r="BA2" s="39">
         <v>46219</v>
       </c>
-      <c r="BB2" s="38">
+      <c r="BB2" s="39">
         <v>46219</v>
       </c>
-      <c r="BC2" s="38">
+      <c r="BC2" s="39">
         <v>46219</v>
       </c>
-      <c r="BD2" s="38">
+      <c r="BD2" s="39">
         <v>46220</v>
       </c>
-      <c r="BE2" s="38">
+      <c r="BE2" s="39">
         <v>46220</v>
       </c>
-      <c r="BF2" s="38">
+      <c r="BF2" s="39">
         <v>46220</v>
       </c>
-      <c r="BG2" s="38"/>
-      <c r="BH2" s="38"/>
-      <c r="BI2" s="38"/>
-      <c r="BJ2" s="38"/>
-      <c r="BK2" s="38"/>
-      <c r="BL2" s="38"/>
-      <c r="BM2" s="38"/>
-      <c r="BN2" s="38"/>
-      <c r="BO2" s="38"/>
-      <c r="BP2" s="38"/>
-      <c r="BQ2" s="38"/>
-      <c r="BR2" s="38"/>
-      <c r="BS2" s="38"/>
-      <c r="BT2" s="38"/>
-      <c r="BU2" s="38"/>
-      <c r="BV2" s="38"/>
-      <c r="BW2" s="38"/>
-      <c r="BX2" s="38"/>
-      <c r="BY2" s="38"/>
-      <c r="BZ2" s="38"/>
-      <c r="CA2" s="38"/>
-      <c r="CB2" s="38"/>
-      <c r="CC2" s="38"/>
-      <c r="CD2" s="38"/>
-      <c r="CE2" s="38"/>
-      <c r="CF2" s="38"/>
-      <c r="CG2" s="38"/>
-      <c r="CH2" s="38"/>
-      <c r="CI2" s="38"/>
-      <c r="CJ2" s="38"/>
-      <c r="CK2" s="38"/>
-      <c r="CL2" s="38"/>
-      <c r="CM2" s="38"/>
-      <c r="CN2" s="38"/>
-      <c r="CO2" s="38"/>
-      <c r="CP2" s="38"/>
-      <c r="CQ2" s="38"/>
-      <c r="CR2" s="38"/>
-      <c r="CS2" s="38"/>
-      <c r="CT2" s="38"/>
-      <c r="CU2" s="38"/>
-      <c r="CV2" s="38"/>
-      <c r="CW2" s="38"/>
-      <c r="CX2" s="38"/>
-      <c r="CY2" s="38"/>
-      <c r="CZ2" s="38"/>
-      <c r="DA2" s="38"/>
-      <c r="DB2" s="38"/>
-      <c r="DC2" s="38"/>
-      <c r="DD2" s="38"/>
-      <c r="DE2" s="38"/>
-      <c r="DF2" s="38"/>
-      <c r="DG2" s="38"/>
-      <c r="DH2" s="38"/>
-      <c r="DI2" s="38"/>
-      <c r="DJ2" s="38"/>
-      <c r="DK2" s="38"/>
-      <c r="DL2" s="38"/>
-      <c r="DM2" s="38"/>
-      <c r="DN2" s="38"/>
-      <c r="DO2" s="38"/>
-      <c r="DP2" s="38"/>
-      <c r="DQ2" s="38"/>
-      <c r="DR2" s="38"/>
-      <c r="DS2" s="38"/>
-      <c r="DT2" s="38"/>
-      <c r="DU2" s="38"/>
-      <c r="DV2" s="38"/>
-      <c r="DW2" s="38"/>
-      <c r="DX2" s="38"/>
-      <c r="DY2" s="38"/>
-      <c r="DZ2" s="38"/>
-      <c r="EA2" s="38"/>
-      <c r="EB2" s="38"/>
-      <c r="EC2" s="38"/>
-      <c r="ED2" s="38"/>
-      <c r="EE2" s="38"/>
-      <c r="EF2" s="38"/>
-      <c r="EG2" s="38"/>
-      <c r="EH2" s="38"/>
-      <c r="EI2" s="38"/>
-      <c r="EJ2" s="38"/>
-      <c r="EK2" s="38"/>
-      <c r="EL2" s="38"/>
-      <c r="EM2" s="38"/>
-      <c r="EN2" s="38"/>
-      <c r="EO2" s="38"/>
+      <c r="BG2" s="39">
+        <v>46225</v>
+      </c>
+      <c r="BH2" s="39"/>
+      <c r="BI2" s="39"/>
+      <c r="BJ2" s="39"/>
+      <c r="BK2" s="39"/>
+      <c r="BL2" s="39"/>
+      <c r="BM2" s="39"/>
+      <c r="BN2" s="39"/>
+      <c r="BO2" s="39"/>
+      <c r="BP2" s="39"/>
+      <c r="BQ2" s="39"/>
+      <c r="BR2" s="39"/>
+      <c r="BS2" s="39"/>
+      <c r="BT2" s="39"/>
+      <c r="BU2" s="39"/>
+      <c r="BV2" s="39"/>
+      <c r="BW2" s="39"/>
+      <c r="BX2" s="39"/>
+      <c r="BY2" s="39"/>
+      <c r="BZ2" s="39"/>
+      <c r="CA2" s="39"/>
+      <c r="CB2" s="39"/>
+      <c r="CC2" s="39"/>
+      <c r="CD2" s="39"/>
+      <c r="CE2" s="39"/>
+      <c r="CF2" s="39"/>
+      <c r="CG2" s="39"/>
+      <c r="CH2" s="39"/>
+      <c r="CI2" s="39"/>
+      <c r="CJ2" s="39"/>
+      <c r="CK2" s="39"/>
+      <c r="CL2" s="39"/>
+      <c r="CM2" s="39"/>
+      <c r="CN2" s="39"/>
+      <c r="CO2" s="39"/>
+      <c r="CP2" s="39"/>
+      <c r="CQ2" s="39"/>
+      <c r="CR2" s="39"/>
+      <c r="CS2" s="39"/>
+      <c r="CT2" s="39"/>
+      <c r="CU2" s="39"/>
+      <c r="CV2" s="39"/>
+      <c r="CW2" s="39"/>
+      <c r="CX2" s="39"/>
+      <c r="CY2" s="39"/>
+      <c r="CZ2" s="39"/>
+      <c r="DA2" s="39"/>
+      <c r="DB2" s="39"/>
+      <c r="DC2" s="39"/>
+      <c r="DD2" s="39"/>
+      <c r="DE2" s="39"/>
+      <c r="DF2" s="39"/>
+      <c r="DG2" s="39"/>
+      <c r="DH2" s="39"/>
+      <c r="DI2" s="39"/>
+      <c r="DJ2" s="39"/>
+      <c r="DK2" s="39"/>
+      <c r="DL2" s="39"/>
+      <c r="DM2" s="39"/>
+      <c r="DN2" s="39"/>
+      <c r="DO2" s="39"/>
+      <c r="DP2" s="39"/>
+      <c r="DQ2" s="39"/>
+      <c r="DR2" s="39"/>
+      <c r="DS2" s="39"/>
+      <c r="DT2" s="39"/>
+      <c r="DU2" s="39"/>
+      <c r="DV2" s="39"/>
+      <c r="DW2" s="39"/>
+      <c r="DX2" s="39"/>
+      <c r="DY2" s="39"/>
+      <c r="DZ2" s="39"/>
+      <c r="EA2" s="39"/>
+      <c r="EB2" s="39"/>
+      <c r="EC2" s="39"/>
+      <c r="ED2" s="39"/>
+      <c r="EE2" s="39"/>
+      <c r="EF2" s="39"/>
+      <c r="EG2" s="39"/>
+      <c r="EH2" s="39"/>
+      <c r="EI2" s="39"/>
+      <c r="EJ2" s="39"/>
+      <c r="EK2" s="39"/>
+      <c r="EL2" s="39"/>
+      <c r="EM2" s="39"/>
+      <c r="EN2" s="39"/>
+      <c r="EO2" s="39"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
-      <c r="AE3" s="38"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="38"/>
-      <c r="AK3" s="38"/>
-      <c r="AL3" s="38"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="38"/>
-      <c r="AO3" s="38"/>
-      <c r="AP3" s="38"/>
-      <c r="AQ3" s="38"/>
-      <c r="AR3" s="38"/>
-      <c r="AS3" s="38"/>
-      <c r="AT3" s="38"/>
-      <c r="AU3" s="38"/>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="38"/>
-      <c r="AX3" s="38"/>
-      <c r="AY3" s="38"/>
-      <c r="AZ3" s="38"/>
-      <c r="BA3" s="38"/>
-      <c r="BB3" s="38"/>
-      <c r="BC3" s="38"/>
-      <c r="BD3" s="38"/>
-      <c r="BE3" s="38"/>
-      <c r="BF3" s="38"/>
-      <c r="BG3" s="38"/>
-      <c r="BH3" s="38"/>
-      <c r="BI3" s="38"/>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="38"/>
-      <c r="BL3" s="38"/>
-      <c r="BM3" s="38"/>
-      <c r="BN3" s="38"/>
-      <c r="BO3" s="38"/>
-      <c r="BP3" s="38"/>
-      <c r="BQ3" s="38"/>
-      <c r="BR3" s="38"/>
-      <c r="BS3" s="38"/>
-      <c r="BT3" s="38"/>
-      <c r="BU3" s="38"/>
-      <c r="BV3" s="38"/>
-      <c r="BW3" s="38"/>
-      <c r="BX3" s="38"/>
-      <c r="BY3" s="38"/>
-      <c r="BZ3" s="38"/>
-      <c r="CA3" s="38"/>
-      <c r="CB3" s="38"/>
-      <c r="CC3" s="38"/>
-      <c r="CD3" s="38"/>
-      <c r="CE3" s="38"/>
-      <c r="CF3" s="38"/>
-      <c r="CG3" s="38"/>
-      <c r="CH3" s="38"/>
-      <c r="CI3" s="38"/>
-      <c r="CJ3" s="38"/>
-      <c r="CK3" s="38"/>
-      <c r="CL3" s="38"/>
-      <c r="CM3" s="38"/>
-      <c r="CN3" s="38"/>
-      <c r="CO3" s="38"/>
-      <c r="CP3" s="38"/>
-      <c r="CQ3" s="38"/>
-      <c r="CR3" s="38"/>
-      <c r="CS3" s="38"/>
-      <c r="CT3" s="38"/>
-      <c r="CU3" s="38"/>
-      <c r="CV3" s="38"/>
-      <c r="CW3" s="38"/>
-      <c r="CX3" s="38"/>
-      <c r="CY3" s="38"/>
-      <c r="CZ3" s="38"/>
-      <c r="DA3" s="38"/>
-      <c r="DB3" s="38"/>
-      <c r="DC3" s="38"/>
-      <c r="DD3" s="38"/>
-      <c r="DE3" s="38"/>
-      <c r="DF3" s="38"/>
-      <c r="DG3" s="38"/>
-      <c r="DH3" s="38"/>
-      <c r="DI3" s="38"/>
-      <c r="DJ3" s="38"/>
-      <c r="DK3" s="38"/>
-      <c r="DL3" s="38"/>
-      <c r="DM3" s="38"/>
-      <c r="DN3" s="38"/>
-      <c r="DO3" s="38"/>
-      <c r="DP3" s="38"/>
-      <c r="DQ3" s="38"/>
-      <c r="DR3" s="38"/>
-      <c r="DS3" s="38"/>
-      <c r="DT3" s="38"/>
-      <c r="DU3" s="38"/>
-      <c r="DV3" s="38"/>
-      <c r="DW3" s="38"/>
-      <c r="DX3" s="38"/>
-      <c r="DY3" s="38"/>
-      <c r="DZ3" s="38"/>
-      <c r="EA3" s="38"/>
-      <c r="EB3" s="38"/>
-      <c r="EC3" s="38"/>
-      <c r="ED3" s="38"/>
-      <c r="EE3" s="38"/>
-      <c r="EF3" s="38"/>
-      <c r="EG3" s="38"/>
-      <c r="EH3" s="38"/>
-      <c r="EI3" s="38"/>
-      <c r="EJ3" s="38"/>
-      <c r="EK3" s="38"/>
-      <c r="EL3" s="38"/>
-      <c r="EM3" s="38"/>
-      <c r="EN3" s="38"/>
-      <c r="EO3" s="38"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="39"/>
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="39"/>
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="39"/>
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="39"/>
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="39"/>
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="39"/>
+      <c r="BX3" s="39"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="39"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="39"/>
+      <c r="CF3" s="39"/>
+      <c r="CG3" s="39"/>
+      <c r="CH3" s="39"/>
+      <c r="CI3" s="39"/>
+      <c r="CJ3" s="39"/>
+      <c r="CK3" s="39"/>
+      <c r="CL3" s="39"/>
+      <c r="CM3" s="39"/>
+      <c r="CN3" s="39"/>
+      <c r="CO3" s="39"/>
+      <c r="CP3" s="39"/>
+      <c r="CQ3" s="39"/>
+      <c r="CR3" s="39"/>
+      <c r="CS3" s="39"/>
+      <c r="CT3" s="39"/>
+      <c r="CU3" s="39"/>
+      <c r="CV3" s="39"/>
+      <c r="CW3" s="39"/>
+      <c r="CX3" s="39"/>
+      <c r="CY3" s="39"/>
+      <c r="CZ3" s="39"/>
+      <c r="DA3" s="39"/>
+      <c r="DB3" s="39"/>
+      <c r="DC3" s="39"/>
+      <c r="DD3" s="39"/>
+      <c r="DE3" s="39"/>
+      <c r="DF3" s="39"/>
+      <c r="DG3" s="39"/>
+      <c r="DH3" s="39"/>
+      <c r="DI3" s="39"/>
+      <c r="DJ3" s="39"/>
+      <c r="DK3" s="39"/>
+      <c r="DL3" s="39"/>
+      <c r="DM3" s="39"/>
+      <c r="DN3" s="39"/>
+      <c r="DO3" s="39"/>
+      <c r="DP3" s="39"/>
+      <c r="DQ3" s="39"/>
+      <c r="DR3" s="39"/>
+      <c r="DS3" s="39"/>
+      <c r="DT3" s="39"/>
+      <c r="DU3" s="39"/>
+      <c r="DV3" s="39"/>
+      <c r="DW3" s="39"/>
+      <c r="DX3" s="39"/>
+      <c r="DY3" s="39"/>
+      <c r="DZ3" s="39"/>
+      <c r="EA3" s="39"/>
+      <c r="EB3" s="39"/>
+      <c r="EC3" s="39"/>
+      <c r="ED3" s="39"/>
+      <c r="EE3" s="39"/>
+      <c r="EF3" s="39"/>
+      <c r="EG3" s="39"/>
+      <c r="EH3" s="39"/>
+      <c r="EI3" s="39"/>
+      <c r="EJ3" s="39"/>
+      <c r="EK3" s="39"/>
+      <c r="EL3" s="39"/>
+      <c r="EM3" s="39"/>
+      <c r="EN3" s="39"/>
+      <c r="EO3" s="39"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="42"/>
-      <c r="AB4" s="42"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
-      <c r="BJ4" s="38"/>
-      <c r="BK4" s="38"/>
-      <c r="BL4" s="38"/>
-      <c r="BM4" s="38"/>
-      <c r="BN4" s="38"/>
-      <c r="BO4" s="38"/>
-      <c r="BP4" s="38"/>
-      <c r="BQ4" s="38"/>
-      <c r="BR4" s="38"/>
-      <c r="BS4" s="38"/>
-      <c r="BT4" s="38"/>
-      <c r="BU4" s="38"/>
-      <c r="BV4" s="38"/>
-      <c r="BW4" s="38"/>
-      <c r="BX4" s="38"/>
-      <c r="BY4" s="38"/>
-      <c r="BZ4" s="38"/>
-      <c r="CA4" s="38"/>
-      <c r="CB4" s="38"/>
-      <c r="CC4" s="38"/>
-      <c r="CD4" s="38"/>
-      <c r="CE4" s="38"/>
-      <c r="CF4" s="38"/>
-      <c r="CG4" s="38"/>
-      <c r="CH4" s="38"/>
-      <c r="CI4" s="38"/>
-      <c r="CJ4" s="38"/>
-      <c r="CK4" s="38"/>
-      <c r="CL4" s="38"/>
-      <c r="CM4" s="38"/>
-      <c r="CN4" s="38"/>
-      <c r="CO4" s="38"/>
-      <c r="CP4" s="38"/>
-      <c r="CQ4" s="38"/>
-      <c r="CR4" s="38"/>
-      <c r="CS4" s="38"/>
-      <c r="CT4" s="38"/>
-      <c r="CU4" s="38"/>
-      <c r="CV4" s="38"/>
-      <c r="CW4" s="38"/>
-      <c r="CX4" s="38"/>
-      <c r="CY4" s="38"/>
-      <c r="CZ4" s="38"/>
-      <c r="DA4" s="38"/>
-      <c r="DB4" s="38"/>
-      <c r="DC4" s="38"/>
-      <c r="DD4" s="38"/>
-      <c r="DE4" s="38"/>
-      <c r="DF4" s="38"/>
-      <c r="DG4" s="38"/>
-      <c r="DH4" s="38"/>
-      <c r="DI4" s="38"/>
-      <c r="DJ4" s="38"/>
-      <c r="DK4" s="38"/>
-      <c r="DL4" s="38"/>
-      <c r="DM4" s="38"/>
-      <c r="DN4" s="38"/>
-      <c r="DO4" s="38"/>
-      <c r="DP4" s="38"/>
-      <c r="DQ4" s="38"/>
-      <c r="DR4" s="38"/>
-      <c r="DS4" s="38"/>
-      <c r="DT4" s="38"/>
-      <c r="DU4" s="38"/>
-      <c r="DV4" s="38"/>
-      <c r="DW4" s="38"/>
-      <c r="DX4" s="38"/>
-      <c r="DY4" s="38"/>
-      <c r="DZ4" s="38"/>
-      <c r="EA4" s="38"/>
-      <c r="EB4" s="38"/>
-      <c r="EC4" s="38"/>
-      <c r="ED4" s="38"/>
-      <c r="EE4" s="38"/>
-      <c r="EF4" s="38"/>
-      <c r="EG4" s="38"/>
-      <c r="EH4" s="38"/>
-      <c r="EI4" s="38"/>
-      <c r="EJ4" s="38"/>
-      <c r="EK4" s="38"/>
-      <c r="EL4" s="38"/>
-      <c r="EM4" s="38"/>
-      <c r="EN4" s="38"/>
-      <c r="EO4" s="38"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="43"/>
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="39"/>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="39"/>
+      <c r="AM4" s="39"/>
+      <c r="AN4" s="39"/>
+      <c r="AO4" s="39"/>
+      <c r="AP4" s="39"/>
+      <c r="AQ4" s="39"/>
+      <c r="AR4" s="39"/>
+      <c r="AS4" s="39"/>
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
+      <c r="AX4" s="39"/>
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
+      <c r="BA4" s="39"/>
+      <c r="BB4" s="39"/>
+      <c r="BC4" s="39"/>
+      <c r="BD4" s="39"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="39"/>
+      <c r="BG4" s="39"/>
+      <c r="BH4" s="39"/>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="39"/>
+      <c r="BL4" s="39"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="39"/>
+      <c r="BQ4" s="39"/>
+      <c r="BR4" s="39"/>
+      <c r="BS4" s="39"/>
+      <c r="BT4" s="39"/>
+      <c r="BU4" s="39"/>
+      <c r="BV4" s="39"/>
+      <c r="BW4" s="39"/>
+      <c r="BX4" s="39"/>
+      <c r="BY4" s="39"/>
+      <c r="BZ4" s="39"/>
+      <c r="CA4" s="39"/>
+      <c r="CB4" s="39"/>
+      <c r="CC4" s="39"/>
+      <c r="CD4" s="39"/>
+      <c r="CE4" s="39"/>
+      <c r="CF4" s="39"/>
+      <c r="CG4" s="39"/>
+      <c r="CH4" s="39"/>
+      <c r="CI4" s="39"/>
+      <c r="CJ4" s="39"/>
+      <c r="CK4" s="39"/>
+      <c r="CL4" s="39"/>
+      <c r="CM4" s="39"/>
+      <c r="CN4" s="39"/>
+      <c r="CO4" s="39"/>
+      <c r="CP4" s="39"/>
+      <c r="CQ4" s="39"/>
+      <c r="CR4" s="39"/>
+      <c r="CS4" s="39"/>
+      <c r="CT4" s="39"/>
+      <c r="CU4" s="39"/>
+      <c r="CV4" s="39"/>
+      <c r="CW4" s="39"/>
+      <c r="CX4" s="39"/>
+      <c r="CY4" s="39"/>
+      <c r="CZ4" s="39"/>
+      <c r="DA4" s="39"/>
+      <c r="DB4" s="39"/>
+      <c r="DC4" s="39"/>
+      <c r="DD4" s="39"/>
+      <c r="DE4" s="39"/>
+      <c r="DF4" s="39"/>
+      <c r="DG4" s="39"/>
+      <c r="DH4" s="39"/>
+      <c r="DI4" s="39"/>
+      <c r="DJ4" s="39"/>
+      <c r="DK4" s="39"/>
+      <c r="DL4" s="39"/>
+      <c r="DM4" s="39"/>
+      <c r="DN4" s="39"/>
+      <c r="DO4" s="39"/>
+      <c r="DP4" s="39"/>
+      <c r="DQ4" s="39"/>
+      <c r="DR4" s="39"/>
+      <c r="DS4" s="39"/>
+      <c r="DT4" s="39"/>
+      <c r="DU4" s="39"/>
+      <c r="DV4" s="39"/>
+      <c r="DW4" s="39"/>
+      <c r="DX4" s="39"/>
+      <c r="DY4" s="39"/>
+      <c r="DZ4" s="39"/>
+      <c r="EA4" s="39"/>
+      <c r="EB4" s="39"/>
+      <c r="EC4" s="39"/>
+      <c r="ED4" s="39"/>
+      <c r="EE4" s="39"/>
+      <c r="EF4" s="39"/>
+      <c r="EG4" s="39"/>
+      <c r="EH4" s="39"/>
+      <c r="EI4" s="39"/>
+      <c r="EJ4" s="39"/>
+      <c r="EK4" s="39"/>
+      <c r="EL4" s="39"/>
+      <c r="EM4" s="39"/>
+      <c r="EN4" s="39"/>
+      <c r="EO4" s="39"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>110</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="42"/>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
-      <c r="BJ5" s="38"/>
-      <c r="BK5" s="38"/>
-      <c r="BL5" s="38"/>
-      <c r="BM5" s="38"/>
-      <c r="BN5" s="38"/>
-      <c r="BO5" s="38"/>
-      <c r="BP5" s="38"/>
-      <c r="BQ5" s="38"/>
-      <c r="BR5" s="38"/>
-      <c r="BS5" s="38"/>
-      <c r="BT5" s="38"/>
-      <c r="BU5" s="38"/>
-      <c r="BV5" s="38"/>
-      <c r="BW5" s="38"/>
-      <c r="BX5" s="38"/>
-      <c r="BY5" s="38"/>
-      <c r="BZ5" s="38"/>
-      <c r="CA5" s="38"/>
-      <c r="CB5" s="38"/>
-      <c r="CC5" s="38"/>
-      <c r="CD5" s="38"/>
-      <c r="CE5" s="38"/>
-      <c r="CF5" s="38"/>
-      <c r="CG5" s="38"/>
-      <c r="CH5" s="38"/>
-      <c r="CI5" s="38"/>
-      <c r="CJ5" s="38"/>
-      <c r="CK5" s="38"/>
-      <c r="CL5" s="38"/>
-      <c r="CM5" s="38"/>
-      <c r="CN5" s="38"/>
-      <c r="CO5" s="38"/>
-      <c r="CP5" s="38"/>
-      <c r="CQ5" s="38"/>
-      <c r="CR5" s="38"/>
-      <c r="CS5" s="38"/>
-      <c r="CT5" s="38"/>
-      <c r="CU5" s="38"/>
-      <c r="CV5" s="38"/>
-      <c r="CW5" s="38"/>
-      <c r="CX5" s="38"/>
-      <c r="CY5" s="38"/>
-      <c r="CZ5" s="38"/>
-      <c r="DA5" s="38"/>
-      <c r="DB5" s="38"/>
-      <c r="DC5" s="38"/>
-      <c r="DD5" s="38"/>
-      <c r="DE5" s="38"/>
-      <c r="DF5" s="38"/>
-      <c r="DG5" s="38"/>
-      <c r="DH5" s="38"/>
-      <c r="DI5" s="38"/>
-      <c r="DJ5" s="38"/>
-      <c r="DK5" s="38"/>
-      <c r="DL5" s="38"/>
-      <c r="DM5" s="38"/>
-      <c r="DN5" s="38"/>
-      <c r="DO5" s="38"/>
-      <c r="DP5" s="38"/>
-      <c r="DQ5" s="38"/>
-      <c r="DR5" s="38"/>
-      <c r="DS5" s="38"/>
-      <c r="DT5" s="38"/>
-      <c r="DU5" s="38"/>
-      <c r="DV5" s="38"/>
-      <c r="DW5" s="38"/>
-      <c r="DX5" s="38"/>
-      <c r="DY5" s="38"/>
-      <c r="DZ5" s="38"/>
-      <c r="EA5" s="38"/>
-      <c r="EB5" s="38"/>
-      <c r="EC5" s="38"/>
-      <c r="ED5" s="38"/>
-      <c r="EE5" s="38"/>
-      <c r="EF5" s="38"/>
-      <c r="EG5" s="38"/>
-      <c r="EH5" s="38"/>
-      <c r="EI5" s="38"/>
-      <c r="EJ5" s="38"/>
-      <c r="EK5" s="38"/>
-      <c r="EL5" s="38"/>
-      <c r="EM5" s="38"/>
-      <c r="EN5" s="38"/>
-      <c r="EO5" s="38"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="43"/>
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="39"/>
+      <c r="AN5" s="39"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="39"/>
+      <c r="AQ5" s="39"/>
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="39"/>
+      <c r="AT5" s="39"/>
+      <c r="AU5" s="39"/>
+      <c r="AV5" s="39"/>
+      <c r="AW5" s="39"/>
+      <c r="AX5" s="39"/>
+      <c r="AY5" s="39"/>
+      <c r="AZ5" s="39"/>
+      <c r="BA5" s="39"/>
+      <c r="BB5" s="39"/>
+      <c r="BC5" s="39"/>
+      <c r="BD5" s="39"/>
+      <c r="BE5" s="39"/>
+      <c r="BF5" s="39"/>
+      <c r="BG5" s="39"/>
+      <c r="BH5" s="39"/>
+      <c r="BI5" s="39"/>
+      <c r="BJ5" s="39"/>
+      <c r="BK5" s="39"/>
+      <c r="BL5" s="39"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
+      <c r="BO5" s="39"/>
+      <c r="BP5" s="39"/>
+      <c r="BQ5" s="39"/>
+      <c r="BR5" s="39"/>
+      <c r="BS5" s="39"/>
+      <c r="BT5" s="39"/>
+      <c r="BU5" s="39"/>
+      <c r="BV5" s="39"/>
+      <c r="BW5" s="39"/>
+      <c r="BX5" s="39"/>
+      <c r="BY5" s="39"/>
+      <c r="BZ5" s="39"/>
+      <c r="CA5" s="39"/>
+      <c r="CB5" s="39"/>
+      <c r="CC5" s="39"/>
+      <c r="CD5" s="39"/>
+      <c r="CE5" s="39"/>
+      <c r="CF5" s="39"/>
+      <c r="CG5" s="39"/>
+      <c r="CH5" s="39"/>
+      <c r="CI5" s="39"/>
+      <c r="CJ5" s="39"/>
+      <c r="CK5" s="39"/>
+      <c r="CL5" s="39"/>
+      <c r="CM5" s="39"/>
+      <c r="CN5" s="39"/>
+      <c r="CO5" s="39"/>
+      <c r="CP5" s="39"/>
+      <c r="CQ5" s="39"/>
+      <c r="CR5" s="39"/>
+      <c r="CS5" s="39"/>
+      <c r="CT5" s="39"/>
+      <c r="CU5" s="39"/>
+      <c r="CV5" s="39"/>
+      <c r="CW5" s="39"/>
+      <c r="CX5" s="39"/>
+      <c r="CY5" s="39"/>
+      <c r="CZ5" s="39"/>
+      <c r="DA5" s="39"/>
+      <c r="DB5" s="39"/>
+      <c r="DC5" s="39"/>
+      <c r="DD5" s="39"/>
+      <c r="DE5" s="39"/>
+      <c r="DF5" s="39"/>
+      <c r="DG5" s="39"/>
+      <c r="DH5" s="39"/>
+      <c r="DI5" s="39"/>
+      <c r="DJ5" s="39"/>
+      <c r="DK5" s="39"/>
+      <c r="DL5" s="39"/>
+      <c r="DM5" s="39"/>
+      <c r="DN5" s="39"/>
+      <c r="DO5" s="39"/>
+      <c r="DP5" s="39"/>
+      <c r="DQ5" s="39"/>
+      <c r="DR5" s="39"/>
+      <c r="DS5" s="39"/>
+      <c r="DT5" s="39"/>
+      <c r="DU5" s="39"/>
+      <c r="DV5" s="39"/>
+      <c r="DW5" s="39"/>
+      <c r="DX5" s="39"/>
+      <c r="DY5" s="39"/>
+      <c r="DZ5" s="39"/>
+      <c r="EA5" s="39"/>
+      <c r="EB5" s="39"/>
+      <c r="EC5" s="39"/>
+      <c r="ED5" s="39"/>
+      <c r="EE5" s="39"/>
+      <c r="EF5" s="39"/>
+      <c r="EG5" s="39"/>
+      <c r="EH5" s="39"/>
+      <c r="EI5" s="39"/>
+      <c r="EJ5" s="39"/>
+      <c r="EK5" s="39"/>
+      <c r="EL5" s="39"/>
+      <c r="EM5" s="39"/>
+      <c r="EN5" s="39"/>
+      <c r="EO5" s="39"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>10</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="42"/>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="38"/>
-      <c r="AE6" s="38"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="38"/>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="38"/>
-      <c r="AN6" s="38"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="38"/>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="38"/>
-      <c r="AY6" s="38"/>
-      <c r="AZ6" s="38"/>
-      <c r="BA6" s="38"/>
-      <c r="BB6" s="38"/>
-      <c r="BC6" s="38"/>
-      <c r="BD6" s="38"/>
-      <c r="BE6" s="38"/>
-      <c r="BF6" s="38"/>
-      <c r="BG6" s="38"/>
-      <c r="BH6" s="38"/>
-      <c r="BI6" s="38"/>
-      <c r="BJ6" s="38"/>
-      <c r="BK6" s="38"/>
-      <c r="BL6" s="38"/>
-      <c r="BM6" s="38"/>
-      <c r="BN6" s="38"/>
-      <c r="BO6" s="38"/>
-      <c r="BP6" s="38"/>
-      <c r="BQ6" s="38"/>
-      <c r="BR6" s="38"/>
-      <c r="BS6" s="38"/>
-      <c r="BT6" s="38"/>
-      <c r="BU6" s="38"/>
-      <c r="BV6" s="38"/>
-      <c r="BW6" s="38"/>
-      <c r="BX6" s="38"/>
-      <c r="BY6" s="38"/>
-      <c r="BZ6" s="38"/>
-      <c r="CA6" s="38"/>
-      <c r="CB6" s="38"/>
-      <c r="CC6" s="38"/>
-      <c r="CD6" s="38"/>
-      <c r="CE6" s="38"/>
-      <c r="CF6" s="38"/>
-      <c r="CG6" s="38"/>
-      <c r="CH6" s="38"/>
-      <c r="CI6" s="38"/>
-      <c r="CJ6" s="38"/>
-      <c r="CK6" s="38"/>
-      <c r="CL6" s="38"/>
-      <c r="CM6" s="38"/>
-      <c r="CN6" s="38"/>
-      <c r="CO6" s="38"/>
-      <c r="CP6" s="38"/>
-      <c r="CQ6" s="38"/>
-      <c r="CR6" s="38"/>
-      <c r="CS6" s="38"/>
-      <c r="CT6" s="38"/>
-      <c r="CU6" s="38"/>
-      <c r="CV6" s="38"/>
-      <c r="CW6" s="38"/>
-      <c r="CX6" s="38"/>
-      <c r="CY6" s="38"/>
-      <c r="CZ6" s="38"/>
-      <c r="DA6" s="38"/>
-      <c r="DB6" s="38"/>
-      <c r="DC6" s="38"/>
-      <c r="DD6" s="38"/>
-      <c r="DE6" s="38"/>
-      <c r="DF6" s="38"/>
-      <c r="DG6" s="38"/>
-      <c r="DH6" s="38"/>
-      <c r="DI6" s="38"/>
-      <c r="DJ6" s="38"/>
-      <c r="DK6" s="38"/>
-      <c r="DL6" s="38"/>
-      <c r="DM6" s="38"/>
-      <c r="DN6" s="38"/>
-      <c r="DO6" s="38"/>
-      <c r="DP6" s="38"/>
-      <c r="DQ6" s="38"/>
-      <c r="DR6" s="38"/>
-      <c r="DS6" s="38"/>
-      <c r="DT6" s="38"/>
-      <c r="DU6" s="38"/>
-      <c r="DV6" s="38"/>
-      <c r="DW6" s="38"/>
-      <c r="DX6" s="38"/>
-      <c r="DY6" s="38"/>
-      <c r="DZ6" s="38"/>
-      <c r="EA6" s="38"/>
-      <c r="EB6" s="38"/>
-      <c r="EC6" s="38"/>
-      <c r="ED6" s="38"/>
-      <c r="EE6" s="38"/>
-      <c r="EF6" s="38"/>
-      <c r="EG6" s="38"/>
-      <c r="EH6" s="38"/>
-      <c r="EI6" s="38"/>
-      <c r="EJ6" s="38"/>
-      <c r="EK6" s="38"/>
-      <c r="EL6" s="38"/>
-      <c r="EM6" s="38"/>
-      <c r="EN6" s="38"/>
-      <c r="EO6" s="38"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="39"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="39"/>
+      <c r="AQ6" s="39"/>
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="39"/>
+      <c r="AU6" s="39"/>
+      <c r="AV6" s="39"/>
+      <c r="AW6" s="39"/>
+      <c r="AX6" s="39"/>
+      <c r="AY6" s="39"/>
+      <c r="AZ6" s="39"/>
+      <c r="BA6" s="39"/>
+      <c r="BB6" s="39"/>
+      <c r="BC6" s="39"/>
+      <c r="BD6" s="39"/>
+      <c r="BE6" s="39"/>
+      <c r="BF6" s="39"/>
+      <c r="BG6" s="39"/>
+      <c r="BH6" s="39"/>
+      <c r="BI6" s="39"/>
+      <c r="BJ6" s="39"/>
+      <c r="BK6" s="39"/>
+      <c r="BL6" s="39"/>
+      <c r="BM6" s="39"/>
+      <c r="BN6" s="39"/>
+      <c r="BO6" s="39"/>
+      <c r="BP6" s="39"/>
+      <c r="BQ6" s="39"/>
+      <c r="BR6" s="39"/>
+      <c r="BS6" s="39"/>
+      <c r="BT6" s="39"/>
+      <c r="BU6" s="39"/>
+      <c r="BV6" s="39"/>
+      <c r="BW6" s="39"/>
+      <c r="BX6" s="39"/>
+      <c r="BY6" s="39"/>
+      <c r="BZ6" s="39"/>
+      <c r="CA6" s="39"/>
+      <c r="CB6" s="39"/>
+      <c r="CC6" s="39"/>
+      <c r="CD6" s="39"/>
+      <c r="CE6" s="39"/>
+      <c r="CF6" s="39"/>
+      <c r="CG6" s="39"/>
+      <c r="CH6" s="39"/>
+      <c r="CI6" s="39"/>
+      <c r="CJ6" s="39"/>
+      <c r="CK6" s="39"/>
+      <c r="CL6" s="39"/>
+      <c r="CM6" s="39"/>
+      <c r="CN6" s="39"/>
+      <c r="CO6" s="39"/>
+      <c r="CP6" s="39"/>
+      <c r="CQ6" s="39"/>
+      <c r="CR6" s="39"/>
+      <c r="CS6" s="39"/>
+      <c r="CT6" s="39"/>
+      <c r="CU6" s="39"/>
+      <c r="CV6" s="39"/>
+      <c r="CW6" s="39"/>
+      <c r="CX6" s="39"/>
+      <c r="CY6" s="39"/>
+      <c r="CZ6" s="39"/>
+      <c r="DA6" s="39"/>
+      <c r="DB6" s="39"/>
+      <c r="DC6" s="39"/>
+      <c r="DD6" s="39"/>
+      <c r="DE6" s="39"/>
+      <c r="DF6" s="39"/>
+      <c r="DG6" s="39"/>
+      <c r="DH6" s="39"/>
+      <c r="DI6" s="39"/>
+      <c r="DJ6" s="39"/>
+      <c r="DK6" s="39"/>
+      <c r="DL6" s="39"/>
+      <c r="DM6" s="39"/>
+      <c r="DN6" s="39"/>
+      <c r="DO6" s="39"/>
+      <c r="DP6" s="39"/>
+      <c r="DQ6" s="39"/>
+      <c r="DR6" s="39"/>
+      <c r="DS6" s="39"/>
+      <c r="DT6" s="39"/>
+      <c r="DU6" s="39"/>
+      <c r="DV6" s="39"/>
+      <c r="DW6" s="39"/>
+      <c r="DX6" s="39"/>
+      <c r="DY6" s="39"/>
+      <c r="DZ6" s="39"/>
+      <c r="EA6" s="39"/>
+      <c r="EB6" s="39"/>
+      <c r="EC6" s="39"/>
+      <c r="ED6" s="39"/>
+      <c r="EE6" s="39"/>
+      <c r="EF6" s="39"/>
+      <c r="EG6" s="39"/>
+      <c r="EH6" s="39"/>
+      <c r="EI6" s="39"/>
+      <c r="EJ6" s="39"/>
+      <c r="EK6" s="39"/>
+      <c r="EL6" s="39"/>
+      <c r="EM6" s="39"/>
+      <c r="EN6" s="39"/>
+      <c r="EO6" s="39"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48">
+      <c r="B7" s="51"/>
+      <c r="C7" s="49">
         <v>30</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="43"/>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="39"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="39"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="39"/>
-      <c r="AQ7" s="39"/>
-      <c r="AR7" s="39"/>
-      <c r="AS7" s="39"/>
-      <c r="AT7" s="39"/>
-      <c r="AU7" s="39"/>
-      <c r="AV7" s="39"/>
-      <c r="AW7" s="39"/>
-      <c r="AX7" s="39"/>
-      <c r="AY7" s="39"/>
-      <c r="AZ7" s="39"/>
-      <c r="BA7" s="39"/>
-      <c r="BB7" s="39"/>
-      <c r="BC7" s="39"/>
-      <c r="BD7" s="39"/>
-      <c r="BE7" s="39"/>
-      <c r="BF7" s="39"/>
-      <c r="BG7" s="39"/>
-      <c r="BH7" s="39"/>
-      <c r="BI7" s="39"/>
-      <c r="BJ7" s="39"/>
-      <c r="BK7" s="39"/>
-      <c r="BL7" s="39"/>
-      <c r="BM7" s="39"/>
-      <c r="BN7" s="39"/>
-      <c r="BO7" s="39"/>
-      <c r="BP7" s="39"/>
-      <c r="BQ7" s="39"/>
-      <c r="BR7" s="39"/>
-      <c r="BS7" s="39"/>
-      <c r="BT7" s="39"/>
-      <c r="BU7" s="39"/>
-      <c r="BV7" s="39"/>
-      <c r="BW7" s="39"/>
-      <c r="BX7" s="39"/>
-      <c r="BY7" s="39"/>
-      <c r="BZ7" s="39"/>
-      <c r="CA7" s="39"/>
-      <c r="CB7" s="39"/>
-      <c r="CC7" s="39"/>
-      <c r="CD7" s="39"/>
-      <c r="CE7" s="39"/>
-      <c r="CF7" s="39"/>
-      <c r="CG7" s="39"/>
-      <c r="CH7" s="39"/>
-      <c r="CI7" s="39"/>
-      <c r="CJ7" s="39"/>
-      <c r="CK7" s="39"/>
-      <c r="CL7" s="39"/>
-      <c r="CM7" s="39"/>
-      <c r="CN7" s="39"/>
-      <c r="CO7" s="39"/>
-      <c r="CP7" s="39"/>
-      <c r="CQ7" s="39"/>
-      <c r="CR7" s="39"/>
-      <c r="CS7" s="39"/>
-      <c r="CT7" s="39"/>
-      <c r="CU7" s="39"/>
-      <c r="CV7" s="39"/>
-      <c r="CW7" s="39"/>
-      <c r="CX7" s="39"/>
-      <c r="CY7" s="39"/>
-      <c r="CZ7" s="39"/>
-      <c r="DA7" s="39"/>
-      <c r="DB7" s="39"/>
-      <c r="DC7" s="39"/>
-      <c r="DD7" s="39"/>
-      <c r="DE7" s="39"/>
-      <c r="DF7" s="39"/>
-      <c r="DG7" s="39"/>
-      <c r="DH7" s="39"/>
-      <c r="DI7" s="39"/>
-      <c r="DJ7" s="39"/>
-      <c r="DK7" s="39"/>
-      <c r="DL7" s="39"/>
-      <c r="DM7" s="39"/>
-      <c r="DN7" s="39"/>
-      <c r="DO7" s="39"/>
-      <c r="DP7" s="39"/>
-      <c r="DQ7" s="39"/>
-      <c r="DR7" s="39"/>
-      <c r="DS7" s="39"/>
-      <c r="DT7" s="39"/>
-      <c r="DU7" s="39"/>
-      <c r="DV7" s="39"/>
-      <c r="DW7" s="39"/>
-      <c r="DX7" s="39"/>
-      <c r="DY7" s="39"/>
-      <c r="DZ7" s="39"/>
-      <c r="EA7" s="39"/>
-      <c r="EB7" s="39"/>
-      <c r="EC7" s="39"/>
-      <c r="ED7" s="39"/>
-      <c r="EE7" s="39"/>
-      <c r="EF7" s="39"/>
-      <c r="EG7" s="39"/>
-      <c r="EH7" s="39"/>
-      <c r="EI7" s="39"/>
-      <c r="EJ7" s="39"/>
-      <c r="EK7" s="39"/>
-      <c r="EL7" s="39"/>
-      <c r="EM7" s="39"/>
-      <c r="EN7" s="39"/>
-      <c r="EO7" s="39"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="44"/>
+      <c r="AB7" s="44"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
+      <c r="BA7" s="40"/>
+      <c r="BB7" s="40"/>
+      <c r="BC7" s="40"/>
+      <c r="BD7" s="40"/>
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="40"/>
+      <c r="BJ7" s="40"/>
+      <c r="BK7" s="40"/>
+      <c r="BL7" s="40"/>
+      <c r="BM7" s="40"/>
+      <c r="BN7" s="40"/>
+      <c r="BO7" s="40"/>
+      <c r="BP7" s="40"/>
+      <c r="BQ7" s="40"/>
+      <c r="BR7" s="40"/>
+      <c r="BS7" s="40"/>
+      <c r="BT7" s="40"/>
+      <c r="BU7" s="40"/>
+      <c r="BV7" s="40"/>
+      <c r="BW7" s="40"/>
+      <c r="BX7" s="40"/>
+      <c r="BY7" s="40"/>
+      <c r="BZ7" s="40"/>
+      <c r="CA7" s="40"/>
+      <c r="CB7" s="40"/>
+      <c r="CC7" s="40"/>
+      <c r="CD7" s="40"/>
+      <c r="CE7" s="40"/>
+      <c r="CF7" s="40"/>
+      <c r="CG7" s="40"/>
+      <c r="CH7" s="40"/>
+      <c r="CI7" s="40"/>
+      <c r="CJ7" s="40"/>
+      <c r="CK7" s="40"/>
+      <c r="CL7" s="40"/>
+      <c r="CM7" s="40"/>
+      <c r="CN7" s="40"/>
+      <c r="CO7" s="40"/>
+      <c r="CP7" s="40"/>
+      <c r="CQ7" s="40"/>
+      <c r="CR7" s="40"/>
+      <c r="CS7" s="40"/>
+      <c r="CT7" s="40"/>
+      <c r="CU7" s="40"/>
+      <c r="CV7" s="40"/>
+      <c r="CW7" s="40"/>
+      <c r="CX7" s="40"/>
+      <c r="CY7" s="40"/>
+      <c r="CZ7" s="40"/>
+      <c r="DA7" s="40"/>
+      <c r="DB7" s="40"/>
+      <c r="DC7" s="40"/>
+      <c r="DD7" s="40"/>
+      <c r="DE7" s="40"/>
+      <c r="DF7" s="40"/>
+      <c r="DG7" s="40"/>
+      <c r="DH7" s="40"/>
+      <c r="DI7" s="40"/>
+      <c r="DJ7" s="40"/>
+      <c r="DK7" s="40"/>
+      <c r="DL7" s="40"/>
+      <c r="DM7" s="40"/>
+      <c r="DN7" s="40"/>
+      <c r="DO7" s="40"/>
+      <c r="DP7" s="40"/>
+      <c r="DQ7" s="40"/>
+      <c r="DR7" s="40"/>
+      <c r="DS7" s="40"/>
+      <c r="DT7" s="40"/>
+      <c r="DU7" s="40"/>
+      <c r="DV7" s="40"/>
+      <c r="DW7" s="40"/>
+      <c r="DX7" s="40"/>
+      <c r="DY7" s="40"/>
+      <c r="DZ7" s="40"/>
+      <c r="EA7" s="40"/>
+      <c r="EB7" s="40"/>
+      <c r="EC7" s="40"/>
+      <c r="ED7" s="40"/>
+      <c r="EE7" s="40"/>
+      <c r="EF7" s="40"/>
+      <c r="EG7" s="40"/>
+      <c r="EH7" s="40"/>
+      <c r="EI7" s="40"/>
+      <c r="EJ7" s="40"/>
+      <c r="EK7" s="40"/>
+      <c r="EL7" s="40"/>
+      <c r="EM7" s="40"/>
+      <c r="EN7" s="40"/>
+      <c r="EO7" s="40"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52">
+      <c r="B8" s="52"/>
+      <c r="C8" s="53">
         <v>150</v>
       </c>
-      <c r="D8" s="46"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="53">
+      <c r="F8" s="54">
         <v>1</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="54">
         <v>2</v>
       </c>
-      <c r="H8" s="53">
+      <c r="H8" s="54">
         <v>3</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="54">
         <v>4</v>
       </c>
-      <c r="J8" s="53">
+      <c r="J8" s="54">
         <v>5</v>
       </c>
-      <c r="K8" s="53">
+      <c r="K8" s="54">
         <v>6</v>
       </c>
-      <c r="L8" s="53">
+      <c r="L8" s="54">
         <v>7</v>
       </c>
-      <c r="M8" s="53">
+      <c r="M8" s="54">
         <v>8</v>
       </c>
-      <c r="N8" s="53">
+      <c r="N8" s="54">
         <v>9</v>
       </c>
-      <c r="O8" s="53">
+      <c r="O8" s="54">
         <v>10</v>
       </c>
-      <c r="P8" s="53">
+      <c r="P8" s="54">
         <v>11</v>
       </c>
-      <c r="Q8" s="53">
+      <c r="Q8" s="54">
         <v>12</v>
       </c>
-      <c r="R8" s="53">
+      <c r="R8" s="54">
         <v>13</v>
       </c>
-      <c r="S8" s="53">
+      <c r="S8" s="54">
         <v>14</v>
       </c>
-      <c r="T8" s="53">
+      <c r="T8" s="54">
         <v>15</v>
       </c>
-      <c r="U8" s="53">
+      <c r="U8" s="54">
         <v>16</v>
       </c>
-      <c r="V8" s="53">
+      <c r="V8" s="54">
         <v>17</v>
       </c>
-      <c r="W8" s="53">
+      <c r="W8" s="54">
         <v>18</v>
       </c>
-      <c r="X8" s="53">
+      <c r="X8" s="54">
         <v>19</v>
       </c>
-      <c r="Y8" s="53">
+      <c r="Y8" s="54">
         <v>20</v>
       </c>
-      <c r="Z8" s="53">
+      <c r="Z8" s="54">
         <v>21</v>
       </c>
-      <c r="AA8" s="53">
+      <c r="AA8" s="54">
         <v>22</v>
       </c>
-      <c r="AB8" s="53">
+      <c r="AB8" s="54">
         <v>23</v>
       </c>
-      <c r="AC8" s="53">
+      <c r="AC8" s="54">
         <v>24</v>
       </c>
-      <c r="AD8" s="53">
+      <c r="AD8" s="54">
         <v>25</v>
       </c>
-      <c r="AE8" s="53">
+      <c r="AE8" s="54">
         <v>26</v>
       </c>
-      <c r="AF8" s="53">
+      <c r="AF8" s="54">
         <v>27</v>
       </c>
-      <c r="AG8" s="53">
+      <c r="AG8" s="54">
         <v>28</v>
       </c>
-      <c r="AH8" s="53">
+      <c r="AH8" s="54">
         <v>29</v>
       </c>
-      <c r="AI8" s="53">
+      <c r="AI8" s="54">
         <v>30</v>
       </c>
-      <c r="AJ8" s="53">
+      <c r="AJ8" s="54">
         <v>31</v>
       </c>
-      <c r="AK8" s="53">
+      <c r="AK8" s="54">
         <v>32</v>
       </c>
-      <c r="AL8" s="53">
+      <c r="AL8" s="54">
         <v>33</v>
       </c>
-      <c r="AM8" s="53">
+      <c r="AM8" s="54">
         <v>34</v>
       </c>
-      <c r="AN8" s="53">
+      <c r="AN8" s="54">
         <v>35</v>
       </c>
-      <c r="AO8" s="53">
+      <c r="AO8" s="54">
         <v>36</v>
       </c>
-      <c r="AP8" s="53">
+      <c r="AP8" s="54">
         <v>37</v>
       </c>
-      <c r="AQ8" s="53">
+      <c r="AQ8" s="54">
         <v>38</v>
       </c>
-      <c r="AR8" s="53">
+      <c r="AR8" s="54">
         <v>39</v>
       </c>
-      <c r="AS8" s="53">
+      <c r="AS8" s="54">
         <v>40</v>
       </c>
-      <c r="AT8" s="53">
+      <c r="AT8" s="54">
         <v>41</v>
       </c>
-      <c r="AU8" s="53">
+      <c r="AU8" s="54">
         <v>42</v>
       </c>
-      <c r="AV8" s="53">
+      <c r="AV8" s="54">
         <v>43</v>
       </c>
-      <c r="AW8" s="53">
+      <c r="AW8" s="54">
         <v>44</v>
       </c>
-      <c r="AX8" s="53">
+      <c r="AX8" s="54">
         <v>45</v>
       </c>
-      <c r="AY8" s="53">
+      <c r="AY8" s="54">
         <v>46</v>
       </c>
-      <c r="AZ8" s="53">
+      <c r="AZ8" s="54">
         <v>47</v>
       </c>
-      <c r="BA8" s="53">
+      <c r="BA8" s="54">
         <v>48</v>
       </c>
-      <c r="BB8" s="53">
+      <c r="BB8" s="54">
         <v>49</v>
       </c>
-      <c r="BC8" s="53">
+      <c r="BC8" s="54">
         <v>50</v>
       </c>
-      <c r="BD8" s="53">
+      <c r="BD8" s="54">
         <v>51</v>
       </c>
-      <c r="BE8" s="53">
+      <c r="BE8" s="54">
         <v>52</v>
       </c>
-      <c r="BF8" s="53">
+      <c r="BF8" s="54">
         <v>53</v>
       </c>
-      <c r="BG8" s="53">
+      <c r="BG8" s="54">
         <v>54</v>
       </c>
-      <c r="BH8" s="53">
+      <c r="BH8" s="54">
         <v>55</v>
       </c>
-      <c r="BI8" s="53">
+      <c r="BI8" s="54">
         <v>56</v>
       </c>
-      <c r="BJ8" s="53">
+      <c r="BJ8" s="54">
         <v>57</v>
       </c>
-      <c r="BK8" s="53">
+      <c r="BK8" s="54">
         <v>58</v>
       </c>
-      <c r="BL8" s="53">
+      <c r="BL8" s="54">
         <v>59</v>
       </c>
-      <c r="BM8" s="53">
+      <c r="BM8" s="54">
         <v>60</v>
       </c>
-      <c r="BN8" s="53">
+      <c r="BN8" s="54">
         <v>61</v>
       </c>
-      <c r="BO8" s="53">
+      <c r="BO8" s="54">
         <v>62</v>
       </c>
-      <c r="BP8" s="53">
+      <c r="BP8" s="54">
         <v>63</v>
       </c>
-      <c r="BQ8" s="53">
+      <c r="BQ8" s="54">
         <v>64</v>
       </c>
-      <c r="BR8" s="53">
+      <c r="BR8" s="54">
         <v>65</v>
       </c>
-      <c r="BS8" s="53">
+      <c r="BS8" s="54">
         <v>66</v>
       </c>
-      <c r="BT8" s="53">
+      <c r="BT8" s="54">
         <v>67</v>
       </c>
-      <c r="BU8" s="53">
+      <c r="BU8" s="54">
         <v>68</v>
       </c>
-      <c r="BV8" s="53">
+      <c r="BV8" s="54">
         <v>69</v>
       </c>
-      <c r="BW8" s="53">
+      <c r="BW8" s="54">
         <v>70</v>
       </c>
-      <c r="BX8" s="53">
+      <c r="BX8" s="54">
         <v>71</v>
       </c>
-      <c r="BY8" s="53">
+      <c r="BY8" s="54">
         <v>72</v>
       </c>
-      <c r="BZ8" s="53">
+      <c r="BZ8" s="54">
         <v>73</v>
       </c>
-      <c r="CA8" s="53">
+      <c r="CA8" s="54">
         <v>74</v>
       </c>
-      <c r="CB8" s="53">
+      <c r="CB8" s="54">
         <v>75</v>
       </c>
-      <c r="CC8" s="53">
+      <c r="CC8" s="54">
         <v>76</v>
       </c>
-      <c r="CD8" s="53">
+      <c r="CD8" s="54">
         <v>77</v>
       </c>
-      <c r="CE8" s="53">
+      <c r="CE8" s="54">
         <v>78</v>
       </c>
-      <c r="CF8" s="53">
+      <c r="CF8" s="54">
         <v>79</v>
       </c>
-      <c r="CG8" s="53">
+      <c r="CG8" s="54">
         <v>80</v>
       </c>
-      <c r="CH8" s="53">
+      <c r="CH8" s="54">
         <v>81</v>
       </c>
-      <c r="CI8" s="53">
+      <c r="CI8" s="54">
         <v>82</v>
       </c>
-      <c r="CJ8" s="53">
+      <c r="CJ8" s="54">
         <v>83</v>
       </c>
-      <c r="CK8" s="53">
+      <c r="CK8" s="54">
         <v>84</v>
       </c>
-      <c r="CL8" s="53">
+      <c r="CL8" s="54">
         <v>85</v>
       </c>
-      <c r="CM8" s="53">
+      <c r="CM8" s="54">
         <v>86</v>
       </c>
-      <c r="CN8" s="53">
+      <c r="CN8" s="54">
         <v>87</v>
       </c>
-      <c r="CO8" s="53">
+      <c r="CO8" s="54">
         <v>88</v>
       </c>
-      <c r="CP8" s="53">
+      <c r="CP8" s="54">
         <v>89</v>
       </c>
-      <c r="CQ8" s="53">
+      <c r="CQ8" s="54">
         <v>90</v>
       </c>
-      <c r="CR8" s="53">
+      <c r="CR8" s="54">
         <v>91</v>
       </c>
-      <c r="CS8" s="53">
+      <c r="CS8" s="54">
         <v>92</v>
       </c>
-      <c r="CT8" s="53">
+      <c r="CT8" s="54">
         <v>93</v>
       </c>
-      <c r="CU8" s="53">
+      <c r="CU8" s="54">
         <v>94</v>
       </c>
-      <c r="CV8" s="53">
+      <c r="CV8" s="54">
         <v>95</v>
       </c>
-      <c r="CW8" s="53">
+      <c r="CW8" s="54">
         <v>96</v>
       </c>
-      <c r="CX8" s="53">
+      <c r="CX8" s="54">
         <v>97</v>
       </c>
-      <c r="CY8" s="53">
+      <c r="CY8" s="54">
         <v>98</v>
       </c>
-      <c r="CZ8" s="53">
+      <c r="CZ8" s="54">
         <v>99</v>
       </c>
-      <c r="DA8" s="53">
+      <c r="DA8" s="54">
         <v>100</v>
       </c>
-      <c r="DB8" s="53">
+      <c r="DB8" s="54">
         <v>101</v>
       </c>
-      <c r="DC8" s="53">
+      <c r="DC8" s="54">
         <v>102</v>
       </c>
-      <c r="DD8" s="53">
+      <c r="DD8" s="54">
         <v>103</v>
       </c>
-      <c r="DE8" s="53">
+      <c r="DE8" s="54">
         <v>104</v>
       </c>
-      <c r="DF8" s="53">
+      <c r="DF8" s="54">
         <v>105</v>
       </c>
-      <c r="DG8" s="53">
+      <c r="DG8" s="54">
         <v>106</v>
       </c>
-      <c r="DH8" s="53">
+      <c r="DH8" s="54">
         <v>107</v>
       </c>
-      <c r="DI8" s="53">
+      <c r="DI8" s="54">
         <v>108</v>
       </c>
-      <c r="DJ8" s="53">
+      <c r="DJ8" s="54">
         <v>109</v>
       </c>
-      <c r="DK8" s="53">
+      <c r="DK8" s="54">
         <v>110</v>
       </c>
-      <c r="DL8" s="53">
+      <c r="DL8" s="54">
         <v>111</v>
       </c>
-      <c r="DM8" s="53">
+      <c r="DM8" s="54">
         <v>112</v>
       </c>
-      <c r="DN8" s="53">
+      <c r="DN8" s="54">
         <v>113</v>
       </c>
-      <c r="DO8" s="53">
+      <c r="DO8" s="54">
         <v>114</v>
       </c>
-      <c r="DP8" s="53">
+      <c r="DP8" s="54">
         <v>115</v>
       </c>
-      <c r="DQ8" s="53">
+      <c r="DQ8" s="54">
         <v>116</v>
       </c>
-      <c r="DR8" s="53">
+      <c r="DR8" s="54">
         <v>117</v>
       </c>
-      <c r="DS8" s="53">
+      <c r="DS8" s="54">
         <v>118</v>
       </c>
-      <c r="DT8" s="53">
+      <c r="DT8" s="54">
         <v>119</v>
       </c>
-      <c r="DU8" s="53">
+      <c r="DU8" s="54">
         <v>120</v>
       </c>
-      <c r="DV8" s="53">
+      <c r="DV8" s="54">
         <v>121</v>
       </c>
-      <c r="DW8" s="53">
+      <c r="DW8" s="54">
         <v>122</v>
       </c>
-      <c r="DX8" s="53">
+      <c r="DX8" s="54">
         <v>123</v>
       </c>
-      <c r="DY8" s="53">
+      <c r="DY8" s="54">
         <v>124</v>
       </c>
-      <c r="DZ8" s="53">
+      <c r="DZ8" s="54">
         <v>125</v>
       </c>
-      <c r="EA8" s="53">
+      <c r="EA8" s="54">
         <v>126</v>
       </c>
-      <c r="EB8" s="53">
+      <c r="EB8" s="54">
         <v>127</v>
       </c>
-      <c r="EC8" s="53">
+      <c r="EC8" s="54">
         <v>128</v>
       </c>
-      <c r="ED8" s="53">
+      <c r="ED8" s="54">
         <v>129</v>
       </c>
-      <c r="EE8" s="53">
+      <c r="EE8" s="54">
         <v>130</v>
       </c>
-      <c r="EF8" s="53">
+      <c r="EF8" s="54">
         <v>131</v>
       </c>
-      <c r="EG8" s="53">
+      <c r="EG8" s="54">
         <v>132</v>
       </c>
-      <c r="EH8" s="53">
+      <c r="EH8" s="54">
         <v>133</v>
       </c>
-      <c r="EI8" s="53">
+      <c r="EI8" s="54">
         <v>134</v>
       </c>
-      <c r="EJ8" s="53">
+      <c r="EJ8" s="54">
         <v>135</v>
       </c>
-      <c r="EK8" s="53">
+      <c r="EK8" s="54">
         <v>136</v>
       </c>
-      <c r="EL8" s="53">
+      <c r="EL8" s="54">
         <v>137</v>
       </c>
-      <c r="EM8" s="53">
+      <c r="EM8" s="54">
         <v>138</v>
       </c>
-      <c r="EN8" s="53">
+      <c r="EN8" s="54">
         <v>139</v>
       </c>
-      <c r="EO8" s="53">
+      <c r="EO8" s="54">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="56"/>
+      <c r="D9" s="57"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="54"/>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="54"/>
-      <c r="AB9" s="54"/>
-      <c r="AC9" s="54"/>
-      <c r="AD9" s="54"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="54"/>
-      <c r="AH9" s="54"/>
-      <c r="AI9" s="54"/>
-      <c r="AJ9" s="54"/>
-      <c r="AK9" s="54"/>
-      <c r="AL9" s="54"/>
-      <c r="AM9" s="54"/>
-      <c r="AN9" s="54"/>
-      <c r="AO9" s="54"/>
-      <c r="AP9" s="54"/>
-      <c r="AQ9" s="54"/>
-      <c r="AR9" s="54"/>
-      <c r="AS9" s="54"/>
-      <c r="AT9" s="54"/>
-      <c r="AU9" s="54"/>
-      <c r="AV9" s="54"/>
-      <c r="AW9" s="54"/>
-      <c r="AX9" s="54"/>
-      <c r="AY9" s="54"/>
-      <c r="AZ9" s="54"/>
-      <c r="BA9" s="54"/>
-      <c r="BB9" s="54"/>
-      <c r="BC9" s="54"/>
-      <c r="BD9" s="54"/>
-      <c r="BE9" s="54"/>
-      <c r="BF9" s="54"/>
-      <c r="BG9" s="54"/>
-      <c r="BH9" s="54"/>
-      <c r="BI9" s="54"/>
-      <c r="BJ9" s="54"/>
-      <c r="BK9" s="54"/>
-      <c r="BL9" s="54"/>
-      <c r="BM9" s="54"/>
-      <c r="BN9" s="54"/>
-      <c r="BO9" s="54"/>
-      <c r="BP9" s="54"/>
-      <c r="BQ9" s="54"/>
-      <c r="BR9" s="54"/>
-      <c r="BS9" s="54"/>
-      <c r="BT9" s="54"/>
-      <c r="BU9" s="54"/>
-      <c r="BV9" s="54"/>
-      <c r="BW9" s="54"/>
-      <c r="BX9" s="54"/>
-      <c r="BY9" s="54"/>
-      <c r="BZ9" s="54"/>
-      <c r="CA9" s="54"/>
-      <c r="CB9" s="54"/>
-      <c r="CC9" s="54"/>
-      <c r="CD9" s="54"/>
-      <c r="CE9" s="54"/>
-      <c r="CF9" s="54"/>
-      <c r="CG9" s="54"/>
-      <c r="CH9" s="54"/>
-      <c r="CI9" s="54"/>
-      <c r="CJ9" s="54"/>
-      <c r="CK9" s="54"/>
-      <c r="CL9" s="54"/>
-      <c r="CM9" s="54"/>
-      <c r="CN9" s="54"/>
-      <c r="CO9" s="54"/>
-      <c r="CP9" s="54"/>
-      <c r="CQ9" s="54"/>
-      <c r="CR9" s="54"/>
-      <c r="CS9" s="54"/>
-      <c r="CT9" s="54"/>
-      <c r="CU9" s="54"/>
-      <c r="CV9" s="54"/>
-      <c r="CW9" s="54"/>
-      <c r="CX9" s="54"/>
-      <c r="CY9" s="54"/>
-      <c r="CZ9" s="54"/>
-      <c r="DA9" s="54"/>
-      <c r="DB9" s="54"/>
-      <c r="DC9" s="54"/>
-      <c r="DD9" s="54"/>
-      <c r="DE9" s="54"/>
-      <c r="DF9" s="54"/>
-      <c r="DG9" s="54"/>
-      <c r="DH9" s="54"/>
-      <c r="DI9" s="54"/>
-      <c r="DJ9" s="54"/>
-      <c r="DK9" s="54"/>
-      <c r="DL9" s="54"/>
-      <c r="DM9" s="54"/>
-      <c r="DN9" s="54"/>
-      <c r="DO9" s="54"/>
-      <c r="DP9" s="54"/>
-      <c r="DQ9" s="54"/>
-      <c r="DR9" s="54"/>
-      <c r="DS9" s="54"/>
-      <c r="DT9" s="54"/>
-      <c r="DU9" s="54"/>
-      <c r="DV9" s="54"/>
-      <c r="DW9" s="54"/>
-      <c r="DX9" s="54"/>
-      <c r="DY9" s="54"/>
-      <c r="DZ9" s="54"/>
-      <c r="EA9" s="54"/>
-      <c r="EB9" s="54"/>
-      <c r="EC9" s="54"/>
-      <c r="ED9" s="54"/>
-      <c r="EE9" s="54"/>
-      <c r="EF9" s="54"/>
-      <c r="EG9" s="54"/>
-      <c r="EH9" s="54"/>
-      <c r="EI9" s="54"/>
-      <c r="EJ9" s="54"/>
-      <c r="EK9" s="54"/>
-      <c r="EL9" s="54"/>
-      <c r="EM9" s="54"/>
-      <c r="EN9" s="54"/>
-      <c r="EO9" s="54"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="55"/>
+      <c r="U9" s="55"/>
+      <c r="V9" s="55"/>
+      <c r="W9" s="55"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="55"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="55"/>
+      <c r="AC9" s="55"/>
+      <c r="AD9" s="55"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="55"/>
+      <c r="AG9" s="55"/>
+      <c r="AH9" s="55"/>
+      <c r="AI9" s="55"/>
+      <c r="AJ9" s="55"/>
+      <c r="AK9" s="55"/>
+      <c r="AL9" s="55"/>
+      <c r="AM9" s="55"/>
+      <c r="AN9" s="55"/>
+      <c r="AO9" s="55"/>
+      <c r="AP9" s="55"/>
+      <c r="AQ9" s="55"/>
+      <c r="AR9" s="55"/>
+      <c r="AS9" s="55"/>
+      <c r="AT9" s="55"/>
+      <c r="AU9" s="55"/>
+      <c r="AV9" s="55"/>
+      <c r="AW9" s="55"/>
+      <c r="AX9" s="55"/>
+      <c r="AY9" s="55"/>
+      <c r="AZ9" s="55"/>
+      <c r="BA9" s="55"/>
+      <c r="BB9" s="55"/>
+      <c r="BC9" s="55"/>
+      <c r="BD9" s="55"/>
+      <c r="BE9" s="55"/>
+      <c r="BF9" s="55"/>
+      <c r="BG9" s="55"/>
+      <c r="BH9" s="55"/>
+      <c r="BI9" s="55"/>
+      <c r="BJ9" s="55"/>
+      <c r="BK9" s="55"/>
+      <c r="BL9" s="55"/>
+      <c r="BM9" s="55"/>
+      <c r="BN9" s="55"/>
+      <c r="BO9" s="55"/>
+      <c r="BP9" s="55"/>
+      <c r="BQ9" s="55"/>
+      <c r="BR9" s="55"/>
+      <c r="BS9" s="55"/>
+      <c r="BT9" s="55"/>
+      <c r="BU9" s="55"/>
+      <c r="BV9" s="55"/>
+      <c r="BW9" s="55"/>
+      <c r="BX9" s="55"/>
+      <c r="BY9" s="55"/>
+      <c r="BZ9" s="55"/>
+      <c r="CA9" s="55"/>
+      <c r="CB9" s="55"/>
+      <c r="CC9" s="55"/>
+      <c r="CD9" s="55"/>
+      <c r="CE9" s="55"/>
+      <c r="CF9" s="55"/>
+      <c r="CG9" s="55"/>
+      <c r="CH9" s="55"/>
+      <c r="CI9" s="55"/>
+      <c r="CJ9" s="55"/>
+      <c r="CK9" s="55"/>
+      <c r="CL9" s="55"/>
+      <c r="CM9" s="55"/>
+      <c r="CN9" s="55"/>
+      <c r="CO9" s="55"/>
+      <c r="CP9" s="55"/>
+      <c r="CQ9" s="55"/>
+      <c r="CR9" s="55"/>
+      <c r="CS9" s="55"/>
+      <c r="CT9" s="55"/>
+      <c r="CU9" s="55"/>
+      <c r="CV9" s="55"/>
+      <c r="CW9" s="55"/>
+      <c r="CX9" s="55"/>
+      <c r="CY9" s="55"/>
+      <c r="CZ9" s="55"/>
+      <c r="DA9" s="55"/>
+      <c r="DB9" s="55"/>
+      <c r="DC9" s="55"/>
+      <c r="DD9" s="55"/>
+      <c r="DE9" s="55"/>
+      <c r="DF9" s="55"/>
+      <c r="DG9" s="55"/>
+      <c r="DH9" s="55"/>
+      <c r="DI9" s="55"/>
+      <c r="DJ9" s="55"/>
+      <c r="DK9" s="55"/>
+      <c r="DL9" s="55"/>
+      <c r="DM9" s="55"/>
+      <c r="DN9" s="55"/>
+      <c r="DO9" s="55"/>
+      <c r="DP9" s="55"/>
+      <c r="DQ9" s="55"/>
+      <c r="DR9" s="55"/>
+      <c r="DS9" s="55"/>
+      <c r="DT9" s="55"/>
+      <c r="DU9" s="55"/>
+      <c r="DV9" s="55"/>
+      <c r="DW9" s="55"/>
+      <c r="DX9" s="55"/>
+      <c r="DY9" s="55"/>
+      <c r="DZ9" s="55"/>
+      <c r="EA9" s="55"/>
+      <c r="EB9" s="55"/>
+      <c r="EC9" s="55"/>
+      <c r="ED9" s="55"/>
+      <c r="EE9" s="55"/>
+      <c r="EF9" s="55"/>
+      <c r="EG9" s="55"/>
+      <c r="EH9" s="55"/>
+      <c r="EI9" s="55"/>
+      <c r="EJ9" s="55"/>
+      <c r="EK9" s="55"/>
+      <c r="EL9" s="55"/>
+      <c r="EM9" s="55"/>
+      <c r="EN9" s="55"/>
+      <c r="EO9" s="55"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="56"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="10"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
@@ -3001,7 +3012,9 @@
       <c r="BD10" s="12"/>
       <c r="BE10" s="12"/>
       <c r="BF10" s="12"/>
-      <c r="BG10" s="12"/>
+      <c r="BG10" s="12">
+        <v>0</v>
+      </c>
       <c r="BH10" s="12"/>
       <c r="BI10" s="12"/>
       <c r="BJ10" s="12"/>
@@ -3257,7 +3270,7 @@
       </c>
       <c r="D12" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="12"/>
@@ -3321,7 +3334,9 @@
       <c r="BD12" s="12"/>
       <c r="BE12" s="12"/>
       <c r="BF12" s="12"/>
-      <c r="BG12" s="12"/>
+      <c r="BG12" s="12">
+        <v>0</v>
+      </c>
       <c r="BH12" s="12"/>
       <c r="BI12" s="12"/>
       <c r="BJ12" s="12"/>
@@ -3421,7 +3436,7 @@
       </c>
       <c r="D13" s="15">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="12"/>
@@ -3501,7 +3516,9 @@
       <c r="BD13" s="12"/>
       <c r="BE13" s="12"/>
       <c r="BF13" s="12"/>
-      <c r="BG13" s="12"/>
+      <c r="BG13" s="12">
+        <v>0</v>
+      </c>
       <c r="BH13" s="12"/>
       <c r="BI13" s="12"/>
       <c r="BJ13" s="12"/>
@@ -3605,7 +3622,7 @@
       </c>
       <c r="D14" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="12"/>
@@ -3669,7 +3686,9 @@
       <c r="BD14" s="12"/>
       <c r="BE14" s="12"/>
       <c r="BF14" s="12"/>
-      <c r="BG14" s="12"/>
+      <c r="BG14" s="12">
+        <v>0</v>
+      </c>
       <c r="BH14" s="12"/>
       <c r="BI14" s="12"/>
       <c r="BJ14" s="12"/>
@@ -3769,7 +3788,7 @@
       </c>
       <c r="D15" s="15">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="12"/>
@@ -3843,7 +3862,9 @@
       <c r="BD15" s="12"/>
       <c r="BE15" s="12"/>
       <c r="BF15" s="12"/>
-      <c r="BG15" s="12"/>
+      <c r="BG15" s="12">
+        <v>0</v>
+      </c>
       <c r="BH15" s="12"/>
       <c r="BI15" s="12"/>
       <c r="BJ15" s="12"/>
@@ -3943,7 +3964,7 @@
       </c>
       <c r="D16" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="12"/>
@@ -4007,7 +4028,9 @@
       <c r="BD16" s="12"/>
       <c r="BE16" s="12"/>
       <c r="BF16" s="12"/>
-      <c r="BG16" s="12"/>
+      <c r="BG16" s="12">
+        <v>0</v>
+      </c>
       <c r="BH16" s="12"/>
       <c r="BI16" s="12"/>
       <c r="BJ16" s="12"/>
@@ -4205,113 +4228,113 @@
       <c r="AN17" s="12">
         <v>0</v>
       </c>
-      <c r="AO17" s="21" t="s">
+      <c r="AO17" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="22"/>
-      <c r="AQ17" s="22"/>
-      <c r="AR17" s="22"/>
-      <c r="AS17" s="22"/>
-      <c r="AT17" s="22"/>
-      <c r="AU17" s="22"/>
-      <c r="AV17" s="22"/>
-      <c r="AW17" s="22"/>
-      <c r="AX17" s="22"/>
-      <c r="AY17" s="22"/>
-      <c r="AZ17" s="22"/>
-      <c r="BA17" s="22"/>
-      <c r="BB17" s="22"/>
-      <c r="BC17" s="22"/>
-      <c r="BD17" s="22"/>
-      <c r="BE17" s="22"/>
-      <c r="BF17" s="22"/>
-      <c r="BG17" s="22"/>
-      <c r="BH17" s="22"/>
-      <c r="BI17" s="22"/>
-      <c r="BJ17" s="22"/>
-      <c r="BK17" s="22"/>
-      <c r="BL17" s="22"/>
-      <c r="BM17" s="22"/>
-      <c r="BN17" s="22"/>
-      <c r="BO17" s="22"/>
-      <c r="BP17" s="22"/>
-      <c r="BQ17" s="22"/>
-      <c r="BR17" s="22"/>
-      <c r="BS17" s="22"/>
-      <c r="BT17" s="22"/>
-      <c r="BU17" s="22"/>
-      <c r="BV17" s="22"/>
-      <c r="BW17" s="22"/>
-      <c r="BX17" s="22"/>
-      <c r="BY17" s="22"/>
-      <c r="BZ17" s="22"/>
-      <c r="CA17" s="22"/>
-      <c r="CB17" s="22"/>
-      <c r="CC17" s="22"/>
-      <c r="CD17" s="22"/>
-      <c r="CE17" s="22"/>
-      <c r="CF17" s="22"/>
-      <c r="CG17" s="22"/>
-      <c r="CH17" s="22"/>
-      <c r="CI17" s="22"/>
-      <c r="CJ17" s="22"/>
-      <c r="CK17" s="22"/>
-      <c r="CL17" s="22"/>
-      <c r="CM17" s="22"/>
-      <c r="CN17" s="22"/>
-      <c r="CO17" s="22"/>
-      <c r="CP17" s="22"/>
-      <c r="CQ17" s="22"/>
-      <c r="CR17" s="22"/>
-      <c r="CS17" s="22"/>
-      <c r="CT17" s="22"/>
-      <c r="CU17" s="22"/>
-      <c r="CV17" s="22"/>
-      <c r="CW17" s="22"/>
-      <c r="CX17" s="22"/>
-      <c r="CY17" s="22"/>
-      <c r="CZ17" s="22"/>
-      <c r="DA17" s="22"/>
-      <c r="DB17" s="22"/>
-      <c r="DC17" s="22"/>
-      <c r="DD17" s="22"/>
-      <c r="DE17" s="22"/>
-      <c r="DF17" s="22"/>
-      <c r="DG17" s="22"/>
-      <c r="DH17" s="22"/>
-      <c r="DI17" s="22"/>
-      <c r="DJ17" s="22"/>
-      <c r="DK17" s="22"/>
-      <c r="DL17" s="22"/>
-      <c r="DM17" s="22"/>
-      <c r="DN17" s="22"/>
-      <c r="DO17" s="22"/>
-      <c r="DP17" s="22"/>
-      <c r="DQ17" s="22"/>
-      <c r="DR17" s="22"/>
-      <c r="DS17" s="22"/>
-      <c r="DT17" s="22"/>
-      <c r="DU17" s="22"/>
-      <c r="DV17" s="22"/>
-      <c r="DW17" s="22"/>
-      <c r="DX17" s="22"/>
-      <c r="DY17" s="22"/>
-      <c r="DZ17" s="22"/>
-      <c r="EA17" s="22"/>
-      <c r="EB17" s="22"/>
-      <c r="EC17" s="22"/>
-      <c r="ED17" s="22"/>
-      <c r="EE17" s="22"/>
-      <c r="EF17" s="22"/>
-      <c r="EG17" s="22"/>
-      <c r="EH17" s="22"/>
-      <c r="EI17" s="22"/>
-      <c r="EJ17" s="22"/>
-      <c r="EK17" s="22"/>
-      <c r="EL17" s="22"/>
-      <c r="EM17" s="22"/>
-      <c r="EN17" s="22"/>
-      <c r="EO17" s="23"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="23"/>
+      <c r="AR17" s="23"/>
+      <c r="AS17" s="23"/>
+      <c r="AT17" s="23"/>
+      <c r="AU17" s="23"/>
+      <c r="AV17" s="23"/>
+      <c r="AW17" s="23"/>
+      <c r="AX17" s="23"/>
+      <c r="AY17" s="23"/>
+      <c r="AZ17" s="23"/>
+      <c r="BA17" s="23"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="23"/>
+      <c r="BD17" s="23"/>
+      <c r="BE17" s="23"/>
+      <c r="BF17" s="23"/>
+      <c r="BG17" s="23"/>
+      <c r="BH17" s="23"/>
+      <c r="BI17" s="23"/>
+      <c r="BJ17" s="23"/>
+      <c r="BK17" s="23"/>
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="23"/>
+      <c r="BP17" s="23"/>
+      <c r="BQ17" s="23"/>
+      <c r="BR17" s="23"/>
+      <c r="BS17" s="23"/>
+      <c r="BT17" s="23"/>
+      <c r="BU17" s="23"/>
+      <c r="BV17" s="23"/>
+      <c r="BW17" s="23"/>
+      <c r="BX17" s="23"/>
+      <c r="BY17" s="23"/>
+      <c r="BZ17" s="23"/>
+      <c r="CA17" s="23"/>
+      <c r="CB17" s="23"/>
+      <c r="CC17" s="23"/>
+      <c r="CD17" s="23"/>
+      <c r="CE17" s="23"/>
+      <c r="CF17" s="23"/>
+      <c r="CG17" s="23"/>
+      <c r="CH17" s="23"/>
+      <c r="CI17" s="23"/>
+      <c r="CJ17" s="23"/>
+      <c r="CK17" s="23"/>
+      <c r="CL17" s="23"/>
+      <c r="CM17" s="23"/>
+      <c r="CN17" s="23"/>
+      <c r="CO17" s="23"/>
+      <c r="CP17" s="23"/>
+      <c r="CQ17" s="23"/>
+      <c r="CR17" s="23"/>
+      <c r="CS17" s="23"/>
+      <c r="CT17" s="23"/>
+      <c r="CU17" s="23"/>
+      <c r="CV17" s="23"/>
+      <c r="CW17" s="23"/>
+      <c r="CX17" s="23"/>
+      <c r="CY17" s="23"/>
+      <c r="CZ17" s="23"/>
+      <c r="DA17" s="23"/>
+      <c r="DB17" s="23"/>
+      <c r="DC17" s="23"/>
+      <c r="DD17" s="23"/>
+      <c r="DE17" s="23"/>
+      <c r="DF17" s="23"/>
+      <c r="DG17" s="23"/>
+      <c r="DH17" s="23"/>
+      <c r="DI17" s="23"/>
+      <c r="DJ17" s="23"/>
+      <c r="DK17" s="23"/>
+      <c r="DL17" s="23"/>
+      <c r="DM17" s="23"/>
+      <c r="DN17" s="23"/>
+      <c r="DO17" s="23"/>
+      <c r="DP17" s="23"/>
+      <c r="DQ17" s="23"/>
+      <c r="DR17" s="23"/>
+      <c r="DS17" s="23"/>
+      <c r="DT17" s="23"/>
+      <c r="DU17" s="23"/>
+      <c r="DV17" s="23"/>
+      <c r="DW17" s="23"/>
+      <c r="DX17" s="23"/>
+      <c r="DY17" s="23"/>
+      <c r="DZ17" s="23"/>
+      <c r="EA17" s="23"/>
+      <c r="EB17" s="23"/>
+      <c r="EC17" s="23"/>
+      <c r="ED17" s="23"/>
+      <c r="EE17" s="23"/>
+      <c r="EF17" s="23"/>
+      <c r="EG17" s="23"/>
+      <c r="EH17" s="23"/>
+      <c r="EI17" s="23"/>
+      <c r="EJ17" s="23"/>
+      <c r="EK17" s="23"/>
+      <c r="EL17" s="23"/>
+      <c r="EM17" s="23"/>
+      <c r="EN17" s="23"/>
+      <c r="EO17" s="24"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
@@ -4325,7 +4348,7 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="12"/>
@@ -4381,7 +4404,9 @@
       <c r="BD18" s="12"/>
       <c r="BE18" s="12"/>
       <c r="BF18" s="12"/>
-      <c r="BG18" s="12"/>
+      <c r="BG18" s="12">
+        <v>0</v>
+      </c>
       <c r="BH18" s="12"/>
       <c r="BI18" s="12"/>
       <c r="BJ18" s="12"/>
@@ -4481,7 +4506,7 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="12"/>
@@ -4545,7 +4570,9 @@
       <c r="BD19" s="12"/>
       <c r="BE19" s="12"/>
       <c r="BF19" s="12"/>
-      <c r="BG19" s="12"/>
+      <c r="BG19" s="12">
+        <v>0</v>
+      </c>
       <c r="BH19" s="12"/>
       <c r="BI19" s="12"/>
       <c r="BJ19" s="12"/>
@@ -4801,7 +4828,7 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="12"/>
@@ -4949,7 +4976,9 @@
       <c r="BF21" s="12">
         <v>0</v>
       </c>
-      <c r="BG21" s="12"/>
+      <c r="BG21" s="12">
+        <v>0</v>
+      </c>
       <c r="BH21" s="12"/>
       <c r="BI21" s="12"/>
       <c r="BJ21" s="12"/>
@@ -5049,7 +5078,7 @@
       </c>
       <c r="D22" s="15">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="16"/>
       <c r="F22" s="12"/>
@@ -5121,7 +5150,9 @@
       <c r="BD22" s="12"/>
       <c r="BE22" s="12"/>
       <c r="BF22" s="12"/>
-      <c r="BG22" s="12"/>
+      <c r="BG22" s="12">
+        <v>0</v>
+      </c>
       <c r="BH22" s="12"/>
       <c r="BI22" s="12"/>
       <c r="BJ22" s="12"/>
@@ -5221,7 +5252,7 @@
       </c>
       <c r="D23" s="15">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="12">
@@ -5373,7 +5404,9 @@
       <c r="BF23" s="12">
         <v>0</v>
       </c>
-      <c r="BG23" s="12"/>
+      <c r="BG23" s="12">
+        <v>0</v>
+      </c>
       <c r="BH23" s="12"/>
       <c r="BI23" s="12"/>
       <c r="BJ23" s="12"/>
@@ -5473,7 +5506,7 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24" s="16"/>
       <c r="F24" s="12"/>
@@ -5553,7 +5586,9 @@
       <c r="BD24" s="12"/>
       <c r="BE24" s="12"/>
       <c r="BF24" s="12"/>
-      <c r="BG24" s="12"/>
+      <c r="BG24" s="12">
+        <v>0</v>
+      </c>
       <c r="BH24" s="12"/>
       <c r="BI24" s="12"/>
       <c r="BJ24" s="12"/>
@@ -5653,7 +5688,7 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="12"/>
@@ -5741,7 +5776,9 @@
       <c r="BD25" s="12"/>
       <c r="BE25" s="12"/>
       <c r="BF25" s="12"/>
-      <c r="BG25" s="12"/>
+      <c r="BG25" s="12">
+        <v>0</v>
+      </c>
       <c r="BH25" s="12"/>
       <c r="BI25" s="12"/>
       <c r="BJ25" s="12"/>
@@ -5841,7 +5878,7 @@
       </c>
       <c r="D26" s="15">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="16"/>
       <c r="F26" s="12"/>
@@ -5913,7 +5950,9 @@
       <c r="BD26" s="12"/>
       <c r="BE26" s="12"/>
       <c r="BF26" s="12"/>
-      <c r="BG26" s="12"/>
+      <c r="BG26" s="12">
+        <v>0</v>
+      </c>
       <c r="BH26" s="12"/>
       <c r="BI26" s="12"/>
       <c r="BJ26" s="12"/>
@@ -6013,7 +6052,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="12"/>
@@ -6161,7 +6200,9 @@
       <c r="BF27" s="12">
         <v>0</v>
       </c>
-      <c r="BG27" s="12"/>
+      <c r="BG27" s="12">
+        <v>0</v>
+      </c>
       <c r="BH27" s="12"/>
       <c r="BI27" s="12"/>
       <c r="BJ27" s="12"/>
@@ -6263,149 +6304,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="58" t="s">
+      <c r="E28" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="58"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="58"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="58"/>
-      <c r="Y28" s="58"/>
-      <c r="Z28" s="58"/>
-      <c r="AA28" s="58"/>
-      <c r="AB28" s="58"/>
-      <c r="AC28" s="58"/>
-      <c r="AD28" s="58"/>
-      <c r="AE28" s="58"/>
-      <c r="AF28" s="58"/>
-      <c r="AG28" s="58"/>
-      <c r="AH28" s="58"/>
-      <c r="AI28" s="58"/>
-      <c r="AJ28" s="58"/>
-      <c r="AK28" s="58"/>
-      <c r="AL28" s="58"/>
-      <c r="AM28" s="58"/>
-      <c r="AN28" s="58"/>
-      <c r="AO28" s="58"/>
-      <c r="AP28" s="58"/>
-      <c r="AQ28" s="58"/>
-      <c r="AR28" s="58"/>
-      <c r="AS28" s="58"/>
-      <c r="AT28" s="58"/>
-      <c r="AU28" s="58"/>
-      <c r="AV28" s="58"/>
-      <c r="AW28" s="58"/>
-      <c r="AX28" s="58"/>
-      <c r="AY28" s="58"/>
-      <c r="AZ28" s="58"/>
-      <c r="BA28" s="58"/>
-      <c r="BB28" s="58"/>
-      <c r="BC28" s="58"/>
-      <c r="BD28" s="58"/>
-      <c r="BE28" s="58"/>
-      <c r="BF28" s="58"/>
-      <c r="BG28" s="58"/>
-      <c r="BH28" s="58"/>
-      <c r="BI28" s="58"/>
-      <c r="BJ28" s="58"/>
-      <c r="BK28" s="58"/>
-      <c r="BL28" s="58"/>
-      <c r="BM28" s="58"/>
-      <c r="BN28" s="58"/>
-      <c r="BO28" s="58"/>
-      <c r="BP28" s="58"/>
-      <c r="BQ28" s="58"/>
-      <c r="BR28" s="58"/>
-      <c r="BS28" s="58"/>
-      <c r="BT28" s="58"/>
-      <c r="BU28" s="58"/>
-      <c r="BV28" s="58"/>
-      <c r="BW28" s="58"/>
-      <c r="BX28" s="58"/>
-      <c r="BY28" s="58"/>
-      <c r="BZ28" s="58"/>
-      <c r="CA28" s="58"/>
-      <c r="CB28" s="58"/>
-      <c r="CC28" s="58"/>
-      <c r="CD28" s="58"/>
-      <c r="CE28" s="58"/>
-      <c r="CF28" s="58"/>
-      <c r="CG28" s="58"/>
-      <c r="CH28" s="58"/>
-      <c r="CI28" s="58"/>
-      <c r="CJ28" s="58"/>
-      <c r="CK28" s="58"/>
-      <c r="CL28" s="58"/>
-      <c r="CM28" s="58"/>
-      <c r="CN28" s="58"/>
-      <c r="CO28" s="58"/>
-      <c r="CP28" s="58"/>
-      <c r="CQ28" s="58"/>
-      <c r="CR28" s="58"/>
-      <c r="CS28" s="58"/>
-      <c r="CT28" s="58"/>
-      <c r="CU28" s="58"/>
-      <c r="CV28" s="58"/>
-      <c r="CW28" s="58"/>
-      <c r="CX28" s="58"/>
-      <c r="CY28" s="58"/>
-      <c r="CZ28" s="58"/>
-      <c r="DA28" s="58"/>
-      <c r="DB28" s="58"/>
-      <c r="DC28" s="58"/>
-      <c r="DD28" s="58"/>
-      <c r="DE28" s="58"/>
-      <c r="DF28" s="58"/>
-      <c r="DG28" s="58"/>
-      <c r="DH28" s="58"/>
-      <c r="DI28" s="58"/>
-      <c r="DJ28" s="58"/>
-      <c r="DK28" s="58"/>
-      <c r="DL28" s="58"/>
-      <c r="DM28" s="58"/>
-      <c r="DN28" s="58"/>
-      <c r="DO28" s="58"/>
-      <c r="DP28" s="58"/>
-      <c r="DQ28" s="58"/>
-      <c r="DR28" s="58"/>
-      <c r="DS28" s="58"/>
-      <c r="DT28" s="58"/>
-      <c r="DU28" s="58"/>
-      <c r="DV28" s="58"/>
-      <c r="DW28" s="58"/>
-      <c r="DX28" s="58"/>
-      <c r="DY28" s="58"/>
-      <c r="DZ28" s="58"/>
-      <c r="EA28" s="58"/>
-      <c r="EB28" s="58"/>
-      <c r="EC28" s="58"/>
-      <c r="ED28" s="58"/>
-      <c r="EE28" s="58"/>
-      <c r="EF28" s="58"/>
-      <c r="EG28" s="58"/>
-      <c r="EH28" s="58"/>
-      <c r="EI28" s="58"/>
-      <c r="EJ28" s="58"/>
-      <c r="EK28" s="58"/>
-      <c r="EL28" s="58"/>
-      <c r="EM28" s="58"/>
-      <c r="EN28" s="58"/>
-      <c r="EO28" s="58"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="59"/>
+      <c r="AC28" s="59"/>
+      <c r="AD28" s="59"/>
+      <c r="AE28" s="59"/>
+      <c r="AF28" s="59"/>
+      <c r="AG28" s="59"/>
+      <c r="AH28" s="59"/>
+      <c r="AI28" s="59"/>
+      <c r="AJ28" s="59"/>
+      <c r="AK28" s="59"/>
+      <c r="AL28" s="59"/>
+      <c r="AM28" s="59"/>
+      <c r="AN28" s="59"/>
+      <c r="AO28" s="59"/>
+      <c r="AP28" s="59"/>
+      <c r="AQ28" s="59"/>
+      <c r="AR28" s="59"/>
+      <c r="AS28" s="59"/>
+      <c r="AT28" s="59"/>
+      <c r="AU28" s="59"/>
+      <c r="AV28" s="59"/>
+      <c r="AW28" s="59"/>
+      <c r="AX28" s="59"/>
+      <c r="AY28" s="59"/>
+      <c r="AZ28" s="59"/>
+      <c r="BA28" s="59"/>
+      <c r="BB28" s="59"/>
+      <c r="BC28" s="59"/>
+      <c r="BD28" s="59"/>
+      <c r="BE28" s="59"/>
+      <c r="BF28" s="59"/>
+      <c r="BG28" s="59"/>
+      <c r="BH28" s="59"/>
+      <c r="BI28" s="59"/>
+      <c r="BJ28" s="59"/>
+      <c r="BK28" s="59"/>
+      <c r="BL28" s="59"/>
+      <c r="BM28" s="59"/>
+      <c r="BN28" s="59"/>
+      <c r="BO28" s="59"/>
+      <c r="BP28" s="59"/>
+      <c r="BQ28" s="59"/>
+      <c r="BR28" s="59"/>
+      <c r="BS28" s="59"/>
+      <c r="BT28" s="59"/>
+      <c r="BU28" s="59"/>
+      <c r="BV28" s="59"/>
+      <c r="BW28" s="59"/>
+      <c r="BX28" s="59"/>
+      <c r="BY28" s="59"/>
+      <c r="BZ28" s="59"/>
+      <c r="CA28" s="59"/>
+      <c r="CB28" s="59"/>
+      <c r="CC28" s="59"/>
+      <c r="CD28" s="59"/>
+      <c r="CE28" s="59"/>
+      <c r="CF28" s="59"/>
+      <c r="CG28" s="59"/>
+      <c r="CH28" s="59"/>
+      <c r="CI28" s="59"/>
+      <c r="CJ28" s="59"/>
+      <c r="CK28" s="59"/>
+      <c r="CL28" s="59"/>
+      <c r="CM28" s="59"/>
+      <c r="CN28" s="59"/>
+      <c r="CO28" s="59"/>
+      <c r="CP28" s="59"/>
+      <c r="CQ28" s="59"/>
+      <c r="CR28" s="59"/>
+      <c r="CS28" s="59"/>
+      <c r="CT28" s="59"/>
+      <c r="CU28" s="59"/>
+      <c r="CV28" s="59"/>
+      <c r="CW28" s="59"/>
+      <c r="CX28" s="59"/>
+      <c r="CY28" s="59"/>
+      <c r="CZ28" s="59"/>
+      <c r="DA28" s="59"/>
+      <c r="DB28" s="59"/>
+      <c r="DC28" s="59"/>
+      <c r="DD28" s="59"/>
+      <c r="DE28" s="59"/>
+      <c r="DF28" s="59"/>
+      <c r="DG28" s="59"/>
+      <c r="DH28" s="59"/>
+      <c r="DI28" s="59"/>
+      <c r="DJ28" s="59"/>
+      <c r="DK28" s="59"/>
+      <c r="DL28" s="59"/>
+      <c r="DM28" s="59"/>
+      <c r="DN28" s="59"/>
+      <c r="DO28" s="59"/>
+      <c r="DP28" s="59"/>
+      <c r="DQ28" s="59"/>
+      <c r="DR28" s="59"/>
+      <c r="DS28" s="59"/>
+      <c r="DT28" s="59"/>
+      <c r="DU28" s="59"/>
+      <c r="DV28" s="59"/>
+      <c r="DW28" s="59"/>
+      <c r="DX28" s="59"/>
+      <c r="DY28" s="59"/>
+      <c r="DZ28" s="59"/>
+      <c r="EA28" s="59"/>
+      <c r="EB28" s="59"/>
+      <c r="EC28" s="59"/>
+      <c r="ED28" s="59"/>
+      <c r="EE28" s="59"/>
+      <c r="EF28" s="59"/>
+      <c r="EG28" s="59"/>
+      <c r="EH28" s="59"/>
+      <c r="EI28" s="59"/>
+      <c r="EJ28" s="59"/>
+      <c r="EK28" s="59"/>
+      <c r="EL28" s="59"/>
+      <c r="EM28" s="59"/>
+      <c r="EN28" s="59"/>
+      <c r="EO28" s="59"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6426,6 +6467,18 @@
     <mergeCell ref="DK8:DK9"/>
     <mergeCell ref="DL8:DL9"/>
     <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="DV8:DV9"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
     <mergeCell ref="E28:EO28"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AE1:AH1"/>
@@ -6450,18 +6503,6 @@
     <mergeCell ref="EC8:EC9"/>
     <mergeCell ref="ED8:ED9"/>
     <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="DV8:DV9"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
     <mergeCell ref="DD8:DD9"/>
     <mergeCell ref="DE8:DE9"/>
     <mergeCell ref="DF8:DF9"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B18342-C3C3-4327-9656-0500A04DF61E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DD465B-FDC3-4578-B1C9-E2C22D89B56D}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -814,6 +814,84 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -864,84 +942,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1170,108 +1170,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
-      <c r="F1" s="30">
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="F1" s="56">
         <v>4</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="32">
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58">
         <v>3</v>
       </c>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32">
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58">
         <v>4</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33">
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="59">
         <v>4</v>
       </c>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="33">
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="59">
         <v>4</v>
       </c>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="33">
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="59">
         <v>4</v>
       </c>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="60">
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="27">
         <v>2</v>
       </c>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="62">
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="22">
         <v>4</v>
       </c>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="64"/>
-      <c r="AI1" s="62">
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="22">
         <v>4</v>
       </c>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="63"/>
-      <c r="AL1" s="64"/>
-      <c r="AM1" s="62">
+      <c r="AJ1" s="23"/>
+      <c r="AK1" s="23"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="22">
         <v>2</v>
       </c>
-      <c r="AN1" s="64"/>
-      <c r="AO1" s="62">
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="22">
         <v>4</v>
       </c>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="64"/>
-      <c r="AS1" s="62">
+      <c r="AP1" s="23"/>
+      <c r="AQ1" s="23"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="22">
         <v>5</v>
       </c>
-      <c r="AT1" s="63"/>
-      <c r="AU1" s="63"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="64"/>
+      <c r="AT1" s="23"/>
+      <c r="AU1" s="23"/>
+      <c r="AV1" s="23"/>
+      <c r="AW1" s="29"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="62">
+      <c r="AY1" s="22">
         <v>5</v>
       </c>
-      <c r="AZ1" s="63"/>
-      <c r="BA1" s="63"/>
-      <c r="BB1" s="63"/>
-      <c r="BC1" s="64"/>
-      <c r="BD1" s="62">
+      <c r="AZ1" s="23"/>
+      <c r="BA1" s="23"/>
+      <c r="BB1" s="23"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="22">
         <v>3</v>
       </c>
-      <c r="BE1" s="63"/>
-      <c r="BF1" s="64"/>
+      <c r="BE1" s="23"/>
+      <c r="BF1" s="29"/>
       <c r="BG1" s="21">
         <v>1</v>
       </c>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
+      <c r="BH1" s="58">
+        <v>5</v>
+      </c>
+      <c r="BI1" s="58"/>
+      <c r="BJ1" s="58"/>
+      <c r="BK1" s="58"/>
+      <c r="BL1" s="58"/>
+      <c r="BM1" s="22">
+        <v>3</v>
+      </c>
+      <c r="BN1" s="23"/>
+      <c r="BO1" s="29"/>
       <c r="BP1" s="5"/>
       <c r="BQ1" s="5"/>
       <c r="BR1" s="5"/>
@@ -1352,1606 +1356,1622 @@
       <c r="EO1" s="4"/>
       <c r="EP1" s="1">
         <f>SUM(E1:EO1)</f>
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="36" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="R2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="41" t="s">
+      <c r="S2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="39" t="s">
+      <c r="U2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="41" t="s">
+      <c r="V2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="41" t="s">
+      <c r="W2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="41" t="s">
+      <c r="X2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Y2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="Z2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="43" t="s">
+      <c r="AA2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="43" t="s">
+      <c r="AB2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>46199</v>
       </c>
-      <c r="AD2" s="39">
+      <c r="AD2" s="36">
         <v>46199</v>
       </c>
-      <c r="AE2" s="39">
+      <c r="AE2" s="36">
         <v>46202</v>
       </c>
-      <c r="AF2" s="39">
+      <c r="AF2" s="36">
         <v>46202</v>
       </c>
-      <c r="AG2" s="39">
+      <c r="AG2" s="36">
         <v>46202</v>
       </c>
-      <c r="AH2" s="39">
+      <c r="AH2" s="36">
         <v>46202</v>
       </c>
-      <c r="AI2" s="39">
+      <c r="AI2" s="36">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="39">
+      <c r="AJ2" s="36">
         <v>46205</v>
       </c>
-      <c r="AK2" s="39">
+      <c r="AK2" s="36">
         <v>46205</v>
       </c>
-      <c r="AL2" s="39">
+      <c r="AL2" s="36">
         <v>46205</v>
       </c>
-      <c r="AM2" s="39">
+      <c r="AM2" s="36">
         <v>46206</v>
       </c>
-      <c r="AN2" s="39">
+      <c r="AN2" s="36">
         <v>46206</v>
       </c>
-      <c r="AO2" s="39">
+      <c r="AO2" s="36">
         <v>46212</v>
       </c>
-      <c r="AP2" s="39">
+      <c r="AP2" s="36">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="39">
+      <c r="AQ2" s="36">
         <v>46212</v>
       </c>
-      <c r="AR2" s="39">
+      <c r="AR2" s="36">
         <v>46212</v>
       </c>
-      <c r="AS2" s="39">
+      <c r="AS2" s="36">
         <v>46213</v>
       </c>
-      <c r="AT2" s="39">
+      <c r="AT2" s="36">
         <v>46213</v>
       </c>
-      <c r="AU2" s="39">
+      <c r="AU2" s="36">
         <v>46213</v>
       </c>
-      <c r="AV2" s="39">
+      <c r="AV2" s="36">
         <v>46213</v>
       </c>
-      <c r="AW2" s="39">
+      <c r="AW2" s="36">
         <v>46213</v>
       </c>
-      <c r="AX2" s="39">
+      <c r="AX2" s="36">
         <v>46218</v>
       </c>
-      <c r="AY2" s="39">
+      <c r="AY2" s="36">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="39">
+      <c r="AZ2" s="36">
         <v>46219</v>
       </c>
-      <c r="BA2" s="39">
+      <c r="BA2" s="36">
         <v>46219</v>
       </c>
-      <c r="BB2" s="39">
+      <c r="BB2" s="36">
         <v>46219</v>
       </c>
-      <c r="BC2" s="39">
+      <c r="BC2" s="36">
         <v>46219</v>
       </c>
-      <c r="BD2" s="39">
+      <c r="BD2" s="36">
         <v>46220</v>
       </c>
-      <c r="BE2" s="39">
+      <c r="BE2" s="36">
         <v>46220</v>
       </c>
-      <c r="BF2" s="39">
+      <c r="BF2" s="36">
         <v>46220</v>
       </c>
-      <c r="BG2" s="39">
+      <c r="BG2" s="36">
         <v>46225</v>
       </c>
-      <c r="BH2" s="39"/>
-      <c r="BI2" s="39"/>
-      <c r="BJ2" s="39"/>
-      <c r="BK2" s="39"/>
-      <c r="BL2" s="39"/>
-      <c r="BM2" s="39"/>
-      <c r="BN2" s="39"/>
-      <c r="BO2" s="39"/>
-      <c r="BP2" s="39"/>
-      <c r="BQ2" s="39"/>
-      <c r="BR2" s="39"/>
-      <c r="BS2" s="39"/>
-      <c r="BT2" s="39"/>
-      <c r="BU2" s="39"/>
-      <c r="BV2" s="39"/>
-      <c r="BW2" s="39"/>
-      <c r="BX2" s="39"/>
-      <c r="BY2" s="39"/>
-      <c r="BZ2" s="39"/>
-      <c r="CA2" s="39"/>
-      <c r="CB2" s="39"/>
-      <c r="CC2" s="39"/>
-      <c r="CD2" s="39"/>
-      <c r="CE2" s="39"/>
-      <c r="CF2" s="39"/>
-      <c r="CG2" s="39"/>
-      <c r="CH2" s="39"/>
-      <c r="CI2" s="39"/>
-      <c r="CJ2" s="39"/>
-      <c r="CK2" s="39"/>
-      <c r="CL2" s="39"/>
-      <c r="CM2" s="39"/>
-      <c r="CN2" s="39"/>
-      <c r="CO2" s="39"/>
-      <c r="CP2" s="39"/>
-      <c r="CQ2" s="39"/>
-      <c r="CR2" s="39"/>
-      <c r="CS2" s="39"/>
-      <c r="CT2" s="39"/>
-      <c r="CU2" s="39"/>
-      <c r="CV2" s="39"/>
-      <c r="CW2" s="39"/>
-      <c r="CX2" s="39"/>
-      <c r="CY2" s="39"/>
-      <c r="CZ2" s="39"/>
-      <c r="DA2" s="39"/>
-      <c r="DB2" s="39"/>
-      <c r="DC2" s="39"/>
-      <c r="DD2" s="39"/>
-      <c r="DE2" s="39"/>
-      <c r="DF2" s="39"/>
-      <c r="DG2" s="39"/>
-      <c r="DH2" s="39"/>
-      <c r="DI2" s="39"/>
-      <c r="DJ2" s="39"/>
-      <c r="DK2" s="39"/>
-      <c r="DL2" s="39"/>
-      <c r="DM2" s="39"/>
-      <c r="DN2" s="39"/>
-      <c r="DO2" s="39"/>
-      <c r="DP2" s="39"/>
-      <c r="DQ2" s="39"/>
-      <c r="DR2" s="39"/>
-      <c r="DS2" s="39"/>
-      <c r="DT2" s="39"/>
-      <c r="DU2" s="39"/>
-      <c r="DV2" s="39"/>
-      <c r="DW2" s="39"/>
-      <c r="DX2" s="39"/>
-      <c r="DY2" s="39"/>
-      <c r="DZ2" s="39"/>
-      <c r="EA2" s="39"/>
-      <c r="EB2" s="39"/>
-      <c r="EC2" s="39"/>
-      <c r="ED2" s="39"/>
-      <c r="EE2" s="39"/>
-      <c r="EF2" s="39"/>
-      <c r="EG2" s="39"/>
-      <c r="EH2" s="39"/>
-      <c r="EI2" s="39"/>
-      <c r="EJ2" s="39"/>
-      <c r="EK2" s="39"/>
-      <c r="EL2" s="39"/>
-      <c r="EM2" s="39"/>
-      <c r="EN2" s="39"/>
-      <c r="EO2" s="39"/>
+      <c r="BH2" s="36">
+        <v>46226</v>
+      </c>
+      <c r="BI2" s="36">
+        <v>46226</v>
+      </c>
+      <c r="BJ2" s="36">
+        <v>46226</v>
+      </c>
+      <c r="BK2" s="36">
+        <v>46226</v>
+      </c>
+      <c r="BL2" s="36">
+        <v>46226</v>
+      </c>
+      <c r="BM2" s="36">
+        <v>46227</v>
+      </c>
+      <c r="BN2" s="36">
+        <v>46227</v>
+      </c>
+      <c r="BO2" s="36">
+        <v>46227</v>
+      </c>
+      <c r="BP2" s="36"/>
+      <c r="BQ2" s="36"/>
+      <c r="BR2" s="36"/>
+      <c r="BS2" s="36"/>
+      <c r="BT2" s="36"/>
+      <c r="BU2" s="36"/>
+      <c r="BV2" s="36"/>
+      <c r="BW2" s="36"/>
+      <c r="BX2" s="36"/>
+      <c r="BY2" s="36"/>
+      <c r="BZ2" s="36"/>
+      <c r="CA2" s="36"/>
+      <c r="CB2" s="36"/>
+      <c r="CC2" s="36"/>
+      <c r="CD2" s="36"/>
+      <c r="CE2" s="36"/>
+      <c r="CF2" s="36"/>
+      <c r="CG2" s="36"/>
+      <c r="CH2" s="36"/>
+      <c r="CI2" s="36"/>
+      <c r="CJ2" s="36"/>
+      <c r="CK2" s="36"/>
+      <c r="CL2" s="36"/>
+      <c r="CM2" s="36"/>
+      <c r="CN2" s="36"/>
+      <c r="CO2" s="36"/>
+      <c r="CP2" s="36"/>
+      <c r="CQ2" s="36"/>
+      <c r="CR2" s="36"/>
+      <c r="CS2" s="36"/>
+      <c r="CT2" s="36"/>
+      <c r="CU2" s="36"/>
+      <c r="CV2" s="36"/>
+      <c r="CW2" s="36"/>
+      <c r="CX2" s="36"/>
+      <c r="CY2" s="36"/>
+      <c r="CZ2" s="36"/>
+      <c r="DA2" s="36"/>
+      <c r="DB2" s="36"/>
+      <c r="DC2" s="36"/>
+      <c r="DD2" s="36"/>
+      <c r="DE2" s="36"/>
+      <c r="DF2" s="36"/>
+      <c r="DG2" s="36"/>
+      <c r="DH2" s="36"/>
+      <c r="DI2" s="36"/>
+      <c r="DJ2" s="36"/>
+      <c r="DK2" s="36"/>
+      <c r="DL2" s="36"/>
+      <c r="DM2" s="36"/>
+      <c r="DN2" s="36"/>
+      <c r="DO2" s="36"/>
+      <c r="DP2" s="36"/>
+      <c r="DQ2" s="36"/>
+      <c r="DR2" s="36"/>
+      <c r="DS2" s="36"/>
+      <c r="DT2" s="36"/>
+      <c r="DU2" s="36"/>
+      <c r="DV2" s="36"/>
+      <c r="DW2" s="36"/>
+      <c r="DX2" s="36"/>
+      <c r="DY2" s="36"/>
+      <c r="DZ2" s="36"/>
+      <c r="EA2" s="36"/>
+      <c r="EB2" s="36"/>
+      <c r="EC2" s="36"/>
+      <c r="ED2" s="36"/>
+      <c r="EE2" s="36"/>
+      <c r="EF2" s="36"/>
+      <c r="EG2" s="36"/>
+      <c r="EH2" s="36"/>
+      <c r="EI2" s="36"/>
+      <c r="EJ2" s="36"/>
+      <c r="EK2" s="36"/>
+      <c r="EL2" s="36"/>
+      <c r="EM2" s="36"/>
+      <c r="EN2" s="36"/>
+      <c r="EO2" s="36"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="39"/>
-      <c r="AW3" s="39"/>
-      <c r="AX3" s="39"/>
-      <c r="AY3" s="39"/>
-      <c r="AZ3" s="39"/>
-      <c r="BA3" s="39"/>
-      <c r="BB3" s="39"/>
-      <c r="BC3" s="39"/>
-      <c r="BD3" s="39"/>
-      <c r="BE3" s="39"/>
-      <c r="BF3" s="39"/>
-      <c r="BG3" s="39"/>
-      <c r="BH3" s="39"/>
-      <c r="BI3" s="39"/>
-      <c r="BJ3" s="39"/>
-      <c r="BK3" s="39"/>
-      <c r="BL3" s="39"/>
-      <c r="BM3" s="39"/>
-      <c r="BN3" s="39"/>
-      <c r="BO3" s="39"/>
-      <c r="BP3" s="39"/>
-      <c r="BQ3" s="39"/>
-      <c r="BR3" s="39"/>
-      <c r="BS3" s="39"/>
-      <c r="BT3" s="39"/>
-      <c r="BU3" s="39"/>
-      <c r="BV3" s="39"/>
-      <c r="BW3" s="39"/>
-      <c r="BX3" s="39"/>
-      <c r="BY3" s="39"/>
-      <c r="BZ3" s="39"/>
-      <c r="CA3" s="39"/>
-      <c r="CB3" s="39"/>
-      <c r="CC3" s="39"/>
-      <c r="CD3" s="39"/>
-      <c r="CE3" s="39"/>
-      <c r="CF3" s="39"/>
-      <c r="CG3" s="39"/>
-      <c r="CH3" s="39"/>
-      <c r="CI3" s="39"/>
-      <c r="CJ3" s="39"/>
-      <c r="CK3" s="39"/>
-      <c r="CL3" s="39"/>
-      <c r="CM3" s="39"/>
-      <c r="CN3" s="39"/>
-      <c r="CO3" s="39"/>
-      <c r="CP3" s="39"/>
-      <c r="CQ3" s="39"/>
-      <c r="CR3" s="39"/>
-      <c r="CS3" s="39"/>
-      <c r="CT3" s="39"/>
-      <c r="CU3" s="39"/>
-      <c r="CV3" s="39"/>
-      <c r="CW3" s="39"/>
-      <c r="CX3" s="39"/>
-      <c r="CY3" s="39"/>
-      <c r="CZ3" s="39"/>
-      <c r="DA3" s="39"/>
-      <c r="DB3" s="39"/>
-      <c r="DC3" s="39"/>
-      <c r="DD3" s="39"/>
-      <c r="DE3" s="39"/>
-      <c r="DF3" s="39"/>
-      <c r="DG3" s="39"/>
-      <c r="DH3" s="39"/>
-      <c r="DI3" s="39"/>
-      <c r="DJ3" s="39"/>
-      <c r="DK3" s="39"/>
-      <c r="DL3" s="39"/>
-      <c r="DM3" s="39"/>
-      <c r="DN3" s="39"/>
-      <c r="DO3" s="39"/>
-      <c r="DP3" s="39"/>
-      <c r="DQ3" s="39"/>
-      <c r="DR3" s="39"/>
-      <c r="DS3" s="39"/>
-      <c r="DT3" s="39"/>
-      <c r="DU3" s="39"/>
-      <c r="DV3" s="39"/>
-      <c r="DW3" s="39"/>
-      <c r="DX3" s="39"/>
-      <c r="DY3" s="39"/>
-      <c r="DZ3" s="39"/>
-      <c r="EA3" s="39"/>
-      <c r="EB3" s="39"/>
-      <c r="EC3" s="39"/>
-      <c r="ED3" s="39"/>
-      <c r="EE3" s="39"/>
-      <c r="EF3" s="39"/>
-      <c r="EG3" s="39"/>
-      <c r="EH3" s="39"/>
-      <c r="EI3" s="39"/>
-      <c r="EJ3" s="39"/>
-      <c r="EK3" s="39"/>
-      <c r="EL3" s="39"/>
-      <c r="EM3" s="39"/>
-      <c r="EN3" s="39"/>
-      <c r="EO3" s="39"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
+      <c r="AM3" s="36"/>
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="36"/>
+      <c r="AP3" s="36"/>
+      <c r="AQ3" s="36"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AT3" s="36"/>
+      <c r="AU3" s="36"/>
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="AY3" s="36"/>
+      <c r="AZ3" s="36"/>
+      <c r="BA3" s="36"/>
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BD3" s="36"/>
+      <c r="BE3" s="36"/>
+      <c r="BF3" s="36"/>
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BI3" s="36"/>
+      <c r="BJ3" s="36"/>
+      <c r="BK3" s="36"/>
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BN3" s="36"/>
+      <c r="BO3" s="36"/>
+      <c r="BP3" s="36"/>
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BS3" s="36"/>
+      <c r="BT3" s="36"/>
+      <c r="BU3" s="36"/>
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36"/>
+      <c r="BX3" s="36"/>
+      <c r="BY3" s="36"/>
+      <c r="BZ3" s="36"/>
+      <c r="CA3" s="36"/>
+      <c r="CB3" s="36"/>
+      <c r="CC3" s="36"/>
+      <c r="CD3" s="36"/>
+      <c r="CE3" s="36"/>
+      <c r="CF3" s="36"/>
+      <c r="CG3" s="36"/>
+      <c r="CH3" s="36"/>
+      <c r="CI3" s="36"/>
+      <c r="CJ3" s="36"/>
+      <c r="CK3" s="36"/>
+      <c r="CL3" s="36"/>
+      <c r="CM3" s="36"/>
+      <c r="CN3" s="36"/>
+      <c r="CO3" s="36"/>
+      <c r="CP3" s="36"/>
+      <c r="CQ3" s="36"/>
+      <c r="CR3" s="36"/>
+      <c r="CS3" s="36"/>
+      <c r="CT3" s="36"/>
+      <c r="CU3" s="36"/>
+      <c r="CV3" s="36"/>
+      <c r="CW3" s="36"/>
+      <c r="CX3" s="36"/>
+      <c r="CY3" s="36"/>
+      <c r="CZ3" s="36"/>
+      <c r="DA3" s="36"/>
+      <c r="DB3" s="36"/>
+      <c r="DC3" s="36"/>
+      <c r="DD3" s="36"/>
+      <c r="DE3" s="36"/>
+      <c r="DF3" s="36"/>
+      <c r="DG3" s="36"/>
+      <c r="DH3" s="36"/>
+      <c r="DI3" s="36"/>
+      <c r="DJ3" s="36"/>
+      <c r="DK3" s="36"/>
+      <c r="DL3" s="36"/>
+      <c r="DM3" s="36"/>
+      <c r="DN3" s="36"/>
+      <c r="DO3" s="36"/>
+      <c r="DP3" s="36"/>
+      <c r="DQ3" s="36"/>
+      <c r="DR3" s="36"/>
+      <c r="DS3" s="36"/>
+      <c r="DT3" s="36"/>
+      <c r="DU3" s="36"/>
+      <c r="DV3" s="36"/>
+      <c r="DW3" s="36"/>
+      <c r="DX3" s="36"/>
+      <c r="DY3" s="36"/>
+      <c r="DZ3" s="36"/>
+      <c r="EA3" s="36"/>
+      <c r="EB3" s="36"/>
+      <c r="EC3" s="36"/>
+      <c r="ED3" s="36"/>
+      <c r="EE3" s="36"/>
+      <c r="EF3" s="36"/>
+      <c r="EG3" s="36"/>
+      <c r="EH3" s="36"/>
+      <c r="EI3" s="36"/>
+      <c r="EJ3" s="36"/>
+      <c r="EK3" s="36"/>
+      <c r="EL3" s="36"/>
+      <c r="EM3" s="36"/>
+      <c r="EN3" s="36"/>
+      <c r="EO3" s="36"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="43"/>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="39"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="39"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="39"/>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="39"/>
-      <c r="AR4" s="39"/>
-      <c r="AS4" s="39"/>
-      <c r="AT4" s="39"/>
-      <c r="AU4" s="39"/>
-      <c r="AV4" s="39"/>
-      <c r="AW4" s="39"/>
-      <c r="AX4" s="39"/>
-      <c r="AY4" s="39"/>
-      <c r="AZ4" s="39"/>
-      <c r="BA4" s="39"/>
-      <c r="BB4" s="39"/>
-      <c r="BC4" s="39"/>
-      <c r="BD4" s="39"/>
-      <c r="BE4" s="39"/>
-      <c r="BF4" s="39"/>
-      <c r="BG4" s="39"/>
-      <c r="BH4" s="39"/>
-      <c r="BI4" s="39"/>
-      <c r="BJ4" s="39"/>
-      <c r="BK4" s="39"/>
-      <c r="BL4" s="39"/>
-      <c r="BM4" s="39"/>
-      <c r="BN4" s="39"/>
-      <c r="BO4" s="39"/>
-      <c r="BP4" s="39"/>
-      <c r="BQ4" s="39"/>
-      <c r="BR4" s="39"/>
-      <c r="BS4" s="39"/>
-      <c r="BT4" s="39"/>
-      <c r="BU4" s="39"/>
-      <c r="BV4" s="39"/>
-      <c r="BW4" s="39"/>
-      <c r="BX4" s="39"/>
-      <c r="BY4" s="39"/>
-      <c r="BZ4" s="39"/>
-      <c r="CA4" s="39"/>
-      <c r="CB4" s="39"/>
-      <c r="CC4" s="39"/>
-      <c r="CD4" s="39"/>
-      <c r="CE4" s="39"/>
-      <c r="CF4" s="39"/>
-      <c r="CG4" s="39"/>
-      <c r="CH4" s="39"/>
-      <c r="CI4" s="39"/>
-      <c r="CJ4" s="39"/>
-      <c r="CK4" s="39"/>
-      <c r="CL4" s="39"/>
-      <c r="CM4" s="39"/>
-      <c r="CN4" s="39"/>
-      <c r="CO4" s="39"/>
-      <c r="CP4" s="39"/>
-      <c r="CQ4" s="39"/>
-      <c r="CR4" s="39"/>
-      <c r="CS4" s="39"/>
-      <c r="CT4" s="39"/>
-      <c r="CU4" s="39"/>
-      <c r="CV4" s="39"/>
-      <c r="CW4" s="39"/>
-      <c r="CX4" s="39"/>
-      <c r="CY4" s="39"/>
-      <c r="CZ4" s="39"/>
-      <c r="DA4" s="39"/>
-      <c r="DB4" s="39"/>
-      <c r="DC4" s="39"/>
-      <c r="DD4" s="39"/>
-      <c r="DE4" s="39"/>
-      <c r="DF4" s="39"/>
-      <c r="DG4" s="39"/>
-      <c r="DH4" s="39"/>
-      <c r="DI4" s="39"/>
-      <c r="DJ4" s="39"/>
-      <c r="DK4" s="39"/>
-      <c r="DL4" s="39"/>
-      <c r="DM4" s="39"/>
-      <c r="DN4" s="39"/>
-      <c r="DO4" s="39"/>
-      <c r="DP4" s="39"/>
-      <c r="DQ4" s="39"/>
-      <c r="DR4" s="39"/>
-      <c r="DS4" s="39"/>
-      <c r="DT4" s="39"/>
-      <c r="DU4" s="39"/>
-      <c r="DV4" s="39"/>
-      <c r="DW4" s="39"/>
-      <c r="DX4" s="39"/>
-      <c r="DY4" s="39"/>
-      <c r="DZ4" s="39"/>
-      <c r="EA4" s="39"/>
-      <c r="EB4" s="39"/>
-      <c r="EC4" s="39"/>
-      <c r="ED4" s="39"/>
-      <c r="EE4" s="39"/>
-      <c r="EF4" s="39"/>
-      <c r="EG4" s="39"/>
-      <c r="EH4" s="39"/>
-      <c r="EI4" s="39"/>
-      <c r="EJ4" s="39"/>
-      <c r="EK4" s="39"/>
-      <c r="EL4" s="39"/>
-      <c r="EM4" s="39"/>
-      <c r="EN4" s="39"/>
-      <c r="EO4" s="39"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
+      <c r="BJ4" s="36"/>
+      <c r="BK4" s="36"/>
+      <c r="BL4" s="36"/>
+      <c r="BM4" s="36"/>
+      <c r="BN4" s="36"/>
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="36"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="36"/>
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="36"/>
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="36"/>
+      <c r="CC4" s="36"/>
+      <c r="CD4" s="36"/>
+      <c r="CE4" s="36"/>
+      <c r="CF4" s="36"/>
+      <c r="CG4" s="36"/>
+      <c r="CH4" s="36"/>
+      <c r="CI4" s="36"/>
+      <c r="CJ4" s="36"/>
+      <c r="CK4" s="36"/>
+      <c r="CL4" s="36"/>
+      <c r="CM4" s="36"/>
+      <c r="CN4" s="36"/>
+      <c r="CO4" s="36"/>
+      <c r="CP4" s="36"/>
+      <c r="CQ4" s="36"/>
+      <c r="CR4" s="36"/>
+      <c r="CS4" s="36"/>
+      <c r="CT4" s="36"/>
+      <c r="CU4" s="36"/>
+      <c r="CV4" s="36"/>
+      <c r="CW4" s="36"/>
+      <c r="CX4" s="36"/>
+      <c r="CY4" s="36"/>
+      <c r="CZ4" s="36"/>
+      <c r="DA4" s="36"/>
+      <c r="DB4" s="36"/>
+      <c r="DC4" s="36"/>
+      <c r="DD4" s="36"/>
+      <c r="DE4" s="36"/>
+      <c r="DF4" s="36"/>
+      <c r="DG4" s="36"/>
+      <c r="DH4" s="36"/>
+      <c r="DI4" s="36"/>
+      <c r="DJ4" s="36"/>
+      <c r="DK4" s="36"/>
+      <c r="DL4" s="36"/>
+      <c r="DM4" s="36"/>
+      <c r="DN4" s="36"/>
+      <c r="DO4" s="36"/>
+      <c r="DP4" s="36"/>
+      <c r="DQ4" s="36"/>
+      <c r="DR4" s="36"/>
+      <c r="DS4" s="36"/>
+      <c r="DT4" s="36"/>
+      <c r="DU4" s="36"/>
+      <c r="DV4" s="36"/>
+      <c r="DW4" s="36"/>
+      <c r="DX4" s="36"/>
+      <c r="DY4" s="36"/>
+      <c r="DZ4" s="36"/>
+      <c r="EA4" s="36"/>
+      <c r="EB4" s="36"/>
+      <c r="EC4" s="36"/>
+      <c r="ED4" s="36"/>
+      <c r="EE4" s="36"/>
+      <c r="EF4" s="36"/>
+      <c r="EG4" s="36"/>
+      <c r="EH4" s="36"/>
+      <c r="EI4" s="36"/>
+      <c r="EJ4" s="36"/>
+      <c r="EK4" s="36"/>
+      <c r="EL4" s="36"/>
+      <c r="EM4" s="36"/>
+      <c r="EN4" s="36"/>
+      <c r="EO4" s="36"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="40"/>
+      <c r="C5" s="41">
         <v>110</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="43"/>
-      <c r="AB5" s="43"/>
-      <c r="AC5" s="39"/>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="39"/>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="39"/>
-      <c r="AH5" s="39"/>
-      <c r="AI5" s="39"/>
-      <c r="AJ5" s="39"/>
-      <c r="AK5" s="39"/>
-      <c r="AL5" s="39"/>
-      <c r="AM5" s="39"/>
-      <c r="AN5" s="39"/>
-      <c r="AO5" s="39"/>
-      <c r="AP5" s="39"/>
-      <c r="AQ5" s="39"/>
-      <c r="AR5" s="39"/>
-      <c r="AS5" s="39"/>
-      <c r="AT5" s="39"/>
-      <c r="AU5" s="39"/>
-      <c r="AV5" s="39"/>
-      <c r="AW5" s="39"/>
-      <c r="AX5" s="39"/>
-      <c r="AY5" s="39"/>
-      <c r="AZ5" s="39"/>
-      <c r="BA5" s="39"/>
-      <c r="BB5" s="39"/>
-      <c r="BC5" s="39"/>
-      <c r="BD5" s="39"/>
-      <c r="BE5" s="39"/>
-      <c r="BF5" s="39"/>
-      <c r="BG5" s="39"/>
-      <c r="BH5" s="39"/>
-      <c r="BI5" s="39"/>
-      <c r="BJ5" s="39"/>
-      <c r="BK5" s="39"/>
-      <c r="BL5" s="39"/>
-      <c r="BM5" s="39"/>
-      <c r="BN5" s="39"/>
-      <c r="BO5" s="39"/>
-      <c r="BP5" s="39"/>
-      <c r="BQ5" s="39"/>
-      <c r="BR5" s="39"/>
-      <c r="BS5" s="39"/>
-      <c r="BT5" s="39"/>
-      <c r="BU5" s="39"/>
-      <c r="BV5" s="39"/>
-      <c r="BW5" s="39"/>
-      <c r="BX5" s="39"/>
-      <c r="BY5" s="39"/>
-      <c r="BZ5" s="39"/>
-      <c r="CA5" s="39"/>
-      <c r="CB5" s="39"/>
-      <c r="CC5" s="39"/>
-      <c r="CD5" s="39"/>
-      <c r="CE5" s="39"/>
-      <c r="CF5" s="39"/>
-      <c r="CG5" s="39"/>
-      <c r="CH5" s="39"/>
-      <c r="CI5" s="39"/>
-      <c r="CJ5" s="39"/>
-      <c r="CK5" s="39"/>
-      <c r="CL5" s="39"/>
-      <c r="CM5" s="39"/>
-      <c r="CN5" s="39"/>
-      <c r="CO5" s="39"/>
-      <c r="CP5" s="39"/>
-      <c r="CQ5" s="39"/>
-      <c r="CR5" s="39"/>
-      <c r="CS5" s="39"/>
-      <c r="CT5" s="39"/>
-      <c r="CU5" s="39"/>
-      <c r="CV5" s="39"/>
-      <c r="CW5" s="39"/>
-      <c r="CX5" s="39"/>
-      <c r="CY5" s="39"/>
-      <c r="CZ5" s="39"/>
-      <c r="DA5" s="39"/>
-      <c r="DB5" s="39"/>
-      <c r="DC5" s="39"/>
-      <c r="DD5" s="39"/>
-      <c r="DE5" s="39"/>
-      <c r="DF5" s="39"/>
-      <c r="DG5" s="39"/>
-      <c r="DH5" s="39"/>
-      <c r="DI5" s="39"/>
-      <c r="DJ5" s="39"/>
-      <c r="DK5" s="39"/>
-      <c r="DL5" s="39"/>
-      <c r="DM5" s="39"/>
-      <c r="DN5" s="39"/>
-      <c r="DO5" s="39"/>
-      <c r="DP5" s="39"/>
-      <c r="DQ5" s="39"/>
-      <c r="DR5" s="39"/>
-      <c r="DS5" s="39"/>
-      <c r="DT5" s="39"/>
-      <c r="DU5" s="39"/>
-      <c r="DV5" s="39"/>
-      <c r="DW5" s="39"/>
-      <c r="DX5" s="39"/>
-      <c r="DY5" s="39"/>
-      <c r="DZ5" s="39"/>
-      <c r="EA5" s="39"/>
-      <c r="EB5" s="39"/>
-      <c r="EC5" s="39"/>
-      <c r="ED5" s="39"/>
-      <c r="EE5" s="39"/>
-      <c r="EF5" s="39"/>
-      <c r="EG5" s="39"/>
-      <c r="EH5" s="39"/>
-      <c r="EI5" s="39"/>
-      <c r="EJ5" s="39"/>
-      <c r="EK5" s="39"/>
-      <c r="EL5" s="39"/>
-      <c r="EM5" s="39"/>
-      <c r="EN5" s="39"/>
-      <c r="EO5" s="39"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="44"/>
+      <c r="AB5" s="44"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="36"/>
+      <c r="AE5" s="36"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="36"/>
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="36"/>
+      <c r="AN5" s="36"/>
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="36"/>
+      <c r="AQ5" s="36"/>
+      <c r="AR5" s="36"/>
+      <c r="AS5" s="36"/>
+      <c r="AT5" s="36"/>
+      <c r="AU5" s="36"/>
+      <c r="AV5" s="36"/>
+      <c r="AW5" s="36"/>
+      <c r="AX5" s="36"/>
+      <c r="AY5" s="36"/>
+      <c r="AZ5" s="36"/>
+      <c r="BA5" s="36"/>
+      <c r="BB5" s="36"/>
+      <c r="BC5" s="36"/>
+      <c r="BD5" s="36"/>
+      <c r="BE5" s="36"/>
+      <c r="BF5" s="36"/>
+      <c r="BG5" s="36"/>
+      <c r="BH5" s="36"/>
+      <c r="BI5" s="36"/>
+      <c r="BJ5" s="36"/>
+      <c r="BK5" s="36"/>
+      <c r="BL5" s="36"/>
+      <c r="BM5" s="36"/>
+      <c r="BN5" s="36"/>
+      <c r="BO5" s="36"/>
+      <c r="BP5" s="36"/>
+      <c r="BQ5" s="36"/>
+      <c r="BR5" s="36"/>
+      <c r="BS5" s="36"/>
+      <c r="BT5" s="36"/>
+      <c r="BU5" s="36"/>
+      <c r="BV5" s="36"/>
+      <c r="BW5" s="36"/>
+      <c r="BX5" s="36"/>
+      <c r="BY5" s="36"/>
+      <c r="BZ5" s="36"/>
+      <c r="CA5" s="36"/>
+      <c r="CB5" s="36"/>
+      <c r="CC5" s="36"/>
+      <c r="CD5" s="36"/>
+      <c r="CE5" s="36"/>
+      <c r="CF5" s="36"/>
+      <c r="CG5" s="36"/>
+      <c r="CH5" s="36"/>
+      <c r="CI5" s="36"/>
+      <c r="CJ5" s="36"/>
+      <c r="CK5" s="36"/>
+      <c r="CL5" s="36"/>
+      <c r="CM5" s="36"/>
+      <c r="CN5" s="36"/>
+      <c r="CO5" s="36"/>
+      <c r="CP5" s="36"/>
+      <c r="CQ5" s="36"/>
+      <c r="CR5" s="36"/>
+      <c r="CS5" s="36"/>
+      <c r="CT5" s="36"/>
+      <c r="CU5" s="36"/>
+      <c r="CV5" s="36"/>
+      <c r="CW5" s="36"/>
+      <c r="CX5" s="36"/>
+      <c r="CY5" s="36"/>
+      <c r="CZ5" s="36"/>
+      <c r="DA5" s="36"/>
+      <c r="DB5" s="36"/>
+      <c r="DC5" s="36"/>
+      <c r="DD5" s="36"/>
+      <c r="DE5" s="36"/>
+      <c r="DF5" s="36"/>
+      <c r="DG5" s="36"/>
+      <c r="DH5" s="36"/>
+      <c r="DI5" s="36"/>
+      <c r="DJ5" s="36"/>
+      <c r="DK5" s="36"/>
+      <c r="DL5" s="36"/>
+      <c r="DM5" s="36"/>
+      <c r="DN5" s="36"/>
+      <c r="DO5" s="36"/>
+      <c r="DP5" s="36"/>
+      <c r="DQ5" s="36"/>
+      <c r="DR5" s="36"/>
+      <c r="DS5" s="36"/>
+      <c r="DT5" s="36"/>
+      <c r="DU5" s="36"/>
+      <c r="DV5" s="36"/>
+      <c r="DW5" s="36"/>
+      <c r="DX5" s="36"/>
+      <c r="DY5" s="36"/>
+      <c r="DZ5" s="36"/>
+      <c r="EA5" s="36"/>
+      <c r="EB5" s="36"/>
+      <c r="EC5" s="36"/>
+      <c r="ED5" s="36"/>
+      <c r="EE5" s="36"/>
+      <c r="EF5" s="36"/>
+      <c r="EG5" s="36"/>
+      <c r="EH5" s="36"/>
+      <c r="EI5" s="36"/>
+      <c r="EJ5" s="36"/>
+      <c r="EK5" s="36"/>
+      <c r="EL5" s="36"/>
+      <c r="EM5" s="36"/>
+      <c r="EN5" s="36"/>
+      <c r="EO5" s="36"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41">
         <v>10</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="43"/>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="39"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="39"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="39"/>
-      <c r="BA6" s="39"/>
-      <c r="BB6" s="39"/>
-      <c r="BC6" s="39"/>
-      <c r="BD6" s="39"/>
-      <c r="BE6" s="39"/>
-      <c r="BF6" s="39"/>
-      <c r="BG6" s="39"/>
-      <c r="BH6" s="39"/>
-      <c r="BI6" s="39"/>
-      <c r="BJ6" s="39"/>
-      <c r="BK6" s="39"/>
-      <c r="BL6" s="39"/>
-      <c r="BM6" s="39"/>
-      <c r="BN6" s="39"/>
-      <c r="BO6" s="39"/>
-      <c r="BP6" s="39"/>
-      <c r="BQ6" s="39"/>
-      <c r="BR6" s="39"/>
-      <c r="BS6" s="39"/>
-      <c r="BT6" s="39"/>
-      <c r="BU6" s="39"/>
-      <c r="BV6" s="39"/>
-      <c r="BW6" s="39"/>
-      <c r="BX6" s="39"/>
-      <c r="BY6" s="39"/>
-      <c r="BZ6" s="39"/>
-      <c r="CA6" s="39"/>
-      <c r="CB6" s="39"/>
-      <c r="CC6" s="39"/>
-      <c r="CD6" s="39"/>
-      <c r="CE6" s="39"/>
-      <c r="CF6" s="39"/>
-      <c r="CG6" s="39"/>
-      <c r="CH6" s="39"/>
-      <c r="CI6" s="39"/>
-      <c r="CJ6" s="39"/>
-      <c r="CK6" s="39"/>
-      <c r="CL6" s="39"/>
-      <c r="CM6" s="39"/>
-      <c r="CN6" s="39"/>
-      <c r="CO6" s="39"/>
-      <c r="CP6" s="39"/>
-      <c r="CQ6" s="39"/>
-      <c r="CR6" s="39"/>
-      <c r="CS6" s="39"/>
-      <c r="CT6" s="39"/>
-      <c r="CU6" s="39"/>
-      <c r="CV6" s="39"/>
-      <c r="CW6" s="39"/>
-      <c r="CX6" s="39"/>
-      <c r="CY6" s="39"/>
-      <c r="CZ6" s="39"/>
-      <c r="DA6" s="39"/>
-      <c r="DB6" s="39"/>
-      <c r="DC6" s="39"/>
-      <c r="DD6" s="39"/>
-      <c r="DE6" s="39"/>
-      <c r="DF6" s="39"/>
-      <c r="DG6" s="39"/>
-      <c r="DH6" s="39"/>
-      <c r="DI6" s="39"/>
-      <c r="DJ6" s="39"/>
-      <c r="DK6" s="39"/>
-      <c r="DL6" s="39"/>
-      <c r="DM6" s="39"/>
-      <c r="DN6" s="39"/>
-      <c r="DO6" s="39"/>
-      <c r="DP6" s="39"/>
-      <c r="DQ6" s="39"/>
-      <c r="DR6" s="39"/>
-      <c r="DS6" s="39"/>
-      <c r="DT6" s="39"/>
-      <c r="DU6" s="39"/>
-      <c r="DV6" s="39"/>
-      <c r="DW6" s="39"/>
-      <c r="DX6" s="39"/>
-      <c r="DY6" s="39"/>
-      <c r="DZ6" s="39"/>
-      <c r="EA6" s="39"/>
-      <c r="EB6" s="39"/>
-      <c r="EC6" s="39"/>
-      <c r="ED6" s="39"/>
-      <c r="EE6" s="39"/>
-      <c r="EF6" s="39"/>
-      <c r="EG6" s="39"/>
-      <c r="EH6" s="39"/>
-      <c r="EI6" s="39"/>
-      <c r="EJ6" s="39"/>
-      <c r="EK6" s="39"/>
-      <c r="EL6" s="39"/>
-      <c r="EM6" s="39"/>
-      <c r="EN6" s="39"/>
-      <c r="EO6" s="39"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="46"/>
+      <c r="AA6" s="44"/>
+      <c r="AB6" s="44"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="36"/>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="36"/>
+      <c r="AN6" s="36"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="36"/>
+      <c r="AQ6" s="36"/>
+      <c r="AR6" s="36"/>
+      <c r="AS6" s="36"/>
+      <c r="AT6" s="36"/>
+      <c r="AU6" s="36"/>
+      <c r="AV6" s="36"/>
+      <c r="AW6" s="36"/>
+      <c r="AX6" s="36"/>
+      <c r="AY6" s="36"/>
+      <c r="AZ6" s="36"/>
+      <c r="BA6" s="36"/>
+      <c r="BB6" s="36"/>
+      <c r="BC6" s="36"/>
+      <c r="BD6" s="36"/>
+      <c r="BE6" s="36"/>
+      <c r="BF6" s="36"/>
+      <c r="BG6" s="36"/>
+      <c r="BH6" s="36"/>
+      <c r="BI6" s="36"/>
+      <c r="BJ6" s="36"/>
+      <c r="BK6" s="36"/>
+      <c r="BL6" s="36"/>
+      <c r="BM6" s="36"/>
+      <c r="BN6" s="36"/>
+      <c r="BO6" s="36"/>
+      <c r="BP6" s="36"/>
+      <c r="BQ6" s="36"/>
+      <c r="BR6" s="36"/>
+      <c r="BS6" s="36"/>
+      <c r="BT6" s="36"/>
+      <c r="BU6" s="36"/>
+      <c r="BV6" s="36"/>
+      <c r="BW6" s="36"/>
+      <c r="BX6" s="36"/>
+      <c r="BY6" s="36"/>
+      <c r="BZ6" s="36"/>
+      <c r="CA6" s="36"/>
+      <c r="CB6" s="36"/>
+      <c r="CC6" s="36"/>
+      <c r="CD6" s="36"/>
+      <c r="CE6" s="36"/>
+      <c r="CF6" s="36"/>
+      <c r="CG6" s="36"/>
+      <c r="CH6" s="36"/>
+      <c r="CI6" s="36"/>
+      <c r="CJ6" s="36"/>
+      <c r="CK6" s="36"/>
+      <c r="CL6" s="36"/>
+      <c r="CM6" s="36"/>
+      <c r="CN6" s="36"/>
+      <c r="CO6" s="36"/>
+      <c r="CP6" s="36"/>
+      <c r="CQ6" s="36"/>
+      <c r="CR6" s="36"/>
+      <c r="CS6" s="36"/>
+      <c r="CT6" s="36"/>
+      <c r="CU6" s="36"/>
+      <c r="CV6" s="36"/>
+      <c r="CW6" s="36"/>
+      <c r="CX6" s="36"/>
+      <c r="CY6" s="36"/>
+      <c r="CZ6" s="36"/>
+      <c r="DA6" s="36"/>
+      <c r="DB6" s="36"/>
+      <c r="DC6" s="36"/>
+      <c r="DD6" s="36"/>
+      <c r="DE6" s="36"/>
+      <c r="DF6" s="36"/>
+      <c r="DG6" s="36"/>
+      <c r="DH6" s="36"/>
+      <c r="DI6" s="36"/>
+      <c r="DJ6" s="36"/>
+      <c r="DK6" s="36"/>
+      <c r="DL6" s="36"/>
+      <c r="DM6" s="36"/>
+      <c r="DN6" s="36"/>
+      <c r="DO6" s="36"/>
+      <c r="DP6" s="36"/>
+      <c r="DQ6" s="36"/>
+      <c r="DR6" s="36"/>
+      <c r="DS6" s="36"/>
+      <c r="DT6" s="36"/>
+      <c r="DU6" s="36"/>
+      <c r="DV6" s="36"/>
+      <c r="DW6" s="36"/>
+      <c r="DX6" s="36"/>
+      <c r="DY6" s="36"/>
+      <c r="DZ6" s="36"/>
+      <c r="EA6" s="36"/>
+      <c r="EB6" s="36"/>
+      <c r="EC6" s="36"/>
+      <c r="ED6" s="36"/>
+      <c r="EE6" s="36"/>
+      <c r="EF6" s="36"/>
+      <c r="EG6" s="36"/>
+      <c r="EH6" s="36"/>
+      <c r="EI6" s="36"/>
+      <c r="EJ6" s="36"/>
+      <c r="EK6" s="36"/>
+      <c r="EL6" s="36"/>
+      <c r="EM6" s="36"/>
+      <c r="EN6" s="36"/>
+      <c r="EO6" s="36"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49">
+      <c r="B7" s="43"/>
+      <c r="C7" s="41">
         <v>30</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="42"/>
-      <c r="W7" s="42"/>
-      <c r="X7" s="42"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="40"/>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="40"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="40"/>
-      <c r="AL7" s="40"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="40"/>
-      <c r="AT7" s="40"/>
-      <c r="AU7" s="40"/>
-      <c r="AV7" s="40"/>
-      <c r="AW7" s="40"/>
-      <c r="AX7" s="40"/>
-      <c r="AY7" s="40"/>
-      <c r="AZ7" s="40"/>
-      <c r="BA7" s="40"/>
-      <c r="BB7" s="40"/>
-      <c r="BC7" s="40"/>
-      <c r="BD7" s="40"/>
-      <c r="BE7" s="40"/>
-      <c r="BF7" s="40"/>
-      <c r="BG7" s="40"/>
-      <c r="BH7" s="40"/>
-      <c r="BI7" s="40"/>
-      <c r="BJ7" s="40"/>
-      <c r="BK7" s="40"/>
-      <c r="BL7" s="40"/>
-      <c r="BM7" s="40"/>
-      <c r="BN7" s="40"/>
-      <c r="BO7" s="40"/>
-      <c r="BP7" s="40"/>
-      <c r="BQ7" s="40"/>
-      <c r="BR7" s="40"/>
-      <c r="BS7" s="40"/>
-      <c r="BT7" s="40"/>
-      <c r="BU7" s="40"/>
-      <c r="BV7" s="40"/>
-      <c r="BW7" s="40"/>
-      <c r="BX7" s="40"/>
-      <c r="BY7" s="40"/>
-      <c r="BZ7" s="40"/>
-      <c r="CA7" s="40"/>
-      <c r="CB7" s="40"/>
-      <c r="CC7" s="40"/>
-      <c r="CD7" s="40"/>
-      <c r="CE7" s="40"/>
-      <c r="CF7" s="40"/>
-      <c r="CG7" s="40"/>
-      <c r="CH7" s="40"/>
-      <c r="CI7" s="40"/>
-      <c r="CJ7" s="40"/>
-      <c r="CK7" s="40"/>
-      <c r="CL7" s="40"/>
-      <c r="CM7" s="40"/>
-      <c r="CN7" s="40"/>
-      <c r="CO7" s="40"/>
-      <c r="CP7" s="40"/>
-      <c r="CQ7" s="40"/>
-      <c r="CR7" s="40"/>
-      <c r="CS7" s="40"/>
-      <c r="CT7" s="40"/>
-      <c r="CU7" s="40"/>
-      <c r="CV7" s="40"/>
-      <c r="CW7" s="40"/>
-      <c r="CX7" s="40"/>
-      <c r="CY7" s="40"/>
-      <c r="CZ7" s="40"/>
-      <c r="DA7" s="40"/>
-      <c r="DB7" s="40"/>
-      <c r="DC7" s="40"/>
-      <c r="DD7" s="40"/>
-      <c r="DE7" s="40"/>
-      <c r="DF7" s="40"/>
-      <c r="DG7" s="40"/>
-      <c r="DH7" s="40"/>
-      <c r="DI7" s="40"/>
-      <c r="DJ7" s="40"/>
-      <c r="DK7" s="40"/>
-      <c r="DL7" s="40"/>
-      <c r="DM7" s="40"/>
-      <c r="DN7" s="40"/>
-      <c r="DO7" s="40"/>
-      <c r="DP7" s="40"/>
-      <c r="DQ7" s="40"/>
-      <c r="DR7" s="40"/>
-      <c r="DS7" s="40"/>
-      <c r="DT7" s="40"/>
-      <c r="DU7" s="40"/>
-      <c r="DV7" s="40"/>
-      <c r="DW7" s="40"/>
-      <c r="DX7" s="40"/>
-      <c r="DY7" s="40"/>
-      <c r="DZ7" s="40"/>
-      <c r="EA7" s="40"/>
-      <c r="EB7" s="40"/>
-      <c r="EC7" s="40"/>
-      <c r="ED7" s="40"/>
-      <c r="EE7" s="40"/>
-      <c r="EF7" s="40"/>
-      <c r="EG7" s="40"/>
-      <c r="EH7" s="40"/>
-      <c r="EI7" s="40"/>
-      <c r="EJ7" s="40"/>
-      <c r="EK7" s="40"/>
-      <c r="EL7" s="40"/>
-      <c r="EM7" s="40"/>
-      <c r="EN7" s="40"/>
-      <c r="EO7" s="40"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="45"/>
+      <c r="AB7" s="45"/>
+      <c r="AC7" s="37"/>
+      <c r="AD7" s="37"/>
+      <c r="AE7" s="37"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="37"/>
+      <c r="AR7" s="37"/>
+      <c r="AS7" s="37"/>
+      <c r="AT7" s="37"/>
+      <c r="AU7" s="37"/>
+      <c r="AV7" s="37"/>
+      <c r="AW7" s="37"/>
+      <c r="AX7" s="37"/>
+      <c r="AY7" s="37"/>
+      <c r="AZ7" s="37"/>
+      <c r="BA7" s="37"/>
+      <c r="BB7" s="37"/>
+      <c r="BC7" s="37"/>
+      <c r="BD7" s="37"/>
+      <c r="BE7" s="37"/>
+      <c r="BF7" s="37"/>
+      <c r="BG7" s="37"/>
+      <c r="BH7" s="37"/>
+      <c r="BI7" s="37"/>
+      <c r="BJ7" s="37"/>
+      <c r="BK7" s="37"/>
+      <c r="BL7" s="37"/>
+      <c r="BM7" s="37"/>
+      <c r="BN7" s="37"/>
+      <c r="BO7" s="37"/>
+      <c r="BP7" s="37"/>
+      <c r="BQ7" s="37"/>
+      <c r="BR7" s="37"/>
+      <c r="BS7" s="37"/>
+      <c r="BT7" s="37"/>
+      <c r="BU7" s="37"/>
+      <c r="BV7" s="37"/>
+      <c r="BW7" s="37"/>
+      <c r="BX7" s="37"/>
+      <c r="BY7" s="37"/>
+      <c r="BZ7" s="37"/>
+      <c r="CA7" s="37"/>
+      <c r="CB7" s="37"/>
+      <c r="CC7" s="37"/>
+      <c r="CD7" s="37"/>
+      <c r="CE7" s="37"/>
+      <c r="CF7" s="37"/>
+      <c r="CG7" s="37"/>
+      <c r="CH7" s="37"/>
+      <c r="CI7" s="37"/>
+      <c r="CJ7" s="37"/>
+      <c r="CK7" s="37"/>
+      <c r="CL7" s="37"/>
+      <c r="CM7" s="37"/>
+      <c r="CN7" s="37"/>
+      <c r="CO7" s="37"/>
+      <c r="CP7" s="37"/>
+      <c r="CQ7" s="37"/>
+      <c r="CR7" s="37"/>
+      <c r="CS7" s="37"/>
+      <c r="CT7" s="37"/>
+      <c r="CU7" s="37"/>
+      <c r="CV7" s="37"/>
+      <c r="CW7" s="37"/>
+      <c r="CX7" s="37"/>
+      <c r="CY7" s="37"/>
+      <c r="CZ7" s="37"/>
+      <c r="DA7" s="37"/>
+      <c r="DB7" s="37"/>
+      <c r="DC7" s="37"/>
+      <c r="DD7" s="37"/>
+      <c r="DE7" s="37"/>
+      <c r="DF7" s="37"/>
+      <c r="DG7" s="37"/>
+      <c r="DH7" s="37"/>
+      <c r="DI7" s="37"/>
+      <c r="DJ7" s="37"/>
+      <c r="DK7" s="37"/>
+      <c r="DL7" s="37"/>
+      <c r="DM7" s="37"/>
+      <c r="DN7" s="37"/>
+      <c r="DO7" s="37"/>
+      <c r="DP7" s="37"/>
+      <c r="DQ7" s="37"/>
+      <c r="DR7" s="37"/>
+      <c r="DS7" s="37"/>
+      <c r="DT7" s="37"/>
+      <c r="DU7" s="37"/>
+      <c r="DV7" s="37"/>
+      <c r="DW7" s="37"/>
+      <c r="DX7" s="37"/>
+      <c r="DY7" s="37"/>
+      <c r="DZ7" s="37"/>
+      <c r="EA7" s="37"/>
+      <c r="EB7" s="37"/>
+      <c r="EC7" s="37"/>
+      <c r="ED7" s="37"/>
+      <c r="EE7" s="37"/>
+      <c r="EF7" s="37"/>
+      <c r="EG7" s="37"/>
+      <c r="EH7" s="37"/>
+      <c r="EI7" s="37"/>
+      <c r="EJ7" s="37"/>
+      <c r="EK7" s="37"/>
+      <c r="EL7" s="37"/>
+      <c r="EM7" s="37"/>
+      <c r="EN7" s="37"/>
+      <c r="EO7" s="37"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31">
         <v>150</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="54">
+      <c r="F8" s="24">
         <v>1</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="24">
         <v>2</v>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="24">
         <v>3</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="24">
         <v>4</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="24">
         <v>5</v>
       </c>
-      <c r="K8" s="54">
+      <c r="K8" s="24">
         <v>6</v>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="24">
         <v>7</v>
       </c>
-      <c r="M8" s="54">
+      <c r="M8" s="24">
         <v>8</v>
       </c>
-      <c r="N8" s="54">
+      <c r="N8" s="24">
         <v>9</v>
       </c>
-      <c r="O8" s="54">
+      <c r="O8" s="24">
         <v>10</v>
       </c>
-      <c r="P8" s="54">
+      <c r="P8" s="24">
         <v>11</v>
       </c>
-      <c r="Q8" s="54">
+      <c r="Q8" s="24">
         <v>12</v>
       </c>
-      <c r="R8" s="54">
+      <c r="R8" s="24">
         <v>13</v>
       </c>
-      <c r="S8" s="54">
+      <c r="S8" s="24">
         <v>14</v>
       </c>
-      <c r="T8" s="54">
+      <c r="T8" s="24">
         <v>15</v>
       </c>
-      <c r="U8" s="54">
+      <c r="U8" s="24">
         <v>16</v>
       </c>
-      <c r="V8" s="54">
+      <c r="V8" s="24">
         <v>17</v>
       </c>
-      <c r="W8" s="54">
+      <c r="W8" s="24">
         <v>18</v>
       </c>
-      <c r="X8" s="54">
+      <c r="X8" s="24">
         <v>19</v>
       </c>
-      <c r="Y8" s="54">
+      <c r="Y8" s="24">
         <v>20</v>
       </c>
-      <c r="Z8" s="54">
+      <c r="Z8" s="24">
         <v>21</v>
       </c>
-      <c r="AA8" s="54">
+      <c r="AA8" s="24">
         <v>22</v>
       </c>
-      <c r="AB8" s="54">
+      <c r="AB8" s="24">
         <v>23</v>
       </c>
-      <c r="AC8" s="54">
+      <c r="AC8" s="24">
         <v>24</v>
       </c>
-      <c r="AD8" s="54">
+      <c r="AD8" s="24">
         <v>25</v>
       </c>
-      <c r="AE8" s="54">
+      <c r="AE8" s="24">
         <v>26</v>
       </c>
-      <c r="AF8" s="54">
+      <c r="AF8" s="24">
         <v>27</v>
       </c>
-      <c r="AG8" s="54">
+      <c r="AG8" s="24">
         <v>28</v>
       </c>
-      <c r="AH8" s="54">
+      <c r="AH8" s="24">
         <v>29</v>
       </c>
-      <c r="AI8" s="54">
+      <c r="AI8" s="24">
         <v>30</v>
       </c>
-      <c r="AJ8" s="54">
+      <c r="AJ8" s="24">
         <v>31</v>
       </c>
-      <c r="AK8" s="54">
+      <c r="AK8" s="24">
         <v>32</v>
       </c>
-      <c r="AL8" s="54">
+      <c r="AL8" s="24">
         <v>33</v>
       </c>
-      <c r="AM8" s="54">
+      <c r="AM8" s="24">
         <v>34</v>
       </c>
-      <c r="AN8" s="54">
+      <c r="AN8" s="24">
         <v>35</v>
       </c>
-      <c r="AO8" s="54">
+      <c r="AO8" s="24">
         <v>36</v>
       </c>
-      <c r="AP8" s="54">
+      <c r="AP8" s="24">
         <v>37</v>
       </c>
-      <c r="AQ8" s="54">
+      <c r="AQ8" s="24">
         <v>38</v>
       </c>
-      <c r="AR8" s="54">
+      <c r="AR8" s="24">
         <v>39</v>
       </c>
-      <c r="AS8" s="54">
+      <c r="AS8" s="24">
         <v>40</v>
       </c>
-      <c r="AT8" s="54">
+      <c r="AT8" s="24">
         <v>41</v>
       </c>
-      <c r="AU8" s="54">
+      <c r="AU8" s="24">
         <v>42</v>
       </c>
-      <c r="AV8" s="54">
+      <c r="AV8" s="24">
         <v>43</v>
       </c>
-      <c r="AW8" s="54">
+      <c r="AW8" s="24">
         <v>44</v>
       </c>
-      <c r="AX8" s="54">
+      <c r="AX8" s="24">
         <v>45</v>
       </c>
-      <c r="AY8" s="54">
+      <c r="AY8" s="24">
         <v>46</v>
       </c>
-      <c r="AZ8" s="54">
+      <c r="AZ8" s="24">
         <v>47</v>
       </c>
-      <c r="BA8" s="54">
+      <c r="BA8" s="24">
         <v>48</v>
       </c>
-      <c r="BB8" s="54">
+      <c r="BB8" s="24">
         <v>49</v>
       </c>
-      <c r="BC8" s="54">
+      <c r="BC8" s="24">
         <v>50</v>
       </c>
-      <c r="BD8" s="54">
+      <c r="BD8" s="24">
         <v>51</v>
       </c>
-      <c r="BE8" s="54">
+      <c r="BE8" s="24">
         <v>52</v>
       </c>
-      <c r="BF8" s="54">
+      <c r="BF8" s="24">
         <v>53</v>
       </c>
-      <c r="BG8" s="54">
+      <c r="BG8" s="24">
         <v>54</v>
       </c>
-      <c r="BH8" s="54">
+      <c r="BH8" s="24">
         <v>55</v>
       </c>
-      <c r="BI8" s="54">
+      <c r="BI8" s="24">
         <v>56</v>
       </c>
-      <c r="BJ8" s="54">
+      <c r="BJ8" s="24">
         <v>57</v>
       </c>
-      <c r="BK8" s="54">
+      <c r="BK8" s="24">
         <v>58</v>
       </c>
-      <c r="BL8" s="54">
+      <c r="BL8" s="24">
         <v>59</v>
       </c>
-      <c r="BM8" s="54">
+      <c r="BM8" s="24">
         <v>60</v>
       </c>
-      <c r="BN8" s="54">
+      <c r="BN8" s="24">
         <v>61</v>
       </c>
-      <c r="BO8" s="54">
+      <c r="BO8" s="24">
         <v>62</v>
       </c>
-      <c r="BP8" s="54">
+      <c r="BP8" s="24">
         <v>63</v>
       </c>
-      <c r="BQ8" s="54">
+      <c r="BQ8" s="24">
         <v>64</v>
       </c>
-      <c r="BR8" s="54">
+      <c r="BR8" s="24">
         <v>65</v>
       </c>
-      <c r="BS8" s="54">
+      <c r="BS8" s="24">
         <v>66</v>
       </c>
-      <c r="BT8" s="54">
+      <c r="BT8" s="24">
         <v>67</v>
       </c>
-      <c r="BU8" s="54">
+      <c r="BU8" s="24">
         <v>68</v>
       </c>
-      <c r="BV8" s="54">
+      <c r="BV8" s="24">
         <v>69</v>
       </c>
-      <c r="BW8" s="54">
+      <c r="BW8" s="24">
         <v>70</v>
       </c>
-      <c r="BX8" s="54">
+      <c r="BX8" s="24">
         <v>71</v>
       </c>
-      <c r="BY8" s="54">
+      <c r="BY8" s="24">
         <v>72</v>
       </c>
-      <c r="BZ8" s="54">
+      <c r="BZ8" s="24">
         <v>73</v>
       </c>
-      <c r="CA8" s="54">
+      <c r="CA8" s="24">
         <v>74</v>
       </c>
-      <c r="CB8" s="54">
+      <c r="CB8" s="24">
         <v>75</v>
       </c>
-      <c r="CC8" s="54">
+      <c r="CC8" s="24">
         <v>76</v>
       </c>
-      <c r="CD8" s="54">
+      <c r="CD8" s="24">
         <v>77</v>
       </c>
-      <c r="CE8" s="54">
+      <c r="CE8" s="24">
         <v>78</v>
       </c>
-      <c r="CF8" s="54">
+      <c r="CF8" s="24">
         <v>79</v>
       </c>
-      <c r="CG8" s="54">
+      <c r="CG8" s="24">
         <v>80</v>
       </c>
-      <c r="CH8" s="54">
+      <c r="CH8" s="24">
         <v>81</v>
       </c>
-      <c r="CI8" s="54">
+      <c r="CI8" s="24">
         <v>82</v>
       </c>
-      <c r="CJ8" s="54">
+      <c r="CJ8" s="24">
         <v>83</v>
       </c>
-      <c r="CK8" s="54">
+      <c r="CK8" s="24">
         <v>84</v>
       </c>
-      <c r="CL8" s="54">
+      <c r="CL8" s="24">
         <v>85</v>
       </c>
-      <c r="CM8" s="54">
+      <c r="CM8" s="24">
         <v>86</v>
       </c>
-      <c r="CN8" s="54">
+      <c r="CN8" s="24">
         <v>87</v>
       </c>
-      <c r="CO8" s="54">
+      <c r="CO8" s="24">
         <v>88</v>
       </c>
-      <c r="CP8" s="54">
+      <c r="CP8" s="24">
         <v>89</v>
       </c>
-      <c r="CQ8" s="54">
+      <c r="CQ8" s="24">
         <v>90</v>
       </c>
-      <c r="CR8" s="54">
+      <c r="CR8" s="24">
         <v>91</v>
       </c>
-      <c r="CS8" s="54">
+      <c r="CS8" s="24">
         <v>92</v>
       </c>
-      <c r="CT8" s="54">
+      <c r="CT8" s="24">
         <v>93</v>
       </c>
-      <c r="CU8" s="54">
+      <c r="CU8" s="24">
         <v>94</v>
       </c>
-      <c r="CV8" s="54">
+      <c r="CV8" s="24">
         <v>95</v>
       </c>
-      <c r="CW8" s="54">
+      <c r="CW8" s="24">
         <v>96</v>
       </c>
-      <c r="CX8" s="54">
+      <c r="CX8" s="24">
         <v>97</v>
       </c>
-      <c r="CY8" s="54">
+      <c r="CY8" s="24">
         <v>98</v>
       </c>
-      <c r="CZ8" s="54">
+      <c r="CZ8" s="24">
         <v>99</v>
       </c>
-      <c r="DA8" s="54">
+      <c r="DA8" s="24">
         <v>100</v>
       </c>
-      <c r="DB8" s="54">
+      <c r="DB8" s="24">
         <v>101</v>
       </c>
-      <c r="DC8" s="54">
+      <c r="DC8" s="24">
         <v>102</v>
       </c>
-      <c r="DD8" s="54">
+      <c r="DD8" s="24">
         <v>103</v>
       </c>
-      <c r="DE8" s="54">
+      <c r="DE8" s="24">
         <v>104</v>
       </c>
-      <c r="DF8" s="54">
+      <c r="DF8" s="24">
         <v>105</v>
       </c>
-      <c r="DG8" s="54">
+      <c r="DG8" s="24">
         <v>106</v>
       </c>
-      <c r="DH8" s="54">
+      <c r="DH8" s="24">
         <v>107</v>
       </c>
-      <c r="DI8" s="54">
+      <c r="DI8" s="24">
         <v>108</v>
       </c>
-      <c r="DJ8" s="54">
+      <c r="DJ8" s="24">
         <v>109</v>
       </c>
-      <c r="DK8" s="54">
+      <c r="DK8" s="24">
         <v>110</v>
       </c>
-      <c r="DL8" s="54">
+      <c r="DL8" s="24">
         <v>111</v>
       </c>
-      <c r="DM8" s="54">
+      <c r="DM8" s="24">
         <v>112</v>
       </c>
-      <c r="DN8" s="54">
+      <c r="DN8" s="24">
         <v>113</v>
       </c>
-      <c r="DO8" s="54">
+      <c r="DO8" s="24">
         <v>114</v>
       </c>
-      <c r="DP8" s="54">
+      <c r="DP8" s="24">
         <v>115</v>
       </c>
-      <c r="DQ8" s="54">
+      <c r="DQ8" s="24">
         <v>116</v>
       </c>
-      <c r="DR8" s="54">
+      <c r="DR8" s="24">
         <v>117</v>
       </c>
-      <c r="DS8" s="54">
+      <c r="DS8" s="24">
         <v>118</v>
       </c>
-      <c r="DT8" s="54">
+      <c r="DT8" s="24">
         <v>119</v>
       </c>
-      <c r="DU8" s="54">
+      <c r="DU8" s="24">
         <v>120</v>
       </c>
-      <c r="DV8" s="54">
+      <c r="DV8" s="24">
         <v>121</v>
       </c>
-      <c r="DW8" s="54">
+      <c r="DW8" s="24">
         <v>122</v>
       </c>
-      <c r="DX8" s="54">
+      <c r="DX8" s="24">
         <v>123</v>
       </c>
-      <c r="DY8" s="54">
+      <c r="DY8" s="24">
         <v>124</v>
       </c>
-      <c r="DZ8" s="54">
+      <c r="DZ8" s="24">
         <v>125</v>
       </c>
-      <c r="EA8" s="54">
+      <c r="EA8" s="24">
         <v>126</v>
       </c>
-      <c r="EB8" s="54">
+      <c r="EB8" s="24">
         <v>127</v>
       </c>
-      <c r="EC8" s="54">
+      <c r="EC8" s="24">
         <v>128</v>
       </c>
-      <c r="ED8" s="54">
+      <c r="ED8" s="24">
         <v>129</v>
       </c>
-      <c r="EE8" s="54">
+      <c r="EE8" s="24">
         <v>130</v>
       </c>
-      <c r="EF8" s="54">
+      <c r="EF8" s="24">
         <v>131</v>
       </c>
-      <c r="EG8" s="54">
+      <c r="EG8" s="24">
         <v>132</v>
       </c>
-      <c r="EH8" s="54">
+      <c r="EH8" s="24">
         <v>133</v>
       </c>
-      <c r="EI8" s="54">
+      <c r="EI8" s="24">
         <v>134</v>
       </c>
-      <c r="EJ8" s="54">
+      <c r="EJ8" s="24">
         <v>135</v>
       </c>
-      <c r="EK8" s="54">
+      <c r="EK8" s="24">
         <v>136</v>
       </c>
-      <c r="EL8" s="54">
+      <c r="EL8" s="24">
         <v>137</v>
       </c>
-      <c r="EM8" s="54">
+      <c r="EM8" s="24">
         <v>138</v>
       </c>
-      <c r="EN8" s="54">
+      <c r="EN8" s="24">
         <v>139</v>
       </c>
-      <c r="EO8" s="54">
+      <c r="EO8" s="24">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="57"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="55"/>
-      <c r="AC9" s="55"/>
-      <c r="AD9" s="55"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="55"/>
-      <c r="AG9" s="55"/>
-      <c r="AH9" s="55"/>
-      <c r="AI9" s="55"/>
-      <c r="AJ9" s="55"/>
-      <c r="AK9" s="55"/>
-      <c r="AL9" s="55"/>
-      <c r="AM9" s="55"/>
-      <c r="AN9" s="55"/>
-      <c r="AO9" s="55"/>
-      <c r="AP9" s="55"/>
-      <c r="AQ9" s="55"/>
-      <c r="AR9" s="55"/>
-      <c r="AS9" s="55"/>
-      <c r="AT9" s="55"/>
-      <c r="AU9" s="55"/>
-      <c r="AV9" s="55"/>
-      <c r="AW9" s="55"/>
-      <c r="AX9" s="55"/>
-      <c r="AY9" s="55"/>
-      <c r="AZ9" s="55"/>
-      <c r="BA9" s="55"/>
-      <c r="BB9" s="55"/>
-      <c r="BC9" s="55"/>
-      <c r="BD9" s="55"/>
-      <c r="BE9" s="55"/>
-      <c r="BF9" s="55"/>
-      <c r="BG9" s="55"/>
-      <c r="BH9" s="55"/>
-      <c r="BI9" s="55"/>
-      <c r="BJ9" s="55"/>
-      <c r="BK9" s="55"/>
-      <c r="BL9" s="55"/>
-      <c r="BM9" s="55"/>
-      <c r="BN9" s="55"/>
-      <c r="BO9" s="55"/>
-      <c r="BP9" s="55"/>
-      <c r="BQ9" s="55"/>
-      <c r="BR9" s="55"/>
-      <c r="BS9" s="55"/>
-      <c r="BT9" s="55"/>
-      <c r="BU9" s="55"/>
-      <c r="BV9" s="55"/>
-      <c r="BW9" s="55"/>
-      <c r="BX9" s="55"/>
-      <c r="BY9" s="55"/>
-      <c r="BZ9" s="55"/>
-      <c r="CA9" s="55"/>
-      <c r="CB9" s="55"/>
-      <c r="CC9" s="55"/>
-      <c r="CD9" s="55"/>
-      <c r="CE9" s="55"/>
-      <c r="CF9" s="55"/>
-      <c r="CG9" s="55"/>
-      <c r="CH9" s="55"/>
-      <c r="CI9" s="55"/>
-      <c r="CJ9" s="55"/>
-      <c r="CK9" s="55"/>
-      <c r="CL9" s="55"/>
-      <c r="CM9" s="55"/>
-      <c r="CN9" s="55"/>
-      <c r="CO9" s="55"/>
-      <c r="CP9" s="55"/>
-      <c r="CQ9" s="55"/>
-      <c r="CR9" s="55"/>
-      <c r="CS9" s="55"/>
-      <c r="CT9" s="55"/>
-      <c r="CU9" s="55"/>
-      <c r="CV9" s="55"/>
-      <c r="CW9" s="55"/>
-      <c r="CX9" s="55"/>
-      <c r="CY9" s="55"/>
-      <c r="CZ9" s="55"/>
-      <c r="DA9" s="55"/>
-      <c r="DB9" s="55"/>
-      <c r="DC9" s="55"/>
-      <c r="DD9" s="55"/>
-      <c r="DE9" s="55"/>
-      <c r="DF9" s="55"/>
-      <c r="DG9" s="55"/>
-      <c r="DH9" s="55"/>
-      <c r="DI9" s="55"/>
-      <c r="DJ9" s="55"/>
-      <c r="DK9" s="55"/>
-      <c r="DL9" s="55"/>
-      <c r="DM9" s="55"/>
-      <c r="DN9" s="55"/>
-      <c r="DO9" s="55"/>
-      <c r="DP9" s="55"/>
-      <c r="DQ9" s="55"/>
-      <c r="DR9" s="55"/>
-      <c r="DS9" s="55"/>
-      <c r="DT9" s="55"/>
-      <c r="DU9" s="55"/>
-      <c r="DV9" s="55"/>
-      <c r="DW9" s="55"/>
-      <c r="DX9" s="55"/>
-      <c r="DY9" s="55"/>
-      <c r="DZ9" s="55"/>
-      <c r="EA9" s="55"/>
-      <c r="EB9" s="55"/>
-      <c r="EC9" s="55"/>
-      <c r="ED9" s="55"/>
-      <c r="EE9" s="55"/>
-      <c r="EF9" s="55"/>
-      <c r="EG9" s="55"/>
-      <c r="EH9" s="55"/>
-      <c r="EI9" s="55"/>
-      <c r="EJ9" s="55"/>
-      <c r="EK9" s="55"/>
-      <c r="EL9" s="55"/>
-      <c r="EM9" s="55"/>
-      <c r="EN9" s="55"/>
-      <c r="EO9" s="55"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="25"/>
+      <c r="AL9" s="25"/>
+      <c r="AM9" s="25"/>
+      <c r="AN9" s="25"/>
+      <c r="AO9" s="25"/>
+      <c r="AP9" s="25"/>
+      <c r="AQ9" s="25"/>
+      <c r="AR9" s="25"/>
+      <c r="AS9" s="25"/>
+      <c r="AT9" s="25"/>
+      <c r="AU9" s="25"/>
+      <c r="AV9" s="25"/>
+      <c r="AW9" s="25"/>
+      <c r="AX9" s="25"/>
+      <c r="AY9" s="25"/>
+      <c r="AZ9" s="25"/>
+      <c r="BA9" s="25"/>
+      <c r="BB9" s="25"/>
+      <c r="BC9" s="25"/>
+      <c r="BD9" s="25"/>
+      <c r="BE9" s="25"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="25"/>
+      <c r="BI9" s="25"/>
+      <c r="BJ9" s="25"/>
+      <c r="BK9" s="25"/>
+      <c r="BL9" s="25"/>
+      <c r="BM9" s="25"/>
+      <c r="BN9" s="25"/>
+      <c r="BO9" s="25"/>
+      <c r="BP9" s="25"/>
+      <c r="BQ9" s="25"/>
+      <c r="BR9" s="25"/>
+      <c r="BS9" s="25"/>
+      <c r="BT9" s="25"/>
+      <c r="BU9" s="25"/>
+      <c r="BV9" s="25"/>
+      <c r="BW9" s="25"/>
+      <c r="BX9" s="25"/>
+      <c r="BY9" s="25"/>
+      <c r="BZ9" s="25"/>
+      <c r="CA9" s="25"/>
+      <c r="CB9" s="25"/>
+      <c r="CC9" s="25"/>
+      <c r="CD9" s="25"/>
+      <c r="CE9" s="25"/>
+      <c r="CF9" s="25"/>
+      <c r="CG9" s="25"/>
+      <c r="CH9" s="25"/>
+      <c r="CI9" s="25"/>
+      <c r="CJ9" s="25"/>
+      <c r="CK9" s="25"/>
+      <c r="CL9" s="25"/>
+      <c r="CM9" s="25"/>
+      <c r="CN9" s="25"/>
+      <c r="CO9" s="25"/>
+      <c r="CP9" s="25"/>
+      <c r="CQ9" s="25"/>
+      <c r="CR9" s="25"/>
+      <c r="CS9" s="25"/>
+      <c r="CT9" s="25"/>
+      <c r="CU9" s="25"/>
+      <c r="CV9" s="25"/>
+      <c r="CW9" s="25"/>
+      <c r="CX9" s="25"/>
+      <c r="CY9" s="25"/>
+      <c r="CZ9" s="25"/>
+      <c r="DA9" s="25"/>
+      <c r="DB9" s="25"/>
+      <c r="DC9" s="25"/>
+      <c r="DD9" s="25"/>
+      <c r="DE9" s="25"/>
+      <c r="DF9" s="25"/>
+      <c r="DG9" s="25"/>
+      <c r="DH9" s="25"/>
+      <c r="DI9" s="25"/>
+      <c r="DJ9" s="25"/>
+      <c r="DK9" s="25"/>
+      <c r="DL9" s="25"/>
+      <c r="DM9" s="25"/>
+      <c r="DN9" s="25"/>
+      <c r="DO9" s="25"/>
+      <c r="DP9" s="25"/>
+      <c r="DQ9" s="25"/>
+      <c r="DR9" s="25"/>
+      <c r="DS9" s="25"/>
+      <c r="DT9" s="25"/>
+      <c r="DU9" s="25"/>
+      <c r="DV9" s="25"/>
+      <c r="DW9" s="25"/>
+      <c r="DX9" s="25"/>
+      <c r="DY9" s="25"/>
+      <c r="DZ9" s="25"/>
+      <c r="EA9" s="25"/>
+      <c r="EB9" s="25"/>
+      <c r="EC9" s="25"/>
+      <c r="ED9" s="25"/>
+      <c r="EE9" s="25"/>
+      <c r="EF9" s="25"/>
+      <c r="EG9" s="25"/>
+      <c r="EH9" s="25"/>
+      <c r="EI9" s="25"/>
+      <c r="EJ9" s="25"/>
+      <c r="EK9" s="25"/>
+      <c r="EL9" s="25"/>
+      <c r="EM9" s="25"/>
+      <c r="EN9" s="25"/>
+      <c r="EO9" s="25"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="10"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
@@ -3270,7 +3290,7 @@
       </c>
       <c r="D12" s="15">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="12"/>
@@ -3337,14 +3357,30 @@
       <c r="BG12" s="12">
         <v>0</v>
       </c>
-      <c r="BH12" s="12"/>
-      <c r="BI12" s="12"/>
-      <c r="BJ12" s="12"/>
-      <c r="BK12" s="12"/>
-      <c r="BL12" s="12"/>
-      <c r="BM12" s="12"/>
-      <c r="BN12" s="12"/>
-      <c r="BO12" s="12"/>
+      <c r="BH12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="12">
+        <v>0</v>
+      </c>
       <c r="BP12" s="12"/>
       <c r="BQ12" s="12"/>
       <c r="BR12" s="12"/>
@@ -3436,7 +3472,7 @@
       </c>
       <c r="D13" s="15">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="12"/>
@@ -3519,14 +3555,30 @@
       <c r="BG13" s="12">
         <v>0</v>
       </c>
-      <c r="BH13" s="12"/>
-      <c r="BI13" s="12"/>
-      <c r="BJ13" s="12"/>
-      <c r="BK13" s="12"/>
-      <c r="BL13" s="12"/>
-      <c r="BM13" s="12"/>
-      <c r="BN13" s="12"/>
-      <c r="BO13" s="12"/>
+      <c r="BH13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="12">
+        <v>0</v>
+      </c>
       <c r="BP13" s="12"/>
       <c r="BQ13" s="12"/>
       <c r="BR13" s="12"/>
@@ -3622,7 +3674,7 @@
       </c>
       <c r="D14" s="15">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="12"/>
@@ -3694,9 +3746,15 @@
       <c r="BJ14" s="12"/>
       <c r="BK14" s="12"/>
       <c r="BL14" s="12"/>
-      <c r="BM14" s="12"/>
-      <c r="BN14" s="12"/>
-      <c r="BO14" s="12"/>
+      <c r="BM14" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN14" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO14" s="12">
+        <v>0</v>
+      </c>
       <c r="BP14" s="12"/>
       <c r="BQ14" s="12"/>
       <c r="BR14" s="12"/>
@@ -3788,7 +3846,7 @@
       </c>
       <c r="D15" s="15">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="12"/>
@@ -3870,9 +3928,15 @@
       <c r="BJ15" s="12"/>
       <c r="BK15" s="12"/>
       <c r="BL15" s="12"/>
-      <c r="BM15" s="12"/>
-      <c r="BN15" s="12"/>
-      <c r="BO15" s="12"/>
+      <c r="BM15" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO15" s="12">
+        <v>0</v>
+      </c>
       <c r="BP15" s="12"/>
       <c r="BQ15" s="12"/>
       <c r="BR15" s="12"/>
@@ -4228,113 +4292,113 @@
       <c r="AN17" s="12">
         <v>0</v>
       </c>
-      <c r="AO17" s="22" t="s">
+      <c r="AO17" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="23"/>
-      <c r="AR17" s="23"/>
-      <c r="AS17" s="23"/>
-      <c r="AT17" s="23"/>
-      <c r="AU17" s="23"/>
-      <c r="AV17" s="23"/>
-      <c r="AW17" s="23"/>
-      <c r="AX17" s="23"/>
-      <c r="AY17" s="23"/>
-      <c r="AZ17" s="23"/>
-      <c r="BA17" s="23"/>
-      <c r="BB17" s="23"/>
-      <c r="BC17" s="23"/>
-      <c r="BD17" s="23"/>
-      <c r="BE17" s="23"/>
-      <c r="BF17" s="23"/>
-      <c r="BG17" s="23"/>
-      <c r="BH17" s="23"/>
-      <c r="BI17" s="23"/>
-      <c r="BJ17" s="23"/>
-      <c r="BK17" s="23"/>
-      <c r="BL17" s="23"/>
-      <c r="BM17" s="23"/>
-      <c r="BN17" s="23"/>
-      <c r="BO17" s="23"/>
-      <c r="BP17" s="23"/>
-      <c r="BQ17" s="23"/>
-      <c r="BR17" s="23"/>
-      <c r="BS17" s="23"/>
-      <c r="BT17" s="23"/>
-      <c r="BU17" s="23"/>
-      <c r="BV17" s="23"/>
-      <c r="BW17" s="23"/>
-      <c r="BX17" s="23"/>
-      <c r="BY17" s="23"/>
-      <c r="BZ17" s="23"/>
-      <c r="CA17" s="23"/>
-      <c r="CB17" s="23"/>
-      <c r="CC17" s="23"/>
-      <c r="CD17" s="23"/>
-      <c r="CE17" s="23"/>
-      <c r="CF17" s="23"/>
-      <c r="CG17" s="23"/>
-      <c r="CH17" s="23"/>
-      <c r="CI17" s="23"/>
-      <c r="CJ17" s="23"/>
-      <c r="CK17" s="23"/>
-      <c r="CL17" s="23"/>
-      <c r="CM17" s="23"/>
-      <c r="CN17" s="23"/>
-      <c r="CO17" s="23"/>
-      <c r="CP17" s="23"/>
-      <c r="CQ17" s="23"/>
-      <c r="CR17" s="23"/>
-      <c r="CS17" s="23"/>
-      <c r="CT17" s="23"/>
-      <c r="CU17" s="23"/>
-      <c r="CV17" s="23"/>
-      <c r="CW17" s="23"/>
-      <c r="CX17" s="23"/>
-      <c r="CY17" s="23"/>
-      <c r="CZ17" s="23"/>
-      <c r="DA17" s="23"/>
-      <c r="DB17" s="23"/>
-      <c r="DC17" s="23"/>
-      <c r="DD17" s="23"/>
-      <c r="DE17" s="23"/>
-      <c r="DF17" s="23"/>
-      <c r="DG17" s="23"/>
-      <c r="DH17" s="23"/>
-      <c r="DI17" s="23"/>
-      <c r="DJ17" s="23"/>
-      <c r="DK17" s="23"/>
-      <c r="DL17" s="23"/>
-      <c r="DM17" s="23"/>
-      <c r="DN17" s="23"/>
-      <c r="DO17" s="23"/>
-      <c r="DP17" s="23"/>
-      <c r="DQ17" s="23"/>
-      <c r="DR17" s="23"/>
-      <c r="DS17" s="23"/>
-      <c r="DT17" s="23"/>
-      <c r="DU17" s="23"/>
-      <c r="DV17" s="23"/>
-      <c r="DW17" s="23"/>
-      <c r="DX17" s="23"/>
-      <c r="DY17" s="23"/>
-      <c r="DZ17" s="23"/>
-      <c r="EA17" s="23"/>
-      <c r="EB17" s="23"/>
-      <c r="EC17" s="23"/>
-      <c r="ED17" s="23"/>
-      <c r="EE17" s="23"/>
-      <c r="EF17" s="23"/>
-      <c r="EG17" s="23"/>
-      <c r="EH17" s="23"/>
-      <c r="EI17" s="23"/>
-      <c r="EJ17" s="23"/>
-      <c r="EK17" s="23"/>
-      <c r="EL17" s="23"/>
-      <c r="EM17" s="23"/>
-      <c r="EN17" s="23"/>
-      <c r="EO17" s="24"/>
+      <c r="AP17" s="49"/>
+      <c r="AQ17" s="49"/>
+      <c r="AR17" s="49"/>
+      <c r="AS17" s="49"/>
+      <c r="AT17" s="49"/>
+      <c r="AU17" s="49"/>
+      <c r="AV17" s="49"/>
+      <c r="AW17" s="49"/>
+      <c r="AX17" s="49"/>
+      <c r="AY17" s="49"/>
+      <c r="AZ17" s="49"/>
+      <c r="BA17" s="49"/>
+      <c r="BB17" s="49"/>
+      <c r="BC17" s="49"/>
+      <c r="BD17" s="49"/>
+      <c r="BE17" s="49"/>
+      <c r="BF17" s="49"/>
+      <c r="BG17" s="49"/>
+      <c r="BH17" s="49"/>
+      <c r="BI17" s="49"/>
+      <c r="BJ17" s="49"/>
+      <c r="BK17" s="49"/>
+      <c r="BL17" s="49"/>
+      <c r="BM17" s="49"/>
+      <c r="BN17" s="49"/>
+      <c r="BO17" s="49"/>
+      <c r="BP17" s="49"/>
+      <c r="BQ17" s="49"/>
+      <c r="BR17" s="49"/>
+      <c r="BS17" s="49"/>
+      <c r="BT17" s="49"/>
+      <c r="BU17" s="49"/>
+      <c r="BV17" s="49"/>
+      <c r="BW17" s="49"/>
+      <c r="BX17" s="49"/>
+      <c r="BY17" s="49"/>
+      <c r="BZ17" s="49"/>
+      <c r="CA17" s="49"/>
+      <c r="CB17" s="49"/>
+      <c r="CC17" s="49"/>
+      <c r="CD17" s="49"/>
+      <c r="CE17" s="49"/>
+      <c r="CF17" s="49"/>
+      <c r="CG17" s="49"/>
+      <c r="CH17" s="49"/>
+      <c r="CI17" s="49"/>
+      <c r="CJ17" s="49"/>
+      <c r="CK17" s="49"/>
+      <c r="CL17" s="49"/>
+      <c r="CM17" s="49"/>
+      <c r="CN17" s="49"/>
+      <c r="CO17" s="49"/>
+      <c r="CP17" s="49"/>
+      <c r="CQ17" s="49"/>
+      <c r="CR17" s="49"/>
+      <c r="CS17" s="49"/>
+      <c r="CT17" s="49"/>
+      <c r="CU17" s="49"/>
+      <c r="CV17" s="49"/>
+      <c r="CW17" s="49"/>
+      <c r="CX17" s="49"/>
+      <c r="CY17" s="49"/>
+      <c r="CZ17" s="49"/>
+      <c r="DA17" s="49"/>
+      <c r="DB17" s="49"/>
+      <c r="DC17" s="49"/>
+      <c r="DD17" s="49"/>
+      <c r="DE17" s="49"/>
+      <c r="DF17" s="49"/>
+      <c r="DG17" s="49"/>
+      <c r="DH17" s="49"/>
+      <c r="DI17" s="49"/>
+      <c r="DJ17" s="49"/>
+      <c r="DK17" s="49"/>
+      <c r="DL17" s="49"/>
+      <c r="DM17" s="49"/>
+      <c r="DN17" s="49"/>
+      <c r="DO17" s="49"/>
+      <c r="DP17" s="49"/>
+      <c r="DQ17" s="49"/>
+      <c r="DR17" s="49"/>
+      <c r="DS17" s="49"/>
+      <c r="DT17" s="49"/>
+      <c r="DU17" s="49"/>
+      <c r="DV17" s="49"/>
+      <c r="DW17" s="49"/>
+      <c r="DX17" s="49"/>
+      <c r="DY17" s="49"/>
+      <c r="DZ17" s="49"/>
+      <c r="EA17" s="49"/>
+      <c r="EB17" s="49"/>
+      <c r="EC17" s="49"/>
+      <c r="ED17" s="49"/>
+      <c r="EE17" s="49"/>
+      <c r="EF17" s="49"/>
+      <c r="EG17" s="49"/>
+      <c r="EH17" s="49"/>
+      <c r="EI17" s="49"/>
+      <c r="EJ17" s="49"/>
+      <c r="EK17" s="49"/>
+      <c r="EL17" s="49"/>
+      <c r="EM17" s="49"/>
+      <c r="EN17" s="49"/>
+      <c r="EO17" s="50"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
@@ -4348,7 +4412,7 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="12"/>
@@ -4412,9 +4476,15 @@
       <c r="BJ18" s="12"/>
       <c r="BK18" s="12"/>
       <c r="BL18" s="12"/>
-      <c r="BM18" s="12"/>
-      <c r="BN18" s="12"/>
-      <c r="BO18" s="12"/>
+      <c r="BM18" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN18" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO18" s="12">
+        <v>0</v>
+      </c>
       <c r="BP18" s="12"/>
       <c r="BQ18" s="12"/>
       <c r="BR18" s="12"/>
@@ -4506,7 +4576,7 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="12"/>
@@ -4573,14 +4643,30 @@
       <c r="BG19" s="12">
         <v>0</v>
       </c>
-      <c r="BH19" s="12"/>
-      <c r="BI19" s="12"/>
-      <c r="BJ19" s="12"/>
-      <c r="BK19" s="12"/>
-      <c r="BL19" s="12"/>
-      <c r="BM19" s="12"/>
-      <c r="BN19" s="12"/>
-      <c r="BO19" s="12"/>
+      <c r="BH19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO19" s="12">
+        <v>0</v>
+      </c>
       <c r="BP19" s="12"/>
       <c r="BQ19" s="12"/>
       <c r="BR19" s="12"/>
@@ -4672,7 +4758,7 @@
       </c>
       <c r="D20" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="12"/>
@@ -4729,11 +4815,21 @@
       <c r="BE20" s="12"/>
       <c r="BF20" s="12"/>
       <c r="BG20" s="12"/>
-      <c r="BH20" s="12"/>
-      <c r="BI20" s="12"/>
-      <c r="BJ20" s="12"/>
-      <c r="BK20" s="12"/>
-      <c r="BL20" s="12"/>
+      <c r="BH20" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK20" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL20" s="12">
+        <v>0</v>
+      </c>
       <c r="BM20" s="12"/>
       <c r="BN20" s="12"/>
       <c r="BO20" s="12"/>
@@ -4828,7 +4924,7 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="12"/>
@@ -4979,14 +5075,30 @@
       <c r="BG21" s="12">
         <v>0</v>
       </c>
-      <c r="BH21" s="12"/>
-      <c r="BI21" s="12"/>
-      <c r="BJ21" s="12"/>
-      <c r="BK21" s="12"/>
-      <c r="BL21" s="12"/>
-      <c r="BM21" s="12"/>
-      <c r="BN21" s="12"/>
-      <c r="BO21" s="12"/>
+      <c r="BH21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN21" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO21" s="12">
+        <v>0</v>
+      </c>
       <c r="BP21" s="12"/>
       <c r="BQ21" s="12"/>
       <c r="BR21" s="12"/>
@@ -5078,7 +5190,7 @@
       </c>
       <c r="D22" s="15">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E22" s="16"/>
       <c r="F22" s="12"/>
@@ -5153,14 +5265,30 @@
       <c r="BG22" s="12">
         <v>0</v>
       </c>
-      <c r="BH22" s="12"/>
-      <c r="BI22" s="12"/>
-      <c r="BJ22" s="12"/>
-      <c r="BK22" s="12"/>
-      <c r="BL22" s="12"/>
-      <c r="BM22" s="12"/>
-      <c r="BN22" s="12"/>
-      <c r="BO22" s="12"/>
+      <c r="BH22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN22" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO22" s="12">
+        <v>0</v>
+      </c>
       <c r="BP22" s="12"/>
       <c r="BQ22" s="12"/>
       <c r="BR22" s="12"/>
@@ -5252,7 +5380,7 @@
       </c>
       <c r="D23" s="15">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="12">
@@ -5407,14 +5535,30 @@
       <c r="BG23" s="12">
         <v>0</v>
       </c>
-      <c r="BH23" s="12"/>
-      <c r="BI23" s="12"/>
-      <c r="BJ23" s="12"/>
-      <c r="BK23" s="12"/>
-      <c r="BL23" s="12"/>
-      <c r="BM23" s="12"/>
-      <c r="BN23" s="12"/>
-      <c r="BO23" s="12"/>
+      <c r="BH23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN23" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO23" s="12">
+        <v>0</v>
+      </c>
       <c r="BP23" s="12"/>
       <c r="BQ23" s="12"/>
       <c r="BR23" s="12"/>
@@ -5506,7 +5650,7 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E24" s="16"/>
       <c r="F24" s="12"/>
@@ -5589,11 +5733,21 @@
       <c r="BG24" s="12">
         <v>0</v>
       </c>
-      <c r="BH24" s="12"/>
-      <c r="BI24" s="12"/>
-      <c r="BJ24" s="12"/>
-      <c r="BK24" s="12"/>
-      <c r="BL24" s="12"/>
+      <c r="BH24" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK24" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL24" s="12">
+        <v>0</v>
+      </c>
       <c r="BM24" s="12"/>
       <c r="BN24" s="12"/>
       <c r="BO24" s="12"/>
@@ -5688,7 +5842,7 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="12"/>
@@ -5779,14 +5933,30 @@
       <c r="BG25" s="12">
         <v>0</v>
       </c>
-      <c r="BH25" s="12"/>
-      <c r="BI25" s="12"/>
-      <c r="BJ25" s="12"/>
-      <c r="BK25" s="12"/>
-      <c r="BL25" s="12"/>
-      <c r="BM25" s="12"/>
-      <c r="BN25" s="12"/>
-      <c r="BO25" s="12"/>
+      <c r="BH25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN25" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO25" s="12">
+        <v>0</v>
+      </c>
       <c r="BP25" s="12"/>
       <c r="BQ25" s="12"/>
       <c r="BR25" s="12"/>
@@ -5878,7 +6048,7 @@
       </c>
       <c r="D26" s="15">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E26" s="16"/>
       <c r="F26" s="12"/>
@@ -5953,14 +6123,30 @@
       <c r="BG26" s="12">
         <v>0</v>
       </c>
-      <c r="BH26" s="12"/>
-      <c r="BI26" s="12"/>
-      <c r="BJ26" s="12"/>
-      <c r="BK26" s="12"/>
-      <c r="BL26" s="12"/>
-      <c r="BM26" s="12"/>
-      <c r="BN26" s="12"/>
-      <c r="BO26" s="12"/>
+      <c r="BH26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN26" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO26" s="12">
+        <v>0</v>
+      </c>
       <c r="BP26" s="12"/>
       <c r="BQ26" s="12"/>
       <c r="BR26" s="12"/>
@@ -6052,7 +6238,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="12"/>
@@ -6203,14 +6389,30 @@
       <c r="BG27" s="12">
         <v>0</v>
       </c>
-      <c r="BH27" s="12"/>
-      <c r="BI27" s="12"/>
-      <c r="BJ27" s="12"/>
-      <c r="BK27" s="12"/>
-      <c r="BL27" s="12"/>
-      <c r="BM27" s="12"/>
-      <c r="BN27" s="12"/>
-      <c r="BO27" s="12"/>
+      <c r="BH27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BK27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BM27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BN27" s="12">
+        <v>0</v>
+      </c>
+      <c r="BO27" s="12">
+        <v>0</v>
+      </c>
       <c r="BP27" s="12"/>
       <c r="BQ27" s="12"/>
       <c r="BR27" s="12"/>
@@ -6304,149 +6506,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="59"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="59"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="59"/>
-      <c r="U28" s="59"/>
-      <c r="V28" s="59"/>
-      <c r="W28" s="59"/>
-      <c r="X28" s="59"/>
-      <c r="Y28" s="59"/>
-      <c r="Z28" s="59"/>
-      <c r="AA28" s="59"/>
-      <c r="AB28" s="59"/>
-      <c r="AC28" s="59"/>
-      <c r="AD28" s="59"/>
-      <c r="AE28" s="59"/>
-      <c r="AF28" s="59"/>
-      <c r="AG28" s="59"/>
-      <c r="AH28" s="59"/>
-      <c r="AI28" s="59"/>
-      <c r="AJ28" s="59"/>
-      <c r="AK28" s="59"/>
-      <c r="AL28" s="59"/>
-      <c r="AM28" s="59"/>
-      <c r="AN28" s="59"/>
-      <c r="AO28" s="59"/>
-      <c r="AP28" s="59"/>
-      <c r="AQ28" s="59"/>
-      <c r="AR28" s="59"/>
-      <c r="AS28" s="59"/>
-      <c r="AT28" s="59"/>
-      <c r="AU28" s="59"/>
-      <c r="AV28" s="59"/>
-      <c r="AW28" s="59"/>
-      <c r="AX28" s="59"/>
-      <c r="AY28" s="59"/>
-      <c r="AZ28" s="59"/>
-      <c r="BA28" s="59"/>
-      <c r="BB28" s="59"/>
-      <c r="BC28" s="59"/>
-      <c r="BD28" s="59"/>
-      <c r="BE28" s="59"/>
-      <c r="BF28" s="59"/>
-      <c r="BG28" s="59"/>
-      <c r="BH28" s="59"/>
-      <c r="BI28" s="59"/>
-      <c r="BJ28" s="59"/>
-      <c r="BK28" s="59"/>
-      <c r="BL28" s="59"/>
-      <c r="BM28" s="59"/>
-      <c r="BN28" s="59"/>
-      <c r="BO28" s="59"/>
-      <c r="BP28" s="59"/>
-      <c r="BQ28" s="59"/>
-      <c r="BR28" s="59"/>
-      <c r="BS28" s="59"/>
-      <c r="BT28" s="59"/>
-      <c r="BU28" s="59"/>
-      <c r="BV28" s="59"/>
-      <c r="BW28" s="59"/>
-      <c r="BX28" s="59"/>
-      <c r="BY28" s="59"/>
-      <c r="BZ28" s="59"/>
-      <c r="CA28" s="59"/>
-      <c r="CB28" s="59"/>
-      <c r="CC28" s="59"/>
-      <c r="CD28" s="59"/>
-      <c r="CE28" s="59"/>
-      <c r="CF28" s="59"/>
-      <c r="CG28" s="59"/>
-      <c r="CH28" s="59"/>
-      <c r="CI28" s="59"/>
-      <c r="CJ28" s="59"/>
-      <c r="CK28" s="59"/>
-      <c r="CL28" s="59"/>
-      <c r="CM28" s="59"/>
-      <c r="CN28" s="59"/>
-      <c r="CO28" s="59"/>
-      <c r="CP28" s="59"/>
-      <c r="CQ28" s="59"/>
-      <c r="CR28" s="59"/>
-      <c r="CS28" s="59"/>
-      <c r="CT28" s="59"/>
-      <c r="CU28" s="59"/>
-      <c r="CV28" s="59"/>
-      <c r="CW28" s="59"/>
-      <c r="CX28" s="59"/>
-      <c r="CY28" s="59"/>
-      <c r="CZ28" s="59"/>
-      <c r="DA28" s="59"/>
-      <c r="DB28" s="59"/>
-      <c r="DC28" s="59"/>
-      <c r="DD28" s="59"/>
-      <c r="DE28" s="59"/>
-      <c r="DF28" s="59"/>
-      <c r="DG28" s="59"/>
-      <c r="DH28" s="59"/>
-      <c r="DI28" s="59"/>
-      <c r="DJ28" s="59"/>
-      <c r="DK28" s="59"/>
-      <c r="DL28" s="59"/>
-      <c r="DM28" s="59"/>
-      <c r="DN28" s="59"/>
-      <c r="DO28" s="59"/>
-      <c r="DP28" s="59"/>
-      <c r="DQ28" s="59"/>
-      <c r="DR28" s="59"/>
-      <c r="DS28" s="59"/>
-      <c r="DT28" s="59"/>
-      <c r="DU28" s="59"/>
-      <c r="DV28" s="59"/>
-      <c r="DW28" s="59"/>
-      <c r="DX28" s="59"/>
-      <c r="DY28" s="59"/>
-      <c r="DZ28" s="59"/>
-      <c r="EA28" s="59"/>
-      <c r="EB28" s="59"/>
-      <c r="EC28" s="59"/>
-      <c r="ED28" s="59"/>
-      <c r="EE28" s="59"/>
-      <c r="EF28" s="59"/>
-      <c r="EG28" s="59"/>
-      <c r="EH28" s="59"/>
-      <c r="EI28" s="59"/>
-      <c r="EJ28" s="59"/>
-      <c r="EK28" s="59"/>
-      <c r="EL28" s="59"/>
-      <c r="EM28" s="59"/>
-      <c r="EN28" s="59"/>
-      <c r="EO28" s="59"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="26"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="26"/>
+      <c r="AB28" s="26"/>
+      <c r="AC28" s="26"/>
+      <c r="AD28" s="26"/>
+      <c r="AE28" s="26"/>
+      <c r="AF28" s="26"/>
+      <c r="AG28" s="26"/>
+      <c r="AH28" s="26"/>
+      <c r="AI28" s="26"/>
+      <c r="AJ28" s="26"/>
+      <c r="AK28" s="26"/>
+      <c r="AL28" s="26"/>
+      <c r="AM28" s="26"/>
+      <c r="AN28" s="26"/>
+      <c r="AO28" s="26"/>
+      <c r="AP28" s="26"/>
+      <c r="AQ28" s="26"/>
+      <c r="AR28" s="26"/>
+      <c r="AS28" s="26"/>
+      <c r="AT28" s="26"/>
+      <c r="AU28" s="26"/>
+      <c r="AV28" s="26"/>
+      <c r="AW28" s="26"/>
+      <c r="AX28" s="26"/>
+      <c r="AY28" s="26"/>
+      <c r="AZ28" s="26"/>
+      <c r="BA28" s="26"/>
+      <c r="BB28" s="26"/>
+      <c r="BC28" s="26"/>
+      <c r="BD28" s="26"/>
+      <c r="BE28" s="26"/>
+      <c r="BF28" s="26"/>
+      <c r="BG28" s="26"/>
+      <c r="BH28" s="26"/>
+      <c r="BI28" s="26"/>
+      <c r="BJ28" s="26"/>
+      <c r="BK28" s="26"/>
+      <c r="BL28" s="26"/>
+      <c r="BM28" s="26"/>
+      <c r="BN28" s="26"/>
+      <c r="BO28" s="26"/>
+      <c r="BP28" s="26"/>
+      <c r="BQ28" s="26"/>
+      <c r="BR28" s="26"/>
+      <c r="BS28" s="26"/>
+      <c r="BT28" s="26"/>
+      <c r="BU28" s="26"/>
+      <c r="BV28" s="26"/>
+      <c r="BW28" s="26"/>
+      <c r="BX28" s="26"/>
+      <c r="BY28" s="26"/>
+      <c r="BZ28" s="26"/>
+      <c r="CA28" s="26"/>
+      <c r="CB28" s="26"/>
+      <c r="CC28" s="26"/>
+      <c r="CD28" s="26"/>
+      <c r="CE28" s="26"/>
+      <c r="CF28" s="26"/>
+      <c r="CG28" s="26"/>
+      <c r="CH28" s="26"/>
+      <c r="CI28" s="26"/>
+      <c r="CJ28" s="26"/>
+      <c r="CK28" s="26"/>
+      <c r="CL28" s="26"/>
+      <c r="CM28" s="26"/>
+      <c r="CN28" s="26"/>
+      <c r="CO28" s="26"/>
+      <c r="CP28" s="26"/>
+      <c r="CQ28" s="26"/>
+      <c r="CR28" s="26"/>
+      <c r="CS28" s="26"/>
+      <c r="CT28" s="26"/>
+      <c r="CU28" s="26"/>
+      <c r="CV28" s="26"/>
+      <c r="CW28" s="26"/>
+      <c r="CX28" s="26"/>
+      <c r="CY28" s="26"/>
+      <c r="CZ28" s="26"/>
+      <c r="DA28" s="26"/>
+      <c r="DB28" s="26"/>
+      <c r="DC28" s="26"/>
+      <c r="DD28" s="26"/>
+      <c r="DE28" s="26"/>
+      <c r="DF28" s="26"/>
+      <c r="DG28" s="26"/>
+      <c r="DH28" s="26"/>
+      <c r="DI28" s="26"/>
+      <c r="DJ28" s="26"/>
+      <c r="DK28" s="26"/>
+      <c r="DL28" s="26"/>
+      <c r="DM28" s="26"/>
+      <c r="DN28" s="26"/>
+      <c r="DO28" s="26"/>
+      <c r="DP28" s="26"/>
+      <c r="DQ28" s="26"/>
+      <c r="DR28" s="26"/>
+      <c r="DS28" s="26"/>
+      <c r="DT28" s="26"/>
+      <c r="DU28" s="26"/>
+      <c r="DV28" s="26"/>
+      <c r="DW28" s="26"/>
+      <c r="DX28" s="26"/>
+      <c r="DY28" s="26"/>
+      <c r="DZ28" s="26"/>
+      <c r="EA28" s="26"/>
+      <c r="EB28" s="26"/>
+      <c r="EC28" s="26"/>
+      <c r="ED28" s="26"/>
+      <c r="EE28" s="26"/>
+      <c r="EF28" s="26"/>
+      <c r="EG28" s="26"/>
+      <c r="EH28" s="26"/>
+      <c r="EI28" s="26"/>
+      <c r="EJ28" s="26"/>
+      <c r="EK28" s="26"/>
+      <c r="EL28" s="26"/>
+      <c r="EM28" s="26"/>
+      <c r="EN28" s="26"/>
+      <c r="EO28" s="26"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6454,30 +6656,274 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="313">
-    <mergeCell ref="EH8:EH9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="DV8:DV9"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
+  <mergeCells count="315">
+    <mergeCell ref="AO17:EO17"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="BM1:BO1"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
     <mergeCell ref="DC8:DC9"/>
     <mergeCell ref="E28:EO28"/>
     <mergeCell ref="AC1:AD1"/>
@@ -6502,272 +6948,30 @@
     <mergeCell ref="EB8:EB9"/>
     <mergeCell ref="EC8:EC9"/>
     <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AO17:EO17"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="DV8:DV9"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB14B79D-3BAF-4ABA-9501-EADE776333C1}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F4A42-CD37-415C-A790-98D22D08A0D9}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,6 +819,105 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -849,9 +948,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -868,102 +964,6 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
@@ -1193,127 +1193,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
-      <c r="F1" s="29">
+      <c r="C1" s="58"/>
+      <c r="D1" s="59"/>
+      <c r="F1" s="62">
         <v>4</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="31">
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="33">
         <v>3</v>
       </c>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31">
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33">
         <v>4</v>
       </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="32">
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="64">
         <v>4</v>
       </c>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="32">
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="64">
         <v>4</v>
       </c>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="32">
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="64">
         <v>4</v>
       </c>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="62">
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="31">
         <v>2</v>
       </c>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="42">
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="25">
         <v>4</v>
       </c>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="42">
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="25">
         <v>4</v>
       </c>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="44"/>
-      <c r="AM1" s="42">
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="27"/>
+      <c r="AM1" s="25">
         <v>2</v>
       </c>
-      <c r="AN1" s="44"/>
-      <c r="AO1" s="42">
+      <c r="AN1" s="27"/>
+      <c r="AO1" s="25">
         <v>4</v>
       </c>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="43"/>
-      <c r="AR1" s="44"/>
-      <c r="AS1" s="42">
+      <c r="AP1" s="26"/>
+      <c r="AQ1" s="26"/>
+      <c r="AR1" s="27"/>
+      <c r="AS1" s="25">
         <v>5</v>
       </c>
-      <c r="AT1" s="43"/>
-      <c r="AU1" s="43"/>
-      <c r="AV1" s="43"/>
-      <c r="AW1" s="44"/>
+      <c r="AT1" s="26"/>
+      <c r="AU1" s="26"/>
+      <c r="AV1" s="26"/>
+      <c r="AW1" s="27"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="42">
+      <c r="AY1" s="25">
         <v>5</v>
       </c>
-      <c r="AZ1" s="43"/>
-      <c r="BA1" s="43"/>
-      <c r="BB1" s="43"/>
-      <c r="BC1" s="44"/>
-      <c r="BD1" s="42">
+      <c r="AZ1" s="26"/>
+      <c r="BA1" s="26"/>
+      <c r="BB1" s="26"/>
+      <c r="BC1" s="27"/>
+      <c r="BD1" s="25">
         <v>3</v>
       </c>
-      <c r="BE1" s="43"/>
-      <c r="BF1" s="44"/>
+      <c r="BE1" s="26"/>
+      <c r="BF1" s="27"/>
       <c r="BG1" s="20">
         <v>1</v>
       </c>
-      <c r="BH1" s="31">
+      <c r="BH1" s="33">
         <v>5</v>
       </c>
-      <c r="BI1" s="31"/>
-      <c r="BJ1" s="31"/>
-      <c r="BK1" s="31"/>
-      <c r="BL1" s="31"/>
-      <c r="BM1" s="42">
+      <c r="BI1" s="33"/>
+      <c r="BJ1" s="33"/>
+      <c r="BK1" s="33"/>
+      <c r="BL1" s="33"/>
+      <c r="BM1" s="25">
         <v>3</v>
       </c>
-      <c r="BN1" s="43"/>
-      <c r="BO1" s="44"/>
-      <c r="BP1" s="64">
+      <c r="BN1" s="26"/>
+      <c r="BO1" s="27"/>
+      <c r="BP1" s="21">
         <v>1</v>
       </c>
-      <c r="BQ1" s="65">
+      <c r="BQ1" s="22">
         <v>5</v>
       </c>
-      <c r="BR1" s="66"/>
-      <c r="BS1" s="66"/>
-      <c r="BT1" s="66"/>
-      <c r="BU1" s="67"/>
-      <c r="BV1" s="42">
+      <c r="BR1" s="23"/>
+      <c r="BS1" s="23"/>
+      <c r="BT1" s="23"/>
+      <c r="BU1" s="24"/>
+      <c r="BV1" s="25">
         <v>3</v>
       </c>
-      <c r="BW1" s="43"/>
-      <c r="BX1" s="44"/>
+      <c r="BW1" s="26"/>
+      <c r="BX1" s="27"/>
       <c r="BY1" s="4"/>
       <c r="BZ1" s="4"/>
       <c r="CA1" s="4"/>
@@ -1389,1636 +1389,1636 @@
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="35" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="O2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="38" t="s">
+      <c r="P2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="38" t="s">
+      <c r="Q2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="R2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="40" t="s">
+      <c r="S2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="40" t="s">
+      <c r="T2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="38" t="s">
+      <c r="U2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="V2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="40" t="s">
+      <c r="W2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Y2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="Z2" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="45" t="s">
+      <c r="AA2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="45" t="s">
+      <c r="AB2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="38">
+      <c r="AC2" s="40">
         <v>46199</v>
       </c>
-      <c r="AD2" s="38">
+      <c r="AD2" s="40">
         <v>46199</v>
       </c>
-      <c r="AE2" s="38">
+      <c r="AE2" s="40">
         <v>46202</v>
       </c>
-      <c r="AF2" s="38">
+      <c r="AF2" s="40">
         <v>46202</v>
       </c>
-      <c r="AG2" s="38">
+      <c r="AG2" s="40">
         <v>46202</v>
       </c>
-      <c r="AH2" s="38">
+      <c r="AH2" s="40">
         <v>46202</v>
       </c>
-      <c r="AI2" s="38">
+      <c r="AI2" s="40">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="38">
+      <c r="AJ2" s="40">
         <v>46205</v>
       </c>
-      <c r="AK2" s="38">
+      <c r="AK2" s="40">
         <v>46205</v>
       </c>
-      <c r="AL2" s="38">
+      <c r="AL2" s="40">
         <v>46205</v>
       </c>
-      <c r="AM2" s="38">
+      <c r="AM2" s="40">
         <v>46206</v>
       </c>
-      <c r="AN2" s="38">
+      <c r="AN2" s="40">
         <v>46206</v>
       </c>
-      <c r="AO2" s="38">
+      <c r="AO2" s="40">
         <v>46212</v>
       </c>
-      <c r="AP2" s="38">
+      <c r="AP2" s="40">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="38">
+      <c r="AQ2" s="40">
         <v>46212</v>
       </c>
-      <c r="AR2" s="38">
+      <c r="AR2" s="40">
         <v>46212</v>
       </c>
-      <c r="AS2" s="38">
+      <c r="AS2" s="40">
         <v>46213</v>
       </c>
-      <c r="AT2" s="38">
+      <c r="AT2" s="40">
         <v>46213</v>
       </c>
-      <c r="AU2" s="38">
+      <c r="AU2" s="40">
         <v>46213</v>
       </c>
-      <c r="AV2" s="38">
+      <c r="AV2" s="40">
         <v>46213</v>
       </c>
-      <c r="AW2" s="38">
+      <c r="AW2" s="40">
         <v>46213</v>
       </c>
-      <c r="AX2" s="38">
+      <c r="AX2" s="40">
         <v>46218</v>
       </c>
-      <c r="AY2" s="38">
+      <c r="AY2" s="40">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="38">
+      <c r="AZ2" s="40">
         <v>46219</v>
       </c>
-      <c r="BA2" s="38">
+      <c r="BA2" s="40">
         <v>46219</v>
       </c>
-      <c r="BB2" s="38">
+      <c r="BB2" s="40">
         <v>46219</v>
       </c>
-      <c r="BC2" s="38">
+      <c r="BC2" s="40">
         <v>46219</v>
       </c>
-      <c r="BD2" s="38">
+      <c r="BD2" s="40">
         <v>46220</v>
       </c>
-      <c r="BE2" s="38">
+      <c r="BE2" s="40">
         <v>46220</v>
       </c>
-      <c r="BF2" s="38">
+      <c r="BF2" s="40">
         <v>46220</v>
       </c>
-      <c r="BG2" s="38">
+      <c r="BG2" s="40">
         <v>46225</v>
       </c>
-      <c r="BH2" s="38">
+      <c r="BH2" s="40">
         <v>46226</v>
       </c>
-      <c r="BI2" s="38">
+      <c r="BI2" s="40">
         <v>46226</v>
       </c>
-      <c r="BJ2" s="38">
+      <c r="BJ2" s="40">
         <v>46226</v>
       </c>
-      <c r="BK2" s="38">
+      <c r="BK2" s="40">
         <v>46226</v>
       </c>
-      <c r="BL2" s="38">
+      <c r="BL2" s="40">
         <v>46226</v>
       </c>
-      <c r="BM2" s="38">
+      <c r="BM2" s="40">
         <v>46227</v>
       </c>
-      <c r="BN2" s="38">
+      <c r="BN2" s="40">
         <v>46227</v>
       </c>
-      <c r="BO2" s="38">
+      <c r="BO2" s="40">
         <v>46227</v>
       </c>
-      <c r="BP2" s="38">
+      <c r="BP2" s="40">
         <v>46232</v>
       </c>
-      <c r="BQ2" s="38">
+      <c r="BQ2" s="40">
         <v>46233</v>
       </c>
-      <c r="BR2" s="38">
+      <c r="BR2" s="40">
         <v>46233</v>
       </c>
-      <c r="BS2" s="38">
+      <c r="BS2" s="40">
         <v>46233</v>
       </c>
-      <c r="BT2" s="38">
+      <c r="BT2" s="40">
         <v>46233</v>
       </c>
-      <c r="BU2" s="38">
+      <c r="BU2" s="40">
         <v>46233</v>
       </c>
-      <c r="BV2" s="38">
+      <c r="BV2" s="40">
         <v>46234</v>
       </c>
-      <c r="BW2" s="38">
+      <c r="BW2" s="40">
         <v>46234</v>
       </c>
-      <c r="BX2" s="68">
+      <c r="BX2" s="48">
         <v>46234</v>
       </c>
-      <c r="BY2" s="38"/>
-      <c r="BZ2" s="38"/>
-      <c r="CA2" s="38"/>
-      <c r="CB2" s="38"/>
-      <c r="CC2" s="38"/>
-      <c r="CD2" s="38"/>
-      <c r="CE2" s="38"/>
-      <c r="CF2" s="38"/>
-      <c r="CG2" s="38"/>
-      <c r="CH2" s="38"/>
-      <c r="CI2" s="38"/>
-      <c r="CJ2" s="38"/>
-      <c r="CK2" s="38"/>
-      <c r="CL2" s="38"/>
-      <c r="CM2" s="38"/>
-      <c r="CN2" s="38"/>
-      <c r="CO2" s="38"/>
-      <c r="CP2" s="38"/>
-      <c r="CQ2" s="38"/>
-      <c r="CR2" s="38"/>
-      <c r="CS2" s="38"/>
-      <c r="CT2" s="38"/>
-      <c r="CU2" s="38"/>
-      <c r="CV2" s="38"/>
-      <c r="CW2" s="38"/>
-      <c r="CX2" s="38"/>
-      <c r="CY2" s="38"/>
-      <c r="CZ2" s="38"/>
-      <c r="DA2" s="38"/>
-      <c r="DB2" s="38"/>
-      <c r="DC2" s="38"/>
-      <c r="DD2" s="38"/>
-      <c r="DE2" s="38"/>
-      <c r="DF2" s="38"/>
-      <c r="DG2" s="38"/>
-      <c r="DH2" s="38"/>
-      <c r="DI2" s="38"/>
-      <c r="DJ2" s="38"/>
-      <c r="DK2" s="38"/>
-      <c r="DL2" s="38"/>
-      <c r="DM2" s="38"/>
-      <c r="DN2" s="38"/>
-      <c r="DO2" s="38"/>
-      <c r="DP2" s="38"/>
-      <c r="DQ2" s="38"/>
-      <c r="DR2" s="38"/>
-      <c r="DS2" s="38"/>
-      <c r="DT2" s="38"/>
-      <c r="DU2" s="38"/>
-      <c r="DV2" s="38"/>
-      <c r="DW2" s="38"/>
-      <c r="DX2" s="38"/>
-      <c r="DY2" s="38"/>
-      <c r="DZ2" s="38"/>
-      <c r="EA2" s="38"/>
-      <c r="EB2" s="38"/>
-      <c r="EC2" s="38"/>
-      <c r="ED2" s="38"/>
-      <c r="EE2" s="38"/>
-      <c r="EF2" s="38"/>
-      <c r="EG2" s="38"/>
-      <c r="EH2" s="38"/>
-      <c r="EI2" s="38"/>
-      <c r="EJ2" s="38"/>
-      <c r="EK2" s="38"/>
-      <c r="EL2" s="38"/>
-      <c r="EM2" s="38"/>
-      <c r="EN2" s="38"/>
-      <c r="EO2" s="38"/>
+      <c r="BY2" s="40"/>
+      <c r="BZ2" s="40"/>
+      <c r="CA2" s="40"/>
+      <c r="CB2" s="40"/>
+      <c r="CC2" s="40"/>
+      <c r="CD2" s="40"/>
+      <c r="CE2" s="40"/>
+      <c r="CF2" s="40"/>
+      <c r="CG2" s="40"/>
+      <c r="CH2" s="40"/>
+      <c r="CI2" s="40"/>
+      <c r="CJ2" s="40"/>
+      <c r="CK2" s="40"/>
+      <c r="CL2" s="40"/>
+      <c r="CM2" s="40"/>
+      <c r="CN2" s="40"/>
+      <c r="CO2" s="40"/>
+      <c r="CP2" s="40"/>
+      <c r="CQ2" s="40"/>
+      <c r="CR2" s="40"/>
+      <c r="CS2" s="40"/>
+      <c r="CT2" s="40"/>
+      <c r="CU2" s="40"/>
+      <c r="CV2" s="40"/>
+      <c r="CW2" s="40"/>
+      <c r="CX2" s="40"/>
+      <c r="CY2" s="40"/>
+      <c r="CZ2" s="40"/>
+      <c r="DA2" s="40"/>
+      <c r="DB2" s="40"/>
+      <c r="DC2" s="40"/>
+      <c r="DD2" s="40"/>
+      <c r="DE2" s="40"/>
+      <c r="DF2" s="40"/>
+      <c r="DG2" s="40"/>
+      <c r="DH2" s="40"/>
+      <c r="DI2" s="40"/>
+      <c r="DJ2" s="40"/>
+      <c r="DK2" s="40"/>
+      <c r="DL2" s="40"/>
+      <c r="DM2" s="40"/>
+      <c r="DN2" s="40"/>
+      <c r="DO2" s="40"/>
+      <c r="DP2" s="40"/>
+      <c r="DQ2" s="40"/>
+      <c r="DR2" s="40"/>
+      <c r="DS2" s="40"/>
+      <c r="DT2" s="40"/>
+      <c r="DU2" s="40"/>
+      <c r="DV2" s="40"/>
+      <c r="DW2" s="40"/>
+      <c r="DX2" s="40"/>
+      <c r="DY2" s="40"/>
+      <c r="DZ2" s="40"/>
+      <c r="EA2" s="40"/>
+      <c r="EB2" s="40"/>
+      <c r="EC2" s="40"/>
+      <c r="ED2" s="40"/>
+      <c r="EE2" s="40"/>
+      <c r="EF2" s="40"/>
+      <c r="EG2" s="40"/>
+      <c r="EH2" s="40"/>
+      <c r="EI2" s="40"/>
+      <c r="EJ2" s="40"/>
+      <c r="EK2" s="40"/>
+      <c r="EL2" s="40"/>
+      <c r="EM2" s="40"/>
+      <c r="EN2" s="40"/>
+      <c r="EO2" s="40"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
-      <c r="AE3" s="38"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="38"/>
-      <c r="AK3" s="38"/>
-      <c r="AL3" s="38"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="38"/>
-      <c r="AO3" s="38"/>
-      <c r="AP3" s="38"/>
-      <c r="AQ3" s="38"/>
-      <c r="AR3" s="38"/>
-      <c r="AS3" s="38"/>
-      <c r="AT3" s="38"/>
-      <c r="AU3" s="38"/>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="38"/>
-      <c r="AX3" s="38"/>
-      <c r="AY3" s="38"/>
-      <c r="AZ3" s="38"/>
-      <c r="BA3" s="38"/>
-      <c r="BB3" s="38"/>
-      <c r="BC3" s="38"/>
-      <c r="BD3" s="38"/>
-      <c r="BE3" s="38"/>
-      <c r="BF3" s="38"/>
-      <c r="BG3" s="38"/>
-      <c r="BH3" s="38"/>
-      <c r="BI3" s="38"/>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="38"/>
-      <c r="BL3" s="38"/>
-      <c r="BM3" s="38"/>
-      <c r="BN3" s="38"/>
-      <c r="BO3" s="38"/>
-      <c r="BP3" s="38"/>
-      <c r="BQ3" s="38"/>
-      <c r="BR3" s="38"/>
-      <c r="BS3" s="38"/>
-      <c r="BT3" s="38"/>
-      <c r="BU3" s="38"/>
-      <c r="BV3" s="38"/>
-      <c r="BW3" s="38"/>
-      <c r="BX3" s="68"/>
-      <c r="BY3" s="38"/>
-      <c r="BZ3" s="38"/>
-      <c r="CA3" s="38"/>
-      <c r="CB3" s="38"/>
-      <c r="CC3" s="38"/>
-      <c r="CD3" s="38"/>
-      <c r="CE3" s="38"/>
-      <c r="CF3" s="38"/>
-      <c r="CG3" s="38"/>
-      <c r="CH3" s="38"/>
-      <c r="CI3" s="38"/>
-      <c r="CJ3" s="38"/>
-      <c r="CK3" s="38"/>
-      <c r="CL3" s="38"/>
-      <c r="CM3" s="38"/>
-      <c r="CN3" s="38"/>
-      <c r="CO3" s="38"/>
-      <c r="CP3" s="38"/>
-      <c r="CQ3" s="38"/>
-      <c r="CR3" s="38"/>
-      <c r="CS3" s="38"/>
-      <c r="CT3" s="38"/>
-      <c r="CU3" s="38"/>
-      <c r="CV3" s="38"/>
-      <c r="CW3" s="38"/>
-      <c r="CX3" s="38"/>
-      <c r="CY3" s="38"/>
-      <c r="CZ3" s="38"/>
-      <c r="DA3" s="38"/>
-      <c r="DB3" s="38"/>
-      <c r="DC3" s="38"/>
-      <c r="DD3" s="38"/>
-      <c r="DE3" s="38"/>
-      <c r="DF3" s="38"/>
-      <c r="DG3" s="38"/>
-      <c r="DH3" s="38"/>
-      <c r="DI3" s="38"/>
-      <c r="DJ3" s="38"/>
-      <c r="DK3" s="38"/>
-      <c r="DL3" s="38"/>
-      <c r="DM3" s="38"/>
-      <c r="DN3" s="38"/>
-      <c r="DO3" s="38"/>
-      <c r="DP3" s="38"/>
-      <c r="DQ3" s="38"/>
-      <c r="DR3" s="38"/>
-      <c r="DS3" s="38"/>
-      <c r="DT3" s="38"/>
-      <c r="DU3" s="38"/>
-      <c r="DV3" s="38"/>
-      <c r="DW3" s="38"/>
-      <c r="DX3" s="38"/>
-      <c r="DY3" s="38"/>
-      <c r="DZ3" s="38"/>
-      <c r="EA3" s="38"/>
-      <c r="EB3" s="38"/>
-      <c r="EC3" s="38"/>
-      <c r="ED3" s="38"/>
-      <c r="EE3" s="38"/>
-      <c r="EF3" s="38"/>
-      <c r="EG3" s="38"/>
-      <c r="EH3" s="38"/>
-      <c r="EI3" s="38"/>
-      <c r="EJ3" s="38"/>
-      <c r="EK3" s="38"/>
-      <c r="EL3" s="38"/>
-      <c r="EM3" s="38"/>
-      <c r="EN3" s="38"/>
-      <c r="EO3" s="38"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="50"/>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40"/>
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="40"/>
+      <c r="AP3" s="40"/>
+      <c r="AQ3" s="40"/>
+      <c r="AR3" s="40"/>
+      <c r="AS3" s="40"/>
+      <c r="AT3" s="40"/>
+      <c r="AU3" s="40"/>
+      <c r="AV3" s="40"/>
+      <c r="AW3" s="40"/>
+      <c r="AX3" s="40"/>
+      <c r="AY3" s="40"/>
+      <c r="AZ3" s="40"/>
+      <c r="BA3" s="40"/>
+      <c r="BB3" s="40"/>
+      <c r="BC3" s="40"/>
+      <c r="BD3" s="40"/>
+      <c r="BE3" s="40"/>
+      <c r="BF3" s="40"/>
+      <c r="BG3" s="40"/>
+      <c r="BH3" s="40"/>
+      <c r="BI3" s="40"/>
+      <c r="BJ3" s="40"/>
+      <c r="BK3" s="40"/>
+      <c r="BL3" s="40"/>
+      <c r="BM3" s="40"/>
+      <c r="BN3" s="40"/>
+      <c r="BO3" s="40"/>
+      <c r="BP3" s="40"/>
+      <c r="BQ3" s="40"/>
+      <c r="BR3" s="40"/>
+      <c r="BS3" s="40"/>
+      <c r="BT3" s="40"/>
+      <c r="BU3" s="40"/>
+      <c r="BV3" s="40"/>
+      <c r="BW3" s="40"/>
+      <c r="BX3" s="48"/>
+      <c r="BY3" s="40"/>
+      <c r="BZ3" s="40"/>
+      <c r="CA3" s="40"/>
+      <c r="CB3" s="40"/>
+      <c r="CC3" s="40"/>
+      <c r="CD3" s="40"/>
+      <c r="CE3" s="40"/>
+      <c r="CF3" s="40"/>
+      <c r="CG3" s="40"/>
+      <c r="CH3" s="40"/>
+      <c r="CI3" s="40"/>
+      <c r="CJ3" s="40"/>
+      <c r="CK3" s="40"/>
+      <c r="CL3" s="40"/>
+      <c r="CM3" s="40"/>
+      <c r="CN3" s="40"/>
+      <c r="CO3" s="40"/>
+      <c r="CP3" s="40"/>
+      <c r="CQ3" s="40"/>
+      <c r="CR3" s="40"/>
+      <c r="CS3" s="40"/>
+      <c r="CT3" s="40"/>
+      <c r="CU3" s="40"/>
+      <c r="CV3" s="40"/>
+      <c r="CW3" s="40"/>
+      <c r="CX3" s="40"/>
+      <c r="CY3" s="40"/>
+      <c r="CZ3" s="40"/>
+      <c r="DA3" s="40"/>
+      <c r="DB3" s="40"/>
+      <c r="DC3" s="40"/>
+      <c r="DD3" s="40"/>
+      <c r="DE3" s="40"/>
+      <c r="DF3" s="40"/>
+      <c r="DG3" s="40"/>
+      <c r="DH3" s="40"/>
+      <c r="DI3" s="40"/>
+      <c r="DJ3" s="40"/>
+      <c r="DK3" s="40"/>
+      <c r="DL3" s="40"/>
+      <c r="DM3" s="40"/>
+      <c r="DN3" s="40"/>
+      <c r="DO3" s="40"/>
+      <c r="DP3" s="40"/>
+      <c r="DQ3" s="40"/>
+      <c r="DR3" s="40"/>
+      <c r="DS3" s="40"/>
+      <c r="DT3" s="40"/>
+      <c r="DU3" s="40"/>
+      <c r="DV3" s="40"/>
+      <c r="DW3" s="40"/>
+      <c r="DX3" s="40"/>
+      <c r="DY3" s="40"/>
+      <c r="DZ3" s="40"/>
+      <c r="EA3" s="40"/>
+      <c r="EB3" s="40"/>
+      <c r="EC3" s="40"/>
+      <c r="ED3" s="40"/>
+      <c r="EE3" s="40"/>
+      <c r="EF3" s="40"/>
+      <c r="EG3" s="40"/>
+      <c r="EH3" s="40"/>
+      <c r="EI3" s="40"/>
+      <c r="EJ3" s="40"/>
+      <c r="EK3" s="40"/>
+      <c r="EL3" s="40"/>
+      <c r="EM3" s="40"/>
+      <c r="EN3" s="40"/>
+      <c r="EO3" s="40"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
-      <c r="BJ4" s="38"/>
-      <c r="BK4" s="38"/>
-      <c r="BL4" s="38"/>
-      <c r="BM4" s="38"/>
-      <c r="BN4" s="38"/>
-      <c r="BO4" s="38"/>
-      <c r="BP4" s="38"/>
-      <c r="BQ4" s="38"/>
-      <c r="BR4" s="38"/>
-      <c r="BS4" s="38"/>
-      <c r="BT4" s="38"/>
-      <c r="BU4" s="38"/>
-      <c r="BV4" s="38"/>
-      <c r="BW4" s="38"/>
-      <c r="BX4" s="68"/>
-      <c r="BY4" s="38"/>
-      <c r="BZ4" s="38"/>
-      <c r="CA4" s="38"/>
-      <c r="CB4" s="38"/>
-      <c r="CC4" s="38"/>
-      <c r="CD4" s="38"/>
-      <c r="CE4" s="38"/>
-      <c r="CF4" s="38"/>
-      <c r="CG4" s="38"/>
-      <c r="CH4" s="38"/>
-      <c r="CI4" s="38"/>
-      <c r="CJ4" s="38"/>
-      <c r="CK4" s="38"/>
-      <c r="CL4" s="38"/>
-      <c r="CM4" s="38"/>
-      <c r="CN4" s="38"/>
-      <c r="CO4" s="38"/>
-      <c r="CP4" s="38"/>
-      <c r="CQ4" s="38"/>
-      <c r="CR4" s="38"/>
-      <c r="CS4" s="38"/>
-      <c r="CT4" s="38"/>
-      <c r="CU4" s="38"/>
-      <c r="CV4" s="38"/>
-      <c r="CW4" s="38"/>
-      <c r="CX4" s="38"/>
-      <c r="CY4" s="38"/>
-      <c r="CZ4" s="38"/>
-      <c r="DA4" s="38"/>
-      <c r="DB4" s="38"/>
-      <c r="DC4" s="38"/>
-      <c r="DD4" s="38"/>
-      <c r="DE4" s="38"/>
-      <c r="DF4" s="38"/>
-      <c r="DG4" s="38"/>
-      <c r="DH4" s="38"/>
-      <c r="DI4" s="38"/>
-      <c r="DJ4" s="38"/>
-      <c r="DK4" s="38"/>
-      <c r="DL4" s="38"/>
-      <c r="DM4" s="38"/>
-      <c r="DN4" s="38"/>
-      <c r="DO4" s="38"/>
-      <c r="DP4" s="38"/>
-      <c r="DQ4" s="38"/>
-      <c r="DR4" s="38"/>
-      <c r="DS4" s="38"/>
-      <c r="DT4" s="38"/>
-      <c r="DU4" s="38"/>
-      <c r="DV4" s="38"/>
-      <c r="DW4" s="38"/>
-      <c r="DX4" s="38"/>
-      <c r="DY4" s="38"/>
-      <c r="DZ4" s="38"/>
-      <c r="EA4" s="38"/>
-      <c r="EB4" s="38"/>
-      <c r="EC4" s="38"/>
-      <c r="ED4" s="38"/>
-      <c r="EE4" s="38"/>
-      <c r="EF4" s="38"/>
-      <c r="EG4" s="38"/>
-      <c r="EH4" s="38"/>
-      <c r="EI4" s="38"/>
-      <c r="EJ4" s="38"/>
-      <c r="EK4" s="38"/>
-      <c r="EL4" s="38"/>
-      <c r="EM4" s="38"/>
-      <c r="EN4" s="38"/>
-      <c r="EO4" s="38"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="40"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="40"/>
+      <c r="AQ4" s="40"/>
+      <c r="AR4" s="40"/>
+      <c r="AS4" s="40"/>
+      <c r="AT4" s="40"/>
+      <c r="AU4" s="40"/>
+      <c r="AV4" s="40"/>
+      <c r="AW4" s="40"/>
+      <c r="AX4" s="40"/>
+      <c r="AY4" s="40"/>
+      <c r="AZ4" s="40"/>
+      <c r="BA4" s="40"/>
+      <c r="BB4" s="40"/>
+      <c r="BC4" s="40"/>
+      <c r="BD4" s="40"/>
+      <c r="BE4" s="40"/>
+      <c r="BF4" s="40"/>
+      <c r="BG4" s="40"/>
+      <c r="BH4" s="40"/>
+      <c r="BI4" s="40"/>
+      <c r="BJ4" s="40"/>
+      <c r="BK4" s="40"/>
+      <c r="BL4" s="40"/>
+      <c r="BM4" s="40"/>
+      <c r="BN4" s="40"/>
+      <c r="BO4" s="40"/>
+      <c r="BP4" s="40"/>
+      <c r="BQ4" s="40"/>
+      <c r="BR4" s="40"/>
+      <c r="BS4" s="40"/>
+      <c r="BT4" s="40"/>
+      <c r="BU4" s="40"/>
+      <c r="BV4" s="40"/>
+      <c r="BW4" s="40"/>
+      <c r="BX4" s="48"/>
+      <c r="BY4" s="40"/>
+      <c r="BZ4" s="40"/>
+      <c r="CA4" s="40"/>
+      <c r="CB4" s="40"/>
+      <c r="CC4" s="40"/>
+      <c r="CD4" s="40"/>
+      <c r="CE4" s="40"/>
+      <c r="CF4" s="40"/>
+      <c r="CG4" s="40"/>
+      <c r="CH4" s="40"/>
+      <c r="CI4" s="40"/>
+      <c r="CJ4" s="40"/>
+      <c r="CK4" s="40"/>
+      <c r="CL4" s="40"/>
+      <c r="CM4" s="40"/>
+      <c r="CN4" s="40"/>
+      <c r="CO4" s="40"/>
+      <c r="CP4" s="40"/>
+      <c r="CQ4" s="40"/>
+      <c r="CR4" s="40"/>
+      <c r="CS4" s="40"/>
+      <c r="CT4" s="40"/>
+      <c r="CU4" s="40"/>
+      <c r="CV4" s="40"/>
+      <c r="CW4" s="40"/>
+      <c r="CX4" s="40"/>
+      <c r="CY4" s="40"/>
+      <c r="CZ4" s="40"/>
+      <c r="DA4" s="40"/>
+      <c r="DB4" s="40"/>
+      <c r="DC4" s="40"/>
+      <c r="DD4" s="40"/>
+      <c r="DE4" s="40"/>
+      <c r="DF4" s="40"/>
+      <c r="DG4" s="40"/>
+      <c r="DH4" s="40"/>
+      <c r="DI4" s="40"/>
+      <c r="DJ4" s="40"/>
+      <c r="DK4" s="40"/>
+      <c r="DL4" s="40"/>
+      <c r="DM4" s="40"/>
+      <c r="DN4" s="40"/>
+      <c r="DO4" s="40"/>
+      <c r="DP4" s="40"/>
+      <c r="DQ4" s="40"/>
+      <c r="DR4" s="40"/>
+      <c r="DS4" s="40"/>
+      <c r="DT4" s="40"/>
+      <c r="DU4" s="40"/>
+      <c r="DV4" s="40"/>
+      <c r="DW4" s="40"/>
+      <c r="DX4" s="40"/>
+      <c r="DY4" s="40"/>
+      <c r="DZ4" s="40"/>
+      <c r="EA4" s="40"/>
+      <c r="EB4" s="40"/>
+      <c r="EC4" s="40"/>
+      <c r="ED4" s="40"/>
+      <c r="EE4" s="40"/>
+      <c r="EF4" s="40"/>
+      <c r="EG4" s="40"/>
+      <c r="EH4" s="40"/>
+      <c r="EI4" s="40"/>
+      <c r="EJ4" s="40"/>
+      <c r="EK4" s="40"/>
+      <c r="EL4" s="40"/>
+      <c r="EM4" s="40"/>
+      <c r="EN4" s="40"/>
+      <c r="EO4" s="40"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45">
         <v>110</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
-      <c r="BJ5" s="38"/>
-      <c r="BK5" s="38"/>
-      <c r="BL5" s="38"/>
-      <c r="BM5" s="38"/>
-      <c r="BN5" s="38"/>
-      <c r="BO5" s="38"/>
-      <c r="BP5" s="38"/>
-      <c r="BQ5" s="38"/>
-      <c r="BR5" s="38"/>
-      <c r="BS5" s="38"/>
-      <c r="BT5" s="38"/>
-      <c r="BU5" s="38"/>
-      <c r="BV5" s="38"/>
-      <c r="BW5" s="38"/>
-      <c r="BX5" s="68"/>
-      <c r="BY5" s="38"/>
-      <c r="BZ5" s="38"/>
-      <c r="CA5" s="38"/>
-      <c r="CB5" s="38"/>
-      <c r="CC5" s="38"/>
-      <c r="CD5" s="38"/>
-      <c r="CE5" s="38"/>
-      <c r="CF5" s="38"/>
-      <c r="CG5" s="38"/>
-      <c r="CH5" s="38"/>
-      <c r="CI5" s="38"/>
-      <c r="CJ5" s="38"/>
-      <c r="CK5" s="38"/>
-      <c r="CL5" s="38"/>
-      <c r="CM5" s="38"/>
-      <c r="CN5" s="38"/>
-      <c r="CO5" s="38"/>
-      <c r="CP5" s="38"/>
-      <c r="CQ5" s="38"/>
-      <c r="CR5" s="38"/>
-      <c r="CS5" s="38"/>
-      <c r="CT5" s="38"/>
-      <c r="CU5" s="38"/>
-      <c r="CV5" s="38"/>
-      <c r="CW5" s="38"/>
-      <c r="CX5" s="38"/>
-      <c r="CY5" s="38"/>
-      <c r="CZ5" s="38"/>
-      <c r="DA5" s="38"/>
-      <c r="DB5" s="38"/>
-      <c r="DC5" s="38"/>
-      <c r="DD5" s="38"/>
-      <c r="DE5" s="38"/>
-      <c r="DF5" s="38"/>
-      <c r="DG5" s="38"/>
-      <c r="DH5" s="38"/>
-      <c r="DI5" s="38"/>
-      <c r="DJ5" s="38"/>
-      <c r="DK5" s="38"/>
-      <c r="DL5" s="38"/>
-      <c r="DM5" s="38"/>
-      <c r="DN5" s="38"/>
-      <c r="DO5" s="38"/>
-      <c r="DP5" s="38"/>
-      <c r="DQ5" s="38"/>
-      <c r="DR5" s="38"/>
-      <c r="DS5" s="38"/>
-      <c r="DT5" s="38"/>
-      <c r="DU5" s="38"/>
-      <c r="DV5" s="38"/>
-      <c r="DW5" s="38"/>
-      <c r="DX5" s="38"/>
-      <c r="DY5" s="38"/>
-      <c r="DZ5" s="38"/>
-      <c r="EA5" s="38"/>
-      <c r="EB5" s="38"/>
-      <c r="EC5" s="38"/>
-      <c r="ED5" s="38"/>
-      <c r="EE5" s="38"/>
-      <c r="EF5" s="38"/>
-      <c r="EG5" s="38"/>
-      <c r="EH5" s="38"/>
-      <c r="EI5" s="38"/>
-      <c r="EJ5" s="38"/>
-      <c r="EK5" s="38"/>
-      <c r="EL5" s="38"/>
-      <c r="EM5" s="38"/>
-      <c r="EN5" s="38"/>
-      <c r="EO5" s="38"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="52"/>
+      <c r="AA5" s="50"/>
+      <c r="AB5" s="50"/>
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="40"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="40"/>
+      <c r="AK5" s="40"/>
+      <c r="AL5" s="40"/>
+      <c r="AM5" s="40"/>
+      <c r="AN5" s="40"/>
+      <c r="AO5" s="40"/>
+      <c r="AP5" s="40"/>
+      <c r="AQ5" s="40"/>
+      <c r="AR5" s="40"/>
+      <c r="AS5" s="40"/>
+      <c r="AT5" s="40"/>
+      <c r="AU5" s="40"/>
+      <c r="AV5" s="40"/>
+      <c r="AW5" s="40"/>
+      <c r="AX5" s="40"/>
+      <c r="AY5" s="40"/>
+      <c r="AZ5" s="40"/>
+      <c r="BA5" s="40"/>
+      <c r="BB5" s="40"/>
+      <c r="BC5" s="40"/>
+      <c r="BD5" s="40"/>
+      <c r="BE5" s="40"/>
+      <c r="BF5" s="40"/>
+      <c r="BG5" s="40"/>
+      <c r="BH5" s="40"/>
+      <c r="BI5" s="40"/>
+      <c r="BJ5" s="40"/>
+      <c r="BK5" s="40"/>
+      <c r="BL5" s="40"/>
+      <c r="BM5" s="40"/>
+      <c r="BN5" s="40"/>
+      <c r="BO5" s="40"/>
+      <c r="BP5" s="40"/>
+      <c r="BQ5" s="40"/>
+      <c r="BR5" s="40"/>
+      <c r="BS5" s="40"/>
+      <c r="BT5" s="40"/>
+      <c r="BU5" s="40"/>
+      <c r="BV5" s="40"/>
+      <c r="BW5" s="40"/>
+      <c r="BX5" s="48"/>
+      <c r="BY5" s="40"/>
+      <c r="BZ5" s="40"/>
+      <c r="CA5" s="40"/>
+      <c r="CB5" s="40"/>
+      <c r="CC5" s="40"/>
+      <c r="CD5" s="40"/>
+      <c r="CE5" s="40"/>
+      <c r="CF5" s="40"/>
+      <c r="CG5" s="40"/>
+      <c r="CH5" s="40"/>
+      <c r="CI5" s="40"/>
+      <c r="CJ5" s="40"/>
+      <c r="CK5" s="40"/>
+      <c r="CL5" s="40"/>
+      <c r="CM5" s="40"/>
+      <c r="CN5" s="40"/>
+      <c r="CO5" s="40"/>
+      <c r="CP5" s="40"/>
+      <c r="CQ5" s="40"/>
+      <c r="CR5" s="40"/>
+      <c r="CS5" s="40"/>
+      <c r="CT5" s="40"/>
+      <c r="CU5" s="40"/>
+      <c r="CV5" s="40"/>
+      <c r="CW5" s="40"/>
+      <c r="CX5" s="40"/>
+      <c r="CY5" s="40"/>
+      <c r="CZ5" s="40"/>
+      <c r="DA5" s="40"/>
+      <c r="DB5" s="40"/>
+      <c r="DC5" s="40"/>
+      <c r="DD5" s="40"/>
+      <c r="DE5" s="40"/>
+      <c r="DF5" s="40"/>
+      <c r="DG5" s="40"/>
+      <c r="DH5" s="40"/>
+      <c r="DI5" s="40"/>
+      <c r="DJ5" s="40"/>
+      <c r="DK5" s="40"/>
+      <c r="DL5" s="40"/>
+      <c r="DM5" s="40"/>
+      <c r="DN5" s="40"/>
+      <c r="DO5" s="40"/>
+      <c r="DP5" s="40"/>
+      <c r="DQ5" s="40"/>
+      <c r="DR5" s="40"/>
+      <c r="DS5" s="40"/>
+      <c r="DT5" s="40"/>
+      <c r="DU5" s="40"/>
+      <c r="DV5" s="40"/>
+      <c r="DW5" s="40"/>
+      <c r="DX5" s="40"/>
+      <c r="DY5" s="40"/>
+      <c r="DZ5" s="40"/>
+      <c r="EA5" s="40"/>
+      <c r="EB5" s="40"/>
+      <c r="EC5" s="40"/>
+      <c r="ED5" s="40"/>
+      <c r="EE5" s="40"/>
+      <c r="EF5" s="40"/>
+      <c r="EG5" s="40"/>
+      <c r="EH5" s="40"/>
+      <c r="EI5" s="40"/>
+      <c r="EJ5" s="40"/>
+      <c r="EK5" s="40"/>
+      <c r="EL5" s="40"/>
+      <c r="EM5" s="40"/>
+      <c r="EN5" s="40"/>
+      <c r="EO5" s="40"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="51">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45">
         <v>10</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="45"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="38"/>
-      <c r="AE6" s="38"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="38"/>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="38"/>
-      <c r="AN6" s="38"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="38"/>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="38"/>
-      <c r="AY6" s="38"/>
-      <c r="AZ6" s="38"/>
-      <c r="BA6" s="38"/>
-      <c r="BB6" s="38"/>
-      <c r="BC6" s="38"/>
-      <c r="BD6" s="38"/>
-      <c r="BE6" s="38"/>
-      <c r="BF6" s="38"/>
-      <c r="BG6" s="38"/>
-      <c r="BH6" s="38"/>
-      <c r="BI6" s="38"/>
-      <c r="BJ6" s="38"/>
-      <c r="BK6" s="38"/>
-      <c r="BL6" s="38"/>
-      <c r="BM6" s="38"/>
-      <c r="BN6" s="38"/>
-      <c r="BO6" s="38"/>
-      <c r="BP6" s="38"/>
-      <c r="BQ6" s="38"/>
-      <c r="BR6" s="38"/>
-      <c r="BS6" s="38"/>
-      <c r="BT6" s="38"/>
-      <c r="BU6" s="38"/>
-      <c r="BV6" s="38"/>
-      <c r="BW6" s="38"/>
-      <c r="BX6" s="68"/>
-      <c r="BY6" s="38"/>
-      <c r="BZ6" s="38"/>
-      <c r="CA6" s="38"/>
-      <c r="CB6" s="38"/>
-      <c r="CC6" s="38"/>
-      <c r="CD6" s="38"/>
-      <c r="CE6" s="38"/>
-      <c r="CF6" s="38"/>
-      <c r="CG6" s="38"/>
-      <c r="CH6" s="38"/>
-      <c r="CI6" s="38"/>
-      <c r="CJ6" s="38"/>
-      <c r="CK6" s="38"/>
-      <c r="CL6" s="38"/>
-      <c r="CM6" s="38"/>
-      <c r="CN6" s="38"/>
-      <c r="CO6" s="38"/>
-      <c r="CP6" s="38"/>
-      <c r="CQ6" s="38"/>
-      <c r="CR6" s="38"/>
-      <c r="CS6" s="38"/>
-      <c r="CT6" s="38"/>
-      <c r="CU6" s="38"/>
-      <c r="CV6" s="38"/>
-      <c r="CW6" s="38"/>
-      <c r="CX6" s="38"/>
-      <c r="CY6" s="38"/>
-      <c r="CZ6" s="38"/>
-      <c r="DA6" s="38"/>
-      <c r="DB6" s="38"/>
-      <c r="DC6" s="38"/>
-      <c r="DD6" s="38"/>
-      <c r="DE6" s="38"/>
-      <c r="DF6" s="38"/>
-      <c r="DG6" s="38"/>
-      <c r="DH6" s="38"/>
-      <c r="DI6" s="38"/>
-      <c r="DJ6" s="38"/>
-      <c r="DK6" s="38"/>
-      <c r="DL6" s="38"/>
-      <c r="DM6" s="38"/>
-      <c r="DN6" s="38"/>
-      <c r="DO6" s="38"/>
-      <c r="DP6" s="38"/>
-      <c r="DQ6" s="38"/>
-      <c r="DR6" s="38"/>
-      <c r="DS6" s="38"/>
-      <c r="DT6" s="38"/>
-      <c r="DU6" s="38"/>
-      <c r="DV6" s="38"/>
-      <c r="DW6" s="38"/>
-      <c r="DX6" s="38"/>
-      <c r="DY6" s="38"/>
-      <c r="DZ6" s="38"/>
-      <c r="EA6" s="38"/>
-      <c r="EB6" s="38"/>
-      <c r="EC6" s="38"/>
-      <c r="ED6" s="38"/>
-      <c r="EE6" s="38"/>
-      <c r="EF6" s="38"/>
-      <c r="EG6" s="38"/>
-      <c r="EH6" s="38"/>
-      <c r="EI6" s="38"/>
-      <c r="EJ6" s="38"/>
-      <c r="EK6" s="38"/>
-      <c r="EL6" s="38"/>
-      <c r="EM6" s="38"/>
-      <c r="EN6" s="38"/>
-      <c r="EO6" s="38"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="52"/>
+      <c r="W6" s="52"/>
+      <c r="X6" s="52"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="52"/>
+      <c r="AA6" s="50"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="40"/>
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="40"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="40"/>
+      <c r="AT6" s="40"/>
+      <c r="AU6" s="40"/>
+      <c r="AV6" s="40"/>
+      <c r="AW6" s="40"/>
+      <c r="AX6" s="40"/>
+      <c r="AY6" s="40"/>
+      <c r="AZ6" s="40"/>
+      <c r="BA6" s="40"/>
+      <c r="BB6" s="40"/>
+      <c r="BC6" s="40"/>
+      <c r="BD6" s="40"/>
+      <c r="BE6" s="40"/>
+      <c r="BF6" s="40"/>
+      <c r="BG6" s="40"/>
+      <c r="BH6" s="40"/>
+      <c r="BI6" s="40"/>
+      <c r="BJ6" s="40"/>
+      <c r="BK6" s="40"/>
+      <c r="BL6" s="40"/>
+      <c r="BM6" s="40"/>
+      <c r="BN6" s="40"/>
+      <c r="BO6" s="40"/>
+      <c r="BP6" s="40"/>
+      <c r="BQ6" s="40"/>
+      <c r="BR6" s="40"/>
+      <c r="BS6" s="40"/>
+      <c r="BT6" s="40"/>
+      <c r="BU6" s="40"/>
+      <c r="BV6" s="40"/>
+      <c r="BW6" s="40"/>
+      <c r="BX6" s="48"/>
+      <c r="BY6" s="40"/>
+      <c r="BZ6" s="40"/>
+      <c r="CA6" s="40"/>
+      <c r="CB6" s="40"/>
+      <c r="CC6" s="40"/>
+      <c r="CD6" s="40"/>
+      <c r="CE6" s="40"/>
+      <c r="CF6" s="40"/>
+      <c r="CG6" s="40"/>
+      <c r="CH6" s="40"/>
+      <c r="CI6" s="40"/>
+      <c r="CJ6" s="40"/>
+      <c r="CK6" s="40"/>
+      <c r="CL6" s="40"/>
+      <c r="CM6" s="40"/>
+      <c r="CN6" s="40"/>
+      <c r="CO6" s="40"/>
+      <c r="CP6" s="40"/>
+      <c r="CQ6" s="40"/>
+      <c r="CR6" s="40"/>
+      <c r="CS6" s="40"/>
+      <c r="CT6" s="40"/>
+      <c r="CU6" s="40"/>
+      <c r="CV6" s="40"/>
+      <c r="CW6" s="40"/>
+      <c r="CX6" s="40"/>
+      <c r="CY6" s="40"/>
+      <c r="CZ6" s="40"/>
+      <c r="DA6" s="40"/>
+      <c r="DB6" s="40"/>
+      <c r="DC6" s="40"/>
+      <c r="DD6" s="40"/>
+      <c r="DE6" s="40"/>
+      <c r="DF6" s="40"/>
+      <c r="DG6" s="40"/>
+      <c r="DH6" s="40"/>
+      <c r="DI6" s="40"/>
+      <c r="DJ6" s="40"/>
+      <c r="DK6" s="40"/>
+      <c r="DL6" s="40"/>
+      <c r="DM6" s="40"/>
+      <c r="DN6" s="40"/>
+      <c r="DO6" s="40"/>
+      <c r="DP6" s="40"/>
+      <c r="DQ6" s="40"/>
+      <c r="DR6" s="40"/>
+      <c r="DS6" s="40"/>
+      <c r="DT6" s="40"/>
+      <c r="DU6" s="40"/>
+      <c r="DV6" s="40"/>
+      <c r="DW6" s="40"/>
+      <c r="DX6" s="40"/>
+      <c r="DY6" s="40"/>
+      <c r="DZ6" s="40"/>
+      <c r="EA6" s="40"/>
+      <c r="EB6" s="40"/>
+      <c r="EC6" s="40"/>
+      <c r="ED6" s="40"/>
+      <c r="EE6" s="40"/>
+      <c r="EF6" s="40"/>
+      <c r="EG6" s="40"/>
+      <c r="EH6" s="40"/>
+      <c r="EI6" s="40"/>
+      <c r="EJ6" s="40"/>
+      <c r="EK6" s="40"/>
+      <c r="EL6" s="40"/>
+      <c r="EM6" s="40"/>
+      <c r="EN6" s="40"/>
+      <c r="EO6" s="40"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="51">
+      <c r="B7" s="47"/>
+      <c r="C7" s="45">
         <v>30</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="39"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="39"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="39"/>
-      <c r="AQ7" s="39"/>
-      <c r="AR7" s="39"/>
-      <c r="AS7" s="39"/>
-      <c r="AT7" s="39"/>
-      <c r="AU7" s="39"/>
-      <c r="AV7" s="39"/>
-      <c r="AW7" s="39"/>
-      <c r="AX7" s="39"/>
-      <c r="AY7" s="39"/>
-      <c r="AZ7" s="39"/>
-      <c r="BA7" s="39"/>
-      <c r="BB7" s="39"/>
-      <c r="BC7" s="39"/>
-      <c r="BD7" s="39"/>
-      <c r="BE7" s="39"/>
-      <c r="BF7" s="39"/>
-      <c r="BG7" s="39"/>
-      <c r="BH7" s="39"/>
-      <c r="BI7" s="39"/>
-      <c r="BJ7" s="39"/>
-      <c r="BK7" s="39"/>
-      <c r="BL7" s="39"/>
-      <c r="BM7" s="39"/>
-      <c r="BN7" s="39"/>
-      <c r="BO7" s="39"/>
-      <c r="BP7" s="39"/>
-      <c r="BQ7" s="39"/>
-      <c r="BR7" s="39"/>
-      <c r="BS7" s="39"/>
-      <c r="BT7" s="39"/>
-      <c r="BU7" s="39"/>
-      <c r="BV7" s="39"/>
-      <c r="BW7" s="39"/>
-      <c r="BX7" s="69"/>
-      <c r="BY7" s="39"/>
-      <c r="BZ7" s="39"/>
-      <c r="CA7" s="39"/>
-      <c r="CB7" s="39"/>
-      <c r="CC7" s="39"/>
-      <c r="CD7" s="39"/>
-      <c r="CE7" s="39"/>
-      <c r="CF7" s="39"/>
-      <c r="CG7" s="39"/>
-      <c r="CH7" s="39"/>
-      <c r="CI7" s="39"/>
-      <c r="CJ7" s="39"/>
-      <c r="CK7" s="39"/>
-      <c r="CL7" s="39"/>
-      <c r="CM7" s="39"/>
-      <c r="CN7" s="39"/>
-      <c r="CO7" s="39"/>
-      <c r="CP7" s="39"/>
-      <c r="CQ7" s="39"/>
-      <c r="CR7" s="39"/>
-      <c r="CS7" s="39"/>
-      <c r="CT7" s="39"/>
-      <c r="CU7" s="39"/>
-      <c r="CV7" s="39"/>
-      <c r="CW7" s="39"/>
-      <c r="CX7" s="39"/>
-      <c r="CY7" s="39"/>
-      <c r="CZ7" s="39"/>
-      <c r="DA7" s="39"/>
-      <c r="DB7" s="39"/>
-      <c r="DC7" s="39"/>
-      <c r="DD7" s="39"/>
-      <c r="DE7" s="39"/>
-      <c r="DF7" s="39"/>
-      <c r="DG7" s="39"/>
-      <c r="DH7" s="39"/>
-      <c r="DI7" s="39"/>
-      <c r="DJ7" s="39"/>
-      <c r="DK7" s="39"/>
-      <c r="DL7" s="39"/>
-      <c r="DM7" s="39"/>
-      <c r="DN7" s="39"/>
-      <c r="DO7" s="39"/>
-      <c r="DP7" s="39"/>
-      <c r="DQ7" s="39"/>
-      <c r="DR7" s="39"/>
-      <c r="DS7" s="39"/>
-      <c r="DT7" s="39"/>
-      <c r="DU7" s="39"/>
-      <c r="DV7" s="39"/>
-      <c r="DW7" s="39"/>
-      <c r="DX7" s="39"/>
-      <c r="DY7" s="39"/>
-      <c r="DZ7" s="39"/>
-      <c r="EA7" s="39"/>
-      <c r="EB7" s="39"/>
-      <c r="EC7" s="39"/>
-      <c r="ED7" s="39"/>
-      <c r="EE7" s="39"/>
-      <c r="EF7" s="39"/>
-      <c r="EG7" s="39"/>
-      <c r="EH7" s="39"/>
-      <c r="EI7" s="39"/>
-      <c r="EJ7" s="39"/>
-      <c r="EK7" s="39"/>
-      <c r="EL7" s="39"/>
-      <c r="EM7" s="39"/>
-      <c r="EN7" s="39"/>
-      <c r="EO7" s="39"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="53"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="53"/>
+      <c r="AA7" s="51"/>
+      <c r="AB7" s="51"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="41"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="41"/>
+      <c r="AJ7" s="41"/>
+      <c r="AK7" s="41"/>
+      <c r="AL7" s="41"/>
+      <c r="AM7" s="41"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="41"/>
+      <c r="AP7" s="41"/>
+      <c r="AQ7" s="41"/>
+      <c r="AR7" s="41"/>
+      <c r="AS7" s="41"/>
+      <c r="AT7" s="41"/>
+      <c r="AU7" s="41"/>
+      <c r="AV7" s="41"/>
+      <c r="AW7" s="41"/>
+      <c r="AX7" s="41"/>
+      <c r="AY7" s="41"/>
+      <c r="AZ7" s="41"/>
+      <c r="BA7" s="41"/>
+      <c r="BB7" s="41"/>
+      <c r="BC7" s="41"/>
+      <c r="BD7" s="41"/>
+      <c r="BE7" s="41"/>
+      <c r="BF7" s="41"/>
+      <c r="BG7" s="41"/>
+      <c r="BH7" s="41"/>
+      <c r="BI7" s="41"/>
+      <c r="BJ7" s="41"/>
+      <c r="BK7" s="41"/>
+      <c r="BL7" s="41"/>
+      <c r="BM7" s="41"/>
+      <c r="BN7" s="41"/>
+      <c r="BO7" s="41"/>
+      <c r="BP7" s="41"/>
+      <c r="BQ7" s="41"/>
+      <c r="BR7" s="41"/>
+      <c r="BS7" s="41"/>
+      <c r="BT7" s="41"/>
+      <c r="BU7" s="41"/>
+      <c r="BV7" s="41"/>
+      <c r="BW7" s="41"/>
+      <c r="BX7" s="49"/>
+      <c r="BY7" s="41"/>
+      <c r="BZ7" s="41"/>
+      <c r="CA7" s="41"/>
+      <c r="CB7" s="41"/>
+      <c r="CC7" s="41"/>
+      <c r="CD7" s="41"/>
+      <c r="CE7" s="41"/>
+      <c r="CF7" s="41"/>
+      <c r="CG7" s="41"/>
+      <c r="CH7" s="41"/>
+      <c r="CI7" s="41"/>
+      <c r="CJ7" s="41"/>
+      <c r="CK7" s="41"/>
+      <c r="CL7" s="41"/>
+      <c r="CM7" s="41"/>
+      <c r="CN7" s="41"/>
+      <c r="CO7" s="41"/>
+      <c r="CP7" s="41"/>
+      <c r="CQ7" s="41"/>
+      <c r="CR7" s="41"/>
+      <c r="CS7" s="41"/>
+      <c r="CT7" s="41"/>
+      <c r="CU7" s="41"/>
+      <c r="CV7" s="41"/>
+      <c r="CW7" s="41"/>
+      <c r="CX7" s="41"/>
+      <c r="CY7" s="41"/>
+      <c r="CZ7" s="41"/>
+      <c r="DA7" s="41"/>
+      <c r="DB7" s="41"/>
+      <c r="DC7" s="41"/>
+      <c r="DD7" s="41"/>
+      <c r="DE7" s="41"/>
+      <c r="DF7" s="41"/>
+      <c r="DG7" s="41"/>
+      <c r="DH7" s="41"/>
+      <c r="DI7" s="41"/>
+      <c r="DJ7" s="41"/>
+      <c r="DK7" s="41"/>
+      <c r="DL7" s="41"/>
+      <c r="DM7" s="41"/>
+      <c r="DN7" s="41"/>
+      <c r="DO7" s="41"/>
+      <c r="DP7" s="41"/>
+      <c r="DQ7" s="41"/>
+      <c r="DR7" s="41"/>
+      <c r="DS7" s="41"/>
+      <c r="DT7" s="41"/>
+      <c r="DU7" s="41"/>
+      <c r="DV7" s="41"/>
+      <c r="DW7" s="41"/>
+      <c r="DX7" s="41"/>
+      <c r="DY7" s="41"/>
+      <c r="DZ7" s="41"/>
+      <c r="EA7" s="41"/>
+      <c r="EB7" s="41"/>
+      <c r="EC7" s="41"/>
+      <c r="ED7" s="41"/>
+      <c r="EE7" s="41"/>
+      <c r="EF7" s="41"/>
+      <c r="EG7" s="41"/>
+      <c r="EH7" s="41"/>
+      <c r="EI7" s="41"/>
+      <c r="EJ7" s="41"/>
+      <c r="EK7" s="41"/>
+      <c r="EL7" s="41"/>
+      <c r="EM7" s="41"/>
+      <c r="EN7" s="41"/>
+      <c r="EO7" s="41"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="55">
+      <c r="B8" s="34"/>
+      <c r="C8" s="35">
         <v>150</v>
       </c>
-      <c r="D8" s="49"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="56">
+      <c r="F8" s="28">
         <v>1</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="28">
         <v>2</v>
       </c>
-      <c r="H8" s="56">
+      <c r="H8" s="28">
         <v>3</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="28">
         <v>4</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="28">
         <v>5</v>
       </c>
-      <c r="K8" s="56">
+      <c r="K8" s="28">
         <v>6</v>
       </c>
-      <c r="L8" s="56">
+      <c r="L8" s="28">
         <v>7</v>
       </c>
-      <c r="M8" s="56">
+      <c r="M8" s="28">
         <v>8</v>
       </c>
-      <c r="N8" s="56">
+      <c r="N8" s="28">
         <v>9</v>
       </c>
-      <c r="O8" s="56">
+      <c r="O8" s="28">
         <v>10</v>
       </c>
-      <c r="P8" s="56">
+      <c r="P8" s="28">
         <v>11</v>
       </c>
-      <c r="Q8" s="56">
+      <c r="Q8" s="28">
         <v>12</v>
       </c>
-      <c r="R8" s="56">
+      <c r="R8" s="28">
         <v>13</v>
       </c>
-      <c r="S8" s="56">
+      <c r="S8" s="28">
         <v>14</v>
       </c>
-      <c r="T8" s="56">
+      <c r="T8" s="28">
         <v>15</v>
       </c>
-      <c r="U8" s="56">
+      <c r="U8" s="28">
         <v>16</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="28">
         <v>17</v>
       </c>
-      <c r="W8" s="56">
+      <c r="W8" s="28">
         <v>18</v>
       </c>
-      <c r="X8" s="56">
+      <c r="X8" s="28">
         <v>19</v>
       </c>
-      <c r="Y8" s="56">
+      <c r="Y8" s="28">
         <v>20</v>
       </c>
-      <c r="Z8" s="56">
+      <c r="Z8" s="28">
         <v>21</v>
       </c>
-      <c r="AA8" s="56">
+      <c r="AA8" s="28">
         <v>22</v>
       </c>
-      <c r="AB8" s="56">
+      <c r="AB8" s="28">
         <v>23</v>
       </c>
-      <c r="AC8" s="56">
+      <c r="AC8" s="28">
         <v>24</v>
       </c>
-      <c r="AD8" s="56">
+      <c r="AD8" s="28">
         <v>25</v>
       </c>
-      <c r="AE8" s="56">
+      <c r="AE8" s="28">
         <v>26</v>
       </c>
-      <c r="AF8" s="56">
+      <c r="AF8" s="28">
         <v>27</v>
       </c>
-      <c r="AG8" s="56">
+      <c r="AG8" s="28">
         <v>28</v>
       </c>
-      <c r="AH8" s="56">
+      <c r="AH8" s="28">
         <v>29</v>
       </c>
-      <c r="AI8" s="56">
+      <c r="AI8" s="28">
         <v>30</v>
       </c>
-      <c r="AJ8" s="56">
+      <c r="AJ8" s="28">
         <v>31</v>
       </c>
-      <c r="AK8" s="56">
+      <c r="AK8" s="28">
         <v>32</v>
       </c>
-      <c r="AL8" s="56">
+      <c r="AL8" s="28">
         <v>33</v>
       </c>
-      <c r="AM8" s="56">
+      <c r="AM8" s="28">
         <v>34</v>
       </c>
-      <c r="AN8" s="56">
+      <c r="AN8" s="28">
         <v>35</v>
       </c>
-      <c r="AO8" s="56">
+      <c r="AO8" s="28">
         <v>36</v>
       </c>
-      <c r="AP8" s="56">
+      <c r="AP8" s="28">
         <v>37</v>
       </c>
-      <c r="AQ8" s="56">
+      <c r="AQ8" s="28">
         <v>38</v>
       </c>
-      <c r="AR8" s="56">
+      <c r="AR8" s="28">
         <v>39</v>
       </c>
-      <c r="AS8" s="56">
+      <c r="AS8" s="28">
         <v>40</v>
       </c>
-      <c r="AT8" s="56">
+      <c r="AT8" s="28">
         <v>41</v>
       </c>
-      <c r="AU8" s="56">
+      <c r="AU8" s="28">
         <v>42</v>
       </c>
-      <c r="AV8" s="56">
+      <c r="AV8" s="28">
         <v>43</v>
       </c>
-      <c r="AW8" s="56">
+      <c r="AW8" s="28">
         <v>44</v>
       </c>
-      <c r="AX8" s="56">
+      <c r="AX8" s="28">
         <v>45</v>
       </c>
-      <c r="AY8" s="56">
+      <c r="AY8" s="28">
         <v>46</v>
       </c>
-      <c r="AZ8" s="56">
+      <c r="AZ8" s="28">
         <v>47</v>
       </c>
-      <c r="BA8" s="56">
+      <c r="BA8" s="28">
         <v>48</v>
       </c>
-      <c r="BB8" s="56">
+      <c r="BB8" s="28">
         <v>49</v>
       </c>
-      <c r="BC8" s="56">
+      <c r="BC8" s="28">
         <v>50</v>
       </c>
-      <c r="BD8" s="56">
+      <c r="BD8" s="28">
         <v>51</v>
       </c>
-      <c r="BE8" s="56">
+      <c r="BE8" s="28">
         <v>52</v>
       </c>
-      <c r="BF8" s="56">
+      <c r="BF8" s="28">
         <v>53</v>
       </c>
-      <c r="BG8" s="56">
+      <c r="BG8" s="28">
         <v>54</v>
       </c>
-      <c r="BH8" s="56">
+      <c r="BH8" s="28">
         <v>55</v>
       </c>
-      <c r="BI8" s="56">
+      <c r="BI8" s="28">
         <v>56</v>
       </c>
-      <c r="BJ8" s="56">
+      <c r="BJ8" s="28">
         <v>57</v>
       </c>
-      <c r="BK8" s="56">
+      <c r="BK8" s="28">
         <v>58</v>
       </c>
-      <c r="BL8" s="56">
+      <c r="BL8" s="28">
         <v>59</v>
       </c>
-      <c r="BM8" s="56">
+      <c r="BM8" s="28">
         <v>60</v>
       </c>
-      <c r="BN8" s="56">
+      <c r="BN8" s="28">
         <v>61</v>
       </c>
-      <c r="BO8" s="56">
+      <c r="BO8" s="28">
         <v>62</v>
       </c>
-      <c r="BP8" s="56">
+      <c r="BP8" s="28">
         <v>63</v>
       </c>
-      <c r="BQ8" s="56">
+      <c r="BQ8" s="28">
         <v>64</v>
       </c>
-      <c r="BR8" s="56">
+      <c r="BR8" s="28">
         <v>65</v>
       </c>
-      <c r="BS8" s="56">
+      <c r="BS8" s="28">
         <v>66</v>
       </c>
-      <c r="BT8" s="56">
+      <c r="BT8" s="28">
         <v>67</v>
       </c>
-      <c r="BU8" s="56">
+      <c r="BU8" s="28">
         <v>68</v>
       </c>
-      <c r="BV8" s="56">
+      <c r="BV8" s="28">
         <v>69</v>
       </c>
-      <c r="BW8" s="56">
+      <c r="BW8" s="28">
         <v>70</v>
       </c>
-      <c r="BX8" s="56">
+      <c r="BX8" s="28">
         <v>71</v>
       </c>
-      <c r="BY8" s="56">
+      <c r="BY8" s="28">
         <v>72</v>
       </c>
-      <c r="BZ8" s="56">
+      <c r="BZ8" s="28">
         <v>73</v>
       </c>
-      <c r="CA8" s="56">
+      <c r="CA8" s="28">
         <v>74</v>
       </c>
-      <c r="CB8" s="56">
+      <c r="CB8" s="28">
         <v>75</v>
       </c>
-      <c r="CC8" s="56">
+      <c r="CC8" s="28">
         <v>76</v>
       </c>
-      <c r="CD8" s="56">
+      <c r="CD8" s="28">
         <v>77</v>
       </c>
-      <c r="CE8" s="56">
+      <c r="CE8" s="28">
         <v>78</v>
       </c>
-      <c r="CF8" s="56">
+      <c r="CF8" s="28">
         <v>79</v>
       </c>
-      <c r="CG8" s="56">
+      <c r="CG8" s="28">
         <v>80</v>
       </c>
-      <c r="CH8" s="56">
+      <c r="CH8" s="28">
         <v>81</v>
       </c>
-      <c r="CI8" s="56">
+      <c r="CI8" s="28">
         <v>82</v>
       </c>
-      <c r="CJ8" s="56">
+      <c r="CJ8" s="28">
         <v>83</v>
       </c>
-      <c r="CK8" s="56">
+      <c r="CK8" s="28">
         <v>84</v>
       </c>
-      <c r="CL8" s="56">
+      <c r="CL8" s="28">
         <v>85</v>
       </c>
-      <c r="CM8" s="56">
+      <c r="CM8" s="28">
         <v>86</v>
       </c>
-      <c r="CN8" s="56">
+      <c r="CN8" s="28">
         <v>87</v>
       </c>
-      <c r="CO8" s="56">
+      <c r="CO8" s="28">
         <v>88</v>
       </c>
-      <c r="CP8" s="56">
+      <c r="CP8" s="28">
         <v>89</v>
       </c>
-      <c r="CQ8" s="56">
+      <c r="CQ8" s="28">
         <v>90</v>
       </c>
-      <c r="CR8" s="56">
+      <c r="CR8" s="28">
         <v>91</v>
       </c>
-      <c r="CS8" s="56">
+      <c r="CS8" s="28">
         <v>92</v>
       </c>
-      <c r="CT8" s="56">
+      <c r="CT8" s="28">
         <v>93</v>
       </c>
-      <c r="CU8" s="56">
+      <c r="CU8" s="28">
         <v>94</v>
       </c>
-      <c r="CV8" s="56">
+      <c r="CV8" s="28">
         <v>95</v>
       </c>
-      <c r="CW8" s="56">
+      <c r="CW8" s="28">
         <v>96</v>
       </c>
-      <c r="CX8" s="56">
+      <c r="CX8" s="28">
         <v>97</v>
       </c>
-      <c r="CY8" s="56">
+      <c r="CY8" s="28">
         <v>98</v>
       </c>
-      <c r="CZ8" s="56">
+      <c r="CZ8" s="28">
         <v>99</v>
       </c>
-      <c r="DA8" s="56">
+      <c r="DA8" s="28">
         <v>100</v>
       </c>
-      <c r="DB8" s="56">
+      <c r="DB8" s="28">
         <v>101</v>
       </c>
-      <c r="DC8" s="56">
+      <c r="DC8" s="28">
         <v>102</v>
       </c>
-      <c r="DD8" s="56">
+      <c r="DD8" s="28">
         <v>103</v>
       </c>
-      <c r="DE8" s="56">
+      <c r="DE8" s="28">
         <v>104</v>
       </c>
-      <c r="DF8" s="56">
+      <c r="DF8" s="28">
         <v>105</v>
       </c>
-      <c r="DG8" s="56">
+      <c r="DG8" s="28">
         <v>106</v>
       </c>
-      <c r="DH8" s="56">
+      <c r="DH8" s="28">
         <v>107</v>
       </c>
-      <c r="DI8" s="56">
+      <c r="DI8" s="28">
         <v>108</v>
       </c>
-      <c r="DJ8" s="56">
+      <c r="DJ8" s="28">
         <v>109</v>
       </c>
-      <c r="DK8" s="56">
+      <c r="DK8" s="28">
         <v>110</v>
       </c>
-      <c r="DL8" s="56">
+      <c r="DL8" s="28">
         <v>111</v>
       </c>
-      <c r="DM8" s="56">
+      <c r="DM8" s="28">
         <v>112</v>
       </c>
-      <c r="DN8" s="56">
+      <c r="DN8" s="28">
         <v>113</v>
       </c>
-      <c r="DO8" s="56">
+      <c r="DO8" s="28">
         <v>114</v>
       </c>
-      <c r="DP8" s="56">
+      <c r="DP8" s="28">
         <v>115</v>
       </c>
-      <c r="DQ8" s="56">
+      <c r="DQ8" s="28">
         <v>116</v>
       </c>
-      <c r="DR8" s="56">
+      <c r="DR8" s="28">
         <v>117</v>
       </c>
-      <c r="DS8" s="56">
+      <c r="DS8" s="28">
         <v>118</v>
       </c>
-      <c r="DT8" s="56">
+      <c r="DT8" s="28">
         <v>119</v>
       </c>
-      <c r="DU8" s="56">
+      <c r="DU8" s="28">
         <v>120</v>
       </c>
-      <c r="DV8" s="56">
+      <c r="DV8" s="28">
         <v>121</v>
       </c>
-      <c r="DW8" s="56">
+      <c r="DW8" s="28">
         <v>122</v>
       </c>
-      <c r="DX8" s="56">
+      <c r="DX8" s="28">
         <v>123</v>
       </c>
-      <c r="DY8" s="56">
+      <c r="DY8" s="28">
         <v>124</v>
       </c>
-      <c r="DZ8" s="56">
+      <c r="DZ8" s="28">
         <v>125</v>
       </c>
-      <c r="EA8" s="56">
+      <c r="EA8" s="28">
         <v>126</v>
       </c>
-      <c r="EB8" s="56">
+      <c r="EB8" s="28">
         <v>127</v>
       </c>
-      <c r="EC8" s="56">
+      <c r="EC8" s="28">
         <v>128</v>
       </c>
-      <c r="ED8" s="56">
+      <c r="ED8" s="28">
         <v>129</v>
       </c>
-      <c r="EE8" s="56">
+      <c r="EE8" s="28">
         <v>130</v>
       </c>
-      <c r="EF8" s="56">
+      <c r="EF8" s="28">
         <v>131</v>
       </c>
-      <c r="EG8" s="56">
+      <c r="EG8" s="28">
         <v>132</v>
       </c>
-      <c r="EH8" s="56">
+      <c r="EH8" s="28">
         <v>133</v>
       </c>
-      <c r="EI8" s="56">
+      <c r="EI8" s="28">
         <v>134</v>
       </c>
-      <c r="EJ8" s="56">
+      <c r="EJ8" s="28">
         <v>135</v>
       </c>
-      <c r="EK8" s="56">
+      <c r="EK8" s="28">
         <v>136</v>
       </c>
-      <c r="EL8" s="56">
+      <c r="EL8" s="28">
         <v>137</v>
       </c>
-      <c r="EM8" s="56">
+      <c r="EM8" s="28">
         <v>138</v>
       </c>
-      <c r="EN8" s="56">
+      <c r="EN8" s="28">
         <v>139</v>
       </c>
-      <c r="EO8" s="56">
+      <c r="EO8" s="28">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="59"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="57"/>
-      <c r="P9" s="57"/>
-      <c r="Q9" s="57"/>
-      <c r="R9" s="57"/>
-      <c r="S9" s="57"/>
-      <c r="T9" s="57"/>
-      <c r="U9" s="57"/>
-      <c r="V9" s="57"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="57"/>
-      <c r="Y9" s="57"/>
-      <c r="Z9" s="57"/>
-      <c r="AA9" s="57"/>
-      <c r="AB9" s="57"/>
-      <c r="AC9" s="57"/>
-      <c r="AD9" s="57"/>
-      <c r="AE9" s="57"/>
-      <c r="AF9" s="57"/>
-      <c r="AG9" s="57"/>
-      <c r="AH9" s="57"/>
-      <c r="AI9" s="57"/>
-      <c r="AJ9" s="57"/>
-      <c r="AK9" s="57"/>
-      <c r="AL9" s="57"/>
-      <c r="AM9" s="57"/>
-      <c r="AN9" s="57"/>
-      <c r="AO9" s="57"/>
-      <c r="AP9" s="57"/>
-      <c r="AQ9" s="57"/>
-      <c r="AR9" s="57"/>
-      <c r="AS9" s="57"/>
-      <c r="AT9" s="57"/>
-      <c r="AU9" s="57"/>
-      <c r="AV9" s="57"/>
-      <c r="AW9" s="57"/>
-      <c r="AX9" s="57"/>
-      <c r="AY9" s="57"/>
-      <c r="AZ9" s="57"/>
-      <c r="BA9" s="57"/>
-      <c r="BB9" s="57"/>
-      <c r="BC9" s="57"/>
-      <c r="BD9" s="57"/>
-      <c r="BE9" s="57"/>
-      <c r="BF9" s="57"/>
-      <c r="BG9" s="57"/>
-      <c r="BH9" s="57"/>
-      <c r="BI9" s="57"/>
-      <c r="BJ9" s="57"/>
-      <c r="BK9" s="57"/>
-      <c r="BL9" s="57"/>
-      <c r="BM9" s="57"/>
-      <c r="BN9" s="57"/>
-      <c r="BO9" s="57"/>
-      <c r="BP9" s="57"/>
-      <c r="BQ9" s="57"/>
-      <c r="BR9" s="57"/>
-      <c r="BS9" s="57"/>
-      <c r="BT9" s="57"/>
-      <c r="BU9" s="57"/>
-      <c r="BV9" s="57"/>
-      <c r="BW9" s="57"/>
-      <c r="BX9" s="57"/>
-      <c r="BY9" s="57"/>
-      <c r="BZ9" s="57"/>
-      <c r="CA9" s="57"/>
-      <c r="CB9" s="57"/>
-      <c r="CC9" s="57"/>
-      <c r="CD9" s="57"/>
-      <c r="CE9" s="57"/>
-      <c r="CF9" s="57"/>
-      <c r="CG9" s="57"/>
-      <c r="CH9" s="57"/>
-      <c r="CI9" s="57"/>
-      <c r="CJ9" s="57"/>
-      <c r="CK9" s="57"/>
-      <c r="CL9" s="57"/>
-      <c r="CM9" s="57"/>
-      <c r="CN9" s="57"/>
-      <c r="CO9" s="57"/>
-      <c r="CP9" s="57"/>
-      <c r="CQ9" s="57"/>
-      <c r="CR9" s="57"/>
-      <c r="CS9" s="57"/>
-      <c r="CT9" s="57"/>
-      <c r="CU9" s="57"/>
-      <c r="CV9" s="57"/>
-      <c r="CW9" s="57"/>
-      <c r="CX9" s="57"/>
-      <c r="CY9" s="57"/>
-      <c r="CZ9" s="57"/>
-      <c r="DA9" s="57"/>
-      <c r="DB9" s="57"/>
-      <c r="DC9" s="57"/>
-      <c r="DD9" s="57"/>
-      <c r="DE9" s="57"/>
-      <c r="DF9" s="57"/>
-      <c r="DG9" s="57"/>
-      <c r="DH9" s="57"/>
-      <c r="DI9" s="57"/>
-      <c r="DJ9" s="57"/>
-      <c r="DK9" s="57"/>
-      <c r="DL9" s="57"/>
-      <c r="DM9" s="57"/>
-      <c r="DN9" s="57"/>
-      <c r="DO9" s="57"/>
-      <c r="DP9" s="57"/>
-      <c r="DQ9" s="57"/>
-      <c r="DR9" s="57"/>
-      <c r="DS9" s="57"/>
-      <c r="DT9" s="57"/>
-      <c r="DU9" s="57"/>
-      <c r="DV9" s="57"/>
-      <c r="DW9" s="57"/>
-      <c r="DX9" s="57"/>
-      <c r="DY9" s="57"/>
-      <c r="DZ9" s="57"/>
-      <c r="EA9" s="57"/>
-      <c r="EB9" s="57"/>
-      <c r="EC9" s="57"/>
-      <c r="ED9" s="57"/>
-      <c r="EE9" s="57"/>
-      <c r="EF9" s="57"/>
-      <c r="EG9" s="57"/>
-      <c r="EH9" s="57"/>
-      <c r="EI9" s="57"/>
-      <c r="EJ9" s="57"/>
-      <c r="EK9" s="57"/>
-      <c r="EL9" s="57"/>
-      <c r="EM9" s="57"/>
-      <c r="EN9" s="57"/>
-      <c r="EO9" s="57"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="29"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="29"/>
+      <c r="AX9" s="29"/>
+      <c r="AY9" s="29"/>
+      <c r="AZ9" s="29"/>
+      <c r="BA9" s="29"/>
+      <c r="BB9" s="29"/>
+      <c r="BC9" s="29"/>
+      <c r="BD9" s="29"/>
+      <c r="BE9" s="29"/>
+      <c r="BF9" s="29"/>
+      <c r="BG9" s="29"/>
+      <c r="BH9" s="29"/>
+      <c r="BI9" s="29"/>
+      <c r="BJ9" s="29"/>
+      <c r="BK9" s="29"/>
+      <c r="BL9" s="29"/>
+      <c r="BM9" s="29"/>
+      <c r="BN9" s="29"/>
+      <c r="BO9" s="29"/>
+      <c r="BP9" s="29"/>
+      <c r="BQ9" s="29"/>
+      <c r="BR9" s="29"/>
+      <c r="BS9" s="29"/>
+      <c r="BT9" s="29"/>
+      <c r="BU9" s="29"/>
+      <c r="BV9" s="29"/>
+      <c r="BW9" s="29"/>
+      <c r="BX9" s="29"/>
+      <c r="BY9" s="29"/>
+      <c r="BZ9" s="29"/>
+      <c r="CA9" s="29"/>
+      <c r="CB9" s="29"/>
+      <c r="CC9" s="29"/>
+      <c r="CD9" s="29"/>
+      <c r="CE9" s="29"/>
+      <c r="CF9" s="29"/>
+      <c r="CG9" s="29"/>
+      <c r="CH9" s="29"/>
+      <c r="CI9" s="29"/>
+      <c r="CJ9" s="29"/>
+      <c r="CK9" s="29"/>
+      <c r="CL9" s="29"/>
+      <c r="CM9" s="29"/>
+      <c r="CN9" s="29"/>
+      <c r="CO9" s="29"/>
+      <c r="CP9" s="29"/>
+      <c r="CQ9" s="29"/>
+      <c r="CR9" s="29"/>
+      <c r="CS9" s="29"/>
+      <c r="CT9" s="29"/>
+      <c r="CU9" s="29"/>
+      <c r="CV9" s="29"/>
+      <c r="CW9" s="29"/>
+      <c r="CX9" s="29"/>
+      <c r="CY9" s="29"/>
+      <c r="CZ9" s="29"/>
+      <c r="DA9" s="29"/>
+      <c r="DB9" s="29"/>
+      <c r="DC9" s="29"/>
+      <c r="DD9" s="29"/>
+      <c r="DE9" s="29"/>
+      <c r="DF9" s="29"/>
+      <c r="DG9" s="29"/>
+      <c r="DH9" s="29"/>
+      <c r="DI9" s="29"/>
+      <c r="DJ9" s="29"/>
+      <c r="DK9" s="29"/>
+      <c r="DL9" s="29"/>
+      <c r="DM9" s="29"/>
+      <c r="DN9" s="29"/>
+      <c r="DO9" s="29"/>
+      <c r="DP9" s="29"/>
+      <c r="DQ9" s="29"/>
+      <c r="DR9" s="29"/>
+      <c r="DS9" s="29"/>
+      <c r="DT9" s="29"/>
+      <c r="DU9" s="29"/>
+      <c r="DV9" s="29"/>
+      <c r="DW9" s="29"/>
+      <c r="DX9" s="29"/>
+      <c r="DY9" s="29"/>
+      <c r="DZ9" s="29"/>
+      <c r="EA9" s="29"/>
+      <c r="EB9" s="29"/>
+      <c r="EC9" s="29"/>
+      <c r="ED9" s="29"/>
+      <c r="EE9" s="29"/>
+      <c r="EF9" s="29"/>
+      <c r="EG9" s="29"/>
+      <c r="EH9" s="29"/>
+      <c r="EI9" s="29"/>
+      <c r="EJ9" s="29"/>
+      <c r="EK9" s="29"/>
+      <c r="EL9" s="29"/>
+      <c r="EM9" s="29"/>
+      <c r="EN9" s="29"/>
+      <c r="EO9" s="29"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
-      <c r="B10" s="59"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="38"/>
       <c r="C10" s="9"/>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -3090,7 +3090,9 @@
       <c r="BM10" s="11"/>
       <c r="BN10" s="11"/>
       <c r="BO10" s="11"/>
-      <c r="BP10" s="11"/>
+      <c r="BP10" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ10" s="11"/>
       <c r="BR10" s="11"/>
       <c r="BS10" s="11"/>
@@ -3180,7 +3182,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="14">
-        <f t="shared" ref="D11:D28" si="0">COUNT(F11:EO11)</f>
+        <f>COUNT(F11:EO11)</f>
         <v>0</v>
       </c>
       <c r="E11" s="15"/>
@@ -3336,8 +3338,8 @@
         <v>24</v>
       </c>
       <c r="D12" s="14">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" ref="D11:D28" si="0">COUNT(F12:EO12)</f>
+        <v>14</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="11"/>
@@ -3428,7 +3430,9 @@
       <c r="BO12" s="11">
         <v>0</v>
       </c>
-      <c r="BP12" s="11"/>
+      <c r="BP12" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ12" s="11"/>
       <c r="BR12" s="11"/>
       <c r="BS12" s="11"/>
@@ -3519,7 +3523,7 @@
       </c>
       <c r="D13" s="14">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="11"/>
@@ -3626,7 +3630,9 @@
       <c r="BO13" s="11">
         <v>0</v>
       </c>
-      <c r="BP13" s="11"/>
+      <c r="BP13" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ13" s="11"/>
       <c r="BR13" s="11"/>
       <c r="BS13" s="11"/>
@@ -3721,7 +3727,7 @@
       </c>
       <c r="D14" s="14">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="11"/>
@@ -3802,7 +3808,9 @@
       <c r="BO14" s="11">
         <v>0</v>
       </c>
-      <c r="BP14" s="11"/>
+      <c r="BP14" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ14" s="11"/>
       <c r="BR14" s="11"/>
       <c r="BS14" s="11"/>
@@ -3893,7 +3901,7 @@
       </c>
       <c r="D15" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="11"/>
@@ -3984,7 +3992,9 @@
       <c r="BO15" s="11">
         <v>0</v>
       </c>
-      <c r="BP15" s="11"/>
+      <c r="BP15" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ15" s="11"/>
       <c r="BR15" s="11"/>
       <c r="BS15" s="11"/>
@@ -4075,7 +4085,7 @@
       </c>
       <c r="D16" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="11"/>
@@ -4150,7 +4160,9 @@
       <c r="BM16" s="11"/>
       <c r="BN16" s="11"/>
       <c r="BO16" s="11"/>
-      <c r="BP16" s="11"/>
+      <c r="BP16" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ16" s="11"/>
       <c r="BR16" s="11"/>
       <c r="BS16" s="11"/>
@@ -4339,113 +4351,113 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AO17" s="21" t="s">
+      <c r="AO17" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="22"/>
-      <c r="AQ17" s="22"/>
-      <c r="AR17" s="22"/>
-      <c r="AS17" s="22"/>
-      <c r="AT17" s="22"/>
-      <c r="AU17" s="22"/>
-      <c r="AV17" s="22"/>
-      <c r="AW17" s="22"/>
-      <c r="AX17" s="22"/>
-      <c r="AY17" s="22"/>
-      <c r="AZ17" s="22"/>
-      <c r="BA17" s="22"/>
-      <c r="BB17" s="22"/>
-      <c r="BC17" s="22"/>
-      <c r="BD17" s="22"/>
-      <c r="BE17" s="22"/>
-      <c r="BF17" s="22"/>
-      <c r="BG17" s="22"/>
-      <c r="BH17" s="22"/>
-      <c r="BI17" s="22"/>
-      <c r="BJ17" s="22"/>
-      <c r="BK17" s="22"/>
-      <c r="BL17" s="22"/>
-      <c r="BM17" s="22"/>
-      <c r="BN17" s="22"/>
-      <c r="BO17" s="22"/>
-      <c r="BP17" s="22"/>
-      <c r="BQ17" s="22"/>
-      <c r="BR17" s="22"/>
-      <c r="BS17" s="22"/>
-      <c r="BT17" s="22"/>
-      <c r="BU17" s="22"/>
-      <c r="BV17" s="22"/>
-      <c r="BW17" s="22"/>
-      <c r="BX17" s="22"/>
-      <c r="BY17" s="22"/>
-      <c r="BZ17" s="22"/>
-      <c r="CA17" s="22"/>
-      <c r="CB17" s="22"/>
-      <c r="CC17" s="22"/>
-      <c r="CD17" s="22"/>
-      <c r="CE17" s="22"/>
-      <c r="CF17" s="22"/>
-      <c r="CG17" s="22"/>
-      <c r="CH17" s="22"/>
-      <c r="CI17" s="22"/>
-      <c r="CJ17" s="22"/>
-      <c r="CK17" s="22"/>
-      <c r="CL17" s="22"/>
-      <c r="CM17" s="22"/>
-      <c r="CN17" s="22"/>
-      <c r="CO17" s="22"/>
-      <c r="CP17" s="22"/>
-      <c r="CQ17" s="22"/>
-      <c r="CR17" s="22"/>
-      <c r="CS17" s="22"/>
-      <c r="CT17" s="22"/>
-      <c r="CU17" s="22"/>
-      <c r="CV17" s="22"/>
-      <c r="CW17" s="22"/>
-      <c r="CX17" s="22"/>
-      <c r="CY17" s="22"/>
-      <c r="CZ17" s="22"/>
-      <c r="DA17" s="22"/>
-      <c r="DB17" s="22"/>
-      <c r="DC17" s="22"/>
-      <c r="DD17" s="22"/>
-      <c r="DE17" s="22"/>
-      <c r="DF17" s="22"/>
-      <c r="DG17" s="22"/>
-      <c r="DH17" s="22"/>
-      <c r="DI17" s="22"/>
-      <c r="DJ17" s="22"/>
-      <c r="DK17" s="22"/>
-      <c r="DL17" s="22"/>
-      <c r="DM17" s="22"/>
-      <c r="DN17" s="22"/>
-      <c r="DO17" s="22"/>
-      <c r="DP17" s="22"/>
-      <c r="DQ17" s="22"/>
-      <c r="DR17" s="22"/>
-      <c r="DS17" s="22"/>
-      <c r="DT17" s="22"/>
-      <c r="DU17" s="22"/>
-      <c r="DV17" s="22"/>
-      <c r="DW17" s="22"/>
-      <c r="DX17" s="22"/>
-      <c r="DY17" s="22"/>
-      <c r="DZ17" s="22"/>
-      <c r="EA17" s="22"/>
-      <c r="EB17" s="22"/>
-      <c r="EC17" s="22"/>
-      <c r="ED17" s="22"/>
-      <c r="EE17" s="22"/>
-      <c r="EF17" s="22"/>
-      <c r="EG17" s="22"/>
-      <c r="EH17" s="22"/>
-      <c r="EI17" s="22"/>
-      <c r="EJ17" s="22"/>
-      <c r="EK17" s="22"/>
-      <c r="EL17" s="22"/>
-      <c r="EM17" s="22"/>
-      <c r="EN17" s="22"/>
-      <c r="EO17" s="23"/>
+      <c r="AP17" s="55"/>
+      <c r="AQ17" s="55"/>
+      <c r="AR17" s="55"/>
+      <c r="AS17" s="55"/>
+      <c r="AT17" s="55"/>
+      <c r="AU17" s="55"/>
+      <c r="AV17" s="55"/>
+      <c r="AW17" s="55"/>
+      <c r="AX17" s="55"/>
+      <c r="AY17" s="55"/>
+      <c r="AZ17" s="55"/>
+      <c r="BA17" s="55"/>
+      <c r="BB17" s="55"/>
+      <c r="BC17" s="55"/>
+      <c r="BD17" s="55"/>
+      <c r="BE17" s="55"/>
+      <c r="BF17" s="55"/>
+      <c r="BG17" s="55"/>
+      <c r="BH17" s="55"/>
+      <c r="BI17" s="55"/>
+      <c r="BJ17" s="55"/>
+      <c r="BK17" s="55"/>
+      <c r="BL17" s="55"/>
+      <c r="BM17" s="55"/>
+      <c r="BN17" s="55"/>
+      <c r="BO17" s="55"/>
+      <c r="BP17" s="55"/>
+      <c r="BQ17" s="55"/>
+      <c r="BR17" s="55"/>
+      <c r="BS17" s="55"/>
+      <c r="BT17" s="55"/>
+      <c r="BU17" s="55"/>
+      <c r="BV17" s="55"/>
+      <c r="BW17" s="55"/>
+      <c r="BX17" s="55"/>
+      <c r="BY17" s="55"/>
+      <c r="BZ17" s="55"/>
+      <c r="CA17" s="55"/>
+      <c r="CB17" s="55"/>
+      <c r="CC17" s="55"/>
+      <c r="CD17" s="55"/>
+      <c r="CE17" s="55"/>
+      <c r="CF17" s="55"/>
+      <c r="CG17" s="55"/>
+      <c r="CH17" s="55"/>
+      <c r="CI17" s="55"/>
+      <c r="CJ17" s="55"/>
+      <c r="CK17" s="55"/>
+      <c r="CL17" s="55"/>
+      <c r="CM17" s="55"/>
+      <c r="CN17" s="55"/>
+      <c r="CO17" s="55"/>
+      <c r="CP17" s="55"/>
+      <c r="CQ17" s="55"/>
+      <c r="CR17" s="55"/>
+      <c r="CS17" s="55"/>
+      <c r="CT17" s="55"/>
+      <c r="CU17" s="55"/>
+      <c r="CV17" s="55"/>
+      <c r="CW17" s="55"/>
+      <c r="CX17" s="55"/>
+      <c r="CY17" s="55"/>
+      <c r="CZ17" s="55"/>
+      <c r="DA17" s="55"/>
+      <c r="DB17" s="55"/>
+      <c r="DC17" s="55"/>
+      <c r="DD17" s="55"/>
+      <c r="DE17" s="55"/>
+      <c r="DF17" s="55"/>
+      <c r="DG17" s="55"/>
+      <c r="DH17" s="55"/>
+      <c r="DI17" s="55"/>
+      <c r="DJ17" s="55"/>
+      <c r="DK17" s="55"/>
+      <c r="DL17" s="55"/>
+      <c r="DM17" s="55"/>
+      <c r="DN17" s="55"/>
+      <c r="DO17" s="55"/>
+      <c r="DP17" s="55"/>
+      <c r="DQ17" s="55"/>
+      <c r="DR17" s="55"/>
+      <c r="DS17" s="55"/>
+      <c r="DT17" s="55"/>
+      <c r="DU17" s="55"/>
+      <c r="DV17" s="55"/>
+      <c r="DW17" s="55"/>
+      <c r="DX17" s="55"/>
+      <c r="DY17" s="55"/>
+      <c r="DZ17" s="55"/>
+      <c r="EA17" s="55"/>
+      <c r="EB17" s="55"/>
+      <c r="EC17" s="55"/>
+      <c r="ED17" s="55"/>
+      <c r="EE17" s="55"/>
+      <c r="EF17" s="55"/>
+      <c r="EG17" s="55"/>
+      <c r="EH17" s="55"/>
+      <c r="EI17" s="55"/>
+      <c r="EJ17" s="55"/>
+      <c r="EK17" s="55"/>
+      <c r="EL17" s="55"/>
+      <c r="EM17" s="55"/>
+      <c r="EN17" s="55"/>
+      <c r="EO17" s="56"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
@@ -4623,7 +4635,7 @@
       </c>
       <c r="D19" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="11"/>
@@ -4714,7 +4726,9 @@
       <c r="BO19" s="11">
         <v>0</v>
       </c>
-      <c r="BP19" s="11"/>
+      <c r="BP19" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ19" s="11"/>
       <c r="BR19" s="11"/>
       <c r="BS19" s="11"/>
@@ -4805,7 +4819,7 @@
       </c>
       <c r="D20" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="11"/>
@@ -4880,7 +4894,9 @@
       <c r="BM20" s="11"/>
       <c r="BN20" s="11"/>
       <c r="BO20" s="11"/>
-      <c r="BP20" s="11"/>
+      <c r="BP20" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ20" s="11"/>
       <c r="BR20" s="11"/>
       <c r="BS20" s="11"/>
@@ -4971,7 +4987,7 @@
       </c>
       <c r="D21" s="14">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="11"/>
@@ -5146,7 +5162,9 @@
       <c r="BO21" s="11">
         <v>0</v>
       </c>
-      <c r="BP21" s="11"/>
+      <c r="BP21" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ21" s="11"/>
       <c r="BR21" s="11"/>
       <c r="BS21" s="11"/>
@@ -5237,7 +5255,7 @@
       </c>
       <c r="D22" s="14">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="11"/>
@@ -5336,7 +5354,9 @@
       <c r="BO22" s="11">
         <v>0</v>
       </c>
-      <c r="BP22" s="11"/>
+      <c r="BP22" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ22" s="11"/>
       <c r="BR22" s="11"/>
       <c r="BS22" s="11"/>
@@ -5427,7 +5447,7 @@
       </c>
       <c r="D23" s="14">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="11">
@@ -5606,7 +5626,9 @@
       <c r="BO23" s="11">
         <v>0</v>
       </c>
-      <c r="BP23" s="11"/>
+      <c r="BP23" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ23" s="11"/>
       <c r="BR23" s="11"/>
       <c r="BS23" s="11"/>
@@ -5697,7 +5719,7 @@
       </c>
       <c r="D24" s="14">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="11"/>
@@ -5798,7 +5820,9 @@
       <c r="BM24" s="11"/>
       <c r="BN24" s="11"/>
       <c r="BO24" s="11"/>
-      <c r="BP24" s="11"/>
+      <c r="BP24" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ24" s="11"/>
       <c r="BR24" s="11"/>
       <c r="BS24" s="11"/>
@@ -5889,7 +5913,7 @@
       </c>
       <c r="D25" s="14">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="11"/>
@@ -6004,7 +6028,9 @@
       <c r="BO25" s="11">
         <v>0</v>
       </c>
-      <c r="BP25" s="11"/>
+      <c r="BP25" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ25" s="11"/>
       <c r="BR25" s="11"/>
       <c r="BS25" s="11"/>
@@ -6095,7 +6121,7 @@
       </c>
       <c r="D26" s="14">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="11"/>
@@ -6194,7 +6220,9 @@
       <c r="BO26" s="11">
         <v>0</v>
       </c>
-      <c r="BP26" s="11"/>
+      <c r="BP26" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ26" s="11"/>
       <c r="BR26" s="11"/>
       <c r="BS26" s="11"/>
@@ -6285,7 +6313,7 @@
       </c>
       <c r="D27" s="14">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="11"/>
@@ -6460,7 +6488,9 @@
       <c r="BO27" s="11">
         <v>0</v>
       </c>
-      <c r="BP27" s="11"/>
+      <c r="BP27" s="11">
+        <v>0</v>
+      </c>
       <c r="BQ27" s="11"/>
       <c r="BR27" s="11"/>
       <c r="BS27" s="11"/>
@@ -6553,149 +6583,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="61" t="s">
+      <c r="E28" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="61"/>
-      <c r="R28" s="61"/>
-      <c r="S28" s="61"/>
-      <c r="T28" s="61"/>
-      <c r="U28" s="61"/>
-      <c r="V28" s="61"/>
-      <c r="W28" s="61"/>
-      <c r="X28" s="61"/>
-      <c r="Y28" s="61"/>
-      <c r="Z28" s="61"/>
-      <c r="AA28" s="61"/>
-      <c r="AB28" s="61"/>
-      <c r="AC28" s="61"/>
-      <c r="AD28" s="61"/>
-      <c r="AE28" s="61"/>
-      <c r="AF28" s="61"/>
-      <c r="AG28" s="61"/>
-      <c r="AH28" s="61"/>
-      <c r="AI28" s="61"/>
-      <c r="AJ28" s="61"/>
-      <c r="AK28" s="61"/>
-      <c r="AL28" s="61"/>
-      <c r="AM28" s="61"/>
-      <c r="AN28" s="61"/>
-      <c r="AO28" s="61"/>
-      <c r="AP28" s="61"/>
-      <c r="AQ28" s="61"/>
-      <c r="AR28" s="61"/>
-      <c r="AS28" s="61"/>
-      <c r="AT28" s="61"/>
-      <c r="AU28" s="61"/>
-      <c r="AV28" s="61"/>
-      <c r="AW28" s="61"/>
-      <c r="AX28" s="61"/>
-      <c r="AY28" s="61"/>
-      <c r="AZ28" s="61"/>
-      <c r="BA28" s="61"/>
-      <c r="BB28" s="61"/>
-      <c r="BC28" s="61"/>
-      <c r="BD28" s="61"/>
-      <c r="BE28" s="61"/>
-      <c r="BF28" s="61"/>
-      <c r="BG28" s="61"/>
-      <c r="BH28" s="61"/>
-      <c r="BI28" s="61"/>
-      <c r="BJ28" s="61"/>
-      <c r="BK28" s="61"/>
-      <c r="BL28" s="61"/>
-      <c r="BM28" s="61"/>
-      <c r="BN28" s="61"/>
-      <c r="BO28" s="61"/>
-      <c r="BP28" s="61"/>
-      <c r="BQ28" s="61"/>
-      <c r="BR28" s="61"/>
-      <c r="BS28" s="61"/>
-      <c r="BT28" s="61"/>
-      <c r="BU28" s="61"/>
-      <c r="BV28" s="61"/>
-      <c r="BW28" s="61"/>
-      <c r="BX28" s="61"/>
-      <c r="BY28" s="61"/>
-      <c r="BZ28" s="61"/>
-      <c r="CA28" s="61"/>
-      <c r="CB28" s="61"/>
-      <c r="CC28" s="61"/>
-      <c r="CD28" s="61"/>
-      <c r="CE28" s="61"/>
-      <c r="CF28" s="61"/>
-      <c r="CG28" s="61"/>
-      <c r="CH28" s="61"/>
-      <c r="CI28" s="61"/>
-      <c r="CJ28" s="61"/>
-      <c r="CK28" s="61"/>
-      <c r="CL28" s="61"/>
-      <c r="CM28" s="61"/>
-      <c r="CN28" s="61"/>
-      <c r="CO28" s="61"/>
-      <c r="CP28" s="61"/>
-      <c r="CQ28" s="61"/>
-      <c r="CR28" s="61"/>
-      <c r="CS28" s="61"/>
-      <c r="CT28" s="61"/>
-      <c r="CU28" s="61"/>
-      <c r="CV28" s="61"/>
-      <c r="CW28" s="61"/>
-      <c r="CX28" s="61"/>
-      <c r="CY28" s="61"/>
-      <c r="CZ28" s="61"/>
-      <c r="DA28" s="61"/>
-      <c r="DB28" s="61"/>
-      <c r="DC28" s="61"/>
-      <c r="DD28" s="61"/>
-      <c r="DE28" s="61"/>
-      <c r="DF28" s="61"/>
-      <c r="DG28" s="61"/>
-      <c r="DH28" s="61"/>
-      <c r="DI28" s="61"/>
-      <c r="DJ28" s="61"/>
-      <c r="DK28" s="61"/>
-      <c r="DL28" s="61"/>
-      <c r="DM28" s="61"/>
-      <c r="DN28" s="61"/>
-      <c r="DO28" s="61"/>
-      <c r="DP28" s="61"/>
-      <c r="DQ28" s="61"/>
-      <c r="DR28" s="61"/>
-      <c r="DS28" s="61"/>
-      <c r="DT28" s="61"/>
-      <c r="DU28" s="61"/>
-      <c r="DV28" s="61"/>
-      <c r="DW28" s="61"/>
-      <c r="DX28" s="61"/>
-      <c r="DY28" s="61"/>
-      <c r="DZ28" s="61"/>
-      <c r="EA28" s="61"/>
-      <c r="EB28" s="61"/>
-      <c r="EC28" s="61"/>
-      <c r="ED28" s="61"/>
-      <c r="EE28" s="61"/>
-      <c r="EF28" s="61"/>
-      <c r="EG28" s="61"/>
-      <c r="EH28" s="61"/>
-      <c r="EI28" s="61"/>
-      <c r="EJ28" s="61"/>
-      <c r="EK28" s="61"/>
-      <c r="EL28" s="61"/>
-      <c r="EM28" s="61"/>
-      <c r="EN28" s="61"/>
-      <c r="EO28" s="61"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="30"/>
+      <c r="AP28" s="30"/>
+      <c r="AQ28" s="30"/>
+      <c r="AR28" s="30"/>
+      <c r="AS28" s="30"/>
+      <c r="AT28" s="30"/>
+      <c r="AU28" s="30"/>
+      <c r="AV28" s="30"/>
+      <c r="AW28" s="30"/>
+      <c r="AX28" s="30"/>
+      <c r="AY28" s="30"/>
+      <c r="AZ28" s="30"/>
+      <c r="BA28" s="30"/>
+      <c r="BB28" s="30"/>
+      <c r="BC28" s="30"/>
+      <c r="BD28" s="30"/>
+      <c r="BE28" s="30"/>
+      <c r="BF28" s="30"/>
+      <c r="BG28" s="30"/>
+      <c r="BH28" s="30"/>
+      <c r="BI28" s="30"/>
+      <c r="BJ28" s="30"/>
+      <c r="BK28" s="30"/>
+      <c r="BL28" s="30"/>
+      <c r="BM28" s="30"/>
+      <c r="BN28" s="30"/>
+      <c r="BO28" s="30"/>
+      <c r="BP28" s="30"/>
+      <c r="BQ28" s="30"/>
+      <c r="BR28" s="30"/>
+      <c r="BS28" s="30"/>
+      <c r="BT28" s="30"/>
+      <c r="BU28" s="30"/>
+      <c r="BV28" s="30"/>
+      <c r="BW28" s="30"/>
+      <c r="BX28" s="30"/>
+      <c r="BY28" s="30"/>
+      <c r="BZ28" s="30"/>
+      <c r="CA28" s="30"/>
+      <c r="CB28" s="30"/>
+      <c r="CC28" s="30"/>
+      <c r="CD28" s="30"/>
+      <c r="CE28" s="30"/>
+      <c r="CF28" s="30"/>
+      <c r="CG28" s="30"/>
+      <c r="CH28" s="30"/>
+      <c r="CI28" s="30"/>
+      <c r="CJ28" s="30"/>
+      <c r="CK28" s="30"/>
+      <c r="CL28" s="30"/>
+      <c r="CM28" s="30"/>
+      <c r="CN28" s="30"/>
+      <c r="CO28" s="30"/>
+      <c r="CP28" s="30"/>
+      <c r="CQ28" s="30"/>
+      <c r="CR28" s="30"/>
+      <c r="CS28" s="30"/>
+      <c r="CT28" s="30"/>
+      <c r="CU28" s="30"/>
+      <c r="CV28" s="30"/>
+      <c r="CW28" s="30"/>
+      <c r="CX28" s="30"/>
+      <c r="CY28" s="30"/>
+      <c r="CZ28" s="30"/>
+      <c r="DA28" s="30"/>
+      <c r="DB28" s="30"/>
+      <c r="DC28" s="30"/>
+      <c r="DD28" s="30"/>
+      <c r="DE28" s="30"/>
+      <c r="DF28" s="30"/>
+      <c r="DG28" s="30"/>
+      <c r="DH28" s="30"/>
+      <c r="DI28" s="30"/>
+      <c r="DJ28" s="30"/>
+      <c r="DK28" s="30"/>
+      <c r="DL28" s="30"/>
+      <c r="DM28" s="30"/>
+      <c r="DN28" s="30"/>
+      <c r="DO28" s="30"/>
+      <c r="DP28" s="30"/>
+      <c r="DQ28" s="30"/>
+      <c r="DR28" s="30"/>
+      <c r="DS28" s="30"/>
+      <c r="DT28" s="30"/>
+      <c r="DU28" s="30"/>
+      <c r="DV28" s="30"/>
+      <c r="DW28" s="30"/>
+      <c r="DX28" s="30"/>
+      <c r="DY28" s="30"/>
+      <c r="DZ28" s="30"/>
+      <c r="EA28" s="30"/>
+      <c r="EB28" s="30"/>
+      <c r="EC28" s="30"/>
+      <c r="ED28" s="30"/>
+      <c r="EE28" s="30"/>
+      <c r="EF28" s="30"/>
+      <c r="EG28" s="30"/>
+      <c r="EH28" s="30"/>
+      <c r="EI28" s="30"/>
+      <c r="EJ28" s="30"/>
+      <c r="EK28" s="30"/>
+      <c r="EL28" s="30"/>
+      <c r="EM28" s="30"/>
+      <c r="EN28" s="30"/>
+      <c r="EO28" s="30"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6704,6 +6734,299 @@
     </row>
   </sheetData>
   <mergeCells count="317">
+    <mergeCell ref="AO17:EO17"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="BM1:BO1"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="E28:EO28"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
     <mergeCell ref="BQ1:BU1"/>
     <mergeCell ref="BV1:BX1"/>
     <mergeCell ref="EH8:EH9"/>
@@ -6728,299 +7051,6 @@
     <mergeCell ref="DX8:DX9"/>
     <mergeCell ref="DY8:DY9"/>
     <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="E28:EO28"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="BH1:BL1"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AO17:EO17"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="BM1:BO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F4A42-CD37-415C-A790-98D22D08A0D9}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5574C9-1A97-415F-89FD-943785BF847C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,102 +822,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -948,6 +852,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -965,6 +872,99 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1193,127 +1193,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
-      <c r="F1" s="62">
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="F1" s="30">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="33">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32">
         <v>3</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33">
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32">
         <v>4</v>
       </c>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="64">
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33">
         <v>4</v>
       </c>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="64">
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="33">
         <v>4</v>
       </c>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="64">
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="33">
         <v>4</v>
       </c>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="31">
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="65">
         <v>2</v>
       </c>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="25">
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="43">
         <v>4</v>
       </c>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="25">
+      <c r="AF1" s="44"/>
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="43">
         <v>4</v>
       </c>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="27"/>
-      <c r="AM1" s="25">
+      <c r="AJ1" s="44"/>
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="43">
         <v>2</v>
       </c>
-      <c r="AN1" s="27"/>
-      <c r="AO1" s="25">
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="43">
         <v>4</v>
       </c>
-      <c r="AP1" s="26"/>
-      <c r="AQ1" s="26"/>
-      <c r="AR1" s="27"/>
-      <c r="AS1" s="25">
+      <c r="AP1" s="44"/>
+      <c r="AQ1" s="44"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="43">
         <v>5</v>
       </c>
-      <c r="AT1" s="26"/>
-      <c r="AU1" s="26"/>
-      <c r="AV1" s="26"/>
-      <c r="AW1" s="27"/>
+      <c r="AT1" s="44"/>
+      <c r="AU1" s="44"/>
+      <c r="AV1" s="44"/>
+      <c r="AW1" s="45"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="25">
+      <c r="AY1" s="43">
         <v>5</v>
       </c>
-      <c r="AZ1" s="26"/>
-      <c r="BA1" s="26"/>
-      <c r="BB1" s="26"/>
-      <c r="BC1" s="27"/>
-      <c r="BD1" s="25">
+      <c r="AZ1" s="44"/>
+      <c r="BA1" s="44"/>
+      <c r="BB1" s="44"/>
+      <c r="BC1" s="45"/>
+      <c r="BD1" s="43">
         <v>3</v>
       </c>
-      <c r="BE1" s="26"/>
-      <c r="BF1" s="27"/>
+      <c r="BE1" s="44"/>
+      <c r="BF1" s="45"/>
       <c r="BG1" s="20">
         <v>1</v>
       </c>
-      <c r="BH1" s="33">
+      <c r="BH1" s="32">
         <v>5</v>
       </c>
-      <c r="BI1" s="33"/>
-      <c r="BJ1" s="33"/>
-      <c r="BK1" s="33"/>
-      <c r="BL1" s="33"/>
-      <c r="BM1" s="25">
+      <c r="BI1" s="32"/>
+      <c r="BJ1" s="32"/>
+      <c r="BK1" s="32"/>
+      <c r="BL1" s="32"/>
+      <c r="BM1" s="43">
         <v>3</v>
       </c>
-      <c r="BN1" s="26"/>
-      <c r="BO1" s="27"/>
+      <c r="BN1" s="44"/>
+      <c r="BO1" s="45"/>
       <c r="BP1" s="21">
         <v>1</v>
       </c>
-      <c r="BQ1" s="22">
+      <c r="BQ1" s="67">
         <v>5</v>
       </c>
-      <c r="BR1" s="23"/>
-      <c r="BS1" s="23"/>
-      <c r="BT1" s="23"/>
-      <c r="BU1" s="24"/>
-      <c r="BV1" s="25">
+      <c r="BR1" s="68"/>
+      <c r="BS1" s="68"/>
+      <c r="BT1" s="68"/>
+      <c r="BU1" s="69"/>
+      <c r="BV1" s="43">
         <v>3</v>
       </c>
-      <c r="BW1" s="26"/>
-      <c r="BX1" s="27"/>
+      <c r="BW1" s="44"/>
+      <c r="BX1" s="45"/>
       <c r="BY1" s="4"/>
       <c r="BZ1" s="4"/>
       <c r="CA1" s="4"/>
@@ -1389,1636 +1389,1636 @@
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="67" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="L2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="52" t="s">
+      <c r="R2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="52" t="s">
+      <c r="S2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="52" t="s">
+      <c r="T2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="52" t="s">
+      <c r="V2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="52" t="s">
+      <c r="W2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="52" t="s">
+      <c r="X2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Y2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="52" t="s">
+      <c r="Z2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="50" t="s">
+      <c r="AA2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="50" t="s">
+      <c r="AB2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="40">
+      <c r="AC2" s="39">
         <v>46199</v>
       </c>
-      <c r="AD2" s="40">
+      <c r="AD2" s="39">
         <v>46199</v>
       </c>
-      <c r="AE2" s="40">
+      <c r="AE2" s="39">
         <v>46202</v>
       </c>
-      <c r="AF2" s="40">
+      <c r="AF2" s="39">
         <v>46202</v>
       </c>
-      <c r="AG2" s="40">
+      <c r="AG2" s="39">
         <v>46202</v>
       </c>
-      <c r="AH2" s="40">
+      <c r="AH2" s="39">
         <v>46202</v>
       </c>
-      <c r="AI2" s="40">
+      <c r="AI2" s="39">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="40">
+      <c r="AJ2" s="39">
         <v>46205</v>
       </c>
-      <c r="AK2" s="40">
+      <c r="AK2" s="39">
         <v>46205</v>
       </c>
-      <c r="AL2" s="40">
+      <c r="AL2" s="39">
         <v>46205</v>
       </c>
-      <c r="AM2" s="40">
+      <c r="AM2" s="39">
         <v>46206</v>
       </c>
-      <c r="AN2" s="40">
+      <c r="AN2" s="39">
         <v>46206</v>
       </c>
-      <c r="AO2" s="40">
+      <c r="AO2" s="39">
         <v>46212</v>
       </c>
-      <c r="AP2" s="40">
+      <c r="AP2" s="39">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="40">
+      <c r="AQ2" s="39">
         <v>46212</v>
       </c>
-      <c r="AR2" s="40">
+      <c r="AR2" s="39">
         <v>46212</v>
       </c>
-      <c r="AS2" s="40">
+      <c r="AS2" s="39">
         <v>46213</v>
       </c>
-      <c r="AT2" s="40">
+      <c r="AT2" s="39">
         <v>46213</v>
       </c>
-      <c r="AU2" s="40">
+      <c r="AU2" s="39">
         <v>46213</v>
       </c>
-      <c r="AV2" s="40">
+      <c r="AV2" s="39">
         <v>46213</v>
       </c>
-      <c r="AW2" s="40">
+      <c r="AW2" s="39">
         <v>46213</v>
       </c>
-      <c r="AX2" s="40">
+      <c r="AX2" s="39">
         <v>46218</v>
       </c>
-      <c r="AY2" s="40">
+      <c r="AY2" s="39">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="40">
+      <c r="AZ2" s="39">
         <v>46219</v>
       </c>
-      <c r="BA2" s="40">
+      <c r="BA2" s="39">
         <v>46219</v>
       </c>
-      <c r="BB2" s="40">
+      <c r="BB2" s="39">
         <v>46219</v>
       </c>
-      <c r="BC2" s="40">
+      <c r="BC2" s="39">
         <v>46219</v>
       </c>
-      <c r="BD2" s="40">
+      <c r="BD2" s="39">
         <v>46220</v>
       </c>
-      <c r="BE2" s="40">
+      <c r="BE2" s="39">
         <v>46220</v>
       </c>
-      <c r="BF2" s="40">
+      <c r="BF2" s="39">
         <v>46220</v>
       </c>
-      <c r="BG2" s="40">
+      <c r="BG2" s="39">
         <v>46225</v>
       </c>
-      <c r="BH2" s="40">
+      <c r="BH2" s="39">
         <v>46226</v>
       </c>
-      <c r="BI2" s="40">
+      <c r="BI2" s="39">
         <v>46226</v>
       </c>
-      <c r="BJ2" s="40">
+      <c r="BJ2" s="39">
         <v>46226</v>
       </c>
-      <c r="BK2" s="40">
+      <c r="BK2" s="39">
         <v>46226</v>
       </c>
-      <c r="BL2" s="40">
+      <c r="BL2" s="39">
         <v>46226</v>
       </c>
-      <c r="BM2" s="40">
+      <c r="BM2" s="39">
         <v>46227</v>
       </c>
-      <c r="BN2" s="40">
+      <c r="BN2" s="39">
         <v>46227</v>
       </c>
-      <c r="BO2" s="40">
+      <c r="BO2" s="39">
         <v>46227</v>
       </c>
-      <c r="BP2" s="40">
+      <c r="BP2" s="39">
         <v>46232</v>
       </c>
-      <c r="BQ2" s="40">
+      <c r="BQ2" s="39">
         <v>46233</v>
       </c>
-      <c r="BR2" s="40">
+      <c r="BR2" s="39">
         <v>46233</v>
       </c>
-      <c r="BS2" s="40">
+      <c r="BS2" s="39">
         <v>46233</v>
       </c>
-      <c r="BT2" s="40">
+      <c r="BT2" s="39">
         <v>46233</v>
       </c>
-      <c r="BU2" s="40">
+      <c r="BU2" s="39">
         <v>46233</v>
       </c>
-      <c r="BV2" s="40">
+      <c r="BV2" s="39">
         <v>46234</v>
       </c>
-      <c r="BW2" s="40">
+      <c r="BW2" s="39">
         <v>46234</v>
       </c>
       <c r="BX2" s="48">
         <v>46234</v>
       </c>
-      <c r="BY2" s="40"/>
-      <c r="BZ2" s="40"/>
-      <c r="CA2" s="40"/>
-      <c r="CB2" s="40"/>
-      <c r="CC2" s="40"/>
-      <c r="CD2" s="40"/>
-      <c r="CE2" s="40"/>
-      <c r="CF2" s="40"/>
-      <c r="CG2" s="40"/>
-      <c r="CH2" s="40"/>
-      <c r="CI2" s="40"/>
-      <c r="CJ2" s="40"/>
-      <c r="CK2" s="40"/>
-      <c r="CL2" s="40"/>
-      <c r="CM2" s="40"/>
-      <c r="CN2" s="40"/>
-      <c r="CO2" s="40"/>
-      <c r="CP2" s="40"/>
-      <c r="CQ2" s="40"/>
-      <c r="CR2" s="40"/>
-      <c r="CS2" s="40"/>
-      <c r="CT2" s="40"/>
-      <c r="CU2" s="40"/>
-      <c r="CV2" s="40"/>
-      <c r="CW2" s="40"/>
-      <c r="CX2" s="40"/>
-      <c r="CY2" s="40"/>
-      <c r="CZ2" s="40"/>
-      <c r="DA2" s="40"/>
-      <c r="DB2" s="40"/>
-      <c r="DC2" s="40"/>
-      <c r="DD2" s="40"/>
-      <c r="DE2" s="40"/>
-      <c r="DF2" s="40"/>
-      <c r="DG2" s="40"/>
-      <c r="DH2" s="40"/>
-      <c r="DI2" s="40"/>
-      <c r="DJ2" s="40"/>
-      <c r="DK2" s="40"/>
-      <c r="DL2" s="40"/>
-      <c r="DM2" s="40"/>
-      <c r="DN2" s="40"/>
-      <c r="DO2" s="40"/>
-      <c r="DP2" s="40"/>
-      <c r="DQ2" s="40"/>
-      <c r="DR2" s="40"/>
-      <c r="DS2" s="40"/>
-      <c r="DT2" s="40"/>
-      <c r="DU2" s="40"/>
-      <c r="DV2" s="40"/>
-      <c r="DW2" s="40"/>
-      <c r="DX2" s="40"/>
-      <c r="DY2" s="40"/>
-      <c r="DZ2" s="40"/>
-      <c r="EA2" s="40"/>
-      <c r="EB2" s="40"/>
-      <c r="EC2" s="40"/>
-      <c r="ED2" s="40"/>
-      <c r="EE2" s="40"/>
-      <c r="EF2" s="40"/>
-      <c r="EG2" s="40"/>
-      <c r="EH2" s="40"/>
-      <c r="EI2" s="40"/>
-      <c r="EJ2" s="40"/>
-      <c r="EK2" s="40"/>
-      <c r="EL2" s="40"/>
-      <c r="EM2" s="40"/>
-      <c r="EN2" s="40"/>
-      <c r="EO2" s="40"/>
+      <c r="BY2" s="39"/>
+      <c r="BZ2" s="39"/>
+      <c r="CA2" s="39"/>
+      <c r="CB2" s="39"/>
+      <c r="CC2" s="39"/>
+      <c r="CD2" s="39"/>
+      <c r="CE2" s="39"/>
+      <c r="CF2" s="39"/>
+      <c r="CG2" s="39"/>
+      <c r="CH2" s="39"/>
+      <c r="CI2" s="39"/>
+      <c r="CJ2" s="39"/>
+      <c r="CK2" s="39"/>
+      <c r="CL2" s="39"/>
+      <c r="CM2" s="39"/>
+      <c r="CN2" s="39"/>
+      <c r="CO2" s="39"/>
+      <c r="CP2" s="39"/>
+      <c r="CQ2" s="39"/>
+      <c r="CR2" s="39"/>
+      <c r="CS2" s="39"/>
+      <c r="CT2" s="39"/>
+      <c r="CU2" s="39"/>
+      <c r="CV2" s="39"/>
+      <c r="CW2" s="39"/>
+      <c r="CX2" s="39"/>
+      <c r="CY2" s="39"/>
+      <c r="CZ2" s="39"/>
+      <c r="DA2" s="39"/>
+      <c r="DB2" s="39"/>
+      <c r="DC2" s="39"/>
+      <c r="DD2" s="39"/>
+      <c r="DE2" s="39"/>
+      <c r="DF2" s="39"/>
+      <c r="DG2" s="39"/>
+      <c r="DH2" s="39"/>
+      <c r="DI2" s="39"/>
+      <c r="DJ2" s="39"/>
+      <c r="DK2" s="39"/>
+      <c r="DL2" s="39"/>
+      <c r="DM2" s="39"/>
+      <c r="DN2" s="39"/>
+      <c r="DO2" s="39"/>
+      <c r="DP2" s="39"/>
+      <c r="DQ2" s="39"/>
+      <c r="DR2" s="39"/>
+      <c r="DS2" s="39"/>
+      <c r="DT2" s="39"/>
+      <c r="DU2" s="39"/>
+      <c r="DV2" s="39"/>
+      <c r="DW2" s="39"/>
+      <c r="DX2" s="39"/>
+      <c r="DY2" s="39"/>
+      <c r="DZ2" s="39"/>
+      <c r="EA2" s="39"/>
+      <c r="EB2" s="39"/>
+      <c r="EC2" s="39"/>
+      <c r="ED2" s="39"/>
+      <c r="EE2" s="39"/>
+      <c r="EF2" s="39"/>
+      <c r="EG2" s="39"/>
+      <c r="EH2" s="39"/>
+      <c r="EI2" s="39"/>
+      <c r="EJ2" s="39"/>
+      <c r="EK2" s="39"/>
+      <c r="EL2" s="39"/>
+      <c r="EM2" s="39"/>
+      <c r="EN2" s="39"/>
+      <c r="EO2" s="39"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="40"/>
-      <c r="AP3" s="40"/>
-      <c r="AQ3" s="40"/>
-      <c r="AR3" s="40"/>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="40"/>
-      <c r="AU3" s="40"/>
-      <c r="AV3" s="40"/>
-      <c r="AW3" s="40"/>
-      <c r="AX3" s="40"/>
-      <c r="AY3" s="40"/>
-      <c r="AZ3" s="40"/>
-      <c r="BA3" s="40"/>
-      <c r="BB3" s="40"/>
-      <c r="BC3" s="40"/>
-      <c r="BD3" s="40"/>
-      <c r="BE3" s="40"/>
-      <c r="BF3" s="40"/>
-      <c r="BG3" s="40"/>
-      <c r="BH3" s="40"/>
-      <c r="BI3" s="40"/>
-      <c r="BJ3" s="40"/>
-      <c r="BK3" s="40"/>
-      <c r="BL3" s="40"/>
-      <c r="BM3" s="40"/>
-      <c r="BN3" s="40"/>
-      <c r="BO3" s="40"/>
-      <c r="BP3" s="40"/>
-      <c r="BQ3" s="40"/>
-      <c r="BR3" s="40"/>
-      <c r="BS3" s="40"/>
-      <c r="BT3" s="40"/>
-      <c r="BU3" s="40"/>
-      <c r="BV3" s="40"/>
-      <c r="BW3" s="40"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="46"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="39"/>
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="39"/>
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="39"/>
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="39"/>
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="39"/>
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="39"/>
       <c r="BX3" s="48"/>
-      <c r="BY3" s="40"/>
-      <c r="BZ3" s="40"/>
-      <c r="CA3" s="40"/>
-      <c r="CB3" s="40"/>
-      <c r="CC3" s="40"/>
-      <c r="CD3" s="40"/>
-      <c r="CE3" s="40"/>
-      <c r="CF3" s="40"/>
-      <c r="CG3" s="40"/>
-      <c r="CH3" s="40"/>
-      <c r="CI3" s="40"/>
-      <c r="CJ3" s="40"/>
-      <c r="CK3" s="40"/>
-      <c r="CL3" s="40"/>
-      <c r="CM3" s="40"/>
-      <c r="CN3" s="40"/>
-      <c r="CO3" s="40"/>
-      <c r="CP3" s="40"/>
-      <c r="CQ3" s="40"/>
-      <c r="CR3" s="40"/>
-      <c r="CS3" s="40"/>
-      <c r="CT3" s="40"/>
-      <c r="CU3" s="40"/>
-      <c r="CV3" s="40"/>
-      <c r="CW3" s="40"/>
-      <c r="CX3" s="40"/>
-      <c r="CY3" s="40"/>
-      <c r="CZ3" s="40"/>
-      <c r="DA3" s="40"/>
-      <c r="DB3" s="40"/>
-      <c r="DC3" s="40"/>
-      <c r="DD3" s="40"/>
-      <c r="DE3" s="40"/>
-      <c r="DF3" s="40"/>
-      <c r="DG3" s="40"/>
-      <c r="DH3" s="40"/>
-      <c r="DI3" s="40"/>
-      <c r="DJ3" s="40"/>
-      <c r="DK3" s="40"/>
-      <c r="DL3" s="40"/>
-      <c r="DM3" s="40"/>
-      <c r="DN3" s="40"/>
-      <c r="DO3" s="40"/>
-      <c r="DP3" s="40"/>
-      <c r="DQ3" s="40"/>
-      <c r="DR3" s="40"/>
-      <c r="DS3" s="40"/>
-      <c r="DT3" s="40"/>
-      <c r="DU3" s="40"/>
-      <c r="DV3" s="40"/>
-      <c r="DW3" s="40"/>
-      <c r="DX3" s="40"/>
-      <c r="DY3" s="40"/>
-      <c r="DZ3" s="40"/>
-      <c r="EA3" s="40"/>
-      <c r="EB3" s="40"/>
-      <c r="EC3" s="40"/>
-      <c r="ED3" s="40"/>
-      <c r="EE3" s="40"/>
-      <c r="EF3" s="40"/>
-      <c r="EG3" s="40"/>
-      <c r="EH3" s="40"/>
-      <c r="EI3" s="40"/>
-      <c r="EJ3" s="40"/>
-      <c r="EK3" s="40"/>
-      <c r="EL3" s="40"/>
-      <c r="EM3" s="40"/>
-      <c r="EN3" s="40"/>
-      <c r="EO3" s="40"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="39"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="39"/>
+      <c r="CF3" s="39"/>
+      <c r="CG3" s="39"/>
+      <c r="CH3" s="39"/>
+      <c r="CI3" s="39"/>
+      <c r="CJ3" s="39"/>
+      <c r="CK3" s="39"/>
+      <c r="CL3" s="39"/>
+      <c r="CM3" s="39"/>
+      <c r="CN3" s="39"/>
+      <c r="CO3" s="39"/>
+      <c r="CP3" s="39"/>
+      <c r="CQ3" s="39"/>
+      <c r="CR3" s="39"/>
+      <c r="CS3" s="39"/>
+      <c r="CT3" s="39"/>
+      <c r="CU3" s="39"/>
+      <c r="CV3" s="39"/>
+      <c r="CW3" s="39"/>
+      <c r="CX3" s="39"/>
+      <c r="CY3" s="39"/>
+      <c r="CZ3" s="39"/>
+      <c r="DA3" s="39"/>
+      <c r="DB3" s="39"/>
+      <c r="DC3" s="39"/>
+      <c r="DD3" s="39"/>
+      <c r="DE3" s="39"/>
+      <c r="DF3" s="39"/>
+      <c r="DG3" s="39"/>
+      <c r="DH3" s="39"/>
+      <c r="DI3" s="39"/>
+      <c r="DJ3" s="39"/>
+      <c r="DK3" s="39"/>
+      <c r="DL3" s="39"/>
+      <c r="DM3" s="39"/>
+      <c r="DN3" s="39"/>
+      <c r="DO3" s="39"/>
+      <c r="DP3" s="39"/>
+      <c r="DQ3" s="39"/>
+      <c r="DR3" s="39"/>
+      <c r="DS3" s="39"/>
+      <c r="DT3" s="39"/>
+      <c r="DU3" s="39"/>
+      <c r="DV3" s="39"/>
+      <c r="DW3" s="39"/>
+      <c r="DX3" s="39"/>
+      <c r="DY3" s="39"/>
+      <c r="DZ3" s="39"/>
+      <c r="EA3" s="39"/>
+      <c r="EB3" s="39"/>
+      <c r="EC3" s="39"/>
+      <c r="ED3" s="39"/>
+      <c r="EE3" s="39"/>
+      <c r="EF3" s="39"/>
+      <c r="EG3" s="39"/>
+      <c r="EH3" s="39"/>
+      <c r="EI3" s="39"/>
+      <c r="EJ3" s="39"/>
+      <c r="EK3" s="39"/>
+      <c r="EL3" s="39"/>
+      <c r="EM3" s="39"/>
+      <c r="EN3" s="39"/>
+      <c r="EO3" s="39"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="43" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="50"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="40"/>
-      <c r="AE4" s="40"/>
-      <c r="AF4" s="40"/>
-      <c r="AG4" s="40"/>
-      <c r="AH4" s="40"/>
-      <c r="AI4" s="40"/>
-      <c r="AJ4" s="40"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="40"/>
-      <c r="AM4" s="40"/>
-      <c r="AN4" s="40"/>
-      <c r="AO4" s="40"/>
-      <c r="AP4" s="40"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="40"/>
-      <c r="AS4" s="40"/>
-      <c r="AT4" s="40"/>
-      <c r="AU4" s="40"/>
-      <c r="AV4" s="40"/>
-      <c r="AW4" s="40"/>
-      <c r="AX4" s="40"/>
-      <c r="AY4" s="40"/>
-      <c r="AZ4" s="40"/>
-      <c r="BA4" s="40"/>
-      <c r="BB4" s="40"/>
-      <c r="BC4" s="40"/>
-      <c r="BD4" s="40"/>
-      <c r="BE4" s="40"/>
-      <c r="BF4" s="40"/>
-      <c r="BG4" s="40"/>
-      <c r="BH4" s="40"/>
-      <c r="BI4" s="40"/>
-      <c r="BJ4" s="40"/>
-      <c r="BK4" s="40"/>
-      <c r="BL4" s="40"/>
-      <c r="BM4" s="40"/>
-      <c r="BN4" s="40"/>
-      <c r="BO4" s="40"/>
-      <c r="BP4" s="40"/>
-      <c r="BQ4" s="40"/>
-      <c r="BR4" s="40"/>
-      <c r="BS4" s="40"/>
-      <c r="BT4" s="40"/>
-      <c r="BU4" s="40"/>
-      <c r="BV4" s="40"/>
-      <c r="BW4" s="40"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="39"/>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="39"/>
+      <c r="AM4" s="39"/>
+      <c r="AN4" s="39"/>
+      <c r="AO4" s="39"/>
+      <c r="AP4" s="39"/>
+      <c r="AQ4" s="39"/>
+      <c r="AR4" s="39"/>
+      <c r="AS4" s="39"/>
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
+      <c r="AX4" s="39"/>
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
+      <c r="BA4" s="39"/>
+      <c r="BB4" s="39"/>
+      <c r="BC4" s="39"/>
+      <c r="BD4" s="39"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="39"/>
+      <c r="BG4" s="39"/>
+      <c r="BH4" s="39"/>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="39"/>
+      <c r="BL4" s="39"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="39"/>
+      <c r="BQ4" s="39"/>
+      <c r="BR4" s="39"/>
+      <c r="BS4" s="39"/>
+      <c r="BT4" s="39"/>
+      <c r="BU4" s="39"/>
+      <c r="BV4" s="39"/>
+      <c r="BW4" s="39"/>
       <c r="BX4" s="48"/>
-      <c r="BY4" s="40"/>
-      <c r="BZ4" s="40"/>
-      <c r="CA4" s="40"/>
-      <c r="CB4" s="40"/>
-      <c r="CC4" s="40"/>
-      <c r="CD4" s="40"/>
-      <c r="CE4" s="40"/>
-      <c r="CF4" s="40"/>
-      <c r="CG4" s="40"/>
-      <c r="CH4" s="40"/>
-      <c r="CI4" s="40"/>
-      <c r="CJ4" s="40"/>
-      <c r="CK4" s="40"/>
-      <c r="CL4" s="40"/>
-      <c r="CM4" s="40"/>
-      <c r="CN4" s="40"/>
-      <c r="CO4" s="40"/>
-      <c r="CP4" s="40"/>
-      <c r="CQ4" s="40"/>
-      <c r="CR4" s="40"/>
-      <c r="CS4" s="40"/>
-      <c r="CT4" s="40"/>
-      <c r="CU4" s="40"/>
-      <c r="CV4" s="40"/>
-      <c r="CW4" s="40"/>
-      <c r="CX4" s="40"/>
-      <c r="CY4" s="40"/>
-      <c r="CZ4" s="40"/>
-      <c r="DA4" s="40"/>
-      <c r="DB4" s="40"/>
-      <c r="DC4" s="40"/>
-      <c r="DD4" s="40"/>
-      <c r="DE4" s="40"/>
-      <c r="DF4" s="40"/>
-      <c r="DG4" s="40"/>
-      <c r="DH4" s="40"/>
-      <c r="DI4" s="40"/>
-      <c r="DJ4" s="40"/>
-      <c r="DK4" s="40"/>
-      <c r="DL4" s="40"/>
-      <c r="DM4" s="40"/>
-      <c r="DN4" s="40"/>
-      <c r="DO4" s="40"/>
-      <c r="DP4" s="40"/>
-      <c r="DQ4" s="40"/>
-      <c r="DR4" s="40"/>
-      <c r="DS4" s="40"/>
-      <c r="DT4" s="40"/>
-      <c r="DU4" s="40"/>
-      <c r="DV4" s="40"/>
-      <c r="DW4" s="40"/>
-      <c r="DX4" s="40"/>
-      <c r="DY4" s="40"/>
-      <c r="DZ4" s="40"/>
-      <c r="EA4" s="40"/>
-      <c r="EB4" s="40"/>
-      <c r="EC4" s="40"/>
-      <c r="ED4" s="40"/>
-      <c r="EE4" s="40"/>
-      <c r="EF4" s="40"/>
-      <c r="EG4" s="40"/>
-      <c r="EH4" s="40"/>
-      <c r="EI4" s="40"/>
-      <c r="EJ4" s="40"/>
-      <c r="EK4" s="40"/>
-      <c r="EL4" s="40"/>
-      <c r="EM4" s="40"/>
-      <c r="EN4" s="40"/>
-      <c r="EO4" s="40"/>
+      <c r="BY4" s="39"/>
+      <c r="BZ4" s="39"/>
+      <c r="CA4" s="39"/>
+      <c r="CB4" s="39"/>
+      <c r="CC4" s="39"/>
+      <c r="CD4" s="39"/>
+      <c r="CE4" s="39"/>
+      <c r="CF4" s="39"/>
+      <c r="CG4" s="39"/>
+      <c r="CH4" s="39"/>
+      <c r="CI4" s="39"/>
+      <c r="CJ4" s="39"/>
+      <c r="CK4" s="39"/>
+      <c r="CL4" s="39"/>
+      <c r="CM4" s="39"/>
+      <c r="CN4" s="39"/>
+      <c r="CO4" s="39"/>
+      <c r="CP4" s="39"/>
+      <c r="CQ4" s="39"/>
+      <c r="CR4" s="39"/>
+      <c r="CS4" s="39"/>
+      <c r="CT4" s="39"/>
+      <c r="CU4" s="39"/>
+      <c r="CV4" s="39"/>
+      <c r="CW4" s="39"/>
+      <c r="CX4" s="39"/>
+      <c r="CY4" s="39"/>
+      <c r="CZ4" s="39"/>
+      <c r="DA4" s="39"/>
+      <c r="DB4" s="39"/>
+      <c r="DC4" s="39"/>
+      <c r="DD4" s="39"/>
+      <c r="DE4" s="39"/>
+      <c r="DF4" s="39"/>
+      <c r="DG4" s="39"/>
+      <c r="DH4" s="39"/>
+      <c r="DI4" s="39"/>
+      <c r="DJ4" s="39"/>
+      <c r="DK4" s="39"/>
+      <c r="DL4" s="39"/>
+      <c r="DM4" s="39"/>
+      <c r="DN4" s="39"/>
+      <c r="DO4" s="39"/>
+      <c r="DP4" s="39"/>
+      <c r="DQ4" s="39"/>
+      <c r="DR4" s="39"/>
+      <c r="DS4" s="39"/>
+      <c r="DT4" s="39"/>
+      <c r="DU4" s="39"/>
+      <c r="DV4" s="39"/>
+      <c r="DW4" s="39"/>
+      <c r="DX4" s="39"/>
+      <c r="DY4" s="39"/>
+      <c r="DZ4" s="39"/>
+      <c r="EA4" s="39"/>
+      <c r="EB4" s="39"/>
+      <c r="EC4" s="39"/>
+      <c r="ED4" s="39"/>
+      <c r="EE4" s="39"/>
+      <c r="EF4" s="39"/>
+      <c r="EG4" s="39"/>
+      <c r="EH4" s="39"/>
+      <c r="EI4" s="39"/>
+      <c r="EJ4" s="39"/>
+      <c r="EK4" s="39"/>
+      <c r="EL4" s="39"/>
+      <c r="EM4" s="39"/>
+      <c r="EN4" s="39"/>
+      <c r="EO4" s="39"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45">
+      <c r="B5" s="53"/>
+      <c r="C5" s="54">
         <v>110</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="52"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="40"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="40"/>
-      <c r="AK5" s="40"/>
-      <c r="AL5" s="40"/>
-      <c r="AM5" s="40"/>
-      <c r="AN5" s="40"/>
-      <c r="AO5" s="40"/>
-      <c r="AP5" s="40"/>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="40"/>
-      <c r="AS5" s="40"/>
-      <c r="AT5" s="40"/>
-      <c r="AU5" s="40"/>
-      <c r="AV5" s="40"/>
-      <c r="AW5" s="40"/>
-      <c r="AX5" s="40"/>
-      <c r="AY5" s="40"/>
-      <c r="AZ5" s="40"/>
-      <c r="BA5" s="40"/>
-      <c r="BB5" s="40"/>
-      <c r="BC5" s="40"/>
-      <c r="BD5" s="40"/>
-      <c r="BE5" s="40"/>
-      <c r="BF5" s="40"/>
-      <c r="BG5" s="40"/>
-      <c r="BH5" s="40"/>
-      <c r="BI5" s="40"/>
-      <c r="BJ5" s="40"/>
-      <c r="BK5" s="40"/>
-      <c r="BL5" s="40"/>
-      <c r="BM5" s="40"/>
-      <c r="BN5" s="40"/>
-      <c r="BO5" s="40"/>
-      <c r="BP5" s="40"/>
-      <c r="BQ5" s="40"/>
-      <c r="BR5" s="40"/>
-      <c r="BS5" s="40"/>
-      <c r="BT5" s="40"/>
-      <c r="BU5" s="40"/>
-      <c r="BV5" s="40"/>
-      <c r="BW5" s="40"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="39"/>
+      <c r="AN5" s="39"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="39"/>
+      <c r="AQ5" s="39"/>
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="39"/>
+      <c r="AT5" s="39"/>
+      <c r="AU5" s="39"/>
+      <c r="AV5" s="39"/>
+      <c r="AW5" s="39"/>
+      <c r="AX5" s="39"/>
+      <c r="AY5" s="39"/>
+      <c r="AZ5" s="39"/>
+      <c r="BA5" s="39"/>
+      <c r="BB5" s="39"/>
+      <c r="BC5" s="39"/>
+      <c r="BD5" s="39"/>
+      <c r="BE5" s="39"/>
+      <c r="BF5" s="39"/>
+      <c r="BG5" s="39"/>
+      <c r="BH5" s="39"/>
+      <c r="BI5" s="39"/>
+      <c r="BJ5" s="39"/>
+      <c r="BK5" s="39"/>
+      <c r="BL5" s="39"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
+      <c r="BO5" s="39"/>
+      <c r="BP5" s="39"/>
+      <c r="BQ5" s="39"/>
+      <c r="BR5" s="39"/>
+      <c r="BS5" s="39"/>
+      <c r="BT5" s="39"/>
+      <c r="BU5" s="39"/>
+      <c r="BV5" s="39"/>
+      <c r="BW5" s="39"/>
       <c r="BX5" s="48"/>
-      <c r="BY5" s="40"/>
-      <c r="BZ5" s="40"/>
-      <c r="CA5" s="40"/>
-      <c r="CB5" s="40"/>
-      <c r="CC5" s="40"/>
-      <c r="CD5" s="40"/>
-      <c r="CE5" s="40"/>
-      <c r="CF5" s="40"/>
-      <c r="CG5" s="40"/>
-      <c r="CH5" s="40"/>
-      <c r="CI5" s="40"/>
-      <c r="CJ5" s="40"/>
-      <c r="CK5" s="40"/>
-      <c r="CL5" s="40"/>
-      <c r="CM5" s="40"/>
-      <c r="CN5" s="40"/>
-      <c r="CO5" s="40"/>
-      <c r="CP5" s="40"/>
-      <c r="CQ5" s="40"/>
-      <c r="CR5" s="40"/>
-      <c r="CS5" s="40"/>
-      <c r="CT5" s="40"/>
-      <c r="CU5" s="40"/>
-      <c r="CV5" s="40"/>
-      <c r="CW5" s="40"/>
-      <c r="CX5" s="40"/>
-      <c r="CY5" s="40"/>
-      <c r="CZ5" s="40"/>
-      <c r="DA5" s="40"/>
-      <c r="DB5" s="40"/>
-      <c r="DC5" s="40"/>
-      <c r="DD5" s="40"/>
-      <c r="DE5" s="40"/>
-      <c r="DF5" s="40"/>
-      <c r="DG5" s="40"/>
-      <c r="DH5" s="40"/>
-      <c r="DI5" s="40"/>
-      <c r="DJ5" s="40"/>
-      <c r="DK5" s="40"/>
-      <c r="DL5" s="40"/>
-      <c r="DM5" s="40"/>
-      <c r="DN5" s="40"/>
-      <c r="DO5" s="40"/>
-      <c r="DP5" s="40"/>
-      <c r="DQ5" s="40"/>
-      <c r="DR5" s="40"/>
-      <c r="DS5" s="40"/>
-      <c r="DT5" s="40"/>
-      <c r="DU5" s="40"/>
-      <c r="DV5" s="40"/>
-      <c r="DW5" s="40"/>
-      <c r="DX5" s="40"/>
-      <c r="DY5" s="40"/>
-      <c r="DZ5" s="40"/>
-      <c r="EA5" s="40"/>
-      <c r="EB5" s="40"/>
-      <c r="EC5" s="40"/>
-      <c r="ED5" s="40"/>
-      <c r="EE5" s="40"/>
-      <c r="EF5" s="40"/>
-      <c r="EG5" s="40"/>
-      <c r="EH5" s="40"/>
-      <c r="EI5" s="40"/>
-      <c r="EJ5" s="40"/>
-      <c r="EK5" s="40"/>
-      <c r="EL5" s="40"/>
-      <c r="EM5" s="40"/>
-      <c r="EN5" s="40"/>
-      <c r="EO5" s="40"/>
+      <c r="BY5" s="39"/>
+      <c r="BZ5" s="39"/>
+      <c r="CA5" s="39"/>
+      <c r="CB5" s="39"/>
+      <c r="CC5" s="39"/>
+      <c r="CD5" s="39"/>
+      <c r="CE5" s="39"/>
+      <c r="CF5" s="39"/>
+      <c r="CG5" s="39"/>
+      <c r="CH5" s="39"/>
+      <c r="CI5" s="39"/>
+      <c r="CJ5" s="39"/>
+      <c r="CK5" s="39"/>
+      <c r="CL5" s="39"/>
+      <c r="CM5" s="39"/>
+      <c r="CN5" s="39"/>
+      <c r="CO5" s="39"/>
+      <c r="CP5" s="39"/>
+      <c r="CQ5" s="39"/>
+      <c r="CR5" s="39"/>
+      <c r="CS5" s="39"/>
+      <c r="CT5" s="39"/>
+      <c r="CU5" s="39"/>
+      <c r="CV5" s="39"/>
+      <c r="CW5" s="39"/>
+      <c r="CX5" s="39"/>
+      <c r="CY5" s="39"/>
+      <c r="CZ5" s="39"/>
+      <c r="DA5" s="39"/>
+      <c r="DB5" s="39"/>
+      <c r="DC5" s="39"/>
+      <c r="DD5" s="39"/>
+      <c r="DE5" s="39"/>
+      <c r="DF5" s="39"/>
+      <c r="DG5" s="39"/>
+      <c r="DH5" s="39"/>
+      <c r="DI5" s="39"/>
+      <c r="DJ5" s="39"/>
+      <c r="DK5" s="39"/>
+      <c r="DL5" s="39"/>
+      <c r="DM5" s="39"/>
+      <c r="DN5" s="39"/>
+      <c r="DO5" s="39"/>
+      <c r="DP5" s="39"/>
+      <c r="DQ5" s="39"/>
+      <c r="DR5" s="39"/>
+      <c r="DS5" s="39"/>
+      <c r="DT5" s="39"/>
+      <c r="DU5" s="39"/>
+      <c r="DV5" s="39"/>
+      <c r="DW5" s="39"/>
+      <c r="DX5" s="39"/>
+      <c r="DY5" s="39"/>
+      <c r="DZ5" s="39"/>
+      <c r="EA5" s="39"/>
+      <c r="EB5" s="39"/>
+      <c r="EC5" s="39"/>
+      <c r="ED5" s="39"/>
+      <c r="EE5" s="39"/>
+      <c r="EF5" s="39"/>
+      <c r="EG5" s="39"/>
+      <c r="EH5" s="39"/>
+      <c r="EI5" s="39"/>
+      <c r="EJ5" s="39"/>
+      <c r="EK5" s="39"/>
+      <c r="EL5" s="39"/>
+      <c r="EM5" s="39"/>
+      <c r="EN5" s="39"/>
+      <c r="EO5" s="39"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45">
+      <c r="B6" s="53"/>
+      <c r="C6" s="54">
         <v>10</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="52"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="50"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="40"/>
-      <c r="AM6" s="40"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="40"/>
-      <c r="AP6" s="40"/>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="40"/>
-      <c r="AS6" s="40"/>
-      <c r="AT6" s="40"/>
-      <c r="AU6" s="40"/>
-      <c r="AV6" s="40"/>
-      <c r="AW6" s="40"/>
-      <c r="AX6" s="40"/>
-      <c r="AY6" s="40"/>
-      <c r="AZ6" s="40"/>
-      <c r="BA6" s="40"/>
-      <c r="BB6" s="40"/>
-      <c r="BC6" s="40"/>
-      <c r="BD6" s="40"/>
-      <c r="BE6" s="40"/>
-      <c r="BF6" s="40"/>
-      <c r="BG6" s="40"/>
-      <c r="BH6" s="40"/>
-      <c r="BI6" s="40"/>
-      <c r="BJ6" s="40"/>
-      <c r="BK6" s="40"/>
-      <c r="BL6" s="40"/>
-      <c r="BM6" s="40"/>
-      <c r="BN6" s="40"/>
-      <c r="BO6" s="40"/>
-      <c r="BP6" s="40"/>
-      <c r="BQ6" s="40"/>
-      <c r="BR6" s="40"/>
-      <c r="BS6" s="40"/>
-      <c r="BT6" s="40"/>
-      <c r="BU6" s="40"/>
-      <c r="BV6" s="40"/>
-      <c r="BW6" s="40"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="39"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="39"/>
+      <c r="AQ6" s="39"/>
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="39"/>
+      <c r="AU6" s="39"/>
+      <c r="AV6" s="39"/>
+      <c r="AW6" s="39"/>
+      <c r="AX6" s="39"/>
+      <c r="AY6" s="39"/>
+      <c r="AZ6" s="39"/>
+      <c r="BA6" s="39"/>
+      <c r="BB6" s="39"/>
+      <c r="BC6" s="39"/>
+      <c r="BD6" s="39"/>
+      <c r="BE6" s="39"/>
+      <c r="BF6" s="39"/>
+      <c r="BG6" s="39"/>
+      <c r="BH6" s="39"/>
+      <c r="BI6" s="39"/>
+      <c r="BJ6" s="39"/>
+      <c r="BK6" s="39"/>
+      <c r="BL6" s="39"/>
+      <c r="BM6" s="39"/>
+      <c r="BN6" s="39"/>
+      <c r="BO6" s="39"/>
+      <c r="BP6" s="39"/>
+      <c r="BQ6" s="39"/>
+      <c r="BR6" s="39"/>
+      <c r="BS6" s="39"/>
+      <c r="BT6" s="39"/>
+      <c r="BU6" s="39"/>
+      <c r="BV6" s="39"/>
+      <c r="BW6" s="39"/>
       <c r="BX6" s="48"/>
-      <c r="BY6" s="40"/>
-      <c r="BZ6" s="40"/>
-      <c r="CA6" s="40"/>
-      <c r="CB6" s="40"/>
-      <c r="CC6" s="40"/>
-      <c r="CD6" s="40"/>
-      <c r="CE6" s="40"/>
-      <c r="CF6" s="40"/>
-      <c r="CG6" s="40"/>
-      <c r="CH6" s="40"/>
-      <c r="CI6" s="40"/>
-      <c r="CJ6" s="40"/>
-      <c r="CK6" s="40"/>
-      <c r="CL6" s="40"/>
-      <c r="CM6" s="40"/>
-      <c r="CN6" s="40"/>
-      <c r="CO6" s="40"/>
-      <c r="CP6" s="40"/>
-      <c r="CQ6" s="40"/>
-      <c r="CR6" s="40"/>
-      <c r="CS6" s="40"/>
-      <c r="CT6" s="40"/>
-      <c r="CU6" s="40"/>
-      <c r="CV6" s="40"/>
-      <c r="CW6" s="40"/>
-      <c r="CX6" s="40"/>
-      <c r="CY6" s="40"/>
-      <c r="CZ6" s="40"/>
-      <c r="DA6" s="40"/>
-      <c r="DB6" s="40"/>
-      <c r="DC6" s="40"/>
-      <c r="DD6" s="40"/>
-      <c r="DE6" s="40"/>
-      <c r="DF6" s="40"/>
-      <c r="DG6" s="40"/>
-      <c r="DH6" s="40"/>
-      <c r="DI6" s="40"/>
-      <c r="DJ6" s="40"/>
-      <c r="DK6" s="40"/>
-      <c r="DL6" s="40"/>
-      <c r="DM6" s="40"/>
-      <c r="DN6" s="40"/>
-      <c r="DO6" s="40"/>
-      <c r="DP6" s="40"/>
-      <c r="DQ6" s="40"/>
-      <c r="DR6" s="40"/>
-      <c r="DS6" s="40"/>
-      <c r="DT6" s="40"/>
-      <c r="DU6" s="40"/>
-      <c r="DV6" s="40"/>
-      <c r="DW6" s="40"/>
-      <c r="DX6" s="40"/>
-      <c r="DY6" s="40"/>
-      <c r="DZ6" s="40"/>
-      <c r="EA6" s="40"/>
-      <c r="EB6" s="40"/>
-      <c r="EC6" s="40"/>
-      <c r="ED6" s="40"/>
-      <c r="EE6" s="40"/>
-      <c r="EF6" s="40"/>
-      <c r="EG6" s="40"/>
-      <c r="EH6" s="40"/>
-      <c r="EI6" s="40"/>
-      <c r="EJ6" s="40"/>
-      <c r="EK6" s="40"/>
-      <c r="EL6" s="40"/>
-      <c r="EM6" s="40"/>
-      <c r="EN6" s="40"/>
-      <c r="EO6" s="40"/>
+      <c r="BY6" s="39"/>
+      <c r="BZ6" s="39"/>
+      <c r="CA6" s="39"/>
+      <c r="CB6" s="39"/>
+      <c r="CC6" s="39"/>
+      <c r="CD6" s="39"/>
+      <c r="CE6" s="39"/>
+      <c r="CF6" s="39"/>
+      <c r="CG6" s="39"/>
+      <c r="CH6" s="39"/>
+      <c r="CI6" s="39"/>
+      <c r="CJ6" s="39"/>
+      <c r="CK6" s="39"/>
+      <c r="CL6" s="39"/>
+      <c r="CM6" s="39"/>
+      <c r="CN6" s="39"/>
+      <c r="CO6" s="39"/>
+      <c r="CP6" s="39"/>
+      <c r="CQ6" s="39"/>
+      <c r="CR6" s="39"/>
+      <c r="CS6" s="39"/>
+      <c r="CT6" s="39"/>
+      <c r="CU6" s="39"/>
+      <c r="CV6" s="39"/>
+      <c r="CW6" s="39"/>
+      <c r="CX6" s="39"/>
+      <c r="CY6" s="39"/>
+      <c r="CZ6" s="39"/>
+      <c r="DA6" s="39"/>
+      <c r="DB6" s="39"/>
+      <c r="DC6" s="39"/>
+      <c r="DD6" s="39"/>
+      <c r="DE6" s="39"/>
+      <c r="DF6" s="39"/>
+      <c r="DG6" s="39"/>
+      <c r="DH6" s="39"/>
+      <c r="DI6" s="39"/>
+      <c r="DJ6" s="39"/>
+      <c r="DK6" s="39"/>
+      <c r="DL6" s="39"/>
+      <c r="DM6" s="39"/>
+      <c r="DN6" s="39"/>
+      <c r="DO6" s="39"/>
+      <c r="DP6" s="39"/>
+      <c r="DQ6" s="39"/>
+      <c r="DR6" s="39"/>
+      <c r="DS6" s="39"/>
+      <c r="DT6" s="39"/>
+      <c r="DU6" s="39"/>
+      <c r="DV6" s="39"/>
+      <c r="DW6" s="39"/>
+      <c r="DX6" s="39"/>
+      <c r="DY6" s="39"/>
+      <c r="DZ6" s="39"/>
+      <c r="EA6" s="39"/>
+      <c r="EB6" s="39"/>
+      <c r="EC6" s="39"/>
+      <c r="ED6" s="39"/>
+      <c r="EE6" s="39"/>
+      <c r="EF6" s="39"/>
+      <c r="EG6" s="39"/>
+      <c r="EH6" s="39"/>
+      <c r="EI6" s="39"/>
+      <c r="EJ6" s="39"/>
+      <c r="EK6" s="39"/>
+      <c r="EL6" s="39"/>
+      <c r="EM6" s="39"/>
+      <c r="EN6" s="39"/>
+      <c r="EO6" s="39"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="45">
+      <c r="B7" s="56"/>
+      <c r="C7" s="54">
         <v>30</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-      <c r="AK7" s="41"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="41"/>
-      <c r="AN7" s="41"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="41"/>
-      <c r="AQ7" s="41"/>
-      <c r="AR7" s="41"/>
-      <c r="AS7" s="41"/>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="41"/>
-      <c r="AV7" s="41"/>
-      <c r="AW7" s="41"/>
-      <c r="AX7" s="41"/>
-      <c r="AY7" s="41"/>
-      <c r="AZ7" s="41"/>
-      <c r="BA7" s="41"/>
-      <c r="BB7" s="41"/>
-      <c r="BC7" s="41"/>
-      <c r="BD7" s="41"/>
-      <c r="BE7" s="41"/>
-      <c r="BF7" s="41"/>
-      <c r="BG7" s="41"/>
-      <c r="BH7" s="41"/>
-      <c r="BI7" s="41"/>
-      <c r="BJ7" s="41"/>
-      <c r="BK7" s="41"/>
-      <c r="BL7" s="41"/>
-      <c r="BM7" s="41"/>
-      <c r="BN7" s="41"/>
-      <c r="BO7" s="41"/>
-      <c r="BP7" s="41"/>
-      <c r="BQ7" s="41"/>
-      <c r="BR7" s="41"/>
-      <c r="BS7" s="41"/>
-      <c r="BT7" s="41"/>
-      <c r="BU7" s="41"/>
-      <c r="BV7" s="41"/>
-      <c r="BW7" s="41"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="47"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
+      <c r="BA7" s="40"/>
+      <c r="BB7" s="40"/>
+      <c r="BC7" s="40"/>
+      <c r="BD7" s="40"/>
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="40"/>
+      <c r="BJ7" s="40"/>
+      <c r="BK7" s="40"/>
+      <c r="BL7" s="40"/>
+      <c r="BM7" s="40"/>
+      <c r="BN7" s="40"/>
+      <c r="BO7" s="40"/>
+      <c r="BP7" s="40"/>
+      <c r="BQ7" s="40"/>
+      <c r="BR7" s="40"/>
+      <c r="BS7" s="40"/>
+      <c r="BT7" s="40"/>
+      <c r="BU7" s="40"/>
+      <c r="BV7" s="40"/>
+      <c r="BW7" s="40"/>
       <c r="BX7" s="49"/>
-      <c r="BY7" s="41"/>
-      <c r="BZ7" s="41"/>
-      <c r="CA7" s="41"/>
-      <c r="CB7" s="41"/>
-      <c r="CC7" s="41"/>
-      <c r="CD7" s="41"/>
-      <c r="CE7" s="41"/>
-      <c r="CF7" s="41"/>
-      <c r="CG7" s="41"/>
-      <c r="CH7" s="41"/>
-      <c r="CI7" s="41"/>
-      <c r="CJ7" s="41"/>
-      <c r="CK7" s="41"/>
-      <c r="CL7" s="41"/>
-      <c r="CM7" s="41"/>
-      <c r="CN7" s="41"/>
-      <c r="CO7" s="41"/>
-      <c r="CP7" s="41"/>
-      <c r="CQ7" s="41"/>
-      <c r="CR7" s="41"/>
-      <c r="CS7" s="41"/>
-      <c r="CT7" s="41"/>
-      <c r="CU7" s="41"/>
-      <c r="CV7" s="41"/>
-      <c r="CW7" s="41"/>
-      <c r="CX7" s="41"/>
-      <c r="CY7" s="41"/>
-      <c r="CZ7" s="41"/>
-      <c r="DA7" s="41"/>
-      <c r="DB7" s="41"/>
-      <c r="DC7" s="41"/>
-      <c r="DD7" s="41"/>
-      <c r="DE7" s="41"/>
-      <c r="DF7" s="41"/>
-      <c r="DG7" s="41"/>
-      <c r="DH7" s="41"/>
-      <c r="DI7" s="41"/>
-      <c r="DJ7" s="41"/>
-      <c r="DK7" s="41"/>
-      <c r="DL7" s="41"/>
-      <c r="DM7" s="41"/>
-      <c r="DN7" s="41"/>
-      <c r="DO7" s="41"/>
-      <c r="DP7" s="41"/>
-      <c r="DQ7" s="41"/>
-      <c r="DR7" s="41"/>
-      <c r="DS7" s="41"/>
-      <c r="DT7" s="41"/>
-      <c r="DU7" s="41"/>
-      <c r="DV7" s="41"/>
-      <c r="DW7" s="41"/>
-      <c r="DX7" s="41"/>
-      <c r="DY7" s="41"/>
-      <c r="DZ7" s="41"/>
-      <c r="EA7" s="41"/>
-      <c r="EB7" s="41"/>
-      <c r="EC7" s="41"/>
-      <c r="ED7" s="41"/>
-      <c r="EE7" s="41"/>
-      <c r="EF7" s="41"/>
-      <c r="EG7" s="41"/>
-      <c r="EH7" s="41"/>
-      <c r="EI7" s="41"/>
-      <c r="EJ7" s="41"/>
-      <c r="EK7" s="41"/>
-      <c r="EL7" s="41"/>
-      <c r="EM7" s="41"/>
-      <c r="EN7" s="41"/>
-      <c r="EO7" s="41"/>
+      <c r="BY7" s="40"/>
+      <c r="BZ7" s="40"/>
+      <c r="CA7" s="40"/>
+      <c r="CB7" s="40"/>
+      <c r="CC7" s="40"/>
+      <c r="CD7" s="40"/>
+      <c r="CE7" s="40"/>
+      <c r="CF7" s="40"/>
+      <c r="CG7" s="40"/>
+      <c r="CH7" s="40"/>
+      <c r="CI7" s="40"/>
+      <c r="CJ7" s="40"/>
+      <c r="CK7" s="40"/>
+      <c r="CL7" s="40"/>
+      <c r="CM7" s="40"/>
+      <c r="CN7" s="40"/>
+      <c r="CO7" s="40"/>
+      <c r="CP7" s="40"/>
+      <c r="CQ7" s="40"/>
+      <c r="CR7" s="40"/>
+      <c r="CS7" s="40"/>
+      <c r="CT7" s="40"/>
+      <c r="CU7" s="40"/>
+      <c r="CV7" s="40"/>
+      <c r="CW7" s="40"/>
+      <c r="CX7" s="40"/>
+      <c r="CY7" s="40"/>
+      <c r="CZ7" s="40"/>
+      <c r="DA7" s="40"/>
+      <c r="DB7" s="40"/>
+      <c r="DC7" s="40"/>
+      <c r="DD7" s="40"/>
+      <c r="DE7" s="40"/>
+      <c r="DF7" s="40"/>
+      <c r="DG7" s="40"/>
+      <c r="DH7" s="40"/>
+      <c r="DI7" s="40"/>
+      <c r="DJ7" s="40"/>
+      <c r="DK7" s="40"/>
+      <c r="DL7" s="40"/>
+      <c r="DM7" s="40"/>
+      <c r="DN7" s="40"/>
+      <c r="DO7" s="40"/>
+      <c r="DP7" s="40"/>
+      <c r="DQ7" s="40"/>
+      <c r="DR7" s="40"/>
+      <c r="DS7" s="40"/>
+      <c r="DT7" s="40"/>
+      <c r="DU7" s="40"/>
+      <c r="DV7" s="40"/>
+      <c r="DW7" s="40"/>
+      <c r="DX7" s="40"/>
+      <c r="DY7" s="40"/>
+      <c r="DZ7" s="40"/>
+      <c r="EA7" s="40"/>
+      <c r="EB7" s="40"/>
+      <c r="EC7" s="40"/>
+      <c r="ED7" s="40"/>
+      <c r="EE7" s="40"/>
+      <c r="EF7" s="40"/>
+      <c r="EG7" s="40"/>
+      <c r="EH7" s="40"/>
+      <c r="EI7" s="40"/>
+      <c r="EJ7" s="40"/>
+      <c r="EK7" s="40"/>
+      <c r="EL7" s="40"/>
+      <c r="EM7" s="40"/>
+      <c r="EN7" s="40"/>
+      <c r="EO7" s="40"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35">
+      <c r="B8" s="57"/>
+      <c r="C8" s="58">
         <v>150</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="28">
+      <c r="F8" s="59">
         <v>1</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="59">
         <v>2</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="59">
         <v>3</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="59">
         <v>4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="59">
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="59">
         <v>6</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="59">
         <v>7</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="59">
         <v>8</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="59">
         <v>9</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="59">
         <v>10</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="59">
         <v>11</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="59">
         <v>12</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="59">
         <v>13</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="59">
         <v>14</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="59">
         <v>15</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="59">
         <v>16</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="59">
         <v>17</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="59">
         <v>18</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="59">
         <v>19</v>
       </c>
-      <c r="Y8" s="28">
+      <c r="Y8" s="59">
         <v>20</v>
       </c>
-      <c r="Z8" s="28">
+      <c r="Z8" s="59">
         <v>21</v>
       </c>
-      <c r="AA8" s="28">
+      <c r="AA8" s="59">
         <v>22</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AB8" s="59">
         <v>23</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="59">
         <v>24</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AD8" s="59">
         <v>25</v>
       </c>
-      <c r="AE8" s="28">
+      <c r="AE8" s="59">
         <v>26</v>
       </c>
-      <c r="AF8" s="28">
+      <c r="AF8" s="59">
         <v>27</v>
       </c>
-      <c r="AG8" s="28">
+      <c r="AG8" s="59">
         <v>28</v>
       </c>
-      <c r="AH8" s="28">
+      <c r="AH8" s="59">
         <v>29</v>
       </c>
-      <c r="AI8" s="28">
+      <c r="AI8" s="59">
         <v>30</v>
       </c>
-      <c r="AJ8" s="28">
+      <c r="AJ8" s="59">
         <v>31</v>
       </c>
-      <c r="AK8" s="28">
+      <c r="AK8" s="59">
         <v>32</v>
       </c>
-      <c r="AL8" s="28">
+      <c r="AL8" s="59">
         <v>33</v>
       </c>
-      <c r="AM8" s="28">
+      <c r="AM8" s="59">
         <v>34</v>
       </c>
-      <c r="AN8" s="28">
+      <c r="AN8" s="59">
         <v>35</v>
       </c>
-      <c r="AO8" s="28">
+      <c r="AO8" s="59">
         <v>36</v>
       </c>
-      <c r="AP8" s="28">
+      <c r="AP8" s="59">
         <v>37</v>
       </c>
-      <c r="AQ8" s="28">
+      <c r="AQ8" s="59">
         <v>38</v>
       </c>
-      <c r="AR8" s="28">
+      <c r="AR8" s="59">
         <v>39</v>
       </c>
-      <c r="AS8" s="28">
+      <c r="AS8" s="59">
         <v>40</v>
       </c>
-      <c r="AT8" s="28">
+      <c r="AT8" s="59">
         <v>41</v>
       </c>
-      <c r="AU8" s="28">
+      <c r="AU8" s="59">
         <v>42</v>
       </c>
-      <c r="AV8" s="28">
+      <c r="AV8" s="59">
         <v>43</v>
       </c>
-      <c r="AW8" s="28">
+      <c r="AW8" s="59">
         <v>44</v>
       </c>
-      <c r="AX8" s="28">
+      <c r="AX8" s="59">
         <v>45</v>
       </c>
-      <c r="AY8" s="28">
+      <c r="AY8" s="59">
         <v>46</v>
       </c>
-      <c r="AZ8" s="28">
+      <c r="AZ8" s="59">
         <v>47</v>
       </c>
-      <c r="BA8" s="28">
+      <c r="BA8" s="59">
         <v>48</v>
       </c>
-      <c r="BB8" s="28">
+      <c r="BB8" s="59">
         <v>49</v>
       </c>
-      <c r="BC8" s="28">
+      <c r="BC8" s="59">
         <v>50</v>
       </c>
-      <c r="BD8" s="28">
+      <c r="BD8" s="59">
         <v>51</v>
       </c>
-      <c r="BE8" s="28">
+      <c r="BE8" s="59">
         <v>52</v>
       </c>
-      <c r="BF8" s="28">
+      <c r="BF8" s="59">
         <v>53</v>
       </c>
-      <c r="BG8" s="28">
+      <c r="BG8" s="59">
         <v>54</v>
       </c>
-      <c r="BH8" s="28">
+      <c r="BH8" s="59">
         <v>55</v>
       </c>
-      <c r="BI8" s="28">
+      <c r="BI8" s="59">
         <v>56</v>
       </c>
-      <c r="BJ8" s="28">
+      <c r="BJ8" s="59">
         <v>57</v>
       </c>
-      <c r="BK8" s="28">
+      <c r="BK8" s="59">
         <v>58</v>
       </c>
-      <c r="BL8" s="28">
+      <c r="BL8" s="59">
         <v>59</v>
       </c>
-      <c r="BM8" s="28">
+      <c r="BM8" s="59">
         <v>60</v>
       </c>
-      <c r="BN8" s="28">
+      <c r="BN8" s="59">
         <v>61</v>
       </c>
-      <c r="BO8" s="28">
+      <c r="BO8" s="59">
         <v>62</v>
       </c>
-      <c r="BP8" s="28">
+      <c r="BP8" s="59">
         <v>63</v>
       </c>
-      <c r="BQ8" s="28">
+      <c r="BQ8" s="59">
         <v>64</v>
       </c>
-      <c r="BR8" s="28">
+      <c r="BR8" s="59">
         <v>65</v>
       </c>
-      <c r="BS8" s="28">
+      <c r="BS8" s="59">
         <v>66</v>
       </c>
-      <c r="BT8" s="28">
+      <c r="BT8" s="59">
         <v>67</v>
       </c>
-      <c r="BU8" s="28">
+      <c r="BU8" s="59">
         <v>68</v>
       </c>
-      <c r="BV8" s="28">
+      <c r="BV8" s="59">
         <v>69</v>
       </c>
-      <c r="BW8" s="28">
+      <c r="BW8" s="59">
         <v>70</v>
       </c>
-      <c r="BX8" s="28">
+      <c r="BX8" s="59">
         <v>71</v>
       </c>
-      <c r="BY8" s="28">
+      <c r="BY8" s="59">
         <v>72</v>
       </c>
-      <c r="BZ8" s="28">
+      <c r="BZ8" s="59">
         <v>73</v>
       </c>
-      <c r="CA8" s="28">
+      <c r="CA8" s="59">
         <v>74</v>
       </c>
-      <c r="CB8" s="28">
+      <c r="CB8" s="59">
         <v>75</v>
       </c>
-      <c r="CC8" s="28">
+      <c r="CC8" s="59">
         <v>76</v>
       </c>
-      <c r="CD8" s="28">
+      <c r="CD8" s="59">
         <v>77</v>
       </c>
-      <c r="CE8" s="28">
+      <c r="CE8" s="59">
         <v>78</v>
       </c>
-      <c r="CF8" s="28">
+      <c r="CF8" s="59">
         <v>79</v>
       </c>
-      <c r="CG8" s="28">
+      <c r="CG8" s="59">
         <v>80</v>
       </c>
-      <c r="CH8" s="28">
+      <c r="CH8" s="59">
         <v>81</v>
       </c>
-      <c r="CI8" s="28">
+      <c r="CI8" s="59">
         <v>82</v>
       </c>
-      <c r="CJ8" s="28">
+      <c r="CJ8" s="59">
         <v>83</v>
       </c>
-      <c r="CK8" s="28">
+      <c r="CK8" s="59">
         <v>84</v>
       </c>
-      <c r="CL8" s="28">
+      <c r="CL8" s="59">
         <v>85</v>
       </c>
-      <c r="CM8" s="28">
+      <c r="CM8" s="59">
         <v>86</v>
       </c>
-      <c r="CN8" s="28">
+      <c r="CN8" s="59">
         <v>87</v>
       </c>
-      <c r="CO8" s="28">
+      <c r="CO8" s="59">
         <v>88</v>
       </c>
-      <c r="CP8" s="28">
+      <c r="CP8" s="59">
         <v>89</v>
       </c>
-      <c r="CQ8" s="28">
+      <c r="CQ8" s="59">
         <v>90</v>
       </c>
-      <c r="CR8" s="28">
+      <c r="CR8" s="59">
         <v>91</v>
       </c>
-      <c r="CS8" s="28">
+      <c r="CS8" s="59">
         <v>92</v>
       </c>
-      <c r="CT8" s="28">
+      <c r="CT8" s="59">
         <v>93</v>
       </c>
-      <c r="CU8" s="28">
+      <c r="CU8" s="59">
         <v>94</v>
       </c>
-      <c r="CV8" s="28">
+      <c r="CV8" s="59">
         <v>95</v>
       </c>
-      <c r="CW8" s="28">
+      <c r="CW8" s="59">
         <v>96</v>
       </c>
-      <c r="CX8" s="28">
+      <c r="CX8" s="59">
         <v>97</v>
       </c>
-      <c r="CY8" s="28">
+      <c r="CY8" s="59">
         <v>98</v>
       </c>
-      <c r="CZ8" s="28">
+      <c r="CZ8" s="59">
         <v>99</v>
       </c>
-      <c r="DA8" s="28">
+      <c r="DA8" s="59">
         <v>100</v>
       </c>
-      <c r="DB8" s="28">
+      <c r="DB8" s="59">
         <v>101</v>
       </c>
-      <c r="DC8" s="28">
+      <c r="DC8" s="59">
         <v>102</v>
       </c>
-      <c r="DD8" s="28">
+      <c r="DD8" s="59">
         <v>103</v>
       </c>
-      <c r="DE8" s="28">
+      <c r="DE8" s="59">
         <v>104</v>
       </c>
-      <c r="DF8" s="28">
+      <c r="DF8" s="59">
         <v>105</v>
       </c>
-      <c r="DG8" s="28">
+      <c r="DG8" s="59">
         <v>106</v>
       </c>
-      <c r="DH8" s="28">
+      <c r="DH8" s="59">
         <v>107</v>
       </c>
-      <c r="DI8" s="28">
+      <c r="DI8" s="59">
         <v>108</v>
       </c>
-      <c r="DJ8" s="28">
+      <c r="DJ8" s="59">
         <v>109</v>
       </c>
-      <c r="DK8" s="28">
+      <c r="DK8" s="59">
         <v>110</v>
       </c>
-      <c r="DL8" s="28">
+      <c r="DL8" s="59">
         <v>111</v>
       </c>
-      <c r="DM8" s="28">
+      <c r="DM8" s="59">
         <v>112</v>
       </c>
-      <c r="DN8" s="28">
+      <c r="DN8" s="59">
         <v>113</v>
       </c>
-      <c r="DO8" s="28">
+      <c r="DO8" s="59">
         <v>114</v>
       </c>
-      <c r="DP8" s="28">
+      <c r="DP8" s="59">
         <v>115</v>
       </c>
-      <c r="DQ8" s="28">
+      <c r="DQ8" s="59">
         <v>116</v>
       </c>
-      <c r="DR8" s="28">
+      <c r="DR8" s="59">
         <v>117</v>
       </c>
-      <c r="DS8" s="28">
+      <c r="DS8" s="59">
         <v>118</v>
       </c>
-      <c r="DT8" s="28">
+      <c r="DT8" s="59">
         <v>119</v>
       </c>
-      <c r="DU8" s="28">
+      <c r="DU8" s="59">
         <v>120</v>
       </c>
-      <c r="DV8" s="28">
+      <c r="DV8" s="59">
         <v>121</v>
       </c>
-      <c r="DW8" s="28">
+      <c r="DW8" s="59">
         <v>122</v>
       </c>
-      <c r="DX8" s="28">
+      <c r="DX8" s="59">
         <v>123</v>
       </c>
-      <c r="DY8" s="28">
+      <c r="DY8" s="59">
         <v>124</v>
       </c>
-      <c r="DZ8" s="28">
+      <c r="DZ8" s="59">
         <v>125</v>
       </c>
-      <c r="EA8" s="28">
+      <c r="EA8" s="59">
         <v>126</v>
       </c>
-      <c r="EB8" s="28">
+      <c r="EB8" s="59">
         <v>127</v>
       </c>
-      <c r="EC8" s="28">
+      <c r="EC8" s="59">
         <v>128</v>
       </c>
-      <c r="ED8" s="28">
+      <c r="ED8" s="59">
         <v>129</v>
       </c>
-      <c r="EE8" s="28">
+      <c r="EE8" s="59">
         <v>130</v>
       </c>
-      <c r="EF8" s="28">
+      <c r="EF8" s="59">
         <v>131</v>
       </c>
-      <c r="EG8" s="28">
+      <c r="EG8" s="59">
         <v>132</v>
       </c>
-      <c r="EH8" s="28">
+      <c r="EH8" s="59">
         <v>133</v>
       </c>
-      <c r="EI8" s="28">
+      <c r="EI8" s="59">
         <v>134</v>
       </c>
-      <c r="EJ8" s="28">
+      <c r="EJ8" s="59">
         <v>135</v>
       </c>
-      <c r="EK8" s="28">
+      <c r="EK8" s="59">
         <v>136</v>
       </c>
-      <c r="EL8" s="28">
+      <c r="EL8" s="59">
         <v>137</v>
       </c>
-      <c r="EM8" s="28">
+      <c r="EM8" s="59">
         <v>138</v>
       </c>
-      <c r="EN8" s="28">
+      <c r="EN8" s="59">
         <v>139</v>
       </c>
-      <c r="EO8" s="28">
+      <c r="EO8" s="59">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="38"/>
+      <c r="D9" s="62"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="29"/>
-      <c r="AX9" s="29"/>
-      <c r="AY9" s="29"/>
-      <c r="AZ9" s="29"/>
-      <c r="BA9" s="29"/>
-      <c r="BB9" s="29"/>
-      <c r="BC9" s="29"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="29"/>
-      <c r="BG9" s="29"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="29"/>
-      <c r="BJ9" s="29"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="29"/>
-      <c r="BM9" s="29"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="29"/>
-      <c r="BT9" s="29"/>
-      <c r="BU9" s="29"/>
-      <c r="BV9" s="29"/>
-      <c r="BW9" s="29"/>
-      <c r="BX9" s="29"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="29"/>
-      <c r="CC9" s="29"/>
-      <c r="CD9" s="29"/>
-      <c r="CE9" s="29"/>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
-      <c r="CI9" s="29"/>
-      <c r="CJ9" s="29"/>
-      <c r="CK9" s="29"/>
-      <c r="CL9" s="29"/>
-      <c r="CM9" s="29"/>
-      <c r="CN9" s="29"/>
-      <c r="CO9" s="29"/>
-      <c r="CP9" s="29"/>
-      <c r="CQ9" s="29"/>
-      <c r="CR9" s="29"/>
-      <c r="CS9" s="29"/>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="29"/>
-      <c r="CV9" s="29"/>
-      <c r="CW9" s="29"/>
-      <c r="CX9" s="29"/>
-      <c r="CY9" s="29"/>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29"/>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29"/>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29"/>
-      <c r="DF9" s="29"/>
-      <c r="DG9" s="29"/>
-      <c r="DH9" s="29"/>
-      <c r="DI9" s="29"/>
-      <c r="DJ9" s="29"/>
-      <c r="DK9" s="29"/>
-      <c r="DL9" s="29"/>
-      <c r="DM9" s="29"/>
-      <c r="DN9" s="29"/>
-      <c r="DO9" s="29"/>
-      <c r="DP9" s="29"/>
-      <c r="DQ9" s="29"/>
-      <c r="DR9" s="29"/>
-      <c r="DS9" s="29"/>
-      <c r="DT9" s="29"/>
-      <c r="DU9" s="29"/>
-      <c r="DV9" s="29"/>
-      <c r="DW9" s="29"/>
-      <c r="DX9" s="29"/>
-      <c r="DY9" s="29"/>
-      <c r="DZ9" s="29"/>
-      <c r="EA9" s="29"/>
-      <c r="EB9" s="29"/>
-      <c r="EC9" s="29"/>
-      <c r="ED9" s="29"/>
-      <c r="EE9" s="29"/>
-      <c r="EF9" s="29"/>
-      <c r="EG9" s="29"/>
-      <c r="EH9" s="29"/>
-      <c r="EI9" s="29"/>
-      <c r="EJ9" s="29"/>
-      <c r="EK9" s="29"/>
-      <c r="EL9" s="29"/>
-      <c r="EM9" s="29"/>
-      <c r="EN9" s="29"/>
-      <c r="EO9" s="29"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="60"/>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="60"/>
+      <c r="AE9" s="60"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+      <c r="BC9" s="60"/>
+      <c r="BD9" s="60"/>
+      <c r="BE9" s="60"/>
+      <c r="BF9" s="60"/>
+      <c r="BG9" s="60"/>
+      <c r="BH9" s="60"/>
+      <c r="BI9" s="60"/>
+      <c r="BJ9" s="60"/>
+      <c r="BK9" s="60"/>
+      <c r="BL9" s="60"/>
+      <c r="BM9" s="60"/>
+      <c r="BN9" s="60"/>
+      <c r="BO9" s="60"/>
+      <c r="BP9" s="60"/>
+      <c r="BQ9" s="60"/>
+      <c r="BR9" s="60"/>
+      <c r="BS9" s="60"/>
+      <c r="BT9" s="60"/>
+      <c r="BU9" s="60"/>
+      <c r="BV9" s="60"/>
+      <c r="BW9" s="60"/>
+      <c r="BX9" s="60"/>
+      <c r="BY9" s="60"/>
+      <c r="BZ9" s="60"/>
+      <c r="CA9" s="60"/>
+      <c r="CB9" s="60"/>
+      <c r="CC9" s="60"/>
+      <c r="CD9" s="60"/>
+      <c r="CE9" s="60"/>
+      <c r="CF9" s="60"/>
+      <c r="CG9" s="60"/>
+      <c r="CH9" s="60"/>
+      <c r="CI9" s="60"/>
+      <c r="CJ9" s="60"/>
+      <c r="CK9" s="60"/>
+      <c r="CL9" s="60"/>
+      <c r="CM9" s="60"/>
+      <c r="CN9" s="60"/>
+      <c r="CO9" s="60"/>
+      <c r="CP9" s="60"/>
+      <c r="CQ9" s="60"/>
+      <c r="CR9" s="60"/>
+      <c r="CS9" s="60"/>
+      <c r="CT9" s="60"/>
+      <c r="CU9" s="60"/>
+      <c r="CV9" s="60"/>
+      <c r="CW9" s="60"/>
+      <c r="CX9" s="60"/>
+      <c r="CY9" s="60"/>
+      <c r="CZ9" s="60"/>
+      <c r="DA9" s="60"/>
+      <c r="DB9" s="60"/>
+      <c r="DC9" s="60"/>
+      <c r="DD9" s="60"/>
+      <c r="DE9" s="60"/>
+      <c r="DF9" s="60"/>
+      <c r="DG9" s="60"/>
+      <c r="DH9" s="60"/>
+      <c r="DI9" s="60"/>
+      <c r="DJ9" s="60"/>
+      <c r="DK9" s="60"/>
+      <c r="DL9" s="60"/>
+      <c r="DM9" s="60"/>
+      <c r="DN9" s="60"/>
+      <c r="DO9" s="60"/>
+      <c r="DP9" s="60"/>
+      <c r="DQ9" s="60"/>
+      <c r="DR9" s="60"/>
+      <c r="DS9" s="60"/>
+      <c r="DT9" s="60"/>
+      <c r="DU9" s="60"/>
+      <c r="DV9" s="60"/>
+      <c r="DW9" s="60"/>
+      <c r="DX9" s="60"/>
+      <c r="DY9" s="60"/>
+      <c r="DZ9" s="60"/>
+      <c r="EA9" s="60"/>
+      <c r="EB9" s="60"/>
+      <c r="EC9" s="60"/>
+      <c r="ED9" s="60"/>
+      <c r="EE9" s="60"/>
+      <c r="EF9" s="60"/>
+      <c r="EG9" s="60"/>
+      <c r="EH9" s="60"/>
+      <c r="EI9" s="60"/>
+      <c r="EJ9" s="60"/>
+      <c r="EK9" s="60"/>
+      <c r="EL9" s="60"/>
+      <c r="EM9" s="60"/>
+      <c r="EN9" s="60"/>
+      <c r="EO9" s="60"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
       <c r="C10" s="9"/>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -3093,14 +3093,30 @@
       <c r="BP10" s="11">
         <v>0</v>
       </c>
-      <c r="BQ10" s="11"/>
-      <c r="BR10" s="11"/>
-      <c r="BS10" s="11"/>
-      <c r="BT10" s="11"/>
-      <c r="BU10" s="11"/>
-      <c r="BV10" s="11"/>
-      <c r="BW10" s="11"/>
-      <c r="BX10" s="11"/>
+      <c r="BQ10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX10" s="11">
+        <v>0</v>
+      </c>
       <c r="BY10" s="11"/>
       <c r="BZ10" s="11"/>
       <c r="CA10" s="11"/>
@@ -3338,8 +3354,8 @@
         <v>24</v>
       </c>
       <c r="D12" s="14">
-        <f t="shared" ref="D11:D28" si="0">COUNT(F12:EO12)</f>
-        <v>14</v>
+        <f t="shared" ref="D12:D28" si="0">COUNT(F12:EO12)</f>
+        <v>17</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="11"/>
@@ -3438,9 +3454,15 @@
       <c r="BS12" s="11"/>
       <c r="BT12" s="11"/>
       <c r="BU12" s="11"/>
-      <c r="BV12" s="11"/>
-      <c r="BW12" s="11"/>
-      <c r="BX12" s="11"/>
+      <c r="BV12" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX12" s="11">
+        <v>0</v>
+      </c>
       <c r="BY12" s="11"/>
       <c r="BZ12" s="11"/>
       <c r="CA12" s="11"/>
@@ -3523,7 +3545,7 @@
       </c>
       <c r="D13" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="11"/>
@@ -3633,14 +3655,30 @@
       <c r="BP13" s="11">
         <v>0</v>
       </c>
-      <c r="BQ13" s="11"/>
-      <c r="BR13" s="11"/>
-      <c r="BS13" s="11"/>
-      <c r="BT13" s="11"/>
-      <c r="BU13" s="11"/>
-      <c r="BV13" s="11"/>
-      <c r="BW13" s="11"/>
-      <c r="BX13" s="11"/>
+      <c r="BQ13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX13" s="11">
+        <v>0</v>
+      </c>
       <c r="BY13" s="11"/>
       <c r="BZ13" s="11"/>
       <c r="CA13" s="11"/>
@@ -3727,7 +3765,7 @@
       </c>
       <c r="D14" s="14">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="11"/>
@@ -3811,14 +3849,30 @@
       <c r="BP14" s="11">
         <v>0</v>
       </c>
-      <c r="BQ14" s="11"/>
-      <c r="BR14" s="11"/>
-      <c r="BS14" s="11"/>
-      <c r="BT14" s="11"/>
-      <c r="BU14" s="11"/>
-      <c r="BV14" s="11"/>
-      <c r="BW14" s="11"/>
-      <c r="BX14" s="11"/>
+      <c r="BQ14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX14" s="11">
+        <v>0</v>
+      </c>
       <c r="BY14" s="11"/>
       <c r="BZ14" s="11"/>
       <c r="CA14" s="11"/>
@@ -3901,7 +3955,7 @@
       </c>
       <c r="D15" s="14">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="11"/>
@@ -3995,14 +4049,30 @@
       <c r="BP15" s="11">
         <v>0</v>
       </c>
-      <c r="BQ15" s="11"/>
-      <c r="BR15" s="11"/>
-      <c r="BS15" s="11"/>
-      <c r="BT15" s="11"/>
-      <c r="BU15" s="11"/>
-      <c r="BV15" s="11"/>
-      <c r="BW15" s="11"/>
-      <c r="BX15" s="11"/>
+      <c r="BQ15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX15" s="11">
+        <v>0</v>
+      </c>
       <c r="BY15" s="11"/>
       <c r="BZ15" s="11"/>
       <c r="CA15" s="11"/>
@@ -4085,7 +4155,7 @@
       </c>
       <c r="D16" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="11"/>
@@ -4163,14 +4233,30 @@
       <c r="BP16" s="11">
         <v>0</v>
       </c>
-      <c r="BQ16" s="11"/>
-      <c r="BR16" s="11"/>
-      <c r="BS16" s="11"/>
-      <c r="BT16" s="11"/>
-      <c r="BU16" s="11"/>
-      <c r="BV16" s="11"/>
-      <c r="BW16" s="11"/>
-      <c r="BX16" s="11"/>
+      <c r="BQ16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX16" s="11">
+        <v>0</v>
+      </c>
       <c r="BY16" s="11"/>
       <c r="BZ16" s="11"/>
       <c r="CA16" s="11"/>
@@ -4351,113 +4437,113 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AO17" s="54" t="s">
+      <c r="AO17" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="55"/>
-      <c r="AQ17" s="55"/>
-      <c r="AR17" s="55"/>
-      <c r="AS17" s="55"/>
-      <c r="AT17" s="55"/>
-      <c r="AU17" s="55"/>
-      <c r="AV17" s="55"/>
-      <c r="AW17" s="55"/>
-      <c r="AX17" s="55"/>
-      <c r="AY17" s="55"/>
-      <c r="AZ17" s="55"/>
-      <c r="BA17" s="55"/>
-      <c r="BB17" s="55"/>
-      <c r="BC17" s="55"/>
-      <c r="BD17" s="55"/>
-      <c r="BE17" s="55"/>
-      <c r="BF17" s="55"/>
-      <c r="BG17" s="55"/>
-      <c r="BH17" s="55"/>
-      <c r="BI17" s="55"/>
-      <c r="BJ17" s="55"/>
-      <c r="BK17" s="55"/>
-      <c r="BL17" s="55"/>
-      <c r="BM17" s="55"/>
-      <c r="BN17" s="55"/>
-      <c r="BO17" s="55"/>
-      <c r="BP17" s="55"/>
-      <c r="BQ17" s="55"/>
-      <c r="BR17" s="55"/>
-      <c r="BS17" s="55"/>
-      <c r="BT17" s="55"/>
-      <c r="BU17" s="55"/>
-      <c r="BV17" s="55"/>
-      <c r="BW17" s="55"/>
-      <c r="BX17" s="55"/>
-      <c r="BY17" s="55"/>
-      <c r="BZ17" s="55"/>
-      <c r="CA17" s="55"/>
-      <c r="CB17" s="55"/>
-      <c r="CC17" s="55"/>
-      <c r="CD17" s="55"/>
-      <c r="CE17" s="55"/>
-      <c r="CF17" s="55"/>
-      <c r="CG17" s="55"/>
-      <c r="CH17" s="55"/>
-      <c r="CI17" s="55"/>
-      <c r="CJ17" s="55"/>
-      <c r="CK17" s="55"/>
-      <c r="CL17" s="55"/>
-      <c r="CM17" s="55"/>
-      <c r="CN17" s="55"/>
-      <c r="CO17" s="55"/>
-      <c r="CP17" s="55"/>
-      <c r="CQ17" s="55"/>
-      <c r="CR17" s="55"/>
-      <c r="CS17" s="55"/>
-      <c r="CT17" s="55"/>
-      <c r="CU17" s="55"/>
-      <c r="CV17" s="55"/>
-      <c r="CW17" s="55"/>
-      <c r="CX17" s="55"/>
-      <c r="CY17" s="55"/>
-      <c r="CZ17" s="55"/>
-      <c r="DA17" s="55"/>
-      <c r="DB17" s="55"/>
-      <c r="DC17" s="55"/>
-      <c r="DD17" s="55"/>
-      <c r="DE17" s="55"/>
-      <c r="DF17" s="55"/>
-      <c r="DG17" s="55"/>
-      <c r="DH17" s="55"/>
-      <c r="DI17" s="55"/>
-      <c r="DJ17" s="55"/>
-      <c r="DK17" s="55"/>
-      <c r="DL17" s="55"/>
-      <c r="DM17" s="55"/>
-      <c r="DN17" s="55"/>
-      <c r="DO17" s="55"/>
-      <c r="DP17" s="55"/>
-      <c r="DQ17" s="55"/>
-      <c r="DR17" s="55"/>
-      <c r="DS17" s="55"/>
-      <c r="DT17" s="55"/>
-      <c r="DU17" s="55"/>
-      <c r="DV17" s="55"/>
-      <c r="DW17" s="55"/>
-      <c r="DX17" s="55"/>
-      <c r="DY17" s="55"/>
-      <c r="DZ17" s="55"/>
-      <c r="EA17" s="55"/>
-      <c r="EB17" s="55"/>
-      <c r="EC17" s="55"/>
-      <c r="ED17" s="55"/>
-      <c r="EE17" s="55"/>
-      <c r="EF17" s="55"/>
-      <c r="EG17" s="55"/>
-      <c r="EH17" s="55"/>
-      <c r="EI17" s="55"/>
-      <c r="EJ17" s="55"/>
-      <c r="EK17" s="55"/>
-      <c r="EL17" s="55"/>
-      <c r="EM17" s="55"/>
-      <c r="EN17" s="55"/>
-      <c r="EO17" s="56"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="23"/>
+      <c r="AR17" s="23"/>
+      <c r="AS17" s="23"/>
+      <c r="AT17" s="23"/>
+      <c r="AU17" s="23"/>
+      <c r="AV17" s="23"/>
+      <c r="AW17" s="23"/>
+      <c r="AX17" s="23"/>
+      <c r="AY17" s="23"/>
+      <c r="AZ17" s="23"/>
+      <c r="BA17" s="23"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="23"/>
+      <c r="BD17" s="23"/>
+      <c r="BE17" s="23"/>
+      <c r="BF17" s="23"/>
+      <c r="BG17" s="23"/>
+      <c r="BH17" s="23"/>
+      <c r="BI17" s="23"/>
+      <c r="BJ17" s="23"/>
+      <c r="BK17" s="23"/>
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="23"/>
+      <c r="BP17" s="23"/>
+      <c r="BQ17" s="23"/>
+      <c r="BR17" s="23"/>
+      <c r="BS17" s="23"/>
+      <c r="BT17" s="23"/>
+      <c r="BU17" s="23"/>
+      <c r="BV17" s="23"/>
+      <c r="BW17" s="23"/>
+      <c r="BX17" s="23"/>
+      <c r="BY17" s="23"/>
+      <c r="BZ17" s="23"/>
+      <c r="CA17" s="23"/>
+      <c r="CB17" s="23"/>
+      <c r="CC17" s="23"/>
+      <c r="CD17" s="23"/>
+      <c r="CE17" s="23"/>
+      <c r="CF17" s="23"/>
+      <c r="CG17" s="23"/>
+      <c r="CH17" s="23"/>
+      <c r="CI17" s="23"/>
+      <c r="CJ17" s="23"/>
+      <c r="CK17" s="23"/>
+      <c r="CL17" s="23"/>
+      <c r="CM17" s="23"/>
+      <c r="CN17" s="23"/>
+      <c r="CO17" s="23"/>
+      <c r="CP17" s="23"/>
+      <c r="CQ17" s="23"/>
+      <c r="CR17" s="23"/>
+      <c r="CS17" s="23"/>
+      <c r="CT17" s="23"/>
+      <c r="CU17" s="23"/>
+      <c r="CV17" s="23"/>
+      <c r="CW17" s="23"/>
+      <c r="CX17" s="23"/>
+      <c r="CY17" s="23"/>
+      <c r="CZ17" s="23"/>
+      <c r="DA17" s="23"/>
+      <c r="DB17" s="23"/>
+      <c r="DC17" s="23"/>
+      <c r="DD17" s="23"/>
+      <c r="DE17" s="23"/>
+      <c r="DF17" s="23"/>
+      <c r="DG17" s="23"/>
+      <c r="DH17" s="23"/>
+      <c r="DI17" s="23"/>
+      <c r="DJ17" s="23"/>
+      <c r="DK17" s="23"/>
+      <c r="DL17" s="23"/>
+      <c r="DM17" s="23"/>
+      <c r="DN17" s="23"/>
+      <c r="DO17" s="23"/>
+      <c r="DP17" s="23"/>
+      <c r="DQ17" s="23"/>
+      <c r="DR17" s="23"/>
+      <c r="DS17" s="23"/>
+      <c r="DT17" s="23"/>
+      <c r="DU17" s="23"/>
+      <c r="DV17" s="23"/>
+      <c r="DW17" s="23"/>
+      <c r="DX17" s="23"/>
+      <c r="DY17" s="23"/>
+      <c r="DZ17" s="23"/>
+      <c r="EA17" s="23"/>
+      <c r="EB17" s="23"/>
+      <c r="EC17" s="23"/>
+      <c r="ED17" s="23"/>
+      <c r="EE17" s="23"/>
+      <c r="EF17" s="23"/>
+      <c r="EG17" s="23"/>
+      <c r="EH17" s="23"/>
+      <c r="EI17" s="23"/>
+      <c r="EJ17" s="23"/>
+      <c r="EK17" s="23"/>
+      <c r="EL17" s="23"/>
+      <c r="EM17" s="23"/>
+      <c r="EN17" s="23"/>
+      <c r="EO17" s="24"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
@@ -4471,7 +4557,7 @@
       </c>
       <c r="D18" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="11"/>
@@ -4545,14 +4631,30 @@
         <v>0</v>
       </c>
       <c r="BP18" s="11"/>
-      <c r="BQ18" s="11"/>
-      <c r="BR18" s="11"/>
-      <c r="BS18" s="11"/>
-      <c r="BT18" s="11"/>
-      <c r="BU18" s="11"/>
-      <c r="BV18" s="11"/>
-      <c r="BW18" s="11"/>
-      <c r="BX18" s="11"/>
+      <c r="BQ18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX18" s="11">
+        <v>0</v>
+      </c>
       <c r="BY18" s="11"/>
       <c r="BZ18" s="11"/>
       <c r="CA18" s="11"/>
@@ -4635,7 +4737,7 @@
       </c>
       <c r="D19" s="14">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="11"/>
@@ -4729,14 +4831,30 @@
       <c r="BP19" s="11">
         <v>0</v>
       </c>
-      <c r="BQ19" s="11"/>
-      <c r="BR19" s="11"/>
-      <c r="BS19" s="11"/>
-      <c r="BT19" s="11"/>
-      <c r="BU19" s="11"/>
-      <c r="BV19" s="11"/>
-      <c r="BW19" s="11"/>
-      <c r="BX19" s="11"/>
+      <c r="BQ19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX19" s="11">
+        <v>0</v>
+      </c>
       <c r="BY19" s="11"/>
       <c r="BZ19" s="11"/>
       <c r="CA19" s="11"/>
@@ -4987,7 +5105,7 @@
       </c>
       <c r="D21" s="14">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="11"/>
@@ -5165,14 +5283,30 @@
       <c r="BP21" s="11">
         <v>0</v>
       </c>
-      <c r="BQ21" s="11"/>
-      <c r="BR21" s="11"/>
-      <c r="BS21" s="11"/>
-      <c r="BT21" s="11"/>
-      <c r="BU21" s="11"/>
-      <c r="BV21" s="11"/>
-      <c r="BW21" s="11"/>
-      <c r="BX21" s="11"/>
+      <c r="BQ21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX21" s="11">
+        <v>0</v>
+      </c>
       <c r="BY21" s="11"/>
       <c r="BZ21" s="11"/>
       <c r="CA21" s="11"/>
@@ -5255,7 +5389,7 @@
       </c>
       <c r="D22" s="14">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="11"/>
@@ -5357,14 +5491,30 @@
       <c r="BP22" s="11">
         <v>0</v>
       </c>
-      <c r="BQ22" s="11"/>
-      <c r="BR22" s="11"/>
-      <c r="BS22" s="11"/>
-      <c r="BT22" s="11"/>
-      <c r="BU22" s="11"/>
-      <c r="BV22" s="11"/>
-      <c r="BW22" s="11"/>
-      <c r="BX22" s="11"/>
+      <c r="BQ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX22" s="11">
+        <v>0</v>
+      </c>
       <c r="BY22" s="11"/>
       <c r="BZ22" s="11"/>
       <c r="CA22" s="11"/>
@@ -5447,7 +5597,7 @@
       </c>
       <c r="D23" s="14">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="11">
@@ -5629,14 +5779,30 @@
       <c r="BP23" s="11">
         <v>0</v>
       </c>
-      <c r="BQ23" s="11"/>
-      <c r="BR23" s="11"/>
-      <c r="BS23" s="11"/>
-      <c r="BT23" s="11"/>
-      <c r="BU23" s="11"/>
-      <c r="BV23" s="11"/>
-      <c r="BW23" s="11"/>
-      <c r="BX23" s="11"/>
+      <c r="BQ23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW23" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX23" s="11">
+        <v>0</v>
+      </c>
       <c r="BY23" s="11"/>
       <c r="BZ23" s="11"/>
       <c r="CA23" s="11"/>
@@ -5719,7 +5885,7 @@
       </c>
       <c r="D24" s="14">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="11"/>
@@ -5823,14 +5989,30 @@
       <c r="BP24" s="11">
         <v>0</v>
       </c>
-      <c r="BQ24" s="11"/>
-      <c r="BR24" s="11"/>
-      <c r="BS24" s="11"/>
-      <c r="BT24" s="11"/>
-      <c r="BU24" s="11"/>
-      <c r="BV24" s="11"/>
-      <c r="BW24" s="11"/>
-      <c r="BX24" s="11"/>
+      <c r="BQ24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX24" s="11">
+        <v>0</v>
+      </c>
       <c r="BY24" s="11"/>
       <c r="BZ24" s="11"/>
       <c r="CA24" s="11"/>
@@ -5913,7 +6095,7 @@
       </c>
       <c r="D25" s="14">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="11"/>
@@ -6031,14 +6213,30 @@
       <c r="BP25" s="11">
         <v>0</v>
       </c>
-      <c r="BQ25" s="11"/>
-      <c r="BR25" s="11"/>
-      <c r="BS25" s="11"/>
-      <c r="BT25" s="11"/>
-      <c r="BU25" s="11"/>
-      <c r="BV25" s="11"/>
-      <c r="BW25" s="11"/>
-      <c r="BX25" s="11"/>
+      <c r="BQ25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX25" s="11">
+        <v>0</v>
+      </c>
       <c r="BY25" s="11"/>
       <c r="BZ25" s="11"/>
       <c r="CA25" s="11"/>
@@ -6121,7 +6319,7 @@
       </c>
       <c r="D26" s="14">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="11"/>
@@ -6223,14 +6421,30 @@
       <c r="BP26" s="11">
         <v>0</v>
       </c>
-      <c r="BQ26" s="11"/>
-      <c r="BR26" s="11"/>
-      <c r="BS26" s="11"/>
-      <c r="BT26" s="11"/>
-      <c r="BU26" s="11"/>
-      <c r="BV26" s="11"/>
-      <c r="BW26" s="11"/>
-      <c r="BX26" s="11"/>
+      <c r="BQ26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX26" s="11">
+        <v>0</v>
+      </c>
       <c r="BY26" s="11"/>
       <c r="BZ26" s="11"/>
       <c r="CA26" s="11"/>
@@ -6313,7 +6527,7 @@
       </c>
       <c r="D27" s="14">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="11"/>
@@ -6491,14 +6705,30 @@
       <c r="BP27" s="11">
         <v>0</v>
       </c>
-      <c r="BQ27" s="11"/>
-      <c r="BR27" s="11"/>
-      <c r="BS27" s="11"/>
-      <c r="BT27" s="11"/>
-      <c r="BU27" s="11"/>
-      <c r="BV27" s="11"/>
-      <c r="BW27" s="11"/>
-      <c r="BX27" s="11"/>
+      <c r="BQ27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BR27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BS27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BT27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BU27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BV27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BW27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BX27" s="11">
+        <v>0</v>
+      </c>
       <c r="BY27" s="11"/>
       <c r="BZ27" s="11"/>
       <c r="CA27" s="11"/>
@@ -6583,149 +6813,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AH28" s="30"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="30"/>
-      <c r="AK28" s="30"/>
-      <c r="AL28" s="30"/>
-      <c r="AM28" s="30"/>
-      <c r="AN28" s="30"/>
-      <c r="AO28" s="30"/>
-      <c r="AP28" s="30"/>
-      <c r="AQ28" s="30"/>
-      <c r="AR28" s="30"/>
-      <c r="AS28" s="30"/>
-      <c r="AT28" s="30"/>
-      <c r="AU28" s="30"/>
-      <c r="AV28" s="30"/>
-      <c r="AW28" s="30"/>
-      <c r="AX28" s="30"/>
-      <c r="AY28" s="30"/>
-      <c r="AZ28" s="30"/>
-      <c r="BA28" s="30"/>
-      <c r="BB28" s="30"/>
-      <c r="BC28" s="30"/>
-      <c r="BD28" s="30"/>
-      <c r="BE28" s="30"/>
-      <c r="BF28" s="30"/>
-      <c r="BG28" s="30"/>
-      <c r="BH28" s="30"/>
-      <c r="BI28" s="30"/>
-      <c r="BJ28" s="30"/>
-      <c r="BK28" s="30"/>
-      <c r="BL28" s="30"/>
-      <c r="BM28" s="30"/>
-      <c r="BN28" s="30"/>
-      <c r="BO28" s="30"/>
-      <c r="BP28" s="30"/>
-      <c r="BQ28" s="30"/>
-      <c r="BR28" s="30"/>
-      <c r="BS28" s="30"/>
-      <c r="BT28" s="30"/>
-      <c r="BU28" s="30"/>
-      <c r="BV28" s="30"/>
-      <c r="BW28" s="30"/>
-      <c r="BX28" s="30"/>
-      <c r="BY28" s="30"/>
-      <c r="BZ28" s="30"/>
-      <c r="CA28" s="30"/>
-      <c r="CB28" s="30"/>
-      <c r="CC28" s="30"/>
-      <c r="CD28" s="30"/>
-      <c r="CE28" s="30"/>
-      <c r="CF28" s="30"/>
-      <c r="CG28" s="30"/>
-      <c r="CH28" s="30"/>
-      <c r="CI28" s="30"/>
-      <c r="CJ28" s="30"/>
-      <c r="CK28" s="30"/>
-      <c r="CL28" s="30"/>
-      <c r="CM28" s="30"/>
-      <c r="CN28" s="30"/>
-      <c r="CO28" s="30"/>
-      <c r="CP28" s="30"/>
-      <c r="CQ28" s="30"/>
-      <c r="CR28" s="30"/>
-      <c r="CS28" s="30"/>
-      <c r="CT28" s="30"/>
-      <c r="CU28" s="30"/>
-      <c r="CV28" s="30"/>
-      <c r="CW28" s="30"/>
-      <c r="CX28" s="30"/>
-      <c r="CY28" s="30"/>
-      <c r="CZ28" s="30"/>
-      <c r="DA28" s="30"/>
-      <c r="DB28" s="30"/>
-      <c r="DC28" s="30"/>
-      <c r="DD28" s="30"/>
-      <c r="DE28" s="30"/>
-      <c r="DF28" s="30"/>
-      <c r="DG28" s="30"/>
-      <c r="DH28" s="30"/>
-      <c r="DI28" s="30"/>
-      <c r="DJ28" s="30"/>
-      <c r="DK28" s="30"/>
-      <c r="DL28" s="30"/>
-      <c r="DM28" s="30"/>
-      <c r="DN28" s="30"/>
-      <c r="DO28" s="30"/>
-      <c r="DP28" s="30"/>
-      <c r="DQ28" s="30"/>
-      <c r="DR28" s="30"/>
-      <c r="DS28" s="30"/>
-      <c r="DT28" s="30"/>
-      <c r="DU28" s="30"/>
-      <c r="DV28" s="30"/>
-      <c r="DW28" s="30"/>
-      <c r="DX28" s="30"/>
-      <c r="DY28" s="30"/>
-      <c r="DZ28" s="30"/>
-      <c r="EA28" s="30"/>
-      <c r="EB28" s="30"/>
-      <c r="EC28" s="30"/>
-      <c r="ED28" s="30"/>
-      <c r="EE28" s="30"/>
-      <c r="EF28" s="30"/>
-      <c r="EG28" s="30"/>
-      <c r="EH28" s="30"/>
-      <c r="EI28" s="30"/>
-      <c r="EJ28" s="30"/>
-      <c r="EK28" s="30"/>
-      <c r="EL28" s="30"/>
-      <c r="EM28" s="30"/>
-      <c r="EN28" s="30"/>
-      <c r="EO28" s="30"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
+      <c r="S28" s="64"/>
+      <c r="T28" s="64"/>
+      <c r="U28" s="64"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="64"/>
+      <c r="AA28" s="64"/>
+      <c r="AB28" s="64"/>
+      <c r="AC28" s="64"/>
+      <c r="AD28" s="64"/>
+      <c r="AE28" s="64"/>
+      <c r="AF28" s="64"/>
+      <c r="AG28" s="64"/>
+      <c r="AH28" s="64"/>
+      <c r="AI28" s="64"/>
+      <c r="AJ28" s="64"/>
+      <c r="AK28" s="64"/>
+      <c r="AL28" s="64"/>
+      <c r="AM28" s="64"/>
+      <c r="AN28" s="64"/>
+      <c r="AO28" s="64"/>
+      <c r="AP28" s="64"/>
+      <c r="AQ28" s="64"/>
+      <c r="AR28" s="64"/>
+      <c r="AS28" s="64"/>
+      <c r="AT28" s="64"/>
+      <c r="AU28" s="64"/>
+      <c r="AV28" s="64"/>
+      <c r="AW28" s="64"/>
+      <c r="AX28" s="64"/>
+      <c r="AY28" s="64"/>
+      <c r="AZ28" s="64"/>
+      <c r="BA28" s="64"/>
+      <c r="BB28" s="64"/>
+      <c r="BC28" s="64"/>
+      <c r="BD28" s="64"/>
+      <c r="BE28" s="64"/>
+      <c r="BF28" s="64"/>
+      <c r="BG28" s="64"/>
+      <c r="BH28" s="64"/>
+      <c r="BI28" s="64"/>
+      <c r="BJ28" s="64"/>
+      <c r="BK28" s="64"/>
+      <c r="BL28" s="64"/>
+      <c r="BM28" s="64"/>
+      <c r="BN28" s="64"/>
+      <c r="BO28" s="64"/>
+      <c r="BP28" s="64"/>
+      <c r="BQ28" s="64"/>
+      <c r="BR28" s="64"/>
+      <c r="BS28" s="64"/>
+      <c r="BT28" s="64"/>
+      <c r="BU28" s="64"/>
+      <c r="BV28" s="64"/>
+      <c r="BW28" s="64"/>
+      <c r="BX28" s="64"/>
+      <c r="BY28" s="64"/>
+      <c r="BZ28" s="64"/>
+      <c r="CA28" s="64"/>
+      <c r="CB28" s="64"/>
+      <c r="CC28" s="64"/>
+      <c r="CD28" s="64"/>
+      <c r="CE28" s="64"/>
+      <c r="CF28" s="64"/>
+      <c r="CG28" s="64"/>
+      <c r="CH28" s="64"/>
+      <c r="CI28" s="64"/>
+      <c r="CJ28" s="64"/>
+      <c r="CK28" s="64"/>
+      <c r="CL28" s="64"/>
+      <c r="CM28" s="64"/>
+      <c r="CN28" s="64"/>
+      <c r="CO28" s="64"/>
+      <c r="CP28" s="64"/>
+      <c r="CQ28" s="64"/>
+      <c r="CR28" s="64"/>
+      <c r="CS28" s="64"/>
+      <c r="CT28" s="64"/>
+      <c r="CU28" s="64"/>
+      <c r="CV28" s="64"/>
+      <c r="CW28" s="64"/>
+      <c r="CX28" s="64"/>
+      <c r="CY28" s="64"/>
+      <c r="CZ28" s="64"/>
+      <c r="DA28" s="64"/>
+      <c r="DB28" s="64"/>
+      <c r="DC28" s="64"/>
+      <c r="DD28" s="64"/>
+      <c r="DE28" s="64"/>
+      <c r="DF28" s="64"/>
+      <c r="DG28" s="64"/>
+      <c r="DH28" s="64"/>
+      <c r="DI28" s="64"/>
+      <c r="DJ28" s="64"/>
+      <c r="DK28" s="64"/>
+      <c r="DL28" s="64"/>
+      <c r="DM28" s="64"/>
+      <c r="DN28" s="64"/>
+      <c r="DO28" s="64"/>
+      <c r="DP28" s="64"/>
+      <c r="DQ28" s="64"/>
+      <c r="DR28" s="64"/>
+      <c r="DS28" s="64"/>
+      <c r="DT28" s="64"/>
+      <c r="DU28" s="64"/>
+      <c r="DV28" s="64"/>
+      <c r="DW28" s="64"/>
+      <c r="DX28" s="64"/>
+      <c r="DY28" s="64"/>
+      <c r="DZ28" s="64"/>
+      <c r="EA28" s="64"/>
+      <c r="EB28" s="64"/>
+      <c r="EC28" s="64"/>
+      <c r="ED28" s="64"/>
+      <c r="EE28" s="64"/>
+      <c r="EF28" s="64"/>
+      <c r="EG28" s="64"/>
+      <c r="EH28" s="64"/>
+      <c r="EI28" s="64"/>
+      <c r="EJ28" s="64"/>
+      <c r="EK28" s="64"/>
+      <c r="EL28" s="64"/>
+      <c r="EM28" s="64"/>
+      <c r="EN28" s="64"/>
+      <c r="EO28" s="64"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6734,6 +6964,299 @@
     </row>
   </sheetData>
   <mergeCells count="317">
+    <mergeCell ref="BQ1:BU1"/>
+    <mergeCell ref="BV1:BX1"/>
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="DV8:DV9"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="E28:EO28"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="AO17:EO17"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D2"/>
@@ -6758,299 +7281,6 @@
     <mergeCell ref="Q2:Q7"/>
     <mergeCell ref="R2:R7"/>
     <mergeCell ref="BM1:BO1"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="BH1:BL1"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="E28:EO28"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="BQ1:BU1"/>
-    <mergeCell ref="BV1:BX1"/>
-    <mergeCell ref="EH8:EH9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="DV8:DV9"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DA8:DA9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5574C9-1A97-415F-89FD-943785BF847C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B3FA54-F681-4C2E-B481-A8C298B04100}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -769,7 +769,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -822,6 +822,105 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -852,9 +951,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -872,99 +968,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1193,128 +1196,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
-      <c r="F1" s="30">
+      <c r="C1" s="59"/>
+      <c r="D1" s="60"/>
+      <c r="F1" s="63">
         <v>4</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="32">
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="34">
         <v>3</v>
       </c>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34">
         <v>4</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33">
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="65">
         <v>4</v>
       </c>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="33">
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="65">
         <v>4</v>
       </c>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="33">
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="65">
         <v>4</v>
       </c>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="65">
+      <c r="Z1" s="66"/>
+      <c r="AA1" s="66"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="32">
         <v>2</v>
       </c>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="43">
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="26">
         <v>4</v>
       </c>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="45"/>
-      <c r="AI1" s="43">
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="26">
         <v>4</v>
       </c>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="44"/>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="43">
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="27"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="26">
         <v>2</v>
       </c>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="43">
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="26">
         <v>4</v>
       </c>
-      <c r="AP1" s="44"/>
-      <c r="AQ1" s="44"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="43">
+      <c r="AP1" s="27"/>
+      <c r="AQ1" s="27"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="26">
         <v>5</v>
       </c>
-      <c r="AT1" s="44"/>
-      <c r="AU1" s="44"/>
-      <c r="AV1" s="44"/>
-      <c r="AW1" s="45"/>
+      <c r="AT1" s="27"/>
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="28"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="43">
+      <c r="AY1" s="26">
         <v>5</v>
       </c>
-      <c r="AZ1" s="44"/>
-      <c r="BA1" s="44"/>
-      <c r="BB1" s="44"/>
-      <c r="BC1" s="45"/>
-      <c r="BD1" s="43">
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
+      <c r="BB1" s="27"/>
+      <c r="BC1" s="28"/>
+      <c r="BD1" s="26">
         <v>3</v>
       </c>
-      <c r="BE1" s="44"/>
-      <c r="BF1" s="45"/>
+      <c r="BE1" s="27"/>
+      <c r="BF1" s="28"/>
       <c r="BG1" s="20">
         <v>1</v>
       </c>
-      <c r="BH1" s="32">
+      <c r="BH1" s="34">
         <v>5</v>
       </c>
-      <c r="BI1" s="32"/>
-      <c r="BJ1" s="32"/>
-      <c r="BK1" s="32"/>
-      <c r="BL1" s="32"/>
-      <c r="BM1" s="43">
+      <c r="BI1" s="34"/>
+      <c r="BJ1" s="34"/>
+      <c r="BK1" s="34"/>
+      <c r="BL1" s="34"/>
+      <c r="BM1" s="26">
         <v>3</v>
       </c>
-      <c r="BN1" s="44"/>
-      <c r="BO1" s="45"/>
+      <c r="BN1" s="27"/>
+      <c r="BO1" s="28"/>
       <c r="BP1" s="21">
         <v>1</v>
       </c>
-      <c r="BQ1" s="67">
+      <c r="BQ1" s="23">
         <v>5</v>
       </c>
-      <c r="BR1" s="68"/>
-      <c r="BS1" s="68"/>
-      <c r="BT1" s="68"/>
-      <c r="BU1" s="69"/>
-      <c r="BV1" s="43">
+      <c r="BR1" s="24"/>
+      <c r="BS1" s="24"/>
+      <c r="BT1" s="24"/>
+      <c r="BU1" s="25"/>
+      <c r="BV1" s="26">
         <v>3</v>
       </c>
-      <c r="BW1" s="44"/>
-      <c r="BX1" s="45"/>
-      <c r="BY1" s="4"/>
+      <c r="BW1" s="27"/>
+      <c r="BX1" s="28"/>
+      <c r="BY1" s="22">
+        <v>1</v>
+      </c>
       <c r="BZ1" s="4"/>
       <c r="CA1" s="4"/>
       <c r="CB1" s="4"/>
@@ -1385,1640 +1390,1642 @@
       <c r="EO1" s="4"/>
       <c r="EP1" s="1">
         <f>SUM(E1:EO1)</f>
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="36" t="s">
+      <c r="A2" s="58"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="R2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="41" t="s">
+      <c r="S2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="39" t="s">
+      <c r="U2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="41" t="s">
+      <c r="V2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="41" t="s">
+      <c r="W2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="41" t="s">
+      <c r="X2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Y2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="Z2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="46" t="s">
+      <c r="AA2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="46" t="s">
+      <c r="AB2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="41">
         <v>46199</v>
       </c>
-      <c r="AD2" s="39">
+      <c r="AD2" s="41">
         <v>46199</v>
       </c>
-      <c r="AE2" s="39">
+      <c r="AE2" s="41">
         <v>46202</v>
       </c>
-      <c r="AF2" s="39">
+      <c r="AF2" s="41">
         <v>46202</v>
       </c>
-      <c r="AG2" s="39">
+      <c r="AG2" s="41">
         <v>46202</v>
       </c>
-      <c r="AH2" s="39">
+      <c r="AH2" s="41">
         <v>46202</v>
       </c>
-      <c r="AI2" s="39">
+      <c r="AI2" s="41">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="39">
+      <c r="AJ2" s="41">
         <v>46205</v>
       </c>
-      <c r="AK2" s="39">
+      <c r="AK2" s="41">
         <v>46205</v>
       </c>
-      <c r="AL2" s="39">
+      <c r="AL2" s="41">
         <v>46205</v>
       </c>
-      <c r="AM2" s="39">
+      <c r="AM2" s="41">
         <v>46206</v>
       </c>
-      <c r="AN2" s="39">
+      <c r="AN2" s="41">
         <v>46206</v>
       </c>
-      <c r="AO2" s="39">
+      <c r="AO2" s="41">
         <v>46212</v>
       </c>
-      <c r="AP2" s="39">
+      <c r="AP2" s="41">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="39">
+      <c r="AQ2" s="41">
         <v>46212</v>
       </c>
-      <c r="AR2" s="39">
+      <c r="AR2" s="41">
         <v>46212</v>
       </c>
-      <c r="AS2" s="39">
+      <c r="AS2" s="41">
         <v>46213</v>
       </c>
-      <c r="AT2" s="39">
+      <c r="AT2" s="41">
         <v>46213</v>
       </c>
-      <c r="AU2" s="39">
+      <c r="AU2" s="41">
         <v>46213</v>
       </c>
-      <c r="AV2" s="39">
+      <c r="AV2" s="41">
         <v>46213</v>
       </c>
-      <c r="AW2" s="39">
+      <c r="AW2" s="41">
         <v>46213</v>
       </c>
-      <c r="AX2" s="39">
+      <c r="AX2" s="41">
         <v>46218</v>
       </c>
-      <c r="AY2" s="39">
+      <c r="AY2" s="41">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="39">
+      <c r="AZ2" s="41">
         <v>46219</v>
       </c>
-      <c r="BA2" s="39">
+      <c r="BA2" s="41">
         <v>46219</v>
       </c>
-      <c r="BB2" s="39">
+      <c r="BB2" s="41">
         <v>46219</v>
       </c>
-      <c r="BC2" s="39">
+      <c r="BC2" s="41">
         <v>46219</v>
       </c>
-      <c r="BD2" s="39">
+      <c r="BD2" s="41">
         <v>46220</v>
       </c>
-      <c r="BE2" s="39">
+      <c r="BE2" s="41">
         <v>46220</v>
       </c>
-      <c r="BF2" s="39">
+      <c r="BF2" s="41">
         <v>46220</v>
       </c>
-      <c r="BG2" s="39">
+      <c r="BG2" s="41">
         <v>46225</v>
       </c>
-      <c r="BH2" s="39">
+      <c r="BH2" s="41">
         <v>46226</v>
       </c>
-      <c r="BI2" s="39">
+      <c r="BI2" s="41">
         <v>46226</v>
       </c>
-      <c r="BJ2" s="39">
+      <c r="BJ2" s="41">
         <v>46226</v>
       </c>
-      <c r="BK2" s="39">
+      <c r="BK2" s="41">
         <v>46226</v>
       </c>
-      <c r="BL2" s="39">
+      <c r="BL2" s="41">
         <v>46226</v>
       </c>
-      <c r="BM2" s="39">
+      <c r="BM2" s="41">
         <v>46227</v>
       </c>
-      <c r="BN2" s="39">
+      <c r="BN2" s="41">
         <v>46227</v>
       </c>
-      <c r="BO2" s="39">
+      <c r="BO2" s="41">
         <v>46227</v>
       </c>
-      <c r="BP2" s="39">
+      <c r="BP2" s="41">
         <v>46232</v>
       </c>
-      <c r="BQ2" s="39">
+      <c r="BQ2" s="41">
         <v>46233</v>
       </c>
-      <c r="BR2" s="39">
+      <c r="BR2" s="41">
         <v>46233</v>
       </c>
-      <c r="BS2" s="39">
+      <c r="BS2" s="41">
         <v>46233</v>
       </c>
-      <c r="BT2" s="39">
+      <c r="BT2" s="41">
         <v>46233</v>
       </c>
-      <c r="BU2" s="39">
+      <c r="BU2" s="41">
         <v>46233</v>
       </c>
-      <c r="BV2" s="39">
+      <c r="BV2" s="41">
         <v>46234</v>
       </c>
-      <c r="BW2" s="39">
+      <c r="BW2" s="41">
         <v>46234</v>
       </c>
-      <c r="BX2" s="48">
+      <c r="BX2" s="49">
         <v>46234</v>
       </c>
-      <c r="BY2" s="39"/>
-      <c r="BZ2" s="39"/>
-      <c r="CA2" s="39"/>
-      <c r="CB2" s="39"/>
-      <c r="CC2" s="39"/>
-      <c r="CD2" s="39"/>
-      <c r="CE2" s="39"/>
-      <c r="CF2" s="39"/>
-      <c r="CG2" s="39"/>
-      <c r="CH2" s="39"/>
-      <c r="CI2" s="39"/>
-      <c r="CJ2" s="39"/>
-      <c r="CK2" s="39"/>
-      <c r="CL2" s="39"/>
-      <c r="CM2" s="39"/>
-      <c r="CN2" s="39"/>
-      <c r="CO2" s="39"/>
-      <c r="CP2" s="39"/>
-      <c r="CQ2" s="39"/>
-      <c r="CR2" s="39"/>
-      <c r="CS2" s="39"/>
-      <c r="CT2" s="39"/>
-      <c r="CU2" s="39"/>
-      <c r="CV2" s="39"/>
-      <c r="CW2" s="39"/>
-      <c r="CX2" s="39"/>
-      <c r="CY2" s="39"/>
-      <c r="CZ2" s="39"/>
-      <c r="DA2" s="39"/>
-      <c r="DB2" s="39"/>
-      <c r="DC2" s="39"/>
-      <c r="DD2" s="39"/>
-      <c r="DE2" s="39"/>
-      <c r="DF2" s="39"/>
-      <c r="DG2" s="39"/>
-      <c r="DH2" s="39"/>
-      <c r="DI2" s="39"/>
-      <c r="DJ2" s="39"/>
-      <c r="DK2" s="39"/>
-      <c r="DL2" s="39"/>
-      <c r="DM2" s="39"/>
-      <c r="DN2" s="39"/>
-      <c r="DO2" s="39"/>
-      <c r="DP2" s="39"/>
-      <c r="DQ2" s="39"/>
-      <c r="DR2" s="39"/>
-      <c r="DS2" s="39"/>
-      <c r="DT2" s="39"/>
-      <c r="DU2" s="39"/>
-      <c r="DV2" s="39"/>
-      <c r="DW2" s="39"/>
-      <c r="DX2" s="39"/>
-      <c r="DY2" s="39"/>
-      <c r="DZ2" s="39"/>
-      <c r="EA2" s="39"/>
-      <c r="EB2" s="39"/>
-      <c r="EC2" s="39"/>
-      <c r="ED2" s="39"/>
-      <c r="EE2" s="39"/>
-      <c r="EF2" s="39"/>
-      <c r="EG2" s="39"/>
-      <c r="EH2" s="39"/>
-      <c r="EI2" s="39"/>
-      <c r="EJ2" s="39"/>
-      <c r="EK2" s="39"/>
-      <c r="EL2" s="39"/>
-      <c r="EM2" s="39"/>
-      <c r="EN2" s="39"/>
-      <c r="EO2" s="39"/>
+      <c r="BY2" s="41">
+        <v>46274</v>
+      </c>
+      <c r="BZ2" s="41"/>
+      <c r="CA2" s="41"/>
+      <c r="CB2" s="41"/>
+      <c r="CC2" s="41"/>
+      <c r="CD2" s="41"/>
+      <c r="CE2" s="41"/>
+      <c r="CF2" s="41"/>
+      <c r="CG2" s="41"/>
+      <c r="CH2" s="41"/>
+      <c r="CI2" s="41"/>
+      <c r="CJ2" s="41"/>
+      <c r="CK2" s="41"/>
+      <c r="CL2" s="41"/>
+      <c r="CM2" s="41"/>
+      <c r="CN2" s="41"/>
+      <c r="CO2" s="41"/>
+      <c r="CP2" s="41"/>
+      <c r="CQ2" s="41"/>
+      <c r="CR2" s="41"/>
+      <c r="CS2" s="41"/>
+      <c r="CT2" s="41"/>
+      <c r="CU2" s="41"/>
+      <c r="CV2" s="41"/>
+      <c r="CW2" s="41"/>
+      <c r="CX2" s="41"/>
+      <c r="CY2" s="41"/>
+      <c r="CZ2" s="41"/>
+      <c r="DA2" s="41"/>
+      <c r="DB2" s="41"/>
+      <c r="DC2" s="41"/>
+      <c r="DD2" s="41"/>
+      <c r="DE2" s="41"/>
+      <c r="DF2" s="41"/>
+      <c r="DG2" s="41"/>
+      <c r="DH2" s="41"/>
+      <c r="DI2" s="41"/>
+      <c r="DJ2" s="41"/>
+      <c r="DK2" s="41"/>
+      <c r="DL2" s="41"/>
+      <c r="DM2" s="41"/>
+      <c r="DN2" s="41"/>
+      <c r="DO2" s="41"/>
+      <c r="DP2" s="41"/>
+      <c r="DQ2" s="41"/>
+      <c r="DR2" s="41"/>
+      <c r="DS2" s="41"/>
+      <c r="DT2" s="41"/>
+      <c r="DU2" s="41"/>
+      <c r="DV2" s="41"/>
+      <c r="DW2" s="41"/>
+      <c r="DX2" s="41"/>
+      <c r="DY2" s="41"/>
+      <c r="DZ2" s="41"/>
+      <c r="EA2" s="41"/>
+      <c r="EB2" s="41"/>
+      <c r="EC2" s="41"/>
+      <c r="ED2" s="41"/>
+      <c r="EE2" s="41"/>
+      <c r="EF2" s="41"/>
+      <c r="EG2" s="41"/>
+      <c r="EH2" s="41"/>
+      <c r="EI2" s="41"/>
+      <c r="EJ2" s="41"/>
+      <c r="EK2" s="41"/>
+      <c r="EL2" s="41"/>
+      <c r="EM2" s="41"/>
+      <c r="EN2" s="41"/>
+      <c r="EO2" s="41"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="46"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="39"/>
-      <c r="AW3" s="39"/>
-      <c r="AX3" s="39"/>
-      <c r="AY3" s="39"/>
-      <c r="AZ3" s="39"/>
-      <c r="BA3" s="39"/>
-      <c r="BB3" s="39"/>
-      <c r="BC3" s="39"/>
-      <c r="BD3" s="39"/>
-      <c r="BE3" s="39"/>
-      <c r="BF3" s="39"/>
-      <c r="BG3" s="39"/>
-      <c r="BH3" s="39"/>
-      <c r="BI3" s="39"/>
-      <c r="BJ3" s="39"/>
-      <c r="BK3" s="39"/>
-      <c r="BL3" s="39"/>
-      <c r="BM3" s="39"/>
-      <c r="BN3" s="39"/>
-      <c r="BO3" s="39"/>
-      <c r="BP3" s="39"/>
-      <c r="BQ3" s="39"/>
-      <c r="BR3" s="39"/>
-      <c r="BS3" s="39"/>
-      <c r="BT3" s="39"/>
-      <c r="BU3" s="39"/>
-      <c r="BV3" s="39"/>
-      <c r="BW3" s="39"/>
-      <c r="BX3" s="48"/>
-      <c r="BY3" s="39"/>
-      <c r="BZ3" s="39"/>
-      <c r="CA3" s="39"/>
-      <c r="CB3" s="39"/>
-      <c r="CC3" s="39"/>
-      <c r="CD3" s="39"/>
-      <c r="CE3" s="39"/>
-      <c r="CF3" s="39"/>
-      <c r="CG3" s="39"/>
-      <c r="CH3" s="39"/>
-      <c r="CI3" s="39"/>
-      <c r="CJ3" s="39"/>
-      <c r="CK3" s="39"/>
-      <c r="CL3" s="39"/>
-      <c r="CM3" s="39"/>
-      <c r="CN3" s="39"/>
-      <c r="CO3" s="39"/>
-      <c r="CP3" s="39"/>
-      <c r="CQ3" s="39"/>
-      <c r="CR3" s="39"/>
-      <c r="CS3" s="39"/>
-      <c r="CT3" s="39"/>
-      <c r="CU3" s="39"/>
-      <c r="CV3" s="39"/>
-      <c r="CW3" s="39"/>
-      <c r="CX3" s="39"/>
-      <c r="CY3" s="39"/>
-      <c r="CZ3" s="39"/>
-      <c r="DA3" s="39"/>
-      <c r="DB3" s="39"/>
-      <c r="DC3" s="39"/>
-      <c r="DD3" s="39"/>
-      <c r="DE3" s="39"/>
-      <c r="DF3" s="39"/>
-      <c r="DG3" s="39"/>
-      <c r="DH3" s="39"/>
-      <c r="DI3" s="39"/>
-      <c r="DJ3" s="39"/>
-      <c r="DK3" s="39"/>
-      <c r="DL3" s="39"/>
-      <c r="DM3" s="39"/>
-      <c r="DN3" s="39"/>
-      <c r="DO3" s="39"/>
-      <c r="DP3" s="39"/>
-      <c r="DQ3" s="39"/>
-      <c r="DR3" s="39"/>
-      <c r="DS3" s="39"/>
-      <c r="DT3" s="39"/>
-      <c r="DU3" s="39"/>
-      <c r="DV3" s="39"/>
-      <c r="DW3" s="39"/>
-      <c r="DX3" s="39"/>
-      <c r="DY3" s="39"/>
-      <c r="DZ3" s="39"/>
-      <c r="EA3" s="39"/>
-      <c r="EB3" s="39"/>
-      <c r="EC3" s="39"/>
-      <c r="ED3" s="39"/>
-      <c r="EE3" s="39"/>
-      <c r="EF3" s="39"/>
-      <c r="EG3" s="39"/>
-      <c r="EH3" s="39"/>
-      <c r="EI3" s="39"/>
-      <c r="EJ3" s="39"/>
-      <c r="EK3" s="39"/>
-      <c r="EL3" s="39"/>
-      <c r="EM3" s="39"/>
-      <c r="EN3" s="39"/>
-      <c r="EO3" s="39"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="41"/>
+      <c r="AU3" s="41"/>
+      <c r="AV3" s="41"/>
+      <c r="AW3" s="41"/>
+      <c r="AX3" s="41"/>
+      <c r="AY3" s="41"/>
+      <c r="AZ3" s="41"/>
+      <c r="BA3" s="41"/>
+      <c r="BB3" s="41"/>
+      <c r="BC3" s="41"/>
+      <c r="BD3" s="41"/>
+      <c r="BE3" s="41"/>
+      <c r="BF3" s="41"/>
+      <c r="BG3" s="41"/>
+      <c r="BH3" s="41"/>
+      <c r="BI3" s="41"/>
+      <c r="BJ3" s="41"/>
+      <c r="BK3" s="41"/>
+      <c r="BL3" s="41"/>
+      <c r="BM3" s="41"/>
+      <c r="BN3" s="41"/>
+      <c r="BO3" s="41"/>
+      <c r="BP3" s="41"/>
+      <c r="BQ3" s="41"/>
+      <c r="BR3" s="41"/>
+      <c r="BS3" s="41"/>
+      <c r="BT3" s="41"/>
+      <c r="BU3" s="41"/>
+      <c r="BV3" s="41"/>
+      <c r="BW3" s="41"/>
+      <c r="BX3" s="49"/>
+      <c r="BY3" s="41"/>
+      <c r="BZ3" s="41"/>
+      <c r="CA3" s="41"/>
+      <c r="CB3" s="41"/>
+      <c r="CC3" s="41"/>
+      <c r="CD3" s="41"/>
+      <c r="CE3" s="41"/>
+      <c r="CF3" s="41"/>
+      <c r="CG3" s="41"/>
+      <c r="CH3" s="41"/>
+      <c r="CI3" s="41"/>
+      <c r="CJ3" s="41"/>
+      <c r="CK3" s="41"/>
+      <c r="CL3" s="41"/>
+      <c r="CM3" s="41"/>
+      <c r="CN3" s="41"/>
+      <c r="CO3" s="41"/>
+      <c r="CP3" s="41"/>
+      <c r="CQ3" s="41"/>
+      <c r="CR3" s="41"/>
+      <c r="CS3" s="41"/>
+      <c r="CT3" s="41"/>
+      <c r="CU3" s="41"/>
+      <c r="CV3" s="41"/>
+      <c r="CW3" s="41"/>
+      <c r="CX3" s="41"/>
+      <c r="CY3" s="41"/>
+      <c r="CZ3" s="41"/>
+      <c r="DA3" s="41"/>
+      <c r="DB3" s="41"/>
+      <c r="DC3" s="41"/>
+      <c r="DD3" s="41"/>
+      <c r="DE3" s="41"/>
+      <c r="DF3" s="41"/>
+      <c r="DG3" s="41"/>
+      <c r="DH3" s="41"/>
+      <c r="DI3" s="41"/>
+      <c r="DJ3" s="41"/>
+      <c r="DK3" s="41"/>
+      <c r="DL3" s="41"/>
+      <c r="DM3" s="41"/>
+      <c r="DN3" s="41"/>
+      <c r="DO3" s="41"/>
+      <c r="DP3" s="41"/>
+      <c r="DQ3" s="41"/>
+      <c r="DR3" s="41"/>
+      <c r="DS3" s="41"/>
+      <c r="DT3" s="41"/>
+      <c r="DU3" s="41"/>
+      <c r="DV3" s="41"/>
+      <c r="DW3" s="41"/>
+      <c r="DX3" s="41"/>
+      <c r="DY3" s="41"/>
+      <c r="DZ3" s="41"/>
+      <c r="EA3" s="41"/>
+      <c r="EB3" s="41"/>
+      <c r="EC3" s="41"/>
+      <c r="ED3" s="41"/>
+      <c r="EE3" s="41"/>
+      <c r="EF3" s="41"/>
+      <c r="EG3" s="41"/>
+      <c r="EH3" s="41"/>
+      <c r="EI3" s="41"/>
+      <c r="EJ3" s="41"/>
+      <c r="EK3" s="41"/>
+      <c r="EL3" s="41"/>
+      <c r="EM3" s="41"/>
+      <c r="EN3" s="41"/>
+      <c r="EO3" s="41"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="39"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="39"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="39"/>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="39"/>
-      <c r="AR4" s="39"/>
-      <c r="AS4" s="39"/>
-      <c r="AT4" s="39"/>
-      <c r="AU4" s="39"/>
-      <c r="AV4" s="39"/>
-      <c r="AW4" s="39"/>
-      <c r="AX4" s="39"/>
-      <c r="AY4" s="39"/>
-      <c r="AZ4" s="39"/>
-      <c r="BA4" s="39"/>
-      <c r="BB4" s="39"/>
-      <c r="BC4" s="39"/>
-      <c r="BD4" s="39"/>
-      <c r="BE4" s="39"/>
-      <c r="BF4" s="39"/>
-      <c r="BG4" s="39"/>
-      <c r="BH4" s="39"/>
-      <c r="BI4" s="39"/>
-      <c r="BJ4" s="39"/>
-      <c r="BK4" s="39"/>
-      <c r="BL4" s="39"/>
-      <c r="BM4" s="39"/>
-      <c r="BN4" s="39"/>
-      <c r="BO4" s="39"/>
-      <c r="BP4" s="39"/>
-      <c r="BQ4" s="39"/>
-      <c r="BR4" s="39"/>
-      <c r="BS4" s="39"/>
-      <c r="BT4" s="39"/>
-      <c r="BU4" s="39"/>
-      <c r="BV4" s="39"/>
-      <c r="BW4" s="39"/>
-      <c r="BX4" s="48"/>
-      <c r="BY4" s="39"/>
-      <c r="BZ4" s="39"/>
-      <c r="CA4" s="39"/>
-      <c r="CB4" s="39"/>
-      <c r="CC4" s="39"/>
-      <c r="CD4" s="39"/>
-      <c r="CE4" s="39"/>
-      <c r="CF4" s="39"/>
-      <c r="CG4" s="39"/>
-      <c r="CH4" s="39"/>
-      <c r="CI4" s="39"/>
-      <c r="CJ4" s="39"/>
-      <c r="CK4" s="39"/>
-      <c r="CL4" s="39"/>
-      <c r="CM4" s="39"/>
-      <c r="CN4" s="39"/>
-      <c r="CO4" s="39"/>
-      <c r="CP4" s="39"/>
-      <c r="CQ4" s="39"/>
-      <c r="CR4" s="39"/>
-      <c r="CS4" s="39"/>
-      <c r="CT4" s="39"/>
-      <c r="CU4" s="39"/>
-      <c r="CV4" s="39"/>
-      <c r="CW4" s="39"/>
-      <c r="CX4" s="39"/>
-      <c r="CY4" s="39"/>
-      <c r="CZ4" s="39"/>
-      <c r="DA4" s="39"/>
-      <c r="DB4" s="39"/>
-      <c r="DC4" s="39"/>
-      <c r="DD4" s="39"/>
-      <c r="DE4" s="39"/>
-      <c r="DF4" s="39"/>
-      <c r="DG4" s="39"/>
-      <c r="DH4" s="39"/>
-      <c r="DI4" s="39"/>
-      <c r="DJ4" s="39"/>
-      <c r="DK4" s="39"/>
-      <c r="DL4" s="39"/>
-      <c r="DM4" s="39"/>
-      <c r="DN4" s="39"/>
-      <c r="DO4" s="39"/>
-      <c r="DP4" s="39"/>
-      <c r="DQ4" s="39"/>
-      <c r="DR4" s="39"/>
-      <c r="DS4" s="39"/>
-      <c r="DT4" s="39"/>
-      <c r="DU4" s="39"/>
-      <c r="DV4" s="39"/>
-      <c r="DW4" s="39"/>
-      <c r="DX4" s="39"/>
-      <c r="DY4" s="39"/>
-      <c r="DZ4" s="39"/>
-      <c r="EA4" s="39"/>
-      <c r="EB4" s="39"/>
-      <c r="EC4" s="39"/>
-      <c r="ED4" s="39"/>
-      <c r="EE4" s="39"/>
-      <c r="EF4" s="39"/>
-      <c r="EG4" s="39"/>
-      <c r="EH4" s="39"/>
-      <c r="EI4" s="39"/>
-      <c r="EJ4" s="39"/>
-      <c r="EK4" s="39"/>
-      <c r="EL4" s="39"/>
-      <c r="EM4" s="39"/>
-      <c r="EN4" s="39"/>
-      <c r="EO4" s="39"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="51"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
+      <c r="BJ4" s="41"/>
+      <c r="BK4" s="41"/>
+      <c r="BL4" s="41"/>
+      <c r="BM4" s="41"/>
+      <c r="BN4" s="41"/>
+      <c r="BO4" s="41"/>
+      <c r="BP4" s="41"/>
+      <c r="BQ4" s="41"/>
+      <c r="BR4" s="41"/>
+      <c r="BS4" s="41"/>
+      <c r="BT4" s="41"/>
+      <c r="BU4" s="41"/>
+      <c r="BV4" s="41"/>
+      <c r="BW4" s="41"/>
+      <c r="BX4" s="49"/>
+      <c r="BY4" s="41"/>
+      <c r="BZ4" s="41"/>
+      <c r="CA4" s="41"/>
+      <c r="CB4" s="41"/>
+      <c r="CC4" s="41"/>
+      <c r="CD4" s="41"/>
+      <c r="CE4" s="41"/>
+      <c r="CF4" s="41"/>
+      <c r="CG4" s="41"/>
+      <c r="CH4" s="41"/>
+      <c r="CI4" s="41"/>
+      <c r="CJ4" s="41"/>
+      <c r="CK4" s="41"/>
+      <c r="CL4" s="41"/>
+      <c r="CM4" s="41"/>
+      <c r="CN4" s="41"/>
+      <c r="CO4" s="41"/>
+      <c r="CP4" s="41"/>
+      <c r="CQ4" s="41"/>
+      <c r="CR4" s="41"/>
+      <c r="CS4" s="41"/>
+      <c r="CT4" s="41"/>
+      <c r="CU4" s="41"/>
+      <c r="CV4" s="41"/>
+      <c r="CW4" s="41"/>
+      <c r="CX4" s="41"/>
+      <c r="CY4" s="41"/>
+      <c r="CZ4" s="41"/>
+      <c r="DA4" s="41"/>
+      <c r="DB4" s="41"/>
+      <c r="DC4" s="41"/>
+      <c r="DD4" s="41"/>
+      <c r="DE4" s="41"/>
+      <c r="DF4" s="41"/>
+      <c r="DG4" s="41"/>
+      <c r="DH4" s="41"/>
+      <c r="DI4" s="41"/>
+      <c r="DJ4" s="41"/>
+      <c r="DK4" s="41"/>
+      <c r="DL4" s="41"/>
+      <c r="DM4" s="41"/>
+      <c r="DN4" s="41"/>
+      <c r="DO4" s="41"/>
+      <c r="DP4" s="41"/>
+      <c r="DQ4" s="41"/>
+      <c r="DR4" s="41"/>
+      <c r="DS4" s="41"/>
+      <c r="DT4" s="41"/>
+      <c r="DU4" s="41"/>
+      <c r="DV4" s="41"/>
+      <c r="DW4" s="41"/>
+      <c r="DX4" s="41"/>
+      <c r="DY4" s="41"/>
+      <c r="DZ4" s="41"/>
+      <c r="EA4" s="41"/>
+      <c r="EB4" s="41"/>
+      <c r="EC4" s="41"/>
+      <c r="ED4" s="41"/>
+      <c r="EE4" s="41"/>
+      <c r="EF4" s="41"/>
+      <c r="EG4" s="41"/>
+      <c r="EH4" s="41"/>
+      <c r="EI4" s="41"/>
+      <c r="EJ4" s="41"/>
+      <c r="EK4" s="41"/>
+      <c r="EL4" s="41"/>
+      <c r="EM4" s="41"/>
+      <c r="EN4" s="41"/>
+      <c r="EO4" s="41"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54">
+      <c r="B5" s="45"/>
+      <c r="C5" s="46">
         <v>110</v>
       </c>
-      <c r="D5" s="55"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="46"/>
-      <c r="AC5" s="39"/>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="39"/>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="39"/>
-      <c r="AH5" s="39"/>
-      <c r="AI5" s="39"/>
-      <c r="AJ5" s="39"/>
-      <c r="AK5" s="39"/>
-      <c r="AL5" s="39"/>
-      <c r="AM5" s="39"/>
-      <c r="AN5" s="39"/>
-      <c r="AO5" s="39"/>
-      <c r="AP5" s="39"/>
-      <c r="AQ5" s="39"/>
-      <c r="AR5" s="39"/>
-      <c r="AS5" s="39"/>
-      <c r="AT5" s="39"/>
-      <c r="AU5" s="39"/>
-      <c r="AV5" s="39"/>
-      <c r="AW5" s="39"/>
-      <c r="AX5" s="39"/>
-      <c r="AY5" s="39"/>
-      <c r="AZ5" s="39"/>
-      <c r="BA5" s="39"/>
-      <c r="BB5" s="39"/>
-      <c r="BC5" s="39"/>
-      <c r="BD5" s="39"/>
-      <c r="BE5" s="39"/>
-      <c r="BF5" s="39"/>
-      <c r="BG5" s="39"/>
-      <c r="BH5" s="39"/>
-      <c r="BI5" s="39"/>
-      <c r="BJ5" s="39"/>
-      <c r="BK5" s="39"/>
-      <c r="BL5" s="39"/>
-      <c r="BM5" s="39"/>
-      <c r="BN5" s="39"/>
-      <c r="BO5" s="39"/>
-      <c r="BP5" s="39"/>
-      <c r="BQ5" s="39"/>
-      <c r="BR5" s="39"/>
-      <c r="BS5" s="39"/>
-      <c r="BT5" s="39"/>
-      <c r="BU5" s="39"/>
-      <c r="BV5" s="39"/>
-      <c r="BW5" s="39"/>
-      <c r="BX5" s="48"/>
-      <c r="BY5" s="39"/>
-      <c r="BZ5" s="39"/>
-      <c r="CA5" s="39"/>
-      <c r="CB5" s="39"/>
-      <c r="CC5" s="39"/>
-      <c r="CD5" s="39"/>
-      <c r="CE5" s="39"/>
-      <c r="CF5" s="39"/>
-      <c r="CG5" s="39"/>
-      <c r="CH5" s="39"/>
-      <c r="CI5" s="39"/>
-      <c r="CJ5" s="39"/>
-      <c r="CK5" s="39"/>
-      <c r="CL5" s="39"/>
-      <c r="CM5" s="39"/>
-      <c r="CN5" s="39"/>
-      <c r="CO5" s="39"/>
-      <c r="CP5" s="39"/>
-      <c r="CQ5" s="39"/>
-      <c r="CR5" s="39"/>
-      <c r="CS5" s="39"/>
-      <c r="CT5" s="39"/>
-      <c r="CU5" s="39"/>
-      <c r="CV5" s="39"/>
-      <c r="CW5" s="39"/>
-      <c r="CX5" s="39"/>
-      <c r="CY5" s="39"/>
-      <c r="CZ5" s="39"/>
-      <c r="DA5" s="39"/>
-      <c r="DB5" s="39"/>
-      <c r="DC5" s="39"/>
-      <c r="DD5" s="39"/>
-      <c r="DE5" s="39"/>
-      <c r="DF5" s="39"/>
-      <c r="DG5" s="39"/>
-      <c r="DH5" s="39"/>
-      <c r="DI5" s="39"/>
-      <c r="DJ5" s="39"/>
-      <c r="DK5" s="39"/>
-      <c r="DL5" s="39"/>
-      <c r="DM5" s="39"/>
-      <c r="DN5" s="39"/>
-      <c r="DO5" s="39"/>
-      <c r="DP5" s="39"/>
-      <c r="DQ5" s="39"/>
-      <c r="DR5" s="39"/>
-      <c r="DS5" s="39"/>
-      <c r="DT5" s="39"/>
-      <c r="DU5" s="39"/>
-      <c r="DV5" s="39"/>
-      <c r="DW5" s="39"/>
-      <c r="DX5" s="39"/>
-      <c r="DY5" s="39"/>
-      <c r="DZ5" s="39"/>
-      <c r="EA5" s="39"/>
-      <c r="EB5" s="39"/>
-      <c r="EC5" s="39"/>
-      <c r="ED5" s="39"/>
-      <c r="EE5" s="39"/>
-      <c r="EF5" s="39"/>
-      <c r="EG5" s="39"/>
-      <c r="EH5" s="39"/>
-      <c r="EI5" s="39"/>
-      <c r="EJ5" s="39"/>
-      <c r="EK5" s="39"/>
-      <c r="EL5" s="39"/>
-      <c r="EM5" s="39"/>
-      <c r="EN5" s="39"/>
-      <c r="EO5" s="39"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="51"/>
+      <c r="AB5" s="51"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="41"/>
+      <c r="BI5" s="41"/>
+      <c r="BJ5" s="41"/>
+      <c r="BK5" s="41"/>
+      <c r="BL5" s="41"/>
+      <c r="BM5" s="41"/>
+      <c r="BN5" s="41"/>
+      <c r="BO5" s="41"/>
+      <c r="BP5" s="41"/>
+      <c r="BQ5" s="41"/>
+      <c r="BR5" s="41"/>
+      <c r="BS5" s="41"/>
+      <c r="BT5" s="41"/>
+      <c r="BU5" s="41"/>
+      <c r="BV5" s="41"/>
+      <c r="BW5" s="41"/>
+      <c r="BX5" s="49"/>
+      <c r="BY5" s="41"/>
+      <c r="BZ5" s="41"/>
+      <c r="CA5" s="41"/>
+      <c r="CB5" s="41"/>
+      <c r="CC5" s="41"/>
+      <c r="CD5" s="41"/>
+      <c r="CE5" s="41"/>
+      <c r="CF5" s="41"/>
+      <c r="CG5" s="41"/>
+      <c r="CH5" s="41"/>
+      <c r="CI5" s="41"/>
+      <c r="CJ5" s="41"/>
+      <c r="CK5" s="41"/>
+      <c r="CL5" s="41"/>
+      <c r="CM5" s="41"/>
+      <c r="CN5" s="41"/>
+      <c r="CO5" s="41"/>
+      <c r="CP5" s="41"/>
+      <c r="CQ5" s="41"/>
+      <c r="CR5" s="41"/>
+      <c r="CS5" s="41"/>
+      <c r="CT5" s="41"/>
+      <c r="CU5" s="41"/>
+      <c r="CV5" s="41"/>
+      <c r="CW5" s="41"/>
+      <c r="CX5" s="41"/>
+      <c r="CY5" s="41"/>
+      <c r="CZ5" s="41"/>
+      <c r="DA5" s="41"/>
+      <c r="DB5" s="41"/>
+      <c r="DC5" s="41"/>
+      <c r="DD5" s="41"/>
+      <c r="DE5" s="41"/>
+      <c r="DF5" s="41"/>
+      <c r="DG5" s="41"/>
+      <c r="DH5" s="41"/>
+      <c r="DI5" s="41"/>
+      <c r="DJ5" s="41"/>
+      <c r="DK5" s="41"/>
+      <c r="DL5" s="41"/>
+      <c r="DM5" s="41"/>
+      <c r="DN5" s="41"/>
+      <c r="DO5" s="41"/>
+      <c r="DP5" s="41"/>
+      <c r="DQ5" s="41"/>
+      <c r="DR5" s="41"/>
+      <c r="DS5" s="41"/>
+      <c r="DT5" s="41"/>
+      <c r="DU5" s="41"/>
+      <c r="DV5" s="41"/>
+      <c r="DW5" s="41"/>
+      <c r="DX5" s="41"/>
+      <c r="DY5" s="41"/>
+      <c r="DZ5" s="41"/>
+      <c r="EA5" s="41"/>
+      <c r="EB5" s="41"/>
+      <c r="EC5" s="41"/>
+      <c r="ED5" s="41"/>
+      <c r="EE5" s="41"/>
+      <c r="EF5" s="41"/>
+      <c r="EG5" s="41"/>
+      <c r="EH5" s="41"/>
+      <c r="EI5" s="41"/>
+      <c r="EJ5" s="41"/>
+      <c r="EK5" s="41"/>
+      <c r="EL5" s="41"/>
+      <c r="EM5" s="41"/>
+      <c r="EN5" s="41"/>
+      <c r="EO5" s="41"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="54">
+      <c r="B6" s="45"/>
+      <c r="C6" s="46">
         <v>10</v>
       </c>
-      <c r="D6" s="55"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="46"/>
-      <c r="AB6" s="46"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="39"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="39"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="39"/>
-      <c r="BA6" s="39"/>
-      <c r="BB6" s="39"/>
-      <c r="BC6" s="39"/>
-      <c r="BD6" s="39"/>
-      <c r="BE6" s="39"/>
-      <c r="BF6" s="39"/>
-      <c r="BG6" s="39"/>
-      <c r="BH6" s="39"/>
-      <c r="BI6" s="39"/>
-      <c r="BJ6" s="39"/>
-      <c r="BK6" s="39"/>
-      <c r="BL6" s="39"/>
-      <c r="BM6" s="39"/>
-      <c r="BN6" s="39"/>
-      <c r="BO6" s="39"/>
-      <c r="BP6" s="39"/>
-      <c r="BQ6" s="39"/>
-      <c r="BR6" s="39"/>
-      <c r="BS6" s="39"/>
-      <c r="BT6" s="39"/>
-      <c r="BU6" s="39"/>
-      <c r="BV6" s="39"/>
-      <c r="BW6" s="39"/>
-      <c r="BX6" s="48"/>
-      <c r="BY6" s="39"/>
-      <c r="BZ6" s="39"/>
-      <c r="CA6" s="39"/>
-      <c r="CB6" s="39"/>
-      <c r="CC6" s="39"/>
-      <c r="CD6" s="39"/>
-      <c r="CE6" s="39"/>
-      <c r="CF6" s="39"/>
-      <c r="CG6" s="39"/>
-      <c r="CH6" s="39"/>
-      <c r="CI6" s="39"/>
-      <c r="CJ6" s="39"/>
-      <c r="CK6" s="39"/>
-      <c r="CL6" s="39"/>
-      <c r="CM6" s="39"/>
-      <c r="CN6" s="39"/>
-      <c r="CO6" s="39"/>
-      <c r="CP6" s="39"/>
-      <c r="CQ6" s="39"/>
-      <c r="CR6" s="39"/>
-      <c r="CS6" s="39"/>
-      <c r="CT6" s="39"/>
-      <c r="CU6" s="39"/>
-      <c r="CV6" s="39"/>
-      <c r="CW6" s="39"/>
-      <c r="CX6" s="39"/>
-      <c r="CY6" s="39"/>
-      <c r="CZ6" s="39"/>
-      <c r="DA6" s="39"/>
-      <c r="DB6" s="39"/>
-      <c r="DC6" s="39"/>
-      <c r="DD6" s="39"/>
-      <c r="DE6" s="39"/>
-      <c r="DF6" s="39"/>
-      <c r="DG6" s="39"/>
-      <c r="DH6" s="39"/>
-      <c r="DI6" s="39"/>
-      <c r="DJ6" s="39"/>
-      <c r="DK6" s="39"/>
-      <c r="DL6" s="39"/>
-      <c r="DM6" s="39"/>
-      <c r="DN6" s="39"/>
-      <c r="DO6" s="39"/>
-      <c r="DP6" s="39"/>
-      <c r="DQ6" s="39"/>
-      <c r="DR6" s="39"/>
-      <c r="DS6" s="39"/>
-      <c r="DT6" s="39"/>
-      <c r="DU6" s="39"/>
-      <c r="DV6" s="39"/>
-      <c r="DW6" s="39"/>
-      <c r="DX6" s="39"/>
-      <c r="DY6" s="39"/>
-      <c r="DZ6" s="39"/>
-      <c r="EA6" s="39"/>
-      <c r="EB6" s="39"/>
-      <c r="EC6" s="39"/>
-      <c r="ED6" s="39"/>
-      <c r="EE6" s="39"/>
-      <c r="EF6" s="39"/>
-      <c r="EG6" s="39"/>
-      <c r="EH6" s="39"/>
-      <c r="EI6" s="39"/>
-      <c r="EJ6" s="39"/>
-      <c r="EK6" s="39"/>
-      <c r="EL6" s="39"/>
-      <c r="EM6" s="39"/>
-      <c r="EN6" s="39"/>
-      <c r="EO6" s="39"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="53"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="51"/>
+      <c r="AB6" s="51"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="41"/>
+      <c r="AK6" s="41"/>
+      <c r="AL6" s="41"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="41"/>
+      <c r="AP6" s="41"/>
+      <c r="AQ6" s="41"/>
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="41"/>
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="41"/>
+      <c r="AY6" s="41"/>
+      <c r="AZ6" s="41"/>
+      <c r="BA6" s="41"/>
+      <c r="BB6" s="41"/>
+      <c r="BC6" s="41"/>
+      <c r="BD6" s="41"/>
+      <c r="BE6" s="41"/>
+      <c r="BF6" s="41"/>
+      <c r="BG6" s="41"/>
+      <c r="BH6" s="41"/>
+      <c r="BI6" s="41"/>
+      <c r="BJ6" s="41"/>
+      <c r="BK6" s="41"/>
+      <c r="BL6" s="41"/>
+      <c r="BM6" s="41"/>
+      <c r="BN6" s="41"/>
+      <c r="BO6" s="41"/>
+      <c r="BP6" s="41"/>
+      <c r="BQ6" s="41"/>
+      <c r="BR6" s="41"/>
+      <c r="BS6" s="41"/>
+      <c r="BT6" s="41"/>
+      <c r="BU6" s="41"/>
+      <c r="BV6" s="41"/>
+      <c r="BW6" s="41"/>
+      <c r="BX6" s="49"/>
+      <c r="BY6" s="41"/>
+      <c r="BZ6" s="41"/>
+      <c r="CA6" s="41"/>
+      <c r="CB6" s="41"/>
+      <c r="CC6" s="41"/>
+      <c r="CD6" s="41"/>
+      <c r="CE6" s="41"/>
+      <c r="CF6" s="41"/>
+      <c r="CG6" s="41"/>
+      <c r="CH6" s="41"/>
+      <c r="CI6" s="41"/>
+      <c r="CJ6" s="41"/>
+      <c r="CK6" s="41"/>
+      <c r="CL6" s="41"/>
+      <c r="CM6" s="41"/>
+      <c r="CN6" s="41"/>
+      <c r="CO6" s="41"/>
+      <c r="CP6" s="41"/>
+      <c r="CQ6" s="41"/>
+      <c r="CR6" s="41"/>
+      <c r="CS6" s="41"/>
+      <c r="CT6" s="41"/>
+      <c r="CU6" s="41"/>
+      <c r="CV6" s="41"/>
+      <c r="CW6" s="41"/>
+      <c r="CX6" s="41"/>
+      <c r="CY6" s="41"/>
+      <c r="CZ6" s="41"/>
+      <c r="DA6" s="41"/>
+      <c r="DB6" s="41"/>
+      <c r="DC6" s="41"/>
+      <c r="DD6" s="41"/>
+      <c r="DE6" s="41"/>
+      <c r="DF6" s="41"/>
+      <c r="DG6" s="41"/>
+      <c r="DH6" s="41"/>
+      <c r="DI6" s="41"/>
+      <c r="DJ6" s="41"/>
+      <c r="DK6" s="41"/>
+      <c r="DL6" s="41"/>
+      <c r="DM6" s="41"/>
+      <c r="DN6" s="41"/>
+      <c r="DO6" s="41"/>
+      <c r="DP6" s="41"/>
+      <c r="DQ6" s="41"/>
+      <c r="DR6" s="41"/>
+      <c r="DS6" s="41"/>
+      <c r="DT6" s="41"/>
+      <c r="DU6" s="41"/>
+      <c r="DV6" s="41"/>
+      <c r="DW6" s="41"/>
+      <c r="DX6" s="41"/>
+      <c r="DY6" s="41"/>
+      <c r="DZ6" s="41"/>
+      <c r="EA6" s="41"/>
+      <c r="EB6" s="41"/>
+      <c r="EC6" s="41"/>
+      <c r="ED6" s="41"/>
+      <c r="EE6" s="41"/>
+      <c r="EF6" s="41"/>
+      <c r="EG6" s="41"/>
+      <c r="EH6" s="41"/>
+      <c r="EI6" s="41"/>
+      <c r="EJ6" s="41"/>
+      <c r="EK6" s="41"/>
+      <c r="EL6" s="41"/>
+      <c r="EM6" s="41"/>
+      <c r="EN6" s="41"/>
+      <c r="EO6" s="41"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="54">
+      <c r="B7" s="48"/>
+      <c r="C7" s="46">
         <v>30</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="42"/>
-      <c r="W7" s="42"/>
-      <c r="X7" s="42"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="47"/>
-      <c r="AB7" s="47"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="40"/>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="40"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="40"/>
-      <c r="AL7" s="40"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="40"/>
-      <c r="AT7" s="40"/>
-      <c r="AU7" s="40"/>
-      <c r="AV7" s="40"/>
-      <c r="AW7" s="40"/>
-      <c r="AX7" s="40"/>
-      <c r="AY7" s="40"/>
-      <c r="AZ7" s="40"/>
-      <c r="BA7" s="40"/>
-      <c r="BB7" s="40"/>
-      <c r="BC7" s="40"/>
-      <c r="BD7" s="40"/>
-      <c r="BE7" s="40"/>
-      <c r="BF7" s="40"/>
-      <c r="BG7" s="40"/>
-      <c r="BH7" s="40"/>
-      <c r="BI7" s="40"/>
-      <c r="BJ7" s="40"/>
-      <c r="BK7" s="40"/>
-      <c r="BL7" s="40"/>
-      <c r="BM7" s="40"/>
-      <c r="BN7" s="40"/>
-      <c r="BO7" s="40"/>
-      <c r="BP7" s="40"/>
-      <c r="BQ7" s="40"/>
-      <c r="BR7" s="40"/>
-      <c r="BS7" s="40"/>
-      <c r="BT7" s="40"/>
-      <c r="BU7" s="40"/>
-      <c r="BV7" s="40"/>
-      <c r="BW7" s="40"/>
-      <c r="BX7" s="49"/>
-      <c r="BY7" s="40"/>
-      <c r="BZ7" s="40"/>
-      <c r="CA7" s="40"/>
-      <c r="CB7" s="40"/>
-      <c r="CC7" s="40"/>
-      <c r="CD7" s="40"/>
-      <c r="CE7" s="40"/>
-      <c r="CF7" s="40"/>
-      <c r="CG7" s="40"/>
-      <c r="CH7" s="40"/>
-      <c r="CI7" s="40"/>
-      <c r="CJ7" s="40"/>
-      <c r="CK7" s="40"/>
-      <c r="CL7" s="40"/>
-      <c r="CM7" s="40"/>
-      <c r="CN7" s="40"/>
-      <c r="CO7" s="40"/>
-      <c r="CP7" s="40"/>
-      <c r="CQ7" s="40"/>
-      <c r="CR7" s="40"/>
-      <c r="CS7" s="40"/>
-      <c r="CT7" s="40"/>
-      <c r="CU7" s="40"/>
-      <c r="CV7" s="40"/>
-      <c r="CW7" s="40"/>
-      <c r="CX7" s="40"/>
-      <c r="CY7" s="40"/>
-      <c r="CZ7" s="40"/>
-      <c r="DA7" s="40"/>
-      <c r="DB7" s="40"/>
-      <c r="DC7" s="40"/>
-      <c r="DD7" s="40"/>
-      <c r="DE7" s="40"/>
-      <c r="DF7" s="40"/>
-      <c r="DG7" s="40"/>
-      <c r="DH7" s="40"/>
-      <c r="DI7" s="40"/>
-      <c r="DJ7" s="40"/>
-      <c r="DK7" s="40"/>
-      <c r="DL7" s="40"/>
-      <c r="DM7" s="40"/>
-      <c r="DN7" s="40"/>
-      <c r="DO7" s="40"/>
-      <c r="DP7" s="40"/>
-      <c r="DQ7" s="40"/>
-      <c r="DR7" s="40"/>
-      <c r="DS7" s="40"/>
-      <c r="DT7" s="40"/>
-      <c r="DU7" s="40"/>
-      <c r="DV7" s="40"/>
-      <c r="DW7" s="40"/>
-      <c r="DX7" s="40"/>
-      <c r="DY7" s="40"/>
-      <c r="DZ7" s="40"/>
-      <c r="EA7" s="40"/>
-      <c r="EB7" s="40"/>
-      <c r="EC7" s="40"/>
-      <c r="ED7" s="40"/>
-      <c r="EE7" s="40"/>
-      <c r="EF7" s="40"/>
-      <c r="EG7" s="40"/>
-      <c r="EH7" s="40"/>
-      <c r="EI7" s="40"/>
-      <c r="EJ7" s="40"/>
-      <c r="EK7" s="40"/>
-      <c r="EL7" s="40"/>
-      <c r="EM7" s="40"/>
-      <c r="EN7" s="40"/>
-      <c r="EO7" s="40"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="42"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="52"/>
+      <c r="AB7" s="52"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="42"/>
+      <c r="AE7" s="42"/>
+      <c r="AF7" s="42"/>
+      <c r="AG7" s="42"/>
+      <c r="AH7" s="42"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="42"/>
+      <c r="AK7" s="42"/>
+      <c r="AL7" s="42"/>
+      <c r="AM7" s="42"/>
+      <c r="AN7" s="42"/>
+      <c r="AO7" s="42"/>
+      <c r="AP7" s="42"/>
+      <c r="AQ7" s="42"/>
+      <c r="AR7" s="42"/>
+      <c r="AS7" s="42"/>
+      <c r="AT7" s="42"/>
+      <c r="AU7" s="42"/>
+      <c r="AV7" s="42"/>
+      <c r="AW7" s="42"/>
+      <c r="AX7" s="42"/>
+      <c r="AY7" s="42"/>
+      <c r="AZ7" s="42"/>
+      <c r="BA7" s="42"/>
+      <c r="BB7" s="42"/>
+      <c r="BC7" s="42"/>
+      <c r="BD7" s="42"/>
+      <c r="BE7" s="42"/>
+      <c r="BF7" s="42"/>
+      <c r="BG7" s="42"/>
+      <c r="BH7" s="42"/>
+      <c r="BI7" s="42"/>
+      <c r="BJ7" s="42"/>
+      <c r="BK7" s="42"/>
+      <c r="BL7" s="42"/>
+      <c r="BM7" s="42"/>
+      <c r="BN7" s="42"/>
+      <c r="BO7" s="42"/>
+      <c r="BP7" s="42"/>
+      <c r="BQ7" s="42"/>
+      <c r="BR7" s="42"/>
+      <c r="BS7" s="42"/>
+      <c r="BT7" s="42"/>
+      <c r="BU7" s="42"/>
+      <c r="BV7" s="42"/>
+      <c r="BW7" s="42"/>
+      <c r="BX7" s="50"/>
+      <c r="BY7" s="42"/>
+      <c r="BZ7" s="42"/>
+      <c r="CA7" s="42"/>
+      <c r="CB7" s="42"/>
+      <c r="CC7" s="42"/>
+      <c r="CD7" s="42"/>
+      <c r="CE7" s="42"/>
+      <c r="CF7" s="42"/>
+      <c r="CG7" s="42"/>
+      <c r="CH7" s="42"/>
+      <c r="CI7" s="42"/>
+      <c r="CJ7" s="42"/>
+      <c r="CK7" s="42"/>
+      <c r="CL7" s="42"/>
+      <c r="CM7" s="42"/>
+      <c r="CN7" s="42"/>
+      <c r="CO7" s="42"/>
+      <c r="CP7" s="42"/>
+      <c r="CQ7" s="42"/>
+      <c r="CR7" s="42"/>
+      <c r="CS7" s="42"/>
+      <c r="CT7" s="42"/>
+      <c r="CU7" s="42"/>
+      <c r="CV7" s="42"/>
+      <c r="CW7" s="42"/>
+      <c r="CX7" s="42"/>
+      <c r="CY7" s="42"/>
+      <c r="CZ7" s="42"/>
+      <c r="DA7" s="42"/>
+      <c r="DB7" s="42"/>
+      <c r="DC7" s="42"/>
+      <c r="DD7" s="42"/>
+      <c r="DE7" s="42"/>
+      <c r="DF7" s="42"/>
+      <c r="DG7" s="42"/>
+      <c r="DH7" s="42"/>
+      <c r="DI7" s="42"/>
+      <c r="DJ7" s="42"/>
+      <c r="DK7" s="42"/>
+      <c r="DL7" s="42"/>
+      <c r="DM7" s="42"/>
+      <c r="DN7" s="42"/>
+      <c r="DO7" s="42"/>
+      <c r="DP7" s="42"/>
+      <c r="DQ7" s="42"/>
+      <c r="DR7" s="42"/>
+      <c r="DS7" s="42"/>
+      <c r="DT7" s="42"/>
+      <c r="DU7" s="42"/>
+      <c r="DV7" s="42"/>
+      <c r="DW7" s="42"/>
+      <c r="DX7" s="42"/>
+      <c r="DY7" s="42"/>
+      <c r="DZ7" s="42"/>
+      <c r="EA7" s="42"/>
+      <c r="EB7" s="42"/>
+      <c r="EC7" s="42"/>
+      <c r="ED7" s="42"/>
+      <c r="EE7" s="42"/>
+      <c r="EF7" s="42"/>
+      <c r="EG7" s="42"/>
+      <c r="EH7" s="42"/>
+      <c r="EI7" s="42"/>
+      <c r="EJ7" s="42"/>
+      <c r="EK7" s="42"/>
+      <c r="EL7" s="42"/>
+      <c r="EM7" s="42"/>
+      <c r="EN7" s="42"/>
+      <c r="EO7" s="42"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="58">
+      <c r="B8" s="35"/>
+      <c r="C8" s="36">
         <v>150</v>
       </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="59">
+      <c r="F8" s="29">
         <v>1</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="29">
         <v>2</v>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="29">
         <v>3</v>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="29">
         <v>4</v>
       </c>
-      <c r="J8" s="59">
+      <c r="J8" s="29">
         <v>5</v>
       </c>
-      <c r="K8" s="59">
+      <c r="K8" s="29">
         <v>6</v>
       </c>
-      <c r="L8" s="59">
+      <c r="L8" s="29">
         <v>7</v>
       </c>
-      <c r="M8" s="59">
+      <c r="M8" s="29">
         <v>8</v>
       </c>
-      <c r="N8" s="59">
+      <c r="N8" s="29">
         <v>9</v>
       </c>
-      <c r="O8" s="59">
+      <c r="O8" s="29">
         <v>10</v>
       </c>
-      <c r="P8" s="59">
+      <c r="P8" s="29">
         <v>11</v>
       </c>
-      <c r="Q8" s="59">
+      <c r="Q8" s="29">
         <v>12</v>
       </c>
-      <c r="R8" s="59">
+      <c r="R8" s="29">
         <v>13</v>
       </c>
-      <c r="S8" s="59">
+      <c r="S8" s="29">
         <v>14</v>
       </c>
-      <c r="T8" s="59">
+      <c r="T8" s="29">
         <v>15</v>
       </c>
-      <c r="U8" s="59">
+      <c r="U8" s="29">
         <v>16</v>
       </c>
-      <c r="V8" s="59">
+      <c r="V8" s="29">
         <v>17</v>
       </c>
-      <c r="W8" s="59">
+      <c r="W8" s="29">
         <v>18</v>
       </c>
-      <c r="X8" s="59">
+      <c r="X8" s="29">
         <v>19</v>
       </c>
-      <c r="Y8" s="59">
+      <c r="Y8" s="29">
         <v>20</v>
       </c>
-      <c r="Z8" s="59">
+      <c r="Z8" s="29">
         <v>21</v>
       </c>
-      <c r="AA8" s="59">
+      <c r="AA8" s="29">
         <v>22</v>
       </c>
-      <c r="AB8" s="59">
+      <c r="AB8" s="29">
         <v>23</v>
       </c>
-      <c r="AC8" s="59">
+      <c r="AC8" s="29">
         <v>24</v>
       </c>
-      <c r="AD8" s="59">
+      <c r="AD8" s="29">
         <v>25</v>
       </c>
-      <c r="AE8" s="59">
+      <c r="AE8" s="29">
         <v>26</v>
       </c>
-      <c r="AF8" s="59">
+      <c r="AF8" s="29">
         <v>27</v>
       </c>
-      <c r="AG8" s="59">
+      <c r="AG8" s="29">
         <v>28</v>
       </c>
-      <c r="AH8" s="59">
+      <c r="AH8" s="29">
         <v>29</v>
       </c>
-      <c r="AI8" s="59">
+      <c r="AI8" s="29">
         <v>30</v>
       </c>
-      <c r="AJ8" s="59">
+      <c r="AJ8" s="29">
         <v>31</v>
       </c>
-      <c r="AK8" s="59">
+      <c r="AK8" s="29">
         <v>32</v>
       </c>
-      <c r="AL8" s="59">
+      <c r="AL8" s="29">
         <v>33</v>
       </c>
-      <c r="AM8" s="59">
+      <c r="AM8" s="29">
         <v>34</v>
       </c>
-      <c r="AN8" s="59">
+      <c r="AN8" s="29">
         <v>35</v>
       </c>
-      <c r="AO8" s="59">
+      <c r="AO8" s="29">
         <v>36</v>
       </c>
-      <c r="AP8" s="59">
+      <c r="AP8" s="29">
         <v>37</v>
       </c>
-      <c r="AQ8" s="59">
+      <c r="AQ8" s="29">
         <v>38</v>
       </c>
-      <c r="AR8" s="59">
+      <c r="AR8" s="29">
         <v>39</v>
       </c>
-      <c r="AS8" s="59">
+      <c r="AS8" s="29">
         <v>40</v>
       </c>
-      <c r="AT8" s="59">
+      <c r="AT8" s="29">
         <v>41</v>
       </c>
-      <c r="AU8" s="59">
+      <c r="AU8" s="29">
         <v>42</v>
       </c>
-      <c r="AV8" s="59">
+      <c r="AV8" s="29">
         <v>43</v>
       </c>
-      <c r="AW8" s="59">
+      <c r="AW8" s="29">
         <v>44</v>
       </c>
-      <c r="AX8" s="59">
+      <c r="AX8" s="29">
         <v>45</v>
       </c>
-      <c r="AY8" s="59">
+      <c r="AY8" s="29">
         <v>46</v>
       </c>
-      <c r="AZ8" s="59">
+      <c r="AZ8" s="29">
         <v>47</v>
       </c>
-      <c r="BA8" s="59">
+      <c r="BA8" s="29">
         <v>48</v>
       </c>
-      <c r="BB8" s="59">
+      <c r="BB8" s="29">
         <v>49</v>
       </c>
-      <c r="BC8" s="59">
+      <c r="BC8" s="29">
         <v>50</v>
       </c>
-      <c r="BD8" s="59">
+      <c r="BD8" s="29">
         <v>51</v>
       </c>
-      <c r="BE8" s="59">
+      <c r="BE8" s="29">
         <v>52</v>
       </c>
-      <c r="BF8" s="59">
+      <c r="BF8" s="29">
         <v>53</v>
       </c>
-      <c r="BG8" s="59">
+      <c r="BG8" s="29">
         <v>54</v>
       </c>
-      <c r="BH8" s="59">
+      <c r="BH8" s="29">
         <v>55</v>
       </c>
-      <c r="BI8" s="59">
+      <c r="BI8" s="29">
         <v>56</v>
       </c>
-      <c r="BJ8" s="59">
+      <c r="BJ8" s="29">
         <v>57</v>
       </c>
-      <c r="BK8" s="59">
+      <c r="BK8" s="29">
         <v>58</v>
       </c>
-      <c r="BL8" s="59">
+      <c r="BL8" s="29">
         <v>59</v>
       </c>
-      <c r="BM8" s="59">
+      <c r="BM8" s="29">
         <v>60</v>
       </c>
-      <c r="BN8" s="59">
+      <c r="BN8" s="29">
         <v>61</v>
       </c>
-      <c r="BO8" s="59">
+      <c r="BO8" s="29">
         <v>62</v>
       </c>
-      <c r="BP8" s="59">
+      <c r="BP8" s="29">
         <v>63</v>
       </c>
-      <c r="BQ8" s="59">
+      <c r="BQ8" s="29">
         <v>64</v>
       </c>
-      <c r="BR8" s="59">
+      <c r="BR8" s="29">
         <v>65</v>
       </c>
-      <c r="BS8" s="59">
+      <c r="BS8" s="29">
         <v>66</v>
       </c>
-      <c r="BT8" s="59">
+      <c r="BT8" s="29">
         <v>67</v>
       </c>
-      <c r="BU8" s="59">
+      <c r="BU8" s="29">
         <v>68</v>
       </c>
-      <c r="BV8" s="59">
+      <c r="BV8" s="29">
         <v>69</v>
       </c>
-      <c r="BW8" s="59">
+      <c r="BW8" s="29">
         <v>70</v>
       </c>
-      <c r="BX8" s="59">
+      <c r="BX8" s="29">
         <v>71</v>
       </c>
-      <c r="BY8" s="59">
+      <c r="BY8" s="29">
         <v>72</v>
       </c>
-      <c r="BZ8" s="59">
+      <c r="BZ8" s="29">
         <v>73</v>
       </c>
-      <c r="CA8" s="59">
+      <c r="CA8" s="29">
         <v>74</v>
       </c>
-      <c r="CB8" s="59">
+      <c r="CB8" s="29">
         <v>75</v>
       </c>
-      <c r="CC8" s="59">
+      <c r="CC8" s="29">
         <v>76</v>
       </c>
-      <c r="CD8" s="59">
+      <c r="CD8" s="29">
         <v>77</v>
       </c>
-      <c r="CE8" s="59">
+      <c r="CE8" s="29">
         <v>78</v>
       </c>
-      <c r="CF8" s="59">
+      <c r="CF8" s="29">
         <v>79</v>
       </c>
-      <c r="CG8" s="59">
+      <c r="CG8" s="29">
         <v>80</v>
       </c>
-      <c r="CH8" s="59">
+      <c r="CH8" s="29">
         <v>81</v>
       </c>
-      <c r="CI8" s="59">
+      <c r="CI8" s="29">
         <v>82</v>
       </c>
-      <c r="CJ8" s="59">
+      <c r="CJ8" s="29">
         <v>83</v>
       </c>
-      <c r="CK8" s="59">
+      <c r="CK8" s="29">
         <v>84</v>
       </c>
-      <c r="CL8" s="59">
+      <c r="CL8" s="29">
         <v>85</v>
       </c>
-      <c r="CM8" s="59">
+      <c r="CM8" s="29">
         <v>86</v>
       </c>
-      <c r="CN8" s="59">
+      <c r="CN8" s="29">
         <v>87</v>
       </c>
-      <c r="CO8" s="59">
+      <c r="CO8" s="29">
         <v>88</v>
       </c>
-      <c r="CP8" s="59">
+      <c r="CP8" s="29">
         <v>89</v>
       </c>
-      <c r="CQ8" s="59">
+      <c r="CQ8" s="29">
         <v>90</v>
       </c>
-      <c r="CR8" s="59">
+      <c r="CR8" s="29">
         <v>91</v>
       </c>
-      <c r="CS8" s="59">
+      <c r="CS8" s="29">
         <v>92</v>
       </c>
-      <c r="CT8" s="59">
+      <c r="CT8" s="29">
         <v>93</v>
       </c>
-      <c r="CU8" s="59">
+      <c r="CU8" s="29">
         <v>94</v>
       </c>
-      <c r="CV8" s="59">
+      <c r="CV8" s="29">
         <v>95</v>
       </c>
-      <c r="CW8" s="59">
+      <c r="CW8" s="29">
         <v>96</v>
       </c>
-      <c r="CX8" s="59">
+      <c r="CX8" s="29">
         <v>97</v>
       </c>
-      <c r="CY8" s="59">
+      <c r="CY8" s="29">
         <v>98</v>
       </c>
-      <c r="CZ8" s="59">
+      <c r="CZ8" s="29">
         <v>99</v>
       </c>
-      <c r="DA8" s="59">
+      <c r="DA8" s="29">
         <v>100</v>
       </c>
-      <c r="DB8" s="59">
+      <c r="DB8" s="29">
         <v>101</v>
       </c>
-      <c r="DC8" s="59">
+      <c r="DC8" s="29">
         <v>102</v>
       </c>
-      <c r="DD8" s="59">
+      <c r="DD8" s="29">
         <v>103</v>
       </c>
-      <c r="DE8" s="59">
+      <c r="DE8" s="29">
         <v>104</v>
       </c>
-      <c r="DF8" s="59">
+      <c r="DF8" s="29">
         <v>105</v>
       </c>
-      <c r="DG8" s="59">
+      <c r="DG8" s="29">
         <v>106</v>
       </c>
-      <c r="DH8" s="59">
+      <c r="DH8" s="29">
         <v>107</v>
       </c>
-      <c r="DI8" s="59">
+      <c r="DI8" s="29">
         <v>108</v>
       </c>
-      <c r="DJ8" s="59">
+      <c r="DJ8" s="29">
         <v>109</v>
       </c>
-      <c r="DK8" s="59">
+      <c r="DK8" s="29">
         <v>110</v>
       </c>
-      <c r="DL8" s="59">
+      <c r="DL8" s="29">
         <v>111</v>
       </c>
-      <c r="DM8" s="59">
+      <c r="DM8" s="29">
         <v>112</v>
       </c>
-      <c r="DN8" s="59">
+      <c r="DN8" s="29">
         <v>113</v>
       </c>
-      <c r="DO8" s="59">
+      <c r="DO8" s="29">
         <v>114</v>
       </c>
-      <c r="DP8" s="59">
+      <c r="DP8" s="29">
         <v>115</v>
       </c>
-      <c r="DQ8" s="59">
+      <c r="DQ8" s="29">
         <v>116</v>
       </c>
-      <c r="DR8" s="59">
+      <c r="DR8" s="29">
         <v>117</v>
       </c>
-      <c r="DS8" s="59">
+      <c r="DS8" s="29">
         <v>118</v>
       </c>
-      <c r="DT8" s="59">
+      <c r="DT8" s="29">
         <v>119</v>
       </c>
-      <c r="DU8" s="59">
+      <c r="DU8" s="29">
         <v>120</v>
       </c>
-      <c r="DV8" s="59">
+      <c r="DV8" s="29">
         <v>121</v>
       </c>
-      <c r="DW8" s="59">
+      <c r="DW8" s="29">
         <v>122</v>
       </c>
-      <c r="DX8" s="59">
+      <c r="DX8" s="29">
         <v>123</v>
       </c>
-      <c r="DY8" s="59">
+      <c r="DY8" s="29">
         <v>124</v>
       </c>
-      <c r="DZ8" s="59">
+      <c r="DZ8" s="29">
         <v>125</v>
       </c>
-      <c r="EA8" s="59">
+      <c r="EA8" s="29">
         <v>126</v>
       </c>
-      <c r="EB8" s="59">
+      <c r="EB8" s="29">
         <v>127</v>
       </c>
-      <c r="EC8" s="59">
+      <c r="EC8" s="29">
         <v>128</v>
       </c>
-      <c r="ED8" s="59">
+      <c r="ED8" s="29">
         <v>129</v>
       </c>
-      <c r="EE8" s="59">
+      <c r="EE8" s="29">
         <v>130</v>
       </c>
-      <c r="EF8" s="59">
+      <c r="EF8" s="29">
         <v>131</v>
       </c>
-      <c r="EG8" s="59">
+      <c r="EG8" s="29">
         <v>132</v>
       </c>
-      <c r="EH8" s="59">
+      <c r="EH8" s="29">
         <v>133</v>
       </c>
-      <c r="EI8" s="59">
+      <c r="EI8" s="29">
         <v>134</v>
       </c>
-      <c r="EJ8" s="59">
+      <c r="EJ8" s="29">
         <v>135</v>
       </c>
-      <c r="EK8" s="59">
+      <c r="EK8" s="29">
         <v>136</v>
       </c>
-      <c r="EL8" s="59">
+      <c r="EL8" s="29">
         <v>137</v>
       </c>
-      <c r="EM8" s="59">
+      <c r="EM8" s="29">
         <v>138</v>
       </c>
-      <c r="EN8" s="59">
+      <c r="EN8" s="29">
         <v>139</v>
       </c>
-      <c r="EO8" s="59">
+      <c r="EO8" s="29">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="62"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="60"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="60"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="60"/>
-      <c r="AD9" s="60"/>
-      <c r="AE9" s="60"/>
-      <c r="AF9" s="60"/>
-      <c r="AG9" s="60"/>
-      <c r="AH9" s="60"/>
-      <c r="AI9" s="60"/>
-      <c r="AJ9" s="60"/>
-      <c r="AK9" s="60"/>
-      <c r="AL9" s="60"/>
-      <c r="AM9" s="60"/>
-      <c r="AN9" s="60"/>
-      <c r="AO9" s="60"/>
-      <c r="AP9" s="60"/>
-      <c r="AQ9" s="60"/>
-      <c r="AR9" s="60"/>
-      <c r="AS9" s="60"/>
-      <c r="AT9" s="60"/>
-      <c r="AU9" s="60"/>
-      <c r="AV9" s="60"/>
-      <c r="AW9" s="60"/>
-      <c r="AX9" s="60"/>
-      <c r="AY9" s="60"/>
-      <c r="AZ9" s="60"/>
-      <c r="BA9" s="60"/>
-      <c r="BB9" s="60"/>
-      <c r="BC9" s="60"/>
-      <c r="BD9" s="60"/>
-      <c r="BE9" s="60"/>
-      <c r="BF9" s="60"/>
-      <c r="BG9" s="60"/>
-      <c r="BH9" s="60"/>
-      <c r="BI9" s="60"/>
-      <c r="BJ9" s="60"/>
-      <c r="BK9" s="60"/>
-      <c r="BL9" s="60"/>
-      <c r="BM9" s="60"/>
-      <c r="BN9" s="60"/>
-      <c r="BO9" s="60"/>
-      <c r="BP9" s="60"/>
-      <c r="BQ9" s="60"/>
-      <c r="BR9" s="60"/>
-      <c r="BS9" s="60"/>
-      <c r="BT9" s="60"/>
-      <c r="BU9" s="60"/>
-      <c r="BV9" s="60"/>
-      <c r="BW9" s="60"/>
-      <c r="BX9" s="60"/>
-      <c r="BY9" s="60"/>
-      <c r="BZ9" s="60"/>
-      <c r="CA9" s="60"/>
-      <c r="CB9" s="60"/>
-      <c r="CC9" s="60"/>
-      <c r="CD9" s="60"/>
-      <c r="CE9" s="60"/>
-      <c r="CF9" s="60"/>
-      <c r="CG9" s="60"/>
-      <c r="CH9" s="60"/>
-      <c r="CI9" s="60"/>
-      <c r="CJ9" s="60"/>
-      <c r="CK9" s="60"/>
-      <c r="CL9" s="60"/>
-      <c r="CM9" s="60"/>
-      <c r="CN9" s="60"/>
-      <c r="CO9" s="60"/>
-      <c r="CP9" s="60"/>
-      <c r="CQ9" s="60"/>
-      <c r="CR9" s="60"/>
-      <c r="CS9" s="60"/>
-      <c r="CT9" s="60"/>
-      <c r="CU9" s="60"/>
-      <c r="CV9" s="60"/>
-      <c r="CW9" s="60"/>
-      <c r="CX9" s="60"/>
-      <c r="CY9" s="60"/>
-      <c r="CZ9" s="60"/>
-      <c r="DA9" s="60"/>
-      <c r="DB9" s="60"/>
-      <c r="DC9" s="60"/>
-      <c r="DD9" s="60"/>
-      <c r="DE9" s="60"/>
-      <c r="DF9" s="60"/>
-      <c r="DG9" s="60"/>
-      <c r="DH9" s="60"/>
-      <c r="DI9" s="60"/>
-      <c r="DJ9" s="60"/>
-      <c r="DK9" s="60"/>
-      <c r="DL9" s="60"/>
-      <c r="DM9" s="60"/>
-      <c r="DN9" s="60"/>
-      <c r="DO9" s="60"/>
-      <c r="DP9" s="60"/>
-      <c r="DQ9" s="60"/>
-      <c r="DR9" s="60"/>
-      <c r="DS9" s="60"/>
-      <c r="DT9" s="60"/>
-      <c r="DU9" s="60"/>
-      <c r="DV9" s="60"/>
-      <c r="DW9" s="60"/>
-      <c r="DX9" s="60"/>
-      <c r="DY9" s="60"/>
-      <c r="DZ9" s="60"/>
-      <c r="EA9" s="60"/>
-      <c r="EB9" s="60"/>
-      <c r="EC9" s="60"/>
-      <c r="ED9" s="60"/>
-      <c r="EE9" s="60"/>
-      <c r="EF9" s="60"/>
-      <c r="EG9" s="60"/>
-      <c r="EH9" s="60"/>
-      <c r="EI9" s="60"/>
-      <c r="EJ9" s="60"/>
-      <c r="EK9" s="60"/>
-      <c r="EL9" s="60"/>
-      <c r="EM9" s="60"/>
-      <c r="EN9" s="60"/>
-      <c r="EO9" s="60"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="30"/>
+      <c r="AP9" s="30"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="30"/>
+      <c r="AS9" s="30"/>
+      <c r="AT9" s="30"/>
+      <c r="AU9" s="30"/>
+      <c r="AV9" s="30"/>
+      <c r="AW9" s="30"/>
+      <c r="AX9" s="30"/>
+      <c r="AY9" s="30"/>
+      <c r="AZ9" s="30"/>
+      <c r="BA9" s="30"/>
+      <c r="BB9" s="30"/>
+      <c r="BC9" s="30"/>
+      <c r="BD9" s="30"/>
+      <c r="BE9" s="30"/>
+      <c r="BF9" s="30"/>
+      <c r="BG9" s="30"/>
+      <c r="BH9" s="30"/>
+      <c r="BI9" s="30"/>
+      <c r="BJ9" s="30"/>
+      <c r="BK9" s="30"/>
+      <c r="BL9" s="30"/>
+      <c r="BM9" s="30"/>
+      <c r="BN9" s="30"/>
+      <c r="BO9" s="30"/>
+      <c r="BP9" s="30"/>
+      <c r="BQ9" s="30"/>
+      <c r="BR9" s="30"/>
+      <c r="BS9" s="30"/>
+      <c r="BT9" s="30"/>
+      <c r="BU9" s="30"/>
+      <c r="BV9" s="30"/>
+      <c r="BW9" s="30"/>
+      <c r="BX9" s="30"/>
+      <c r="BY9" s="30"/>
+      <c r="BZ9" s="30"/>
+      <c r="CA9" s="30"/>
+      <c r="CB9" s="30"/>
+      <c r="CC9" s="30"/>
+      <c r="CD9" s="30"/>
+      <c r="CE9" s="30"/>
+      <c r="CF9" s="30"/>
+      <c r="CG9" s="30"/>
+      <c r="CH9" s="30"/>
+      <c r="CI9" s="30"/>
+      <c r="CJ9" s="30"/>
+      <c r="CK9" s="30"/>
+      <c r="CL9" s="30"/>
+      <c r="CM9" s="30"/>
+      <c r="CN9" s="30"/>
+      <c r="CO9" s="30"/>
+      <c r="CP9" s="30"/>
+      <c r="CQ9" s="30"/>
+      <c r="CR9" s="30"/>
+      <c r="CS9" s="30"/>
+      <c r="CT9" s="30"/>
+      <c r="CU9" s="30"/>
+      <c r="CV9" s="30"/>
+      <c r="CW9" s="30"/>
+      <c r="CX9" s="30"/>
+      <c r="CY9" s="30"/>
+      <c r="CZ9" s="30"/>
+      <c r="DA9" s="30"/>
+      <c r="DB9" s="30"/>
+      <c r="DC9" s="30"/>
+      <c r="DD9" s="30"/>
+      <c r="DE9" s="30"/>
+      <c r="DF9" s="30"/>
+      <c r="DG9" s="30"/>
+      <c r="DH9" s="30"/>
+      <c r="DI9" s="30"/>
+      <c r="DJ9" s="30"/>
+      <c r="DK9" s="30"/>
+      <c r="DL9" s="30"/>
+      <c r="DM9" s="30"/>
+      <c r="DN9" s="30"/>
+      <c r="DO9" s="30"/>
+      <c r="DP9" s="30"/>
+      <c r="DQ9" s="30"/>
+      <c r="DR9" s="30"/>
+      <c r="DS9" s="30"/>
+      <c r="DT9" s="30"/>
+      <c r="DU9" s="30"/>
+      <c r="DV9" s="30"/>
+      <c r="DW9" s="30"/>
+      <c r="DX9" s="30"/>
+      <c r="DY9" s="30"/>
+      <c r="DZ9" s="30"/>
+      <c r="EA9" s="30"/>
+      <c r="EB9" s="30"/>
+      <c r="EC9" s="30"/>
+      <c r="ED9" s="30"/>
+      <c r="EE9" s="30"/>
+      <c r="EF9" s="30"/>
+      <c r="EG9" s="30"/>
+      <c r="EH9" s="30"/>
+      <c r="EI9" s="30"/>
+      <c r="EJ9" s="30"/>
+      <c r="EK9" s="30"/>
+      <c r="EL9" s="30"/>
+      <c r="EM9" s="30"/>
+      <c r="EN9" s="30"/>
+      <c r="EO9" s="30"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="61"/>
-      <c r="B10" s="62"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="9"/>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -3355,7 +3362,7 @@
       </c>
       <c r="D12" s="14">
         <f t="shared" ref="D12:D28" si="0">COUNT(F12:EO12)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="11"/>
@@ -3463,7 +3470,9 @@
       <c r="BX12" s="11">
         <v>0</v>
       </c>
-      <c r="BY12" s="11"/>
+      <c r="BY12" s="11">
+        <v>0</v>
+      </c>
       <c r="BZ12" s="11"/>
       <c r="CA12" s="11"/>
       <c r="CB12" s="11"/>
@@ -4437,113 +4446,113 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AO17" s="22" t="s">
+      <c r="AO17" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="23"/>
-      <c r="AR17" s="23"/>
-      <c r="AS17" s="23"/>
-      <c r="AT17" s="23"/>
-      <c r="AU17" s="23"/>
-      <c r="AV17" s="23"/>
-      <c r="AW17" s="23"/>
-      <c r="AX17" s="23"/>
-      <c r="AY17" s="23"/>
-      <c r="AZ17" s="23"/>
-      <c r="BA17" s="23"/>
-      <c r="BB17" s="23"/>
-      <c r="BC17" s="23"/>
-      <c r="BD17" s="23"/>
-      <c r="BE17" s="23"/>
-      <c r="BF17" s="23"/>
-      <c r="BG17" s="23"/>
-      <c r="BH17" s="23"/>
-      <c r="BI17" s="23"/>
-      <c r="BJ17" s="23"/>
-      <c r="BK17" s="23"/>
-      <c r="BL17" s="23"/>
-      <c r="BM17" s="23"/>
-      <c r="BN17" s="23"/>
-      <c r="BO17" s="23"/>
-      <c r="BP17" s="23"/>
-      <c r="BQ17" s="23"/>
-      <c r="BR17" s="23"/>
-      <c r="BS17" s="23"/>
-      <c r="BT17" s="23"/>
-      <c r="BU17" s="23"/>
-      <c r="BV17" s="23"/>
-      <c r="BW17" s="23"/>
-      <c r="BX17" s="23"/>
-      <c r="BY17" s="23"/>
-      <c r="BZ17" s="23"/>
-      <c r="CA17" s="23"/>
-      <c r="CB17" s="23"/>
-      <c r="CC17" s="23"/>
-      <c r="CD17" s="23"/>
-      <c r="CE17" s="23"/>
-      <c r="CF17" s="23"/>
-      <c r="CG17" s="23"/>
-      <c r="CH17" s="23"/>
-      <c r="CI17" s="23"/>
-      <c r="CJ17" s="23"/>
-      <c r="CK17" s="23"/>
-      <c r="CL17" s="23"/>
-      <c r="CM17" s="23"/>
-      <c r="CN17" s="23"/>
-      <c r="CO17" s="23"/>
-      <c r="CP17" s="23"/>
-      <c r="CQ17" s="23"/>
-      <c r="CR17" s="23"/>
-      <c r="CS17" s="23"/>
-      <c r="CT17" s="23"/>
-      <c r="CU17" s="23"/>
-      <c r="CV17" s="23"/>
-      <c r="CW17" s="23"/>
-      <c r="CX17" s="23"/>
-      <c r="CY17" s="23"/>
-      <c r="CZ17" s="23"/>
-      <c r="DA17" s="23"/>
-      <c r="DB17" s="23"/>
-      <c r="DC17" s="23"/>
-      <c r="DD17" s="23"/>
-      <c r="DE17" s="23"/>
-      <c r="DF17" s="23"/>
-      <c r="DG17" s="23"/>
-      <c r="DH17" s="23"/>
-      <c r="DI17" s="23"/>
-      <c r="DJ17" s="23"/>
-      <c r="DK17" s="23"/>
-      <c r="DL17" s="23"/>
-      <c r="DM17" s="23"/>
-      <c r="DN17" s="23"/>
-      <c r="DO17" s="23"/>
-      <c r="DP17" s="23"/>
-      <c r="DQ17" s="23"/>
-      <c r="DR17" s="23"/>
-      <c r="DS17" s="23"/>
-      <c r="DT17" s="23"/>
-      <c r="DU17" s="23"/>
-      <c r="DV17" s="23"/>
-      <c r="DW17" s="23"/>
-      <c r="DX17" s="23"/>
-      <c r="DY17" s="23"/>
-      <c r="DZ17" s="23"/>
-      <c r="EA17" s="23"/>
-      <c r="EB17" s="23"/>
-      <c r="EC17" s="23"/>
-      <c r="ED17" s="23"/>
-      <c r="EE17" s="23"/>
-      <c r="EF17" s="23"/>
-      <c r="EG17" s="23"/>
-      <c r="EH17" s="23"/>
-      <c r="EI17" s="23"/>
-      <c r="EJ17" s="23"/>
-      <c r="EK17" s="23"/>
-      <c r="EL17" s="23"/>
-      <c r="EM17" s="23"/>
-      <c r="EN17" s="23"/>
-      <c r="EO17" s="24"/>
+      <c r="AP17" s="56"/>
+      <c r="AQ17" s="56"/>
+      <c r="AR17" s="56"/>
+      <c r="AS17" s="56"/>
+      <c r="AT17" s="56"/>
+      <c r="AU17" s="56"/>
+      <c r="AV17" s="56"/>
+      <c r="AW17" s="56"/>
+      <c r="AX17" s="56"/>
+      <c r="AY17" s="56"/>
+      <c r="AZ17" s="56"/>
+      <c r="BA17" s="56"/>
+      <c r="BB17" s="56"/>
+      <c r="BC17" s="56"/>
+      <c r="BD17" s="56"/>
+      <c r="BE17" s="56"/>
+      <c r="BF17" s="56"/>
+      <c r="BG17" s="56"/>
+      <c r="BH17" s="56"/>
+      <c r="BI17" s="56"/>
+      <c r="BJ17" s="56"/>
+      <c r="BK17" s="56"/>
+      <c r="BL17" s="56"/>
+      <c r="BM17" s="56"/>
+      <c r="BN17" s="56"/>
+      <c r="BO17" s="56"/>
+      <c r="BP17" s="56"/>
+      <c r="BQ17" s="56"/>
+      <c r="BR17" s="56"/>
+      <c r="BS17" s="56"/>
+      <c r="BT17" s="56"/>
+      <c r="BU17" s="56"/>
+      <c r="BV17" s="56"/>
+      <c r="BW17" s="56"/>
+      <c r="BX17" s="56"/>
+      <c r="BY17" s="56"/>
+      <c r="BZ17" s="56"/>
+      <c r="CA17" s="56"/>
+      <c r="CB17" s="56"/>
+      <c r="CC17" s="56"/>
+      <c r="CD17" s="56"/>
+      <c r="CE17" s="56"/>
+      <c r="CF17" s="56"/>
+      <c r="CG17" s="56"/>
+      <c r="CH17" s="56"/>
+      <c r="CI17" s="56"/>
+      <c r="CJ17" s="56"/>
+      <c r="CK17" s="56"/>
+      <c r="CL17" s="56"/>
+      <c r="CM17" s="56"/>
+      <c r="CN17" s="56"/>
+      <c r="CO17" s="56"/>
+      <c r="CP17" s="56"/>
+      <c r="CQ17" s="56"/>
+      <c r="CR17" s="56"/>
+      <c r="CS17" s="56"/>
+      <c r="CT17" s="56"/>
+      <c r="CU17" s="56"/>
+      <c r="CV17" s="56"/>
+      <c r="CW17" s="56"/>
+      <c r="CX17" s="56"/>
+      <c r="CY17" s="56"/>
+      <c r="CZ17" s="56"/>
+      <c r="DA17" s="56"/>
+      <c r="DB17" s="56"/>
+      <c r="DC17" s="56"/>
+      <c r="DD17" s="56"/>
+      <c r="DE17" s="56"/>
+      <c r="DF17" s="56"/>
+      <c r="DG17" s="56"/>
+      <c r="DH17" s="56"/>
+      <c r="DI17" s="56"/>
+      <c r="DJ17" s="56"/>
+      <c r="DK17" s="56"/>
+      <c r="DL17" s="56"/>
+      <c r="DM17" s="56"/>
+      <c r="DN17" s="56"/>
+      <c r="DO17" s="56"/>
+      <c r="DP17" s="56"/>
+      <c r="DQ17" s="56"/>
+      <c r="DR17" s="56"/>
+      <c r="DS17" s="56"/>
+      <c r="DT17" s="56"/>
+      <c r="DU17" s="56"/>
+      <c r="DV17" s="56"/>
+      <c r="DW17" s="56"/>
+      <c r="DX17" s="56"/>
+      <c r="DY17" s="56"/>
+      <c r="DZ17" s="56"/>
+      <c r="EA17" s="56"/>
+      <c r="EB17" s="56"/>
+      <c r="EC17" s="56"/>
+      <c r="ED17" s="56"/>
+      <c r="EE17" s="56"/>
+      <c r="EF17" s="56"/>
+      <c r="EG17" s="56"/>
+      <c r="EH17" s="56"/>
+      <c r="EI17" s="56"/>
+      <c r="EJ17" s="56"/>
+      <c r="EK17" s="56"/>
+      <c r="EL17" s="56"/>
+      <c r="EM17" s="56"/>
+      <c r="EN17" s="56"/>
+      <c r="EO17" s="57"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
@@ -5389,7 +5398,7 @@
       </c>
       <c r="D22" s="14">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="11"/>
@@ -5515,7 +5524,9 @@
       <c r="BX22" s="11">
         <v>0</v>
       </c>
-      <c r="BY22" s="11"/>
+      <c r="BY22" s="11">
+        <v>0</v>
+      </c>
       <c r="BZ22" s="11"/>
       <c r="CA22" s="11"/>
       <c r="CB22" s="11"/>
@@ -6095,7 +6106,7 @@
       </c>
       <c r="D25" s="14">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="11"/>
@@ -6237,7 +6248,9 @@
       <c r="BX25" s="11">
         <v>0</v>
       </c>
-      <c r="BY25" s="11"/>
+      <c r="BY25" s="11">
+        <v>0</v>
+      </c>
       <c r="BZ25" s="11"/>
       <c r="CA25" s="11"/>
       <c r="CB25" s="11"/>
@@ -6319,7 +6332,7 @@
       </c>
       <c r="D26" s="14">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="11"/>
@@ -6445,7 +6458,9 @@
       <c r="BX26" s="11">
         <v>0</v>
       </c>
-      <c r="BY26" s="11"/>
+      <c r="BY26" s="11">
+        <v>0</v>
+      </c>
       <c r="BZ26" s="11"/>
       <c r="CA26" s="11"/>
       <c r="CB26" s="11"/>
@@ -6527,7 +6542,7 @@
       </c>
       <c r="D27" s="14">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="11"/>
@@ -6729,7 +6744,9 @@
       <c r="BX27" s="11">
         <v>0</v>
       </c>
-      <c r="BY27" s="11"/>
+      <c r="BY27" s="11">
+        <v>0</v>
+      </c>
       <c r="BZ27" s="11"/>
       <c r="CA27" s="11"/>
       <c r="CB27" s="11"/>
@@ -6813,149 +6830,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="64"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="64"/>
-      <c r="R28" s="64"/>
-      <c r="S28" s="64"/>
-      <c r="T28" s="64"/>
-      <c r="U28" s="64"/>
-      <c r="V28" s="64"/>
-      <c r="W28" s="64"/>
-      <c r="X28" s="64"/>
-      <c r="Y28" s="64"/>
-      <c r="Z28" s="64"/>
-      <c r="AA28" s="64"/>
-      <c r="AB28" s="64"/>
-      <c r="AC28" s="64"/>
-      <c r="AD28" s="64"/>
-      <c r="AE28" s="64"/>
-      <c r="AF28" s="64"/>
-      <c r="AG28" s="64"/>
-      <c r="AH28" s="64"/>
-      <c r="AI28" s="64"/>
-      <c r="AJ28" s="64"/>
-      <c r="AK28" s="64"/>
-      <c r="AL28" s="64"/>
-      <c r="AM28" s="64"/>
-      <c r="AN28" s="64"/>
-      <c r="AO28" s="64"/>
-      <c r="AP28" s="64"/>
-      <c r="AQ28" s="64"/>
-      <c r="AR28" s="64"/>
-      <c r="AS28" s="64"/>
-      <c r="AT28" s="64"/>
-      <c r="AU28" s="64"/>
-      <c r="AV28" s="64"/>
-      <c r="AW28" s="64"/>
-      <c r="AX28" s="64"/>
-      <c r="AY28" s="64"/>
-      <c r="AZ28" s="64"/>
-      <c r="BA28" s="64"/>
-      <c r="BB28" s="64"/>
-      <c r="BC28" s="64"/>
-      <c r="BD28" s="64"/>
-      <c r="BE28" s="64"/>
-      <c r="BF28" s="64"/>
-      <c r="BG28" s="64"/>
-      <c r="BH28" s="64"/>
-      <c r="BI28" s="64"/>
-      <c r="BJ28" s="64"/>
-      <c r="BK28" s="64"/>
-      <c r="BL28" s="64"/>
-      <c r="BM28" s="64"/>
-      <c r="BN28" s="64"/>
-      <c r="BO28" s="64"/>
-      <c r="BP28" s="64"/>
-      <c r="BQ28" s="64"/>
-      <c r="BR28" s="64"/>
-      <c r="BS28" s="64"/>
-      <c r="BT28" s="64"/>
-      <c r="BU28" s="64"/>
-      <c r="BV28" s="64"/>
-      <c r="BW28" s="64"/>
-      <c r="BX28" s="64"/>
-      <c r="BY28" s="64"/>
-      <c r="BZ28" s="64"/>
-      <c r="CA28" s="64"/>
-      <c r="CB28" s="64"/>
-      <c r="CC28" s="64"/>
-      <c r="CD28" s="64"/>
-      <c r="CE28" s="64"/>
-      <c r="CF28" s="64"/>
-      <c r="CG28" s="64"/>
-      <c r="CH28" s="64"/>
-      <c r="CI28" s="64"/>
-      <c r="CJ28" s="64"/>
-      <c r="CK28" s="64"/>
-      <c r="CL28" s="64"/>
-      <c r="CM28" s="64"/>
-      <c r="CN28" s="64"/>
-      <c r="CO28" s="64"/>
-      <c r="CP28" s="64"/>
-      <c r="CQ28" s="64"/>
-      <c r="CR28" s="64"/>
-      <c r="CS28" s="64"/>
-      <c r="CT28" s="64"/>
-      <c r="CU28" s="64"/>
-      <c r="CV28" s="64"/>
-      <c r="CW28" s="64"/>
-      <c r="CX28" s="64"/>
-      <c r="CY28" s="64"/>
-      <c r="CZ28" s="64"/>
-      <c r="DA28" s="64"/>
-      <c r="DB28" s="64"/>
-      <c r="DC28" s="64"/>
-      <c r="DD28" s="64"/>
-      <c r="DE28" s="64"/>
-      <c r="DF28" s="64"/>
-      <c r="DG28" s="64"/>
-      <c r="DH28" s="64"/>
-      <c r="DI28" s="64"/>
-      <c r="DJ28" s="64"/>
-      <c r="DK28" s="64"/>
-      <c r="DL28" s="64"/>
-      <c r="DM28" s="64"/>
-      <c r="DN28" s="64"/>
-      <c r="DO28" s="64"/>
-      <c r="DP28" s="64"/>
-      <c r="DQ28" s="64"/>
-      <c r="DR28" s="64"/>
-      <c r="DS28" s="64"/>
-      <c r="DT28" s="64"/>
-      <c r="DU28" s="64"/>
-      <c r="DV28" s="64"/>
-      <c r="DW28" s="64"/>
-      <c r="DX28" s="64"/>
-      <c r="DY28" s="64"/>
-      <c r="DZ28" s="64"/>
-      <c r="EA28" s="64"/>
-      <c r="EB28" s="64"/>
-      <c r="EC28" s="64"/>
-      <c r="ED28" s="64"/>
-      <c r="EE28" s="64"/>
-      <c r="EF28" s="64"/>
-      <c r="EG28" s="64"/>
-      <c r="EH28" s="64"/>
-      <c r="EI28" s="64"/>
-      <c r="EJ28" s="64"/>
-      <c r="EK28" s="64"/>
-      <c r="EL28" s="64"/>
-      <c r="EM28" s="64"/>
-      <c r="EN28" s="64"/>
-      <c r="EO28" s="64"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="31"/>
+      <c r="AN28" s="31"/>
+      <c r="AO28" s="31"/>
+      <c r="AP28" s="31"/>
+      <c r="AQ28" s="31"/>
+      <c r="AR28" s="31"/>
+      <c r="AS28" s="31"/>
+      <c r="AT28" s="31"/>
+      <c r="AU28" s="31"/>
+      <c r="AV28" s="31"/>
+      <c r="AW28" s="31"/>
+      <c r="AX28" s="31"/>
+      <c r="AY28" s="31"/>
+      <c r="AZ28" s="31"/>
+      <c r="BA28" s="31"/>
+      <c r="BB28" s="31"/>
+      <c r="BC28" s="31"/>
+      <c r="BD28" s="31"/>
+      <c r="BE28" s="31"/>
+      <c r="BF28" s="31"/>
+      <c r="BG28" s="31"/>
+      <c r="BH28" s="31"/>
+      <c r="BI28" s="31"/>
+      <c r="BJ28" s="31"/>
+      <c r="BK28" s="31"/>
+      <c r="BL28" s="31"/>
+      <c r="BM28" s="31"/>
+      <c r="BN28" s="31"/>
+      <c r="BO28" s="31"/>
+      <c r="BP28" s="31"/>
+      <c r="BQ28" s="31"/>
+      <c r="BR28" s="31"/>
+      <c r="BS28" s="31"/>
+      <c r="BT28" s="31"/>
+      <c r="BU28" s="31"/>
+      <c r="BV28" s="31"/>
+      <c r="BW28" s="31"/>
+      <c r="BX28" s="31"/>
+      <c r="BY28" s="31"/>
+      <c r="BZ28" s="31"/>
+      <c r="CA28" s="31"/>
+      <c r="CB28" s="31"/>
+      <c r="CC28" s="31"/>
+      <c r="CD28" s="31"/>
+      <c r="CE28" s="31"/>
+      <c r="CF28" s="31"/>
+      <c r="CG28" s="31"/>
+      <c r="CH28" s="31"/>
+      <c r="CI28" s="31"/>
+      <c r="CJ28" s="31"/>
+      <c r="CK28" s="31"/>
+      <c r="CL28" s="31"/>
+      <c r="CM28" s="31"/>
+      <c r="CN28" s="31"/>
+      <c r="CO28" s="31"/>
+      <c r="CP28" s="31"/>
+      <c r="CQ28" s="31"/>
+      <c r="CR28" s="31"/>
+      <c r="CS28" s="31"/>
+      <c r="CT28" s="31"/>
+      <c r="CU28" s="31"/>
+      <c r="CV28" s="31"/>
+      <c r="CW28" s="31"/>
+      <c r="CX28" s="31"/>
+      <c r="CY28" s="31"/>
+      <c r="CZ28" s="31"/>
+      <c r="DA28" s="31"/>
+      <c r="DB28" s="31"/>
+      <c r="DC28" s="31"/>
+      <c r="DD28" s="31"/>
+      <c r="DE28" s="31"/>
+      <c r="DF28" s="31"/>
+      <c r="DG28" s="31"/>
+      <c r="DH28" s="31"/>
+      <c r="DI28" s="31"/>
+      <c r="DJ28" s="31"/>
+      <c r="DK28" s="31"/>
+      <c r="DL28" s="31"/>
+      <c r="DM28" s="31"/>
+      <c r="DN28" s="31"/>
+      <c r="DO28" s="31"/>
+      <c r="DP28" s="31"/>
+      <c r="DQ28" s="31"/>
+      <c r="DR28" s="31"/>
+      <c r="DS28" s="31"/>
+      <c r="DT28" s="31"/>
+      <c r="DU28" s="31"/>
+      <c r="DV28" s="31"/>
+      <c r="DW28" s="31"/>
+      <c r="DX28" s="31"/>
+      <c r="DY28" s="31"/>
+      <c r="DZ28" s="31"/>
+      <c r="EA28" s="31"/>
+      <c r="EB28" s="31"/>
+      <c r="EC28" s="31"/>
+      <c r="ED28" s="31"/>
+      <c r="EE28" s="31"/>
+      <c r="EF28" s="31"/>
+      <c r="EG28" s="31"/>
+      <c r="EH28" s="31"/>
+      <c r="EI28" s="31"/>
+      <c r="EJ28" s="31"/>
+      <c r="EK28" s="31"/>
+      <c r="EL28" s="31"/>
+      <c r="EM28" s="31"/>
+      <c r="EN28" s="31"/>
+      <c r="EO28" s="31"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6964,6 +6981,299 @@
     </row>
   </sheetData>
   <mergeCells count="317">
+    <mergeCell ref="AO17:EO17"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="BM1:BO1"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="E28:EO28"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
     <mergeCell ref="BQ1:BU1"/>
     <mergeCell ref="BV1:BX1"/>
     <mergeCell ref="EH8:EH9"/>
@@ -6988,299 +7298,6 @@
     <mergeCell ref="DX8:DX9"/>
     <mergeCell ref="DY8:DY9"/>
     <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="E28:EO28"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="BH1:BL1"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AO17:EO17"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="BM1:BO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B3FA54-F681-4C2E-B481-A8C298B04100}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8A0702-49D6-4E98-B8B6-2CBA26E2BE0E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -825,102 +825,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -951,6 +855,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -968,6 +875,99 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1196,133 +1196,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="59" t="s">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="60"/>
-      <c r="F1" s="63">
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="F1" s="31">
         <v>4</v>
       </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="34">
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="33">
         <v>3</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34">
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33">
         <v>4</v>
       </c>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="65">
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34">
         <v>4</v>
       </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="65">
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="34">
         <v>4</v>
       </c>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="65">
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="34">
         <v>4</v>
       </c>
-      <c r="Z1" s="66"/>
-      <c r="AA1" s="66"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="32">
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="66">
         <v>2</v>
       </c>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="26">
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="44">
         <v>4</v>
       </c>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="26">
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="44">
         <v>4</v>
       </c>
-      <c r="AJ1" s="27"/>
-      <c r="AK1" s="27"/>
-      <c r="AL1" s="28"/>
-      <c r="AM1" s="26">
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="44">
         <v>2</v>
       </c>
-      <c r="AN1" s="28"/>
-      <c r="AO1" s="26">
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="44">
         <v>4</v>
       </c>
-      <c r="AP1" s="27"/>
-      <c r="AQ1" s="27"/>
-      <c r="AR1" s="28"/>
-      <c r="AS1" s="26">
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="44">
         <v>5</v>
       </c>
-      <c r="AT1" s="27"/>
-      <c r="AU1" s="27"/>
-      <c r="AV1" s="27"/>
-      <c r="AW1" s="28"/>
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
+      <c r="AV1" s="45"/>
+      <c r="AW1" s="46"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="26">
+      <c r="AY1" s="44">
         <v>5</v>
       </c>
-      <c r="AZ1" s="27"/>
-      <c r="BA1" s="27"/>
-      <c r="BB1" s="27"/>
-      <c r="BC1" s="28"/>
-      <c r="BD1" s="26">
+      <c r="AZ1" s="45"/>
+      <c r="BA1" s="45"/>
+      <c r="BB1" s="45"/>
+      <c r="BC1" s="46"/>
+      <c r="BD1" s="44">
         <v>3</v>
       </c>
-      <c r="BE1" s="27"/>
-      <c r="BF1" s="28"/>
+      <c r="BE1" s="45"/>
+      <c r="BF1" s="46"/>
       <c r="BG1" s="20">
         <v>1</v>
       </c>
-      <c r="BH1" s="34">
+      <c r="BH1" s="33">
         <v>5</v>
       </c>
-      <c r="BI1" s="34"/>
-      <c r="BJ1" s="34"/>
-      <c r="BK1" s="34"/>
-      <c r="BL1" s="34"/>
-      <c r="BM1" s="26">
+      <c r="BI1" s="33"/>
+      <c r="BJ1" s="33"/>
+      <c r="BK1" s="33"/>
+      <c r="BL1" s="33"/>
+      <c r="BM1" s="44">
         <v>3</v>
       </c>
-      <c r="BN1" s="27"/>
-      <c r="BO1" s="28"/>
+      <c r="BN1" s="45"/>
+      <c r="BO1" s="46"/>
       <c r="BP1" s="21">
         <v>1</v>
       </c>
-      <c r="BQ1" s="23">
+      <c r="BQ1" s="68">
         <v>5</v>
       </c>
-      <c r="BR1" s="24"/>
-      <c r="BS1" s="24"/>
-      <c r="BT1" s="24"/>
-      <c r="BU1" s="25"/>
-      <c r="BV1" s="26">
+      <c r="BR1" s="69"/>
+      <c r="BS1" s="69"/>
+      <c r="BT1" s="69"/>
+      <c r="BU1" s="70"/>
+      <c r="BV1" s="44">
         <v>3</v>
       </c>
-      <c r="BW1" s="27"/>
-      <c r="BX1" s="28"/>
+      <c r="BW1" s="45"/>
+      <c r="BX1" s="46"/>
       <c r="BY1" s="22">
         <v>1</v>
       </c>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
+      <c r="BZ1" s="44">
+        <v>3</v>
+      </c>
+      <c r="CA1" s="45"/>
+      <c r="CB1" s="46"/>
       <c r="CC1" s="4"/>
       <c r="CD1" s="4"/>
       <c r="CE1" s="4"/>
@@ -1390,1642 +1392,1648 @@
       <c r="EO1" s="4"/>
       <c r="EP1" s="1">
         <f>SUM(E1:EO1)</f>
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="68" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="53" t="s">
+      <c r="K2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="53" t="s">
+      <c r="L2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="41" t="s">
+      <c r="N2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="41" t="s">
+      <c r="O2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="P2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="41" t="s">
+      <c r="Q2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="53" t="s">
+      <c r="R2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="53" t="s">
+      <c r="S2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="53" t="s">
+      <c r="T2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="41" t="s">
+      <c r="U2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="53" t="s">
+      <c r="V2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="53" t="s">
+      <c r="W2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="53" t="s">
+      <c r="X2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Y2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="53" t="s">
+      <c r="Z2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="51" t="s">
+      <c r="AA2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="51" t="s">
+      <c r="AB2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="41">
+      <c r="AC2" s="40">
         <v>46199</v>
       </c>
-      <c r="AD2" s="41">
+      <c r="AD2" s="40">
         <v>46199</v>
       </c>
-      <c r="AE2" s="41">
+      <c r="AE2" s="40">
         <v>46202</v>
       </c>
-      <c r="AF2" s="41">
+      <c r="AF2" s="40">
         <v>46202</v>
       </c>
-      <c r="AG2" s="41">
+      <c r="AG2" s="40">
         <v>46202</v>
       </c>
-      <c r="AH2" s="41">
+      <c r="AH2" s="40">
         <v>46202</v>
       </c>
-      <c r="AI2" s="41">
+      <c r="AI2" s="40">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="41">
+      <c r="AJ2" s="40">
         <v>46205</v>
       </c>
-      <c r="AK2" s="41">
+      <c r="AK2" s="40">
         <v>46205</v>
       </c>
-      <c r="AL2" s="41">
+      <c r="AL2" s="40">
         <v>46205</v>
       </c>
-      <c r="AM2" s="41">
+      <c r="AM2" s="40">
         <v>46206</v>
       </c>
-      <c r="AN2" s="41">
+      <c r="AN2" s="40">
         <v>46206</v>
       </c>
-      <c r="AO2" s="41">
+      <c r="AO2" s="40">
         <v>46212</v>
       </c>
-      <c r="AP2" s="41">
+      <c r="AP2" s="40">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="41">
+      <c r="AQ2" s="40">
         <v>46212</v>
       </c>
-      <c r="AR2" s="41">
+      <c r="AR2" s="40">
         <v>46212</v>
       </c>
-      <c r="AS2" s="41">
+      <c r="AS2" s="40">
         <v>46213</v>
       </c>
-      <c r="AT2" s="41">
+      <c r="AT2" s="40">
         <v>46213</v>
       </c>
-      <c r="AU2" s="41">
+      <c r="AU2" s="40">
         <v>46213</v>
       </c>
-      <c r="AV2" s="41">
+      <c r="AV2" s="40">
         <v>46213</v>
       </c>
-      <c r="AW2" s="41">
+      <c r="AW2" s="40">
         <v>46213</v>
       </c>
-      <c r="AX2" s="41">
+      <c r="AX2" s="40">
         <v>46218</v>
       </c>
-      <c r="AY2" s="41">
+      <c r="AY2" s="40">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="41">
+      <c r="AZ2" s="40">
         <v>46219</v>
       </c>
-      <c r="BA2" s="41">
+      <c r="BA2" s="40">
         <v>46219</v>
       </c>
-      <c r="BB2" s="41">
+      <c r="BB2" s="40">
         <v>46219</v>
       </c>
-      <c r="BC2" s="41">
+      <c r="BC2" s="40">
         <v>46219</v>
       </c>
-      <c r="BD2" s="41">
+      <c r="BD2" s="40">
         <v>46220</v>
       </c>
-      <c r="BE2" s="41">
+      <c r="BE2" s="40">
         <v>46220</v>
       </c>
-      <c r="BF2" s="41">
+      <c r="BF2" s="40">
         <v>46220</v>
       </c>
-      <c r="BG2" s="41">
+      <c r="BG2" s="40">
         <v>46225</v>
       </c>
-      <c r="BH2" s="41">
+      <c r="BH2" s="40">
         <v>46226</v>
       </c>
-      <c r="BI2" s="41">
+      <c r="BI2" s="40">
         <v>46226</v>
       </c>
-      <c r="BJ2" s="41">
+      <c r="BJ2" s="40">
         <v>46226</v>
       </c>
-      <c r="BK2" s="41">
+      <c r="BK2" s="40">
         <v>46226</v>
       </c>
-      <c r="BL2" s="41">
+      <c r="BL2" s="40">
         <v>46226</v>
       </c>
-      <c r="BM2" s="41">
+      <c r="BM2" s="40">
         <v>46227</v>
       </c>
-      <c r="BN2" s="41">
+      <c r="BN2" s="40">
         <v>46227</v>
       </c>
-      <c r="BO2" s="41">
+      <c r="BO2" s="40">
         <v>46227</v>
       </c>
-      <c r="BP2" s="41">
+      <c r="BP2" s="40">
         <v>46232</v>
       </c>
-      <c r="BQ2" s="41">
+      <c r="BQ2" s="40">
         <v>46233</v>
       </c>
-      <c r="BR2" s="41">
+      <c r="BR2" s="40">
         <v>46233</v>
       </c>
-      <c r="BS2" s="41">
+      <c r="BS2" s="40">
         <v>46233</v>
       </c>
-      <c r="BT2" s="41">
+      <c r="BT2" s="40">
         <v>46233</v>
       </c>
-      <c r="BU2" s="41">
+      <c r="BU2" s="40">
         <v>46233</v>
       </c>
-      <c r="BV2" s="41">
+      <c r="BV2" s="40">
         <v>46234</v>
       </c>
-      <c r="BW2" s="41">
+      <c r="BW2" s="40">
         <v>46234</v>
       </c>
       <c r="BX2" s="49">
         <v>46234</v>
       </c>
-      <c r="BY2" s="41">
+      <c r="BY2" s="40">
         <v>46274</v>
       </c>
-      <c r="BZ2" s="41"/>
-      <c r="CA2" s="41"/>
-      <c r="CB2" s="41"/>
-      <c r="CC2" s="41"/>
-      <c r="CD2" s="41"/>
-      <c r="CE2" s="41"/>
-      <c r="CF2" s="41"/>
-      <c r="CG2" s="41"/>
-      <c r="CH2" s="41"/>
-      <c r="CI2" s="41"/>
-      <c r="CJ2" s="41"/>
-      <c r="CK2" s="41"/>
-      <c r="CL2" s="41"/>
-      <c r="CM2" s="41"/>
-      <c r="CN2" s="41"/>
-      <c r="CO2" s="41"/>
-      <c r="CP2" s="41"/>
-      <c r="CQ2" s="41"/>
-      <c r="CR2" s="41"/>
-      <c r="CS2" s="41"/>
-      <c r="CT2" s="41"/>
-      <c r="CU2" s="41"/>
-      <c r="CV2" s="41"/>
-      <c r="CW2" s="41"/>
-      <c r="CX2" s="41"/>
-      <c r="CY2" s="41"/>
-      <c r="CZ2" s="41"/>
-      <c r="DA2" s="41"/>
-      <c r="DB2" s="41"/>
-      <c r="DC2" s="41"/>
-      <c r="DD2" s="41"/>
-      <c r="DE2" s="41"/>
-      <c r="DF2" s="41"/>
-      <c r="DG2" s="41"/>
-      <c r="DH2" s="41"/>
-      <c r="DI2" s="41"/>
-      <c r="DJ2" s="41"/>
-      <c r="DK2" s="41"/>
-      <c r="DL2" s="41"/>
-      <c r="DM2" s="41"/>
-      <c r="DN2" s="41"/>
-      <c r="DO2" s="41"/>
-      <c r="DP2" s="41"/>
-      <c r="DQ2" s="41"/>
-      <c r="DR2" s="41"/>
-      <c r="DS2" s="41"/>
-      <c r="DT2" s="41"/>
-      <c r="DU2" s="41"/>
-      <c r="DV2" s="41"/>
-      <c r="DW2" s="41"/>
-      <c r="DX2" s="41"/>
-      <c r="DY2" s="41"/>
-      <c r="DZ2" s="41"/>
-      <c r="EA2" s="41"/>
-      <c r="EB2" s="41"/>
-      <c r="EC2" s="41"/>
-      <c r="ED2" s="41"/>
-      <c r="EE2" s="41"/>
-      <c r="EF2" s="41"/>
-      <c r="EG2" s="41"/>
-      <c r="EH2" s="41"/>
-      <c r="EI2" s="41"/>
-      <c r="EJ2" s="41"/>
-      <c r="EK2" s="41"/>
-      <c r="EL2" s="41"/>
-      <c r="EM2" s="41"/>
-      <c r="EN2" s="41"/>
-      <c r="EO2" s="41"/>
+      <c r="BZ2" s="40">
+        <v>46276</v>
+      </c>
+      <c r="CA2" s="40">
+        <v>46276</v>
+      </c>
+      <c r="CB2" s="40">
+        <v>46276</v>
+      </c>
+      <c r="CC2" s="40"/>
+      <c r="CD2" s="40"/>
+      <c r="CE2" s="40"/>
+      <c r="CF2" s="40"/>
+      <c r="CG2" s="40"/>
+      <c r="CH2" s="40"/>
+      <c r="CI2" s="40"/>
+      <c r="CJ2" s="40"/>
+      <c r="CK2" s="40"/>
+      <c r="CL2" s="40"/>
+      <c r="CM2" s="40"/>
+      <c r="CN2" s="40"/>
+      <c r="CO2" s="40"/>
+      <c r="CP2" s="40"/>
+      <c r="CQ2" s="40"/>
+      <c r="CR2" s="40"/>
+      <c r="CS2" s="40"/>
+      <c r="CT2" s="40"/>
+      <c r="CU2" s="40"/>
+      <c r="CV2" s="40"/>
+      <c r="CW2" s="40"/>
+      <c r="CX2" s="40"/>
+      <c r="CY2" s="40"/>
+      <c r="CZ2" s="40"/>
+      <c r="DA2" s="40"/>
+      <c r="DB2" s="40"/>
+      <c r="DC2" s="40"/>
+      <c r="DD2" s="40"/>
+      <c r="DE2" s="40"/>
+      <c r="DF2" s="40"/>
+      <c r="DG2" s="40"/>
+      <c r="DH2" s="40"/>
+      <c r="DI2" s="40"/>
+      <c r="DJ2" s="40"/>
+      <c r="DK2" s="40"/>
+      <c r="DL2" s="40"/>
+      <c r="DM2" s="40"/>
+      <c r="DN2" s="40"/>
+      <c r="DO2" s="40"/>
+      <c r="DP2" s="40"/>
+      <c r="DQ2" s="40"/>
+      <c r="DR2" s="40"/>
+      <c r="DS2" s="40"/>
+      <c r="DT2" s="40"/>
+      <c r="DU2" s="40"/>
+      <c r="DV2" s="40"/>
+      <c r="DW2" s="40"/>
+      <c r="DX2" s="40"/>
+      <c r="DY2" s="40"/>
+      <c r="DZ2" s="40"/>
+      <c r="EA2" s="40"/>
+      <c r="EB2" s="40"/>
+      <c r="EC2" s="40"/>
+      <c r="ED2" s="40"/>
+      <c r="EE2" s="40"/>
+      <c r="EF2" s="40"/>
+      <c r="EG2" s="40"/>
+      <c r="EH2" s="40"/>
+      <c r="EI2" s="40"/>
+      <c r="EJ2" s="40"/>
+      <c r="EK2" s="40"/>
+      <c r="EL2" s="40"/>
+      <c r="EM2" s="40"/>
+      <c r="EN2" s="40"/>
+      <c r="EO2" s="40"/>
     </row>
     <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="51"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="41"/>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="41"/>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="41"/>
-      <c r="BF3" s="41"/>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="41"/>
-      <c r="BI3" s="41"/>
-      <c r="BJ3" s="41"/>
-      <c r="BK3" s="41"/>
-      <c r="BL3" s="41"/>
-      <c r="BM3" s="41"/>
-      <c r="BN3" s="41"/>
-      <c r="BO3" s="41"/>
-      <c r="BP3" s="41"/>
-      <c r="BQ3" s="41"/>
-      <c r="BR3" s="41"/>
-      <c r="BS3" s="41"/>
-      <c r="BT3" s="41"/>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="41"/>
-      <c r="BW3" s="41"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40"/>
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="40"/>
+      <c r="AP3" s="40"/>
+      <c r="AQ3" s="40"/>
+      <c r="AR3" s="40"/>
+      <c r="AS3" s="40"/>
+      <c r="AT3" s="40"/>
+      <c r="AU3" s="40"/>
+      <c r="AV3" s="40"/>
+      <c r="AW3" s="40"/>
+      <c r="AX3" s="40"/>
+      <c r="AY3" s="40"/>
+      <c r="AZ3" s="40"/>
+      <c r="BA3" s="40"/>
+      <c r="BB3" s="40"/>
+      <c r="BC3" s="40"/>
+      <c r="BD3" s="40"/>
+      <c r="BE3" s="40"/>
+      <c r="BF3" s="40"/>
+      <c r="BG3" s="40"/>
+      <c r="BH3" s="40"/>
+      <c r="BI3" s="40"/>
+      <c r="BJ3" s="40"/>
+      <c r="BK3" s="40"/>
+      <c r="BL3" s="40"/>
+      <c r="BM3" s="40"/>
+      <c r="BN3" s="40"/>
+      <c r="BO3" s="40"/>
+      <c r="BP3" s="40"/>
+      <c r="BQ3" s="40"/>
+      <c r="BR3" s="40"/>
+      <c r="BS3" s="40"/>
+      <c r="BT3" s="40"/>
+      <c r="BU3" s="40"/>
+      <c r="BV3" s="40"/>
+      <c r="BW3" s="40"/>
       <c r="BX3" s="49"/>
-      <c r="BY3" s="41"/>
-      <c r="BZ3" s="41"/>
-      <c r="CA3" s="41"/>
-      <c r="CB3" s="41"/>
-      <c r="CC3" s="41"/>
-      <c r="CD3" s="41"/>
-      <c r="CE3" s="41"/>
-      <c r="CF3" s="41"/>
-      <c r="CG3" s="41"/>
-      <c r="CH3" s="41"/>
-      <c r="CI3" s="41"/>
-      <c r="CJ3" s="41"/>
-      <c r="CK3" s="41"/>
-      <c r="CL3" s="41"/>
-      <c r="CM3" s="41"/>
-      <c r="CN3" s="41"/>
-      <c r="CO3" s="41"/>
-      <c r="CP3" s="41"/>
-      <c r="CQ3" s="41"/>
-      <c r="CR3" s="41"/>
-      <c r="CS3" s="41"/>
-      <c r="CT3" s="41"/>
-      <c r="CU3" s="41"/>
-      <c r="CV3" s="41"/>
-      <c r="CW3" s="41"/>
-      <c r="CX3" s="41"/>
-      <c r="CY3" s="41"/>
-      <c r="CZ3" s="41"/>
-      <c r="DA3" s="41"/>
-      <c r="DB3" s="41"/>
-      <c r="DC3" s="41"/>
-      <c r="DD3" s="41"/>
-      <c r="DE3" s="41"/>
-      <c r="DF3" s="41"/>
-      <c r="DG3" s="41"/>
-      <c r="DH3" s="41"/>
-      <c r="DI3" s="41"/>
-      <c r="DJ3" s="41"/>
-      <c r="DK3" s="41"/>
-      <c r="DL3" s="41"/>
-      <c r="DM3" s="41"/>
-      <c r="DN3" s="41"/>
-      <c r="DO3" s="41"/>
-      <c r="DP3" s="41"/>
-      <c r="DQ3" s="41"/>
-      <c r="DR3" s="41"/>
-      <c r="DS3" s="41"/>
-      <c r="DT3" s="41"/>
-      <c r="DU3" s="41"/>
-      <c r="DV3" s="41"/>
-      <c r="DW3" s="41"/>
-      <c r="DX3" s="41"/>
-      <c r="DY3" s="41"/>
-      <c r="DZ3" s="41"/>
-      <c r="EA3" s="41"/>
-      <c r="EB3" s="41"/>
-      <c r="EC3" s="41"/>
-      <c r="ED3" s="41"/>
-      <c r="EE3" s="41"/>
-      <c r="EF3" s="41"/>
-      <c r="EG3" s="41"/>
-      <c r="EH3" s="41"/>
-      <c r="EI3" s="41"/>
-      <c r="EJ3" s="41"/>
-      <c r="EK3" s="41"/>
-      <c r="EL3" s="41"/>
-      <c r="EM3" s="41"/>
-      <c r="EN3" s="41"/>
-      <c r="EO3" s="41"/>
+      <c r="BY3" s="40"/>
+      <c r="BZ3" s="40"/>
+      <c r="CA3" s="40"/>
+      <c r="CB3" s="40"/>
+      <c r="CC3" s="40"/>
+      <c r="CD3" s="40"/>
+      <c r="CE3" s="40"/>
+      <c r="CF3" s="40"/>
+      <c r="CG3" s="40"/>
+      <c r="CH3" s="40"/>
+      <c r="CI3" s="40"/>
+      <c r="CJ3" s="40"/>
+      <c r="CK3" s="40"/>
+      <c r="CL3" s="40"/>
+      <c r="CM3" s="40"/>
+      <c r="CN3" s="40"/>
+      <c r="CO3" s="40"/>
+      <c r="CP3" s="40"/>
+      <c r="CQ3" s="40"/>
+      <c r="CR3" s="40"/>
+      <c r="CS3" s="40"/>
+      <c r="CT3" s="40"/>
+      <c r="CU3" s="40"/>
+      <c r="CV3" s="40"/>
+      <c r="CW3" s="40"/>
+      <c r="CX3" s="40"/>
+      <c r="CY3" s="40"/>
+      <c r="CZ3" s="40"/>
+      <c r="DA3" s="40"/>
+      <c r="DB3" s="40"/>
+      <c r="DC3" s="40"/>
+      <c r="DD3" s="40"/>
+      <c r="DE3" s="40"/>
+      <c r="DF3" s="40"/>
+      <c r="DG3" s="40"/>
+      <c r="DH3" s="40"/>
+      <c r="DI3" s="40"/>
+      <c r="DJ3" s="40"/>
+      <c r="DK3" s="40"/>
+      <c r="DL3" s="40"/>
+      <c r="DM3" s="40"/>
+      <c r="DN3" s="40"/>
+      <c r="DO3" s="40"/>
+      <c r="DP3" s="40"/>
+      <c r="DQ3" s="40"/>
+      <c r="DR3" s="40"/>
+      <c r="DS3" s="40"/>
+      <c r="DT3" s="40"/>
+      <c r="DU3" s="40"/>
+      <c r="DV3" s="40"/>
+      <c r="DW3" s="40"/>
+      <c r="DX3" s="40"/>
+      <c r="DY3" s="40"/>
+      <c r="DZ3" s="40"/>
+      <c r="EA3" s="40"/>
+      <c r="EB3" s="40"/>
+      <c r="EC3" s="40"/>
+      <c r="ED3" s="40"/>
+      <c r="EE3" s="40"/>
+      <c r="EF3" s="40"/>
+      <c r="EG3" s="40"/>
+      <c r="EH3" s="40"/>
+      <c r="EI3" s="40"/>
+      <c r="EJ3" s="40"/>
+      <c r="EK3" s="40"/>
+      <c r="EL3" s="40"/>
+      <c r="EM3" s="40"/>
+      <c r="EN3" s="40"/>
+      <c r="EO3" s="40"/>
     </row>
     <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="53"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="53"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="41"/>
-      <c r="AE4" s="41"/>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="41"/>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="41"/>
-      <c r="AK4" s="41"/>
-      <c r="AL4" s="41"/>
-      <c r="AM4" s="41"/>
-      <c r="AN4" s="41"/>
-      <c r="AO4" s="41"/>
-      <c r="AP4" s="41"/>
-      <c r="AQ4" s="41"/>
-      <c r="AR4" s="41"/>
-      <c r="AS4" s="41"/>
-      <c r="AT4" s="41"/>
-      <c r="AU4" s="41"/>
-      <c r="AV4" s="41"/>
-      <c r="AW4" s="41"/>
-      <c r="AX4" s="41"/>
-      <c r="AY4" s="41"/>
-      <c r="AZ4" s="41"/>
-      <c r="BA4" s="41"/>
-      <c r="BB4" s="41"/>
-      <c r="BC4" s="41"/>
-      <c r="BD4" s="41"/>
-      <c r="BE4" s="41"/>
-      <c r="BF4" s="41"/>
-      <c r="BG4" s="41"/>
-      <c r="BH4" s="41"/>
-      <c r="BI4" s="41"/>
-      <c r="BJ4" s="41"/>
-      <c r="BK4" s="41"/>
-      <c r="BL4" s="41"/>
-      <c r="BM4" s="41"/>
-      <c r="BN4" s="41"/>
-      <c r="BO4" s="41"/>
-      <c r="BP4" s="41"/>
-      <c r="BQ4" s="41"/>
-      <c r="BR4" s="41"/>
-      <c r="BS4" s="41"/>
-      <c r="BT4" s="41"/>
-      <c r="BU4" s="41"/>
-      <c r="BV4" s="41"/>
-      <c r="BW4" s="41"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="40"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="40"/>
+      <c r="AQ4" s="40"/>
+      <c r="AR4" s="40"/>
+      <c r="AS4" s="40"/>
+      <c r="AT4" s="40"/>
+      <c r="AU4" s="40"/>
+      <c r="AV4" s="40"/>
+      <c r="AW4" s="40"/>
+      <c r="AX4" s="40"/>
+      <c r="AY4" s="40"/>
+      <c r="AZ4" s="40"/>
+      <c r="BA4" s="40"/>
+      <c r="BB4" s="40"/>
+      <c r="BC4" s="40"/>
+      <c r="BD4" s="40"/>
+      <c r="BE4" s="40"/>
+      <c r="BF4" s="40"/>
+      <c r="BG4" s="40"/>
+      <c r="BH4" s="40"/>
+      <c r="BI4" s="40"/>
+      <c r="BJ4" s="40"/>
+      <c r="BK4" s="40"/>
+      <c r="BL4" s="40"/>
+      <c r="BM4" s="40"/>
+      <c r="BN4" s="40"/>
+      <c r="BO4" s="40"/>
+      <c r="BP4" s="40"/>
+      <c r="BQ4" s="40"/>
+      <c r="BR4" s="40"/>
+      <c r="BS4" s="40"/>
+      <c r="BT4" s="40"/>
+      <c r="BU4" s="40"/>
+      <c r="BV4" s="40"/>
+      <c r="BW4" s="40"/>
       <c r="BX4" s="49"/>
-      <c r="BY4" s="41"/>
-      <c r="BZ4" s="41"/>
-      <c r="CA4" s="41"/>
-      <c r="CB4" s="41"/>
-      <c r="CC4" s="41"/>
-      <c r="CD4" s="41"/>
-      <c r="CE4" s="41"/>
-      <c r="CF4" s="41"/>
-      <c r="CG4" s="41"/>
-      <c r="CH4" s="41"/>
-      <c r="CI4" s="41"/>
-      <c r="CJ4" s="41"/>
-      <c r="CK4" s="41"/>
-      <c r="CL4" s="41"/>
-      <c r="CM4" s="41"/>
-      <c r="CN4" s="41"/>
-      <c r="CO4" s="41"/>
-      <c r="CP4" s="41"/>
-      <c r="CQ4" s="41"/>
-      <c r="CR4" s="41"/>
-      <c r="CS4" s="41"/>
-      <c r="CT4" s="41"/>
-      <c r="CU4" s="41"/>
-      <c r="CV4" s="41"/>
-      <c r="CW4" s="41"/>
-      <c r="CX4" s="41"/>
-      <c r="CY4" s="41"/>
-      <c r="CZ4" s="41"/>
-      <c r="DA4" s="41"/>
-      <c r="DB4" s="41"/>
-      <c r="DC4" s="41"/>
-      <c r="DD4" s="41"/>
-      <c r="DE4" s="41"/>
-      <c r="DF4" s="41"/>
-      <c r="DG4" s="41"/>
-      <c r="DH4" s="41"/>
-      <c r="DI4" s="41"/>
-      <c r="DJ4" s="41"/>
-      <c r="DK4" s="41"/>
-      <c r="DL4" s="41"/>
-      <c r="DM4" s="41"/>
-      <c r="DN4" s="41"/>
-      <c r="DO4" s="41"/>
-      <c r="DP4" s="41"/>
-      <c r="DQ4" s="41"/>
-      <c r="DR4" s="41"/>
-      <c r="DS4" s="41"/>
-      <c r="DT4" s="41"/>
-      <c r="DU4" s="41"/>
-      <c r="DV4" s="41"/>
-      <c r="DW4" s="41"/>
-      <c r="DX4" s="41"/>
-      <c r="DY4" s="41"/>
-      <c r="DZ4" s="41"/>
-      <c r="EA4" s="41"/>
-      <c r="EB4" s="41"/>
-      <c r="EC4" s="41"/>
-      <c r="ED4" s="41"/>
-      <c r="EE4" s="41"/>
-      <c r="EF4" s="41"/>
-      <c r="EG4" s="41"/>
-      <c r="EH4" s="41"/>
-      <c r="EI4" s="41"/>
-      <c r="EJ4" s="41"/>
-      <c r="EK4" s="41"/>
-      <c r="EL4" s="41"/>
-      <c r="EM4" s="41"/>
-      <c r="EN4" s="41"/>
-      <c r="EO4" s="41"/>
+      <c r="BY4" s="40"/>
+      <c r="BZ4" s="40"/>
+      <c r="CA4" s="40"/>
+      <c r="CB4" s="40"/>
+      <c r="CC4" s="40"/>
+      <c r="CD4" s="40"/>
+      <c r="CE4" s="40"/>
+      <c r="CF4" s="40"/>
+      <c r="CG4" s="40"/>
+      <c r="CH4" s="40"/>
+      <c r="CI4" s="40"/>
+      <c r="CJ4" s="40"/>
+      <c r="CK4" s="40"/>
+      <c r="CL4" s="40"/>
+      <c r="CM4" s="40"/>
+      <c r="CN4" s="40"/>
+      <c r="CO4" s="40"/>
+      <c r="CP4" s="40"/>
+      <c r="CQ4" s="40"/>
+      <c r="CR4" s="40"/>
+      <c r="CS4" s="40"/>
+      <c r="CT4" s="40"/>
+      <c r="CU4" s="40"/>
+      <c r="CV4" s="40"/>
+      <c r="CW4" s="40"/>
+      <c r="CX4" s="40"/>
+      <c r="CY4" s="40"/>
+      <c r="CZ4" s="40"/>
+      <c r="DA4" s="40"/>
+      <c r="DB4" s="40"/>
+      <c r="DC4" s="40"/>
+      <c r="DD4" s="40"/>
+      <c r="DE4" s="40"/>
+      <c r="DF4" s="40"/>
+      <c r="DG4" s="40"/>
+      <c r="DH4" s="40"/>
+      <c r="DI4" s="40"/>
+      <c r="DJ4" s="40"/>
+      <c r="DK4" s="40"/>
+      <c r="DL4" s="40"/>
+      <c r="DM4" s="40"/>
+      <c r="DN4" s="40"/>
+      <c r="DO4" s="40"/>
+      <c r="DP4" s="40"/>
+      <c r="DQ4" s="40"/>
+      <c r="DR4" s="40"/>
+      <c r="DS4" s="40"/>
+      <c r="DT4" s="40"/>
+      <c r="DU4" s="40"/>
+      <c r="DV4" s="40"/>
+      <c r="DW4" s="40"/>
+      <c r="DX4" s="40"/>
+      <c r="DY4" s="40"/>
+      <c r="DZ4" s="40"/>
+      <c r="EA4" s="40"/>
+      <c r="EB4" s="40"/>
+      <c r="EC4" s="40"/>
+      <c r="ED4" s="40"/>
+      <c r="EE4" s="40"/>
+      <c r="EF4" s="40"/>
+      <c r="EG4" s="40"/>
+      <c r="EH4" s="40"/>
+      <c r="EI4" s="40"/>
+      <c r="EJ4" s="40"/>
+      <c r="EK4" s="40"/>
+      <c r="EL4" s="40"/>
+      <c r="EM4" s="40"/>
+      <c r="EN4" s="40"/>
+      <c r="EO4" s="40"/>
     </row>
     <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46">
+      <c r="B5" s="54"/>
+      <c r="C5" s="55">
         <v>110</v>
       </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="53"/>
-      <c r="X5" s="53"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="41"/>
-      <c r="AD5" s="41"/>
-      <c r="AE5" s="41"/>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="41"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="41"/>
-      <c r="AK5" s="41"/>
-      <c r="AL5" s="41"/>
-      <c r="AM5" s="41"/>
-      <c r="AN5" s="41"/>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="41"/>
-      <c r="AQ5" s="41"/>
-      <c r="AR5" s="41"/>
-      <c r="AS5" s="41"/>
-      <c r="AT5" s="41"/>
-      <c r="AU5" s="41"/>
-      <c r="AV5" s="41"/>
-      <c r="AW5" s="41"/>
-      <c r="AX5" s="41"/>
-      <c r="AY5" s="41"/>
-      <c r="AZ5" s="41"/>
-      <c r="BA5" s="41"/>
-      <c r="BB5" s="41"/>
-      <c r="BC5" s="41"/>
-      <c r="BD5" s="41"/>
-      <c r="BE5" s="41"/>
-      <c r="BF5" s="41"/>
-      <c r="BG5" s="41"/>
-      <c r="BH5" s="41"/>
-      <c r="BI5" s="41"/>
-      <c r="BJ5" s="41"/>
-      <c r="BK5" s="41"/>
-      <c r="BL5" s="41"/>
-      <c r="BM5" s="41"/>
-      <c r="BN5" s="41"/>
-      <c r="BO5" s="41"/>
-      <c r="BP5" s="41"/>
-      <c r="BQ5" s="41"/>
-      <c r="BR5" s="41"/>
-      <c r="BS5" s="41"/>
-      <c r="BT5" s="41"/>
-      <c r="BU5" s="41"/>
-      <c r="BV5" s="41"/>
-      <c r="BW5" s="41"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="42"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="40"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="40"/>
+      <c r="AK5" s="40"/>
+      <c r="AL5" s="40"/>
+      <c r="AM5" s="40"/>
+      <c r="AN5" s="40"/>
+      <c r="AO5" s="40"/>
+      <c r="AP5" s="40"/>
+      <c r="AQ5" s="40"/>
+      <c r="AR5" s="40"/>
+      <c r="AS5" s="40"/>
+      <c r="AT5" s="40"/>
+      <c r="AU5" s="40"/>
+      <c r="AV5" s="40"/>
+      <c r="AW5" s="40"/>
+      <c r="AX5" s="40"/>
+      <c r="AY5" s="40"/>
+      <c r="AZ5" s="40"/>
+      <c r="BA5" s="40"/>
+      <c r="BB5" s="40"/>
+      <c r="BC5" s="40"/>
+      <c r="BD5" s="40"/>
+      <c r="BE5" s="40"/>
+      <c r="BF5" s="40"/>
+      <c r="BG5" s="40"/>
+      <c r="BH5" s="40"/>
+      <c r="BI5" s="40"/>
+      <c r="BJ5" s="40"/>
+      <c r="BK5" s="40"/>
+      <c r="BL5" s="40"/>
+      <c r="BM5" s="40"/>
+      <c r="BN5" s="40"/>
+      <c r="BO5" s="40"/>
+      <c r="BP5" s="40"/>
+      <c r="BQ5" s="40"/>
+      <c r="BR5" s="40"/>
+      <c r="BS5" s="40"/>
+      <c r="BT5" s="40"/>
+      <c r="BU5" s="40"/>
+      <c r="BV5" s="40"/>
+      <c r="BW5" s="40"/>
       <c r="BX5" s="49"/>
-      <c r="BY5" s="41"/>
-      <c r="BZ5" s="41"/>
-      <c r="CA5" s="41"/>
-      <c r="CB5" s="41"/>
-      <c r="CC5" s="41"/>
-      <c r="CD5" s="41"/>
-      <c r="CE5" s="41"/>
-      <c r="CF5" s="41"/>
-      <c r="CG5" s="41"/>
-      <c r="CH5" s="41"/>
-      <c r="CI5" s="41"/>
-      <c r="CJ5" s="41"/>
-      <c r="CK5" s="41"/>
-      <c r="CL5" s="41"/>
-      <c r="CM5" s="41"/>
-      <c r="CN5" s="41"/>
-      <c r="CO5" s="41"/>
-      <c r="CP5" s="41"/>
-      <c r="CQ5" s="41"/>
-      <c r="CR5" s="41"/>
-      <c r="CS5" s="41"/>
-      <c r="CT5" s="41"/>
-      <c r="CU5" s="41"/>
-      <c r="CV5" s="41"/>
-      <c r="CW5" s="41"/>
-      <c r="CX5" s="41"/>
-      <c r="CY5" s="41"/>
-      <c r="CZ5" s="41"/>
-      <c r="DA5" s="41"/>
-      <c r="DB5" s="41"/>
-      <c r="DC5" s="41"/>
-      <c r="DD5" s="41"/>
-      <c r="DE5" s="41"/>
-      <c r="DF5" s="41"/>
-      <c r="DG5" s="41"/>
-      <c r="DH5" s="41"/>
-      <c r="DI5" s="41"/>
-      <c r="DJ5" s="41"/>
-      <c r="DK5" s="41"/>
-      <c r="DL5" s="41"/>
-      <c r="DM5" s="41"/>
-      <c r="DN5" s="41"/>
-      <c r="DO5" s="41"/>
-      <c r="DP5" s="41"/>
-      <c r="DQ5" s="41"/>
-      <c r="DR5" s="41"/>
-      <c r="DS5" s="41"/>
-      <c r="DT5" s="41"/>
-      <c r="DU5" s="41"/>
-      <c r="DV5" s="41"/>
-      <c r="DW5" s="41"/>
-      <c r="DX5" s="41"/>
-      <c r="DY5" s="41"/>
-      <c r="DZ5" s="41"/>
-      <c r="EA5" s="41"/>
-      <c r="EB5" s="41"/>
-      <c r="EC5" s="41"/>
-      <c r="ED5" s="41"/>
-      <c r="EE5" s="41"/>
-      <c r="EF5" s="41"/>
-      <c r="EG5" s="41"/>
-      <c r="EH5" s="41"/>
-      <c r="EI5" s="41"/>
-      <c r="EJ5" s="41"/>
-      <c r="EK5" s="41"/>
-      <c r="EL5" s="41"/>
-      <c r="EM5" s="41"/>
-      <c r="EN5" s="41"/>
-      <c r="EO5" s="41"/>
+      <c r="BY5" s="40"/>
+      <c r="BZ5" s="40"/>
+      <c r="CA5" s="40"/>
+      <c r="CB5" s="40"/>
+      <c r="CC5" s="40"/>
+      <c r="CD5" s="40"/>
+      <c r="CE5" s="40"/>
+      <c r="CF5" s="40"/>
+      <c r="CG5" s="40"/>
+      <c r="CH5" s="40"/>
+      <c r="CI5" s="40"/>
+      <c r="CJ5" s="40"/>
+      <c r="CK5" s="40"/>
+      <c r="CL5" s="40"/>
+      <c r="CM5" s="40"/>
+      <c r="CN5" s="40"/>
+      <c r="CO5" s="40"/>
+      <c r="CP5" s="40"/>
+      <c r="CQ5" s="40"/>
+      <c r="CR5" s="40"/>
+      <c r="CS5" s="40"/>
+      <c r="CT5" s="40"/>
+      <c r="CU5" s="40"/>
+      <c r="CV5" s="40"/>
+      <c r="CW5" s="40"/>
+      <c r="CX5" s="40"/>
+      <c r="CY5" s="40"/>
+      <c r="CZ5" s="40"/>
+      <c r="DA5" s="40"/>
+      <c r="DB5" s="40"/>
+      <c r="DC5" s="40"/>
+      <c r="DD5" s="40"/>
+      <c r="DE5" s="40"/>
+      <c r="DF5" s="40"/>
+      <c r="DG5" s="40"/>
+      <c r="DH5" s="40"/>
+      <c r="DI5" s="40"/>
+      <c r="DJ5" s="40"/>
+      <c r="DK5" s="40"/>
+      <c r="DL5" s="40"/>
+      <c r="DM5" s="40"/>
+      <c r="DN5" s="40"/>
+      <c r="DO5" s="40"/>
+      <c r="DP5" s="40"/>
+      <c r="DQ5" s="40"/>
+      <c r="DR5" s="40"/>
+      <c r="DS5" s="40"/>
+      <c r="DT5" s="40"/>
+      <c r="DU5" s="40"/>
+      <c r="DV5" s="40"/>
+      <c r="DW5" s="40"/>
+      <c r="DX5" s="40"/>
+      <c r="DY5" s="40"/>
+      <c r="DZ5" s="40"/>
+      <c r="EA5" s="40"/>
+      <c r="EB5" s="40"/>
+      <c r="EC5" s="40"/>
+      <c r="ED5" s="40"/>
+      <c r="EE5" s="40"/>
+      <c r="EF5" s="40"/>
+      <c r="EG5" s="40"/>
+      <c r="EH5" s="40"/>
+      <c r="EI5" s="40"/>
+      <c r="EJ5" s="40"/>
+      <c r="EK5" s="40"/>
+      <c r="EL5" s="40"/>
+      <c r="EM5" s="40"/>
+      <c r="EN5" s="40"/>
+      <c r="EO5" s="40"/>
     </row>
     <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46">
+      <c r="B6" s="54"/>
+      <c r="C6" s="55">
         <v>10</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="53"/>
-      <c r="T6" s="53"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="53"/>
-      <c r="W6" s="53"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="41"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="41"/>
-      <c r="AJ6" s="41"/>
-      <c r="AK6" s="41"/>
-      <c r="AL6" s="41"/>
-      <c r="AM6" s="41"/>
-      <c r="AN6" s="41"/>
-      <c r="AO6" s="41"/>
-      <c r="AP6" s="41"/>
-      <c r="AQ6" s="41"/>
-      <c r="AR6" s="41"/>
-      <c r="AS6" s="41"/>
-      <c r="AT6" s="41"/>
-      <c r="AU6" s="41"/>
-      <c r="AV6" s="41"/>
-      <c r="AW6" s="41"/>
-      <c r="AX6" s="41"/>
-      <c r="AY6" s="41"/>
-      <c r="AZ6" s="41"/>
-      <c r="BA6" s="41"/>
-      <c r="BB6" s="41"/>
-      <c r="BC6" s="41"/>
-      <c r="BD6" s="41"/>
-      <c r="BE6" s="41"/>
-      <c r="BF6" s="41"/>
-      <c r="BG6" s="41"/>
-      <c r="BH6" s="41"/>
-      <c r="BI6" s="41"/>
-      <c r="BJ6" s="41"/>
-      <c r="BK6" s="41"/>
-      <c r="BL6" s="41"/>
-      <c r="BM6" s="41"/>
-      <c r="BN6" s="41"/>
-      <c r="BO6" s="41"/>
-      <c r="BP6" s="41"/>
-      <c r="BQ6" s="41"/>
-      <c r="BR6" s="41"/>
-      <c r="BS6" s="41"/>
-      <c r="BT6" s="41"/>
-      <c r="BU6" s="41"/>
-      <c r="BV6" s="41"/>
-      <c r="BW6" s="41"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="42"/>
+      <c r="W6" s="42"/>
+      <c r="X6" s="42"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="42"/>
+      <c r="AA6" s="47"/>
+      <c r="AB6" s="47"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="40"/>
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="40"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="40"/>
+      <c r="AT6" s="40"/>
+      <c r="AU6" s="40"/>
+      <c r="AV6" s="40"/>
+      <c r="AW6" s="40"/>
+      <c r="AX6" s="40"/>
+      <c r="AY6" s="40"/>
+      <c r="AZ6" s="40"/>
+      <c r="BA6" s="40"/>
+      <c r="BB6" s="40"/>
+      <c r="BC6" s="40"/>
+      <c r="BD6" s="40"/>
+      <c r="BE6" s="40"/>
+      <c r="BF6" s="40"/>
+      <c r="BG6" s="40"/>
+      <c r="BH6" s="40"/>
+      <c r="BI6" s="40"/>
+      <c r="BJ6" s="40"/>
+      <c r="BK6" s="40"/>
+      <c r="BL6" s="40"/>
+      <c r="BM6" s="40"/>
+      <c r="BN6" s="40"/>
+      <c r="BO6" s="40"/>
+      <c r="BP6" s="40"/>
+      <c r="BQ6" s="40"/>
+      <c r="BR6" s="40"/>
+      <c r="BS6" s="40"/>
+      <c r="BT6" s="40"/>
+      <c r="BU6" s="40"/>
+      <c r="BV6" s="40"/>
+      <c r="BW6" s="40"/>
       <c r="BX6" s="49"/>
-      <c r="BY6" s="41"/>
-      <c r="BZ6" s="41"/>
-      <c r="CA6" s="41"/>
-      <c r="CB6" s="41"/>
-      <c r="CC6" s="41"/>
-      <c r="CD6" s="41"/>
-      <c r="CE6" s="41"/>
-      <c r="CF6" s="41"/>
-      <c r="CG6" s="41"/>
-      <c r="CH6" s="41"/>
-      <c r="CI6" s="41"/>
-      <c r="CJ6" s="41"/>
-      <c r="CK6" s="41"/>
-      <c r="CL6" s="41"/>
-      <c r="CM6" s="41"/>
-      <c r="CN6" s="41"/>
-      <c r="CO6" s="41"/>
-      <c r="CP6" s="41"/>
-      <c r="CQ6" s="41"/>
-      <c r="CR6" s="41"/>
-      <c r="CS6" s="41"/>
-      <c r="CT6" s="41"/>
-      <c r="CU6" s="41"/>
-      <c r="CV6" s="41"/>
-      <c r="CW6" s="41"/>
-      <c r="CX6" s="41"/>
-      <c r="CY6" s="41"/>
-      <c r="CZ6" s="41"/>
-      <c r="DA6" s="41"/>
-      <c r="DB6" s="41"/>
-      <c r="DC6" s="41"/>
-      <c r="DD6" s="41"/>
-      <c r="DE6" s="41"/>
-      <c r="DF6" s="41"/>
-      <c r="DG6" s="41"/>
-      <c r="DH6" s="41"/>
-      <c r="DI6" s="41"/>
-      <c r="DJ6" s="41"/>
-      <c r="DK6" s="41"/>
-      <c r="DL6" s="41"/>
-      <c r="DM6" s="41"/>
-      <c r="DN6" s="41"/>
-      <c r="DO6" s="41"/>
-      <c r="DP6" s="41"/>
-      <c r="DQ6" s="41"/>
-      <c r="DR6" s="41"/>
-      <c r="DS6" s="41"/>
-      <c r="DT6" s="41"/>
-      <c r="DU6" s="41"/>
-      <c r="DV6" s="41"/>
-      <c r="DW6" s="41"/>
-      <c r="DX6" s="41"/>
-      <c r="DY6" s="41"/>
-      <c r="DZ6" s="41"/>
-      <c r="EA6" s="41"/>
-      <c r="EB6" s="41"/>
-      <c r="EC6" s="41"/>
-      <c r="ED6" s="41"/>
-      <c r="EE6" s="41"/>
-      <c r="EF6" s="41"/>
-      <c r="EG6" s="41"/>
-      <c r="EH6" s="41"/>
-      <c r="EI6" s="41"/>
-      <c r="EJ6" s="41"/>
-      <c r="EK6" s="41"/>
-      <c r="EL6" s="41"/>
-      <c r="EM6" s="41"/>
-      <c r="EN6" s="41"/>
-      <c r="EO6" s="41"/>
+      <c r="BY6" s="40"/>
+      <c r="BZ6" s="40"/>
+      <c r="CA6" s="40"/>
+      <c r="CB6" s="40"/>
+      <c r="CC6" s="40"/>
+      <c r="CD6" s="40"/>
+      <c r="CE6" s="40"/>
+      <c r="CF6" s="40"/>
+      <c r="CG6" s="40"/>
+      <c r="CH6" s="40"/>
+      <c r="CI6" s="40"/>
+      <c r="CJ6" s="40"/>
+      <c r="CK6" s="40"/>
+      <c r="CL6" s="40"/>
+      <c r="CM6" s="40"/>
+      <c r="CN6" s="40"/>
+      <c r="CO6" s="40"/>
+      <c r="CP6" s="40"/>
+      <c r="CQ6" s="40"/>
+      <c r="CR6" s="40"/>
+      <c r="CS6" s="40"/>
+      <c r="CT6" s="40"/>
+      <c r="CU6" s="40"/>
+      <c r="CV6" s="40"/>
+      <c r="CW6" s="40"/>
+      <c r="CX6" s="40"/>
+      <c r="CY6" s="40"/>
+      <c r="CZ6" s="40"/>
+      <c r="DA6" s="40"/>
+      <c r="DB6" s="40"/>
+      <c r="DC6" s="40"/>
+      <c r="DD6" s="40"/>
+      <c r="DE6" s="40"/>
+      <c r="DF6" s="40"/>
+      <c r="DG6" s="40"/>
+      <c r="DH6" s="40"/>
+      <c r="DI6" s="40"/>
+      <c r="DJ6" s="40"/>
+      <c r="DK6" s="40"/>
+      <c r="DL6" s="40"/>
+      <c r="DM6" s="40"/>
+      <c r="DN6" s="40"/>
+      <c r="DO6" s="40"/>
+      <c r="DP6" s="40"/>
+      <c r="DQ6" s="40"/>
+      <c r="DR6" s="40"/>
+      <c r="DS6" s="40"/>
+      <c r="DT6" s="40"/>
+      <c r="DU6" s="40"/>
+      <c r="DV6" s="40"/>
+      <c r="DW6" s="40"/>
+      <c r="DX6" s="40"/>
+      <c r="DY6" s="40"/>
+      <c r="DZ6" s="40"/>
+      <c r="EA6" s="40"/>
+      <c r="EB6" s="40"/>
+      <c r="EC6" s="40"/>
+      <c r="ED6" s="40"/>
+      <c r="EE6" s="40"/>
+      <c r="EF6" s="40"/>
+      <c r="EG6" s="40"/>
+      <c r="EH6" s="40"/>
+      <c r="EI6" s="40"/>
+      <c r="EJ6" s="40"/>
+      <c r="EK6" s="40"/>
+      <c r="EL6" s="40"/>
+      <c r="EM6" s="40"/>
+      <c r="EN6" s="40"/>
+      <c r="EO6" s="40"/>
     </row>
     <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="46">
+      <c r="B7" s="57"/>
+      <c r="C7" s="55">
         <v>30</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="54"/>
-      <c r="X7" s="54"/>
-      <c r="Y7" s="42"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="52"/>
-      <c r="AB7" s="52"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="42"/>
-      <c r="AE7" s="42"/>
-      <c r="AF7" s="42"/>
-      <c r="AG7" s="42"/>
-      <c r="AH7" s="42"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="42"/>
-      <c r="AK7" s="42"/>
-      <c r="AL7" s="42"/>
-      <c r="AM7" s="42"/>
-      <c r="AN7" s="42"/>
-      <c r="AO7" s="42"/>
-      <c r="AP7" s="42"/>
-      <c r="AQ7" s="42"/>
-      <c r="AR7" s="42"/>
-      <c r="AS7" s="42"/>
-      <c r="AT7" s="42"/>
-      <c r="AU7" s="42"/>
-      <c r="AV7" s="42"/>
-      <c r="AW7" s="42"/>
-      <c r="AX7" s="42"/>
-      <c r="AY7" s="42"/>
-      <c r="AZ7" s="42"/>
-      <c r="BA7" s="42"/>
-      <c r="BB7" s="42"/>
-      <c r="BC7" s="42"/>
-      <c r="BD7" s="42"/>
-      <c r="BE7" s="42"/>
-      <c r="BF7" s="42"/>
-      <c r="BG7" s="42"/>
-      <c r="BH7" s="42"/>
-      <c r="BI7" s="42"/>
-      <c r="BJ7" s="42"/>
-      <c r="BK7" s="42"/>
-      <c r="BL7" s="42"/>
-      <c r="BM7" s="42"/>
-      <c r="BN7" s="42"/>
-      <c r="BO7" s="42"/>
-      <c r="BP7" s="42"/>
-      <c r="BQ7" s="42"/>
-      <c r="BR7" s="42"/>
-      <c r="BS7" s="42"/>
-      <c r="BT7" s="42"/>
-      <c r="BU7" s="42"/>
-      <c r="BV7" s="42"/>
-      <c r="BW7" s="42"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="43"/>
+      <c r="AA7" s="48"/>
+      <c r="AB7" s="48"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="41"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="41"/>
+      <c r="AJ7" s="41"/>
+      <c r="AK7" s="41"/>
+      <c r="AL7" s="41"/>
+      <c r="AM7" s="41"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="41"/>
+      <c r="AP7" s="41"/>
+      <c r="AQ7" s="41"/>
+      <c r="AR7" s="41"/>
+      <c r="AS7" s="41"/>
+      <c r="AT7" s="41"/>
+      <c r="AU7" s="41"/>
+      <c r="AV7" s="41"/>
+      <c r="AW7" s="41"/>
+      <c r="AX7" s="41"/>
+      <c r="AY7" s="41"/>
+      <c r="AZ7" s="41"/>
+      <c r="BA7" s="41"/>
+      <c r="BB7" s="41"/>
+      <c r="BC7" s="41"/>
+      <c r="BD7" s="41"/>
+      <c r="BE7" s="41"/>
+      <c r="BF7" s="41"/>
+      <c r="BG7" s="41"/>
+      <c r="BH7" s="41"/>
+      <c r="BI7" s="41"/>
+      <c r="BJ7" s="41"/>
+      <c r="BK7" s="41"/>
+      <c r="BL7" s="41"/>
+      <c r="BM7" s="41"/>
+      <c r="BN7" s="41"/>
+      <c r="BO7" s="41"/>
+      <c r="BP7" s="41"/>
+      <c r="BQ7" s="41"/>
+      <c r="BR7" s="41"/>
+      <c r="BS7" s="41"/>
+      <c r="BT7" s="41"/>
+      <c r="BU7" s="41"/>
+      <c r="BV7" s="41"/>
+      <c r="BW7" s="41"/>
       <c r="BX7" s="50"/>
-      <c r="BY7" s="42"/>
-      <c r="BZ7" s="42"/>
-      <c r="CA7" s="42"/>
-      <c r="CB7" s="42"/>
-      <c r="CC7" s="42"/>
-      <c r="CD7" s="42"/>
-      <c r="CE7" s="42"/>
-      <c r="CF7" s="42"/>
-      <c r="CG7" s="42"/>
-      <c r="CH7" s="42"/>
-      <c r="CI7" s="42"/>
-      <c r="CJ7" s="42"/>
-      <c r="CK7" s="42"/>
-      <c r="CL7" s="42"/>
-      <c r="CM7" s="42"/>
-      <c r="CN7" s="42"/>
-      <c r="CO7" s="42"/>
-      <c r="CP7" s="42"/>
-      <c r="CQ7" s="42"/>
-      <c r="CR7" s="42"/>
-      <c r="CS7" s="42"/>
-      <c r="CT7" s="42"/>
-      <c r="CU7" s="42"/>
-      <c r="CV7" s="42"/>
-      <c r="CW7" s="42"/>
-      <c r="CX7" s="42"/>
-      <c r="CY7" s="42"/>
-      <c r="CZ7" s="42"/>
-      <c r="DA7" s="42"/>
-      <c r="DB7" s="42"/>
-      <c r="DC7" s="42"/>
-      <c r="DD7" s="42"/>
-      <c r="DE7" s="42"/>
-      <c r="DF7" s="42"/>
-      <c r="DG7" s="42"/>
-      <c r="DH7" s="42"/>
-      <c r="DI7" s="42"/>
-      <c r="DJ7" s="42"/>
-      <c r="DK7" s="42"/>
-      <c r="DL7" s="42"/>
-      <c r="DM7" s="42"/>
-      <c r="DN7" s="42"/>
-      <c r="DO7" s="42"/>
-      <c r="DP7" s="42"/>
-      <c r="DQ7" s="42"/>
-      <c r="DR7" s="42"/>
-      <c r="DS7" s="42"/>
-      <c r="DT7" s="42"/>
-      <c r="DU7" s="42"/>
-      <c r="DV7" s="42"/>
-      <c r="DW7" s="42"/>
-      <c r="DX7" s="42"/>
-      <c r="DY7" s="42"/>
-      <c r="DZ7" s="42"/>
-      <c r="EA7" s="42"/>
-      <c r="EB7" s="42"/>
-      <c r="EC7" s="42"/>
-      <c r="ED7" s="42"/>
-      <c r="EE7" s="42"/>
-      <c r="EF7" s="42"/>
-      <c r="EG7" s="42"/>
-      <c r="EH7" s="42"/>
-      <c r="EI7" s="42"/>
-      <c r="EJ7" s="42"/>
-      <c r="EK7" s="42"/>
-      <c r="EL7" s="42"/>
-      <c r="EM7" s="42"/>
-      <c r="EN7" s="42"/>
-      <c r="EO7" s="42"/>
+      <c r="BY7" s="41"/>
+      <c r="BZ7" s="41"/>
+      <c r="CA7" s="41"/>
+      <c r="CB7" s="41"/>
+      <c r="CC7" s="41"/>
+      <c r="CD7" s="41"/>
+      <c r="CE7" s="41"/>
+      <c r="CF7" s="41"/>
+      <c r="CG7" s="41"/>
+      <c r="CH7" s="41"/>
+      <c r="CI7" s="41"/>
+      <c r="CJ7" s="41"/>
+      <c r="CK7" s="41"/>
+      <c r="CL7" s="41"/>
+      <c r="CM7" s="41"/>
+      <c r="CN7" s="41"/>
+      <c r="CO7" s="41"/>
+      <c r="CP7" s="41"/>
+      <c r="CQ7" s="41"/>
+      <c r="CR7" s="41"/>
+      <c r="CS7" s="41"/>
+      <c r="CT7" s="41"/>
+      <c r="CU7" s="41"/>
+      <c r="CV7" s="41"/>
+      <c r="CW7" s="41"/>
+      <c r="CX7" s="41"/>
+      <c r="CY7" s="41"/>
+      <c r="CZ7" s="41"/>
+      <c r="DA7" s="41"/>
+      <c r="DB7" s="41"/>
+      <c r="DC7" s="41"/>
+      <c r="DD7" s="41"/>
+      <c r="DE7" s="41"/>
+      <c r="DF7" s="41"/>
+      <c r="DG7" s="41"/>
+      <c r="DH7" s="41"/>
+      <c r="DI7" s="41"/>
+      <c r="DJ7" s="41"/>
+      <c r="DK7" s="41"/>
+      <c r="DL7" s="41"/>
+      <c r="DM7" s="41"/>
+      <c r="DN7" s="41"/>
+      <c r="DO7" s="41"/>
+      <c r="DP7" s="41"/>
+      <c r="DQ7" s="41"/>
+      <c r="DR7" s="41"/>
+      <c r="DS7" s="41"/>
+      <c r="DT7" s="41"/>
+      <c r="DU7" s="41"/>
+      <c r="DV7" s="41"/>
+      <c r="DW7" s="41"/>
+      <c r="DX7" s="41"/>
+      <c r="DY7" s="41"/>
+      <c r="DZ7" s="41"/>
+      <c r="EA7" s="41"/>
+      <c r="EB7" s="41"/>
+      <c r="EC7" s="41"/>
+      <c r="ED7" s="41"/>
+      <c r="EE7" s="41"/>
+      <c r="EF7" s="41"/>
+      <c r="EG7" s="41"/>
+      <c r="EH7" s="41"/>
+      <c r="EI7" s="41"/>
+      <c r="EJ7" s="41"/>
+      <c r="EK7" s="41"/>
+      <c r="EL7" s="41"/>
+      <c r="EM7" s="41"/>
+      <c r="EN7" s="41"/>
+      <c r="EO7" s="41"/>
     </row>
     <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36">
+      <c r="B8" s="58"/>
+      <c r="C8" s="59">
         <v>150</v>
       </c>
-      <c r="D8" s="37"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="29">
+      <c r="F8" s="60">
         <v>1</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="60">
         <v>2</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="60">
         <v>3</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="60">
         <v>4</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="60">
         <v>5</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="60">
         <v>6</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="60">
         <v>7</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="60">
         <v>8</v>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="60">
         <v>9</v>
       </c>
-      <c r="O8" s="29">
+      <c r="O8" s="60">
         <v>10</v>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="60">
         <v>11</v>
       </c>
-      <c r="Q8" s="29">
+      <c r="Q8" s="60">
         <v>12</v>
       </c>
-      <c r="R8" s="29">
+      <c r="R8" s="60">
         <v>13</v>
       </c>
-      <c r="S8" s="29">
+      <c r="S8" s="60">
         <v>14</v>
       </c>
-      <c r="T8" s="29">
+      <c r="T8" s="60">
         <v>15</v>
       </c>
-      <c r="U8" s="29">
+      <c r="U8" s="60">
         <v>16</v>
       </c>
-      <c r="V8" s="29">
+      <c r="V8" s="60">
         <v>17</v>
       </c>
-      <c r="W8" s="29">
+      <c r="W8" s="60">
         <v>18</v>
       </c>
-      <c r="X8" s="29">
+      <c r="X8" s="60">
         <v>19</v>
       </c>
-      <c r="Y8" s="29">
+      <c r="Y8" s="60">
         <v>20</v>
       </c>
-      <c r="Z8" s="29">
+      <c r="Z8" s="60">
         <v>21</v>
       </c>
-      <c r="AA8" s="29">
+      <c r="AA8" s="60">
         <v>22</v>
       </c>
-      <c r="AB8" s="29">
+      <c r="AB8" s="60">
         <v>23</v>
       </c>
-      <c r="AC8" s="29">
+      <c r="AC8" s="60">
         <v>24</v>
       </c>
-      <c r="AD8" s="29">
+      <c r="AD8" s="60">
         <v>25</v>
       </c>
-      <c r="AE8" s="29">
+      <c r="AE8" s="60">
         <v>26</v>
       </c>
-      <c r="AF8" s="29">
+      <c r="AF8" s="60">
         <v>27</v>
       </c>
-      <c r="AG8" s="29">
+      <c r="AG8" s="60">
         <v>28</v>
       </c>
-      <c r="AH8" s="29">
+      <c r="AH8" s="60">
         <v>29</v>
       </c>
-      <c r="AI8" s="29">
+      <c r="AI8" s="60">
         <v>30</v>
       </c>
-      <c r="AJ8" s="29">
+      <c r="AJ8" s="60">
         <v>31</v>
       </c>
-      <c r="AK8" s="29">
+      <c r="AK8" s="60">
         <v>32</v>
       </c>
-      <c r="AL8" s="29">
+      <c r="AL8" s="60">
         <v>33</v>
       </c>
-      <c r="AM8" s="29">
+      <c r="AM8" s="60">
         <v>34</v>
       </c>
-      <c r="AN8" s="29">
+      <c r="AN8" s="60">
         <v>35</v>
       </c>
-      <c r="AO8" s="29">
+      <c r="AO8" s="60">
         <v>36</v>
       </c>
-      <c r="AP8" s="29">
+      <c r="AP8" s="60">
         <v>37</v>
       </c>
-      <c r="AQ8" s="29">
+      <c r="AQ8" s="60">
         <v>38</v>
       </c>
-      <c r="AR8" s="29">
+      <c r="AR8" s="60">
         <v>39</v>
       </c>
-      <c r="AS8" s="29">
+      <c r="AS8" s="60">
         <v>40</v>
       </c>
-      <c r="AT8" s="29">
+      <c r="AT8" s="60">
         <v>41</v>
       </c>
-      <c r="AU8" s="29">
+      <c r="AU8" s="60">
         <v>42</v>
       </c>
-      <c r="AV8" s="29">
+      <c r="AV8" s="60">
         <v>43</v>
       </c>
-      <c r="AW8" s="29">
+      <c r="AW8" s="60">
         <v>44</v>
       </c>
-      <c r="AX8" s="29">
+      <c r="AX8" s="60">
         <v>45</v>
       </c>
-      <c r="AY8" s="29">
+      <c r="AY8" s="60">
         <v>46</v>
       </c>
-      <c r="AZ8" s="29">
+      <c r="AZ8" s="60">
         <v>47</v>
       </c>
-      <c r="BA8" s="29">
+      <c r="BA8" s="60">
         <v>48</v>
       </c>
-      <c r="BB8" s="29">
+      <c r="BB8" s="60">
         <v>49</v>
       </c>
-      <c r="BC8" s="29">
+      <c r="BC8" s="60">
         <v>50</v>
       </c>
-      <c r="BD8" s="29">
+      <c r="BD8" s="60">
         <v>51</v>
       </c>
-      <c r="BE8" s="29">
+      <c r="BE8" s="60">
         <v>52</v>
       </c>
-      <c r="BF8" s="29">
+      <c r="BF8" s="60">
         <v>53</v>
       </c>
-      <c r="BG8" s="29">
+      <c r="BG8" s="60">
         <v>54</v>
       </c>
-      <c r="BH8" s="29">
+      <c r="BH8" s="60">
         <v>55</v>
       </c>
-      <c r="BI8" s="29">
+      <c r="BI8" s="60">
         <v>56</v>
       </c>
-      <c r="BJ8" s="29">
+      <c r="BJ8" s="60">
         <v>57</v>
       </c>
-      <c r="BK8" s="29">
+      <c r="BK8" s="60">
         <v>58</v>
       </c>
-      <c r="BL8" s="29">
+      <c r="BL8" s="60">
         <v>59</v>
       </c>
-      <c r="BM8" s="29">
+      <c r="BM8" s="60">
         <v>60</v>
       </c>
-      <c r="BN8" s="29">
+      <c r="BN8" s="60">
         <v>61</v>
       </c>
-      <c r="BO8" s="29">
+      <c r="BO8" s="60">
         <v>62</v>
       </c>
-      <c r="BP8" s="29">
+      <c r="BP8" s="60">
         <v>63</v>
       </c>
-      <c r="BQ8" s="29">
+      <c r="BQ8" s="60">
         <v>64</v>
       </c>
-      <c r="BR8" s="29">
+      <c r="BR8" s="60">
         <v>65</v>
       </c>
-      <c r="BS8" s="29">
+      <c r="BS8" s="60">
         <v>66</v>
       </c>
-      <c r="BT8" s="29">
+      <c r="BT8" s="60">
         <v>67</v>
       </c>
-      <c r="BU8" s="29">
+      <c r="BU8" s="60">
         <v>68</v>
       </c>
-      <c r="BV8" s="29">
+      <c r="BV8" s="60">
         <v>69</v>
       </c>
-      <c r="BW8" s="29">
+      <c r="BW8" s="60">
         <v>70</v>
       </c>
-      <c r="BX8" s="29">
+      <c r="BX8" s="60">
         <v>71</v>
       </c>
-      <c r="BY8" s="29">
+      <c r="BY8" s="60">
         <v>72</v>
       </c>
-      <c r="BZ8" s="29">
+      <c r="BZ8" s="60">
         <v>73</v>
       </c>
-      <c r="CA8" s="29">
+      <c r="CA8" s="60">
         <v>74</v>
       </c>
-      <c r="CB8" s="29">
+      <c r="CB8" s="60">
         <v>75</v>
       </c>
-      <c r="CC8" s="29">
+      <c r="CC8" s="60">
         <v>76</v>
       </c>
-      <c r="CD8" s="29">
+      <c r="CD8" s="60">
         <v>77</v>
       </c>
-      <c r="CE8" s="29">
+      <c r="CE8" s="60">
         <v>78</v>
       </c>
-      <c r="CF8" s="29">
+      <c r="CF8" s="60">
         <v>79</v>
       </c>
-      <c r="CG8" s="29">
+      <c r="CG8" s="60">
         <v>80</v>
       </c>
-      <c r="CH8" s="29">
+      <c r="CH8" s="60">
         <v>81</v>
       </c>
-      <c r="CI8" s="29">
+      <c r="CI8" s="60">
         <v>82</v>
       </c>
-      <c r="CJ8" s="29">
+      <c r="CJ8" s="60">
         <v>83</v>
       </c>
-      <c r="CK8" s="29">
+      <c r="CK8" s="60">
         <v>84</v>
       </c>
-      <c r="CL8" s="29">
+      <c r="CL8" s="60">
         <v>85</v>
       </c>
-      <c r="CM8" s="29">
+      <c r="CM8" s="60">
         <v>86</v>
       </c>
-      <c r="CN8" s="29">
+      <c r="CN8" s="60">
         <v>87</v>
       </c>
-      <c r="CO8" s="29">
+      <c r="CO8" s="60">
         <v>88</v>
       </c>
-      <c r="CP8" s="29">
+      <c r="CP8" s="60">
         <v>89</v>
       </c>
-      <c r="CQ8" s="29">
+      <c r="CQ8" s="60">
         <v>90</v>
       </c>
-      <c r="CR8" s="29">
+      <c r="CR8" s="60">
         <v>91</v>
       </c>
-      <c r="CS8" s="29">
+      <c r="CS8" s="60">
         <v>92</v>
       </c>
-      <c r="CT8" s="29">
+      <c r="CT8" s="60">
         <v>93</v>
       </c>
-      <c r="CU8" s="29">
+      <c r="CU8" s="60">
         <v>94</v>
       </c>
-      <c r="CV8" s="29">
+      <c r="CV8" s="60">
         <v>95</v>
       </c>
-      <c r="CW8" s="29">
+      <c r="CW8" s="60">
         <v>96</v>
       </c>
-      <c r="CX8" s="29">
+      <c r="CX8" s="60">
         <v>97</v>
       </c>
-      <c r="CY8" s="29">
+      <c r="CY8" s="60">
         <v>98</v>
       </c>
-      <c r="CZ8" s="29">
+      <c r="CZ8" s="60">
         <v>99</v>
       </c>
-      <c r="DA8" s="29">
+      <c r="DA8" s="60">
         <v>100</v>
       </c>
-      <c r="DB8" s="29">
+      <c r="DB8" s="60">
         <v>101</v>
       </c>
-      <c r="DC8" s="29">
+      <c r="DC8" s="60">
         <v>102</v>
       </c>
-      <c r="DD8" s="29">
+      <c r="DD8" s="60">
         <v>103</v>
       </c>
-      <c r="DE8" s="29">
+      <c r="DE8" s="60">
         <v>104</v>
       </c>
-      <c r="DF8" s="29">
+      <c r="DF8" s="60">
         <v>105</v>
       </c>
-      <c r="DG8" s="29">
+      <c r="DG8" s="60">
         <v>106</v>
       </c>
-      <c r="DH8" s="29">
+      <c r="DH8" s="60">
         <v>107</v>
       </c>
-      <c r="DI8" s="29">
+      <c r="DI8" s="60">
         <v>108</v>
       </c>
-      <c r="DJ8" s="29">
+      <c r="DJ8" s="60">
         <v>109</v>
       </c>
-      <c r="DK8" s="29">
+      <c r="DK8" s="60">
         <v>110</v>
       </c>
-      <c r="DL8" s="29">
+      <c r="DL8" s="60">
         <v>111</v>
       </c>
-      <c r="DM8" s="29">
+      <c r="DM8" s="60">
         <v>112</v>
       </c>
-      <c r="DN8" s="29">
+      <c r="DN8" s="60">
         <v>113</v>
       </c>
-      <c r="DO8" s="29">
+      <c r="DO8" s="60">
         <v>114</v>
       </c>
-      <c r="DP8" s="29">
+      <c r="DP8" s="60">
         <v>115</v>
       </c>
-      <c r="DQ8" s="29">
+      <c r="DQ8" s="60">
         <v>116</v>
       </c>
-      <c r="DR8" s="29">
+      <c r="DR8" s="60">
         <v>117</v>
       </c>
-      <c r="DS8" s="29">
+      <c r="DS8" s="60">
         <v>118</v>
       </c>
-      <c r="DT8" s="29">
+      <c r="DT8" s="60">
         <v>119</v>
       </c>
-      <c r="DU8" s="29">
+      <c r="DU8" s="60">
         <v>120</v>
       </c>
-      <c r="DV8" s="29">
+      <c r="DV8" s="60">
         <v>121</v>
       </c>
-      <c r="DW8" s="29">
+      <c r="DW8" s="60">
         <v>122</v>
       </c>
-      <c r="DX8" s="29">
+      <c r="DX8" s="60">
         <v>123</v>
       </c>
-      <c r="DY8" s="29">
+      <c r="DY8" s="60">
         <v>124</v>
       </c>
-      <c r="DZ8" s="29">
+      <c r="DZ8" s="60">
         <v>125</v>
       </c>
-      <c r="EA8" s="29">
+      <c r="EA8" s="60">
         <v>126</v>
       </c>
-      <c r="EB8" s="29">
+      <c r="EB8" s="60">
         <v>127</v>
       </c>
-      <c r="EC8" s="29">
+      <c r="EC8" s="60">
         <v>128</v>
       </c>
-      <c r="ED8" s="29">
+      <c r="ED8" s="60">
         <v>129</v>
       </c>
-      <c r="EE8" s="29">
+      <c r="EE8" s="60">
         <v>130</v>
       </c>
-      <c r="EF8" s="29">
+      <c r="EF8" s="60">
         <v>131</v>
       </c>
-      <c r="EG8" s="29">
+      <c r="EG8" s="60">
         <v>132</v>
       </c>
-      <c r="EH8" s="29">
+      <c r="EH8" s="60">
         <v>133</v>
       </c>
-      <c r="EI8" s="29">
+      <c r="EI8" s="60">
         <v>134</v>
       </c>
-      <c r="EJ8" s="29">
+      <c r="EJ8" s="60">
         <v>135</v>
       </c>
-      <c r="EK8" s="29">
+      <c r="EK8" s="60">
         <v>136</v>
       </c>
-      <c r="EL8" s="29">
+      <c r="EL8" s="60">
         <v>137</v>
       </c>
-      <c r="EM8" s="29">
+      <c r="EM8" s="60">
         <v>138</v>
       </c>
-      <c r="EN8" s="29">
+      <c r="EN8" s="60">
         <v>139</v>
       </c>
-      <c r="EO8" s="29">
+      <c r="EO8" s="60">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="39"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="30"/>
-      <c r="AD9" s="30"/>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="30"/>
-      <c r="AK9" s="30"/>
-      <c r="AL9" s="30"/>
-      <c r="AM9" s="30"/>
-      <c r="AN9" s="30"/>
-      <c r="AO9" s="30"/>
-      <c r="AP9" s="30"/>
-      <c r="AQ9" s="30"/>
-      <c r="AR9" s="30"/>
-      <c r="AS9" s="30"/>
-      <c r="AT9" s="30"/>
-      <c r="AU9" s="30"/>
-      <c r="AV9" s="30"/>
-      <c r="AW9" s="30"/>
-      <c r="AX9" s="30"/>
-      <c r="AY9" s="30"/>
-      <c r="AZ9" s="30"/>
-      <c r="BA9" s="30"/>
-      <c r="BB9" s="30"/>
-      <c r="BC9" s="30"/>
-      <c r="BD9" s="30"/>
-      <c r="BE9" s="30"/>
-      <c r="BF9" s="30"/>
-      <c r="BG9" s="30"/>
-      <c r="BH9" s="30"/>
-      <c r="BI9" s="30"/>
-      <c r="BJ9" s="30"/>
-      <c r="BK9" s="30"/>
-      <c r="BL9" s="30"/>
-      <c r="BM9" s="30"/>
-      <c r="BN9" s="30"/>
-      <c r="BO9" s="30"/>
-      <c r="BP9" s="30"/>
-      <c r="BQ9" s="30"/>
-      <c r="BR9" s="30"/>
-      <c r="BS9" s="30"/>
-      <c r="BT9" s="30"/>
-      <c r="BU9" s="30"/>
-      <c r="BV9" s="30"/>
-      <c r="BW9" s="30"/>
-      <c r="BX9" s="30"/>
-      <c r="BY9" s="30"/>
-      <c r="BZ9" s="30"/>
-      <c r="CA9" s="30"/>
-      <c r="CB9" s="30"/>
-      <c r="CC9" s="30"/>
-      <c r="CD9" s="30"/>
-      <c r="CE9" s="30"/>
-      <c r="CF9" s="30"/>
-      <c r="CG9" s="30"/>
-      <c r="CH9" s="30"/>
-      <c r="CI9" s="30"/>
-      <c r="CJ9" s="30"/>
-      <c r="CK9" s="30"/>
-      <c r="CL9" s="30"/>
-      <c r="CM9" s="30"/>
-      <c r="CN9" s="30"/>
-      <c r="CO9" s="30"/>
-      <c r="CP9" s="30"/>
-      <c r="CQ9" s="30"/>
-      <c r="CR9" s="30"/>
-      <c r="CS9" s="30"/>
-      <c r="CT9" s="30"/>
-      <c r="CU9" s="30"/>
-      <c r="CV9" s="30"/>
-      <c r="CW9" s="30"/>
-      <c r="CX9" s="30"/>
-      <c r="CY9" s="30"/>
-      <c r="CZ9" s="30"/>
-      <c r="DA9" s="30"/>
-      <c r="DB9" s="30"/>
-      <c r="DC9" s="30"/>
-      <c r="DD9" s="30"/>
-      <c r="DE9" s="30"/>
-      <c r="DF9" s="30"/>
-      <c r="DG9" s="30"/>
-      <c r="DH9" s="30"/>
-      <c r="DI9" s="30"/>
-      <c r="DJ9" s="30"/>
-      <c r="DK9" s="30"/>
-      <c r="DL9" s="30"/>
-      <c r="DM9" s="30"/>
-      <c r="DN9" s="30"/>
-      <c r="DO9" s="30"/>
-      <c r="DP9" s="30"/>
-      <c r="DQ9" s="30"/>
-      <c r="DR9" s="30"/>
-      <c r="DS9" s="30"/>
-      <c r="DT9" s="30"/>
-      <c r="DU9" s="30"/>
-      <c r="DV9" s="30"/>
-      <c r="DW9" s="30"/>
-      <c r="DX9" s="30"/>
-      <c r="DY9" s="30"/>
-      <c r="DZ9" s="30"/>
-      <c r="EA9" s="30"/>
-      <c r="EB9" s="30"/>
-      <c r="EC9" s="30"/>
-      <c r="ED9" s="30"/>
-      <c r="EE9" s="30"/>
-      <c r="EF9" s="30"/>
-      <c r="EG9" s="30"/>
-      <c r="EH9" s="30"/>
-      <c r="EI9" s="30"/>
-      <c r="EJ9" s="30"/>
-      <c r="EK9" s="30"/>
-      <c r="EL9" s="30"/>
-      <c r="EM9" s="30"/>
-      <c r="EN9" s="30"/>
-      <c r="EO9" s="30"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="61"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="61"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="61"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="61"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="61"/>
+      <c r="Y9" s="61"/>
+      <c r="Z9" s="61"/>
+      <c r="AA9" s="61"/>
+      <c r="AB9" s="61"/>
+      <c r="AC9" s="61"/>
+      <c r="AD9" s="61"/>
+      <c r="AE9" s="61"/>
+      <c r="AF9" s="61"/>
+      <c r="AG9" s="61"/>
+      <c r="AH9" s="61"/>
+      <c r="AI9" s="61"/>
+      <c r="AJ9" s="61"/>
+      <c r="AK9" s="61"/>
+      <c r="AL9" s="61"/>
+      <c r="AM9" s="61"/>
+      <c r="AN9" s="61"/>
+      <c r="AO9" s="61"/>
+      <c r="AP9" s="61"/>
+      <c r="AQ9" s="61"/>
+      <c r="AR9" s="61"/>
+      <c r="AS9" s="61"/>
+      <c r="AT9" s="61"/>
+      <c r="AU9" s="61"/>
+      <c r="AV9" s="61"/>
+      <c r="AW9" s="61"/>
+      <c r="AX9" s="61"/>
+      <c r="AY9" s="61"/>
+      <c r="AZ9" s="61"/>
+      <c r="BA9" s="61"/>
+      <c r="BB9" s="61"/>
+      <c r="BC9" s="61"/>
+      <c r="BD9" s="61"/>
+      <c r="BE9" s="61"/>
+      <c r="BF9" s="61"/>
+      <c r="BG9" s="61"/>
+      <c r="BH9" s="61"/>
+      <c r="BI9" s="61"/>
+      <c r="BJ9" s="61"/>
+      <c r="BK9" s="61"/>
+      <c r="BL9" s="61"/>
+      <c r="BM9" s="61"/>
+      <c r="BN9" s="61"/>
+      <c r="BO9" s="61"/>
+      <c r="BP9" s="61"/>
+      <c r="BQ9" s="61"/>
+      <c r="BR9" s="61"/>
+      <c r="BS9" s="61"/>
+      <c r="BT9" s="61"/>
+      <c r="BU9" s="61"/>
+      <c r="BV9" s="61"/>
+      <c r="BW9" s="61"/>
+      <c r="BX9" s="61"/>
+      <c r="BY9" s="61"/>
+      <c r="BZ9" s="61"/>
+      <c r="CA9" s="61"/>
+      <c r="CB9" s="61"/>
+      <c r="CC9" s="61"/>
+      <c r="CD9" s="61"/>
+      <c r="CE9" s="61"/>
+      <c r="CF9" s="61"/>
+      <c r="CG9" s="61"/>
+      <c r="CH9" s="61"/>
+      <c r="CI9" s="61"/>
+      <c r="CJ9" s="61"/>
+      <c r="CK9" s="61"/>
+      <c r="CL9" s="61"/>
+      <c r="CM9" s="61"/>
+      <c r="CN9" s="61"/>
+      <c r="CO9" s="61"/>
+      <c r="CP9" s="61"/>
+      <c r="CQ9" s="61"/>
+      <c r="CR9" s="61"/>
+      <c r="CS9" s="61"/>
+      <c r="CT9" s="61"/>
+      <c r="CU9" s="61"/>
+      <c r="CV9" s="61"/>
+      <c r="CW9" s="61"/>
+      <c r="CX9" s="61"/>
+      <c r="CY9" s="61"/>
+      <c r="CZ9" s="61"/>
+      <c r="DA9" s="61"/>
+      <c r="DB9" s="61"/>
+      <c r="DC9" s="61"/>
+      <c r="DD9" s="61"/>
+      <c r="DE9" s="61"/>
+      <c r="DF9" s="61"/>
+      <c r="DG9" s="61"/>
+      <c r="DH9" s="61"/>
+      <c r="DI9" s="61"/>
+      <c r="DJ9" s="61"/>
+      <c r="DK9" s="61"/>
+      <c r="DL9" s="61"/>
+      <c r="DM9" s="61"/>
+      <c r="DN9" s="61"/>
+      <c r="DO9" s="61"/>
+      <c r="DP9" s="61"/>
+      <c r="DQ9" s="61"/>
+      <c r="DR9" s="61"/>
+      <c r="DS9" s="61"/>
+      <c r="DT9" s="61"/>
+      <c r="DU9" s="61"/>
+      <c r="DV9" s="61"/>
+      <c r="DW9" s="61"/>
+      <c r="DX9" s="61"/>
+      <c r="DY9" s="61"/>
+      <c r="DZ9" s="61"/>
+      <c r="EA9" s="61"/>
+      <c r="EB9" s="61"/>
+      <c r="EC9" s="61"/>
+      <c r="ED9" s="61"/>
+      <c r="EE9" s="61"/>
+      <c r="EF9" s="61"/>
+      <c r="EG9" s="61"/>
+      <c r="EH9" s="61"/>
+      <c r="EI9" s="61"/>
+      <c r="EJ9" s="61"/>
+      <c r="EK9" s="61"/>
+      <c r="EL9" s="61"/>
+      <c r="EM9" s="61"/>
+      <c r="EN9" s="61"/>
+      <c r="EO9" s="61"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38"/>
-      <c r="B10" s="39"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
       <c r="C10" s="9"/>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -3362,7 +3370,7 @@
       </c>
       <c r="D12" s="14">
         <f t="shared" ref="D12:D28" si="0">COUNT(F12:EO12)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="11"/>
@@ -3473,9 +3481,15 @@
       <c r="BY12" s="11">
         <v>0</v>
       </c>
-      <c r="BZ12" s="11"/>
-      <c r="CA12" s="11"/>
-      <c r="CB12" s="11"/>
+      <c r="BZ12" s="11">
+        <v>0</v>
+      </c>
+      <c r="CA12" s="11">
+        <v>0</v>
+      </c>
+      <c r="CB12" s="11">
+        <v>0</v>
+      </c>
       <c r="CC12" s="11"/>
       <c r="CD12" s="11"/>
       <c r="CE12" s="11"/>
@@ -3554,7 +3568,7 @@
       </c>
       <c r="D13" s="14">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="11"/>
@@ -3689,9 +3703,15 @@
         <v>0</v>
       </c>
       <c r="BY13" s="11"/>
-      <c r="BZ13" s="11"/>
-      <c r="CA13" s="11"/>
-      <c r="CB13" s="11"/>
+      <c r="BZ13" s="11">
+        <v>0</v>
+      </c>
+      <c r="CA13" s="11">
+        <v>0</v>
+      </c>
+      <c r="CB13" s="11">
+        <v>0</v>
+      </c>
       <c r="CC13" s="11"/>
       <c r="CD13" s="11"/>
       <c r="CE13" s="11"/>
@@ -3774,7 +3794,7 @@
       </c>
       <c r="D14" s="14">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="11"/>
@@ -3883,9 +3903,15 @@
         <v>0</v>
       </c>
       <c r="BY14" s="11"/>
-      <c r="BZ14" s="11"/>
-      <c r="CA14" s="11"/>
-      <c r="CB14" s="11"/>
+      <c r="BZ14" s="11">
+        <v>0</v>
+      </c>
+      <c r="CA14" s="11">
+        <v>0</v>
+      </c>
+      <c r="CB14" s="11">
+        <v>0</v>
+      </c>
       <c r="CC14" s="11"/>
       <c r="CD14" s="11"/>
       <c r="CE14" s="11"/>
@@ -4164,7 +4190,7 @@
       </c>
       <c r="D16" s="14">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="11"/>
@@ -4267,9 +4293,15 @@
         <v>0</v>
       </c>
       <c r="BY16" s="11"/>
-      <c r="BZ16" s="11"/>
-      <c r="CA16" s="11"/>
-      <c r="CB16" s="11"/>
+      <c r="BZ16" s="11">
+        <v>0</v>
+      </c>
+      <c r="CA16" s="11">
+        <v>0</v>
+      </c>
+      <c r="CB16" s="11">
+        <v>0</v>
+      </c>
       <c r="CC16" s="11"/>
       <c r="CD16" s="11"/>
       <c r="CE16" s="11"/>
@@ -4446,113 +4478,113 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AO17" s="55" t="s">
+      <c r="AO17" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="56"/>
-      <c r="AQ17" s="56"/>
-      <c r="AR17" s="56"/>
-      <c r="AS17" s="56"/>
-      <c r="AT17" s="56"/>
-      <c r="AU17" s="56"/>
-      <c r="AV17" s="56"/>
-      <c r="AW17" s="56"/>
-      <c r="AX17" s="56"/>
-      <c r="AY17" s="56"/>
-      <c r="AZ17" s="56"/>
-      <c r="BA17" s="56"/>
-      <c r="BB17" s="56"/>
-      <c r="BC17" s="56"/>
-      <c r="BD17" s="56"/>
-      <c r="BE17" s="56"/>
-      <c r="BF17" s="56"/>
-      <c r="BG17" s="56"/>
-      <c r="BH17" s="56"/>
-      <c r="BI17" s="56"/>
-      <c r="BJ17" s="56"/>
-      <c r="BK17" s="56"/>
-      <c r="BL17" s="56"/>
-      <c r="BM17" s="56"/>
-      <c r="BN17" s="56"/>
-      <c r="BO17" s="56"/>
-      <c r="BP17" s="56"/>
-      <c r="BQ17" s="56"/>
-      <c r="BR17" s="56"/>
-      <c r="BS17" s="56"/>
-      <c r="BT17" s="56"/>
-      <c r="BU17" s="56"/>
-      <c r="BV17" s="56"/>
-      <c r="BW17" s="56"/>
-      <c r="BX17" s="56"/>
-      <c r="BY17" s="56"/>
-      <c r="BZ17" s="56"/>
-      <c r="CA17" s="56"/>
-      <c r="CB17" s="56"/>
-      <c r="CC17" s="56"/>
-      <c r="CD17" s="56"/>
-      <c r="CE17" s="56"/>
-      <c r="CF17" s="56"/>
-      <c r="CG17" s="56"/>
-      <c r="CH17" s="56"/>
-      <c r="CI17" s="56"/>
-      <c r="CJ17" s="56"/>
-      <c r="CK17" s="56"/>
-      <c r="CL17" s="56"/>
-      <c r="CM17" s="56"/>
-      <c r="CN17" s="56"/>
-      <c r="CO17" s="56"/>
-      <c r="CP17" s="56"/>
-      <c r="CQ17" s="56"/>
-      <c r="CR17" s="56"/>
-      <c r="CS17" s="56"/>
-      <c r="CT17" s="56"/>
-      <c r="CU17" s="56"/>
-      <c r="CV17" s="56"/>
-      <c r="CW17" s="56"/>
-      <c r="CX17" s="56"/>
-      <c r="CY17" s="56"/>
-      <c r="CZ17" s="56"/>
-      <c r="DA17" s="56"/>
-      <c r="DB17" s="56"/>
-      <c r="DC17" s="56"/>
-      <c r="DD17" s="56"/>
-      <c r="DE17" s="56"/>
-      <c r="DF17" s="56"/>
-      <c r="DG17" s="56"/>
-      <c r="DH17" s="56"/>
-      <c r="DI17" s="56"/>
-      <c r="DJ17" s="56"/>
-      <c r="DK17" s="56"/>
-      <c r="DL17" s="56"/>
-      <c r="DM17" s="56"/>
-      <c r="DN17" s="56"/>
-      <c r="DO17" s="56"/>
-      <c r="DP17" s="56"/>
-      <c r="DQ17" s="56"/>
-      <c r="DR17" s="56"/>
-      <c r="DS17" s="56"/>
-      <c r="DT17" s="56"/>
-      <c r="DU17" s="56"/>
-      <c r="DV17" s="56"/>
-      <c r="DW17" s="56"/>
-      <c r="DX17" s="56"/>
-      <c r="DY17" s="56"/>
-      <c r="DZ17" s="56"/>
-      <c r="EA17" s="56"/>
-      <c r="EB17" s="56"/>
-      <c r="EC17" s="56"/>
-      <c r="ED17" s="56"/>
-      <c r="EE17" s="56"/>
-      <c r="EF17" s="56"/>
-      <c r="EG17" s="56"/>
-      <c r="EH17" s="56"/>
-      <c r="EI17" s="56"/>
-      <c r="EJ17" s="56"/>
-      <c r="EK17" s="56"/>
-      <c r="EL17" s="56"/>
-      <c r="EM17" s="56"/>
-      <c r="EN17" s="56"/>
-      <c r="EO17" s="57"/>
+      <c r="AP17" s="24"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="24"/>
+      <c r="AS17" s="24"/>
+      <c r="AT17" s="24"/>
+      <c r="AU17" s="24"/>
+      <c r="AV17" s="24"/>
+      <c r="AW17" s="24"/>
+      <c r="AX17" s="24"/>
+      <c r="AY17" s="24"/>
+      <c r="AZ17" s="24"/>
+      <c r="BA17" s="24"/>
+      <c r="BB17" s="24"/>
+      <c r="BC17" s="24"/>
+      <c r="BD17" s="24"/>
+      <c r="BE17" s="24"/>
+      <c r="BF17" s="24"/>
+      <c r="BG17" s="24"/>
+      <c r="BH17" s="24"/>
+      <c r="BI17" s="24"/>
+      <c r="BJ17" s="24"/>
+      <c r="BK17" s="24"/>
+      <c r="BL17" s="24"/>
+      <c r="BM17" s="24"/>
+      <c r="BN17" s="24"/>
+      <c r="BO17" s="24"/>
+      <c r="BP17" s="24"/>
+      <c r="BQ17" s="24"/>
+      <c r="BR17" s="24"/>
+      <c r="BS17" s="24"/>
+      <c r="BT17" s="24"/>
+      <c r="BU17" s="24"/>
+      <c r="BV17" s="24"/>
+      <c r="BW17" s="24"/>
+      <c r="BX17" s="24"/>
+      <c r="BY17" s="24"/>
+      <c r="BZ17" s="24"/>
+      <c r="CA17" s="24"/>
+      <c r="CB17" s="24"/>
+      <c r="CC17" s="24"/>
+      <c r="CD17" s="24"/>
+      <c r="CE17" s="24"/>
+      <c r="CF17" s="24"/>
+      <c r="CG17" s="24"/>
+      <c r="CH17" s="24"/>
+      <c r="CI17" s="24"/>
+      <c r="CJ17" s="24"/>
+      <c r="CK17" s="24"/>
+      <c r="CL17" s="24"/>
+      <c r="CM17" s="24"/>
+      <c r="CN17" s="24"/>
+      <c r="CO17" s="24"/>
+      <c r="CP17" s="24"/>
+      <c r="CQ17" s="24"/>
+      <c r="CR17" s="24"/>
+      <c r="CS17" s="24"/>
+      <c r="CT17" s="24"/>
+      <c r="CU17" s="24"/>
+      <c r="CV17" s="24"/>
+      <c r="CW17" s="24"/>
+      <c r="CX17" s="24"/>
+      <c r="CY17" s="24"/>
+      <c r="CZ17" s="24"/>
+      <c r="DA17" s="24"/>
+      <c r="DB17" s="24"/>
+      <c r="DC17" s="24"/>
+      <c r="DD17" s="24"/>
+      <c r="DE17" s="24"/>
+      <c r="DF17" s="24"/>
+      <c r="DG17" s="24"/>
+      <c r="DH17" s="24"/>
+      <c r="DI17" s="24"/>
+      <c r="DJ17" s="24"/>
+      <c r="DK17" s="24"/>
+      <c r="DL17" s="24"/>
+      <c r="DM17" s="24"/>
+      <c r="DN17" s="24"/>
+      <c r="DO17" s="24"/>
+      <c r="DP17" s="24"/>
+      <c r="DQ17" s="24"/>
+      <c r="DR17" s="24"/>
+      <c r="DS17" s="24"/>
+      <c r="DT17" s="24"/>
+      <c r="DU17" s="24"/>
+      <c r="DV17" s="24"/>
+      <c r="DW17" s="24"/>
+      <c r="DX17" s="24"/>
+      <c r="DY17" s="24"/>
+      <c r="DZ17" s="24"/>
+      <c r="EA17" s="24"/>
+      <c r="EB17" s="24"/>
+      <c r="EC17" s="24"/>
+      <c r="ED17" s="24"/>
+      <c r="EE17" s="24"/>
+      <c r="EF17" s="24"/>
+      <c r="EG17" s="24"/>
+      <c r="EH17" s="24"/>
+      <c r="EI17" s="24"/>
+      <c r="EJ17" s="24"/>
+      <c r="EK17" s="24"/>
+      <c r="EL17" s="24"/>
+      <c r="EM17" s="24"/>
+      <c r="EN17" s="24"/>
+      <c r="EO17" s="25"/>
     </row>
     <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
@@ -4946,7 +4978,7 @@
       </c>
       <c r="D20" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="11"/>
@@ -5035,7 +5067,9 @@
       <c r="BY20" s="11"/>
       <c r="BZ20" s="11"/>
       <c r="CA20" s="11"/>
-      <c r="CB20" s="11"/>
+      <c r="CB20" s="11">
+        <v>0</v>
+      </c>
       <c r="CC20" s="11"/>
       <c r="CD20" s="11"/>
       <c r="CE20" s="11"/>
@@ -5398,7 +5432,7 @@
       </c>
       <c r="D22" s="14">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="11"/>
@@ -5527,9 +5561,15 @@
       <c r="BY22" s="11">
         <v>0</v>
       </c>
-      <c r="BZ22" s="11"/>
-      <c r="CA22" s="11"/>
-      <c r="CB22" s="11"/>
+      <c r="BZ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="CA22" s="11">
+        <v>0</v>
+      </c>
+      <c r="CB22" s="11">
+        <v>0</v>
+      </c>
       <c r="CC22" s="11"/>
       <c r="CD22" s="11"/>
       <c r="CE22" s="11"/>
@@ -6332,7 +6372,7 @@
       </c>
       <c r="D26" s="14">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="11"/>
@@ -6461,9 +6501,15 @@
       <c r="BY26" s="11">
         <v>0</v>
       </c>
-      <c r="BZ26" s="11"/>
-      <c r="CA26" s="11"/>
-      <c r="CB26" s="11"/>
+      <c r="BZ26" s="11">
+        <v>0</v>
+      </c>
+      <c r="CA26" s="11">
+        <v>0</v>
+      </c>
+      <c r="CB26" s="11">
+        <v>0</v>
+      </c>
       <c r="CC26" s="11"/>
       <c r="CD26" s="11"/>
       <c r="CE26" s="11"/>
@@ -6830,149 +6876,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="31"/>
-      <c r="AM28" s="31"/>
-      <c r="AN28" s="31"/>
-      <c r="AO28" s="31"/>
-      <c r="AP28" s="31"/>
-      <c r="AQ28" s="31"/>
-      <c r="AR28" s="31"/>
-      <c r="AS28" s="31"/>
-      <c r="AT28" s="31"/>
-      <c r="AU28" s="31"/>
-      <c r="AV28" s="31"/>
-      <c r="AW28" s="31"/>
-      <c r="AX28" s="31"/>
-      <c r="AY28" s="31"/>
-      <c r="AZ28" s="31"/>
-      <c r="BA28" s="31"/>
-      <c r="BB28" s="31"/>
-      <c r="BC28" s="31"/>
-      <c r="BD28" s="31"/>
-      <c r="BE28" s="31"/>
-      <c r="BF28" s="31"/>
-      <c r="BG28" s="31"/>
-      <c r="BH28" s="31"/>
-      <c r="BI28" s="31"/>
-      <c r="BJ28" s="31"/>
-      <c r="BK28" s="31"/>
-      <c r="BL28" s="31"/>
-      <c r="BM28" s="31"/>
-      <c r="BN28" s="31"/>
-      <c r="BO28" s="31"/>
-      <c r="BP28" s="31"/>
-      <c r="BQ28" s="31"/>
-      <c r="BR28" s="31"/>
-      <c r="BS28" s="31"/>
-      <c r="BT28" s="31"/>
-      <c r="BU28" s="31"/>
-      <c r="BV28" s="31"/>
-      <c r="BW28" s="31"/>
-      <c r="BX28" s="31"/>
-      <c r="BY28" s="31"/>
-      <c r="BZ28" s="31"/>
-      <c r="CA28" s="31"/>
-      <c r="CB28" s="31"/>
-      <c r="CC28" s="31"/>
-      <c r="CD28" s="31"/>
-      <c r="CE28" s="31"/>
-      <c r="CF28" s="31"/>
-      <c r="CG28" s="31"/>
-      <c r="CH28" s="31"/>
-      <c r="CI28" s="31"/>
-      <c r="CJ28" s="31"/>
-      <c r="CK28" s="31"/>
-      <c r="CL28" s="31"/>
-      <c r="CM28" s="31"/>
-      <c r="CN28" s="31"/>
-      <c r="CO28" s="31"/>
-      <c r="CP28" s="31"/>
-      <c r="CQ28" s="31"/>
-      <c r="CR28" s="31"/>
-      <c r="CS28" s="31"/>
-      <c r="CT28" s="31"/>
-      <c r="CU28" s="31"/>
-      <c r="CV28" s="31"/>
-      <c r="CW28" s="31"/>
-      <c r="CX28" s="31"/>
-      <c r="CY28" s="31"/>
-      <c r="CZ28" s="31"/>
-      <c r="DA28" s="31"/>
-      <c r="DB28" s="31"/>
-      <c r="DC28" s="31"/>
-      <c r="DD28" s="31"/>
-      <c r="DE28" s="31"/>
-      <c r="DF28" s="31"/>
-      <c r="DG28" s="31"/>
-      <c r="DH28" s="31"/>
-      <c r="DI28" s="31"/>
-      <c r="DJ28" s="31"/>
-      <c r="DK28" s="31"/>
-      <c r="DL28" s="31"/>
-      <c r="DM28" s="31"/>
-      <c r="DN28" s="31"/>
-      <c r="DO28" s="31"/>
-      <c r="DP28" s="31"/>
-      <c r="DQ28" s="31"/>
-      <c r="DR28" s="31"/>
-      <c r="DS28" s="31"/>
-      <c r="DT28" s="31"/>
-      <c r="DU28" s="31"/>
-      <c r="DV28" s="31"/>
-      <c r="DW28" s="31"/>
-      <c r="DX28" s="31"/>
-      <c r="DY28" s="31"/>
-      <c r="DZ28" s="31"/>
-      <c r="EA28" s="31"/>
-      <c r="EB28" s="31"/>
-      <c r="EC28" s="31"/>
-      <c r="ED28" s="31"/>
-      <c r="EE28" s="31"/>
-      <c r="EF28" s="31"/>
-      <c r="EG28" s="31"/>
-      <c r="EH28" s="31"/>
-      <c r="EI28" s="31"/>
-      <c r="EJ28" s="31"/>
-      <c r="EK28" s="31"/>
-      <c r="EL28" s="31"/>
-      <c r="EM28" s="31"/>
-      <c r="EN28" s="31"/>
-      <c r="EO28" s="31"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="65"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="65"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
+      <c r="Z28" s="65"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="65"/>
+      <c r="AC28" s="65"/>
+      <c r="AD28" s="65"/>
+      <c r="AE28" s="65"/>
+      <c r="AF28" s="65"/>
+      <c r="AG28" s="65"/>
+      <c r="AH28" s="65"/>
+      <c r="AI28" s="65"/>
+      <c r="AJ28" s="65"/>
+      <c r="AK28" s="65"/>
+      <c r="AL28" s="65"/>
+      <c r="AM28" s="65"/>
+      <c r="AN28" s="65"/>
+      <c r="AO28" s="65"/>
+      <c r="AP28" s="65"/>
+      <c r="AQ28" s="65"/>
+      <c r="AR28" s="65"/>
+      <c r="AS28" s="65"/>
+      <c r="AT28" s="65"/>
+      <c r="AU28" s="65"/>
+      <c r="AV28" s="65"/>
+      <c r="AW28" s="65"/>
+      <c r="AX28" s="65"/>
+      <c r="AY28" s="65"/>
+      <c r="AZ28" s="65"/>
+      <c r="BA28" s="65"/>
+      <c r="BB28" s="65"/>
+      <c r="BC28" s="65"/>
+      <c r="BD28" s="65"/>
+      <c r="BE28" s="65"/>
+      <c r="BF28" s="65"/>
+      <c r="BG28" s="65"/>
+      <c r="BH28" s="65"/>
+      <c r="BI28" s="65"/>
+      <c r="BJ28" s="65"/>
+      <c r="BK28" s="65"/>
+      <c r="BL28" s="65"/>
+      <c r="BM28" s="65"/>
+      <c r="BN28" s="65"/>
+      <c r="BO28" s="65"/>
+      <c r="BP28" s="65"/>
+      <c r="BQ28" s="65"/>
+      <c r="BR28" s="65"/>
+      <c r="BS28" s="65"/>
+      <c r="BT28" s="65"/>
+      <c r="BU28" s="65"/>
+      <c r="BV28" s="65"/>
+      <c r="BW28" s="65"/>
+      <c r="BX28" s="65"/>
+      <c r="BY28" s="65"/>
+      <c r="BZ28" s="65"/>
+      <c r="CA28" s="65"/>
+      <c r="CB28" s="65"/>
+      <c r="CC28" s="65"/>
+      <c r="CD28" s="65"/>
+      <c r="CE28" s="65"/>
+      <c r="CF28" s="65"/>
+      <c r="CG28" s="65"/>
+      <c r="CH28" s="65"/>
+      <c r="CI28" s="65"/>
+      <c r="CJ28" s="65"/>
+      <c r="CK28" s="65"/>
+      <c r="CL28" s="65"/>
+      <c r="CM28" s="65"/>
+      <c r="CN28" s="65"/>
+      <c r="CO28" s="65"/>
+      <c r="CP28" s="65"/>
+      <c r="CQ28" s="65"/>
+      <c r="CR28" s="65"/>
+      <c r="CS28" s="65"/>
+      <c r="CT28" s="65"/>
+      <c r="CU28" s="65"/>
+      <c r="CV28" s="65"/>
+      <c r="CW28" s="65"/>
+      <c r="CX28" s="65"/>
+      <c r="CY28" s="65"/>
+      <c r="CZ28" s="65"/>
+      <c r="DA28" s="65"/>
+      <c r="DB28" s="65"/>
+      <c r="DC28" s="65"/>
+      <c r="DD28" s="65"/>
+      <c r="DE28" s="65"/>
+      <c r="DF28" s="65"/>
+      <c r="DG28" s="65"/>
+      <c r="DH28" s="65"/>
+      <c r="DI28" s="65"/>
+      <c r="DJ28" s="65"/>
+      <c r="DK28" s="65"/>
+      <c r="DL28" s="65"/>
+      <c r="DM28" s="65"/>
+      <c r="DN28" s="65"/>
+      <c r="DO28" s="65"/>
+      <c r="DP28" s="65"/>
+      <c r="DQ28" s="65"/>
+      <c r="DR28" s="65"/>
+      <c r="DS28" s="65"/>
+      <c r="DT28" s="65"/>
+      <c r="DU28" s="65"/>
+      <c r="DV28" s="65"/>
+      <c r="DW28" s="65"/>
+      <c r="DX28" s="65"/>
+      <c r="DY28" s="65"/>
+      <c r="DZ28" s="65"/>
+      <c r="EA28" s="65"/>
+      <c r="EB28" s="65"/>
+      <c r="EC28" s="65"/>
+      <c r="ED28" s="65"/>
+      <c r="EE28" s="65"/>
+      <c r="EF28" s="65"/>
+      <c r="EG28" s="65"/>
+      <c r="EH28" s="65"/>
+      <c r="EI28" s="65"/>
+      <c r="EJ28" s="65"/>
+      <c r="EK28" s="65"/>
+      <c r="EL28" s="65"/>
+      <c r="EM28" s="65"/>
+      <c r="EN28" s="65"/>
+      <c r="EO28" s="65"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -6980,7 +7026,301 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="317">
+  <mergeCells count="318">
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BQ1:BU1"/>
+    <mergeCell ref="BV1:BX1"/>
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="DV8:DV9"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="E28:EO28"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="AO17:EO17"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D2"/>
@@ -7005,299 +7345,6 @@
     <mergeCell ref="Q2:Q7"/>
     <mergeCell ref="R2:R7"/>
     <mergeCell ref="BM1:BO1"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="BH1:BL1"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="E28:EO28"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="BQ1:BU1"/>
-    <mergeCell ref="BV1:BX1"/>
-    <mergeCell ref="EH8:EH9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="DV8:DV9"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DA8:DA9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\designer\Desktop\Front\01. - Front-end-docs\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8A0702-49D6-4E98-B8B6-2CBA26E2BE0E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8A0702-49D6-4E98-B8B6-2CBA26E2BE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="367" yWindow="14" windowWidth="20962" windowHeight="9727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="301 ინტეგრირებული" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -769,7 +782,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -807,23 +820,113 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -855,9 +958,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -875,99 +975,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1186,145 +1193,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:ET31"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="2"/>
+    <col min="1" max="1" width="3.5703125" style="2"/>
     <col min="2" max="3" width="21" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="3.625" style="1"/>
+    <col min="5" max="5" width="5.5703125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="3.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-      <c r="F1" s="31">
+      <c r="C1" s="57"/>
+      <c r="D1" s="58"/>
+      <c r="F1" s="61">
         <v>4</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33">
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="32">
         <v>3</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33">
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32">
         <v>4</v>
       </c>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34">
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="63">
         <v>4</v>
       </c>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="34">
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="63">
         <v>4</v>
       </c>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="34">
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="63">
         <v>4</v>
       </c>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="66">
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="30">
         <v>2</v>
       </c>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="44">
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="21">
         <v>4</v>
       </c>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="44">
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="23"/>
+      <c r="AI1" s="21">
         <v>4</v>
       </c>
-      <c r="AJ1" s="45"/>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="44">
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="23"/>
+      <c r="AM1" s="21">
         <v>2</v>
       </c>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="44">
+      <c r="AN1" s="23"/>
+      <c r="AO1" s="21">
         <v>4</v>
       </c>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="44">
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
+      <c r="AR1" s="23"/>
+      <c r="AS1" s="21">
         <v>5</v>
       </c>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
-      <c r="AV1" s="45"/>
-      <c r="AW1" s="46"/>
+      <c r="AT1" s="22"/>
+      <c r="AU1" s="22"/>
+      <c r="AV1" s="22"/>
+      <c r="AW1" s="23"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="44">
+      <c r="AY1" s="21">
         <v>5</v>
       </c>
-      <c r="AZ1" s="45"/>
-      <c r="BA1" s="45"/>
-      <c r="BB1" s="45"/>
-      <c r="BC1" s="46"/>
-      <c r="BD1" s="44">
+      <c r="AZ1" s="22"/>
+      <c r="BA1" s="22"/>
+      <c r="BB1" s="22"/>
+      <c r="BC1" s="23"/>
+      <c r="BD1" s="21">
         <v>3</v>
       </c>
-      <c r="BE1" s="45"/>
-      <c r="BF1" s="46"/>
-      <c r="BG1" s="20">
+      <c r="BE1" s="22"/>
+      <c r="BF1" s="23"/>
+      <c r="BG1" s="3">
         <v>1</v>
       </c>
-      <c r="BH1" s="33">
+      <c r="BH1" s="32">
         <v>5</v>
       </c>
-      <c r="BI1" s="33"/>
-      <c r="BJ1" s="33"/>
-      <c r="BK1" s="33"/>
-      <c r="BL1" s="33"/>
-      <c r="BM1" s="44">
+      <c r="BI1" s="32"/>
+      <c r="BJ1" s="32"/>
+      <c r="BK1" s="32"/>
+      <c r="BL1" s="32"/>
+      <c r="BM1" s="21">
         <v>3</v>
       </c>
-      <c r="BN1" s="45"/>
-      <c r="BO1" s="46"/>
-      <c r="BP1" s="21">
+      <c r="BN1" s="22"/>
+      <c r="BO1" s="23"/>
+      <c r="BP1" s="20">
         <v>1</v>
       </c>
-      <c r="BQ1" s="68">
+      <c r="BQ1" s="24">
         <v>5</v>
       </c>
-      <c r="BR1" s="69"/>
-      <c r="BS1" s="69"/>
-      <c r="BT1" s="69"/>
-      <c r="BU1" s="70"/>
-      <c r="BV1" s="44">
+      <c r="BR1" s="25"/>
+      <c r="BS1" s="25"/>
+      <c r="BT1" s="25"/>
+      <c r="BU1" s="26"/>
+      <c r="BV1" s="21">
         <v>3</v>
       </c>
-      <c r="BW1" s="45"/>
-      <c r="BX1" s="46"/>
-      <c r="BY1" s="22">
+      <c r="BW1" s="22"/>
+      <c r="BX1" s="23"/>
+      <c r="BY1" s="3">
         <v>1</v>
       </c>
-      <c r="BZ1" s="44">
+      <c r="BZ1" s="21">
         <v>3</v>
       </c>
-      <c r="CA1" s="45"/>
-      <c r="CB1" s="46"/>
+      <c r="CA1" s="22"/>
+      <c r="CB1" s="23"/>
       <c r="CC1" s="4"/>
       <c r="CD1" s="4"/>
       <c r="CE1" s="4"/>
@@ -1396,1644 +1403,1644 @@
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="37" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="42" t="s">
+      <c r="K2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="42" t="s">
+      <c r="L2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="42" t="s">
+      <c r="R2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="42" t="s">
+      <c r="S2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="V2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="W2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="42" t="s">
+      <c r="X2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Y2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="Z2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="47" t="s">
+      <c r="AA2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="47" t="s">
+      <c r="AB2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="40">
+      <c r="AC2" s="39">
         <v>46199</v>
       </c>
-      <c r="AD2" s="40">
+      <c r="AD2" s="39">
         <v>46199</v>
       </c>
-      <c r="AE2" s="40">
+      <c r="AE2" s="39">
         <v>46202</v>
       </c>
-      <c r="AF2" s="40">
+      <c r="AF2" s="39">
         <v>46202</v>
       </c>
-      <c r="AG2" s="40">
+      <c r="AG2" s="39">
         <v>46202</v>
       </c>
-      <c r="AH2" s="40">
+      <c r="AH2" s="39">
         <v>46202</v>
       </c>
-      <c r="AI2" s="40">
+      <c r="AI2" s="39">
         <v>46205</v>
       </c>
-      <c r="AJ2" s="40">
+      <c r="AJ2" s="39">
         <v>46205</v>
       </c>
-      <c r="AK2" s="40">
+      <c r="AK2" s="39">
         <v>46205</v>
       </c>
-      <c r="AL2" s="40">
+      <c r="AL2" s="39">
         <v>46205</v>
       </c>
-      <c r="AM2" s="40">
+      <c r="AM2" s="39">
         <v>46206</v>
       </c>
-      <c r="AN2" s="40">
+      <c r="AN2" s="39">
         <v>46206</v>
       </c>
-      <c r="AO2" s="40">
+      <c r="AO2" s="39">
         <v>46212</v>
       </c>
-      <c r="AP2" s="40">
+      <c r="AP2" s="39">
         <v>46212</v>
       </c>
-      <c r="AQ2" s="40">
+      <c r="AQ2" s="39">
         <v>46212</v>
       </c>
-      <c r="AR2" s="40">
+      <c r="AR2" s="39">
         <v>46212</v>
       </c>
-      <c r="AS2" s="40">
+      <c r="AS2" s="39">
         <v>46213</v>
       </c>
-      <c r="AT2" s="40">
+      <c r="AT2" s="39">
         <v>46213</v>
       </c>
-      <c r="AU2" s="40">
+      <c r="AU2" s="39">
         <v>46213</v>
       </c>
-      <c r="AV2" s="40">
+      <c r="AV2" s="39">
         <v>46213</v>
       </c>
-      <c r="AW2" s="40">
+      <c r="AW2" s="39">
         <v>46213</v>
       </c>
-      <c r="AX2" s="40">
+      <c r="AX2" s="39">
         <v>46218</v>
       </c>
-      <c r="AY2" s="40">
+      <c r="AY2" s="39">
         <v>46219</v>
       </c>
-      <c r="AZ2" s="40">
+      <c r="AZ2" s="39">
         <v>46219</v>
       </c>
-      <c r="BA2" s="40">
+      <c r="BA2" s="39">
         <v>46219</v>
       </c>
-      <c r="BB2" s="40">
+      <c r="BB2" s="39">
         <v>46219</v>
       </c>
-      <c r="BC2" s="40">
+      <c r="BC2" s="39">
         <v>46219</v>
       </c>
-      <c r="BD2" s="40">
+      <c r="BD2" s="39">
         <v>46220</v>
       </c>
-      <c r="BE2" s="40">
+      <c r="BE2" s="39">
         <v>46220</v>
       </c>
-      <c r="BF2" s="40">
+      <c r="BF2" s="39">
         <v>46220</v>
       </c>
-      <c r="BG2" s="40">
+      <c r="BG2" s="39">
         <v>46225</v>
       </c>
-      <c r="BH2" s="40">
+      <c r="BH2" s="39">
         <v>46226</v>
       </c>
-      <c r="BI2" s="40">
+      <c r="BI2" s="39">
         <v>46226</v>
       </c>
-      <c r="BJ2" s="40">
+      <c r="BJ2" s="39">
         <v>46226</v>
       </c>
-      <c r="BK2" s="40">
+      <c r="BK2" s="39">
         <v>46226</v>
       </c>
-      <c r="BL2" s="40">
+      <c r="BL2" s="39">
         <v>46226</v>
       </c>
-      <c r="BM2" s="40">
+      <c r="BM2" s="39">
         <v>46227</v>
       </c>
-      <c r="BN2" s="40">
+      <c r="BN2" s="39">
         <v>46227</v>
       </c>
-      <c r="BO2" s="40">
+      <c r="BO2" s="39">
         <v>46227</v>
       </c>
-      <c r="BP2" s="40">
+      <c r="BP2" s="39">
         <v>46232</v>
       </c>
-      <c r="BQ2" s="40">
+      <c r="BQ2" s="39">
         <v>46233</v>
       </c>
-      <c r="BR2" s="40">
+      <c r="BR2" s="39">
         <v>46233</v>
       </c>
-      <c r="BS2" s="40">
+      <c r="BS2" s="39">
         <v>46233</v>
       </c>
-      <c r="BT2" s="40">
+      <c r="BT2" s="39">
         <v>46233</v>
       </c>
-      <c r="BU2" s="40">
+      <c r="BU2" s="39">
         <v>46233</v>
       </c>
-      <c r="BV2" s="40">
+      <c r="BV2" s="39">
         <v>46234</v>
       </c>
-      <c r="BW2" s="40">
+      <c r="BW2" s="39">
         <v>46234</v>
       </c>
-      <c r="BX2" s="49">
+      <c r="BX2" s="47">
         <v>46234</v>
       </c>
-      <c r="BY2" s="40">
+      <c r="BY2" s="39">
         <v>46274</v>
       </c>
-      <c r="BZ2" s="40">
+      <c r="BZ2" s="39">
         <v>46276</v>
       </c>
-      <c r="CA2" s="40">
+      <c r="CA2" s="39">
         <v>46276</v>
       </c>
-      <c r="CB2" s="40">
+      <c r="CB2" s="39">
         <v>46276</v>
       </c>
-      <c r="CC2" s="40"/>
-      <c r="CD2" s="40"/>
-      <c r="CE2" s="40"/>
-      <c r="CF2" s="40"/>
-      <c r="CG2" s="40"/>
-      <c r="CH2" s="40"/>
-      <c r="CI2" s="40"/>
-      <c r="CJ2" s="40"/>
-      <c r="CK2" s="40"/>
-      <c r="CL2" s="40"/>
-      <c r="CM2" s="40"/>
-      <c r="CN2" s="40"/>
-      <c r="CO2" s="40"/>
-      <c r="CP2" s="40"/>
-      <c r="CQ2" s="40"/>
-      <c r="CR2" s="40"/>
-      <c r="CS2" s="40"/>
-      <c r="CT2" s="40"/>
-      <c r="CU2" s="40"/>
-      <c r="CV2" s="40"/>
-      <c r="CW2" s="40"/>
-      <c r="CX2" s="40"/>
-      <c r="CY2" s="40"/>
-      <c r="CZ2" s="40"/>
-      <c r="DA2" s="40"/>
-      <c r="DB2" s="40"/>
-      <c r="DC2" s="40"/>
-      <c r="DD2" s="40"/>
-      <c r="DE2" s="40"/>
-      <c r="DF2" s="40"/>
-      <c r="DG2" s="40"/>
-      <c r="DH2" s="40"/>
-      <c r="DI2" s="40"/>
-      <c r="DJ2" s="40"/>
-      <c r="DK2" s="40"/>
-      <c r="DL2" s="40"/>
-      <c r="DM2" s="40"/>
-      <c r="DN2" s="40"/>
-      <c r="DO2" s="40"/>
-      <c r="DP2" s="40"/>
-      <c r="DQ2" s="40"/>
-      <c r="DR2" s="40"/>
-      <c r="DS2" s="40"/>
-      <c r="DT2" s="40"/>
-      <c r="DU2" s="40"/>
-      <c r="DV2" s="40"/>
-      <c r="DW2" s="40"/>
-      <c r="DX2" s="40"/>
-      <c r="DY2" s="40"/>
-      <c r="DZ2" s="40"/>
-      <c r="EA2" s="40"/>
-      <c r="EB2" s="40"/>
-      <c r="EC2" s="40"/>
-      <c r="ED2" s="40"/>
-      <c r="EE2" s="40"/>
-      <c r="EF2" s="40"/>
-      <c r="EG2" s="40"/>
-      <c r="EH2" s="40"/>
-      <c r="EI2" s="40"/>
-      <c r="EJ2" s="40"/>
-      <c r="EK2" s="40"/>
-      <c r="EL2" s="40"/>
-      <c r="EM2" s="40"/>
-      <c r="EN2" s="40"/>
-      <c r="EO2" s="40"/>
+      <c r="CC2" s="39"/>
+      <c r="CD2" s="39"/>
+      <c r="CE2" s="39"/>
+      <c r="CF2" s="39"/>
+      <c r="CG2" s="39"/>
+      <c r="CH2" s="39"/>
+      <c r="CI2" s="39"/>
+      <c r="CJ2" s="39"/>
+      <c r="CK2" s="39"/>
+      <c r="CL2" s="39"/>
+      <c r="CM2" s="39"/>
+      <c r="CN2" s="39"/>
+      <c r="CO2" s="39"/>
+      <c r="CP2" s="39"/>
+      <c r="CQ2" s="39"/>
+      <c r="CR2" s="39"/>
+      <c r="CS2" s="39"/>
+      <c r="CT2" s="39"/>
+      <c r="CU2" s="39"/>
+      <c r="CV2" s="39"/>
+      <c r="CW2" s="39"/>
+      <c r="CX2" s="39"/>
+      <c r="CY2" s="39"/>
+      <c r="CZ2" s="39"/>
+      <c r="DA2" s="39"/>
+      <c r="DB2" s="39"/>
+      <c r="DC2" s="39"/>
+      <c r="DD2" s="39"/>
+      <c r="DE2" s="39"/>
+      <c r="DF2" s="39"/>
+      <c r="DG2" s="39"/>
+      <c r="DH2" s="39"/>
+      <c r="DI2" s="39"/>
+      <c r="DJ2" s="39"/>
+      <c r="DK2" s="39"/>
+      <c r="DL2" s="39"/>
+      <c r="DM2" s="39"/>
+      <c r="DN2" s="39"/>
+      <c r="DO2" s="39"/>
+      <c r="DP2" s="39"/>
+      <c r="DQ2" s="39"/>
+      <c r="DR2" s="39"/>
+      <c r="DS2" s="39"/>
+      <c r="DT2" s="39"/>
+      <c r="DU2" s="39"/>
+      <c r="DV2" s="39"/>
+      <c r="DW2" s="39"/>
+      <c r="DX2" s="39"/>
+      <c r="DY2" s="39"/>
+      <c r="DZ2" s="39"/>
+      <c r="EA2" s="39"/>
+      <c r="EB2" s="39"/>
+      <c r="EC2" s="39"/>
+      <c r="ED2" s="39"/>
+      <c r="EE2" s="39"/>
+      <c r="EF2" s="39"/>
+      <c r="EG2" s="39"/>
+      <c r="EH2" s="39"/>
+      <c r="EI2" s="39"/>
+      <c r="EJ2" s="39"/>
+      <c r="EK2" s="39"/>
+      <c r="EL2" s="39"/>
+      <c r="EM2" s="39"/>
+      <c r="EN2" s="39"/>
+      <c r="EO2" s="39"/>
     </row>
-    <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+    <row r="3" spans="1:150" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="40"/>
-      <c r="AP3" s="40"/>
-      <c r="AQ3" s="40"/>
-      <c r="AR3" s="40"/>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="40"/>
-      <c r="AU3" s="40"/>
-      <c r="AV3" s="40"/>
-      <c r="AW3" s="40"/>
-      <c r="AX3" s="40"/>
-      <c r="AY3" s="40"/>
-      <c r="AZ3" s="40"/>
-      <c r="BA3" s="40"/>
-      <c r="BB3" s="40"/>
-      <c r="BC3" s="40"/>
-      <c r="BD3" s="40"/>
-      <c r="BE3" s="40"/>
-      <c r="BF3" s="40"/>
-      <c r="BG3" s="40"/>
-      <c r="BH3" s="40"/>
-      <c r="BI3" s="40"/>
-      <c r="BJ3" s="40"/>
-      <c r="BK3" s="40"/>
-      <c r="BL3" s="40"/>
-      <c r="BM3" s="40"/>
-      <c r="BN3" s="40"/>
-      <c r="BO3" s="40"/>
-      <c r="BP3" s="40"/>
-      <c r="BQ3" s="40"/>
-      <c r="BR3" s="40"/>
-      <c r="BS3" s="40"/>
-      <c r="BT3" s="40"/>
-      <c r="BU3" s="40"/>
-      <c r="BV3" s="40"/>
-      <c r="BW3" s="40"/>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="40"/>
-      <c r="BZ3" s="40"/>
-      <c r="CA3" s="40"/>
-      <c r="CB3" s="40"/>
-      <c r="CC3" s="40"/>
-      <c r="CD3" s="40"/>
-      <c r="CE3" s="40"/>
-      <c r="CF3" s="40"/>
-      <c r="CG3" s="40"/>
-      <c r="CH3" s="40"/>
-      <c r="CI3" s="40"/>
-      <c r="CJ3" s="40"/>
-      <c r="CK3" s="40"/>
-      <c r="CL3" s="40"/>
-      <c r="CM3" s="40"/>
-      <c r="CN3" s="40"/>
-      <c r="CO3" s="40"/>
-      <c r="CP3" s="40"/>
-      <c r="CQ3" s="40"/>
-      <c r="CR3" s="40"/>
-      <c r="CS3" s="40"/>
-      <c r="CT3" s="40"/>
-      <c r="CU3" s="40"/>
-      <c r="CV3" s="40"/>
-      <c r="CW3" s="40"/>
-      <c r="CX3" s="40"/>
-      <c r="CY3" s="40"/>
-      <c r="CZ3" s="40"/>
-      <c r="DA3" s="40"/>
-      <c r="DB3" s="40"/>
-      <c r="DC3" s="40"/>
-      <c r="DD3" s="40"/>
-      <c r="DE3" s="40"/>
-      <c r="DF3" s="40"/>
-      <c r="DG3" s="40"/>
-      <c r="DH3" s="40"/>
-      <c r="DI3" s="40"/>
-      <c r="DJ3" s="40"/>
-      <c r="DK3" s="40"/>
-      <c r="DL3" s="40"/>
-      <c r="DM3" s="40"/>
-      <c r="DN3" s="40"/>
-      <c r="DO3" s="40"/>
-      <c r="DP3" s="40"/>
-      <c r="DQ3" s="40"/>
-      <c r="DR3" s="40"/>
-      <c r="DS3" s="40"/>
-      <c r="DT3" s="40"/>
-      <c r="DU3" s="40"/>
-      <c r="DV3" s="40"/>
-      <c r="DW3" s="40"/>
-      <c r="DX3" s="40"/>
-      <c r="DY3" s="40"/>
-      <c r="DZ3" s="40"/>
-      <c r="EA3" s="40"/>
-      <c r="EB3" s="40"/>
-      <c r="EC3" s="40"/>
-      <c r="ED3" s="40"/>
-      <c r="EE3" s="40"/>
-      <c r="EF3" s="40"/>
-      <c r="EG3" s="40"/>
-      <c r="EH3" s="40"/>
-      <c r="EI3" s="40"/>
-      <c r="EJ3" s="40"/>
-      <c r="EK3" s="40"/>
-      <c r="EL3" s="40"/>
-      <c r="EM3" s="40"/>
-      <c r="EN3" s="40"/>
-      <c r="EO3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="39"/>
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="39"/>
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="39"/>
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="39"/>
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="39"/>
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="39"/>
+      <c r="BX3" s="47"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="39"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="39"/>
+      <c r="CF3" s="39"/>
+      <c r="CG3" s="39"/>
+      <c r="CH3" s="39"/>
+      <c r="CI3" s="39"/>
+      <c r="CJ3" s="39"/>
+      <c r="CK3" s="39"/>
+      <c r="CL3" s="39"/>
+      <c r="CM3" s="39"/>
+      <c r="CN3" s="39"/>
+      <c r="CO3" s="39"/>
+      <c r="CP3" s="39"/>
+      <c r="CQ3" s="39"/>
+      <c r="CR3" s="39"/>
+      <c r="CS3" s="39"/>
+      <c r="CT3" s="39"/>
+      <c r="CU3" s="39"/>
+      <c r="CV3" s="39"/>
+      <c r="CW3" s="39"/>
+      <c r="CX3" s="39"/>
+      <c r="CY3" s="39"/>
+      <c r="CZ3" s="39"/>
+      <c r="DA3" s="39"/>
+      <c r="DB3" s="39"/>
+      <c r="DC3" s="39"/>
+      <c r="DD3" s="39"/>
+      <c r="DE3" s="39"/>
+      <c r="DF3" s="39"/>
+      <c r="DG3" s="39"/>
+      <c r="DH3" s="39"/>
+      <c r="DI3" s="39"/>
+      <c r="DJ3" s="39"/>
+      <c r="DK3" s="39"/>
+      <c r="DL3" s="39"/>
+      <c r="DM3" s="39"/>
+      <c r="DN3" s="39"/>
+      <c r="DO3" s="39"/>
+      <c r="DP3" s="39"/>
+      <c r="DQ3" s="39"/>
+      <c r="DR3" s="39"/>
+      <c r="DS3" s="39"/>
+      <c r="DT3" s="39"/>
+      <c r="DU3" s="39"/>
+      <c r="DV3" s="39"/>
+      <c r="DW3" s="39"/>
+      <c r="DX3" s="39"/>
+      <c r="DY3" s="39"/>
+      <c r="DZ3" s="39"/>
+      <c r="EA3" s="39"/>
+      <c r="EB3" s="39"/>
+      <c r="EC3" s="39"/>
+      <c r="ED3" s="39"/>
+      <c r="EE3" s="39"/>
+      <c r="EF3" s="39"/>
+      <c r="EG3" s="39"/>
+      <c r="EH3" s="39"/>
+      <c r="EI3" s="39"/>
+      <c r="EJ3" s="39"/>
+      <c r="EK3" s="39"/>
+      <c r="EL3" s="39"/>
+      <c r="EM3" s="39"/>
+      <c r="EN3" s="39"/>
+      <c r="EO3" s="39"/>
     </row>
-    <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+    <row r="4" spans="1:150" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="40"/>
-      <c r="AE4" s="40"/>
-      <c r="AF4" s="40"/>
-      <c r="AG4" s="40"/>
-      <c r="AH4" s="40"/>
-      <c r="AI4" s="40"/>
-      <c r="AJ4" s="40"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="40"/>
-      <c r="AM4" s="40"/>
-      <c r="AN4" s="40"/>
-      <c r="AO4" s="40"/>
-      <c r="AP4" s="40"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="40"/>
-      <c r="AS4" s="40"/>
-      <c r="AT4" s="40"/>
-      <c r="AU4" s="40"/>
-      <c r="AV4" s="40"/>
-      <c r="AW4" s="40"/>
-      <c r="AX4" s="40"/>
-      <c r="AY4" s="40"/>
-      <c r="AZ4" s="40"/>
-      <c r="BA4" s="40"/>
-      <c r="BB4" s="40"/>
-      <c r="BC4" s="40"/>
-      <c r="BD4" s="40"/>
-      <c r="BE4" s="40"/>
-      <c r="BF4" s="40"/>
-      <c r="BG4" s="40"/>
-      <c r="BH4" s="40"/>
-      <c r="BI4" s="40"/>
-      <c r="BJ4" s="40"/>
-      <c r="BK4" s="40"/>
-      <c r="BL4" s="40"/>
-      <c r="BM4" s="40"/>
-      <c r="BN4" s="40"/>
-      <c r="BO4" s="40"/>
-      <c r="BP4" s="40"/>
-      <c r="BQ4" s="40"/>
-      <c r="BR4" s="40"/>
-      <c r="BS4" s="40"/>
-      <c r="BT4" s="40"/>
-      <c r="BU4" s="40"/>
-      <c r="BV4" s="40"/>
-      <c r="BW4" s="40"/>
-      <c r="BX4" s="49"/>
-      <c r="BY4" s="40"/>
-      <c r="BZ4" s="40"/>
-      <c r="CA4" s="40"/>
-      <c r="CB4" s="40"/>
-      <c r="CC4" s="40"/>
-      <c r="CD4" s="40"/>
-      <c r="CE4" s="40"/>
-      <c r="CF4" s="40"/>
-      <c r="CG4" s="40"/>
-      <c r="CH4" s="40"/>
-      <c r="CI4" s="40"/>
-      <c r="CJ4" s="40"/>
-      <c r="CK4" s="40"/>
-      <c r="CL4" s="40"/>
-      <c r="CM4" s="40"/>
-      <c r="CN4" s="40"/>
-      <c r="CO4" s="40"/>
-      <c r="CP4" s="40"/>
-      <c r="CQ4" s="40"/>
-      <c r="CR4" s="40"/>
-      <c r="CS4" s="40"/>
-      <c r="CT4" s="40"/>
-      <c r="CU4" s="40"/>
-      <c r="CV4" s="40"/>
-      <c r="CW4" s="40"/>
-      <c r="CX4" s="40"/>
-      <c r="CY4" s="40"/>
-      <c r="CZ4" s="40"/>
-      <c r="DA4" s="40"/>
-      <c r="DB4" s="40"/>
-      <c r="DC4" s="40"/>
-      <c r="DD4" s="40"/>
-      <c r="DE4" s="40"/>
-      <c r="DF4" s="40"/>
-      <c r="DG4" s="40"/>
-      <c r="DH4" s="40"/>
-      <c r="DI4" s="40"/>
-      <c r="DJ4" s="40"/>
-      <c r="DK4" s="40"/>
-      <c r="DL4" s="40"/>
-      <c r="DM4" s="40"/>
-      <c r="DN4" s="40"/>
-      <c r="DO4" s="40"/>
-      <c r="DP4" s="40"/>
-      <c r="DQ4" s="40"/>
-      <c r="DR4" s="40"/>
-      <c r="DS4" s="40"/>
-      <c r="DT4" s="40"/>
-      <c r="DU4" s="40"/>
-      <c r="DV4" s="40"/>
-      <c r="DW4" s="40"/>
-      <c r="DX4" s="40"/>
-      <c r="DY4" s="40"/>
-      <c r="DZ4" s="40"/>
-      <c r="EA4" s="40"/>
-      <c r="EB4" s="40"/>
-      <c r="EC4" s="40"/>
-      <c r="ED4" s="40"/>
-      <c r="EE4" s="40"/>
-      <c r="EF4" s="40"/>
-      <c r="EG4" s="40"/>
-      <c r="EH4" s="40"/>
-      <c r="EI4" s="40"/>
-      <c r="EJ4" s="40"/>
-      <c r="EK4" s="40"/>
-      <c r="EL4" s="40"/>
-      <c r="EM4" s="40"/>
-      <c r="EN4" s="40"/>
-      <c r="EO4" s="40"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="39"/>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="39"/>
+      <c r="AM4" s="39"/>
+      <c r="AN4" s="39"/>
+      <c r="AO4" s="39"/>
+      <c r="AP4" s="39"/>
+      <c r="AQ4" s="39"/>
+      <c r="AR4" s="39"/>
+      <c r="AS4" s="39"/>
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
+      <c r="AX4" s="39"/>
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
+      <c r="BA4" s="39"/>
+      <c r="BB4" s="39"/>
+      <c r="BC4" s="39"/>
+      <c r="BD4" s="39"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="39"/>
+      <c r="BG4" s="39"/>
+      <c r="BH4" s="39"/>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="39"/>
+      <c r="BL4" s="39"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="39"/>
+      <c r="BQ4" s="39"/>
+      <c r="BR4" s="39"/>
+      <c r="BS4" s="39"/>
+      <c r="BT4" s="39"/>
+      <c r="BU4" s="39"/>
+      <c r="BV4" s="39"/>
+      <c r="BW4" s="39"/>
+      <c r="BX4" s="47"/>
+      <c r="BY4" s="39"/>
+      <c r="BZ4" s="39"/>
+      <c r="CA4" s="39"/>
+      <c r="CB4" s="39"/>
+      <c r="CC4" s="39"/>
+      <c r="CD4" s="39"/>
+      <c r="CE4" s="39"/>
+      <c r="CF4" s="39"/>
+      <c r="CG4" s="39"/>
+      <c r="CH4" s="39"/>
+      <c r="CI4" s="39"/>
+      <c r="CJ4" s="39"/>
+      <c r="CK4" s="39"/>
+      <c r="CL4" s="39"/>
+      <c r="CM4" s="39"/>
+      <c r="CN4" s="39"/>
+      <c r="CO4" s="39"/>
+      <c r="CP4" s="39"/>
+      <c r="CQ4" s="39"/>
+      <c r="CR4" s="39"/>
+      <c r="CS4" s="39"/>
+      <c r="CT4" s="39"/>
+      <c r="CU4" s="39"/>
+      <c r="CV4" s="39"/>
+      <c r="CW4" s="39"/>
+      <c r="CX4" s="39"/>
+      <c r="CY4" s="39"/>
+      <c r="CZ4" s="39"/>
+      <c r="DA4" s="39"/>
+      <c r="DB4" s="39"/>
+      <c r="DC4" s="39"/>
+      <c r="DD4" s="39"/>
+      <c r="DE4" s="39"/>
+      <c r="DF4" s="39"/>
+      <c r="DG4" s="39"/>
+      <c r="DH4" s="39"/>
+      <c r="DI4" s="39"/>
+      <c r="DJ4" s="39"/>
+      <c r="DK4" s="39"/>
+      <c r="DL4" s="39"/>
+      <c r="DM4" s="39"/>
+      <c r="DN4" s="39"/>
+      <c r="DO4" s="39"/>
+      <c r="DP4" s="39"/>
+      <c r="DQ4" s="39"/>
+      <c r="DR4" s="39"/>
+      <c r="DS4" s="39"/>
+      <c r="DT4" s="39"/>
+      <c r="DU4" s="39"/>
+      <c r="DV4" s="39"/>
+      <c r="DW4" s="39"/>
+      <c r="DX4" s="39"/>
+      <c r="DY4" s="39"/>
+      <c r="DZ4" s="39"/>
+      <c r="EA4" s="39"/>
+      <c r="EB4" s="39"/>
+      <c r="EC4" s="39"/>
+      <c r="ED4" s="39"/>
+      <c r="EE4" s="39"/>
+      <c r="EF4" s="39"/>
+      <c r="EG4" s="39"/>
+      <c r="EH4" s="39"/>
+      <c r="EI4" s="39"/>
+      <c r="EJ4" s="39"/>
+      <c r="EK4" s="39"/>
+      <c r="EL4" s="39"/>
+      <c r="EM4" s="39"/>
+      <c r="EN4" s="39"/>
+      <c r="EO4" s="39"/>
     </row>
-    <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+    <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55">
+      <c r="B5" s="43"/>
+      <c r="C5" s="44">
         <v>110</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="40"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="40"/>
-      <c r="AK5" s="40"/>
-      <c r="AL5" s="40"/>
-      <c r="AM5" s="40"/>
-      <c r="AN5" s="40"/>
-      <c r="AO5" s="40"/>
-      <c r="AP5" s="40"/>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="40"/>
-      <c r="AS5" s="40"/>
-      <c r="AT5" s="40"/>
-      <c r="AU5" s="40"/>
-      <c r="AV5" s="40"/>
-      <c r="AW5" s="40"/>
-      <c r="AX5" s="40"/>
-      <c r="AY5" s="40"/>
-      <c r="AZ5" s="40"/>
-      <c r="BA5" s="40"/>
-      <c r="BB5" s="40"/>
-      <c r="BC5" s="40"/>
-      <c r="BD5" s="40"/>
-      <c r="BE5" s="40"/>
-      <c r="BF5" s="40"/>
-      <c r="BG5" s="40"/>
-      <c r="BH5" s="40"/>
-      <c r="BI5" s="40"/>
-      <c r="BJ5" s="40"/>
-      <c r="BK5" s="40"/>
-      <c r="BL5" s="40"/>
-      <c r="BM5" s="40"/>
-      <c r="BN5" s="40"/>
-      <c r="BO5" s="40"/>
-      <c r="BP5" s="40"/>
-      <c r="BQ5" s="40"/>
-      <c r="BR5" s="40"/>
-      <c r="BS5" s="40"/>
-      <c r="BT5" s="40"/>
-      <c r="BU5" s="40"/>
-      <c r="BV5" s="40"/>
-      <c r="BW5" s="40"/>
-      <c r="BX5" s="49"/>
-      <c r="BY5" s="40"/>
-      <c r="BZ5" s="40"/>
-      <c r="CA5" s="40"/>
-      <c r="CB5" s="40"/>
-      <c r="CC5" s="40"/>
-      <c r="CD5" s="40"/>
-      <c r="CE5" s="40"/>
-      <c r="CF5" s="40"/>
-      <c r="CG5" s="40"/>
-      <c r="CH5" s="40"/>
-      <c r="CI5" s="40"/>
-      <c r="CJ5" s="40"/>
-      <c r="CK5" s="40"/>
-      <c r="CL5" s="40"/>
-      <c r="CM5" s="40"/>
-      <c r="CN5" s="40"/>
-      <c r="CO5" s="40"/>
-      <c r="CP5" s="40"/>
-      <c r="CQ5" s="40"/>
-      <c r="CR5" s="40"/>
-      <c r="CS5" s="40"/>
-      <c r="CT5" s="40"/>
-      <c r="CU5" s="40"/>
-      <c r="CV5" s="40"/>
-      <c r="CW5" s="40"/>
-      <c r="CX5" s="40"/>
-      <c r="CY5" s="40"/>
-      <c r="CZ5" s="40"/>
-      <c r="DA5" s="40"/>
-      <c r="DB5" s="40"/>
-      <c r="DC5" s="40"/>
-      <c r="DD5" s="40"/>
-      <c r="DE5" s="40"/>
-      <c r="DF5" s="40"/>
-      <c r="DG5" s="40"/>
-      <c r="DH5" s="40"/>
-      <c r="DI5" s="40"/>
-      <c r="DJ5" s="40"/>
-      <c r="DK5" s="40"/>
-      <c r="DL5" s="40"/>
-      <c r="DM5" s="40"/>
-      <c r="DN5" s="40"/>
-      <c r="DO5" s="40"/>
-      <c r="DP5" s="40"/>
-      <c r="DQ5" s="40"/>
-      <c r="DR5" s="40"/>
-      <c r="DS5" s="40"/>
-      <c r="DT5" s="40"/>
-      <c r="DU5" s="40"/>
-      <c r="DV5" s="40"/>
-      <c r="DW5" s="40"/>
-      <c r="DX5" s="40"/>
-      <c r="DY5" s="40"/>
-      <c r="DZ5" s="40"/>
-      <c r="EA5" s="40"/>
-      <c r="EB5" s="40"/>
-      <c r="EC5" s="40"/>
-      <c r="ED5" s="40"/>
-      <c r="EE5" s="40"/>
-      <c r="EF5" s="40"/>
-      <c r="EG5" s="40"/>
-      <c r="EH5" s="40"/>
-      <c r="EI5" s="40"/>
-      <c r="EJ5" s="40"/>
-      <c r="EK5" s="40"/>
-      <c r="EL5" s="40"/>
-      <c r="EM5" s="40"/>
-      <c r="EN5" s="40"/>
-      <c r="EO5" s="40"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="39"/>
+      <c r="AN5" s="39"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="39"/>
+      <c r="AQ5" s="39"/>
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="39"/>
+      <c r="AT5" s="39"/>
+      <c r="AU5" s="39"/>
+      <c r="AV5" s="39"/>
+      <c r="AW5" s="39"/>
+      <c r="AX5" s="39"/>
+      <c r="AY5" s="39"/>
+      <c r="AZ5" s="39"/>
+      <c r="BA5" s="39"/>
+      <c r="BB5" s="39"/>
+      <c r="BC5" s="39"/>
+      <c r="BD5" s="39"/>
+      <c r="BE5" s="39"/>
+      <c r="BF5" s="39"/>
+      <c r="BG5" s="39"/>
+      <c r="BH5" s="39"/>
+      <c r="BI5" s="39"/>
+      <c r="BJ5" s="39"/>
+      <c r="BK5" s="39"/>
+      <c r="BL5" s="39"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
+      <c r="BO5" s="39"/>
+      <c r="BP5" s="39"/>
+      <c r="BQ5" s="39"/>
+      <c r="BR5" s="39"/>
+      <c r="BS5" s="39"/>
+      <c r="BT5" s="39"/>
+      <c r="BU5" s="39"/>
+      <c r="BV5" s="39"/>
+      <c r="BW5" s="39"/>
+      <c r="BX5" s="47"/>
+      <c r="BY5" s="39"/>
+      <c r="BZ5" s="39"/>
+      <c r="CA5" s="39"/>
+      <c r="CB5" s="39"/>
+      <c r="CC5" s="39"/>
+      <c r="CD5" s="39"/>
+      <c r="CE5" s="39"/>
+      <c r="CF5" s="39"/>
+      <c r="CG5" s="39"/>
+      <c r="CH5" s="39"/>
+      <c r="CI5" s="39"/>
+      <c r="CJ5" s="39"/>
+      <c r="CK5" s="39"/>
+      <c r="CL5" s="39"/>
+      <c r="CM5" s="39"/>
+      <c r="CN5" s="39"/>
+      <c r="CO5" s="39"/>
+      <c r="CP5" s="39"/>
+      <c r="CQ5" s="39"/>
+      <c r="CR5" s="39"/>
+      <c r="CS5" s="39"/>
+      <c r="CT5" s="39"/>
+      <c r="CU5" s="39"/>
+      <c r="CV5" s="39"/>
+      <c r="CW5" s="39"/>
+      <c r="CX5" s="39"/>
+      <c r="CY5" s="39"/>
+      <c r="CZ5" s="39"/>
+      <c r="DA5" s="39"/>
+      <c r="DB5" s="39"/>
+      <c r="DC5" s="39"/>
+      <c r="DD5" s="39"/>
+      <c r="DE5" s="39"/>
+      <c r="DF5" s="39"/>
+      <c r="DG5" s="39"/>
+      <c r="DH5" s="39"/>
+      <c r="DI5" s="39"/>
+      <c r="DJ5" s="39"/>
+      <c r="DK5" s="39"/>
+      <c r="DL5" s="39"/>
+      <c r="DM5" s="39"/>
+      <c r="DN5" s="39"/>
+      <c r="DO5" s="39"/>
+      <c r="DP5" s="39"/>
+      <c r="DQ5" s="39"/>
+      <c r="DR5" s="39"/>
+      <c r="DS5" s="39"/>
+      <c r="DT5" s="39"/>
+      <c r="DU5" s="39"/>
+      <c r="DV5" s="39"/>
+      <c r="DW5" s="39"/>
+      <c r="DX5" s="39"/>
+      <c r="DY5" s="39"/>
+      <c r="DZ5" s="39"/>
+      <c r="EA5" s="39"/>
+      <c r="EB5" s="39"/>
+      <c r="EC5" s="39"/>
+      <c r="ED5" s="39"/>
+      <c r="EE5" s="39"/>
+      <c r="EF5" s="39"/>
+      <c r="EG5" s="39"/>
+      <c r="EH5" s="39"/>
+      <c r="EI5" s="39"/>
+      <c r="EJ5" s="39"/>
+      <c r="EK5" s="39"/>
+      <c r="EL5" s="39"/>
+      <c r="EM5" s="39"/>
+      <c r="EN5" s="39"/>
+      <c r="EO5" s="39"/>
     </row>
-    <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
+    <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55">
+      <c r="B6" s="43"/>
+      <c r="C6" s="44">
         <v>10</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="47"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="40"/>
-      <c r="AM6" s="40"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="40"/>
-      <c r="AP6" s="40"/>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="40"/>
-      <c r="AS6" s="40"/>
-      <c r="AT6" s="40"/>
-      <c r="AU6" s="40"/>
-      <c r="AV6" s="40"/>
-      <c r="AW6" s="40"/>
-      <c r="AX6" s="40"/>
-      <c r="AY6" s="40"/>
-      <c r="AZ6" s="40"/>
-      <c r="BA6" s="40"/>
-      <c r="BB6" s="40"/>
-      <c r="BC6" s="40"/>
-      <c r="BD6" s="40"/>
-      <c r="BE6" s="40"/>
-      <c r="BF6" s="40"/>
-      <c r="BG6" s="40"/>
-      <c r="BH6" s="40"/>
-      <c r="BI6" s="40"/>
-      <c r="BJ6" s="40"/>
-      <c r="BK6" s="40"/>
-      <c r="BL6" s="40"/>
-      <c r="BM6" s="40"/>
-      <c r="BN6" s="40"/>
-      <c r="BO6" s="40"/>
-      <c r="BP6" s="40"/>
-      <c r="BQ6" s="40"/>
-      <c r="BR6" s="40"/>
-      <c r="BS6" s="40"/>
-      <c r="BT6" s="40"/>
-      <c r="BU6" s="40"/>
-      <c r="BV6" s="40"/>
-      <c r="BW6" s="40"/>
-      <c r="BX6" s="49"/>
-      <c r="BY6" s="40"/>
-      <c r="BZ6" s="40"/>
-      <c r="CA6" s="40"/>
-      <c r="CB6" s="40"/>
-      <c r="CC6" s="40"/>
-      <c r="CD6" s="40"/>
-      <c r="CE6" s="40"/>
-      <c r="CF6" s="40"/>
-      <c r="CG6" s="40"/>
-      <c r="CH6" s="40"/>
-      <c r="CI6" s="40"/>
-      <c r="CJ6" s="40"/>
-      <c r="CK6" s="40"/>
-      <c r="CL6" s="40"/>
-      <c r="CM6" s="40"/>
-      <c r="CN6" s="40"/>
-      <c r="CO6" s="40"/>
-      <c r="CP6" s="40"/>
-      <c r="CQ6" s="40"/>
-      <c r="CR6" s="40"/>
-      <c r="CS6" s="40"/>
-      <c r="CT6" s="40"/>
-      <c r="CU6" s="40"/>
-      <c r="CV6" s="40"/>
-      <c r="CW6" s="40"/>
-      <c r="CX6" s="40"/>
-      <c r="CY6" s="40"/>
-      <c r="CZ6" s="40"/>
-      <c r="DA6" s="40"/>
-      <c r="DB6" s="40"/>
-      <c r="DC6" s="40"/>
-      <c r="DD6" s="40"/>
-      <c r="DE6" s="40"/>
-      <c r="DF6" s="40"/>
-      <c r="DG6" s="40"/>
-      <c r="DH6" s="40"/>
-      <c r="DI6" s="40"/>
-      <c r="DJ6" s="40"/>
-      <c r="DK6" s="40"/>
-      <c r="DL6" s="40"/>
-      <c r="DM6" s="40"/>
-      <c r="DN6" s="40"/>
-      <c r="DO6" s="40"/>
-      <c r="DP6" s="40"/>
-      <c r="DQ6" s="40"/>
-      <c r="DR6" s="40"/>
-      <c r="DS6" s="40"/>
-      <c r="DT6" s="40"/>
-      <c r="DU6" s="40"/>
-      <c r="DV6" s="40"/>
-      <c r="DW6" s="40"/>
-      <c r="DX6" s="40"/>
-      <c r="DY6" s="40"/>
-      <c r="DZ6" s="40"/>
-      <c r="EA6" s="40"/>
-      <c r="EB6" s="40"/>
-      <c r="EC6" s="40"/>
-      <c r="ED6" s="40"/>
-      <c r="EE6" s="40"/>
-      <c r="EF6" s="40"/>
-      <c r="EG6" s="40"/>
-      <c r="EH6" s="40"/>
-      <c r="EI6" s="40"/>
-      <c r="EJ6" s="40"/>
-      <c r="EK6" s="40"/>
-      <c r="EL6" s="40"/>
-      <c r="EM6" s="40"/>
-      <c r="EN6" s="40"/>
-      <c r="EO6" s="40"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="51"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="51"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="51"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="39"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="39"/>
+      <c r="AQ6" s="39"/>
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="39"/>
+      <c r="AU6" s="39"/>
+      <c r="AV6" s="39"/>
+      <c r="AW6" s="39"/>
+      <c r="AX6" s="39"/>
+      <c r="AY6" s="39"/>
+      <c r="AZ6" s="39"/>
+      <c r="BA6" s="39"/>
+      <c r="BB6" s="39"/>
+      <c r="BC6" s="39"/>
+      <c r="BD6" s="39"/>
+      <c r="BE6" s="39"/>
+      <c r="BF6" s="39"/>
+      <c r="BG6" s="39"/>
+      <c r="BH6" s="39"/>
+      <c r="BI6" s="39"/>
+      <c r="BJ6" s="39"/>
+      <c r="BK6" s="39"/>
+      <c r="BL6" s="39"/>
+      <c r="BM6" s="39"/>
+      <c r="BN6" s="39"/>
+      <c r="BO6" s="39"/>
+      <c r="BP6" s="39"/>
+      <c r="BQ6" s="39"/>
+      <c r="BR6" s="39"/>
+      <c r="BS6" s="39"/>
+      <c r="BT6" s="39"/>
+      <c r="BU6" s="39"/>
+      <c r="BV6" s="39"/>
+      <c r="BW6" s="39"/>
+      <c r="BX6" s="47"/>
+      <c r="BY6" s="39"/>
+      <c r="BZ6" s="39"/>
+      <c r="CA6" s="39"/>
+      <c r="CB6" s="39"/>
+      <c r="CC6" s="39"/>
+      <c r="CD6" s="39"/>
+      <c r="CE6" s="39"/>
+      <c r="CF6" s="39"/>
+      <c r="CG6" s="39"/>
+      <c r="CH6" s="39"/>
+      <c r="CI6" s="39"/>
+      <c r="CJ6" s="39"/>
+      <c r="CK6" s="39"/>
+      <c r="CL6" s="39"/>
+      <c r="CM6" s="39"/>
+      <c r="CN6" s="39"/>
+      <c r="CO6" s="39"/>
+      <c r="CP6" s="39"/>
+      <c r="CQ6" s="39"/>
+      <c r="CR6" s="39"/>
+      <c r="CS6" s="39"/>
+      <c r="CT6" s="39"/>
+      <c r="CU6" s="39"/>
+      <c r="CV6" s="39"/>
+      <c r="CW6" s="39"/>
+      <c r="CX6" s="39"/>
+      <c r="CY6" s="39"/>
+      <c r="CZ6" s="39"/>
+      <c r="DA6" s="39"/>
+      <c r="DB6" s="39"/>
+      <c r="DC6" s="39"/>
+      <c r="DD6" s="39"/>
+      <c r="DE6" s="39"/>
+      <c r="DF6" s="39"/>
+      <c r="DG6" s="39"/>
+      <c r="DH6" s="39"/>
+      <c r="DI6" s="39"/>
+      <c r="DJ6" s="39"/>
+      <c r="DK6" s="39"/>
+      <c r="DL6" s="39"/>
+      <c r="DM6" s="39"/>
+      <c r="DN6" s="39"/>
+      <c r="DO6" s="39"/>
+      <c r="DP6" s="39"/>
+      <c r="DQ6" s="39"/>
+      <c r="DR6" s="39"/>
+      <c r="DS6" s="39"/>
+      <c r="DT6" s="39"/>
+      <c r="DU6" s="39"/>
+      <c r="DV6" s="39"/>
+      <c r="DW6" s="39"/>
+      <c r="DX6" s="39"/>
+      <c r="DY6" s="39"/>
+      <c r="DZ6" s="39"/>
+      <c r="EA6" s="39"/>
+      <c r="EB6" s="39"/>
+      <c r="EC6" s="39"/>
+      <c r="ED6" s="39"/>
+      <c r="EE6" s="39"/>
+      <c r="EF6" s="39"/>
+      <c r="EG6" s="39"/>
+      <c r="EH6" s="39"/>
+      <c r="EI6" s="39"/>
+      <c r="EJ6" s="39"/>
+      <c r="EK6" s="39"/>
+      <c r="EL6" s="39"/>
+      <c r="EM6" s="39"/>
+      <c r="EN6" s="39"/>
+      <c r="EO6" s="39"/>
     </row>
-    <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="57" t="s">
+    <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="55">
+      <c r="B7" s="46"/>
+      <c r="C7" s="44">
         <v>30</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="48"/>
-      <c r="AB7" s="48"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-      <c r="AK7" s="41"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="41"/>
-      <c r="AN7" s="41"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="41"/>
-      <c r="AQ7" s="41"/>
-      <c r="AR7" s="41"/>
-      <c r="AS7" s="41"/>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="41"/>
-      <c r="AV7" s="41"/>
-      <c r="AW7" s="41"/>
-      <c r="AX7" s="41"/>
-      <c r="AY7" s="41"/>
-      <c r="AZ7" s="41"/>
-      <c r="BA7" s="41"/>
-      <c r="BB7" s="41"/>
-      <c r="BC7" s="41"/>
-      <c r="BD7" s="41"/>
-      <c r="BE7" s="41"/>
-      <c r="BF7" s="41"/>
-      <c r="BG7" s="41"/>
-      <c r="BH7" s="41"/>
-      <c r="BI7" s="41"/>
-      <c r="BJ7" s="41"/>
-      <c r="BK7" s="41"/>
-      <c r="BL7" s="41"/>
-      <c r="BM7" s="41"/>
-      <c r="BN7" s="41"/>
-      <c r="BO7" s="41"/>
-      <c r="BP7" s="41"/>
-      <c r="BQ7" s="41"/>
-      <c r="BR7" s="41"/>
-      <c r="BS7" s="41"/>
-      <c r="BT7" s="41"/>
-      <c r="BU7" s="41"/>
-      <c r="BV7" s="41"/>
-      <c r="BW7" s="41"/>
-      <c r="BX7" s="50"/>
-      <c r="BY7" s="41"/>
-      <c r="BZ7" s="41"/>
-      <c r="CA7" s="41"/>
-      <c r="CB7" s="41"/>
-      <c r="CC7" s="41"/>
-      <c r="CD7" s="41"/>
-      <c r="CE7" s="41"/>
-      <c r="CF7" s="41"/>
-      <c r="CG7" s="41"/>
-      <c r="CH7" s="41"/>
-      <c r="CI7" s="41"/>
-      <c r="CJ7" s="41"/>
-      <c r="CK7" s="41"/>
-      <c r="CL7" s="41"/>
-      <c r="CM7" s="41"/>
-      <c r="CN7" s="41"/>
-      <c r="CO7" s="41"/>
-      <c r="CP7" s="41"/>
-      <c r="CQ7" s="41"/>
-      <c r="CR7" s="41"/>
-      <c r="CS7" s="41"/>
-      <c r="CT7" s="41"/>
-      <c r="CU7" s="41"/>
-      <c r="CV7" s="41"/>
-      <c r="CW7" s="41"/>
-      <c r="CX7" s="41"/>
-      <c r="CY7" s="41"/>
-      <c r="CZ7" s="41"/>
-      <c r="DA7" s="41"/>
-      <c r="DB7" s="41"/>
-      <c r="DC7" s="41"/>
-      <c r="DD7" s="41"/>
-      <c r="DE7" s="41"/>
-      <c r="DF7" s="41"/>
-      <c r="DG7" s="41"/>
-      <c r="DH7" s="41"/>
-      <c r="DI7" s="41"/>
-      <c r="DJ7" s="41"/>
-      <c r="DK7" s="41"/>
-      <c r="DL7" s="41"/>
-      <c r="DM7" s="41"/>
-      <c r="DN7" s="41"/>
-      <c r="DO7" s="41"/>
-      <c r="DP7" s="41"/>
-      <c r="DQ7" s="41"/>
-      <c r="DR7" s="41"/>
-      <c r="DS7" s="41"/>
-      <c r="DT7" s="41"/>
-      <c r="DU7" s="41"/>
-      <c r="DV7" s="41"/>
-      <c r="DW7" s="41"/>
-      <c r="DX7" s="41"/>
-      <c r="DY7" s="41"/>
-      <c r="DZ7" s="41"/>
-      <c r="EA7" s="41"/>
-      <c r="EB7" s="41"/>
-      <c r="EC7" s="41"/>
-      <c r="ED7" s="41"/>
-      <c r="EE7" s="41"/>
-      <c r="EF7" s="41"/>
-      <c r="EG7" s="41"/>
-      <c r="EH7" s="41"/>
-      <c r="EI7" s="41"/>
-      <c r="EJ7" s="41"/>
-      <c r="EK7" s="41"/>
-      <c r="EL7" s="41"/>
-      <c r="EM7" s="41"/>
-      <c r="EN7" s="41"/>
-      <c r="EO7" s="41"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="52"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="52"/>
+      <c r="AA7" s="50"/>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
+      <c r="BA7" s="40"/>
+      <c r="BB7" s="40"/>
+      <c r="BC7" s="40"/>
+      <c r="BD7" s="40"/>
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="40"/>
+      <c r="BJ7" s="40"/>
+      <c r="BK7" s="40"/>
+      <c r="BL7" s="40"/>
+      <c r="BM7" s="40"/>
+      <c r="BN7" s="40"/>
+      <c r="BO7" s="40"/>
+      <c r="BP7" s="40"/>
+      <c r="BQ7" s="40"/>
+      <c r="BR7" s="40"/>
+      <c r="BS7" s="40"/>
+      <c r="BT7" s="40"/>
+      <c r="BU7" s="40"/>
+      <c r="BV7" s="40"/>
+      <c r="BW7" s="40"/>
+      <c r="BX7" s="48"/>
+      <c r="BY7" s="40"/>
+      <c r="BZ7" s="40"/>
+      <c r="CA7" s="40"/>
+      <c r="CB7" s="40"/>
+      <c r="CC7" s="40"/>
+      <c r="CD7" s="40"/>
+      <c r="CE7" s="40"/>
+      <c r="CF7" s="40"/>
+      <c r="CG7" s="40"/>
+      <c r="CH7" s="40"/>
+      <c r="CI7" s="40"/>
+      <c r="CJ7" s="40"/>
+      <c r="CK7" s="40"/>
+      <c r="CL7" s="40"/>
+      <c r="CM7" s="40"/>
+      <c r="CN7" s="40"/>
+      <c r="CO7" s="40"/>
+      <c r="CP7" s="40"/>
+      <c r="CQ7" s="40"/>
+      <c r="CR7" s="40"/>
+      <c r="CS7" s="40"/>
+      <c r="CT7" s="40"/>
+      <c r="CU7" s="40"/>
+      <c r="CV7" s="40"/>
+      <c r="CW7" s="40"/>
+      <c r="CX7" s="40"/>
+      <c r="CY7" s="40"/>
+      <c r="CZ7" s="40"/>
+      <c r="DA7" s="40"/>
+      <c r="DB7" s="40"/>
+      <c r="DC7" s="40"/>
+      <c r="DD7" s="40"/>
+      <c r="DE7" s="40"/>
+      <c r="DF7" s="40"/>
+      <c r="DG7" s="40"/>
+      <c r="DH7" s="40"/>
+      <c r="DI7" s="40"/>
+      <c r="DJ7" s="40"/>
+      <c r="DK7" s="40"/>
+      <c r="DL7" s="40"/>
+      <c r="DM7" s="40"/>
+      <c r="DN7" s="40"/>
+      <c r="DO7" s="40"/>
+      <c r="DP7" s="40"/>
+      <c r="DQ7" s="40"/>
+      <c r="DR7" s="40"/>
+      <c r="DS7" s="40"/>
+      <c r="DT7" s="40"/>
+      <c r="DU7" s="40"/>
+      <c r="DV7" s="40"/>
+      <c r="DW7" s="40"/>
+      <c r="DX7" s="40"/>
+      <c r="DY7" s="40"/>
+      <c r="DZ7" s="40"/>
+      <c r="EA7" s="40"/>
+      <c r="EB7" s="40"/>
+      <c r="EC7" s="40"/>
+      <c r="ED7" s="40"/>
+      <c r="EE7" s="40"/>
+      <c r="EF7" s="40"/>
+      <c r="EG7" s="40"/>
+      <c r="EH7" s="40"/>
+      <c r="EI7" s="40"/>
+      <c r="EJ7" s="40"/>
+      <c r="EK7" s="40"/>
+      <c r="EL7" s="40"/>
+      <c r="EM7" s="40"/>
+      <c r="EN7" s="40"/>
+      <c r="EO7" s="40"/>
     </row>
-    <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58" t="s">
+    <row r="8" spans="1:150" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="59">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34">
         <v>150</v>
       </c>
-      <c r="D8" s="53"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="60">
+      <c r="F8" s="27">
         <v>1</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="60">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="60">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="60">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="60">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="60">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="60">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="60">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="60">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="60">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="60">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="60">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="60">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="60">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="60">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="60">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="60">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="60">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="60">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="60">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="60">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="60">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="60">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="60">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="60">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="60">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="60">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="60">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="60">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="60">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="60">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="60">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="60">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="60">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="60">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="60">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="60">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="60">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="60">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="60">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="60">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="60">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="60">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="60">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="60">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="60">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="60">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="60">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="60">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="60">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="60">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="60">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="60">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="60">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="60">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="60">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="60">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="60">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="60">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="60">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="60">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="60">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="60">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="60">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="60">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="60">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
-      <c r="BX8" s="60">
+      <c r="BX8" s="27">
         <v>71</v>
       </c>
-      <c r="BY8" s="60">
+      <c r="BY8" s="27">
         <v>72</v>
       </c>
-      <c r="BZ8" s="60">
+      <c r="BZ8" s="27">
         <v>73</v>
       </c>
-      <c r="CA8" s="60">
+      <c r="CA8" s="27">
         <v>74</v>
       </c>
-      <c r="CB8" s="60">
+      <c r="CB8" s="27">
         <v>75</v>
       </c>
-      <c r="CC8" s="60">
+      <c r="CC8" s="27">
         <v>76</v>
       </c>
-      <c r="CD8" s="60">
+      <c r="CD8" s="27">
         <v>77</v>
       </c>
-      <c r="CE8" s="60">
+      <c r="CE8" s="27">
         <v>78</v>
       </c>
-      <c r="CF8" s="60">
+      <c r="CF8" s="27">
         <v>79</v>
       </c>
-      <c r="CG8" s="60">
+      <c r="CG8" s="27">
         <v>80</v>
       </c>
-      <c r="CH8" s="60">
+      <c r="CH8" s="27">
         <v>81</v>
       </c>
-      <c r="CI8" s="60">
+      <c r="CI8" s="27">
         <v>82</v>
       </c>
-      <c r="CJ8" s="60">
+      <c r="CJ8" s="27">
         <v>83</v>
       </c>
-      <c r="CK8" s="60">
+      <c r="CK8" s="27">
         <v>84</v>
       </c>
-      <c r="CL8" s="60">
+      <c r="CL8" s="27">
         <v>85</v>
       </c>
-      <c r="CM8" s="60">
+      <c r="CM8" s="27">
         <v>86</v>
       </c>
-      <c r="CN8" s="60">
+      <c r="CN8" s="27">
         <v>87</v>
       </c>
-      <c r="CO8" s="60">
+      <c r="CO8" s="27">
         <v>88</v>
       </c>
-      <c r="CP8" s="60">
+      <c r="CP8" s="27">
         <v>89</v>
       </c>
-      <c r="CQ8" s="60">
+      <c r="CQ8" s="27">
         <v>90</v>
       </c>
-      <c r="CR8" s="60">
+      <c r="CR8" s="27">
         <v>91</v>
       </c>
-      <c r="CS8" s="60">
+      <c r="CS8" s="27">
         <v>92</v>
       </c>
-      <c r="CT8" s="60">
+      <c r="CT8" s="27">
         <v>93</v>
       </c>
-      <c r="CU8" s="60">
+      <c r="CU8" s="27">
         <v>94</v>
       </c>
-      <c r="CV8" s="60">
+      <c r="CV8" s="27">
         <v>95</v>
       </c>
-      <c r="CW8" s="60">
+      <c r="CW8" s="27">
         <v>96</v>
       </c>
-      <c r="CX8" s="60">
+      <c r="CX8" s="27">
         <v>97</v>
       </c>
-      <c r="CY8" s="60">
+      <c r="CY8" s="27">
         <v>98</v>
       </c>
-      <c r="CZ8" s="60">
+      <c r="CZ8" s="27">
         <v>99</v>
       </c>
-      <c r="DA8" s="60">
+      <c r="DA8" s="27">
         <v>100</v>
       </c>
-      <c r="DB8" s="60">
+      <c r="DB8" s="27">
         <v>101</v>
       </c>
-      <c r="DC8" s="60">
+      <c r="DC8" s="27">
         <v>102</v>
       </c>
-      <c r="DD8" s="60">
+      <c r="DD8" s="27">
         <v>103</v>
       </c>
-      <c r="DE8" s="60">
+      <c r="DE8" s="27">
         <v>104</v>
       </c>
-      <c r="DF8" s="60">
+      <c r="DF8" s="27">
         <v>105</v>
       </c>
-      <c r="DG8" s="60">
+      <c r="DG8" s="27">
         <v>106</v>
       </c>
-      <c r="DH8" s="60">
+      <c r="DH8" s="27">
         <v>107</v>
       </c>
-      <c r="DI8" s="60">
+      <c r="DI8" s="27">
         <v>108</v>
       </c>
-      <c r="DJ8" s="60">
+      <c r="DJ8" s="27">
         <v>109</v>
       </c>
-      <c r="DK8" s="60">
+      <c r="DK8" s="27">
         <v>110</v>
       </c>
-      <c r="DL8" s="60">
+      <c r="DL8" s="27">
         <v>111</v>
       </c>
-      <c r="DM8" s="60">
+      <c r="DM8" s="27">
         <v>112</v>
       </c>
-      <c r="DN8" s="60">
+      <c r="DN8" s="27">
         <v>113</v>
       </c>
-      <c r="DO8" s="60">
+      <c r="DO8" s="27">
         <v>114</v>
       </c>
-      <c r="DP8" s="60">
+      <c r="DP8" s="27">
         <v>115</v>
       </c>
-      <c r="DQ8" s="60">
+      <c r="DQ8" s="27">
         <v>116</v>
       </c>
-      <c r="DR8" s="60">
+      <c r="DR8" s="27">
         <v>117</v>
       </c>
-      <c r="DS8" s="60">
+      <c r="DS8" s="27">
         <v>118</v>
       </c>
-      <c r="DT8" s="60">
+      <c r="DT8" s="27">
         <v>119</v>
       </c>
-      <c r="DU8" s="60">
+      <c r="DU8" s="27">
         <v>120</v>
       </c>
-      <c r="DV8" s="60">
+      <c r="DV8" s="27">
         <v>121</v>
       </c>
-      <c r="DW8" s="60">
+      <c r="DW8" s="27">
         <v>122</v>
       </c>
-      <c r="DX8" s="60">
+      <c r="DX8" s="27">
         <v>123</v>
       </c>
-      <c r="DY8" s="60">
+      <c r="DY8" s="27">
         <v>124</v>
       </c>
-      <c r="DZ8" s="60">
+      <c r="DZ8" s="27">
         <v>125</v>
       </c>
-      <c r="EA8" s="60">
+      <c r="EA8" s="27">
         <v>126</v>
       </c>
-      <c r="EB8" s="60">
+      <c r="EB8" s="27">
         <v>127</v>
       </c>
-      <c r="EC8" s="60">
+      <c r="EC8" s="27">
         <v>128</v>
       </c>
-      <c r="ED8" s="60">
+      <c r="ED8" s="27">
         <v>129</v>
       </c>
-      <c r="EE8" s="60">
+      <c r="EE8" s="27">
         <v>130</v>
       </c>
-      <c r="EF8" s="60">
+      <c r="EF8" s="27">
         <v>131</v>
       </c>
-      <c r="EG8" s="60">
+      <c r="EG8" s="27">
         <v>132</v>
       </c>
-      <c r="EH8" s="60">
+      <c r="EH8" s="27">
         <v>133</v>
       </c>
-      <c r="EI8" s="60">
+      <c r="EI8" s="27">
         <v>134</v>
       </c>
-      <c r="EJ8" s="60">
+      <c r="EJ8" s="27">
         <v>135</v>
       </c>
-      <c r="EK8" s="60">
+      <c r="EK8" s="27">
         <v>136</v>
       </c>
-      <c r="EL8" s="60">
+      <c r="EL8" s="27">
         <v>137</v>
       </c>
-      <c r="EM8" s="60">
+      <c r="EM8" s="27">
         <v>138</v>
       </c>
-      <c r="EN8" s="60">
+      <c r="EN8" s="27">
         <v>139</v>
       </c>
-      <c r="EO8" s="60">
+      <c r="EO8" s="27">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="63"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="61"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="61"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="61"/>
-      <c r="S9" s="61"/>
-      <c r="T9" s="61"/>
-      <c r="U9" s="61"/>
-      <c r="V9" s="61"/>
-      <c r="W9" s="61"/>
-      <c r="X9" s="61"/>
-      <c r="Y9" s="61"/>
-      <c r="Z9" s="61"/>
-      <c r="AA9" s="61"/>
-      <c r="AB9" s="61"/>
-      <c r="AC9" s="61"/>
-      <c r="AD9" s="61"/>
-      <c r="AE9" s="61"/>
-      <c r="AF9" s="61"/>
-      <c r="AG9" s="61"/>
-      <c r="AH9" s="61"/>
-      <c r="AI9" s="61"/>
-      <c r="AJ9" s="61"/>
-      <c r="AK9" s="61"/>
-      <c r="AL9" s="61"/>
-      <c r="AM9" s="61"/>
-      <c r="AN9" s="61"/>
-      <c r="AO9" s="61"/>
-      <c r="AP9" s="61"/>
-      <c r="AQ9" s="61"/>
-      <c r="AR9" s="61"/>
-      <c r="AS9" s="61"/>
-      <c r="AT9" s="61"/>
-      <c r="AU9" s="61"/>
-      <c r="AV9" s="61"/>
-      <c r="AW9" s="61"/>
-      <c r="AX9" s="61"/>
-      <c r="AY9" s="61"/>
-      <c r="AZ9" s="61"/>
-      <c r="BA9" s="61"/>
-      <c r="BB9" s="61"/>
-      <c r="BC9" s="61"/>
-      <c r="BD9" s="61"/>
-      <c r="BE9" s="61"/>
-      <c r="BF9" s="61"/>
-      <c r="BG9" s="61"/>
-      <c r="BH9" s="61"/>
-      <c r="BI9" s="61"/>
-      <c r="BJ9" s="61"/>
-      <c r="BK9" s="61"/>
-      <c r="BL9" s="61"/>
-      <c r="BM9" s="61"/>
-      <c r="BN9" s="61"/>
-      <c r="BO9" s="61"/>
-      <c r="BP9" s="61"/>
-      <c r="BQ9" s="61"/>
-      <c r="BR9" s="61"/>
-      <c r="BS9" s="61"/>
-      <c r="BT9" s="61"/>
-      <c r="BU9" s="61"/>
-      <c r="BV9" s="61"/>
-      <c r="BW9" s="61"/>
-      <c r="BX9" s="61"/>
-      <c r="BY9" s="61"/>
-      <c r="BZ9" s="61"/>
-      <c r="CA9" s="61"/>
-      <c r="CB9" s="61"/>
-      <c r="CC9" s="61"/>
-      <c r="CD9" s="61"/>
-      <c r="CE9" s="61"/>
-      <c r="CF9" s="61"/>
-      <c r="CG9" s="61"/>
-      <c r="CH9" s="61"/>
-      <c r="CI9" s="61"/>
-      <c r="CJ9" s="61"/>
-      <c r="CK9" s="61"/>
-      <c r="CL9" s="61"/>
-      <c r="CM9" s="61"/>
-      <c r="CN9" s="61"/>
-      <c r="CO9" s="61"/>
-      <c r="CP9" s="61"/>
-      <c r="CQ9" s="61"/>
-      <c r="CR9" s="61"/>
-      <c r="CS9" s="61"/>
-      <c r="CT9" s="61"/>
-      <c r="CU9" s="61"/>
-      <c r="CV9" s="61"/>
-      <c r="CW9" s="61"/>
-      <c r="CX9" s="61"/>
-      <c r="CY9" s="61"/>
-      <c r="CZ9" s="61"/>
-      <c r="DA9" s="61"/>
-      <c r="DB9" s="61"/>
-      <c r="DC9" s="61"/>
-      <c r="DD9" s="61"/>
-      <c r="DE9" s="61"/>
-      <c r="DF9" s="61"/>
-      <c r="DG9" s="61"/>
-      <c r="DH9" s="61"/>
-      <c r="DI9" s="61"/>
-      <c r="DJ9" s="61"/>
-      <c r="DK9" s="61"/>
-      <c r="DL9" s="61"/>
-      <c r="DM9" s="61"/>
-      <c r="DN9" s="61"/>
-      <c r="DO9" s="61"/>
-      <c r="DP9" s="61"/>
-      <c r="DQ9" s="61"/>
-      <c r="DR9" s="61"/>
-      <c r="DS9" s="61"/>
-      <c r="DT9" s="61"/>
-      <c r="DU9" s="61"/>
-      <c r="DV9" s="61"/>
-      <c r="DW9" s="61"/>
-      <c r="DX9" s="61"/>
-      <c r="DY9" s="61"/>
-      <c r="DZ9" s="61"/>
-      <c r="EA9" s="61"/>
-      <c r="EB9" s="61"/>
-      <c r="EC9" s="61"/>
-      <c r="ED9" s="61"/>
-      <c r="EE9" s="61"/>
-      <c r="EF9" s="61"/>
-      <c r="EG9" s="61"/>
-      <c r="EH9" s="61"/>
-      <c r="EI9" s="61"/>
-      <c r="EJ9" s="61"/>
-      <c r="EK9" s="61"/>
-      <c r="EL9" s="61"/>
-      <c r="EM9" s="61"/>
-      <c r="EN9" s="61"/>
-      <c r="EO9" s="61"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
+      <c r="BX9" s="28"/>
+      <c r="BY9" s="28"/>
+      <c r="BZ9" s="28"/>
+      <c r="CA9" s="28"/>
+      <c r="CB9" s="28"/>
+      <c r="CC9" s="28"/>
+      <c r="CD9" s="28"/>
+      <c r="CE9" s="28"/>
+      <c r="CF9" s="28"/>
+      <c r="CG9" s="28"/>
+      <c r="CH9" s="28"/>
+      <c r="CI9" s="28"/>
+      <c r="CJ9" s="28"/>
+      <c r="CK9" s="28"/>
+      <c r="CL9" s="28"/>
+      <c r="CM9" s="28"/>
+      <c r="CN9" s="28"/>
+      <c r="CO9" s="28"/>
+      <c r="CP9" s="28"/>
+      <c r="CQ9" s="28"/>
+      <c r="CR9" s="28"/>
+      <c r="CS9" s="28"/>
+      <c r="CT9" s="28"/>
+      <c r="CU9" s="28"/>
+      <c r="CV9" s="28"/>
+      <c r="CW9" s="28"/>
+      <c r="CX9" s="28"/>
+      <c r="CY9" s="28"/>
+      <c r="CZ9" s="28"/>
+      <c r="DA9" s="28"/>
+      <c r="DB9" s="28"/>
+      <c r="DC9" s="28"/>
+      <c r="DD9" s="28"/>
+      <c r="DE9" s="28"/>
+      <c r="DF9" s="28"/>
+      <c r="DG9" s="28"/>
+      <c r="DH9" s="28"/>
+      <c r="DI9" s="28"/>
+      <c r="DJ9" s="28"/>
+      <c r="DK9" s="28"/>
+      <c r="DL9" s="28"/>
+      <c r="DM9" s="28"/>
+      <c r="DN9" s="28"/>
+      <c r="DO9" s="28"/>
+      <c r="DP9" s="28"/>
+      <c r="DQ9" s="28"/>
+      <c r="DR9" s="28"/>
+      <c r="DS9" s="28"/>
+      <c r="DT9" s="28"/>
+      <c r="DU9" s="28"/>
+      <c r="DV9" s="28"/>
+      <c r="DW9" s="28"/>
+      <c r="DX9" s="28"/>
+      <c r="DY9" s="28"/>
+      <c r="DZ9" s="28"/>
+      <c r="EA9" s="28"/>
+      <c r="EB9" s="28"/>
+      <c r="EC9" s="28"/>
+      <c r="ED9" s="28"/>
+      <c r="EE9" s="28"/>
+      <c r="EF9" s="28"/>
+      <c r="EG9" s="28"/>
+      <c r="EH9" s="28"/>
+      <c r="EI9" s="28"/>
+      <c r="EJ9" s="28"/>
+      <c r="EK9" s="28"/>
+      <c r="EL9" s="28"/>
+      <c r="EM9" s="28"/>
+      <c r="EN9" s="28"/>
+      <c r="EO9" s="28"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="9"/>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -3202,7 +3209,7 @@
       <c r="EN10" s="11"/>
       <c r="EO10" s="11"/>
     </row>
-    <row r="11" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>1</v>
       </c>
@@ -3358,7 +3365,7 @@
       <c r="EN11" s="11"/>
       <c r="EO11" s="11"/>
     </row>
-    <row r="12" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>2</v>
       </c>
@@ -3556,7 +3563,7 @@
       <c r="EN12" s="11"/>
       <c r="EO12" s="11"/>
     </row>
-    <row r="13" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>3</v>
       </c>
@@ -3782,7 +3789,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>4</v>
       </c>
@@ -3978,7 +3985,7 @@
       <c r="EN14" s="11"/>
       <c r="EO14" s="11"/>
     </row>
-    <row r="15" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>5</v>
       </c>
@@ -4178,7 +4185,7 @@
       <c r="EN15" s="11"/>
       <c r="EO15" s="11"/>
     </row>
-    <row r="16" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>6</v>
       </c>
@@ -4368,7 +4375,7 @@
       <c r="EN16" s="11"/>
       <c r="EO16" s="11"/>
     </row>
-    <row r="17" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>7</v>
       </c>
@@ -4478,115 +4485,115 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AO17" s="23" t="s">
+      <c r="AO17" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="24"/>
-      <c r="AQ17" s="24"/>
-      <c r="AR17" s="24"/>
-      <c r="AS17" s="24"/>
-      <c r="AT17" s="24"/>
-      <c r="AU17" s="24"/>
-      <c r="AV17" s="24"/>
-      <c r="AW17" s="24"/>
-      <c r="AX17" s="24"/>
-      <c r="AY17" s="24"/>
-      <c r="AZ17" s="24"/>
-      <c r="BA17" s="24"/>
-      <c r="BB17" s="24"/>
-      <c r="BC17" s="24"/>
-      <c r="BD17" s="24"/>
-      <c r="BE17" s="24"/>
-      <c r="BF17" s="24"/>
-      <c r="BG17" s="24"/>
-      <c r="BH17" s="24"/>
-      <c r="BI17" s="24"/>
-      <c r="BJ17" s="24"/>
-      <c r="BK17" s="24"/>
-      <c r="BL17" s="24"/>
-      <c r="BM17" s="24"/>
-      <c r="BN17" s="24"/>
-      <c r="BO17" s="24"/>
-      <c r="BP17" s="24"/>
-      <c r="BQ17" s="24"/>
-      <c r="BR17" s="24"/>
-      <c r="BS17" s="24"/>
-      <c r="BT17" s="24"/>
-      <c r="BU17" s="24"/>
-      <c r="BV17" s="24"/>
-      <c r="BW17" s="24"/>
-      <c r="BX17" s="24"/>
-      <c r="BY17" s="24"/>
-      <c r="BZ17" s="24"/>
-      <c r="CA17" s="24"/>
-      <c r="CB17" s="24"/>
-      <c r="CC17" s="24"/>
-      <c r="CD17" s="24"/>
-      <c r="CE17" s="24"/>
-      <c r="CF17" s="24"/>
-      <c r="CG17" s="24"/>
-      <c r="CH17" s="24"/>
-      <c r="CI17" s="24"/>
-      <c r="CJ17" s="24"/>
-      <c r="CK17" s="24"/>
-      <c r="CL17" s="24"/>
-      <c r="CM17" s="24"/>
-      <c r="CN17" s="24"/>
-      <c r="CO17" s="24"/>
-      <c r="CP17" s="24"/>
-      <c r="CQ17" s="24"/>
-      <c r="CR17" s="24"/>
-      <c r="CS17" s="24"/>
-      <c r="CT17" s="24"/>
-      <c r="CU17" s="24"/>
-      <c r="CV17" s="24"/>
-      <c r="CW17" s="24"/>
-      <c r="CX17" s="24"/>
-      <c r="CY17" s="24"/>
-      <c r="CZ17" s="24"/>
-      <c r="DA17" s="24"/>
-      <c r="DB17" s="24"/>
-      <c r="DC17" s="24"/>
-      <c r="DD17" s="24"/>
-      <c r="DE17" s="24"/>
-      <c r="DF17" s="24"/>
-      <c r="DG17" s="24"/>
-      <c r="DH17" s="24"/>
-      <c r="DI17" s="24"/>
-      <c r="DJ17" s="24"/>
-      <c r="DK17" s="24"/>
-      <c r="DL17" s="24"/>
-      <c r="DM17" s="24"/>
-      <c r="DN17" s="24"/>
-      <c r="DO17" s="24"/>
-      <c r="DP17" s="24"/>
-      <c r="DQ17" s="24"/>
-      <c r="DR17" s="24"/>
-      <c r="DS17" s="24"/>
-      <c r="DT17" s="24"/>
-      <c r="DU17" s="24"/>
-      <c r="DV17" s="24"/>
-      <c r="DW17" s="24"/>
-      <c r="DX17" s="24"/>
-      <c r="DY17" s="24"/>
-      <c r="DZ17" s="24"/>
-      <c r="EA17" s="24"/>
-      <c r="EB17" s="24"/>
-      <c r="EC17" s="24"/>
-      <c r="ED17" s="24"/>
-      <c r="EE17" s="24"/>
-      <c r="EF17" s="24"/>
-      <c r="EG17" s="24"/>
-      <c r="EH17" s="24"/>
-      <c r="EI17" s="24"/>
-      <c r="EJ17" s="24"/>
-      <c r="EK17" s="24"/>
-      <c r="EL17" s="24"/>
-      <c r="EM17" s="24"/>
-      <c r="EN17" s="24"/>
-      <c r="EO17" s="25"/>
+      <c r="AP17" s="54"/>
+      <c r="AQ17" s="54"/>
+      <c r="AR17" s="54"/>
+      <c r="AS17" s="54"/>
+      <c r="AT17" s="54"/>
+      <c r="AU17" s="54"/>
+      <c r="AV17" s="54"/>
+      <c r="AW17" s="54"/>
+      <c r="AX17" s="54"/>
+      <c r="AY17" s="54"/>
+      <c r="AZ17" s="54"/>
+      <c r="BA17" s="54"/>
+      <c r="BB17" s="54"/>
+      <c r="BC17" s="54"/>
+      <c r="BD17" s="54"/>
+      <c r="BE17" s="54"/>
+      <c r="BF17" s="54"/>
+      <c r="BG17" s="54"/>
+      <c r="BH17" s="54"/>
+      <c r="BI17" s="54"/>
+      <c r="BJ17" s="54"/>
+      <c r="BK17" s="54"/>
+      <c r="BL17" s="54"/>
+      <c r="BM17" s="54"/>
+      <c r="BN17" s="54"/>
+      <c r="BO17" s="54"/>
+      <c r="BP17" s="54"/>
+      <c r="BQ17" s="54"/>
+      <c r="BR17" s="54"/>
+      <c r="BS17" s="54"/>
+      <c r="BT17" s="54"/>
+      <c r="BU17" s="54"/>
+      <c r="BV17" s="54"/>
+      <c r="BW17" s="54"/>
+      <c r="BX17" s="54"/>
+      <c r="BY17" s="54"/>
+      <c r="BZ17" s="54"/>
+      <c r="CA17" s="54"/>
+      <c r="CB17" s="54"/>
+      <c r="CC17" s="54"/>
+      <c r="CD17" s="54"/>
+      <c r="CE17" s="54"/>
+      <c r="CF17" s="54"/>
+      <c r="CG17" s="54"/>
+      <c r="CH17" s="54"/>
+      <c r="CI17" s="54"/>
+      <c r="CJ17" s="54"/>
+      <c r="CK17" s="54"/>
+      <c r="CL17" s="54"/>
+      <c r="CM17" s="54"/>
+      <c r="CN17" s="54"/>
+      <c r="CO17" s="54"/>
+      <c r="CP17" s="54"/>
+      <c r="CQ17" s="54"/>
+      <c r="CR17" s="54"/>
+      <c r="CS17" s="54"/>
+      <c r="CT17" s="54"/>
+      <c r="CU17" s="54"/>
+      <c r="CV17" s="54"/>
+      <c r="CW17" s="54"/>
+      <c r="CX17" s="54"/>
+      <c r="CY17" s="54"/>
+      <c r="CZ17" s="54"/>
+      <c r="DA17" s="54"/>
+      <c r="DB17" s="54"/>
+      <c r="DC17" s="54"/>
+      <c r="DD17" s="54"/>
+      <c r="DE17" s="54"/>
+      <c r="DF17" s="54"/>
+      <c r="DG17" s="54"/>
+      <c r="DH17" s="54"/>
+      <c r="DI17" s="54"/>
+      <c r="DJ17" s="54"/>
+      <c r="DK17" s="54"/>
+      <c r="DL17" s="54"/>
+      <c r="DM17" s="54"/>
+      <c r="DN17" s="54"/>
+      <c r="DO17" s="54"/>
+      <c r="DP17" s="54"/>
+      <c r="DQ17" s="54"/>
+      <c r="DR17" s="54"/>
+      <c r="DS17" s="54"/>
+      <c r="DT17" s="54"/>
+      <c r="DU17" s="54"/>
+      <c r="DV17" s="54"/>
+      <c r="DW17" s="54"/>
+      <c r="DX17" s="54"/>
+      <c r="DY17" s="54"/>
+      <c r="DZ17" s="54"/>
+      <c r="EA17" s="54"/>
+      <c r="EB17" s="54"/>
+      <c r="EC17" s="54"/>
+      <c r="ED17" s="54"/>
+      <c r="EE17" s="54"/>
+      <c r="EF17" s="54"/>
+      <c r="EG17" s="54"/>
+      <c r="EH17" s="54"/>
+      <c r="EI17" s="54"/>
+      <c r="EJ17" s="54"/>
+      <c r="EK17" s="54"/>
+      <c r="EL17" s="54"/>
+      <c r="EM17" s="54"/>
+      <c r="EN17" s="54"/>
+      <c r="EO17" s="55"/>
     </row>
-    <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>8</v>
       </c>
@@ -4766,7 +4773,7 @@
       <c r="EN18" s="11"/>
       <c r="EO18" s="11"/>
     </row>
-    <row r="19" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>9</v>
       </c>
@@ -4966,7 +4973,7 @@
       <c r="EN19" s="11"/>
       <c r="EO19" s="11"/>
     </row>
-    <row r="20" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>10</v>
       </c>
@@ -5136,7 +5143,7 @@
       <c r="EN20" s="11"/>
       <c r="EO20" s="11"/>
     </row>
-    <row r="21" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>11</v>
       </c>
@@ -5420,7 +5427,7 @@
       <c r="EN21" s="11"/>
       <c r="EO21" s="11"/>
     </row>
-    <row r="22" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>12</v>
       </c>
@@ -5636,7 +5643,7 @@
       <c r="EN22" s="11"/>
       <c r="EO22" s="11"/>
     </row>
-    <row r="23" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>13</v>
       </c>
@@ -5924,7 +5931,7 @@
       <c r="EN23" s="11"/>
       <c r="EO23" s="11"/>
     </row>
-    <row r="24" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>14</v>
       </c>
@@ -6134,7 +6141,7 @@
       <c r="EN24" s="11"/>
       <c r="EO24" s="11"/>
     </row>
-    <row r="25" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>15</v>
       </c>
@@ -6360,7 +6367,7 @@
       <c r="EN25" s="11"/>
       <c r="EO25" s="11"/>
     </row>
-    <row r="26" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>16</v>
       </c>
@@ -6576,7 +6583,7 @@
       <c r="EN26" s="11"/>
       <c r="EO26" s="11"/>
     </row>
-    <row r="27" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>17</v>
       </c>
@@ -6862,7 +6869,7 @@
       <c r="EN27" s="11"/>
       <c r="EO27" s="11"/>
     </row>
-    <row r="28" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>18</v>
       </c>
@@ -6876,149 +6883,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="65"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="65"/>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65"/>
-      <c r="T28" s="65"/>
-      <c r="U28" s="65"/>
-      <c r="V28" s="65"/>
-      <c r="W28" s="65"/>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="65"/>
-      <c r="Z28" s="65"/>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="65"/>
-      <c r="AC28" s="65"/>
-      <c r="AD28" s="65"/>
-      <c r="AE28" s="65"/>
-      <c r="AF28" s="65"/>
-      <c r="AG28" s="65"/>
-      <c r="AH28" s="65"/>
-      <c r="AI28" s="65"/>
-      <c r="AJ28" s="65"/>
-      <c r="AK28" s="65"/>
-      <c r="AL28" s="65"/>
-      <c r="AM28" s="65"/>
-      <c r="AN28" s="65"/>
-      <c r="AO28" s="65"/>
-      <c r="AP28" s="65"/>
-      <c r="AQ28" s="65"/>
-      <c r="AR28" s="65"/>
-      <c r="AS28" s="65"/>
-      <c r="AT28" s="65"/>
-      <c r="AU28" s="65"/>
-      <c r="AV28" s="65"/>
-      <c r="AW28" s="65"/>
-      <c r="AX28" s="65"/>
-      <c r="AY28" s="65"/>
-      <c r="AZ28" s="65"/>
-      <c r="BA28" s="65"/>
-      <c r="BB28" s="65"/>
-      <c r="BC28" s="65"/>
-      <c r="BD28" s="65"/>
-      <c r="BE28" s="65"/>
-      <c r="BF28" s="65"/>
-      <c r="BG28" s="65"/>
-      <c r="BH28" s="65"/>
-      <c r="BI28" s="65"/>
-      <c r="BJ28" s="65"/>
-      <c r="BK28" s="65"/>
-      <c r="BL28" s="65"/>
-      <c r="BM28" s="65"/>
-      <c r="BN28" s="65"/>
-      <c r="BO28" s="65"/>
-      <c r="BP28" s="65"/>
-      <c r="BQ28" s="65"/>
-      <c r="BR28" s="65"/>
-      <c r="BS28" s="65"/>
-      <c r="BT28" s="65"/>
-      <c r="BU28" s="65"/>
-      <c r="BV28" s="65"/>
-      <c r="BW28" s="65"/>
-      <c r="BX28" s="65"/>
-      <c r="BY28" s="65"/>
-      <c r="BZ28" s="65"/>
-      <c r="CA28" s="65"/>
-      <c r="CB28" s="65"/>
-      <c r="CC28" s="65"/>
-      <c r="CD28" s="65"/>
-      <c r="CE28" s="65"/>
-      <c r="CF28" s="65"/>
-      <c r="CG28" s="65"/>
-      <c r="CH28" s="65"/>
-      <c r="CI28" s="65"/>
-      <c r="CJ28" s="65"/>
-      <c r="CK28" s="65"/>
-      <c r="CL28" s="65"/>
-      <c r="CM28" s="65"/>
-      <c r="CN28" s="65"/>
-      <c r="CO28" s="65"/>
-      <c r="CP28" s="65"/>
-      <c r="CQ28" s="65"/>
-      <c r="CR28" s="65"/>
-      <c r="CS28" s="65"/>
-      <c r="CT28" s="65"/>
-      <c r="CU28" s="65"/>
-      <c r="CV28" s="65"/>
-      <c r="CW28" s="65"/>
-      <c r="CX28" s="65"/>
-      <c r="CY28" s="65"/>
-      <c r="CZ28" s="65"/>
-      <c r="DA28" s="65"/>
-      <c r="DB28" s="65"/>
-      <c r="DC28" s="65"/>
-      <c r="DD28" s="65"/>
-      <c r="DE28" s="65"/>
-      <c r="DF28" s="65"/>
-      <c r="DG28" s="65"/>
-      <c r="DH28" s="65"/>
-      <c r="DI28" s="65"/>
-      <c r="DJ28" s="65"/>
-      <c r="DK28" s="65"/>
-      <c r="DL28" s="65"/>
-      <c r="DM28" s="65"/>
-      <c r="DN28" s="65"/>
-      <c r="DO28" s="65"/>
-      <c r="DP28" s="65"/>
-      <c r="DQ28" s="65"/>
-      <c r="DR28" s="65"/>
-      <c r="DS28" s="65"/>
-      <c r="DT28" s="65"/>
-      <c r="DU28" s="65"/>
-      <c r="DV28" s="65"/>
-      <c r="DW28" s="65"/>
-      <c r="DX28" s="65"/>
-      <c r="DY28" s="65"/>
-      <c r="DZ28" s="65"/>
-      <c r="EA28" s="65"/>
-      <c r="EB28" s="65"/>
-      <c r="EC28" s="65"/>
-      <c r="ED28" s="65"/>
-      <c r="EE28" s="65"/>
-      <c r="EF28" s="65"/>
-      <c r="EG28" s="65"/>
-      <c r="EH28" s="65"/>
-      <c r="EI28" s="65"/>
-      <c r="EJ28" s="65"/>
-      <c r="EK28" s="65"/>
-      <c r="EL28" s="65"/>
-      <c r="EM28" s="65"/>
-      <c r="EN28" s="65"/>
-      <c r="EO28" s="65"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29"/>
+      <c r="AC28" s="29"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="29"/>
+      <c r="AF28" s="29"/>
+      <c r="AG28" s="29"/>
+      <c r="AH28" s="29"/>
+      <c r="AI28" s="29"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="29"/>
+      <c r="AL28" s="29"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="29"/>
+      <c r="AO28" s="29"/>
+      <c r="AP28" s="29"/>
+      <c r="AQ28" s="29"/>
+      <c r="AR28" s="29"/>
+      <c r="AS28" s="29"/>
+      <c r="AT28" s="29"/>
+      <c r="AU28" s="29"/>
+      <c r="AV28" s="29"/>
+      <c r="AW28" s="29"/>
+      <c r="AX28" s="29"/>
+      <c r="AY28" s="29"/>
+      <c r="AZ28" s="29"/>
+      <c r="BA28" s="29"/>
+      <c r="BB28" s="29"/>
+      <c r="BC28" s="29"/>
+      <c r="BD28" s="29"/>
+      <c r="BE28" s="29"/>
+      <c r="BF28" s="29"/>
+      <c r="BG28" s="29"/>
+      <c r="BH28" s="29"/>
+      <c r="BI28" s="29"/>
+      <c r="BJ28" s="29"/>
+      <c r="BK28" s="29"/>
+      <c r="BL28" s="29"/>
+      <c r="BM28" s="29"/>
+      <c r="BN28" s="29"/>
+      <c r="BO28" s="29"/>
+      <c r="BP28" s="29"/>
+      <c r="BQ28" s="29"/>
+      <c r="BR28" s="29"/>
+      <c r="BS28" s="29"/>
+      <c r="BT28" s="29"/>
+      <c r="BU28" s="29"/>
+      <c r="BV28" s="29"/>
+      <c r="BW28" s="29"/>
+      <c r="BX28" s="29"/>
+      <c r="BY28" s="29"/>
+      <c r="BZ28" s="29"/>
+      <c r="CA28" s="29"/>
+      <c r="CB28" s="29"/>
+      <c r="CC28" s="29"/>
+      <c r="CD28" s="29"/>
+      <c r="CE28" s="29"/>
+      <c r="CF28" s="29"/>
+      <c r="CG28" s="29"/>
+      <c r="CH28" s="29"/>
+      <c r="CI28" s="29"/>
+      <c r="CJ28" s="29"/>
+      <c r="CK28" s="29"/>
+      <c r="CL28" s="29"/>
+      <c r="CM28" s="29"/>
+      <c r="CN28" s="29"/>
+      <c r="CO28" s="29"/>
+      <c r="CP28" s="29"/>
+      <c r="CQ28" s="29"/>
+      <c r="CR28" s="29"/>
+      <c r="CS28" s="29"/>
+      <c r="CT28" s="29"/>
+      <c r="CU28" s="29"/>
+      <c r="CV28" s="29"/>
+      <c r="CW28" s="29"/>
+      <c r="CX28" s="29"/>
+      <c r="CY28" s="29"/>
+      <c r="CZ28" s="29"/>
+      <c r="DA28" s="29"/>
+      <c r="DB28" s="29"/>
+      <c r="DC28" s="29"/>
+      <c r="DD28" s="29"/>
+      <c r="DE28" s="29"/>
+      <c r="DF28" s="29"/>
+      <c r="DG28" s="29"/>
+      <c r="DH28" s="29"/>
+      <c r="DI28" s="29"/>
+      <c r="DJ28" s="29"/>
+      <c r="DK28" s="29"/>
+      <c r="DL28" s="29"/>
+      <c r="DM28" s="29"/>
+      <c r="DN28" s="29"/>
+      <c r="DO28" s="29"/>
+      <c r="DP28" s="29"/>
+      <c r="DQ28" s="29"/>
+      <c r="DR28" s="29"/>
+      <c r="DS28" s="29"/>
+      <c r="DT28" s="29"/>
+      <c r="DU28" s="29"/>
+      <c r="DV28" s="29"/>
+      <c r="DW28" s="29"/>
+      <c r="DX28" s="29"/>
+      <c r="DY28" s="29"/>
+      <c r="DZ28" s="29"/>
+      <c r="EA28" s="29"/>
+      <c r="EB28" s="29"/>
+      <c r="EC28" s="29"/>
+      <c r="ED28" s="29"/>
+      <c r="EE28" s="29"/>
+      <c r="EF28" s="29"/>
+      <c r="EG28" s="29"/>
+      <c r="EH28" s="29"/>
+      <c r="EI28" s="29"/>
+      <c r="EJ28" s="29"/>
+      <c r="EK28" s="29"/>
+      <c r="EL28" s="29"/>
+      <c r="EM28" s="29"/>
+      <c r="EN28" s="29"/>
+      <c r="EO28" s="29"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -7027,6 +7034,300 @@
     </row>
   </sheetData>
   <mergeCells count="318">
+    <mergeCell ref="AO17:EO17"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="BM1:BO1"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="E28:EO28"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EC8:EC9"/>
     <mergeCell ref="BZ1:CB1"/>
     <mergeCell ref="BQ1:BU1"/>
     <mergeCell ref="BV1:BX1"/>
@@ -7051,300 +7352,6 @@
     <mergeCell ref="DW8:DW9"/>
     <mergeCell ref="DX8:DX9"/>
     <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="E28:EO28"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="BH1:BL1"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AO17:EO17"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="BM1:BO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
+++ b/ჟურნალი/4. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - TypeScript.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\designer\Desktop\Front\01. - Front-end-docs\ჟურნალი\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8A0702-49D6-4E98-B8B6-2CBA26E2BE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A7B98B-B4BB-408B-9551-205B00031EE4}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-122" yWindow="-122" windowWidth="29045" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="301 ინტეგრირებული" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -782,7 +769,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -832,101 +819,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -958,6 +852,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -975,6 +872,99 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1193,30 +1183,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:ET31"/>
-  <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="2"/>
+    <col min="1" max="1" width="3.625" style="2"/>
     <col min="2" max="3" width="21" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="3.5703125" style="1"/>
+    <col min="5" max="5" width="5.625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="3.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="57" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-      <c r="F1" s="61">
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="F1" s="30">
         <v>4</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="32">
         <v>3</v>
       </c>
@@ -1228,72 +1218,72 @@
       <c r="N1" s="32"/>
       <c r="O1" s="32"/>
       <c r="P1" s="32"/>
-      <c r="Q1" s="63">
+      <c r="Q1" s="33">
         <v>4</v>
       </c>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="63">
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="33">
         <v>4</v>
       </c>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="63">
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="33">
         <v>4</v>
       </c>
-      <c r="Z1" s="64"/>
-      <c r="AA1" s="64"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="30">
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="65">
         <v>2</v>
       </c>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="21">
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="43">
         <v>4</v>
       </c>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="21">
+      <c r="AF1" s="44"/>
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="43">
         <v>4</v>
       </c>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="21">
+      <c r="AJ1" s="44"/>
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="43">
         <v>2</v>
       </c>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="21">
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="43">
         <v>4</v>
       </c>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="22"/>
-      <c r="AR1" s="23"/>
-      <c r="AS1" s="21">
+      <c r="AP1" s="44"/>
+      <c r="AQ1" s="44"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="43">
         <v>5</v>
       </c>
-      <c r="AT1" s="22"/>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
-      <c r="AW1" s="23"/>
+      <c r="AT1" s="44"/>
+      <c r="AU1" s="44"/>
+      <c r="AV1" s="44"/>
+      <c r="AW1" s="45"/>
       <c r="AX1" s="3">
         <v>1</v>
       </c>
-      <c r="AY1" s="21">
+      <c r="AY1" s="43">
         <v>5</v>
       </c>
-      <c r="AZ1" s="22"/>
-      <c r="BA1" s="22"/>
-      <c r="BB1" s="22"/>
-      <c r="BC1" s="23"/>
-      <c r="BD1" s="21">
+      <c r="AZ1" s="44"/>
+      <c r="BA1" s="44"/>
+      <c r="BB1" s="44"/>
+      <c r="BC1" s="45"/>
+      <c r="BD1" s="43">
         <v>3</v>
       </c>
-      <c r="BE1" s="22"/>
-      <c r="BF1" s="23"/>
+      <c r="BE1" s="44"/>
+      <c r="BF1" s="45"/>
       <c r="BG1" s="3">
         <v>1</v>
       </c>
@@ -1304,36 +1294,36 @@
       <c r="BJ1" s="32"/>
       <c r="BK1" s="32"/>
       <c r="BL1" s="32"/>
-      <c r="BM1" s="21">
+      <c r="BM1" s="43">
         <v>3</v>
       </c>
-      <c r="BN1" s="22"/>
-      <c r="BO1" s="23"/>
+      <c r="BN1" s="44"/>
+      <c r="BO1" s="45"/>
       <c r="BP1" s="20">
         <v>1</v>
       </c>
-      <c r="BQ1" s="24">
+      <c r="BQ1" s="67">
         <v>5</v>
       </c>
-      <c r="BR1" s="25"/>
-      <c r="BS1" s="25"/>
-      <c r="BT1" s="25"/>
-      <c r="BU1" s="26"/>
-      <c r="BV1" s="21">
+      <c r="BR1" s="68"/>
+      <c r="BS1" s="68"/>
+      <c r="BT1" s="68"/>
+      <c r="BU1" s="69"/>
+      <c r="BV1" s="43">
         <v>3</v>
       </c>
-      <c r="BW1" s="22"/>
-      <c r="BX1" s="23"/>
+      <c r="BW1" s="44"/>
+      <c r="BX1" s="45"/>
       <c r="BY1" s="3">
         <v>1</v>
       </c>
-      <c r="BZ1" s="21">
+      <c r="BZ1" s="43">
         <v>3</v>
       </c>
-      <c r="CA1" s="22"/>
-      <c r="CB1" s="23"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
+      <c r="CA1" s="44"/>
+      <c r="CB1" s="45"/>
+      <c r="CC1" s="21"/>
+      <c r="CD1" s="21"/>
       <c r="CE1" s="4"/>
       <c r="CF1" s="4"/>
       <c r="CG1" s="4"/>
@@ -1403,32 +1393,32 @@
       </c>
     </row>
     <row r="2" spans="1:150" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="56"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="66" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="41" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="41" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="39" t="s">
@@ -1446,37 +1436,37 @@
       <c r="Q2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="41" t="s">
         <v>6</v>
       </c>
       <c r="U2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="51" t="s">
+      <c r="W2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="51" t="s">
+      <c r="X2" s="41" t="s">
         <v>7</v>
       </c>
       <c r="Y2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="51" t="s">
+      <c r="Z2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="49" t="s">
+      <c r="AA2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="49" t="s">
+      <c r="AB2" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AC2" s="39">
@@ -1620,7 +1610,7 @@
       <c r="BW2" s="39">
         <v>46234</v>
       </c>
-      <c r="BX2" s="47">
+      <c r="BX2" s="48">
         <v>46234</v>
       </c>
       <c r="BY2" s="39">
@@ -1701,37 +1691,37 @@
       <c r="EN2" s="39"/>
       <c r="EO2" s="39"/>
     </row>
-    <row r="3" spans="1:150" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+    <row r="3" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="67"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="37"/>
       <c r="F3" s="39"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
       <c r="J3" s="39"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
       <c r="O3" s="39"/>
       <c r="P3" s="39"/>
       <c r="Q3" s="39"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
       <c r="U3" s="39"/>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="51"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
       <c r="Y3" s="39"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="46"/>
       <c r="AC3" s="39"/>
       <c r="AD3" s="39"/>
       <c r="AE3" s="39"/>
@@ -1779,7 +1769,7 @@
       <c r="BU3" s="39"/>
       <c r="BV3" s="39"/>
       <c r="BW3" s="39"/>
-      <c r="BX3" s="47"/>
+      <c r="BX3" s="48"/>
       <c r="BY3" s="39"/>
       <c r="BZ3" s="39"/>
       <c r="CA3" s="39"/>
@@ -1850,39 +1840,39 @@
       <c r="EN3" s="39"/>
       <c r="EO3" s="39"/>
     </row>
-    <row r="4" spans="1:150" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+    <row r="4" spans="1:150" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="67"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="39"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="39"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
       <c r="M4" s="39"/>
       <c r="N4" s="39"/>
       <c r="O4" s="39"/>
       <c r="P4" s="39"/>
       <c r="Q4" s="39"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
       <c r="U4" s="39"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="51"/>
-      <c r="X4" s="51"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
       <c r="Y4" s="39"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="49"/>
-      <c r="AB4" s="49"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
       <c r="AC4" s="39"/>
       <c r="AD4" s="39"/>
       <c r="AE4" s="39"/>
@@ -1930,7 +1920,7 @@
       <c r="BU4" s="39"/>
       <c r="BV4" s="39"/>
       <c r="BW4" s="39"/>
-      <c r="BX4" s="47"/>
+      <c r="BX4" s="48"/>
       <c r="BY4" s="39"/>
       <c r="BZ4" s="39"/>
       <c r="CA4" s="39"/>
@@ -2001,39 +1991,39 @@
       <c r="EN4" s="39"/>
       <c r="EO4" s="39"/>
     </row>
-    <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+    <row r="5" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44">
+      <c r="B5" s="53"/>
+      <c r="C5" s="54">
         <v>110</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="67"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="39"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
       <c r="M5" s="39"/>
       <c r="N5" s="39"/>
       <c r="O5" s="39"/>
       <c r="P5" s="39"/>
       <c r="Q5" s="39"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
       <c r="U5" s="39"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
       <c r="Y5" s="39"/>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="49"/>
-      <c r="AB5" s="49"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
       <c r="AC5" s="39"/>
       <c r="AD5" s="39"/>
       <c r="AE5" s="39"/>
@@ -2081,7 +2071,7 @@
       <c r="BU5" s="39"/>
       <c r="BV5" s="39"/>
       <c r="BW5" s="39"/>
-      <c r="BX5" s="47"/>
+      <c r="BX5" s="48"/>
       <c r="BY5" s="39"/>
       <c r="BZ5" s="39"/>
       <c r="CA5" s="39"/>
@@ -2152,39 +2142,39 @@
       <c r="EN5" s="39"/>
       <c r="EO5" s="39"/>
     </row>
-    <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+    <row r="6" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44">
+      <c r="B6" s="53"/>
+      <c r="C6" s="54">
         <v>10</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="67"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="39"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="39"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
       <c r="M6" s="39"/>
       <c r="N6" s="39"/>
       <c r="O6" s="39"/>
       <c r="P6" s="39"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="39"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
       <c r="Y6" s="39"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="49"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
       <c r="AC6" s="39"/>
       <c r="AD6" s="39"/>
       <c r="AE6" s="39"/>
@@ -2232,7 +2222,7 @@
       <c r="BU6" s="39"/>
       <c r="BV6" s="39"/>
       <c r="BW6" s="39"/>
-      <c r="BX6" s="47"/>
+      <c r="BX6" s="48"/>
       <c r="BY6" s="39"/>
       <c r="BZ6" s="39"/>
       <c r="CA6" s="39"/>
@@ -2303,39 +2293,39 @@
       <c r="EN6" s="39"/>
       <c r="EO6" s="39"/>
     </row>
-    <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+    <row r="7" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="44">
+      <c r="B7" s="56"/>
+      <c r="C7" s="54">
         <v>30</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="68"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="38"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
       <c r="J7" s="40"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
       <c r="M7" s="40"/>
       <c r="N7" s="40"/>
       <c r="O7" s="40"/>
       <c r="P7" s="40"/>
       <c r="Q7" s="40"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
       <c r="U7" s="40"/>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
-      <c r="X7" s="52"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
       <c r="Y7" s="40"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="50"/>
-      <c r="AB7" s="50"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="47"/>
+      <c r="AB7" s="47"/>
       <c r="AC7" s="40"/>
       <c r="AD7" s="40"/>
       <c r="AE7" s="40"/>
@@ -2383,7 +2373,7 @@
       <c r="BU7" s="40"/>
       <c r="BV7" s="40"/>
       <c r="BW7" s="40"/>
-      <c r="BX7" s="48"/>
+      <c r="BX7" s="49"/>
       <c r="BY7" s="40"/>
       <c r="BZ7" s="40"/>
       <c r="CA7" s="40"/>
@@ -2454,593 +2444,593 @@
       <c r="EN7" s="40"/>
       <c r="EO7" s="40"/>
     </row>
-    <row r="8" spans="1:150" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+    <row r="8" spans="1:150" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="34">
+      <c r="B8" s="57"/>
+      <c r="C8" s="58">
         <v>150</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="27">
+      <c r="F8" s="59">
         <v>1</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="59">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="59">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="59">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="59">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="59">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="59">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="59">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="59">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="59">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="59">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="59">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="59">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="59">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="59">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="59">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="59">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="59">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="59">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="59">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="59">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="59">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="59">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="59">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="59">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="59">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="59">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="59">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="59">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="59">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="59">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="59">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="59">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="59">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="59">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="59">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="59">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="59">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="59">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="59">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="59">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="59">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="59">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="59">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="59">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="59">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="59">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="59">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="59">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="59">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="59">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="59">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="59">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="59">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="59">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="59">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="59">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="59">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="59">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="59">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="59">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="59">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="59">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="59">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="59">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="59">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="59">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="59">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="59">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="59">
         <v>70</v>
       </c>
-      <c r="BX8" s="27">
+      <c r="BX8" s="59">
         <v>71</v>
       </c>
-      <c r="BY8" s="27">
+      <c r="BY8" s="59">
         <v>72</v>
       </c>
-      <c r="BZ8" s="27">
+      <c r="BZ8" s="59">
         <v>73</v>
       </c>
-      <c r="CA8" s="27">
+      <c r="CA8" s="59">
         <v>74</v>
       </c>
-      <c r="CB8" s="27">
+      <c r="CB8" s="59">
         <v>75</v>
       </c>
-      <c r="CC8" s="27">
+      <c r="CC8" s="59">
         <v>76</v>
       </c>
-      <c r="CD8" s="27">
+      <c r="CD8" s="59">
         <v>77</v>
       </c>
-      <c r="CE8" s="27">
+      <c r="CE8" s="59">
         <v>78</v>
       </c>
-      <c r="CF8" s="27">
+      <c r="CF8" s="59">
         <v>79</v>
       </c>
-      <c r="CG8" s="27">
+      <c r="CG8" s="59">
         <v>80</v>
       </c>
-      <c r="CH8" s="27">
+      <c r="CH8" s="59">
         <v>81</v>
       </c>
-      <c r="CI8" s="27">
+      <c r="CI8" s="59">
         <v>82</v>
       </c>
-      <c r="CJ8" s="27">
+      <c r="CJ8" s="59">
         <v>83</v>
       </c>
-      <c r="CK8" s="27">
+      <c r="CK8" s="59">
         <v>84</v>
       </c>
-      <c r="CL8" s="27">
+      <c r="CL8" s="59">
         <v>85</v>
       </c>
-      <c r="CM8" s="27">
+      <c r="CM8" s="59">
         <v>86</v>
       </c>
-      <c r="CN8" s="27">
+      <c r="CN8" s="59">
         <v>87</v>
       </c>
-      <c r="CO8" s="27">
+      <c r="CO8" s="59">
         <v>88</v>
       </c>
-      <c r="CP8" s="27">
+      <c r="CP8" s="59">
         <v>89</v>
       </c>
-      <c r="CQ8" s="27">
+      <c r="CQ8" s="59">
         <v>90</v>
       </c>
-      <c r="CR8" s="27">
+      <c r="CR8" s="59">
         <v>91</v>
       </c>
-      <c r="CS8" s="27">
+      <c r="CS8" s="59">
         <v>92</v>
       </c>
-      <c r="CT8" s="27">
+      <c r="CT8" s="59">
         <v>93</v>
       </c>
-      <c r="CU8" s="27">
+      <c r="CU8" s="59">
         <v>94</v>
       </c>
-      <c r="CV8" s="27">
+      <c r="CV8" s="59">
         <v>95</v>
       </c>
-      <c r="CW8" s="27">
+      <c r="CW8" s="59">
         <v>96</v>
       </c>
-      <c r="CX8" s="27">
+      <c r="CX8" s="59">
         <v>97</v>
       </c>
-      <c r="CY8" s="27">
+      <c r="CY8" s="59">
         <v>98</v>
       </c>
-      <c r="CZ8" s="27">
+      <c r="CZ8" s="59">
         <v>99</v>
       </c>
-      <c r="DA8" s="27">
+      <c r="DA8" s="59">
         <v>100</v>
       </c>
-      <c r="DB8" s="27">
+      <c r="DB8" s="59">
         <v>101</v>
       </c>
-      <c r="DC8" s="27">
+      <c r="DC8" s="59">
         <v>102</v>
       </c>
-      <c r="DD8" s="27">
+      <c r="DD8" s="59">
         <v>103</v>
       </c>
-      <c r="DE8" s="27">
+      <c r="DE8" s="59">
         <v>104</v>
       </c>
-      <c r="DF8" s="27">
+      <c r="DF8" s="59">
         <v>105</v>
       </c>
-      <c r="DG8" s="27">
+      <c r="DG8" s="59">
         <v>106</v>
       </c>
-      <c r="DH8" s="27">
+      <c r="DH8" s="59">
         <v>107</v>
       </c>
-      <c r="DI8" s="27">
+      <c r="DI8" s="59">
         <v>108</v>
       </c>
-      <c r="DJ8" s="27">
+      <c r="DJ8" s="59">
         <v>109</v>
       </c>
-      <c r="DK8" s="27">
+      <c r="DK8" s="59">
         <v>110</v>
       </c>
-      <c r="DL8" s="27">
+      <c r="DL8" s="59">
         <v>111</v>
       </c>
-      <c r="DM8" s="27">
+      <c r="DM8" s="59">
         <v>112</v>
       </c>
-      <c r="DN8" s="27">
+      <c r="DN8" s="59">
         <v>113</v>
       </c>
-      <c r="DO8" s="27">
+      <c r="DO8" s="59">
         <v>114</v>
       </c>
-      <c r="DP8" s="27">
+      <c r="DP8" s="59">
         <v>115</v>
       </c>
-      <c r="DQ8" s="27">
+      <c r="DQ8" s="59">
         <v>116</v>
       </c>
-      <c r="DR8" s="27">
+      <c r="DR8" s="59">
         <v>117</v>
       </c>
-      <c r="DS8" s="27">
+      <c r="DS8" s="59">
         <v>118</v>
       </c>
-      <c r="DT8" s="27">
+      <c r="DT8" s="59">
         <v>119</v>
       </c>
-      <c r="DU8" s="27">
+      <c r="DU8" s="59">
         <v>120</v>
       </c>
-      <c r="DV8" s="27">
+      <c r="DV8" s="59">
         <v>121</v>
       </c>
-      <c r="DW8" s="27">
+      <c r="DW8" s="59">
         <v>122</v>
       </c>
-      <c r="DX8" s="27">
+      <c r="DX8" s="59">
         <v>123</v>
       </c>
-      <c r="DY8" s="27">
+      <c r="DY8" s="59">
         <v>124</v>
       </c>
-      <c r="DZ8" s="27">
+      <c r="DZ8" s="59">
         <v>125</v>
       </c>
-      <c r="EA8" s="27">
+      <c r="EA8" s="59">
         <v>126</v>
       </c>
-      <c r="EB8" s="27">
+      <c r="EB8" s="59">
         <v>127</v>
       </c>
-      <c r="EC8" s="27">
+      <c r="EC8" s="59">
         <v>128</v>
       </c>
-      <c r="ED8" s="27">
+      <c r="ED8" s="59">
         <v>129</v>
       </c>
-      <c r="EE8" s="27">
+      <c r="EE8" s="59">
         <v>130</v>
       </c>
-      <c r="EF8" s="27">
+      <c r="EF8" s="59">
         <v>131</v>
       </c>
-      <c r="EG8" s="27">
+      <c r="EG8" s="59">
         <v>132</v>
       </c>
-      <c r="EH8" s="27">
+      <c r="EH8" s="59">
         <v>133</v>
       </c>
-      <c r="EI8" s="27">
+      <c r="EI8" s="59">
         <v>134</v>
       </c>
-      <c r="EJ8" s="27">
+      <c r="EJ8" s="59">
         <v>135</v>
       </c>
-      <c r="EK8" s="27">
+      <c r="EK8" s="59">
         <v>136</v>
       </c>
-      <c r="EL8" s="27">
+      <c r="EL8" s="59">
         <v>137</v>
       </c>
-      <c r="EM8" s="27">
+      <c r="EM8" s="59">
         <v>138</v>
       </c>
-      <c r="EN8" s="27">
+      <c r="EN8" s="59">
         <v>139</v>
       </c>
-      <c r="EO8" s="27">
+      <c r="EO8" s="59">
         <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="37"/>
+      <c r="D9" s="62"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
-      <c r="BX9" s="28"/>
-      <c r="BY9" s="28"/>
-      <c r="BZ9" s="28"/>
-      <c r="CA9" s="28"/>
-      <c r="CB9" s="28"/>
-      <c r="CC9" s="28"/>
-      <c r="CD9" s="28"/>
-      <c r="CE9" s="28"/>
-      <c r="CF9" s="28"/>
-      <c r="CG9" s="28"/>
-      <c r="CH9" s="28"/>
-      <c r="CI9" s="28"/>
-      <c r="CJ9" s="28"/>
-      <c r="CK9" s="28"/>
-      <c r="CL9" s="28"/>
-      <c r="CM9" s="28"/>
-      <c r="CN9" s="28"/>
-      <c r="CO9" s="28"/>
-      <c r="CP9" s="28"/>
-      <c r="CQ9" s="28"/>
-      <c r="CR9" s="28"/>
-      <c r="CS9" s="28"/>
-      <c r="CT9" s="28"/>
-      <c r="CU9" s="28"/>
-      <c r="CV9" s="28"/>
-      <c r="CW9" s="28"/>
-      <c r="CX9" s="28"/>
-      <c r="CY9" s="28"/>
-      <c r="CZ9" s="28"/>
-      <c r="DA9" s="28"/>
-      <c r="DB9" s="28"/>
-      <c r="DC9" s="28"/>
-      <c r="DD9" s="28"/>
-      <c r="DE9" s="28"/>
-      <c r="DF9" s="28"/>
-      <c r="DG9" s="28"/>
-      <c r="DH9" s="28"/>
-      <c r="DI9" s="28"/>
-      <c r="DJ9" s="28"/>
-      <c r="DK9" s="28"/>
-      <c r="DL9" s="28"/>
-      <c r="DM9" s="28"/>
-      <c r="DN9" s="28"/>
-      <c r="DO9" s="28"/>
-      <c r="DP9" s="28"/>
-      <c r="DQ9" s="28"/>
-      <c r="DR9" s="28"/>
-      <c r="DS9" s="28"/>
-      <c r="DT9" s="28"/>
-      <c r="DU9" s="28"/>
-      <c r="DV9" s="28"/>
-      <c r="DW9" s="28"/>
-      <c r="DX9" s="28"/>
-      <c r="DY9" s="28"/>
-      <c r="DZ9" s="28"/>
-      <c r="EA9" s="28"/>
-      <c r="EB9" s="28"/>
-      <c r="EC9" s="28"/>
-      <c r="ED9" s="28"/>
-      <c r="EE9" s="28"/>
-      <c r="EF9" s="28"/>
-      <c r="EG9" s="28"/>
-      <c r="EH9" s="28"/>
-      <c r="EI9" s="28"/>
-      <c r="EJ9" s="28"/>
-      <c r="EK9" s="28"/>
-      <c r="EL9" s="28"/>
-      <c r="EM9" s="28"/>
-      <c r="EN9" s="28"/>
-      <c r="EO9" s="28"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="60"/>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="60"/>
+      <c r="AE9" s="60"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+      <c r="BC9" s="60"/>
+      <c r="BD9" s="60"/>
+      <c r="BE9" s="60"/>
+      <c r="BF9" s="60"/>
+      <c r="BG9" s="60"/>
+      <c r="BH9" s="60"/>
+      <c r="BI9" s="60"/>
+      <c r="BJ9" s="60"/>
+      <c r="BK9" s="60"/>
+      <c r="BL9" s="60"/>
+      <c r="BM9" s="60"/>
+      <c r="BN9" s="60"/>
+      <c r="BO9" s="60"/>
+      <c r="BP9" s="60"/>
+      <c r="BQ9" s="60"/>
+      <c r="BR9" s="60"/>
+      <c r="BS9" s="60"/>
+      <c r="BT9" s="60"/>
+      <c r="BU9" s="60"/>
+      <c r="BV9" s="60"/>
+      <c r="BW9" s="60"/>
+      <c r="BX9" s="60"/>
+      <c r="BY9" s="60"/>
+      <c r="BZ9" s="60"/>
+      <c r="CA9" s="60"/>
+      <c r="CB9" s="60"/>
+      <c r="CC9" s="60"/>
+      <c r="CD9" s="60"/>
+      <c r="CE9" s="60"/>
+      <c r="CF9" s="60"/>
+      <c r="CG9" s="60"/>
+      <c r="CH9" s="60"/>
+      <c r="CI9" s="60"/>
+      <c r="CJ9" s="60"/>
+      <c r="CK9" s="60"/>
+      <c r="CL9" s="60"/>
+      <c r="CM9" s="60"/>
+      <c r="CN9" s="60"/>
+      <c r="CO9" s="60"/>
+      <c r="CP9" s="60"/>
+      <c r="CQ9" s="60"/>
+      <c r="CR9" s="60"/>
+      <c r="CS9" s="60"/>
+      <c r="CT9" s="60"/>
+      <c r="CU9" s="60"/>
+      <c r="CV9" s="60"/>
+      <c r="CW9" s="60"/>
+      <c r="CX9" s="60"/>
+      <c r="CY9" s="60"/>
+      <c r="CZ9" s="60"/>
+      <c r="DA9" s="60"/>
+      <c r="DB9" s="60"/>
+      <c r="DC9" s="60"/>
+      <c r="DD9" s="60"/>
+      <c r="DE9" s="60"/>
+      <c r="DF9" s="60"/>
+      <c r="DG9" s="60"/>
+      <c r="DH9" s="60"/>
+      <c r="DI9" s="60"/>
+      <c r="DJ9" s="60"/>
+      <c r="DK9" s="60"/>
+      <c r="DL9" s="60"/>
+      <c r="DM9" s="60"/>
+      <c r="DN9" s="60"/>
+      <c r="DO9" s="60"/>
+      <c r="DP9" s="60"/>
+      <c r="DQ9" s="60"/>
+      <c r="DR9" s="60"/>
+      <c r="DS9" s="60"/>
+      <c r="DT9" s="60"/>
+      <c r="DU9" s="60"/>
+      <c r="DV9" s="60"/>
+      <c r="DW9" s="60"/>
+      <c r="DX9" s="60"/>
+      <c r="DY9" s="60"/>
+      <c r="DZ9" s="60"/>
+      <c r="EA9" s="60"/>
+      <c r="EB9" s="60"/>
+      <c r="EC9" s="60"/>
+      <c r="ED9" s="60"/>
+      <c r="EE9" s="60"/>
+      <c r="EF9" s="60"/>
+      <c r="EG9" s="60"/>
+      <c r="EH9" s="60"/>
+      <c r="EI9" s="60"/>
+      <c r="EJ9" s="60"/>
+      <c r="EK9" s="60"/>
+      <c r="EL9" s="60"/>
+      <c r="EM9" s="60"/>
+      <c r="EN9" s="60"/>
+      <c r="EO9" s="60"/>
     </row>
     <row r="10" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
       <c r="C10" s="9"/>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -3209,7 +3199,7 @@
       <c r="EN10" s="11"/>
       <c r="EO10" s="11"/>
     </row>
-    <row r="11" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <v>1</v>
       </c>
@@ -3365,7 +3355,7 @@
       <c r="EN11" s="11"/>
       <c r="EO11" s="11"/>
     </row>
-    <row r="12" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <v>2</v>
       </c>
@@ -3563,7 +3553,7 @@
       <c r="EN12" s="11"/>
       <c r="EO12" s="11"/>
     </row>
-    <row r="13" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <v>3</v>
       </c>
@@ -3789,7 +3779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <v>4</v>
       </c>
@@ -3985,7 +3975,7 @@
       <c r="EN14" s="11"/>
       <c r="EO14" s="11"/>
     </row>
-    <row r="15" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <v>5</v>
       </c>
@@ -4185,7 +4175,7 @@
       <c r="EN15" s="11"/>
       <c r="EO15" s="11"/>
     </row>
-    <row r="16" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:150" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <v>6</v>
       </c>
@@ -4375,7 +4365,7 @@
       <c r="EN16" s="11"/>
       <c r="EO16" s="11"/>
     </row>
-    <row r="17" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
         <v>7</v>
       </c>
@@ -4485,115 +4475,115 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AO17" s="53" t="s">
+      <c r="AO17" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AP17" s="54"/>
-      <c r="AQ17" s="54"/>
-      <c r="AR17" s="54"/>
-      <c r="AS17" s="54"/>
-      <c r="AT17" s="54"/>
-      <c r="AU17" s="54"/>
-      <c r="AV17" s="54"/>
-      <c r="AW17" s="54"/>
-      <c r="AX17" s="54"/>
-      <c r="AY17" s="54"/>
-      <c r="AZ17" s="54"/>
-      <c r="BA17" s="54"/>
-      <c r="BB17" s="54"/>
-      <c r="BC17" s="54"/>
-      <c r="BD17" s="54"/>
-      <c r="BE17" s="54"/>
-      <c r="BF17" s="54"/>
-      <c r="BG17" s="54"/>
-      <c r="BH17" s="54"/>
-      <c r="BI17" s="54"/>
-      <c r="BJ17" s="54"/>
-      <c r="BK17" s="54"/>
-      <c r="BL17" s="54"/>
-      <c r="BM17" s="54"/>
-      <c r="BN17" s="54"/>
-      <c r="BO17" s="54"/>
-      <c r="BP17" s="54"/>
-      <c r="BQ17" s="54"/>
-      <c r="BR17" s="54"/>
-      <c r="BS17" s="54"/>
-      <c r="BT17" s="54"/>
-      <c r="BU17" s="54"/>
-      <c r="BV17" s="54"/>
-      <c r="BW17" s="54"/>
-      <c r="BX17" s="54"/>
-      <c r="BY17" s="54"/>
-      <c r="BZ17" s="54"/>
-      <c r="CA17" s="54"/>
-      <c r="CB17" s="54"/>
-      <c r="CC17" s="54"/>
-      <c r="CD17" s="54"/>
-      <c r="CE17" s="54"/>
-      <c r="CF17" s="54"/>
-      <c r="CG17" s="54"/>
-      <c r="CH17" s="54"/>
-      <c r="CI17" s="54"/>
-      <c r="CJ17" s="54"/>
-      <c r="CK17" s="54"/>
-      <c r="CL17" s="54"/>
-      <c r="CM17" s="54"/>
-      <c r="CN17" s="54"/>
-      <c r="CO17" s="54"/>
-      <c r="CP17" s="54"/>
-      <c r="CQ17" s="54"/>
-      <c r="CR17" s="54"/>
-      <c r="CS17" s="54"/>
-      <c r="CT17" s="54"/>
-      <c r="CU17" s="54"/>
-      <c r="CV17" s="54"/>
-      <c r="CW17" s="54"/>
-      <c r="CX17" s="54"/>
-      <c r="CY17" s="54"/>
-      <c r="CZ17" s="54"/>
-      <c r="DA17" s="54"/>
-      <c r="DB17" s="54"/>
-      <c r="DC17" s="54"/>
-      <c r="DD17" s="54"/>
-      <c r="DE17" s="54"/>
-      <c r="DF17" s="54"/>
-      <c r="DG17" s="54"/>
-      <c r="DH17" s="54"/>
-      <c r="DI17" s="54"/>
-      <c r="DJ17" s="54"/>
-      <c r="DK17" s="54"/>
-      <c r="DL17" s="54"/>
-      <c r="DM17" s="54"/>
-      <c r="DN17" s="54"/>
-      <c r="DO17" s="54"/>
-      <c r="DP17" s="54"/>
-      <c r="DQ17" s="54"/>
-      <c r="DR17" s="54"/>
-      <c r="DS17" s="54"/>
-      <c r="DT17" s="54"/>
-      <c r="DU17" s="54"/>
-      <c r="DV17" s="54"/>
-      <c r="DW17" s="54"/>
-      <c r="DX17" s="54"/>
-      <c r="DY17" s="54"/>
-      <c r="DZ17" s="54"/>
-      <c r="EA17" s="54"/>
-      <c r="EB17" s="54"/>
-      <c r="EC17" s="54"/>
-      <c r="ED17" s="54"/>
-      <c r="EE17" s="54"/>
-      <c r="EF17" s="54"/>
-      <c r="EG17" s="54"/>
-      <c r="EH17" s="54"/>
-      <c r="EI17" s="54"/>
-      <c r="EJ17" s="54"/>
-      <c r="EK17" s="54"/>
-      <c r="EL17" s="54"/>
-      <c r="EM17" s="54"/>
-      <c r="EN17" s="54"/>
-      <c r="EO17" s="55"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="23"/>
+      <c r="AR17" s="23"/>
+      <c r="AS17" s="23"/>
+      <c r="AT17" s="23"/>
+      <c r="AU17" s="23"/>
+      <c r="AV17" s="23"/>
+      <c r="AW17" s="23"/>
+      <c r="AX17" s="23"/>
+      <c r="AY17" s="23"/>
+      <c r="AZ17" s="23"/>
+      <c r="BA17" s="23"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="23"/>
+      <c r="BD17" s="23"/>
+      <c r="BE17" s="23"/>
+      <c r="BF17" s="23"/>
+      <c r="BG17" s="23"/>
+      <c r="BH17" s="23"/>
+      <c r="BI17" s="23"/>
+      <c r="BJ17" s="23"/>
+      <c r="BK17" s="23"/>
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="23"/>
+      <c r="BP17" s="23"/>
+      <c r="BQ17" s="23"/>
+      <c r="BR17" s="23"/>
+      <c r="BS17" s="23"/>
+      <c r="BT17" s="23"/>
+      <c r="BU17" s="23"/>
+      <c r="BV17" s="23"/>
+      <c r="BW17" s="23"/>
+      <c r="BX17" s="23"/>
+      <c r="BY17" s="23"/>
+      <c r="BZ17" s="23"/>
+      <c r="CA17" s="23"/>
+      <c r="CB17" s="23"/>
+      <c r="CC17" s="23"/>
+      <c r="CD17" s="23"/>
+      <c r="CE17" s="23"/>
+      <c r="CF17" s="23"/>
+      <c r="CG17" s="23"/>
+      <c r="CH17" s="23"/>
+      <c r="CI17" s="23"/>
+      <c r="CJ17" s="23"/>
+      <c r="CK17" s="23"/>
+      <c r="CL17" s="23"/>
+      <c r="CM17" s="23"/>
+      <c r="CN17" s="23"/>
+      <c r="CO17" s="23"/>
+      <c r="CP17" s="23"/>
+      <c r="CQ17" s="23"/>
+      <c r="CR17" s="23"/>
+      <c r="CS17" s="23"/>
+      <c r="CT17" s="23"/>
+      <c r="CU17" s="23"/>
+      <c r="CV17" s="23"/>
+      <c r="CW17" s="23"/>
+      <c r="CX17" s="23"/>
+      <c r="CY17" s="23"/>
+      <c r="CZ17" s="23"/>
+      <c r="DA17" s="23"/>
+      <c r="DB17" s="23"/>
+      <c r="DC17" s="23"/>
+      <c r="DD17" s="23"/>
+      <c r="DE17" s="23"/>
+      <c r="DF17" s="23"/>
+      <c r="DG17" s="23"/>
+      <c r="DH17" s="23"/>
+      <c r="DI17" s="23"/>
+      <c r="DJ17" s="23"/>
+      <c r="DK17" s="23"/>
+      <c r="DL17" s="23"/>
+      <c r="DM17" s="23"/>
+      <c r="DN17" s="23"/>
+      <c r="DO17" s="23"/>
+      <c r="DP17" s="23"/>
+      <c r="DQ17" s="23"/>
+      <c r="DR17" s="23"/>
+      <c r="DS17" s="23"/>
+      <c r="DT17" s="23"/>
+      <c r="DU17" s="23"/>
+      <c r="DV17" s="23"/>
+      <c r="DW17" s="23"/>
+      <c r="DX17" s="23"/>
+      <c r="DY17" s="23"/>
+      <c r="DZ17" s="23"/>
+      <c r="EA17" s="23"/>
+      <c r="EB17" s="23"/>
+      <c r="EC17" s="23"/>
+      <c r="ED17" s="23"/>
+      <c r="EE17" s="23"/>
+      <c r="EF17" s="23"/>
+      <c r="EG17" s="23"/>
+      <c r="EH17" s="23"/>
+      <c r="EI17" s="23"/>
+      <c r="EJ17" s="23"/>
+      <c r="EK17" s="23"/>
+      <c r="EL17" s="23"/>
+      <c r="EM17" s="23"/>
+      <c r="EN17" s="23"/>
+      <c r="EO17" s="24"/>
     </row>
-    <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <v>8</v>
       </c>
@@ -4773,7 +4763,7 @@
       <c r="EN18" s="11"/>
       <c r="EO18" s="11"/>
     </row>
-    <row r="19" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
         <v>9</v>
       </c>
@@ -4973,7 +4963,7 @@
       <c r="EN19" s="11"/>
       <c r="EO19" s="11"/>
     </row>
-    <row r="20" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
         <v>10</v>
       </c>
@@ -5143,7 +5133,7 @@
       <c r="EN20" s="11"/>
       <c r="EO20" s="11"/>
     </row>
-    <row r="21" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
         <v>11</v>
       </c>
@@ -5427,7 +5417,7 @@
       <c r="EN21" s="11"/>
       <c r="EO21" s="11"/>
     </row>
-    <row r="22" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
         <v>12</v>
       </c>
@@ -5643,7 +5633,7 @@
       <c r="EN22" s="11"/>
       <c r="EO22" s="11"/>
     </row>
-    <row r="23" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12">
         <v>13</v>
       </c>
@@ -5931,7 +5921,7 @@
       <c r="EN23" s="11"/>
       <c r="EO23" s="11"/>
     </row>
-    <row r="24" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12">
         <v>14</v>
       </c>
@@ -6141,7 +6131,7 @@
       <c r="EN24" s="11"/>
       <c r="EO24" s="11"/>
     </row>
-    <row r="25" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12">
         <v>15</v>
       </c>
@@ -6367,7 +6357,7 @@
       <c r="EN25" s="11"/>
       <c r="EO25" s="11"/>
     </row>
-    <row r="26" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12">
         <v>16</v>
       </c>
@@ -6583,7 +6573,7 @@
       <c r="EN26" s="11"/>
       <c r="EO26" s="11"/>
     </row>
-    <row r="27" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
         <v>17</v>
       </c>
@@ -6869,7 +6859,7 @@
       <c r="EN27" s="11"/>
       <c r="EO27" s="11"/>
     </row>
-    <row r="28" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <v>18</v>
       </c>
@@ -6883,149 +6873,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29"/>
-      <c r="Y28" s="29"/>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-      <c r="AG28" s="29"/>
-      <c r="AH28" s="29"/>
-      <c r="AI28" s="29"/>
-      <c r="AJ28" s="29"/>
-      <c r="AK28" s="29"/>
-      <c r="AL28" s="29"/>
-      <c r="AM28" s="29"/>
-      <c r="AN28" s="29"/>
-      <c r="AO28" s="29"/>
-      <c r="AP28" s="29"/>
-      <c r="AQ28" s="29"/>
-      <c r="AR28" s="29"/>
-      <c r="AS28" s="29"/>
-      <c r="AT28" s="29"/>
-      <c r="AU28" s="29"/>
-      <c r="AV28" s="29"/>
-      <c r="AW28" s="29"/>
-      <c r="AX28" s="29"/>
-      <c r="AY28" s="29"/>
-      <c r="AZ28" s="29"/>
-      <c r="BA28" s="29"/>
-      <c r="BB28" s="29"/>
-      <c r="BC28" s="29"/>
-      <c r="BD28" s="29"/>
-      <c r="BE28" s="29"/>
-      <c r="BF28" s="29"/>
-      <c r="BG28" s="29"/>
-      <c r="BH28" s="29"/>
-      <c r="BI28" s="29"/>
-      <c r="BJ28" s="29"/>
-      <c r="BK28" s="29"/>
-      <c r="BL28" s="29"/>
-      <c r="BM28" s="29"/>
-      <c r="BN28" s="29"/>
-      <c r="BO28" s="29"/>
-      <c r="BP28" s="29"/>
-      <c r="BQ28" s="29"/>
-      <c r="BR28" s="29"/>
-      <c r="BS28" s="29"/>
-      <c r="BT28" s="29"/>
-      <c r="BU28" s="29"/>
-      <c r="BV28" s="29"/>
-      <c r="BW28" s="29"/>
-      <c r="BX28" s="29"/>
-      <c r="BY28" s="29"/>
-      <c r="BZ28" s="29"/>
-      <c r="CA28" s="29"/>
-      <c r="CB28" s="29"/>
-      <c r="CC28" s="29"/>
-      <c r="CD28" s="29"/>
-      <c r="CE28" s="29"/>
-      <c r="CF28" s="29"/>
-      <c r="CG28" s="29"/>
-      <c r="CH28" s="29"/>
-      <c r="CI28" s="29"/>
-      <c r="CJ28" s="29"/>
-      <c r="CK28" s="29"/>
-      <c r="CL28" s="29"/>
-      <c r="CM28" s="29"/>
-      <c r="CN28" s="29"/>
-      <c r="CO28" s="29"/>
-      <c r="CP28" s="29"/>
-      <c r="CQ28" s="29"/>
-      <c r="CR28" s="29"/>
-      <c r="CS28" s="29"/>
-      <c r="CT28" s="29"/>
-      <c r="CU28" s="29"/>
-      <c r="CV28" s="29"/>
-      <c r="CW28" s="29"/>
-      <c r="CX28" s="29"/>
-      <c r="CY28" s="29"/>
-      <c r="CZ28" s="29"/>
-      <c r="DA28" s="29"/>
-      <c r="DB28" s="29"/>
-      <c r="DC28" s="29"/>
-      <c r="DD28" s="29"/>
-      <c r="DE28" s="29"/>
-      <c r="DF28" s="29"/>
-      <c r="DG28" s="29"/>
-      <c r="DH28" s="29"/>
-      <c r="DI28" s="29"/>
-      <c r="DJ28" s="29"/>
-      <c r="DK28" s="29"/>
-      <c r="DL28" s="29"/>
-      <c r="DM28" s="29"/>
-      <c r="DN28" s="29"/>
-      <c r="DO28" s="29"/>
-      <c r="DP28" s="29"/>
-      <c r="DQ28" s="29"/>
-      <c r="DR28" s="29"/>
-      <c r="DS28" s="29"/>
-      <c r="DT28" s="29"/>
-      <c r="DU28" s="29"/>
-      <c r="DV28" s="29"/>
-      <c r="DW28" s="29"/>
-      <c r="DX28" s="29"/>
-      <c r="DY28" s="29"/>
-      <c r="DZ28" s="29"/>
-      <c r="EA28" s="29"/>
-      <c r="EB28" s="29"/>
-      <c r="EC28" s="29"/>
-      <c r="ED28" s="29"/>
-      <c r="EE28" s="29"/>
-      <c r="EF28" s="29"/>
-      <c r="EG28" s="29"/>
-      <c r="EH28" s="29"/>
-      <c r="EI28" s="29"/>
-      <c r="EJ28" s="29"/>
-      <c r="EK28" s="29"/>
-      <c r="EL28" s="29"/>
-      <c r="EM28" s="29"/>
-      <c r="EN28" s="29"/>
-      <c r="EO28" s="29"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
+      <c r="S28" s="64"/>
+      <c r="T28" s="64"/>
+      <c r="U28" s="64"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="64"/>
+      <c r="AA28" s="64"/>
+      <c r="AB28" s="64"/>
+      <c r="AC28" s="64"/>
+      <c r="AD28" s="64"/>
+      <c r="AE28" s="64"/>
+      <c r="AF28" s="64"/>
+      <c r="AG28" s="64"/>
+      <c r="AH28" s="64"/>
+      <c r="AI28" s="64"/>
+      <c r="AJ28" s="64"/>
+      <c r="AK28" s="64"/>
+      <c r="AL28" s="64"/>
+      <c r="AM28" s="64"/>
+      <c r="AN28" s="64"/>
+      <c r="AO28" s="64"/>
+      <c r="AP28" s="64"/>
+      <c r="AQ28" s="64"/>
+      <c r="AR28" s="64"/>
+      <c r="AS28" s="64"/>
+      <c r="AT28" s="64"/>
+      <c r="AU28" s="64"/>
+      <c r="AV28" s="64"/>
+      <c r="AW28" s="64"/>
+      <c r="AX28" s="64"/>
+      <c r="AY28" s="64"/>
+      <c r="AZ28" s="64"/>
+      <c r="BA28" s="64"/>
+      <c r="BB28" s="64"/>
+      <c r="BC28" s="64"/>
+      <c r="BD28" s="64"/>
+      <c r="BE28" s="64"/>
+      <c r="BF28" s="64"/>
+      <c r="BG28" s="64"/>
+      <c r="BH28" s="64"/>
+      <c r="BI28" s="64"/>
+      <c r="BJ28" s="64"/>
+      <c r="BK28" s="64"/>
+      <c r="BL28" s="64"/>
+      <c r="BM28" s="64"/>
+      <c r="BN28" s="64"/>
+      <c r="BO28" s="64"/>
+      <c r="BP28" s="64"/>
+      <c r="BQ28" s="64"/>
+      <c r="BR28" s="64"/>
+      <c r="BS28" s="64"/>
+      <c r="BT28" s="64"/>
+      <c r="BU28" s="64"/>
+      <c r="BV28" s="64"/>
+      <c r="BW28" s="64"/>
+      <c r="BX28" s="64"/>
+      <c r="BY28" s="64"/>
+      <c r="BZ28" s="64"/>
+      <c r="CA28" s="64"/>
+      <c r="CB28" s="64"/>
+      <c r="CC28" s="64"/>
+      <c r="CD28" s="64"/>
+      <c r="CE28" s="64"/>
+      <c r="CF28" s="64"/>
+      <c r="CG28" s="64"/>
+      <c r="CH28" s="64"/>
+      <c r="CI28" s="64"/>
+      <c r="CJ28" s="64"/>
+      <c r="CK28" s="64"/>
+      <c r="CL28" s="64"/>
+      <c r="CM28" s="64"/>
+      <c r="CN28" s="64"/>
+      <c r="CO28" s="64"/>
+      <c r="CP28" s="64"/>
+      <c r="CQ28" s="64"/>
+      <c r="CR28" s="64"/>
+      <c r="CS28" s="64"/>
+      <c r="CT28" s="64"/>
+      <c r="CU28" s="64"/>
+      <c r="CV28" s="64"/>
+      <c r="CW28" s="64"/>
+      <c r="CX28" s="64"/>
+      <c r="CY28" s="64"/>
+      <c r="CZ28" s="64"/>
+      <c r="DA28" s="64"/>
+      <c r="DB28" s="64"/>
+      <c r="DC28" s="64"/>
+      <c r="DD28" s="64"/>
+      <c r="DE28" s="64"/>
+      <c r="DF28" s="64"/>
+      <c r="DG28" s="64"/>
+      <c r="DH28" s="64"/>
+      <c r="DI28" s="64"/>
+      <c r="DJ28" s="64"/>
+      <c r="DK28" s="64"/>
+      <c r="DL28" s="64"/>
+      <c r="DM28" s="64"/>
+      <c r="DN28" s="64"/>
+      <c r="DO28" s="64"/>
+      <c r="DP28" s="64"/>
+      <c r="DQ28" s="64"/>
+      <c r="DR28" s="64"/>
+      <c r="DS28" s="64"/>
+      <c r="DT28" s="64"/>
+      <c r="DU28" s="64"/>
+      <c r="DV28" s="64"/>
+      <c r="DW28" s="64"/>
+      <c r="DX28" s="64"/>
+      <c r="DY28" s="64"/>
+      <c r="DZ28" s="64"/>
+      <c r="EA28" s="64"/>
+      <c r="EB28" s="64"/>
+      <c r="EC28" s="64"/>
+      <c r="ED28" s="64"/>
+      <c r="EE28" s="64"/>
+      <c r="EF28" s="64"/>
+      <c r="EG28" s="64"/>
+      <c r="EH28" s="64"/>
+      <c r="EI28" s="64"/>
+      <c r="EJ28" s="64"/>
+      <c r="EK28" s="64"/>
+      <c r="EL28" s="64"/>
+      <c r="EM28" s="64"/>
+      <c r="EN28" s="64"/>
+      <c r="EO28" s="64"/>
     </row>
     <row r="31" spans="1:145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="CN31" s="1" t="s">
@@ -7034,6 +7024,300 @@
     </row>
   </sheetData>
   <mergeCells count="318">
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BQ1:BU1"/>
+    <mergeCell ref="BV1:BX1"/>
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="DV8:DV9"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="E28:EO28"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AY1:BC1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="AO17:EO17"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D2"/>
@@ -7058,300 +7342,6 @@
     <mergeCell ref="Q2:Q7"/>
     <mergeCell ref="R2:R7"/>
     <mergeCell ref="BM1:BO1"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="BH1:BL1"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="E28:EO28"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AY1:BC1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BQ1:BU1"/>
-    <mergeCell ref="BV1:BX1"/>
-    <mergeCell ref="EH8:EH9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="DV8:DV9"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DY8:DY9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>
